--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/Stocks/Data/Stocks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F44AB4-1BC6-A945-BDAB-EFFD8EA96E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65A1C60-8D92-ED43-BFFF-B7FDC4A62566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2459,28 +2459,19 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
+      <sheetName val="1. List_AutomaticData"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="4">
           <cell r="C4">
-            <v>102.61</v>
-          </cell>
-          <cell r="F4">
-            <v>0.84350000000000003</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="C10">
-            <v>42.82</v>
+            <v>100.51</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2974,7 +2965,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$4</f>
-        <v>102.61</v>
+        <v>100.51</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -3000,7 +2991,7 @@
       </c>
       <c r="C11" s="95">
         <f>$C$3/'Statement Q'!$N$22</f>
-        <v>12.078116004572928</v>
+        <v>11.830927196370968</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -3009,7 +3000,7 @@
       </c>
       <c r="C12" s="95">
         <f>C3/Statements!S20</f>
-        <v>30.055581751527924</v>
+        <v>29.440468978131488</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -3018,7 +3009,7 @@
       </c>
       <c r="C13" s="103">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$20)</f>
-        <v>4.819948075233536</v>
+        <v>4.7213037817144787</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -3027,7 +3018,7 @@
       </c>
       <c r="C15" s="20">
         <f>C3*'Statement Q'!J116</f>
-        <v>4863714</v>
+        <v>4764174</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -3054,7 +3045,7 @@
       </c>
       <c r="C18" s="20">
         <f>C15+C17-C16</f>
-        <v>3817026</v>
+        <v>3717486</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -12321,7 +12312,7 @@
       </c>
       <c r="C6" s="190">
         <f>Overview!C3</f>
-        <v>102.61</v>
+        <v>100.51</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12330,7 +12321,7 @@
       </c>
       <c r="C7" s="192">
         <f>C5*C6</f>
-        <v>4863714</v>
+        <v>4764174</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12347,7 +12338,6 @@
         <v>353</v>
       </c>
       <c r="C9" s="215">
-        <f>[1]Sheet1!$C$10/1000</f>
         <v>4.2819999999999997E-2</v>
       </c>
     </row>
@@ -12356,7 +12346,6 @@
         <v>354</v>
       </c>
       <c r="C10" s="190">
-        <f>[1]Sheet1!$F$4</f>
         <v>0.84350000000000003</v>
       </c>
     </row>
@@ -12397,7 +12386,7 @@
       </c>
       <c r="C16" s="193">
         <f>C8/(C8+C7)</f>
-        <v>1.8916617734003861E-2</v>
+        <v>1.9304221345904336E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12406,7 +12395,7 @@
       </c>
       <c r="C17" s="193">
         <f>C7/(C8+C7)</f>
-        <v>0.98108338226599612</v>
+        <v>0.98069577865409563</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12433,7 +12422,7 @@
       </c>
       <c r="C20" s="193">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>8.8557540485886724E-2</v>
+        <v>8.8544120292230077E-2</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -12707,7 +12696,7 @@
       </c>
       <c r="L8" s="167">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>11084999.913049465</v>
+        <v>11087170.235534936</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="7"/>
@@ -12761,23 +12750,23 @@
       <c r="G10" s="195"/>
       <c r="H10" s="167">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>104016.56206188875</v>
+        <v>104017.84443747677</v>
       </c>
       <c r="I10" s="167">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$15)^I9</f>
-        <v>185086.65614710536</v>
+        <v>185091.2198832625</v>
       </c>
       <c r="J10" s="167">
         <f t="shared" ca="1" si="1"/>
-        <v>219009.34617548957</v>
+        <v>219017.44649228649</v>
       </c>
       <c r="K10" s="167">
         <f t="shared" ca="1" si="1"/>
-        <v>320201.21048894653</v>
+        <v>320217.00127460668</v>
       </c>
       <c r="L10" s="167">
         <f t="shared" ca="1" si="1"/>
-        <v>487454.17951931816</v>
+        <v>487484.22832794365</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -12796,7 +12785,7 @@
       <c r="K11" s="160"/>
       <c r="L11" s="167">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>7252349.7719708746</v>
+        <v>7254216.85732638</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -12819,7 +12808,7 @@
       </c>
       <c r="C15" s="194">
         <f>WACC!C20</f>
-        <v>8.8557540485886724E-2</v>
+        <v>8.8544120292230077E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -12834,7 +12823,7 @@
       </c>
       <c r="C19" s="109">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1315767.9543927484</v>
+        <v>1315827.7404155761</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -12843,7 +12832,7 @@
       </c>
       <c r="C20" s="109">
         <f ca="1">L11</f>
-        <v>7252349.7719708746</v>
+        <v>7254216.85732638</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -12852,7 +12841,7 @@
       </c>
       <c r="C21" s="114">
         <f ca="1">C19+C20</f>
-        <v>8568117.7263636235</v>
+        <v>8570044.5977419559</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -12879,7 +12868,7 @@
       </c>
       <c r="C24" s="114">
         <f ca="1">C21+C22-C23</f>
-        <v>9614805.7263636235</v>
+        <v>9616732.5977419559</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -12897,7 +12886,7 @@
       </c>
       <c r="C26" s="197">
         <f ca="1">C24/C25</f>
-        <v>197.2706531385997</v>
+        <v>197.31018749697736</v>
       </c>
     </row>
   </sheetData>
@@ -13444,7 +13433,7 @@
       </c>
       <c r="C22" s="175">
         <f>WACC!C20</f>
-        <v>8.8557540485886724E-2</v>
+        <v>8.8544120292230077E-2</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -13470,7 +13459,7 @@
       </c>
       <c r="C25" s="20">
         <f ca="1">C21/(1+C22)^5</f>
-        <v>375698.48056071467</v>
+        <v>375721.64025903627</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
@@ -13479,7 +13468,7 @@
       </c>
       <c r="C26" s="197">
         <f ca="1">C25/C24*C23</f>
-        <v>170.99355027676998</v>
+        <v>171.00409106744192</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -13503,7 +13492,7 @@
       </c>
       <c r="C30" s="175">
         <f>WACC!C20</f>
-        <v>8.8557540485886724E-2</v>
+        <v>8.8544120292230077E-2</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
@@ -13529,7 +13518,7 @@
       </c>
       <c r="C33" s="20">
         <f>C29/(1+C30)^5</f>
-        <v>2501757.7373538148</v>
+        <v>2501911.956647926</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.2">
@@ -13538,7 +13527,7 @@
       </c>
       <c r="C34" s="197">
         <f>C33/C32*C31</f>
-        <v>159.40927190487432</v>
+        <v>159.41909858993694</v>
       </c>
     </row>
   </sheetData>
@@ -13596,7 +13585,7 @@
       </c>
       <c r="C5" s="212">
         <f ca="1">DCF!C26</f>
-        <v>197.2706531385997</v>
+        <v>197.31018749697736</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -13605,7 +13594,7 @@
       </c>
       <c r="C6" s="212">
         <f ca="1">'PE and PS'!C26</f>
-        <v>170.99355027676998</v>
+        <v>171.00409106744192</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -13614,7 +13603,7 @@
       </c>
       <c r="C7" s="212">
         <f>'PE and PS'!C34</f>
-        <v>159.40927190487432</v>
+        <v>159.41909858993694</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -13623,7 +13612,7 @@
       </c>
       <c r="C8" s="197">
         <f ca="1">AVERAGE(C5:C7)</f>
-        <v>175.89115844008134</v>
+        <v>175.91112571811877</v>
       </c>
     </row>
   </sheetData>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65A1C60-8D92-ED43-BFFF-B7FDC4A62566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB423C4-F656-F241-882F-3123936020DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="20" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2459,6 +2459,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
       <sheetName val="1. List_AutomaticData"/>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB423C4-F656-F241-882F-3123936020DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FF7FED-536C-5444-8ED8-3767D25F69A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="20" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2403,6 +2403,18 @@
     <xf numFmtId="165" fontId="24" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="18" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2412,22 +2424,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3267,20 +3267,20 @@
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
-      <c r="C5" s="226" t="s">
+      <c r="C5" s="223" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="226"/>
-      <c r="E5" s="226"/>
-      <c r="F5" s="226"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="230" t="s">
+      <c r="D5" s="223"/>
+      <c r="E5" s="223"/>
+      <c r="F5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="I5" s="226"/>
-      <c r="J5" s="226"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="226"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="223"/>
+      <c r="K5" s="223"/>
+      <c r="L5" s="223"/>
       <c r="P5" s="231"/>
       <c r="Q5" s="231"/>
       <c r="R5" s="231"/>
@@ -3298,18 +3298,18 @@
     <row r="7" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="110"/>
       <c r="B7" s="94"/>
-      <c r="C7" s="225" t="s">
+      <c r="C7" s="222" t="s">
         <v>188</v>
       </c>
-      <c r="D7" s="225"/>
-      <c r="E7" s="225"/>
-      <c r="F7" s="225"/>
-      <c r="G7" s="225"/>
-      <c r="H7" s="225"/>
-      <c r="I7" s="225"/>
-      <c r="J7" s="225"/>
-      <c r="K7" s="225"/>
-      <c r="L7" s="225"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="222"/>
+      <c r="F7" s="222"/>
+      <c r="G7" s="222"/>
+      <c r="H7" s="222"/>
+      <c r="I7" s="222"/>
+      <c r="J7" s="222"/>
+      <c r="K7" s="222"/>
+      <c r="L7" s="222"/>
       <c r="P7" s="231"/>
       <c r="Q7" s="231"/>
       <c r="R7" s="231"/>
@@ -3447,18 +3447,18 @@
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C12" s="225" t="s">
+      <c r="C12" s="222" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="225"/>
-      <c r="E12" s="225"/>
-      <c r="F12" s="225"/>
-      <c r="G12" s="225"/>
-      <c r="H12" s="225"/>
-      <c r="I12" s="225"/>
-      <c r="J12" s="225"/>
-      <c r="K12" s="225"/>
-      <c r="L12" s="225"/>
+      <c r="D12" s="222"/>
+      <c r="E12" s="222"/>
+      <c r="F12" s="222"/>
+      <c r="G12" s="222"/>
+      <c r="H12" s="222"/>
+      <c r="I12" s="222"/>
+      <c r="J12" s="222"/>
+      <c r="K12" s="222"/>
+      <c r="L12" s="222"/>
       <c r="N12" s="93"/>
       <c r="P12" s="231"/>
       <c r="Q12" s="231"/>
@@ -3772,18 +3772,18 @@
       <c r="D18" s="20"/>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C20" s="225" t="s">
+      <c r="C20" s="222" t="s">
         <v>237</v>
       </c>
-      <c r="D20" s="225"/>
-      <c r="E20" s="225"/>
-      <c r="F20" s="225"/>
-      <c r="G20" s="225"/>
-      <c r="H20" s="225"/>
-      <c r="I20" s="225"/>
-      <c r="J20" s="225"/>
-      <c r="K20" s="225"/>
-      <c r="L20" s="225"/>
+      <c r="D20" s="222"/>
+      <c r="E20" s="222"/>
+      <c r="F20" s="222"/>
+      <c r="G20" s="222"/>
+      <c r="H20" s="222"/>
+      <c r="I20" s="222"/>
+      <c r="J20" s="222"/>
+      <c r="K20" s="222"/>
+      <c r="L20" s="222"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
@@ -4008,10 +4008,10 @@
       <c r="C27" s="231"/>
     </row>
     <row r="28" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B28" s="226" t="s">
+      <c r="B28" s="223" t="s">
         <v>260</v>
       </c>
-      <c r="C28" s="226"/>
+      <c r="C28" s="223"/>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
@@ -4022,18 +4022,18 @@
       </c>
     </row>
     <row r="31" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C31" s="225" t="s">
+      <c r="C31" s="222" t="s">
         <v>261</v>
       </c>
-      <c r="D31" s="225"/>
-      <c r="E31" s="225"/>
-      <c r="F31" s="225"/>
-      <c r="G31" s="225"/>
-      <c r="H31" s="225"/>
-      <c r="I31" s="225"/>
-      <c r="J31" s="225"/>
-      <c r="K31" s="225"/>
-      <c r="L31" s="225"/>
+      <c r="D31" s="222"/>
+      <c r="E31" s="222"/>
+      <c r="F31" s="222"/>
+      <c r="G31" s="222"/>
+      <c r="H31" s="222"/>
+      <c r="I31" s="222"/>
+      <c r="J31" s="222"/>
+      <c r="K31" s="222"/>
+      <c r="L31" s="222"/>
     </row>
     <row r="32" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
@@ -4240,18 +4240,18 @@
       <c r="C40" s="231"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C41" s="225" t="s">
+      <c r="C41" s="222" t="s">
         <v>262</v>
       </c>
-      <c r="D41" s="225"/>
-      <c r="E41" s="225"/>
-      <c r="F41" s="225"/>
-      <c r="G41" s="225"/>
-      <c r="H41" s="225"/>
-      <c r="I41" s="225"/>
-      <c r="J41" s="225"/>
-      <c r="K41" s="225"/>
-      <c r="L41" s="225"/>
+      <c r="D41" s="222"/>
+      <c r="E41" s="222"/>
+      <c r="F41" s="222"/>
+      <c r="G41" s="222"/>
+      <c r="H41" s="222"/>
+      <c r="I41" s="222"/>
+      <c r="J41" s="222"/>
+      <c r="K41" s="222"/>
+      <c r="L41" s="222"/>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B42" s="7" t="s">
@@ -4328,11 +4328,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C41:L41"/>
-    <mergeCell ref="C12:L12"/>
     <mergeCell ref="P12:Z12"/>
     <mergeCell ref="C20:L20"/>
     <mergeCell ref="B27:C27"/>
@@ -4342,6 +4337,11 @@
     <mergeCell ref="X5:Z5"/>
     <mergeCell ref="C7:L7"/>
     <mergeCell ref="P7:Z7"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C41:L41"/>
+    <mergeCell ref="C12:L12"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{4B588CCE-B4FF-384B-9E03-C176DEB70053}">
@@ -4386,20 +4386,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="105"/>
-      <c r="C3" s="226" t="s">
+      <c r="C3" s="223" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="226"/>
-      <c r="E3" s="226"/>
-      <c r="F3" s="226"/>
-      <c r="G3" s="229"/>
-      <c r="H3" s="230" t="s">
+      <c r="D3" s="223"/>
+      <c r="E3" s="223"/>
+      <c r="F3" s="223"/>
+      <c r="G3" s="224"/>
+      <c r="H3" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="226"/>
-      <c r="J3" s="226"/>
-      <c r="K3" s="226"/>
-      <c r="L3" s="226"/>
+      <c r="I3" s="223"/>
+      <c r="J3" s="223"/>
+      <c r="K3" s="223"/>
+      <c r="L3" s="223"/>
       <c r="P3" s="231"/>
       <c r="Q3" s="231"/>
       <c r="R3" s="231"/>
@@ -4417,18 +4417,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="110"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="225" t="s">
+      <c r="C5" s="222" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="225"/>
-      <c r="E5" s="225"/>
-      <c r="F5" s="225"/>
-      <c r="G5" s="225"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="225"/>
-      <c r="K5" s="225"/>
-      <c r="L5" s="225"/>
+      <c r="D5" s="222"/>
+      <c r="E5" s="222"/>
+      <c r="F5" s="222"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="222"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="222"/>
+      <c r="L5" s="222"/>
       <c r="P5" s="231"/>
       <c r="Q5" s="231"/>
       <c r="R5" s="231"/>
@@ -4684,18 +4684,18 @@
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C12" s="225" t="s">
+      <c r="C12" s="222" t="s">
         <v>248</v>
       </c>
-      <c r="D12" s="225"/>
-      <c r="E12" s="225"/>
-      <c r="F12" s="225"/>
-      <c r="G12" s="225"/>
-      <c r="H12" s="225"/>
-      <c r="I12" s="225"/>
-      <c r="J12" s="225"/>
-      <c r="K12" s="225"/>
-      <c r="L12" s="225"/>
+      <c r="D12" s="222"/>
+      <c r="E12" s="222"/>
+      <c r="F12" s="222"/>
+      <c r="G12" s="222"/>
+      <c r="H12" s="222"/>
+      <c r="I12" s="222"/>
+      <c r="J12" s="222"/>
+      <c r="K12" s="222"/>
+      <c r="L12" s="222"/>
       <c r="N12" s="93"/>
       <c r="P12" s="231"/>
       <c r="Q12" s="231"/>
@@ -4948,18 +4948,18 @@
       <c r="D17" s="20"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C19" s="225" t="s">
+      <c r="C19" s="222" t="s">
         <v>267</v>
       </c>
-      <c r="D19" s="225"/>
-      <c r="E19" s="225"/>
-      <c r="F19" s="225"/>
-      <c r="G19" s="225"/>
-      <c r="H19" s="225"/>
-      <c r="I19" s="225"/>
-      <c r="J19" s="225"/>
-      <c r="K19" s="225"/>
-      <c r="L19" s="225"/>
+      <c r="D19" s="222"/>
+      <c r="E19" s="222"/>
+      <c r="F19" s="222"/>
+      <c r="G19" s="222"/>
+      <c r="H19" s="222"/>
+      <c r="I19" s="222"/>
+      <c r="J19" s="222"/>
+      <c r="K19" s="222"/>
+      <c r="L19" s="222"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="7" t="s">
@@ -5146,18 +5146,18 @@
       <c r="C25" s="231"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C26" s="225" t="s">
+      <c r="C26" s="222" t="s">
         <v>278</v>
       </c>
-      <c r="D26" s="225"/>
-      <c r="E26" s="225"/>
-      <c r="F26" s="225"/>
-      <c r="G26" s="225"/>
-      <c r="H26" s="225"/>
-      <c r="I26" s="225"/>
-      <c r="J26" s="225"/>
-      <c r="K26" s="225"/>
-      <c r="L26" s="225"/>
+      <c r="D26" s="222"/>
+      <c r="E26" s="222"/>
+      <c r="F26" s="222"/>
+      <c r="G26" s="222"/>
+      <c r="H26" s="222"/>
+      <c r="I26" s="222"/>
+      <c r="J26" s="222"/>
+      <c r="K26" s="222"/>
+      <c r="L26" s="222"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -5401,18 +5401,18 @@
       <c r="G33" s="146"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C34" s="225" t="s">
+      <c r="C34" s="222" t="s">
         <v>279</v>
       </c>
-      <c r="D34" s="225"/>
-      <c r="E34" s="225"/>
-      <c r="F34" s="225"/>
-      <c r="G34" s="225"/>
-      <c r="H34" s="225"/>
-      <c r="I34" s="225"/>
-      <c r="J34" s="225"/>
-      <c r="K34" s="225"/>
-      <c r="L34" s="225"/>
+      <c r="D34" s="222"/>
+      <c r="E34" s="222"/>
+      <c r="F34" s="222"/>
+      <c r="G34" s="222"/>
+      <c r="H34" s="222"/>
+      <c r="I34" s="222"/>
+      <c r="J34" s="222"/>
+      <c r="K34" s="222"/>
+      <c r="L34" s="222"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35" s="7" t="s">
@@ -5634,6 +5634,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="C12:L12"/>
     <mergeCell ref="P12:Z12"/>
@@ -5641,12 +5647,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C34:L34"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5685,20 +5685,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="105"/>
-      <c r="C3" s="226" t="s">
+      <c r="C3" s="223" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="226"/>
-      <c r="E3" s="226"/>
-      <c r="F3" s="226"/>
-      <c r="G3" s="229"/>
-      <c r="H3" s="230" t="s">
+      <c r="D3" s="223"/>
+      <c r="E3" s="223"/>
+      <c r="F3" s="223"/>
+      <c r="G3" s="224"/>
+      <c r="H3" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="226"/>
-      <c r="J3" s="226"/>
-      <c r="K3" s="226"/>
-      <c r="L3" s="226"/>
+      <c r="I3" s="223"/>
+      <c r="J3" s="223"/>
+      <c r="K3" s="223"/>
+      <c r="L3" s="223"/>
       <c r="P3" s="231"/>
       <c r="Q3" s="231"/>
       <c r="R3" s="231"/>
@@ -5716,18 +5716,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="110"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="225" t="s">
+      <c r="C5" s="222" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="225"/>
-      <c r="E5" s="225"/>
-      <c r="F5" s="225"/>
-      <c r="G5" s="225"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="225"/>
-      <c r="K5" s="225"/>
-      <c r="L5" s="225"/>
+      <c r="D5" s="222"/>
+      <c r="E5" s="222"/>
+      <c r="F5" s="222"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="222"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="222"/>
+      <c r="L5" s="222"/>
       <c r="P5" s="231"/>
       <c r="Q5" s="231"/>
       <c r="R5" s="231"/>
@@ -6043,18 +6043,18 @@
       <c r="C12" s="231"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C13" s="225" t="s">
+      <c r="C13" s="222" t="s">
         <v>300</v>
       </c>
-      <c r="D13" s="225"/>
-      <c r="E13" s="225"/>
-      <c r="F13" s="225"/>
-      <c r="G13" s="225"/>
-      <c r="H13" s="225"/>
-      <c r="I13" s="225"/>
-      <c r="J13" s="225"/>
-      <c r="K13" s="225"/>
-      <c r="L13" s="225"/>
+      <c r="D13" s="222"/>
+      <c r="E13" s="222"/>
+      <c r="F13" s="222"/>
+      <c r="G13" s="222"/>
+      <c r="H13" s="222"/>
+      <c r="I13" s="222"/>
+      <c r="J13" s="222"/>
+      <c r="K13" s="222"/>
+      <c r="L13" s="222"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
@@ -6298,18 +6298,18 @@
       <c r="G20" s="146"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C21" s="225" t="s">
+      <c r="C21" s="222" t="s">
         <v>279</v>
       </c>
-      <c r="D21" s="225"/>
-      <c r="E21" s="225"/>
-      <c r="F21" s="225"/>
-      <c r="G21" s="225"/>
-      <c r="H21" s="225"/>
-      <c r="I21" s="225"/>
-      <c r="J21" s="225"/>
-      <c r="K21" s="225"/>
-      <c r="L21" s="225"/>
+      <c r="D21" s="222"/>
+      <c r="E21" s="222"/>
+      <c r="F21" s="222"/>
+      <c r="G21" s="222"/>
+      <c r="H21" s="222"/>
+      <c r="I21" s="222"/>
+      <c r="J21" s="222"/>
+      <c r="K21" s="222"/>
+      <c r="L21" s="222"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
@@ -6598,20 +6598,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="105"/>
-      <c r="C3" s="226" t="s">
+      <c r="C3" s="223" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="226"/>
-      <c r="E3" s="226"/>
-      <c r="F3" s="226"/>
-      <c r="G3" s="229"/>
-      <c r="H3" s="230" t="s">
+      <c r="D3" s="223"/>
+      <c r="E3" s="223"/>
+      <c r="F3" s="223"/>
+      <c r="G3" s="224"/>
+      <c r="H3" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="226"/>
-      <c r="J3" s="226"/>
-      <c r="K3" s="226"/>
-      <c r="L3" s="226"/>
+      <c r="I3" s="223"/>
+      <c r="J3" s="223"/>
+      <c r="K3" s="223"/>
+      <c r="L3" s="223"/>
       <c r="P3" s="231"/>
       <c r="Q3" s="231"/>
       <c r="R3" s="231"/>
@@ -6629,18 +6629,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="110"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="225" t="s">
+      <c r="C5" s="222" t="s">
         <v>312</v>
       </c>
-      <c r="D5" s="225"/>
-      <c r="E5" s="225"/>
-      <c r="F5" s="225"/>
-      <c r="G5" s="225"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="225"/>
-      <c r="K5" s="225"/>
-      <c r="L5" s="225"/>
+      <c r="D5" s="222"/>
+      <c r="E5" s="222"/>
+      <c r="F5" s="222"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="222"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="222"/>
+      <c r="L5" s="222"/>
       <c r="P5" s="231"/>
       <c r="Q5" s="231"/>
       <c r="R5" s="231"/>
@@ -6837,18 +6837,18 @@
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B11" s="148"/>
-      <c r="C11" s="225" t="s">
+      <c r="C11" s="222" t="s">
         <v>312</v>
       </c>
-      <c r="D11" s="225"/>
-      <c r="E11" s="225"/>
-      <c r="F11" s="225"/>
-      <c r="G11" s="225"/>
-      <c r="H11" s="225"/>
-      <c r="I11" s="225"/>
-      <c r="J11" s="225"/>
-      <c r="K11" s="225"/>
-      <c r="L11" s="225"/>
+      <c r="D11" s="222"/>
+      <c r="E11" s="222"/>
+      <c r="F11" s="222"/>
+      <c r="G11" s="222"/>
+      <c r="H11" s="222"/>
+      <c r="I11" s="222"/>
+      <c r="J11" s="222"/>
+      <c r="K11" s="222"/>
+      <c r="L11" s="222"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B12" s="7" t="s">
@@ -7118,18 +7118,18 @@
       <c r="C19" s="165"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C21" s="225" t="s">
+      <c r="C21" s="222" t="s">
         <v>320</v>
       </c>
-      <c r="D21" s="225"/>
-      <c r="E21" s="225"/>
-      <c r="F21" s="225"/>
-      <c r="G21" s="225"/>
-      <c r="H21" s="225"/>
-      <c r="I21" s="225"/>
-      <c r="J21" s="225"/>
-      <c r="K21" s="225"/>
-      <c r="L21" s="225"/>
+      <c r="D21" s="222"/>
+      <c r="E21" s="222"/>
+      <c r="F21" s="222"/>
+      <c r="G21" s="222"/>
+      <c r="H21" s="222"/>
+      <c r="I21" s="222"/>
+      <c r="J21" s="222"/>
+      <c r="K21" s="222"/>
+      <c r="L21" s="222"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
@@ -7352,10 +7352,10 @@
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B29" s="226" t="s">
+      <c r="B29" s="223" t="s">
         <v>316</v>
       </c>
-      <c r="C29" s="226"/>
+      <c r="C29" s="223"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
@@ -7383,18 +7383,18 @@
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35" s="94"/>
-      <c r="C35" s="225" t="s">
+      <c r="C35" s="222" t="s">
         <v>188</v>
       </c>
-      <c r="D35" s="225"/>
-      <c r="E35" s="225"/>
-      <c r="F35" s="225"/>
-      <c r="G35" s="225"/>
-      <c r="H35" s="225"/>
-      <c r="I35" s="225"/>
-      <c r="J35" s="225"/>
-      <c r="K35" s="225"/>
-      <c r="L35" s="225"/>
+      <c r="D35" s="222"/>
+      <c r="E35" s="222"/>
+      <c r="F35" s="222"/>
+      <c r="G35" s="222"/>
+      <c r="H35" s="222"/>
+      <c r="I35" s="222"/>
+      <c r="J35" s="222"/>
+      <c r="K35" s="222"/>
+      <c r="L35" s="222"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" s="7" t="s">
@@ -7487,18 +7487,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="225" t="s">
+      <c r="C39" s="222" t="s">
         <v>328</v>
       </c>
-      <c r="D39" s="225"/>
-      <c r="E39" s="225"/>
-      <c r="F39" s="225"/>
-      <c r="G39" s="225"/>
-      <c r="H39" s="225"/>
-      <c r="I39" s="225"/>
-      <c r="J39" s="225"/>
-      <c r="K39" s="225"/>
-      <c r="L39" s="225"/>
+      <c r="D39" s="222"/>
+      <c r="E39" s="222"/>
+      <c r="F39" s="222"/>
+      <c r="G39" s="222"/>
+      <c r="H39" s="222"/>
+      <c r="I39" s="222"/>
+      <c r="J39" s="222"/>
+      <c r="K39" s="222"/>
+      <c r="L39" s="222"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="183">
@@ -7633,18 +7633,18 @@
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C44" s="225" t="s">
+      <c r="C44" s="222" t="s">
         <v>330</v>
       </c>
-      <c r="D44" s="225"/>
-      <c r="E44" s="225"/>
-      <c r="F44" s="225"/>
-      <c r="G44" s="225"/>
-      <c r="H44" s="225"/>
-      <c r="I44" s="225"/>
-      <c r="J44" s="225"/>
-      <c r="K44" s="225"/>
-      <c r="L44" s="225"/>
+      <c r="D44" s="222"/>
+      <c r="E44" s="222"/>
+      <c r="F44" s="222"/>
+      <c r="G44" s="222"/>
+      <c r="H44" s="222"/>
+      <c r="I44" s="222"/>
+      <c r="J44" s="222"/>
+      <c r="K44" s="222"/>
+      <c r="L44" s="222"/>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="7" t="s">
@@ -7773,18 +7773,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C35:L35"/>
     <mergeCell ref="C39:L39"/>
     <mergeCell ref="C44:L44"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="C21:L21"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7842,20 +7842,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="105"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="223" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230" t="s">
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="224"/>
+      <c r="H2" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="223"/>
       <c r="S2" s="231"/>
       <c r="T2" s="231"/>
       <c r="U2" s="231"/>
@@ -7873,18 +7873,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="110"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="225" t="s">
+      <c r="C4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="225"/>
-      <c r="E4" s="225"/>
-      <c r="F4" s="225"/>
-      <c r="G4" s="225"/>
-      <c r="H4" s="225"/>
-      <c r="I4" s="225"/>
-      <c r="J4" s="225"/>
-      <c r="K4" s="225"/>
-      <c r="L4" s="225"/>
+      <c r="D4" s="222"/>
+      <c r="E4" s="222"/>
+      <c r="F4" s="222"/>
+      <c r="G4" s="222"/>
+      <c r="H4" s="222"/>
+      <c r="I4" s="222"/>
+      <c r="J4" s="222"/>
+      <c r="K4" s="222"/>
+      <c r="L4" s="222"/>
       <c r="S4" s="231"/>
       <c r="T4" s="231"/>
       <c r="U4" s="231"/>
@@ -8679,18 +8679,18 @@
       <c r="AE17" s="114"/>
     </row>
     <row r="20" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C20" s="225" t="s">
+      <c r="C20" s="222" t="s">
         <v>286</v>
       </c>
-      <c r="D20" s="225"/>
-      <c r="E20" s="225"/>
-      <c r="F20" s="225"/>
-      <c r="G20" s="225"/>
-      <c r="H20" s="225"/>
-      <c r="I20" s="225"/>
-      <c r="J20" s="225"/>
-      <c r="K20" s="225"/>
-      <c r="L20" s="225"/>
+      <c r="D20" s="222"/>
+      <c r="E20" s="222"/>
+      <c r="F20" s="222"/>
+      <c r="G20" s="222"/>
+      <c r="H20" s="222"/>
+      <c r="I20" s="222"/>
+      <c r="J20" s="222"/>
+      <c r="K20" s="222"/>
+      <c r="L20" s="222"/>
     </row>
     <row r="21" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C21" s="62">
@@ -8822,20 +8822,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="105"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="223" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230" t="s">
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="224"/>
+      <c r="H2" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="223"/>
       <c r="S2" s="231"/>
       <c r="T2" s="231"/>
       <c r="U2" s="231"/>
@@ -8853,18 +8853,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="110"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="225" t="s">
+      <c r="C4" s="222" t="s">
         <v>268</v>
       </c>
-      <c r="D4" s="225"/>
-      <c r="E4" s="225"/>
-      <c r="F4" s="225"/>
-      <c r="G4" s="225"/>
-      <c r="H4" s="225"/>
-      <c r="I4" s="225"/>
-      <c r="J4" s="225"/>
-      <c r="K4" s="225"/>
-      <c r="L4" s="225"/>
+      <c r="D4" s="222"/>
+      <c r="E4" s="222"/>
+      <c r="F4" s="222"/>
+      <c r="G4" s="222"/>
+      <c r="H4" s="222"/>
+      <c r="I4" s="222"/>
+      <c r="J4" s="222"/>
+      <c r="K4" s="222"/>
+      <c r="L4" s="222"/>
       <c r="S4" s="231"/>
       <c r="T4" s="231"/>
       <c r="U4" s="231"/>
@@ -10612,20 +10612,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="105"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="223" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230" t="s">
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="224"/>
+      <c r="H2" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="223"/>
       <c r="S2" s="231"/>
       <c r="T2" s="231"/>
       <c r="U2" s="231"/>
@@ -10643,18 +10643,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="110"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="225" t="s">
+      <c r="C4" s="222" t="s">
         <v>269</v>
       </c>
-      <c r="D4" s="225"/>
-      <c r="E4" s="225"/>
-      <c r="F4" s="225"/>
-      <c r="G4" s="225"/>
-      <c r="H4" s="225"/>
-      <c r="I4" s="225"/>
-      <c r="J4" s="225"/>
-      <c r="K4" s="225"/>
-      <c r="L4" s="225"/>
+      <c r="D4" s="222"/>
+      <c r="E4" s="222"/>
+      <c r="F4" s="222"/>
+      <c r="G4" s="222"/>
+      <c r="H4" s="222"/>
+      <c r="I4" s="222"/>
+      <c r="J4" s="222"/>
+      <c r="K4" s="222"/>
+      <c r="L4" s="222"/>
       <c r="S4" s="231"/>
       <c r="T4" s="231"/>
       <c r="U4" s="231"/>
@@ -11933,18 +11933,18 @@
       <c r="I27" s="109"/>
     </row>
     <row r="29" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C29" s="225" t="s">
+      <c r="C29" s="222" t="s">
         <v>286</v>
       </c>
-      <c r="D29" s="225"/>
-      <c r="E29" s="225"/>
-      <c r="F29" s="225"/>
-      <c r="G29" s="225"/>
-      <c r="H29" s="225"/>
-      <c r="I29" s="225"/>
-      <c r="J29" s="225"/>
-      <c r="K29" s="225"/>
-      <c r="L29" s="225"/>
+      <c r="D29" s="222"/>
+      <c r="E29" s="222"/>
+      <c r="F29" s="222"/>
+      <c r="G29" s="222"/>
+      <c r="H29" s="222"/>
+      <c r="I29" s="222"/>
+      <c r="J29" s="222"/>
+      <c r="K29" s="222"/>
+      <c r="L29" s="222"/>
     </row>
     <row r="30" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C30" s="62">
@@ -12295,10 +12295,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="226" t="s">
+      <c r="B4" s="223" t="s">
         <v>351</v>
       </c>
-      <c r="C4" s="226"/>
+      <c r="C4" s="223"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -12378,10 +12378,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="226" t="s">
+      <c r="B15" s="223" t="s">
         <v>357</v>
       </c>
-      <c r="C15" s="226"/>
+      <c r="C15" s="223"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -12493,20 +12493,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="105"/>
-      <c r="C3" s="226" t="s">
+      <c r="C3" s="223" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="226"/>
-      <c r="E3" s="226"/>
-      <c r="F3" s="226"/>
-      <c r="G3" s="229"/>
-      <c r="H3" s="230" t="s">
+      <c r="D3" s="223"/>
+      <c r="E3" s="223"/>
+      <c r="F3" s="223"/>
+      <c r="G3" s="224"/>
+      <c r="H3" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="226"/>
-      <c r="J3" s="226"/>
-      <c r="K3" s="226"/>
-      <c r="L3" s="226"/>
+      <c r="I3" s="223"/>
+      <c r="J3" s="223"/>
+      <c r="K3" s="223"/>
+      <c r="L3" s="223"/>
       <c r="P3" s="231"/>
       <c r="Q3" s="231"/>
       <c r="R3" s="231"/>
@@ -12524,18 +12524,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="110"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="225" t="s">
+      <c r="C5" s="222" t="s">
         <v>371</v>
       </c>
-      <c r="D5" s="225"/>
-      <c r="E5" s="225"/>
-      <c r="F5" s="225"/>
-      <c r="G5" s="225"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="225"/>
-      <c r="K5" s="225"/>
-      <c r="L5" s="225"/>
+      <c r="D5" s="222"/>
+      <c r="E5" s="222"/>
+      <c r="F5" s="222"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="222"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="222"/>
+      <c r="L5" s="222"/>
       <c r="P5" s="231"/>
       <c r="Q5" s="231"/>
       <c r="R5" s="231"/>
@@ -12792,10 +12792,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="226" t="s">
+      <c r="B13" s="223" t="s">
         <v>372</v>
       </c>
-      <c r="C13" s="226"/>
+      <c r="C13" s="223"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -12815,10 +12815,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="226" t="s">
+      <c r="B18" s="223" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="226"/>
+      <c r="C18" s="223"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -12932,37 +12932,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="105"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="223" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230" t="s">
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="224"/>
+      <c r="H2" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="223"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="110"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="225" t="s">
+      <c r="C4" s="222" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="225"/>
-      <c r="E4" s="225"/>
-      <c r="F4" s="225"/>
-      <c r="G4" s="225"/>
-      <c r="H4" s="225"/>
-      <c r="I4" s="225"/>
-      <c r="J4" s="225"/>
-      <c r="K4" s="225"/>
-      <c r="L4" s="225"/>
+      <c r="D4" s="222"/>
+      <c r="E4" s="222"/>
+      <c r="F4" s="222"/>
+      <c r="G4" s="222"/>
+      <c r="H4" s="222"/>
+      <c r="I4" s="222"/>
+      <c r="J4" s="222"/>
+      <c r="K4" s="222"/>
+      <c r="L4" s="222"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -13105,18 +13105,18 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="225" t="s">
+      <c r="C9" s="222" t="s">
         <v>194</v>
       </c>
-      <c r="D9" s="225"/>
-      <c r="E9" s="225"/>
-      <c r="F9" s="225"/>
-      <c r="G9" s="225"/>
-      <c r="H9" s="225"/>
-      <c r="I9" s="225"/>
-      <c r="J9" s="225"/>
-      <c r="K9" s="225"/>
-      <c r="L9" s="225"/>
+      <c r="D9" s="222"/>
+      <c r="E9" s="222"/>
+      <c r="F9" s="222"/>
+      <c r="G9" s="222"/>
+      <c r="H9" s="222"/>
+      <c r="I9" s="222"/>
+      <c r="J9" s="222"/>
+      <c r="K9" s="222"/>
+      <c r="L9" s="222"/>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -13267,18 +13267,18 @@
       <c r="N13" s="93"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="225" t="s">
+      <c r="C14" s="222" t="s">
         <v>420</v>
       </c>
-      <c r="D14" s="225"/>
-      <c r="E14" s="225"/>
-      <c r="F14" s="225"/>
-      <c r="G14" s="225"/>
-      <c r="H14" s="225"/>
-      <c r="I14" s="225"/>
-      <c r="J14" s="225"/>
-      <c r="K14" s="225"/>
-      <c r="L14" s="225"/>
+      <c r="D14" s="222"/>
+      <c r="E14" s="222"/>
+      <c r="F14" s="222"/>
+      <c r="G14" s="222"/>
+      <c r="H14" s="222"/>
+      <c r="I14" s="222"/>
+      <c r="J14" s="222"/>
+      <c r="K14" s="222"/>
+      <c r="L14" s="222"/>
       <c r="N14" s="93"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -13415,10 +13415,10 @@
       <c r="N19" s="93"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="226" t="s">
+      <c r="B20" s="223" t="s">
         <v>388</v>
       </c>
-      <c r="C20" s="226"/>
+      <c r="C20" s="223"/>
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -13475,10 +13475,10 @@
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B28" s="226" t="s">
+      <c r="B28" s="223" t="s">
         <v>391</v>
       </c>
-      <c r="C28" s="226"/>
+      <c r="C28" s="223"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
@@ -13576,10 +13576,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="226" t="s">
+      <c r="B4" s="223" t="s">
         <v>401</v>
       </c>
-      <c r="C4" s="226"/>
+      <c r="C4" s="223"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -18181,11 +18181,11 @@
         <v>86</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="222" t="s">
+      <c r="P4" s="226" t="s">
         <v>87</v>
       </c>
-      <c r="Q4" s="223"/>
-      <c r="R4" s="224"/>
+      <c r="Q4" s="227"/>
+      <c r="R4" s="228"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -28540,36 +28540,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="105"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="223" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230" t="s">
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="224"/>
+      <c r="H2" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="223"/>
       <c r="O2" s="92"/>
-      <c r="S2" s="226" t="s">
+      <c r="S2" s="223" t="s">
         <v>178</v>
       </c>
-      <c r="T2" s="226"/>
-      <c r="U2" s="226"/>
-      <c r="V2" s="226"/>
-      <c r="W2" s="226"/>
-      <c r="X2" s="226"/>
-      <c r="Y2" s="226"/>
-      <c r="Z2" s="226"/>
-      <c r="AA2" s="226" t="s">
+      <c r="T2" s="223"/>
+      <c r="U2" s="223"/>
+      <c r="V2" s="223"/>
+      <c r="W2" s="223"/>
+      <c r="X2" s="223"/>
+      <c r="Y2" s="223"/>
+      <c r="Z2" s="223"/>
+      <c r="AA2" s="223" t="s">
         <v>179</v>
       </c>
-      <c r="AB2" s="226"/>
-      <c r="AC2" s="226"/>
+      <c r="AB2" s="223"/>
+      <c r="AC2" s="223"/>
       <c r="AE2" s="129" t="s">
         <v>86</v>
       </c>
@@ -28580,32 +28580,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="110"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="225" t="s">
+      <c r="C4" s="222" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="225"/>
-      <c r="E4" s="225"/>
-      <c r="F4" s="225"/>
-      <c r="G4" s="225"/>
-      <c r="H4" s="225"/>
-      <c r="I4" s="225"/>
-      <c r="J4" s="225"/>
-      <c r="K4" s="225"/>
-      <c r="L4" s="225"/>
+      <c r="D4" s="222"/>
+      <c r="E4" s="222"/>
+      <c r="F4" s="222"/>
+      <c r="G4" s="222"/>
+      <c r="H4" s="222"/>
+      <c r="I4" s="222"/>
+      <c r="J4" s="222"/>
+      <c r="K4" s="222"/>
+      <c r="L4" s="222"/>
       <c r="O4" s="92"/>
-      <c r="S4" s="227" t="s">
+      <c r="S4" s="229" t="s">
         <v>188</v>
       </c>
-      <c r="T4" s="228"/>
-      <c r="U4" s="228"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="228"/>
-      <c r="X4" s="228"/>
-      <c r="Y4" s="228"/>
-      <c r="Z4" s="228"/>
-      <c r="AA4" s="228"/>
-      <c r="AB4" s="228"/>
-      <c r="AC4" s="228"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="230"/>
+      <c r="Y4" s="230"/>
+      <c r="Z4" s="230"/>
+      <c r="AA4" s="230"/>
+      <c r="AB4" s="230"/>
+      <c r="AC4" s="230"/>
       <c r="AE4" s="141" t="s">
         <v>213</v>
       </c>
@@ -29401,33 +29401,33 @@
       <c r="Q13" s="93"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C14" s="225" t="s">
+      <c r="C14" s="222" t="s">
         <v>194</v>
       </c>
-      <c r="D14" s="225"/>
-      <c r="E14" s="225"/>
-      <c r="F14" s="225"/>
-      <c r="G14" s="225"/>
-      <c r="H14" s="225"/>
-      <c r="I14" s="225"/>
-      <c r="J14" s="225"/>
-      <c r="K14" s="225"/>
-      <c r="L14" s="225"/>
+      <c r="D14" s="222"/>
+      <c r="E14" s="222"/>
+      <c r="F14" s="222"/>
+      <c r="G14" s="222"/>
+      <c r="H14" s="222"/>
+      <c r="I14" s="222"/>
+      <c r="J14" s="222"/>
+      <c r="K14" s="222"/>
+      <c r="L14" s="222"/>
       <c r="O14" s="92"/>
       <c r="Q14" s="93"/>
-      <c r="S14" s="227" t="s">
+      <c r="S14" s="229" t="s">
         <v>194</v>
       </c>
-      <c r="T14" s="228"/>
-      <c r="U14" s="228"/>
-      <c r="V14" s="228"/>
-      <c r="W14" s="228"/>
-      <c r="X14" s="228"/>
-      <c r="Y14" s="228"/>
-      <c r="Z14" s="228"/>
-      <c r="AA14" s="228"/>
-      <c r="AB14" s="228"/>
-      <c r="AC14" s="228"/>
+      <c r="T14" s="230"/>
+      <c r="U14" s="230"/>
+      <c r="V14" s="230"/>
+      <c r="W14" s="230"/>
+      <c r="X14" s="230"/>
+      <c r="Y14" s="230"/>
+      <c r="Z14" s="230"/>
+      <c r="AA14" s="230"/>
+      <c r="AB14" s="230"/>
+      <c r="AC14" s="230"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B15" s="7" t="s">
@@ -30120,33 +30120,33 @@
       <c r="Q24" s="93"/>
     </row>
     <row r="25" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C25" s="225" t="s">
+      <c r="C25" s="222" t="s">
         <v>196</v>
       </c>
-      <c r="D25" s="225"/>
-      <c r="E25" s="225"/>
-      <c r="F25" s="225"/>
-      <c r="G25" s="225"/>
-      <c r="H25" s="225"/>
-      <c r="I25" s="225"/>
-      <c r="J25" s="225"/>
-      <c r="K25" s="225"/>
-      <c r="L25" s="225"/>
+      <c r="D25" s="222"/>
+      <c r="E25" s="222"/>
+      <c r="F25" s="222"/>
+      <c r="G25" s="222"/>
+      <c r="H25" s="222"/>
+      <c r="I25" s="222"/>
+      <c r="J25" s="222"/>
+      <c r="K25" s="222"/>
+      <c r="L25" s="222"/>
       <c r="O25" s="92"/>
       <c r="Q25" s="93"/>
-      <c r="S25" s="227" t="s">
+      <c r="S25" s="229" t="s">
         <v>196</v>
       </c>
-      <c r="T25" s="228"/>
-      <c r="U25" s="228"/>
-      <c r="V25" s="228"/>
-      <c r="W25" s="228"/>
-      <c r="X25" s="228"/>
-      <c r="Y25" s="228"/>
-      <c r="Z25" s="228"/>
-      <c r="AA25" s="228"/>
-      <c r="AB25" s="228"/>
-      <c r="AC25" s="228"/>
+      <c r="T25" s="230"/>
+      <c r="U25" s="230"/>
+      <c r="V25" s="230"/>
+      <c r="W25" s="230"/>
+      <c r="X25" s="230"/>
+      <c r="Y25" s="230"/>
+      <c r="Z25" s="230"/>
+      <c r="AA25" s="230"/>
+      <c r="AB25" s="230"/>
+      <c r="AC25" s="230"/>
       <c r="AE25" s="141" t="str">
         <f>AE4</f>
         <v>Q1-Q2-Q3</v>
@@ -31469,32 +31469,32 @@
       <c r="O42" s="92"/>
     </row>
     <row r="43" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C43" s="225" t="s">
+      <c r="C43" s="222" t="s">
         <v>208</v>
       </c>
-      <c r="D43" s="225"/>
-      <c r="E43" s="225"/>
-      <c r="F43" s="225"/>
-      <c r="G43" s="225"/>
-      <c r="H43" s="225"/>
-      <c r="I43" s="225"/>
-      <c r="J43" s="225"/>
-      <c r="K43" s="225"/>
-      <c r="L43" s="225"/>
+      <c r="D43" s="222"/>
+      <c r="E43" s="222"/>
+      <c r="F43" s="222"/>
+      <c r="G43" s="222"/>
+      <c r="H43" s="222"/>
+      <c r="I43" s="222"/>
+      <c r="J43" s="222"/>
+      <c r="K43" s="222"/>
+      <c r="L43" s="222"/>
       <c r="O43" s="92"/>
-      <c r="S43" s="227" t="s">
+      <c r="S43" s="229" t="s">
         <v>208</v>
       </c>
-      <c r="T43" s="228"/>
-      <c r="U43" s="228"/>
-      <c r="V43" s="228"/>
-      <c r="W43" s="228"/>
-      <c r="X43" s="228"/>
-      <c r="Y43" s="228"/>
-      <c r="Z43" s="228"/>
-      <c r="AA43" s="228"/>
-      <c r="AB43" s="228"/>
-      <c r="AC43" s="228"/>
+      <c r="T43" s="230"/>
+      <c r="U43" s="230"/>
+      <c r="V43" s="230"/>
+      <c r="W43" s="230"/>
+      <c r="X43" s="230"/>
+      <c r="Y43" s="230"/>
+      <c r="Z43" s="230"/>
+      <c r="AA43" s="230"/>
+      <c r="AB43" s="230"/>
+      <c r="AC43" s="230"/>
     </row>
     <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B44" s="7" t="s">
@@ -32110,35 +32110,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="105"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="223" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230" t="s">
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="224"/>
+      <c r="H2" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
-      <c r="P2" s="226" t="s">
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="223"/>
+      <c r="P2" s="223" t="s">
         <v>178</v>
       </c>
-      <c r="Q2" s="226"/>
-      <c r="R2" s="226"/>
-      <c r="S2" s="226"/>
-      <c r="T2" s="226"/>
-      <c r="U2" s="226"/>
-      <c r="V2" s="226"/>
-      <c r="W2" s="226"/>
-      <c r="X2" s="226" t="s">
+      <c r="Q2" s="223"/>
+      <c r="R2" s="223"/>
+      <c r="S2" s="223"/>
+      <c r="T2" s="223"/>
+      <c r="U2" s="223"/>
+      <c r="V2" s="223"/>
+      <c r="W2" s="223"/>
+      <c r="X2" s="223" t="s">
         <v>179</v>
       </c>
-      <c r="Y2" s="226"/>
-      <c r="Z2" s="226"/>
+      <c r="Y2" s="223"/>
+      <c r="Z2" s="223"/>
       <c r="AB2" s="129" t="s">
         <v>86</v>
       </c>
@@ -32147,31 +32147,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="110"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="225" t="s">
+      <c r="C4" s="222" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="225"/>
-      <c r="E4" s="225"/>
-      <c r="F4" s="225"/>
-      <c r="G4" s="225"/>
-      <c r="H4" s="225"/>
-      <c r="I4" s="225"/>
-      <c r="J4" s="225"/>
-      <c r="K4" s="225"/>
-      <c r="L4" s="225"/>
-      <c r="P4" s="228" t="s">
+      <c r="D4" s="222"/>
+      <c r="E4" s="222"/>
+      <c r="F4" s="222"/>
+      <c r="G4" s="222"/>
+      <c r="H4" s="222"/>
+      <c r="I4" s="222"/>
+      <c r="J4" s="222"/>
+      <c r="K4" s="222"/>
+      <c r="L4" s="222"/>
+      <c r="P4" s="230" t="s">
         <v>188</v>
       </c>
-      <c r="Q4" s="228"/>
-      <c r="R4" s="228"/>
-      <c r="S4" s="228"/>
-      <c r="T4" s="228"/>
-      <c r="U4" s="228"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="228"/>
-      <c r="X4" s="228"/>
-      <c r="Y4" s="228"/>
-      <c r="Z4" s="228"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="230"/>
+      <c r="Y4" s="230"/>
+      <c r="Z4" s="230"/>
       <c r="AB4" s="141" t="s">
         <v>213</v>
       </c>
@@ -32372,32 +32372,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="225" t="s">
+      <c r="C9" s="222" t="s">
         <v>215</v>
       </c>
-      <c r="D9" s="225"/>
-      <c r="E9" s="225"/>
-      <c r="F9" s="225"/>
-      <c r="G9" s="225"/>
-      <c r="H9" s="225"/>
-      <c r="I9" s="225"/>
-      <c r="J9" s="225"/>
-      <c r="K9" s="225"/>
-      <c r="L9" s="225"/>
+      <c r="D9" s="222"/>
+      <c r="E9" s="222"/>
+      <c r="F9" s="222"/>
+      <c r="G9" s="222"/>
+      <c r="H9" s="222"/>
+      <c r="I9" s="222"/>
+      <c r="J9" s="222"/>
+      <c r="K9" s="222"/>
+      <c r="L9" s="222"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="228" t="s">
+      <c r="P9" s="230" t="s">
         <v>220</v>
       </c>
-      <c r="Q9" s="228"/>
-      <c r="R9" s="228"/>
-      <c r="S9" s="228"/>
-      <c r="T9" s="228"/>
-      <c r="U9" s="228"/>
-      <c r="V9" s="228"/>
-      <c r="W9" s="228"/>
-      <c r="X9" s="228"/>
-      <c r="Y9" s="228"/>
-      <c r="Z9" s="228"/>
+      <c r="Q9" s="230"/>
+      <c r="R9" s="230"/>
+      <c r="S9" s="230"/>
+      <c r="T9" s="230"/>
+      <c r="U9" s="230"/>
+      <c r="V9" s="230"/>
+      <c r="W9" s="230"/>
+      <c r="X9" s="230"/>
+      <c r="Y9" s="230"/>
+      <c r="Z9" s="230"/>
       <c r="AB9" s="141" t="str">
         <f>AB4</f>
         <v>Q1-Q2-Q3</v>
@@ -32959,31 +32959,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="225" t="s">
+      <c r="C18" s="222" t="s">
         <v>218</v>
       </c>
-      <c r="D18" s="225"/>
-      <c r="E18" s="225"/>
-      <c r="F18" s="225"/>
-      <c r="G18" s="225"/>
-      <c r="H18" s="225"/>
-      <c r="I18" s="225"/>
-      <c r="J18" s="225"/>
-      <c r="K18" s="225"/>
-      <c r="L18" s="225"/>
-      <c r="P18" s="228" t="s">
+      <c r="D18" s="222"/>
+      <c r="E18" s="222"/>
+      <c r="F18" s="222"/>
+      <c r="G18" s="222"/>
+      <c r="H18" s="222"/>
+      <c r="I18" s="222"/>
+      <c r="J18" s="222"/>
+      <c r="K18" s="222"/>
+      <c r="L18" s="222"/>
+      <c r="P18" s="230" t="s">
         <v>218</v>
       </c>
-      <c r="Q18" s="228"/>
-      <c r="R18" s="228"/>
-      <c r="S18" s="228"/>
-      <c r="T18" s="228"/>
-      <c r="U18" s="228"/>
-      <c r="V18" s="228"/>
-      <c r="W18" s="228"/>
-      <c r="X18" s="228"/>
-      <c r="Y18" s="228"/>
-      <c r="Z18" s="228"/>
+      <c r="Q18" s="230"/>
+      <c r="R18" s="230"/>
+      <c r="S18" s="230"/>
+      <c r="T18" s="230"/>
+      <c r="U18" s="230"/>
+      <c r="V18" s="230"/>
+      <c r="W18" s="230"/>
+      <c r="X18" s="230"/>
+      <c r="Y18" s="230"/>
+      <c r="Z18" s="230"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -33468,20 +33468,20 @@
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
-      <c r="C5" s="226" t="s">
+      <c r="C5" s="223" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="226"/>
-      <c r="E5" s="226"/>
-      <c r="F5" s="226"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="230" t="s">
+      <c r="D5" s="223"/>
+      <c r="E5" s="223"/>
+      <c r="F5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="I5" s="226"/>
-      <c r="J5" s="226"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="226"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="223"/>
+      <c r="K5" s="223"/>
+      <c r="L5" s="223"/>
       <c r="P5" s="231"/>
       <c r="Q5" s="231"/>
       <c r="R5" s="231"/>
@@ -33499,18 +33499,18 @@
     <row r="7" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="110"/>
       <c r="B7" s="94"/>
-      <c r="C7" s="225" t="s">
+      <c r="C7" s="222" t="s">
         <v>188</v>
       </c>
-      <c r="D7" s="225"/>
-      <c r="E7" s="225"/>
-      <c r="F7" s="225"/>
-      <c r="G7" s="225"/>
-      <c r="H7" s="225"/>
-      <c r="I7" s="225"/>
-      <c r="J7" s="225"/>
-      <c r="K7" s="225"/>
-      <c r="L7" s="225"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="222"/>
+      <c r="F7" s="222"/>
+      <c r="G7" s="222"/>
+      <c r="H7" s="222"/>
+      <c r="I7" s="222"/>
+      <c r="J7" s="222"/>
+      <c r="K7" s="222"/>
+      <c r="L7" s="222"/>
       <c r="P7" s="231"/>
       <c r="Q7" s="231"/>
       <c r="R7" s="231"/>
@@ -33648,18 +33648,18 @@
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C12" s="225" t="s">
+      <c r="C12" s="222" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="225"/>
-      <c r="E12" s="225"/>
-      <c r="F12" s="225"/>
-      <c r="G12" s="225"/>
-      <c r="H12" s="225"/>
-      <c r="I12" s="225"/>
-      <c r="J12" s="225"/>
-      <c r="K12" s="225"/>
-      <c r="L12" s="225"/>
+      <c r="D12" s="222"/>
+      <c r="E12" s="222"/>
+      <c r="F12" s="222"/>
+      <c r="G12" s="222"/>
+      <c r="H12" s="222"/>
+      <c r="I12" s="222"/>
+      <c r="J12" s="222"/>
+      <c r="K12" s="222"/>
+      <c r="L12" s="222"/>
       <c r="N12" s="93"/>
       <c r="P12" s="231"/>
       <c r="Q12" s="231"/>
@@ -33973,18 +33973,18 @@
       <c r="D18" s="20"/>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C20" s="225" t="s">
+      <c r="C20" s="222" t="s">
         <v>247</v>
       </c>
-      <c r="D20" s="225"/>
-      <c r="E20" s="225"/>
-      <c r="F20" s="225"/>
-      <c r="G20" s="225"/>
-      <c r="H20" s="225"/>
-      <c r="I20" s="225"/>
-      <c r="J20" s="225"/>
-      <c r="K20" s="225"/>
-      <c r="L20" s="225"/>
+      <c r="D20" s="222"/>
+      <c r="E20" s="222"/>
+      <c r="F20" s="222"/>
+      <c r="G20" s="222"/>
+      <c r="H20" s="222"/>
+      <c r="I20" s="222"/>
+      <c r="J20" s="222"/>
+      <c r="K20" s="222"/>
+      <c r="L20" s="222"/>
       <c r="P20" s="231"/>
       <c r="Q20" s="231"/>
       <c r="R20" s="231"/>
@@ -34250,18 +34250,18 @@
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C30" s="225" t="s">
+      <c r="C30" s="222" t="s">
         <v>237</v>
       </c>
-      <c r="D30" s="225"/>
-      <c r="E30" s="225"/>
-      <c r="F30" s="225"/>
-      <c r="G30" s="225"/>
-      <c r="H30" s="225"/>
-      <c r="I30" s="225"/>
-      <c r="J30" s="225"/>
-      <c r="K30" s="225"/>
-      <c r="L30" s="225"/>
+      <c r="D30" s="222"/>
+      <c r="E30" s="222"/>
+      <c r="F30" s="222"/>
+      <c r="G30" s="222"/>
+      <c r="H30" s="222"/>
+      <c r="I30" s="222"/>
+      <c r="J30" s="222"/>
+      <c r="K30" s="222"/>
+      <c r="L30" s="222"/>
     </row>
     <row r="31" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
@@ -34489,10 +34489,10 @@
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B37" s="226" t="s">
+      <c r="B37" s="223" t="s">
         <v>239</v>
       </c>
-      <c r="C37" s="226"/>
+      <c r="C37" s="223"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
@@ -34512,13 +34512,13 @@
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B42" s="7"/>
-      <c r="C42" s="226" t="s">
+      <c r="C42" s="223" t="s">
         <v>238</v>
       </c>
-      <c r="D42" s="226"/>
-      <c r="E42" s="226"/>
-      <c r="F42" s="226"/>
-      <c r="G42" s="226"/>
+      <c r="D42" s="223"/>
+      <c r="E42" s="223"/>
+      <c r="F42" s="223"/>
+      <c r="G42" s="223"/>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="7" t="s">
@@ -34648,10 +34648,10 @@
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B50" s="226" t="s">
+      <c r="B50" s="223" t="s">
         <v>243</v>
       </c>
-      <c r="C50" s="226"/>
+      <c r="C50" s="223"/>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
@@ -34682,6 +34682,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="P5:W5"/>
+    <mergeCell ref="X5:Z5"/>
+    <mergeCell ref="C7:L7"/>
+    <mergeCell ref="P7:Z7"/>
     <mergeCell ref="B50:C50"/>
     <mergeCell ref="C12:L12"/>
     <mergeCell ref="P12:Z12"/>
@@ -34690,12 +34696,6 @@
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="C42:G42"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="P5:W5"/>
-    <mergeCell ref="X5:Z5"/>
-    <mergeCell ref="C7:L7"/>
-    <mergeCell ref="P7:Z7"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{7B0EB6A4-3658-0541-ACD6-B6D16EB047D2}">

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FF7FED-536C-5444-8ED8-3767D25F69A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BD172A-C60A-DD43-B1DD-7E3FCF26CDDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2403,18 +2403,6 @@
     <xf numFmtId="165" fontId="24" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="18" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2424,10 +2412,22 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2470,7 +2470,7 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="C4">
-            <v>100.51</v>
+            <v>99.84</v>
           </cell>
         </row>
       </sheetData>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$4</f>
-        <v>100.51</v>
+        <v>99.84</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C11" s="95">
         <f>$C$3/'Statement Q'!$N$22</f>
-        <v>11.830927196370968</v>
+        <v>11.752062195658914</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C12" s="95">
         <f>C3/Statements!S20</f>
-        <v>29.440468978131488</v>
+        <v>29.244218712333577</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="C13" s="103">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$20)</f>
-        <v>4.7213037817144787</v>
+        <v>4.6898315547345897</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C15" s="20">
         <f>C3*'Statement Q'!J116</f>
-        <v>4764174</v>
+        <v>4732416</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C18" s="20">
         <f>C15+C17-C16</f>
-        <v>3717486</v>
+        <v>3685728</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -3267,20 +3267,20 @@
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
-      <c r="C5" s="223" t="s">
+      <c r="C5" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="223"/>
-      <c r="G5" s="224"/>
-      <c r="H5" s="225" t="s">
+      <c r="D5" s="226"/>
+      <c r="E5" s="226"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="230" t="s">
         <v>179</v>
       </c>
-      <c r="I5" s="223"/>
-      <c r="J5" s="223"/>
-      <c r="K5" s="223"/>
-      <c r="L5" s="223"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="226"/>
+      <c r="K5" s="226"/>
+      <c r="L5" s="226"/>
       <c r="P5" s="231"/>
       <c r="Q5" s="231"/>
       <c r="R5" s="231"/>
@@ -3298,18 +3298,18 @@
     <row r="7" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="110"/>
       <c r="B7" s="94"/>
-      <c r="C7" s="222" t="s">
+      <c r="C7" s="225" t="s">
         <v>188</v>
       </c>
-      <c r="D7" s="222"/>
-      <c r="E7" s="222"/>
-      <c r="F7" s="222"/>
-      <c r="G7" s="222"/>
-      <c r="H7" s="222"/>
-      <c r="I7" s="222"/>
-      <c r="J7" s="222"/>
-      <c r="K7" s="222"/>
-      <c r="L7" s="222"/>
+      <c r="D7" s="225"/>
+      <c r="E7" s="225"/>
+      <c r="F7" s="225"/>
+      <c r="G7" s="225"/>
+      <c r="H7" s="225"/>
+      <c r="I7" s="225"/>
+      <c r="J7" s="225"/>
+      <c r="K7" s="225"/>
+      <c r="L7" s="225"/>
       <c r="P7" s="231"/>
       <c r="Q7" s="231"/>
       <c r="R7" s="231"/>
@@ -3447,18 +3447,18 @@
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C12" s="222" t="s">
+      <c r="C12" s="225" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="222"/>
-      <c r="E12" s="222"/>
-      <c r="F12" s="222"/>
-      <c r="G12" s="222"/>
-      <c r="H12" s="222"/>
-      <c r="I12" s="222"/>
-      <c r="J12" s="222"/>
-      <c r="K12" s="222"/>
-      <c r="L12" s="222"/>
+      <c r="D12" s="225"/>
+      <c r="E12" s="225"/>
+      <c r="F12" s="225"/>
+      <c r="G12" s="225"/>
+      <c r="H12" s="225"/>
+      <c r="I12" s="225"/>
+      <c r="J12" s="225"/>
+      <c r="K12" s="225"/>
+      <c r="L12" s="225"/>
       <c r="N12" s="93"/>
       <c r="P12" s="231"/>
       <c r="Q12" s="231"/>
@@ -3772,18 +3772,18 @@
       <c r="D18" s="20"/>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C20" s="222" t="s">
+      <c r="C20" s="225" t="s">
         <v>237</v>
       </c>
-      <c r="D20" s="222"/>
-      <c r="E20" s="222"/>
-      <c r="F20" s="222"/>
-      <c r="G20" s="222"/>
-      <c r="H20" s="222"/>
-      <c r="I20" s="222"/>
-      <c r="J20" s="222"/>
-      <c r="K20" s="222"/>
-      <c r="L20" s="222"/>
+      <c r="D20" s="225"/>
+      <c r="E20" s="225"/>
+      <c r="F20" s="225"/>
+      <c r="G20" s="225"/>
+      <c r="H20" s="225"/>
+      <c r="I20" s="225"/>
+      <c r="J20" s="225"/>
+      <c r="K20" s="225"/>
+      <c r="L20" s="225"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
@@ -4008,10 +4008,10 @@
       <c r="C27" s="231"/>
     </row>
     <row r="28" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B28" s="223" t="s">
+      <c r="B28" s="226" t="s">
         <v>260</v>
       </c>
-      <c r="C28" s="223"/>
+      <c r="C28" s="226"/>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
@@ -4022,18 +4022,18 @@
       </c>
     </row>
     <row r="31" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C31" s="222" t="s">
+      <c r="C31" s="225" t="s">
         <v>261</v>
       </c>
-      <c r="D31" s="222"/>
-      <c r="E31" s="222"/>
-      <c r="F31" s="222"/>
-      <c r="G31" s="222"/>
-      <c r="H31" s="222"/>
-      <c r="I31" s="222"/>
-      <c r="J31" s="222"/>
-      <c r="K31" s="222"/>
-      <c r="L31" s="222"/>
+      <c r="D31" s="225"/>
+      <c r="E31" s="225"/>
+      <c r="F31" s="225"/>
+      <c r="G31" s="225"/>
+      <c r="H31" s="225"/>
+      <c r="I31" s="225"/>
+      <c r="J31" s="225"/>
+      <c r="K31" s="225"/>
+      <c r="L31" s="225"/>
     </row>
     <row r="32" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
@@ -4240,18 +4240,18 @@
       <c r="C40" s="231"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C41" s="222" t="s">
+      <c r="C41" s="225" t="s">
         <v>262</v>
       </c>
-      <c r="D41" s="222"/>
-      <c r="E41" s="222"/>
-      <c r="F41" s="222"/>
-      <c r="G41" s="222"/>
-      <c r="H41" s="222"/>
-      <c r="I41" s="222"/>
-      <c r="J41" s="222"/>
-      <c r="K41" s="222"/>
-      <c r="L41" s="222"/>
+      <c r="D41" s="225"/>
+      <c r="E41" s="225"/>
+      <c r="F41" s="225"/>
+      <c r="G41" s="225"/>
+      <c r="H41" s="225"/>
+      <c r="I41" s="225"/>
+      <c r="J41" s="225"/>
+      <c r="K41" s="225"/>
+      <c r="L41" s="225"/>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B42" s="7" t="s">
@@ -4328,6 +4328,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C41:L41"/>
+    <mergeCell ref="C12:L12"/>
     <mergeCell ref="P12:Z12"/>
     <mergeCell ref="C20:L20"/>
     <mergeCell ref="B27:C27"/>
@@ -4337,11 +4342,6 @@
     <mergeCell ref="X5:Z5"/>
     <mergeCell ref="C7:L7"/>
     <mergeCell ref="P7:Z7"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C41:L41"/>
-    <mergeCell ref="C12:L12"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{4B588CCE-B4FF-384B-9E03-C176DEB70053}">
@@ -4386,20 +4386,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="105"/>
-      <c r="C3" s="223" t="s">
+      <c r="C3" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="223"/>
-      <c r="E3" s="223"/>
-      <c r="F3" s="223"/>
-      <c r="G3" s="224"/>
-      <c r="H3" s="225" t="s">
+      <c r="D3" s="226"/>
+      <c r="E3" s="226"/>
+      <c r="F3" s="226"/>
+      <c r="G3" s="229"/>
+      <c r="H3" s="230" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="223"/>
-      <c r="J3" s="223"/>
-      <c r="K3" s="223"/>
-      <c r="L3" s="223"/>
+      <c r="I3" s="226"/>
+      <c r="J3" s="226"/>
+      <c r="K3" s="226"/>
+      <c r="L3" s="226"/>
       <c r="P3" s="231"/>
       <c r="Q3" s="231"/>
       <c r="R3" s="231"/>
@@ -4417,18 +4417,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="110"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="222" t="s">
+      <c r="C5" s="225" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="222"/>
-      <c r="E5" s="222"/>
-      <c r="F5" s="222"/>
-      <c r="G5" s="222"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="222"/>
-      <c r="J5" s="222"/>
-      <c r="K5" s="222"/>
-      <c r="L5" s="222"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="225"/>
+      <c r="F5" s="225"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="225"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
+      <c r="L5" s="225"/>
       <c r="P5" s="231"/>
       <c r="Q5" s="231"/>
       <c r="R5" s="231"/>
@@ -4684,18 +4684,18 @@
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C12" s="222" t="s">
+      <c r="C12" s="225" t="s">
         <v>248</v>
       </c>
-      <c r="D12" s="222"/>
-      <c r="E12" s="222"/>
-      <c r="F12" s="222"/>
-      <c r="G12" s="222"/>
-      <c r="H12" s="222"/>
-      <c r="I12" s="222"/>
-      <c r="J12" s="222"/>
-      <c r="K12" s="222"/>
-      <c r="L12" s="222"/>
+      <c r="D12" s="225"/>
+      <c r="E12" s="225"/>
+      <c r="F12" s="225"/>
+      <c r="G12" s="225"/>
+      <c r="H12" s="225"/>
+      <c r="I12" s="225"/>
+      <c r="J12" s="225"/>
+      <c r="K12" s="225"/>
+      <c r="L12" s="225"/>
       <c r="N12" s="93"/>
       <c r="P12" s="231"/>
       <c r="Q12" s="231"/>
@@ -4948,18 +4948,18 @@
       <c r="D17" s="20"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C19" s="222" t="s">
+      <c r="C19" s="225" t="s">
         <v>267</v>
       </c>
-      <c r="D19" s="222"/>
-      <c r="E19" s="222"/>
-      <c r="F19" s="222"/>
-      <c r="G19" s="222"/>
-      <c r="H19" s="222"/>
-      <c r="I19" s="222"/>
-      <c r="J19" s="222"/>
-      <c r="K19" s="222"/>
-      <c r="L19" s="222"/>
+      <c r="D19" s="225"/>
+      <c r="E19" s="225"/>
+      <c r="F19" s="225"/>
+      <c r="G19" s="225"/>
+      <c r="H19" s="225"/>
+      <c r="I19" s="225"/>
+      <c r="J19" s="225"/>
+      <c r="K19" s="225"/>
+      <c r="L19" s="225"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="7" t="s">
@@ -5146,18 +5146,18 @@
       <c r="C25" s="231"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C26" s="222" t="s">
+      <c r="C26" s="225" t="s">
         <v>278</v>
       </c>
-      <c r="D26" s="222"/>
-      <c r="E26" s="222"/>
-      <c r="F26" s="222"/>
-      <c r="G26" s="222"/>
-      <c r="H26" s="222"/>
-      <c r="I26" s="222"/>
-      <c r="J26" s="222"/>
-      <c r="K26" s="222"/>
-      <c r="L26" s="222"/>
+      <c r="D26" s="225"/>
+      <c r="E26" s="225"/>
+      <c r="F26" s="225"/>
+      <c r="G26" s="225"/>
+      <c r="H26" s="225"/>
+      <c r="I26" s="225"/>
+      <c r="J26" s="225"/>
+      <c r="K26" s="225"/>
+      <c r="L26" s="225"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -5401,18 +5401,18 @@
       <c r="G33" s="146"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C34" s="222" t="s">
+      <c r="C34" s="225" t="s">
         <v>279</v>
       </c>
-      <c r="D34" s="222"/>
-      <c r="E34" s="222"/>
-      <c r="F34" s="222"/>
-      <c r="G34" s="222"/>
-      <c r="H34" s="222"/>
-      <c r="I34" s="222"/>
-      <c r="J34" s="222"/>
-      <c r="K34" s="222"/>
-      <c r="L34" s="222"/>
+      <c r="D34" s="225"/>
+      <c r="E34" s="225"/>
+      <c r="F34" s="225"/>
+      <c r="G34" s="225"/>
+      <c r="H34" s="225"/>
+      <c r="I34" s="225"/>
+      <c r="J34" s="225"/>
+      <c r="K34" s="225"/>
+      <c r="L34" s="225"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35" s="7" t="s">
@@ -5634,12 +5634,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="C12:L12"/>
     <mergeCell ref="P12:Z12"/>
@@ -5647,6 +5641,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5685,20 +5685,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="105"/>
-      <c r="C3" s="223" t="s">
+      <c r="C3" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="223"/>
-      <c r="E3" s="223"/>
-      <c r="F3" s="223"/>
-      <c r="G3" s="224"/>
-      <c r="H3" s="225" t="s">
+      <c r="D3" s="226"/>
+      <c r="E3" s="226"/>
+      <c r="F3" s="226"/>
+      <c r="G3" s="229"/>
+      <c r="H3" s="230" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="223"/>
-      <c r="J3" s="223"/>
-      <c r="K3" s="223"/>
-      <c r="L3" s="223"/>
+      <c r="I3" s="226"/>
+      <c r="J3" s="226"/>
+      <c r="K3" s="226"/>
+      <c r="L3" s="226"/>
       <c r="P3" s="231"/>
       <c r="Q3" s="231"/>
       <c r="R3" s="231"/>
@@ -5716,18 +5716,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="110"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="222" t="s">
+      <c r="C5" s="225" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="222"/>
-      <c r="E5" s="222"/>
-      <c r="F5" s="222"/>
-      <c r="G5" s="222"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="222"/>
-      <c r="J5" s="222"/>
-      <c r="K5" s="222"/>
-      <c r="L5" s="222"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="225"/>
+      <c r="F5" s="225"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="225"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
+      <c r="L5" s="225"/>
       <c r="P5" s="231"/>
       <c r="Q5" s="231"/>
       <c r="R5" s="231"/>
@@ -6043,18 +6043,18 @@
       <c r="C12" s="231"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C13" s="222" t="s">
+      <c r="C13" s="225" t="s">
         <v>300</v>
       </c>
-      <c r="D13" s="222"/>
-      <c r="E13" s="222"/>
-      <c r="F13" s="222"/>
-      <c r="G13" s="222"/>
-      <c r="H13" s="222"/>
-      <c r="I13" s="222"/>
-      <c r="J13" s="222"/>
-      <c r="K13" s="222"/>
-      <c r="L13" s="222"/>
+      <c r="D13" s="225"/>
+      <c r="E13" s="225"/>
+      <c r="F13" s="225"/>
+      <c r="G13" s="225"/>
+      <c r="H13" s="225"/>
+      <c r="I13" s="225"/>
+      <c r="J13" s="225"/>
+      <c r="K13" s="225"/>
+      <c r="L13" s="225"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
@@ -6298,18 +6298,18 @@
       <c r="G20" s="146"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C21" s="222" t="s">
+      <c r="C21" s="225" t="s">
         <v>279</v>
       </c>
-      <c r="D21" s="222"/>
-      <c r="E21" s="222"/>
-      <c r="F21" s="222"/>
-      <c r="G21" s="222"/>
-      <c r="H21" s="222"/>
-      <c r="I21" s="222"/>
-      <c r="J21" s="222"/>
-      <c r="K21" s="222"/>
-      <c r="L21" s="222"/>
+      <c r="D21" s="225"/>
+      <c r="E21" s="225"/>
+      <c r="F21" s="225"/>
+      <c r="G21" s="225"/>
+      <c r="H21" s="225"/>
+      <c r="I21" s="225"/>
+      <c r="J21" s="225"/>
+      <c r="K21" s="225"/>
+      <c r="L21" s="225"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
@@ -6598,20 +6598,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="105"/>
-      <c r="C3" s="223" t="s">
+      <c r="C3" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="223"/>
-      <c r="E3" s="223"/>
-      <c r="F3" s="223"/>
-      <c r="G3" s="224"/>
-      <c r="H3" s="225" t="s">
+      <c r="D3" s="226"/>
+      <c r="E3" s="226"/>
+      <c r="F3" s="226"/>
+      <c r="G3" s="229"/>
+      <c r="H3" s="230" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="223"/>
-      <c r="J3" s="223"/>
-      <c r="K3" s="223"/>
-      <c r="L3" s="223"/>
+      <c r="I3" s="226"/>
+      <c r="J3" s="226"/>
+      <c r="K3" s="226"/>
+      <c r="L3" s="226"/>
       <c r="P3" s="231"/>
       <c r="Q3" s="231"/>
       <c r="R3" s="231"/>
@@ -6629,18 +6629,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="110"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="222" t="s">
+      <c r="C5" s="225" t="s">
         <v>312</v>
       </c>
-      <c r="D5" s="222"/>
-      <c r="E5" s="222"/>
-      <c r="F5" s="222"/>
-      <c r="G5" s="222"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="222"/>
-      <c r="J5" s="222"/>
-      <c r="K5" s="222"/>
-      <c r="L5" s="222"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="225"/>
+      <c r="F5" s="225"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="225"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
+      <c r="L5" s="225"/>
       <c r="P5" s="231"/>
       <c r="Q5" s="231"/>
       <c r="R5" s="231"/>
@@ -6837,18 +6837,18 @@
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B11" s="148"/>
-      <c r="C11" s="222" t="s">
+      <c r="C11" s="225" t="s">
         <v>312</v>
       </c>
-      <c r="D11" s="222"/>
-      <c r="E11" s="222"/>
-      <c r="F11" s="222"/>
-      <c r="G11" s="222"/>
-      <c r="H11" s="222"/>
-      <c r="I11" s="222"/>
-      <c r="J11" s="222"/>
-      <c r="K11" s="222"/>
-      <c r="L11" s="222"/>
+      <c r="D11" s="225"/>
+      <c r="E11" s="225"/>
+      <c r="F11" s="225"/>
+      <c r="G11" s="225"/>
+      <c r="H11" s="225"/>
+      <c r="I11" s="225"/>
+      <c r="J11" s="225"/>
+      <c r="K11" s="225"/>
+      <c r="L11" s="225"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B12" s="7" t="s">
@@ -7118,18 +7118,18 @@
       <c r="C19" s="165"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C21" s="222" t="s">
+      <c r="C21" s="225" t="s">
         <v>320</v>
       </c>
-      <c r="D21" s="222"/>
-      <c r="E21" s="222"/>
-      <c r="F21" s="222"/>
-      <c r="G21" s="222"/>
-      <c r="H21" s="222"/>
-      <c r="I21" s="222"/>
-      <c r="J21" s="222"/>
-      <c r="K21" s="222"/>
-      <c r="L21" s="222"/>
+      <c r="D21" s="225"/>
+      <c r="E21" s="225"/>
+      <c r="F21" s="225"/>
+      <c r="G21" s="225"/>
+      <c r="H21" s="225"/>
+      <c r="I21" s="225"/>
+      <c r="J21" s="225"/>
+      <c r="K21" s="225"/>
+      <c r="L21" s="225"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
@@ -7352,10 +7352,10 @@
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B29" s="223" t="s">
+      <c r="B29" s="226" t="s">
         <v>316</v>
       </c>
-      <c r="C29" s="223"/>
+      <c r="C29" s="226"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
@@ -7383,18 +7383,18 @@
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35" s="94"/>
-      <c r="C35" s="222" t="s">
+      <c r="C35" s="225" t="s">
         <v>188</v>
       </c>
-      <c r="D35" s="222"/>
-      <c r="E35" s="222"/>
-      <c r="F35" s="222"/>
-      <c r="G35" s="222"/>
-      <c r="H35" s="222"/>
-      <c r="I35" s="222"/>
-      <c r="J35" s="222"/>
-      <c r="K35" s="222"/>
-      <c r="L35" s="222"/>
+      <c r="D35" s="225"/>
+      <c r="E35" s="225"/>
+      <c r="F35" s="225"/>
+      <c r="G35" s="225"/>
+      <c r="H35" s="225"/>
+      <c r="I35" s="225"/>
+      <c r="J35" s="225"/>
+      <c r="K35" s="225"/>
+      <c r="L35" s="225"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" s="7" t="s">
@@ -7487,18 +7487,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="222" t="s">
+      <c r="C39" s="225" t="s">
         <v>328</v>
       </c>
-      <c r="D39" s="222"/>
-      <c r="E39" s="222"/>
-      <c r="F39" s="222"/>
-      <c r="G39" s="222"/>
-      <c r="H39" s="222"/>
-      <c r="I39" s="222"/>
-      <c r="J39" s="222"/>
-      <c r="K39" s="222"/>
-      <c r="L39" s="222"/>
+      <c r="D39" s="225"/>
+      <c r="E39" s="225"/>
+      <c r="F39" s="225"/>
+      <c r="G39" s="225"/>
+      <c r="H39" s="225"/>
+      <c r="I39" s="225"/>
+      <c r="J39" s="225"/>
+      <c r="K39" s="225"/>
+      <c r="L39" s="225"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="183">
@@ -7633,18 +7633,18 @@
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C44" s="222" t="s">
+      <c r="C44" s="225" t="s">
         <v>330</v>
       </c>
-      <c r="D44" s="222"/>
-      <c r="E44" s="222"/>
-      <c r="F44" s="222"/>
-      <c r="G44" s="222"/>
-      <c r="H44" s="222"/>
-      <c r="I44" s="222"/>
-      <c r="J44" s="222"/>
-      <c r="K44" s="222"/>
-      <c r="L44" s="222"/>
+      <c r="D44" s="225"/>
+      <c r="E44" s="225"/>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="225"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="225"/>
+      <c r="K44" s="225"/>
+      <c r="L44" s="225"/>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="7" t="s">
@@ -7773,18 +7773,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C35:L35"/>
+    <mergeCell ref="C39:L39"/>
+    <mergeCell ref="C44:L44"/>
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="C21:L21"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="C35:L35"/>
-    <mergeCell ref="C39:L39"/>
-    <mergeCell ref="C44:L44"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="C21:L21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7842,20 +7842,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="105"/>
-      <c r="C2" s="223" t="s">
+      <c r="C2" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="224"/>
-      <c r="H2" s="225" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="229"/>
+      <c r="H2" s="230" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="223"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="223"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="226"/>
       <c r="S2" s="231"/>
       <c r="T2" s="231"/>
       <c r="U2" s="231"/>
@@ -7873,18 +7873,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="110"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="222" t="s">
+      <c r="C4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="222"/>
-      <c r="E4" s="222"/>
-      <c r="F4" s="222"/>
-      <c r="G4" s="222"/>
-      <c r="H4" s="222"/>
-      <c r="I4" s="222"/>
-      <c r="J4" s="222"/>
-      <c r="K4" s="222"/>
-      <c r="L4" s="222"/>
+      <c r="D4" s="225"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="225"/>
+      <c r="G4" s="225"/>
+      <c r="H4" s="225"/>
+      <c r="I4" s="225"/>
+      <c r="J4" s="225"/>
+      <c r="K4" s="225"/>
+      <c r="L4" s="225"/>
       <c r="S4" s="231"/>
       <c r="T4" s="231"/>
       <c r="U4" s="231"/>
@@ -8679,18 +8679,18 @@
       <c r="AE17" s="114"/>
     </row>
     <row r="20" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C20" s="222" t="s">
+      <c r="C20" s="225" t="s">
         <v>286</v>
       </c>
-      <c r="D20" s="222"/>
-      <c r="E20" s="222"/>
-      <c r="F20" s="222"/>
-      <c r="G20" s="222"/>
-      <c r="H20" s="222"/>
-      <c r="I20" s="222"/>
-      <c r="J20" s="222"/>
-      <c r="K20" s="222"/>
-      <c r="L20" s="222"/>
+      <c r="D20" s="225"/>
+      <c r="E20" s="225"/>
+      <c r="F20" s="225"/>
+      <c r="G20" s="225"/>
+      <c r="H20" s="225"/>
+      <c r="I20" s="225"/>
+      <c r="J20" s="225"/>
+      <c r="K20" s="225"/>
+      <c r="L20" s="225"/>
     </row>
     <row r="21" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C21" s="62">
@@ -8822,20 +8822,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="105"/>
-      <c r="C2" s="223" t="s">
+      <c r="C2" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="224"/>
-      <c r="H2" s="225" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="229"/>
+      <c r="H2" s="230" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="223"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="223"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="226"/>
       <c r="S2" s="231"/>
       <c r="T2" s="231"/>
       <c r="U2" s="231"/>
@@ -8853,18 +8853,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="110"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="222" t="s">
+      <c r="C4" s="225" t="s">
         <v>268</v>
       </c>
-      <c r="D4" s="222"/>
-      <c r="E4" s="222"/>
-      <c r="F4" s="222"/>
-      <c r="G4" s="222"/>
-      <c r="H4" s="222"/>
-      <c r="I4" s="222"/>
-      <c r="J4" s="222"/>
-      <c r="K4" s="222"/>
-      <c r="L4" s="222"/>
+      <c r="D4" s="225"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="225"/>
+      <c r="G4" s="225"/>
+      <c r="H4" s="225"/>
+      <c r="I4" s="225"/>
+      <c r="J4" s="225"/>
+      <c r="K4" s="225"/>
+      <c r="L4" s="225"/>
       <c r="S4" s="231"/>
       <c r="T4" s="231"/>
       <c r="U4" s="231"/>
@@ -10612,20 +10612,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="105"/>
-      <c r="C2" s="223" t="s">
+      <c r="C2" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="224"/>
-      <c r="H2" s="225" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="229"/>
+      <c r="H2" s="230" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="223"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="223"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="226"/>
       <c r="S2" s="231"/>
       <c r="T2" s="231"/>
       <c r="U2" s="231"/>
@@ -10643,18 +10643,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="110"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="222" t="s">
+      <c r="C4" s="225" t="s">
         <v>269</v>
       </c>
-      <c r="D4" s="222"/>
-      <c r="E4" s="222"/>
-      <c r="F4" s="222"/>
-      <c r="G4" s="222"/>
-      <c r="H4" s="222"/>
-      <c r="I4" s="222"/>
-      <c r="J4" s="222"/>
-      <c r="K4" s="222"/>
-      <c r="L4" s="222"/>
+      <c r="D4" s="225"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="225"/>
+      <c r="G4" s="225"/>
+      <c r="H4" s="225"/>
+      <c r="I4" s="225"/>
+      <c r="J4" s="225"/>
+      <c r="K4" s="225"/>
+      <c r="L4" s="225"/>
       <c r="S4" s="231"/>
       <c r="T4" s="231"/>
       <c r="U4" s="231"/>
@@ -11933,18 +11933,18 @@
       <c r="I27" s="109"/>
     </row>
     <row r="29" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C29" s="222" t="s">
+      <c r="C29" s="225" t="s">
         <v>286</v>
       </c>
-      <c r="D29" s="222"/>
-      <c r="E29" s="222"/>
-      <c r="F29" s="222"/>
-      <c r="G29" s="222"/>
-      <c r="H29" s="222"/>
-      <c r="I29" s="222"/>
-      <c r="J29" s="222"/>
-      <c r="K29" s="222"/>
-      <c r="L29" s="222"/>
+      <c r="D29" s="225"/>
+      <c r="E29" s="225"/>
+      <c r="F29" s="225"/>
+      <c r="G29" s="225"/>
+      <c r="H29" s="225"/>
+      <c r="I29" s="225"/>
+      <c r="J29" s="225"/>
+      <c r="K29" s="225"/>
+      <c r="L29" s="225"/>
     </row>
     <row r="30" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C30" s="62">
@@ -12295,10 +12295,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="223" t="s">
+      <c r="B4" s="226" t="s">
         <v>351</v>
       </c>
-      <c r="C4" s="223"/>
+      <c r="C4" s="226"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="C6" s="190">
         <f>Overview!C3</f>
-        <v>100.51</v>
+        <v>99.84</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="C7" s="192">
         <f>C5*C6</f>
-        <v>4764174</v>
+        <v>4732416</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12378,10 +12378,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="223" t="s">
+      <c r="B15" s="226" t="s">
         <v>357</v>
       </c>
-      <c r="C15" s="223"/>
+      <c r="C15" s="226"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="C16" s="193">
         <f>C8/(C8+C7)</f>
-        <v>1.9304221345904336E-2</v>
+        <v>1.9431249669770907E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="C17" s="193">
         <f>C7/(C8+C7)</f>
-        <v>0.98069577865409563</v>
+        <v>0.98056875033022906</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="C20" s="193">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>8.8544120292230077E-2</v>
+        <v>8.8539722127058684E-2</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -12493,20 +12493,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="105"/>
-      <c r="C3" s="223" t="s">
+      <c r="C3" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="223"/>
-      <c r="E3" s="223"/>
-      <c r="F3" s="223"/>
-      <c r="G3" s="224"/>
-      <c r="H3" s="225" t="s">
+      <c r="D3" s="226"/>
+      <c r="E3" s="226"/>
+      <c r="F3" s="226"/>
+      <c r="G3" s="229"/>
+      <c r="H3" s="230" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="223"/>
-      <c r="J3" s="223"/>
-      <c r="K3" s="223"/>
-      <c r="L3" s="223"/>
+      <c r="I3" s="226"/>
+      <c r="J3" s="226"/>
+      <c r="K3" s="226"/>
+      <c r="L3" s="226"/>
       <c r="P3" s="231"/>
       <c r="Q3" s="231"/>
       <c r="R3" s="231"/>
@@ -12524,18 +12524,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="110"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="222" t="s">
+      <c r="C5" s="225" t="s">
         <v>371</v>
       </c>
-      <c r="D5" s="222"/>
-      <c r="E5" s="222"/>
-      <c r="F5" s="222"/>
-      <c r="G5" s="222"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="222"/>
-      <c r="J5" s="222"/>
-      <c r="K5" s="222"/>
-      <c r="L5" s="222"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="225"/>
+      <c r="F5" s="225"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="225"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
+      <c r="L5" s="225"/>
       <c r="P5" s="231"/>
       <c r="Q5" s="231"/>
       <c r="R5" s="231"/>
@@ -12699,7 +12699,7 @@
       </c>
       <c r="L8" s="167">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>11087170.235534936</v>
+        <v>11087881.694590589</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="7"/>
@@ -12753,23 +12753,23 @@
       <c r="G10" s="195"/>
       <c r="H10" s="167">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>104017.84443747677</v>
+        <v>104018.26471397319</v>
       </c>
       <c r="I10" s="167">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$15)^I9</f>
-        <v>185091.2198832625</v>
+        <v>185092.71558137043</v>
       </c>
       <c r="J10" s="167">
         <f t="shared" ca="1" si="1"/>
-        <v>219017.44649228649</v>
+        <v>219020.10127495785</v>
       </c>
       <c r="K10" s="167">
         <f t="shared" ca="1" si="1"/>
-        <v>320217.00127460668</v>
+        <v>320222.17655951105</v>
       </c>
       <c r="L10" s="167">
         <f t="shared" ca="1" si="1"/>
-        <v>487484.22832794365</v>
+        <v>487494.07662946533</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -12788,14 +12788,14 @@
       <c r="K11" s="160"/>
       <c r="L11" s="167">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>7254216.85732638</v>
+        <v>7254828.9186271532</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="223" t="s">
+      <c r="B13" s="226" t="s">
         <v>372</v>
       </c>
-      <c r="C13" s="223"/>
+      <c r="C13" s="226"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -12811,14 +12811,14 @@
       </c>
       <c r="C15" s="194">
         <f>WACC!C20</f>
-        <v>8.8544120292230077E-2</v>
+        <v>8.8539722127058684E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="223" t="s">
+      <c r="B18" s="226" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="223"/>
+      <c r="C18" s="226"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="C19" s="109">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1315827.7404155761</v>
+        <v>1315847.3347592778</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="C20" s="109">
         <f ca="1">L11</f>
-        <v>7254216.85732638</v>
+        <v>7254828.9186271532</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="C21" s="114">
         <f ca="1">C19+C20</f>
-        <v>8570044.5977419559</v>
+        <v>8570676.2533864304</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="C24" s="114">
         <f ca="1">C21+C22-C23</f>
-        <v>9616732.5977419559</v>
+        <v>9617364.2533864304</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="C26" s="197">
         <f ca="1">C24/C25</f>
-        <v>197.31018749697736</v>
+        <v>197.32314741786297</v>
       </c>
     </row>
   </sheetData>
@@ -12932,37 +12932,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="105"/>
-      <c r="C2" s="223" t="s">
+      <c r="C2" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="224"/>
-      <c r="H2" s="225" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="229"/>
+      <c r="H2" s="230" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="223"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="223"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="226"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="110"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="222" t="s">
+      <c r="C4" s="225" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="222"/>
-      <c r="E4" s="222"/>
-      <c r="F4" s="222"/>
-      <c r="G4" s="222"/>
-      <c r="H4" s="222"/>
-      <c r="I4" s="222"/>
-      <c r="J4" s="222"/>
-      <c r="K4" s="222"/>
-      <c r="L4" s="222"/>
+      <c r="D4" s="225"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="225"/>
+      <c r="G4" s="225"/>
+      <c r="H4" s="225"/>
+      <c r="I4" s="225"/>
+      <c r="J4" s="225"/>
+      <c r="K4" s="225"/>
+      <c r="L4" s="225"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -13105,18 +13105,18 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="222" t="s">
+      <c r="C9" s="225" t="s">
         <v>194</v>
       </c>
-      <c r="D9" s="222"/>
-      <c r="E9" s="222"/>
-      <c r="F9" s="222"/>
-      <c r="G9" s="222"/>
-      <c r="H9" s="222"/>
-      <c r="I9" s="222"/>
-      <c r="J9" s="222"/>
-      <c r="K9" s="222"/>
-      <c r="L9" s="222"/>
+      <c r="D9" s="225"/>
+      <c r="E9" s="225"/>
+      <c r="F9" s="225"/>
+      <c r="G9" s="225"/>
+      <c r="H9" s="225"/>
+      <c r="I9" s="225"/>
+      <c r="J9" s="225"/>
+      <c r="K9" s="225"/>
+      <c r="L9" s="225"/>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -13267,18 +13267,18 @@
       <c r="N13" s="93"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="222" t="s">
+      <c r="C14" s="225" t="s">
         <v>420</v>
       </c>
-      <c r="D14" s="222"/>
-      <c r="E14" s="222"/>
-      <c r="F14" s="222"/>
-      <c r="G14" s="222"/>
-      <c r="H14" s="222"/>
-      <c r="I14" s="222"/>
-      <c r="J14" s="222"/>
-      <c r="K14" s="222"/>
-      <c r="L14" s="222"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="225"/>
+      <c r="F14" s="225"/>
+      <c r="G14" s="225"/>
+      <c r="H14" s="225"/>
+      <c r="I14" s="225"/>
+      <c r="J14" s="225"/>
+      <c r="K14" s="225"/>
+      <c r="L14" s="225"/>
       <c r="N14" s="93"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -13415,10 +13415,10 @@
       <c r="N19" s="93"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="223" t="s">
+      <c r="B20" s="226" t="s">
         <v>388</v>
       </c>
-      <c r="C20" s="223"/>
+      <c r="C20" s="226"/>
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="C22" s="175">
         <f>WACC!C20</f>
-        <v>8.8544120292230077E-2</v>
+        <v>8.8539722127058684E-2</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -13462,7 +13462,7 @@
       </c>
       <c r="C25" s="20">
         <f ca="1">C21/(1+C22)^5</f>
-        <v>375721.64025903627</v>
+        <v>375729.23069947812</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
@@ -13471,14 +13471,14 @@
       </c>
       <c r="C26" s="197">
         <f ca="1">C25/C24*C23</f>
-        <v>171.00409106744192</v>
+        <v>171.0075457430035</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B28" s="223" t="s">
+      <c r="B28" s="226" t="s">
         <v>391</v>
       </c>
-      <c r="C28" s="223"/>
+      <c r="C28" s="226"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="C30" s="175">
         <f>WACC!C20</f>
-        <v>8.8544120292230077E-2</v>
+        <v>8.8539722127058684E-2</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="C33" s="20">
         <f>C29/(1+C30)^5</f>
-        <v>2501911.956647926</v>
+        <v>2501962.5010181805</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.2">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="C34" s="197">
         <f>C33/C32*C31</f>
-        <v>159.41909858993694</v>
+        <v>159.42231922203126</v>
       </c>
     </row>
   </sheetData>
@@ -13576,10 +13576,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="223" t="s">
+      <c r="B4" s="226" t="s">
         <v>401</v>
       </c>
-      <c r="C4" s="223"/>
+      <c r="C4" s="226"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="C5" s="212">
         <f ca="1">DCF!C26</f>
-        <v>197.31018749697736</v>
+        <v>197.32314741786297</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -13597,7 +13597,7 @@
       </c>
       <c r="C6" s="212">
         <f ca="1">'PE and PS'!C26</f>
-        <v>171.00409106744192</v>
+        <v>171.0075457430035</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="C7" s="212">
         <f>'PE and PS'!C34</f>
-        <v>159.41909858993694</v>
+        <v>159.42231922203126</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="C8" s="197">
         <f ca="1">AVERAGE(C5:C7)</f>
-        <v>175.91112571811877</v>
+        <v>175.91767079429926</v>
       </c>
     </row>
   </sheetData>
@@ -18181,11 +18181,11 @@
         <v>86</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="226" t="s">
+      <c r="P4" s="222" t="s">
         <v>87</v>
       </c>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="228"/>
+      <c r="Q4" s="223"/>
+      <c r="R4" s="224"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -28540,36 +28540,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="105"/>
-      <c r="C2" s="223" t="s">
+      <c r="C2" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="224"/>
-      <c r="H2" s="225" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="229"/>
+      <c r="H2" s="230" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="223"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="223"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="226"/>
       <c r="O2" s="92"/>
-      <c r="S2" s="223" t="s">
+      <c r="S2" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="T2" s="223"/>
-      <c r="U2" s="223"/>
-      <c r="V2" s="223"/>
-      <c r="W2" s="223"/>
-      <c r="X2" s="223"/>
-      <c r="Y2" s="223"/>
-      <c r="Z2" s="223"/>
-      <c r="AA2" s="223" t="s">
+      <c r="T2" s="226"/>
+      <c r="U2" s="226"/>
+      <c r="V2" s="226"/>
+      <c r="W2" s="226"/>
+      <c r="X2" s="226"/>
+      <c r="Y2" s="226"/>
+      <c r="Z2" s="226"/>
+      <c r="AA2" s="226" t="s">
         <v>179</v>
       </c>
-      <c r="AB2" s="223"/>
-      <c r="AC2" s="223"/>
+      <c r="AB2" s="226"/>
+      <c r="AC2" s="226"/>
       <c r="AE2" s="129" t="s">
         <v>86</v>
       </c>
@@ -28580,32 +28580,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="110"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="222" t="s">
+      <c r="C4" s="225" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="222"/>
-      <c r="E4" s="222"/>
-      <c r="F4" s="222"/>
-      <c r="G4" s="222"/>
-      <c r="H4" s="222"/>
-      <c r="I4" s="222"/>
-      <c r="J4" s="222"/>
-      <c r="K4" s="222"/>
-      <c r="L4" s="222"/>
+      <c r="D4" s="225"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="225"/>
+      <c r="G4" s="225"/>
+      <c r="H4" s="225"/>
+      <c r="I4" s="225"/>
+      <c r="J4" s="225"/>
+      <c r="K4" s="225"/>
+      <c r="L4" s="225"/>
       <c r="O4" s="92"/>
-      <c r="S4" s="229" t="s">
+      <c r="S4" s="227" t="s">
         <v>188</v>
       </c>
-      <c r="T4" s="230"/>
-      <c r="U4" s="230"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="230"/>
-      <c r="X4" s="230"/>
-      <c r="Y4" s="230"/>
-      <c r="Z4" s="230"/>
-      <c r="AA4" s="230"/>
-      <c r="AB4" s="230"/>
-      <c r="AC4" s="230"/>
+      <c r="T4" s="228"/>
+      <c r="U4" s="228"/>
+      <c r="V4" s="228"/>
+      <c r="W4" s="228"/>
+      <c r="X4" s="228"/>
+      <c r="Y4" s="228"/>
+      <c r="Z4" s="228"/>
+      <c r="AA4" s="228"/>
+      <c r="AB4" s="228"/>
+      <c r="AC4" s="228"/>
       <c r="AE4" s="141" t="s">
         <v>213</v>
       </c>
@@ -29401,33 +29401,33 @@
       <c r="Q13" s="93"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C14" s="222" t="s">
+      <c r="C14" s="225" t="s">
         <v>194</v>
       </c>
-      <c r="D14" s="222"/>
-      <c r="E14" s="222"/>
-      <c r="F14" s="222"/>
-      <c r="G14" s="222"/>
-      <c r="H14" s="222"/>
-      <c r="I14" s="222"/>
-      <c r="J14" s="222"/>
-      <c r="K14" s="222"/>
-      <c r="L14" s="222"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="225"/>
+      <c r="F14" s="225"/>
+      <c r="G14" s="225"/>
+      <c r="H14" s="225"/>
+      <c r="I14" s="225"/>
+      <c r="J14" s="225"/>
+      <c r="K14" s="225"/>
+      <c r="L14" s="225"/>
       <c r="O14" s="92"/>
       <c r="Q14" s="93"/>
-      <c r="S14" s="229" t="s">
+      <c r="S14" s="227" t="s">
         <v>194</v>
       </c>
-      <c r="T14" s="230"/>
-      <c r="U14" s="230"/>
-      <c r="V14" s="230"/>
-      <c r="W14" s="230"/>
-      <c r="X14" s="230"/>
-      <c r="Y14" s="230"/>
-      <c r="Z14" s="230"/>
-      <c r="AA14" s="230"/>
-      <c r="AB14" s="230"/>
-      <c r="AC14" s="230"/>
+      <c r="T14" s="228"/>
+      <c r="U14" s="228"/>
+      <c r="V14" s="228"/>
+      <c r="W14" s="228"/>
+      <c r="X14" s="228"/>
+      <c r="Y14" s="228"/>
+      <c r="Z14" s="228"/>
+      <c r="AA14" s="228"/>
+      <c r="AB14" s="228"/>
+      <c r="AC14" s="228"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B15" s="7" t="s">
@@ -30120,33 +30120,33 @@
       <c r="Q24" s="93"/>
     </row>
     <row r="25" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C25" s="222" t="s">
+      <c r="C25" s="225" t="s">
         <v>196</v>
       </c>
-      <c r="D25" s="222"/>
-      <c r="E25" s="222"/>
-      <c r="F25" s="222"/>
-      <c r="G25" s="222"/>
-      <c r="H25" s="222"/>
-      <c r="I25" s="222"/>
-      <c r="J25" s="222"/>
-      <c r="K25" s="222"/>
-      <c r="L25" s="222"/>
+      <c r="D25" s="225"/>
+      <c r="E25" s="225"/>
+      <c r="F25" s="225"/>
+      <c r="G25" s="225"/>
+      <c r="H25" s="225"/>
+      <c r="I25" s="225"/>
+      <c r="J25" s="225"/>
+      <c r="K25" s="225"/>
+      <c r="L25" s="225"/>
       <c r="O25" s="92"/>
       <c r="Q25" s="93"/>
-      <c r="S25" s="229" t="s">
+      <c r="S25" s="227" t="s">
         <v>196</v>
       </c>
-      <c r="T25" s="230"/>
-      <c r="U25" s="230"/>
-      <c r="V25" s="230"/>
-      <c r="W25" s="230"/>
-      <c r="X25" s="230"/>
-      <c r="Y25" s="230"/>
-      <c r="Z25" s="230"/>
-      <c r="AA25" s="230"/>
-      <c r="AB25" s="230"/>
-      <c r="AC25" s="230"/>
+      <c r="T25" s="228"/>
+      <c r="U25" s="228"/>
+      <c r="V25" s="228"/>
+      <c r="W25" s="228"/>
+      <c r="X25" s="228"/>
+      <c r="Y25" s="228"/>
+      <c r="Z25" s="228"/>
+      <c r="AA25" s="228"/>
+      <c r="AB25" s="228"/>
+      <c r="AC25" s="228"/>
       <c r="AE25" s="141" t="str">
         <f>AE4</f>
         <v>Q1-Q2-Q3</v>
@@ -31469,32 +31469,32 @@
       <c r="O42" s="92"/>
     </row>
     <row r="43" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C43" s="222" t="s">
+      <c r="C43" s="225" t="s">
         <v>208</v>
       </c>
-      <c r="D43" s="222"/>
-      <c r="E43" s="222"/>
-      <c r="F43" s="222"/>
-      <c r="G43" s="222"/>
-      <c r="H43" s="222"/>
-      <c r="I43" s="222"/>
-      <c r="J43" s="222"/>
-      <c r="K43" s="222"/>
-      <c r="L43" s="222"/>
+      <c r="D43" s="225"/>
+      <c r="E43" s="225"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="225"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="225"/>
+      <c r="K43" s="225"/>
+      <c r="L43" s="225"/>
       <c r="O43" s="92"/>
-      <c r="S43" s="229" t="s">
+      <c r="S43" s="227" t="s">
         <v>208</v>
       </c>
-      <c r="T43" s="230"/>
-      <c r="U43" s="230"/>
-      <c r="V43" s="230"/>
-      <c r="W43" s="230"/>
-      <c r="X43" s="230"/>
-      <c r="Y43" s="230"/>
-      <c r="Z43" s="230"/>
-      <c r="AA43" s="230"/>
-      <c r="AB43" s="230"/>
-      <c r="AC43" s="230"/>
+      <c r="T43" s="228"/>
+      <c r="U43" s="228"/>
+      <c r="V43" s="228"/>
+      <c r="W43" s="228"/>
+      <c r="X43" s="228"/>
+      <c r="Y43" s="228"/>
+      <c r="Z43" s="228"/>
+      <c r="AA43" s="228"/>
+      <c r="AB43" s="228"/>
+      <c r="AC43" s="228"/>
     </row>
     <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B44" s="7" t="s">
@@ -32110,35 +32110,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="105"/>
-      <c r="C2" s="223" t="s">
+      <c r="C2" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="224"/>
-      <c r="H2" s="225" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="229"/>
+      <c r="H2" s="230" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="223"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="223"/>
-      <c r="P2" s="223" t="s">
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="226"/>
+      <c r="P2" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="Q2" s="223"/>
-      <c r="R2" s="223"/>
-      <c r="S2" s="223"/>
-      <c r="T2" s="223"/>
-      <c r="U2" s="223"/>
-      <c r="V2" s="223"/>
-      <c r="W2" s="223"/>
-      <c r="X2" s="223" t="s">
+      <c r="Q2" s="226"/>
+      <c r="R2" s="226"/>
+      <c r="S2" s="226"/>
+      <c r="T2" s="226"/>
+      <c r="U2" s="226"/>
+      <c r="V2" s="226"/>
+      <c r="W2" s="226"/>
+      <c r="X2" s="226" t="s">
         <v>179</v>
       </c>
-      <c r="Y2" s="223"/>
-      <c r="Z2" s="223"/>
+      <c r="Y2" s="226"/>
+      <c r="Z2" s="226"/>
       <c r="AB2" s="129" t="s">
         <v>86</v>
       </c>
@@ -32147,31 +32147,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="110"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="222" t="s">
+      <c r="C4" s="225" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="222"/>
-      <c r="E4" s="222"/>
-      <c r="F4" s="222"/>
-      <c r="G4" s="222"/>
-      <c r="H4" s="222"/>
-      <c r="I4" s="222"/>
-      <c r="J4" s="222"/>
-      <c r="K4" s="222"/>
-      <c r="L4" s="222"/>
-      <c r="P4" s="230" t="s">
+      <c r="D4" s="225"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="225"/>
+      <c r="G4" s="225"/>
+      <c r="H4" s="225"/>
+      <c r="I4" s="225"/>
+      <c r="J4" s="225"/>
+      <c r="K4" s="225"/>
+      <c r="L4" s="225"/>
+      <c r="P4" s="228" t="s">
         <v>188</v>
       </c>
-      <c r="Q4" s="230"/>
-      <c r="R4" s="230"/>
-      <c r="S4" s="230"/>
-      <c r="T4" s="230"/>
-      <c r="U4" s="230"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="230"/>
-      <c r="X4" s="230"/>
-      <c r="Y4" s="230"/>
-      <c r="Z4" s="230"/>
+      <c r="Q4" s="228"/>
+      <c r="R4" s="228"/>
+      <c r="S4" s="228"/>
+      <c r="T4" s="228"/>
+      <c r="U4" s="228"/>
+      <c r="V4" s="228"/>
+      <c r="W4" s="228"/>
+      <c r="X4" s="228"/>
+      <c r="Y4" s="228"/>
+      <c r="Z4" s="228"/>
       <c r="AB4" s="141" t="s">
         <v>213</v>
       </c>
@@ -32372,32 +32372,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="222" t="s">
+      <c r="C9" s="225" t="s">
         <v>215</v>
       </c>
-      <c r="D9" s="222"/>
-      <c r="E9" s="222"/>
-      <c r="F9" s="222"/>
-      <c r="G9" s="222"/>
-      <c r="H9" s="222"/>
-      <c r="I9" s="222"/>
-      <c r="J9" s="222"/>
-      <c r="K9" s="222"/>
-      <c r="L9" s="222"/>
+      <c r="D9" s="225"/>
+      <c r="E9" s="225"/>
+      <c r="F9" s="225"/>
+      <c r="G9" s="225"/>
+      <c r="H9" s="225"/>
+      <c r="I9" s="225"/>
+      <c r="J9" s="225"/>
+      <c r="K9" s="225"/>
+      <c r="L9" s="225"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="230" t="s">
+      <c r="P9" s="228" t="s">
         <v>220</v>
       </c>
-      <c r="Q9" s="230"/>
-      <c r="R9" s="230"/>
-      <c r="S9" s="230"/>
-      <c r="T9" s="230"/>
-      <c r="U9" s="230"/>
-      <c r="V9" s="230"/>
-      <c r="W9" s="230"/>
-      <c r="X9" s="230"/>
-      <c r="Y9" s="230"/>
-      <c r="Z9" s="230"/>
+      <c r="Q9" s="228"/>
+      <c r="R9" s="228"/>
+      <c r="S9" s="228"/>
+      <c r="T9" s="228"/>
+      <c r="U9" s="228"/>
+      <c r="V9" s="228"/>
+      <c r="W9" s="228"/>
+      <c r="X9" s="228"/>
+      <c r="Y9" s="228"/>
+      <c r="Z9" s="228"/>
       <c r="AB9" s="141" t="str">
         <f>AB4</f>
         <v>Q1-Q2-Q3</v>
@@ -32959,31 +32959,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="222" t="s">
+      <c r="C18" s="225" t="s">
         <v>218</v>
       </c>
-      <c r="D18" s="222"/>
-      <c r="E18" s="222"/>
-      <c r="F18" s="222"/>
-      <c r="G18" s="222"/>
-      <c r="H18" s="222"/>
-      <c r="I18" s="222"/>
-      <c r="J18" s="222"/>
-      <c r="K18" s="222"/>
-      <c r="L18" s="222"/>
-      <c r="P18" s="230" t="s">
+      <c r="D18" s="225"/>
+      <c r="E18" s="225"/>
+      <c r="F18" s="225"/>
+      <c r="G18" s="225"/>
+      <c r="H18" s="225"/>
+      <c r="I18" s="225"/>
+      <c r="J18" s="225"/>
+      <c r="K18" s="225"/>
+      <c r="L18" s="225"/>
+      <c r="P18" s="228" t="s">
         <v>218</v>
       </c>
-      <c r="Q18" s="230"/>
-      <c r="R18" s="230"/>
-      <c r="S18" s="230"/>
-      <c r="T18" s="230"/>
-      <c r="U18" s="230"/>
-      <c r="V18" s="230"/>
-      <c r="W18" s="230"/>
-      <c r="X18" s="230"/>
-      <c r="Y18" s="230"/>
-      <c r="Z18" s="230"/>
+      <c r="Q18" s="228"/>
+      <c r="R18" s="228"/>
+      <c r="S18" s="228"/>
+      <c r="T18" s="228"/>
+      <c r="U18" s="228"/>
+      <c r="V18" s="228"/>
+      <c r="W18" s="228"/>
+      <c r="X18" s="228"/>
+      <c r="Y18" s="228"/>
+      <c r="Z18" s="228"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -33468,20 +33468,20 @@
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
-      <c r="C5" s="223" t="s">
+      <c r="C5" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="223"/>
-      <c r="G5" s="224"/>
-      <c r="H5" s="225" t="s">
+      <c r="D5" s="226"/>
+      <c r="E5" s="226"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="230" t="s">
         <v>179</v>
       </c>
-      <c r="I5" s="223"/>
-      <c r="J5" s="223"/>
-      <c r="K5" s="223"/>
-      <c r="L5" s="223"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="226"/>
+      <c r="K5" s="226"/>
+      <c r="L5" s="226"/>
       <c r="P5" s="231"/>
       <c r="Q5" s="231"/>
       <c r="R5" s="231"/>
@@ -33499,18 +33499,18 @@
     <row r="7" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="110"/>
       <c r="B7" s="94"/>
-      <c r="C7" s="222" t="s">
+      <c r="C7" s="225" t="s">
         <v>188</v>
       </c>
-      <c r="D7" s="222"/>
-      <c r="E7" s="222"/>
-      <c r="F7" s="222"/>
-      <c r="G7" s="222"/>
-      <c r="H7" s="222"/>
-      <c r="I7" s="222"/>
-      <c r="J7" s="222"/>
-      <c r="K7" s="222"/>
-      <c r="L7" s="222"/>
+      <c r="D7" s="225"/>
+      <c r="E7" s="225"/>
+      <c r="F7" s="225"/>
+      <c r="G7" s="225"/>
+      <c r="H7" s="225"/>
+      <c r="I7" s="225"/>
+      <c r="J7" s="225"/>
+      <c r="K7" s="225"/>
+      <c r="L7" s="225"/>
       <c r="P7" s="231"/>
       <c r="Q7" s="231"/>
       <c r="R7" s="231"/>
@@ -33648,18 +33648,18 @@
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C12" s="222" t="s">
+      <c r="C12" s="225" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="222"/>
-      <c r="E12" s="222"/>
-      <c r="F12" s="222"/>
-      <c r="G12" s="222"/>
-      <c r="H12" s="222"/>
-      <c r="I12" s="222"/>
-      <c r="J12" s="222"/>
-      <c r="K12" s="222"/>
-      <c r="L12" s="222"/>
+      <c r="D12" s="225"/>
+      <c r="E12" s="225"/>
+      <c r="F12" s="225"/>
+      <c r="G12" s="225"/>
+      <c r="H12" s="225"/>
+      <c r="I12" s="225"/>
+      <c r="J12" s="225"/>
+      <c r="K12" s="225"/>
+      <c r="L12" s="225"/>
       <c r="N12" s="93"/>
       <c r="P12" s="231"/>
       <c r="Q12" s="231"/>
@@ -33973,18 +33973,18 @@
       <c r="D18" s="20"/>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C20" s="222" t="s">
+      <c r="C20" s="225" t="s">
         <v>247</v>
       </c>
-      <c r="D20" s="222"/>
-      <c r="E20" s="222"/>
-      <c r="F20" s="222"/>
-      <c r="G20" s="222"/>
-      <c r="H20" s="222"/>
-      <c r="I20" s="222"/>
-      <c r="J20" s="222"/>
-      <c r="K20" s="222"/>
-      <c r="L20" s="222"/>
+      <c r="D20" s="225"/>
+      <c r="E20" s="225"/>
+      <c r="F20" s="225"/>
+      <c r="G20" s="225"/>
+      <c r="H20" s="225"/>
+      <c r="I20" s="225"/>
+      <c r="J20" s="225"/>
+      <c r="K20" s="225"/>
+      <c r="L20" s="225"/>
       <c r="P20" s="231"/>
       <c r="Q20" s="231"/>
       <c r="R20" s="231"/>
@@ -34250,18 +34250,18 @@
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C30" s="222" t="s">
+      <c r="C30" s="225" t="s">
         <v>237</v>
       </c>
-      <c r="D30" s="222"/>
-      <c r="E30" s="222"/>
-      <c r="F30" s="222"/>
-      <c r="G30" s="222"/>
-      <c r="H30" s="222"/>
-      <c r="I30" s="222"/>
-      <c r="J30" s="222"/>
-      <c r="K30" s="222"/>
-      <c r="L30" s="222"/>
+      <c r="D30" s="225"/>
+      <c r="E30" s="225"/>
+      <c r="F30" s="225"/>
+      <c r="G30" s="225"/>
+      <c r="H30" s="225"/>
+      <c r="I30" s="225"/>
+      <c r="J30" s="225"/>
+      <c r="K30" s="225"/>
+      <c r="L30" s="225"/>
     </row>
     <row r="31" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
@@ -34489,10 +34489,10 @@
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B37" s="223" t="s">
+      <c r="B37" s="226" t="s">
         <v>239</v>
       </c>
-      <c r="C37" s="223"/>
+      <c r="C37" s="226"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
@@ -34512,13 +34512,13 @@
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B42" s="7"/>
-      <c r="C42" s="223" t="s">
+      <c r="C42" s="226" t="s">
         <v>238</v>
       </c>
-      <c r="D42" s="223"/>
-      <c r="E42" s="223"/>
-      <c r="F42" s="223"/>
-      <c r="G42" s="223"/>
+      <c r="D42" s="226"/>
+      <c r="E42" s="226"/>
+      <c r="F42" s="226"/>
+      <c r="G42" s="226"/>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="7" t="s">
@@ -34648,10 +34648,10 @@
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B50" s="223" t="s">
+      <c r="B50" s="226" t="s">
         <v>243</v>
       </c>
-      <c r="C50" s="223"/>
+      <c r="C50" s="226"/>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
@@ -34682,12 +34682,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="P5:W5"/>
-    <mergeCell ref="X5:Z5"/>
-    <mergeCell ref="C7:L7"/>
-    <mergeCell ref="P7:Z7"/>
     <mergeCell ref="B50:C50"/>
     <mergeCell ref="C12:L12"/>
     <mergeCell ref="P12:Z12"/>
@@ -34696,6 +34690,12 @@
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="C42:G42"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="P5:W5"/>
+    <mergeCell ref="X5:Z5"/>
+    <mergeCell ref="C7:L7"/>
+    <mergeCell ref="P7:Z7"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{7B0EB6A4-3658-0541-ACD6-B6D16EB047D2}">

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D36DC1-81D7-114C-B440-89E9756B74C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007E8E21-4A4E-7E45-9632-889550CC8448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="4" activeTab="13" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="13" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -215,7 +215,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="352">
   <si>
     <t>Date</t>
   </si>
@@ -1813,7 +1813,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2065,6 +2065,23 @@
     <xf numFmtId="2" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="1" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2074,25 +2091,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2126,7 +2128,6 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
-      <sheetName val="1. List_AutomaticData"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -2136,7 +2137,6 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2599,7 +2599,7 @@
         <v>85</v>
       </c>
       <c r="C3" s="35">
-        <f>[1]Sheet1!$C$4</f>
+        <f ca="1">[1]Sheet1!$C$4</f>
         <v>103.45</v>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>183</v>
       </c>
       <c r="C11" s="95">
-        <f>$C$3/'Statement Q'!$N$22</f>
+        <f ca="1">$C$3/'Statement Q'!$N$22</f>
         <v>12.176991527853712</v>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
         <v>285</v>
       </c>
       <c r="C12" s="95">
-        <f>C3/Statements!S20</f>
+        <f ca="1">C3/Statements!S20</f>
         <v>30.3016268608865</v>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
         <v>184</v>
       </c>
       <c r="C13" s="102">
-        <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$20)</f>
+        <f ca="1">$C$3/('Statement Q'!$N$5/'Statement Q'!$N$20)</f>
         <v>4.8594057926411587</v>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
         <v>242</v>
       </c>
       <c r="C15" s="20">
-        <f>C3*'Statement Q'!N116</f>
+        <f ca="1">C3*'Statement Q'!N116</f>
         <v>4903530</v>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
         <v>244</v>
       </c>
       <c r="C18" s="20">
-        <f>C15+C17-C16</f>
+        <f ca="1">C15+C17-C16</f>
         <v>3763063</v>
       </c>
     </row>
@@ -2882,60 +2882,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="209" t="s">
+      <c r="C2" s="208" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="212"/>
-      <c r="H2" s="213" t="s">
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="209"/>
+      <c r="H2" s="210" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="209"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="209"/>
-      <c r="S2" s="214"/>
-      <c r="T2" s="214"/>
-      <c r="U2" s="214"/>
-      <c r="V2" s="214"/>
-      <c r="W2" s="214"/>
-      <c r="X2" s="214"/>
-      <c r="Y2" s="214"/>
-      <c r="Z2" s="214"/>
-      <c r="AA2" s="214"/>
-      <c r="AB2" s="214"/>
-      <c r="AC2" s="214"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="211"/>
+      <c r="U2" s="211"/>
+      <c r="V2" s="211"/>
+      <c r="W2" s="211"/>
+      <c r="X2" s="211"/>
+      <c r="Y2" s="211"/>
+      <c r="Z2" s="211"/>
+      <c r="AA2" s="211"/>
+      <c r="AB2" s="211"/>
+      <c r="AC2" s="211"/>
       <c r="AE2" s="143"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="208" t="s">
+      <c r="C4" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
-      <c r="L4" s="208"/>
-      <c r="S4" s="214"/>
-      <c r="T4" s="214"/>
-      <c r="U4" s="214"/>
-      <c r="V4" s="214"/>
-      <c r="W4" s="214"/>
-      <c r="X4" s="214"/>
-      <c r="Y4" s="214"/>
-      <c r="Z4" s="214"/>
-      <c r="AA4" s="214"/>
-      <c r="AB4" s="214"/>
-      <c r="AC4" s="214"/>
+      <c r="D4" s="207"/>
+      <c r="E4" s="207"/>
+      <c r="F4" s="207"/>
+      <c r="G4" s="207"/>
+      <c r="H4" s="207"/>
+      <c r="I4" s="207"/>
+      <c r="J4" s="207"/>
+      <c r="K4" s="207"/>
+      <c r="L4" s="207"/>
+      <c r="S4" s="211"/>
+      <c r="T4" s="211"/>
+      <c r="U4" s="211"/>
+      <c r="V4" s="211"/>
+      <c r="W4" s="211"/>
+      <c r="X4" s="211"/>
+      <c r="Y4" s="211"/>
+      <c r="Z4" s="211"/>
+      <c r="AA4" s="211"/>
+      <c r="AB4" s="211"/>
+      <c r="AC4" s="211"/>
       <c r="AE4" s="144"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -3481,18 +3481,18 @@
       <c r="AE13" s="108"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C16" s="208" t="s">
+      <c r="C16" s="207" t="s">
         <v>236</v>
       </c>
-      <c r="D16" s="208"/>
-      <c r="E16" s="208"/>
-      <c r="F16" s="208"/>
-      <c r="G16" s="208"/>
-      <c r="H16" s="208"/>
-      <c r="I16" s="208"/>
-      <c r="J16" s="208"/>
-      <c r="K16" s="208"/>
-      <c r="L16" s="208"/>
+      <c r="D16" s="207"/>
+      <c r="E16" s="207"/>
+      <c r="F16" s="207"/>
+      <c r="G16" s="207"/>
+      <c r="H16" s="207"/>
+      <c r="I16" s="207"/>
+      <c r="J16" s="207"/>
+      <c r="K16" s="207"/>
+      <c r="L16" s="207"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C17" s="62">
@@ -3576,18 +3576,18 @@
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="208" t="s">
+      <c r="C21" s="207" t="s">
         <v>331</v>
       </c>
-      <c r="D21" s="208"/>
-      <c r="E21" s="208"/>
-      <c r="F21" s="208"/>
-      <c r="G21" s="208"/>
-      <c r="H21" s="208"/>
-      <c r="I21" s="208"/>
-      <c r="J21" s="208"/>
-      <c r="K21" s="208"/>
-      <c r="L21" s="208"/>
+      <c r="D21" s="207"/>
+      <c r="E21" s="207"/>
+      <c r="F21" s="207"/>
+      <c r="G21" s="207"/>
+      <c r="H21" s="207"/>
+      <c r="I21" s="207"/>
+      <c r="J21" s="207"/>
+      <c r="K21" s="207"/>
+      <c r="L21" s="207"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
@@ -3779,18 +3779,18 @@
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C28" s="208" t="s">
+      <c r="C28" s="207" t="s">
         <v>238</v>
       </c>
-      <c r="D28" s="208"/>
-      <c r="E28" s="208"/>
-      <c r="F28" s="208"/>
-      <c r="G28" s="208"/>
-      <c r="H28" s="208"/>
-      <c r="I28" s="208"/>
-      <c r="J28" s="208"/>
-      <c r="K28" s="208"/>
-      <c r="L28" s="208"/>
+      <c r="D28" s="207"/>
+      <c r="E28" s="207"/>
+      <c r="F28" s="207"/>
+      <c r="G28" s="207"/>
+      <c r="H28" s="207"/>
+      <c r="I28" s="207"/>
+      <c r="J28" s="207"/>
+      <c r="K28" s="207"/>
+      <c r="L28" s="207"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
@@ -3929,7 +3929,6 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C21:L21"/>
     <mergeCell ref="C28:L28"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
@@ -3938,6 +3937,7 @@
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C16:L16"/>
+    <mergeCell ref="C21:L21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="208" t="s">
         <v>255</v>
       </c>
-      <c r="C4" s="209"/>
+      <c r="C4" s="208"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4016,7 +4016,7 @@
         <v>85</v>
       </c>
       <c r="C6" s="166">
-        <f>Overview!C3</f>
+        <f ca="1">Overview!C3</f>
         <v>103.45</v>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
         <v>240</v>
       </c>
       <c r="C7" s="168">
-        <f>C5*C6</f>
+        <f ca="1">C5*C6</f>
         <v>4903530</v>
       </c>
     </row>
@@ -4079,17 +4079,17 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="209" t="s">
+      <c r="B15" s="208" t="s">
         <v>261</v>
       </c>
-      <c r="C15" s="209"/>
+      <c r="C15" s="208"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>252</v>
       </c>
       <c r="C16" s="169">
-        <f>C8/(C8+C7)</f>
+        <f ca="1">C8/(C8+C7)</f>
         <v>0</v>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
         <v>253</v>
       </c>
       <c r="C17" s="169">
-        <f>C7/(C8+C7)</f>
+        <f ca="1">C7/(C8+C7)</f>
         <v>1</v>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
         <v>251</v>
       </c>
       <c r="C20" s="169">
-        <f>(C17*C19)+(C16*C18)</f>
+        <f ca="1">(C17*C19)+(C16*C18)</f>
         <v>8.92125E-2</v>
       </c>
     </row>
@@ -4173,60 +4173,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="104"/>
-      <c r="C3" s="209" t="s">
+      <c r="C3" s="208" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="209"/>
-      <c r="E3" s="209"/>
-      <c r="F3" s="209"/>
-      <c r="G3" s="212"/>
-      <c r="H3" s="213" t="s">
+      <c r="D3" s="208"/>
+      <c r="E3" s="208"/>
+      <c r="F3" s="208"/>
+      <c r="G3" s="209"/>
+      <c r="H3" s="210" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="209"/>
-      <c r="J3" s="209"/>
-      <c r="K3" s="209"/>
-      <c r="L3" s="209"/>
-      <c r="P3" s="214"/>
-      <c r="Q3" s="214"/>
-      <c r="R3" s="214"/>
-      <c r="S3" s="214"/>
-      <c r="T3" s="214"/>
-      <c r="U3" s="214"/>
-      <c r="V3" s="214"/>
-      <c r="W3" s="214"/>
-      <c r="X3" s="214"/>
-      <c r="Y3" s="214"/>
-      <c r="Z3" s="214"/>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
+      <c r="L3" s="208"/>
+      <c r="P3" s="211"/>
+      <c r="Q3" s="211"/>
+      <c r="R3" s="211"/>
+      <c r="S3" s="211"/>
+      <c r="T3" s="211"/>
+      <c r="U3" s="211"/>
+      <c r="V3" s="211"/>
+      <c r="W3" s="211"/>
+      <c r="X3" s="211"/>
+      <c r="Y3" s="211"/>
+      <c r="Z3" s="211"/>
       <c r="AB3" s="143"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="109"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="208" t="s">
+      <c r="C5" s="207" t="s">
         <v>275</v>
       </c>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="208"/>
-      <c r="K5" s="208"/>
-      <c r="L5" s="208"/>
-      <c r="P5" s="214"/>
-      <c r="Q5" s="214"/>
-      <c r="R5" s="214"/>
-      <c r="S5" s="214"/>
-      <c r="T5" s="214"/>
-      <c r="U5" s="214"/>
-      <c r="V5" s="214"/>
-      <c r="W5" s="214"/>
-      <c r="X5" s="214"/>
-      <c r="Y5" s="214"/>
-      <c r="Z5" s="214"/>
+      <c r="D5" s="207"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="207"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="207"/>
+      <c r="I5" s="207"/>
+      <c r="J5" s="207"/>
+      <c r="K5" s="207"/>
+      <c r="L5" s="207"/>
+      <c r="P5" s="211"/>
+      <c r="Q5" s="211"/>
+      <c r="R5" s="211"/>
+      <c r="S5" s="211"/>
+      <c r="T5" s="211"/>
+      <c r="U5" s="211"/>
+      <c r="V5" s="211"/>
+      <c r="W5" s="211"/>
+      <c r="X5" s="211"/>
+      <c r="Y5" s="211"/>
+      <c r="Z5" s="211"/>
       <c r="AB5" s="144"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4378,7 +4378,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="154">
-        <f>L7*(1+C14)/(C15-C14)</f>
+        <f ca="1">L7*(1+C14)/(C15-C14)</f>
         <v>9769189.6342976131</v>
       </c>
       <c r="N8" s="93"/>
@@ -4432,23 +4432,23 @@
       <c r="F10" s="151"/>
       <c r="G10" s="171"/>
       <c r="H10" s="154">
-        <f>H7/(1+$C$15)^H9</f>
+        <f ca="1">H7/(1+$C$15)^H9</f>
         <v>142663.24731757896</v>
       </c>
       <c r="I10" s="154">
-        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$15)^I9</f>
+        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$15)^I9</f>
         <v>215054.65665710828</v>
       </c>
       <c r="J10" s="154">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>253165.64877963354</v>
       </c>
       <c r="K10" s="154">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>292974.83315485454</v>
       </c>
       <c r="L10" s="154">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>432394.16138159652</v>
       </c>
       <c r="N10" s="93"/>
@@ -4467,15 +4467,15 @@
       <c r="J11" s="151"/>
       <c r="K11" s="151"/>
       <c r="L11" s="154">
-        <f>L8/(1+C15)^L9</f>
+        <f ca="1">L8/(1+C15)^L9</f>
         <v>6372288.8872563262</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="209" t="s">
+      <c r="B13" s="208" t="s">
         <v>276</v>
       </c>
-      <c r="C13" s="209"/>
+      <c r="C13" s="208"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4490,22 +4490,22 @@
         <v>251</v>
       </c>
       <c r="C15" s="170">
-        <f>WACC!C20</f>
+        <f ca="1">WACC!C20</f>
         <v>8.92125E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="209" t="s">
+      <c r="B18" s="208" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="209"/>
+      <c r="C18" s="208"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>274</v>
       </c>
       <c r="C19" s="108">
-        <f>SUM(H10:L10)</f>
+        <f ca="1">SUM(H10:L10)</f>
         <v>1336252.5472907717</v>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
         <v>268</v>
       </c>
       <c r="C20" s="108">
-        <f>L11</f>
+        <f ca="1">L11</f>
         <v>6372288.8872563262</v>
       </c>
     </row>
@@ -4523,7 +4523,7 @@
         <v>271</v>
       </c>
       <c r="C21" s="113">
-        <f>C19+C20</f>
+        <f ca="1">C19+C20</f>
         <v>7708541.4345470984</v>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
         <v>272</v>
       </c>
       <c r="C24" s="113">
-        <f>C21+C22-C23</f>
+        <f ca="1">C21+C22-C23</f>
         <v>8755229.4345470984</v>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
         <v>273</v>
       </c>
       <c r="C26" s="173">
-        <f>C24/C25</f>
+        <f ca="1">C24/C25</f>
         <v>179.63439700040797</v>
       </c>
     </row>
@@ -4612,37 +4612,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="209" t="s">
+      <c r="C2" s="208" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="212"/>
-      <c r="H2" s="213" t="s">
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="209"/>
+      <c r="H2" s="210" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="209"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="209"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="208" t="s">
+      <c r="C4" s="207" t="s">
         <v>338</v>
       </c>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
-      <c r="L4" s="208"/>
+      <c r="D4" s="207"/>
+      <c r="E4" s="207"/>
+      <c r="F4" s="207"/>
+      <c r="G4" s="207"/>
+      <c r="H4" s="207"/>
+      <c r="I4" s="207"/>
+      <c r="J4" s="207"/>
+      <c r="K4" s="207"/>
+      <c r="L4" s="207"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -4831,18 +4831,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="208" t="s">
+      <c r="C10" s="207" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="208"/>
-      <c r="E10" s="208"/>
-      <c r="F10" s="208"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="208"/>
-      <c r="I10" s="208"/>
-      <c r="J10" s="208"/>
-      <c r="K10" s="208"/>
-      <c r="L10" s="208"/>
+      <c r="D10" s="207"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="207"/>
+      <c r="H10" s="207"/>
+      <c r="I10" s="207"/>
+      <c r="J10" s="207"/>
+      <c r="K10" s="207"/>
+      <c r="L10" s="207"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5024,18 +5024,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="208" t="s">
+      <c r="C16" s="207" t="s">
         <v>317</v>
       </c>
-      <c r="D16" s="208"/>
-      <c r="E16" s="208"/>
-      <c r="F16" s="208"/>
-      <c r="G16" s="208"/>
-      <c r="H16" s="208"/>
-      <c r="I16" s="208"/>
-      <c r="J16" s="208"/>
-      <c r="K16" s="208"/>
-      <c r="L16" s="208"/>
+      <c r="D16" s="207"/>
+      <c r="E16" s="207"/>
+      <c r="F16" s="207"/>
+      <c r="G16" s="207"/>
+      <c r="H16" s="207"/>
+      <c r="I16" s="207"/>
+      <c r="J16" s="207"/>
+      <c r="K16" s="207"/>
+      <c r="L16" s="207"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5169,18 +5169,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="208" t="s">
+      <c r="C21" s="207" t="s">
         <v>339</v>
       </c>
-      <c r="D21" s="208"/>
-      <c r="E21" s="208"/>
-      <c r="F21" s="208"/>
-      <c r="G21" s="208"/>
-      <c r="H21" s="208"/>
-      <c r="I21" s="208"/>
-      <c r="J21" s="208"/>
-      <c r="K21" s="208"/>
-      <c r="L21" s="208"/>
+      <c r="D21" s="207"/>
+      <c r="E21" s="207"/>
+      <c r="F21" s="207"/>
+      <c r="G21" s="207"/>
+      <c r="H21" s="207"/>
+      <c r="I21" s="207"/>
+      <c r="J21" s="207"/>
+      <c r="K21" s="207"/>
+      <c r="L21" s="207"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5264,18 +5264,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="208" t="s">
+      <c r="C26" s="207" t="s">
         <v>341</v>
       </c>
-      <c r="D26" s="208"/>
-      <c r="E26" s="208"/>
-      <c r="F26" s="208"/>
-      <c r="G26" s="208"/>
-      <c r="H26" s="208"/>
-      <c r="I26" s="208"/>
-      <c r="J26" s="208"/>
-      <c r="K26" s="208"/>
-      <c r="L26" s="208"/>
+      <c r="D26" s="207"/>
+      <c r="E26" s="207"/>
+      <c r="F26" s="207"/>
+      <c r="G26" s="207"/>
+      <c r="H26" s="207"/>
+      <c r="I26" s="207"/>
+      <c r="J26" s="207"/>
+      <c r="K26" s="207"/>
+      <c r="L26" s="207"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -5413,23 +5413,23 @@
       <c r="B31" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C31" s="107">
+      <c r="C31" s="205">
         <f>Statements!D23</f>
         <v>553922</v>
       </c>
-      <c r="D31" s="199">
+      <c r="D31" s="205">
         <f>Statements!E23</f>
         <v>608180</v>
       </c>
-      <c r="E31" s="199">
+      <c r="E31" s="205">
         <f>Statements!F23</f>
         <v>747610</v>
       </c>
-      <c r="F31" s="199">
+      <c r="F31" s="205">
         <f>Statements!G23</f>
         <v>877645</v>
       </c>
-      <c r="G31" s="201">
+      <c r="G31" s="206">
         <f>Statements!H23</f>
         <v>1140467</v>
       </c>
@@ -5540,10 +5540,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="209" t="s">
+      <c r="B37" s="208" t="s">
         <v>343</v>
       </c>
-      <c r="C37" s="209"/>
+      <c r="C37" s="208"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -5554,16 +5554,13 @@
         <f>L7</f>
         <v>588874.73944865074</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>334</v>
-      </c>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
         <v>251</v>
       </c>
       <c r="C39" s="159">
-        <f>WACC!C20</f>
+        <f ca="1">WACC!C20</f>
         <v>8.92125E-2</v>
       </c>
     </row>
@@ -5607,15 +5604,15 @@
         <v>340</v>
       </c>
       <c r="C44" s="173">
-        <f>C43/(1+C48)^5</f>
+        <f ca="1">C43/(1+C48)^5</f>
         <v>188.36678673157266</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="209" t="s">
+      <c r="B46" s="208" t="s">
         <v>290</v>
       </c>
-      <c r="C46" s="209"/>
+      <c r="C46" s="208"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -5631,7 +5628,7 @@
         <v>251</v>
       </c>
       <c r="C48" s="159">
-        <f>WACC!C20</f>
+        <f ca="1">WACC!C20</f>
         <v>8.92125E-2</v>
       </c>
     </row>
@@ -5666,15 +5663,15 @@
         <v>340</v>
       </c>
       <c r="C52" s="173">
-        <f>C51/(1+C48)^5</f>
+        <f ca="1">C51/(1+C48)^5</f>
         <v>181.63493970006886</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="209" t="s">
+      <c r="B54" s="208" t="s">
         <v>347</v>
       </c>
-      <c r="C54" s="209"/>
+      <c r="C54" s="208"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -5690,7 +5687,7 @@
         <v>251</v>
       </c>
       <c r="C56" s="159">
-        <f>WACC!C20</f>
+        <f ca="1">WACC!C20</f>
         <v>8.92125E-2</v>
       </c>
     </row>
@@ -5734,7 +5731,7 @@
         <v>340</v>
       </c>
       <c r="C61" s="173">
-        <f>C60/(1+C56)^5</f>
+        <f ca="1">C60/(1+C56)^5</f>
         <v>170.98135113942183</v>
       </c>
     </row>
@@ -5784,10 +5781,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="208" t="s">
         <v>298</v>
       </c>
-      <c r="C4" s="209"/>
+      <c r="C4" s="208"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -5795,7 +5792,7 @@
         <v>295</v>
       </c>
       <c r="C5" s="188">
-        <f>DCF!C26</f>
+        <f ca="1">DCF!C26</f>
         <v>179.63439700040797</v>
       </c>
     </row>
@@ -5804,7 +5801,7 @@
         <v>346</v>
       </c>
       <c r="C6" s="188">
-        <f>Multiples!C44</f>
+        <f ca="1">Multiples!C44</f>
         <v>188.36678673157266</v>
       </c>
     </row>
@@ -5813,7 +5810,7 @@
         <v>296</v>
       </c>
       <c r="C7" s="188">
-        <f>Multiples!C52</f>
+        <f ca="1">Multiples!C52</f>
         <v>181.63493970006886</v>
       </c>
     </row>
@@ -5822,7 +5819,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="188">
-        <f>Multiples!C61</f>
+        <f ca="1">Multiples!C61</f>
         <v>170.98135113942183</v>
       </c>
     </row>
@@ -5831,7 +5828,7 @@
         <v>294</v>
       </c>
       <c r="C9" s="173">
-        <f>AVERAGE(C5:C8)</f>
+        <f ca="1">AVERAGE(C5:C8)</f>
         <v>180.15436864286784</v>
       </c>
     </row>
@@ -10451,11 +10448,11 @@
         <v>86</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="205" t="s">
+      <c r="P4" s="212" t="s">
         <v>87</v>
       </c>
-      <c r="Q4" s="206"/>
-      <c r="R4" s="207"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="214"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -20810,36 +20807,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="209" t="s">
+      <c r="C2" s="208" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="212"/>
-      <c r="H2" s="213" t="s">
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="209"/>
+      <c r="H2" s="210" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="209"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="209"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
       <c r="O2" s="92"/>
-      <c r="S2" s="209" t="s">
+      <c r="S2" s="208" t="s">
         <v>178</v>
       </c>
-      <c r="T2" s="209"/>
-      <c r="U2" s="209"/>
-      <c r="V2" s="209"/>
-      <c r="W2" s="209"/>
-      <c r="X2" s="209"/>
-      <c r="Y2" s="209"/>
-      <c r="Z2" s="209"/>
-      <c r="AA2" s="209" t="s">
+      <c r="T2" s="208"/>
+      <c r="U2" s="208"/>
+      <c r="V2" s="208"/>
+      <c r="W2" s="208"/>
+      <c r="X2" s="208"/>
+      <c r="Y2" s="208"/>
+      <c r="Z2" s="208"/>
+      <c r="AA2" s="208" t="s">
         <v>179</v>
       </c>
-      <c r="AB2" s="209"/>
-      <c r="AC2" s="209"/>
+      <c r="AB2" s="208"/>
+      <c r="AC2" s="208"/>
       <c r="AE2" s="128" t="s">
         <v>86</v>
       </c>
@@ -20850,32 +20847,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="208" t="s">
+      <c r="C4" s="207" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
-      <c r="L4" s="208"/>
+      <c r="D4" s="207"/>
+      <c r="E4" s="207"/>
+      <c r="F4" s="207"/>
+      <c r="G4" s="207"/>
+      <c r="H4" s="207"/>
+      <c r="I4" s="207"/>
+      <c r="J4" s="207"/>
+      <c r="K4" s="207"/>
+      <c r="L4" s="207"/>
       <c r="O4" s="92"/>
-      <c r="S4" s="210" t="s">
+      <c r="S4" s="215" t="s">
         <v>187</v>
       </c>
-      <c r="T4" s="211"/>
-      <c r="U4" s="211"/>
-      <c r="V4" s="211"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="211"/>
-      <c r="Y4" s="211"/>
-      <c r="Z4" s="211"/>
-      <c r="AA4" s="211"/>
-      <c r="AB4" s="211"/>
-      <c r="AC4" s="211"/>
+      <c r="T4" s="216"/>
+      <c r="U4" s="216"/>
+      <c r="V4" s="216"/>
+      <c r="W4" s="216"/>
+      <c r="X4" s="216"/>
+      <c r="Y4" s="216"/>
+      <c r="Z4" s="216"/>
+      <c r="AA4" s="216"/>
+      <c r="AB4" s="216"/>
+      <c r="AC4" s="216"/>
       <c r="AE4" s="140" t="s">
         <v>212</v>
       </c>
@@ -21671,33 +21668,33 @@
       <c r="Q13" s="93"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C14" s="208" t="s">
+      <c r="C14" s="207" t="s">
         <v>193</v>
       </c>
-      <c r="D14" s="208"/>
-      <c r="E14" s="208"/>
-      <c r="F14" s="208"/>
-      <c r="G14" s="208"/>
-      <c r="H14" s="208"/>
-      <c r="I14" s="208"/>
-      <c r="J14" s="208"/>
-      <c r="K14" s="208"/>
-      <c r="L14" s="208"/>
+      <c r="D14" s="207"/>
+      <c r="E14" s="207"/>
+      <c r="F14" s="207"/>
+      <c r="G14" s="207"/>
+      <c r="H14" s="207"/>
+      <c r="I14" s="207"/>
+      <c r="J14" s="207"/>
+      <c r="K14" s="207"/>
+      <c r="L14" s="207"/>
       <c r="O14" s="92"/>
       <c r="Q14" s="93"/>
-      <c r="S14" s="210" t="s">
+      <c r="S14" s="215" t="s">
         <v>193</v>
       </c>
-      <c r="T14" s="211"/>
-      <c r="U14" s="211"/>
-      <c r="V14" s="211"/>
-      <c r="W14" s="211"/>
-      <c r="X14" s="211"/>
-      <c r="Y14" s="211"/>
-      <c r="Z14" s="211"/>
-      <c r="AA14" s="211"/>
-      <c r="AB14" s="211"/>
-      <c r="AC14" s="211"/>
+      <c r="T14" s="216"/>
+      <c r="U14" s="216"/>
+      <c r="V14" s="216"/>
+      <c r="W14" s="216"/>
+      <c r="X14" s="216"/>
+      <c r="Y14" s="216"/>
+      <c r="Z14" s="216"/>
+      <c r="AA14" s="216"/>
+      <c r="AB14" s="216"/>
+      <c r="AC14" s="216"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B15" s="7" t="s">
@@ -22390,33 +22387,33 @@
       <c r="Q24" s="93"/>
     </row>
     <row r="25" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C25" s="208" t="s">
+      <c r="C25" s="207" t="s">
         <v>195</v>
       </c>
-      <c r="D25" s="208"/>
-      <c r="E25" s="208"/>
-      <c r="F25" s="208"/>
-      <c r="G25" s="208"/>
-      <c r="H25" s="208"/>
-      <c r="I25" s="208"/>
-      <c r="J25" s="208"/>
-      <c r="K25" s="208"/>
-      <c r="L25" s="208"/>
+      <c r="D25" s="207"/>
+      <c r="E25" s="207"/>
+      <c r="F25" s="207"/>
+      <c r="G25" s="207"/>
+      <c r="H25" s="207"/>
+      <c r="I25" s="207"/>
+      <c r="J25" s="207"/>
+      <c r="K25" s="207"/>
+      <c r="L25" s="207"/>
       <c r="O25" s="92"/>
       <c r="Q25" s="93"/>
-      <c r="S25" s="210" t="s">
+      <c r="S25" s="215" t="s">
         <v>195</v>
       </c>
-      <c r="T25" s="211"/>
-      <c r="U25" s="211"/>
-      <c r="V25" s="211"/>
-      <c r="W25" s="211"/>
-      <c r="X25" s="211"/>
-      <c r="Y25" s="211"/>
-      <c r="Z25" s="211"/>
-      <c r="AA25" s="211"/>
-      <c r="AB25" s="211"/>
-      <c r="AC25" s="211"/>
+      <c r="T25" s="216"/>
+      <c r="U25" s="216"/>
+      <c r="V25" s="216"/>
+      <c r="W25" s="216"/>
+      <c r="X25" s="216"/>
+      <c r="Y25" s="216"/>
+      <c r="Z25" s="216"/>
+      <c r="AA25" s="216"/>
+      <c r="AB25" s="216"/>
+      <c r="AC25" s="216"/>
       <c r="AE25" s="140" t="str">
         <f>AE4</f>
         <v>Q1-Q2-Q3</v>
@@ -23739,32 +23736,32 @@
       <c r="O42" s="92"/>
     </row>
     <row r="43" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C43" s="208" t="s">
+      <c r="C43" s="207" t="s">
         <v>207</v>
       </c>
-      <c r="D43" s="208"/>
-      <c r="E43" s="208"/>
-      <c r="F43" s="208"/>
-      <c r="G43" s="208"/>
-      <c r="H43" s="208"/>
-      <c r="I43" s="208"/>
-      <c r="J43" s="208"/>
-      <c r="K43" s="208"/>
-      <c r="L43" s="208"/>
+      <c r="D43" s="207"/>
+      <c r="E43" s="207"/>
+      <c r="F43" s="207"/>
+      <c r="G43" s="207"/>
+      <c r="H43" s="207"/>
+      <c r="I43" s="207"/>
+      <c r="J43" s="207"/>
+      <c r="K43" s="207"/>
+      <c r="L43" s="207"/>
       <c r="O43" s="92"/>
-      <c r="S43" s="210" t="s">
+      <c r="S43" s="215" t="s">
         <v>207</v>
       </c>
-      <c r="T43" s="211"/>
-      <c r="U43" s="211"/>
-      <c r="V43" s="211"/>
-      <c r="W43" s="211"/>
-      <c r="X43" s="211"/>
-      <c r="Y43" s="211"/>
-      <c r="Z43" s="211"/>
-      <c r="AA43" s="211"/>
-      <c r="AB43" s="211"/>
-      <c r="AC43" s="211"/>
+      <c r="T43" s="216"/>
+      <c r="U43" s="216"/>
+      <c r="V43" s="216"/>
+      <c r="W43" s="216"/>
+      <c r="X43" s="216"/>
+      <c r="Y43" s="216"/>
+      <c r="Z43" s="216"/>
+      <c r="AA43" s="216"/>
+      <c r="AB43" s="216"/>
+      <c r="AC43" s="216"/>
     </row>
     <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B44" s="7" t="s">
@@ -24380,35 +24377,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="209" t="s">
+      <c r="C2" s="208" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="212"/>
-      <c r="H2" s="213" t="s">
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="209"/>
+      <c r="H2" s="210" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="209"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="209"/>
-      <c r="P2" s="209" t="s">
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="P2" s="208" t="s">
         <v>178</v>
       </c>
-      <c r="Q2" s="209"/>
-      <c r="R2" s="209"/>
-      <c r="S2" s="209"/>
-      <c r="T2" s="209"/>
-      <c r="U2" s="209"/>
-      <c r="V2" s="209"/>
-      <c r="W2" s="209"/>
-      <c r="X2" s="209" t="s">
+      <c r="Q2" s="208"/>
+      <c r="R2" s="208"/>
+      <c r="S2" s="208"/>
+      <c r="T2" s="208"/>
+      <c r="U2" s="208"/>
+      <c r="V2" s="208"/>
+      <c r="W2" s="208"/>
+      <c r="X2" s="208" t="s">
         <v>179</v>
       </c>
-      <c r="Y2" s="209"/>
-      <c r="Z2" s="209"/>
+      <c r="Y2" s="208"/>
+      <c r="Z2" s="208"/>
       <c r="AB2" s="128" t="s">
         <v>86</v>
       </c>
@@ -24417,31 +24414,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="208" t="s">
+      <c r="C4" s="207" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
-      <c r="L4" s="208"/>
-      <c r="P4" s="211" t="s">
+      <c r="D4" s="207"/>
+      <c r="E4" s="207"/>
+      <c r="F4" s="207"/>
+      <c r="G4" s="207"/>
+      <c r="H4" s="207"/>
+      <c r="I4" s="207"/>
+      <c r="J4" s="207"/>
+      <c r="K4" s="207"/>
+      <c r="L4" s="207"/>
+      <c r="P4" s="216" t="s">
         <v>187</v>
       </c>
-      <c r="Q4" s="211"/>
-      <c r="R4" s="211"/>
-      <c r="S4" s="211"/>
-      <c r="T4" s="211"/>
-      <c r="U4" s="211"/>
-      <c r="V4" s="211"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="211"/>
-      <c r="Y4" s="211"/>
-      <c r="Z4" s="211"/>
+      <c r="Q4" s="216"/>
+      <c r="R4" s="216"/>
+      <c r="S4" s="216"/>
+      <c r="T4" s="216"/>
+      <c r="U4" s="216"/>
+      <c r="V4" s="216"/>
+      <c r="W4" s="216"/>
+      <c r="X4" s="216"/>
+      <c r="Y4" s="216"/>
+      <c r="Z4" s="216"/>
       <c r="AB4" s="140" t="s">
         <v>212</v>
       </c>
@@ -24642,32 +24639,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="208" t="s">
+      <c r="C9" s="207" t="s">
         <v>214</v>
       </c>
-      <c r="D9" s="208"/>
-      <c r="E9" s="208"/>
-      <c r="F9" s="208"/>
-      <c r="G9" s="208"/>
-      <c r="H9" s="208"/>
-      <c r="I9" s="208"/>
-      <c r="J9" s="208"/>
-      <c r="K9" s="208"/>
-      <c r="L9" s="208"/>
+      <c r="D9" s="207"/>
+      <c r="E9" s="207"/>
+      <c r="F9" s="207"/>
+      <c r="G9" s="207"/>
+      <c r="H9" s="207"/>
+      <c r="I9" s="207"/>
+      <c r="J9" s="207"/>
+      <c r="K9" s="207"/>
+      <c r="L9" s="207"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="211" t="s">
+      <c r="P9" s="216" t="s">
         <v>219</v>
       </c>
-      <c r="Q9" s="211"/>
-      <c r="R9" s="211"/>
-      <c r="S9" s="211"/>
-      <c r="T9" s="211"/>
-      <c r="U9" s="211"/>
-      <c r="V9" s="211"/>
-      <c r="W9" s="211"/>
-      <c r="X9" s="211"/>
-      <c r="Y9" s="211"/>
-      <c r="Z9" s="211"/>
+      <c r="Q9" s="216"/>
+      <c r="R9" s="216"/>
+      <c r="S9" s="216"/>
+      <c r="T9" s="216"/>
+      <c r="U9" s="216"/>
+      <c r="V9" s="216"/>
+      <c r="W9" s="216"/>
+      <c r="X9" s="216"/>
+      <c r="Y9" s="216"/>
+      <c r="Z9" s="216"/>
       <c r="AB9" s="140" t="str">
         <f>AB4</f>
         <v>Q1-Q2-Q3</v>
@@ -25229,31 +25226,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="208" t="s">
+      <c r="C18" s="207" t="s">
         <v>217</v>
       </c>
-      <c r="D18" s="208"/>
-      <c r="E18" s="208"/>
-      <c r="F18" s="208"/>
-      <c r="G18" s="208"/>
-      <c r="H18" s="208"/>
-      <c r="I18" s="208"/>
-      <c r="J18" s="208"/>
-      <c r="K18" s="208"/>
-      <c r="L18" s="208"/>
-      <c r="P18" s="211" t="s">
+      <c r="D18" s="207"/>
+      <c r="E18" s="207"/>
+      <c r="F18" s="207"/>
+      <c r="G18" s="207"/>
+      <c r="H18" s="207"/>
+      <c r="I18" s="207"/>
+      <c r="J18" s="207"/>
+      <c r="K18" s="207"/>
+      <c r="L18" s="207"/>
+      <c r="P18" s="216" t="s">
         <v>217</v>
       </c>
-      <c r="Q18" s="211"/>
-      <c r="R18" s="211"/>
-      <c r="S18" s="211"/>
-      <c r="T18" s="211"/>
-      <c r="U18" s="211"/>
-      <c r="V18" s="211"/>
-      <c r="W18" s="211"/>
-      <c r="X18" s="211"/>
-      <c r="Y18" s="211"/>
-      <c r="Z18" s="211"/>
+      <c r="Q18" s="216"/>
+      <c r="R18" s="216"/>
+      <c r="S18" s="216"/>
+      <c r="T18" s="216"/>
+      <c r="U18" s="216"/>
+      <c r="V18" s="216"/>
+      <c r="W18" s="216"/>
+      <c r="X18" s="216"/>
+      <c r="Y18" s="216"/>
+      <c r="Z18" s="216"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -25725,60 +25722,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="104"/>
-      <c r="C3" s="209" t="s">
+      <c r="C3" s="208" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="209"/>
-      <c r="E3" s="209"/>
-      <c r="F3" s="209"/>
-      <c r="G3" s="212"/>
-      <c r="H3" s="213" t="s">
+      <c r="D3" s="208"/>
+      <c r="E3" s="208"/>
+      <c r="F3" s="208"/>
+      <c r="G3" s="209"/>
+      <c r="H3" s="210" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="209"/>
-      <c r="J3" s="209"/>
-      <c r="K3" s="209"/>
-      <c r="L3" s="209"/>
-      <c r="P3" s="214"/>
-      <c r="Q3" s="214"/>
-      <c r="R3" s="214"/>
-      <c r="S3" s="214"/>
-      <c r="T3" s="214"/>
-      <c r="U3" s="214"/>
-      <c r="V3" s="214"/>
-      <c r="W3" s="214"/>
-      <c r="X3" s="214"/>
-      <c r="Y3" s="214"/>
-      <c r="Z3" s="214"/>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
+      <c r="L3" s="208"/>
+      <c r="P3" s="211"/>
+      <c r="Q3" s="211"/>
+      <c r="R3" s="211"/>
+      <c r="S3" s="211"/>
+      <c r="T3" s="211"/>
+      <c r="U3" s="211"/>
+      <c r="V3" s="211"/>
+      <c r="W3" s="211"/>
+      <c r="X3" s="211"/>
+      <c r="Y3" s="211"/>
+      <c r="Z3" s="211"/>
       <c r="AB3" s="143"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="109"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="208" t="s">
+      <c r="C5" s="207" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="208"/>
-      <c r="K5" s="208"/>
-      <c r="L5" s="208"/>
-      <c r="P5" s="214"/>
-      <c r="Q5" s="214"/>
-      <c r="R5" s="214"/>
-      <c r="S5" s="214"/>
-      <c r="T5" s="214"/>
-      <c r="U5" s="214"/>
-      <c r="V5" s="214"/>
-      <c r="W5" s="214"/>
-      <c r="X5" s="214"/>
-      <c r="Y5" s="214"/>
-      <c r="Z5" s="214"/>
+      <c r="D5" s="207"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="207"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="207"/>
+      <c r="I5" s="207"/>
+      <c r="J5" s="207"/>
+      <c r="K5" s="207"/>
+      <c r="L5" s="207"/>
+      <c r="P5" s="211"/>
+      <c r="Q5" s="211"/>
+      <c r="R5" s="211"/>
+      <c r="S5" s="211"/>
+      <c r="T5" s="211"/>
+      <c r="U5" s="211"/>
+      <c r="V5" s="211"/>
+      <c r="W5" s="211"/>
+      <c r="X5" s="211"/>
+      <c r="Y5" s="211"/>
+      <c r="Z5" s="211"/>
       <c r="AB5" s="144"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -26023,30 +26020,30 @@
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C12" s="208" t="s">
+      <c r="C12" s="207" t="s">
         <v>226</v>
       </c>
-      <c r="D12" s="208"/>
-      <c r="E12" s="208"/>
-      <c r="F12" s="208"/>
-      <c r="G12" s="208"/>
-      <c r="H12" s="208"/>
-      <c r="I12" s="208"/>
-      <c r="J12" s="208"/>
-      <c r="K12" s="208"/>
-      <c r="L12" s="208"/>
+      <c r="D12" s="207"/>
+      <c r="E12" s="207"/>
+      <c r="F12" s="207"/>
+      <c r="G12" s="207"/>
+      <c r="H12" s="207"/>
+      <c r="I12" s="207"/>
+      <c r="J12" s="207"/>
+      <c r="K12" s="207"/>
+      <c r="L12" s="207"/>
       <c r="N12" s="93"/>
-      <c r="P12" s="214"/>
-      <c r="Q12" s="214"/>
-      <c r="R12" s="214"/>
-      <c r="S12" s="214"/>
-      <c r="T12" s="214"/>
-      <c r="U12" s="214"/>
-      <c r="V12" s="214"/>
-      <c r="W12" s="214"/>
-      <c r="X12" s="214"/>
-      <c r="Y12" s="214"/>
-      <c r="Z12" s="214"/>
+      <c r="P12" s="211"/>
+      <c r="Q12" s="211"/>
+      <c r="R12" s="211"/>
+      <c r="S12" s="211"/>
+      <c r="T12" s="211"/>
+      <c r="U12" s="211"/>
+      <c r="V12" s="211"/>
+      <c r="W12" s="211"/>
+      <c r="X12" s="211"/>
+      <c r="Y12" s="211"/>
+      <c r="Z12" s="211"/>
       <c r="AB12" s="144"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -26229,18 +26226,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="208" t="s">
+      <c r="C18" s="207" t="s">
         <v>235</v>
       </c>
-      <c r="D18" s="208"/>
-      <c r="E18" s="208"/>
-      <c r="F18" s="208"/>
-      <c r="G18" s="208"/>
-      <c r="H18" s="208"/>
-      <c r="I18" s="208"/>
-      <c r="J18" s="208"/>
-      <c r="K18" s="208"/>
-      <c r="L18" s="208"/>
+      <c r="D18" s="207"/>
+      <c r="E18" s="207"/>
+      <c r="F18" s="207"/>
+      <c r="G18" s="207"/>
+      <c r="H18" s="207"/>
+      <c r="I18" s="207"/>
+      <c r="J18" s="207"/>
+      <c r="K18" s="207"/>
+      <c r="L18" s="207"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -26423,23 +26420,23 @@
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B24" s="214"/>
-      <c r="C24" s="214"/>
+      <c r="B24" s="211"/>
+      <c r="C24" s="211"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="143"/>
-      <c r="C25" s="208" t="s">
+      <c r="C25" s="207" t="s">
         <v>320</v>
       </c>
-      <c r="D25" s="208"/>
-      <c r="E25" s="208"/>
-      <c r="F25" s="208"/>
-      <c r="G25" s="208"/>
-      <c r="H25" s="208"/>
-      <c r="I25" s="208"/>
-      <c r="J25" s="208"/>
-      <c r="K25" s="208"/>
-      <c r="L25" s="208"/>
+      <c r="D25" s="207"/>
+      <c r="E25" s="207"/>
+      <c r="F25" s="207"/>
+      <c r="G25" s="207"/>
+      <c r="H25" s="207"/>
+      <c r="I25" s="207"/>
+      <c r="J25" s="207"/>
+      <c r="K25" s="207"/>
+      <c r="L25" s="207"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
@@ -26586,18 +26583,18 @@
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="143"/>
-      <c r="C31" s="208" t="s">
+      <c r="C31" s="207" t="s">
         <v>323</v>
       </c>
-      <c r="D31" s="208"/>
-      <c r="E31" s="208"/>
-      <c r="F31" s="208"/>
-      <c r="G31" s="208"/>
-      <c r="H31" s="208"/>
-      <c r="I31" s="208"/>
-      <c r="J31" s="208"/>
-      <c r="K31" s="208"/>
-      <c r="L31" s="208"/>
+      <c r="D31" s="207"/>
+      <c r="E31" s="207"/>
+      <c r="F31" s="207"/>
+      <c r="G31" s="207"/>
+      <c r="H31" s="207"/>
+      <c r="I31" s="207"/>
+      <c r="J31" s="207"/>
+      <c r="K31" s="207"/>
+      <c r="L31" s="207"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
@@ -26781,18 +26778,18 @@
       <c r="C37" s="152"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C38" s="208" t="s">
+      <c r="C38" s="207" t="s">
         <v>327</v>
       </c>
-      <c r="D38" s="208"/>
-      <c r="E38" s="208"/>
-      <c r="F38" s="208"/>
-      <c r="G38" s="208"/>
-      <c r="H38" s="208"/>
-      <c r="I38" s="208"/>
-      <c r="J38" s="208"/>
-      <c r="K38" s="208"/>
-      <c r="L38" s="208"/>
+      <c r="D38" s="207"/>
+      <c r="E38" s="207"/>
+      <c r="F38" s="207"/>
+      <c r="G38" s="207"/>
+      <c r="H38" s="207"/>
+      <c r="I38" s="207"/>
+      <c r="J38" s="207"/>
+      <c r="K38" s="207"/>
+      <c r="L38" s="207"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B39" s="7" t="s">

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007E8E21-4A4E-7E45-9632-889550CC8448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694E0D33-1D1F-7C4D-9489-CF7A585AF272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="13" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="15" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -28,9 +28,11 @@
     <sheet name="DCF" sheetId="22" r:id="rId13"/>
     <sheet name="Multiples" sheetId="24" r:id="rId14"/>
     <sheet name="AVG target price" sheetId="25" r:id="rId15"/>
+    <sheet name="Reverse DCF" sheetId="28" r:id="rId16"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId16"/>
+    <externalReference r:id="rId17"/>
+    <externalReference r:id="rId18"/>
   </externalReferences>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -215,7 +217,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="368">
   <si>
     <t>Date</t>
   </si>
@@ -1271,6 +1273,54 @@
   </si>
   <si>
     <t>Multiples valuations</t>
+  </si>
+  <si>
+    <t>Current price</t>
+  </si>
+  <si>
+    <t>Upside/Downside</t>
+  </si>
+  <si>
+    <t>Reverse DCF</t>
+  </si>
+  <si>
+    <t>Growth adjustment</t>
+  </si>
+  <si>
+    <t>Current Price</t>
+  </si>
+  <si>
+    <t>Calculated Price</t>
+  </si>
+  <si>
+    <t>UFCF Growth</t>
+  </si>
+  <si>
+    <t>Modify until Calculated Price is very close to Current Price</t>
+  </si>
+  <si>
+    <t>Enterprise Value</t>
+  </si>
+  <si>
+    <t>Compare Metrics and growth rates</t>
+  </si>
+  <si>
+    <t>UFCF to EBIT margin</t>
+  </si>
+  <si>
+    <t>UFCF to Revenue margin</t>
+  </si>
+  <si>
+    <t>UFCF growth</t>
+  </si>
+  <si>
+    <t>EBIT growth</t>
+  </si>
+  <si>
+    <t>Revenue growth</t>
+  </si>
+  <si>
+    <t>EBIT margin</t>
   </si>
 </sst>
 </file>
@@ -1557,7 +1607,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1808,12 +1858,100 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="217">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2073,13 +2211,16 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2091,12 +2232,33 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="8" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="8" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="3" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="0" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="2" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="1" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="38" fontId="0" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2120,6 +2282,71 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>128348</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>20266</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>716064</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>216170</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Right Arrow 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D547EA05-C8C4-8F41-8ED0-F5231D2F1EC5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="3544648" y="3258766"/>
+          <a:ext cx="587716" cy="195904"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -2128,15 +2355,162 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
+      <sheetName val="1. List_AutomaticData"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="4">
           <cell r="C4">
-            <v>103.45</v>
+            <v>106.24</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>43.36</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="Financials -&gt;"/>
+      <sheetName val="Statement Y"/>
+      <sheetName val="Statement Q"/>
+      <sheetName val="Statements"/>
+      <sheetName val="Forecast -&gt;"/>
+      <sheetName val="Revenue"/>
+      <sheetName val="COGS &amp; OpEx"/>
+      <sheetName val="WC &amp; Investments"/>
+      <sheetName val="FCF &amp; Other"/>
+      <sheetName val="Valuation -&gt;"/>
+      <sheetName val="WACC"/>
+      <sheetName val="DCF"/>
+      <sheetName val="Multiples"/>
+      <sheetName val="AVG target price"/>
+      <sheetName val="Reverse DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
+        <row r="21">
+          <cell r="W21">
+            <v>66907</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="W27">
+            <v>77888</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="W35">
+            <v>1997</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="W36">
+            <v>11827</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="W38">
+            <v>76685</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6">
+        <row r="5">
+          <cell r="C5">
+            <v>2021</v>
+          </cell>
+          <cell r="D5">
+            <v>2022</v>
+          </cell>
+          <cell r="E5">
+            <v>2023</v>
+          </cell>
+          <cell r="F5">
+            <v>2024</v>
+          </cell>
+          <cell r="G5">
+            <v>2025</v>
+          </cell>
+          <cell r="H5">
+            <v>2026</v>
+          </cell>
+          <cell r="I5">
+            <v>2027</v>
+          </cell>
+          <cell r="J5">
+            <v>2028</v>
+          </cell>
+          <cell r="K5">
+            <v>2029</v>
+          </cell>
+          <cell r="L5">
+            <v>2030</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9">
+        <row r="6">
+          <cell r="C6">
+            <v>365817</v>
+          </cell>
+          <cell r="D6">
+            <v>394328</v>
+          </cell>
+          <cell r="E6">
+            <v>383285</v>
+          </cell>
+          <cell r="F6">
+            <v>391035</v>
+          </cell>
+          <cell r="G6">
+            <v>416161</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>108949</v>
+          </cell>
+          <cell r="D12">
+            <v>119437</v>
+          </cell>
+          <cell r="E12">
+            <v>114301</v>
+          </cell>
+          <cell r="F12">
+            <v>123216</v>
+          </cell>
+          <cell r="G12">
+            <v>133050</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2599,8 +2973,8 @@
         <v>85</v>
       </c>
       <c r="C3" s="35">
-        <f ca="1">[1]Sheet1!$C$4</f>
-        <v>103.45</v>
+        <f>[1]Sheet1!$C$4</f>
+        <v>106.24</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2625,8 +2999,8 @@
         <v>183</v>
       </c>
       <c r="C11" s="95">
-        <f ca="1">$C$3/'Statement Q'!$N$22</f>
-        <v>12.176991527853712</v>
+        <f>$C$3/'Statement Q'!$N$22</f>
+        <v>12.505399515893458</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2634,8 +3008,8 @@
         <v>285</v>
       </c>
       <c r="C12" s="95">
-        <f ca="1">C3/Statements!S20</f>
-        <v>30.3016268608865</v>
+        <f>C3/Statements!S20</f>
+        <v>31.118848116970341</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2643,8 +3017,8 @@
         <v>184</v>
       </c>
       <c r="C13" s="102">
-        <f ca="1">$C$3/('Statement Q'!$N$5/'Statement Q'!$N$20)</f>
-        <v>4.8594057926411587</v>
+        <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$20)</f>
+        <v>4.9904617826021909</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -2652,8 +3026,8 @@
         <v>242</v>
       </c>
       <c r="C15" s="20">
-        <f ca="1">C3*'Statement Q'!N116</f>
-        <v>4903530</v>
+        <f>C3*'Statement Q'!N116</f>
+        <v>5035776</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2678,8 +3052,8 @@
         <v>244</v>
       </c>
       <c r="C18" s="20">
-        <f ca="1">C15+C17-C16</f>
-        <v>3763063</v>
+        <f>C15+C17-C16</f>
+        <v>3895309</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -2888,25 +3262,25 @@
       <c r="D2" s="208"/>
       <c r="E2" s="208"/>
       <c r="F2" s="208"/>
-      <c r="G2" s="209"/>
-      <c r="H2" s="210" t="s">
+      <c r="G2" s="211"/>
+      <c r="H2" s="212" t="s">
         <v>179</v>
       </c>
       <c r="I2" s="208"/>
       <c r="J2" s="208"/>
       <c r="K2" s="208"/>
       <c r="L2" s="208"/>
-      <c r="S2" s="211"/>
-      <c r="T2" s="211"/>
-      <c r="U2" s="211"/>
-      <c r="V2" s="211"/>
-      <c r="W2" s="211"/>
-      <c r="X2" s="211"/>
-      <c r="Y2" s="211"/>
-      <c r="Z2" s="211"/>
-      <c r="AA2" s="211"/>
-      <c r="AB2" s="211"/>
-      <c r="AC2" s="211"/>
+      <c r="S2" s="216"/>
+      <c r="T2" s="216"/>
+      <c r="U2" s="216"/>
+      <c r="V2" s="216"/>
+      <c r="W2" s="216"/>
+      <c r="X2" s="216"/>
+      <c r="Y2" s="216"/>
+      <c r="Z2" s="216"/>
+      <c r="AA2" s="216"/>
+      <c r="AB2" s="216"/>
+      <c r="AC2" s="216"/>
       <c r="AE2" s="143"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2925,17 +3299,17 @@
       <c r="J4" s="207"/>
       <c r="K4" s="207"/>
       <c r="L4" s="207"/>
-      <c r="S4" s="211"/>
-      <c r="T4" s="211"/>
-      <c r="U4" s="211"/>
-      <c r="V4" s="211"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="211"/>
-      <c r="Y4" s="211"/>
-      <c r="Z4" s="211"/>
-      <c r="AA4" s="211"/>
-      <c r="AB4" s="211"/>
-      <c r="AC4" s="211"/>
+      <c r="S4" s="216"/>
+      <c r="T4" s="216"/>
+      <c r="U4" s="216"/>
+      <c r="V4" s="216"/>
+      <c r="W4" s="216"/>
+      <c r="X4" s="216"/>
+      <c r="Y4" s="216"/>
+      <c r="Z4" s="216"/>
+      <c r="AA4" s="216"/>
+      <c r="AB4" s="216"/>
+      <c r="AC4" s="216"/>
       <c r="AE4" s="144"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -4016,8 +4390,8 @@
         <v>85</v>
       </c>
       <c r="C6" s="166">
-        <f ca="1">Overview!C3</f>
-        <v>103.45</v>
+        <f>Overview!C3</f>
+        <v>106.24</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4025,8 +4399,8 @@
         <v>240</v>
       </c>
       <c r="C7" s="168">
-        <f ca="1">C5*C6</f>
-        <v>4903530</v>
+        <f>C5*C6</f>
+        <v>5035776</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4042,7 +4416,8 @@
         <v>257</v>
       </c>
       <c r="C9" s="191">
-        <v>4.2819999999999997E-2</v>
+        <f>[1]Sheet1!$C$10/1000</f>
+        <v>4.3360000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4058,7 +4433,7 @@
         <v>259</v>
       </c>
       <c r="C11" s="167">
-        <v>5.5E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4089,7 +4464,7 @@
         <v>252</v>
       </c>
       <c r="C16" s="169">
-        <f ca="1">C8/(C8+C7)</f>
+        <f>C8/(C8+C7)</f>
         <v>0</v>
       </c>
     </row>
@@ -4098,7 +4473,7 @@
         <v>253</v>
       </c>
       <c r="C17" s="169">
-        <f ca="1">C7/(C8+C7)</f>
+        <f>C7/(C8+C7)</f>
         <v>1</v>
       </c>
     </row>
@@ -4117,7 +4492,7 @@
       </c>
       <c r="C19" s="169">
         <f>C9+C10*C11</f>
-        <v>8.92125E-2</v>
+        <v>8.5535E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4125,8 +4500,8 @@
         <v>251</v>
       </c>
       <c r="C20" s="169">
-        <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.92125E-2</v>
+        <f>(C17*C19)+(C16*C18)</f>
+        <v>8.5535E-2</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4179,25 +4554,25 @@
       <c r="D3" s="208"/>
       <c r="E3" s="208"/>
       <c r="F3" s="208"/>
-      <c r="G3" s="209"/>
-      <c r="H3" s="210" t="s">
+      <c r="G3" s="211"/>
+      <c r="H3" s="212" t="s">
         <v>179</v>
       </c>
       <c r="I3" s="208"/>
       <c r="J3" s="208"/>
       <c r="K3" s="208"/>
       <c r="L3" s="208"/>
-      <c r="P3" s="211"/>
-      <c r="Q3" s="211"/>
-      <c r="R3" s="211"/>
-      <c r="S3" s="211"/>
-      <c r="T3" s="211"/>
-      <c r="U3" s="211"/>
-      <c r="V3" s="211"/>
-      <c r="W3" s="211"/>
-      <c r="X3" s="211"/>
-      <c r="Y3" s="211"/>
-      <c r="Z3" s="211"/>
+      <c r="P3" s="216"/>
+      <c r="Q3" s="216"/>
+      <c r="R3" s="216"/>
+      <c r="S3" s="216"/>
+      <c r="T3" s="216"/>
+      <c r="U3" s="216"/>
+      <c r="V3" s="216"/>
+      <c r="W3" s="216"/>
+      <c r="X3" s="216"/>
+      <c r="Y3" s="216"/>
+      <c r="Z3" s="216"/>
       <c r="AB3" s="143"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4216,17 +4591,17 @@
       <c r="J5" s="207"/>
       <c r="K5" s="207"/>
       <c r="L5" s="207"/>
-      <c r="P5" s="211"/>
-      <c r="Q5" s="211"/>
-      <c r="R5" s="211"/>
-      <c r="S5" s="211"/>
-      <c r="T5" s="211"/>
-      <c r="U5" s="211"/>
-      <c r="V5" s="211"/>
-      <c r="W5" s="211"/>
-      <c r="X5" s="211"/>
-      <c r="Y5" s="211"/>
-      <c r="Z5" s="211"/>
+      <c r="P5" s="216"/>
+      <c r="Q5" s="216"/>
+      <c r="R5" s="216"/>
+      <c r="S5" s="216"/>
+      <c r="T5" s="216"/>
+      <c r="U5" s="216"/>
+      <c r="V5" s="216"/>
+      <c r="W5" s="216"/>
+      <c r="X5" s="216"/>
+      <c r="Y5" s="216"/>
+      <c r="Z5" s="216"/>
       <c r="AB5" s="144"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4378,8 +4753,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="154">
-        <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>9769189.6342976131</v>
+        <f>L7*(1+C14)/(C15-C14)</f>
+        <v>10317388.228638493</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="7"/>
@@ -4432,24 +4807,24 @@
       <c r="F10" s="151"/>
       <c r="G10" s="171"/>
       <c r="H10" s="154">
-        <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>142663.24731757896</v>
+        <f>H7/(1+$C$15)^H9</f>
+        <v>143146.55194802422</v>
       </c>
       <c r="I10" s="154">
-        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$15)^I9</f>
-        <v>215054.65665710828</v>
+        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$15)^I9</f>
+        <v>216514.21920653529</v>
       </c>
       <c r="J10" s="154">
-        <f t="shared" ca="1" si="1"/>
-        <v>253165.64877963354</v>
+        <f t="shared" si="1"/>
+        <v>255747.34610477317</v>
       </c>
       <c r="K10" s="154">
-        <f t="shared" ca="1" si="1"/>
-        <v>292974.83315485454</v>
+        <f t="shared" si="1"/>
+        <v>296965.13217522728</v>
       </c>
       <c r="L10" s="154">
-        <f t="shared" ca="1" si="1"/>
-        <v>432394.16138159652</v>
+        <f t="shared" si="1"/>
+        <v>439768.12882532179</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -4467,8 +4842,8 @@
       <c r="J11" s="151"/>
       <c r="K11" s="151"/>
       <c r="L11" s="154">
-        <f ca="1">L8/(1+C15)^L9</f>
-        <v>6372288.8872563262</v>
+        <f>L8/(1+C15)^L9</f>
+        <v>6844640.1373590948</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -4490,8 +4865,8 @@
         <v>251</v>
       </c>
       <c r="C15" s="170">
-        <f ca="1">WACC!C20</f>
-        <v>8.92125E-2</v>
+        <f>WACC!C20</f>
+        <v>8.5535E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -4505,8 +4880,8 @@
         <v>274</v>
       </c>
       <c r="C19" s="108">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>1336252.5472907717</v>
+        <f>SUM(H10:L10)</f>
+        <v>1352141.3782598819</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -4514,8 +4889,8 @@
         <v>268</v>
       </c>
       <c r="C20" s="108">
-        <f ca="1">L11</f>
-        <v>6372288.8872563262</v>
+        <f>L11</f>
+        <v>6844640.1373590948</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -4523,8 +4898,8 @@
         <v>271</v>
       </c>
       <c r="C21" s="113">
-        <f ca="1">C19+C20</f>
-        <v>7708541.4345470984</v>
+        <f>C19+C20</f>
+        <v>8196781.5156189762</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -4550,8 +4925,8 @@
         <v>272</v>
       </c>
       <c r="C24" s="113">
-        <f ca="1">C21+C22-C23</f>
-        <v>8755229.4345470984</v>
+        <f>C21+C22-C23</f>
+        <v>9243469.5156189762</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -4568,8 +4943,8 @@
         <v>273</v>
       </c>
       <c r="C26" s="173">
-        <f ca="1">C24/C25</f>
-        <v>179.63439700040797</v>
+        <f>C24/C25</f>
+        <v>189.65180581995355</v>
       </c>
     </row>
   </sheetData>
@@ -4618,8 +4993,8 @@
       <c r="D2" s="208"/>
       <c r="E2" s="208"/>
       <c r="F2" s="208"/>
-      <c r="G2" s="209"/>
-      <c r="H2" s="210" t="s">
+      <c r="G2" s="211"/>
+      <c r="H2" s="212" t="s">
         <v>179</v>
       </c>
       <c r="I2" s="208"/>
@@ -5560,8 +5935,8 @@
         <v>251</v>
       </c>
       <c r="C39" s="159">
-        <f ca="1">WACC!C20</f>
-        <v>8.92125E-2</v>
+        <f>WACC!C20</f>
+        <v>8.5535E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -5604,8 +5979,8 @@
         <v>340</v>
       </c>
       <c r="C44" s="173">
-        <f ca="1">C43/(1+C48)^5</f>
-        <v>188.36678673157266</v>
+        <f>C43/(1+C48)^5</f>
+        <v>191.57915793566005</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -5628,8 +6003,8 @@
         <v>251</v>
       </c>
       <c r="C48" s="159">
-        <f ca="1">WACC!C20</f>
-        <v>8.92125E-2</v>
+        <f>WACC!C20</f>
+        <v>8.5535E-2</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -5663,8 +6038,8 @@
         <v>340</v>
       </c>
       <c r="C52" s="173">
-        <f ca="1">C51/(1+C48)^5</f>
-        <v>181.63493970006886</v>
+        <f>C51/(1+C48)^5</f>
+        <v>184.73250727062003</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
@@ -5687,8 +6062,8 @@
         <v>251</v>
       </c>
       <c r="C56" s="159">
-        <f ca="1">WACC!C20</f>
-        <v>8.92125E-2</v>
+        <f>WACC!C20</f>
+        <v>8.5535E-2</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -5731,8 +6106,8 @@
         <v>340</v>
       </c>
       <c r="C61" s="173">
-        <f ca="1">C60/(1+C56)^5</f>
-        <v>170.98135113942183</v>
+        <f>C60/(1+C56)^5</f>
+        <v>173.89723444542597</v>
       </c>
     </row>
   </sheetData>
@@ -5754,7 +6129,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41CA1518-986C-904D-A3A8-59534CD71A6D}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="103" customWidth="1"/>
@@ -5792,8 +6167,8 @@
         <v>295</v>
       </c>
       <c r="C5" s="188">
-        <f ca="1">DCF!C26</f>
-        <v>179.63439700040797</v>
+        <f>DCF!C26</f>
+        <v>189.65180581995355</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -5801,8 +6176,8 @@
         <v>346</v>
       </c>
       <c r="C6" s="188">
-        <f ca="1">Multiples!C44</f>
-        <v>188.36678673157266</v>
+        <f>Multiples!C44</f>
+        <v>191.57915793566005</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -5810,8 +6185,8 @@
         <v>296</v>
       </c>
       <c r="C7" s="188">
-        <f ca="1">Multiples!C52</f>
-        <v>181.63493970006886</v>
+        <f>Multiples!C52</f>
+        <v>184.73250727062003</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -5819,8 +6194,8 @@
         <v>350</v>
       </c>
       <c r="C8" s="188">
-        <f ca="1">Multiples!C61</f>
-        <v>170.98135113942183</v>
+        <f>Multiples!C61</f>
+        <v>173.89723444542597</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -5828,8 +6203,26 @@
         <v>294</v>
       </c>
       <c r="C9" s="173">
-        <f ca="1">AVERAGE(C5:C8)</f>
-        <v>180.15436864286784</v>
+        <f>AVERAGE(C5:C8)</f>
+        <v>184.96517636791492</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C10" s="35">
+        <f>Overview!C3</f>
+        <v>106.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C11" s="91">
+        <f>(C9-C10)/C10</f>
+        <v>0.74101257876425952</v>
       </c>
     </row>
   </sheetData>
@@ -5837,6 +6230,968 @@
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09BAEB35-DDA3-D84C-96C2-DB72934E2714}">
+  <dimension ref="A1:AB49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2" style="103" customWidth="1"/>
+    <col min="2" max="2" width="32" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="10.83203125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="10.83203125" style="1"/>
+    <col min="13" max="13" width="28" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5" style="1" customWidth="1"/>
+    <col min="15" max="15" width="24.6640625" style="1" customWidth="1"/>
+    <col min="16" max="26" width="10.83203125" style="1"/>
+    <col min="27" max="27" width="2" style="1" customWidth="1"/>
+    <col min="28" max="28" width="12.33203125" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="103" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="104"/>
+      <c r="B1" s="105" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" s="103" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="104"/>
+      <c r="B2" s="105"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A3" s="104"/>
+      <c r="C3" s="208" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" s="208"/>
+      <c r="E3" s="208"/>
+      <c r="F3" s="208"/>
+      <c r="G3" s="211"/>
+      <c r="H3" s="212" t="s">
+        <v>179</v>
+      </c>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
+      <c r="L3" s="208"/>
+      <c r="P3" s="216"/>
+      <c r="Q3" s="216"/>
+      <c r="R3" s="216"/>
+      <c r="S3" s="216"/>
+      <c r="T3" s="216"/>
+      <c r="U3" s="216"/>
+      <c r="V3" s="216"/>
+      <c r="W3" s="216"/>
+      <c r="X3" s="216"/>
+      <c r="Y3" s="216"/>
+      <c r="Z3" s="216"/>
+      <c r="AB3" s="143"/>
+    </row>
+    <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="109"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="207" t="s">
+        <v>275</v>
+      </c>
+      <c r="D5" s="207"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="207"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="207"/>
+      <c r="I5" s="207"/>
+      <c r="J5" s="207"/>
+      <c r="K5" s="207"/>
+      <c r="L5" s="207"/>
+      <c r="P5" s="216"/>
+      <c r="Q5" s="216"/>
+      <c r="R5" s="216"/>
+      <c r="S5" s="216"/>
+      <c r="T5" s="216"/>
+      <c r="U5" s="216"/>
+      <c r="V5" s="216"/>
+      <c r="W5" s="216"/>
+      <c r="X5" s="216"/>
+      <c r="Y5" s="216"/>
+      <c r="Z5" s="216"/>
+      <c r="AB5" s="144"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B6" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="62">
+        <f>[2]Revenue!C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D6" s="62">
+        <f>[2]Revenue!D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E6" s="62">
+        <f>[2]Revenue!E5</f>
+        <v>2023</v>
+      </c>
+      <c r="F6" s="62">
+        <f>[2]Revenue!F5</f>
+        <v>2024</v>
+      </c>
+      <c r="G6" s="62">
+        <f>[2]Revenue!G5</f>
+        <v>2025</v>
+      </c>
+      <c r="H6" s="62">
+        <f>[2]Revenue!H5</f>
+        <v>2026</v>
+      </c>
+      <c r="I6" s="62">
+        <f>[2]Revenue!I5</f>
+        <v>2027</v>
+      </c>
+      <c r="J6" s="62">
+        <f>[2]Revenue!J5</f>
+        <v>2028</v>
+      </c>
+      <c r="K6" s="62">
+        <f>[2]Revenue!K5</f>
+        <v>2029</v>
+      </c>
+      <c r="L6" s="62">
+        <f>[2]Revenue!L5</f>
+        <v>2030</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="145"/>
+      <c r="Q6" s="145"/>
+      <c r="R6" s="145"/>
+      <c r="S6" s="145"/>
+      <c r="T6" s="145"/>
+      <c r="U6" s="145"/>
+      <c r="V6" s="145"/>
+      <c r="W6" s="145"/>
+      <c r="X6" s="145"/>
+      <c r="Y6" s="145"/>
+      <c r="Z6" s="145"/>
+      <c r="AB6" s="144"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B7" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="153">
+        <f>'FCF &amp; Other'!C31</f>
+        <v>-34914.855348744117</v>
+      </c>
+      <c r="D7" s="153">
+        <f>'FCF &amp; Other'!D31</f>
+        <v>-30304.075687291086</v>
+      </c>
+      <c r="E7" s="153">
+        <f>'FCF &amp; Other'!E31</f>
+        <v>26818.405861506442</v>
+      </c>
+      <c r="F7" s="153">
+        <f>'FCF &amp; Other'!F31</f>
+        <v>128852.20010556566</v>
+      </c>
+      <c r="G7" s="155">
+        <f>'FCF &amp; Other'!G31</f>
+        <v>152361.29999999999</v>
+      </c>
+      <c r="H7" s="154">
+        <f>G7*(1+$C$17)</f>
+        <v>179786.33399999997</v>
+      </c>
+      <c r="I7" s="154">
+        <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
+        <v>212147.87411999996</v>
+      </c>
+      <c r="J7" s="154">
+        <f t="shared" si="0"/>
+        <v>250334.49146159994</v>
+      </c>
+      <c r="K7" s="154">
+        <f t="shared" si="0"/>
+        <v>295394.69992468791</v>
+      </c>
+      <c r="L7" s="154">
+        <f t="shared" si="0"/>
+        <v>348565.74591113173</v>
+      </c>
+      <c r="N7" s="93"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="111"/>
+      <c r="Q7" s="111"/>
+      <c r="R7" s="111"/>
+      <c r="S7" s="111"/>
+      <c r="T7" s="111"/>
+      <c r="U7" s="111"/>
+      <c r="V7" s="111"/>
+      <c r="W7" s="111"/>
+      <c r="X7" s="113"/>
+      <c r="Y7" s="113"/>
+      <c r="Z7" s="113"/>
+      <c r="AB7" s="113"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B8" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="C8" s="151"/>
+      <c r="D8" s="151"/>
+      <c r="E8" s="151"/>
+      <c r="F8" s="151"/>
+      <c r="G8" s="171"/>
+      <c r="H8" s="151"/>
+      <c r="I8" s="151"/>
+      <c r="J8" s="151"/>
+      <c r="K8" s="151"/>
+      <c r="L8" s="154">
+        <f>L7*(1+C20)/(C21-C20)</f>
+        <v>5902038.3176494585</v>
+      </c>
+      <c r="N8" s="93"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="111"/>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="111"/>
+      <c r="S8" s="111"/>
+      <c r="T8" s="111"/>
+      <c r="U8" s="111"/>
+      <c r="V8" s="111"/>
+      <c r="W8" s="111"/>
+      <c r="X8" s="113"/>
+      <c r="Y8" s="113"/>
+      <c r="Z8" s="113"/>
+      <c r="AB8" s="113"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C9" s="151"/>
+      <c r="D9" s="151"/>
+      <c r="E9" s="151"/>
+      <c r="F9" s="151"/>
+      <c r="G9" s="171"/>
+      <c r="H9" s="36">
+        <v>1</v>
+      </c>
+      <c r="I9" s="36">
+        <v>2</v>
+      </c>
+      <c r="J9" s="36">
+        <v>3</v>
+      </c>
+      <c r="K9" s="36">
+        <v>4</v>
+      </c>
+      <c r="L9" s="36">
+        <v>5</v>
+      </c>
+      <c r="N9" s="93"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C10" s="151"/>
+      <c r="D10" s="151"/>
+      <c r="E10" s="151"/>
+      <c r="F10" s="151"/>
+      <c r="G10" s="171"/>
+      <c r="H10" s="154">
+        <f>H7/(1+$C$21)^H9</f>
+        <v>165620.02514888972</v>
+      </c>
+      <c r="I10" s="154">
+        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
+        <v>180032.54586511708</v>
+      </c>
+      <c r="J10" s="154">
+        <f t="shared" si="1"/>
+        <v>195699.26729293683</v>
+      </c>
+      <c r="K10" s="154">
+        <f t="shared" si="1"/>
+        <v>212729.33199359346</v>
+      </c>
+      <c r="L10" s="154">
+        <f t="shared" si="1"/>
+        <v>231241.38028938754</v>
+      </c>
+      <c r="N10" s="93"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C11" s="151"/>
+      <c r="D11" s="151"/>
+      <c r="E11" s="151"/>
+      <c r="F11" s="151"/>
+      <c r="G11" s="171"/>
+      <c r="H11" s="151"/>
+      <c r="I11" s="151"/>
+      <c r="J11" s="151"/>
+      <c r="K11" s="151"/>
+      <c r="L11" s="154">
+        <f>L8/(1+C21)^L9</f>
+        <v>3915460.7218406242</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B14" s="217" t="s">
+        <v>355</v>
+      </c>
+      <c r="C14" s="218"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B15" s="219" t="s">
+        <v>356</v>
+      </c>
+      <c r="C15" s="220">
+        <f>Overview!C3</f>
+        <v>106.24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B16" s="219" t="s">
+        <v>357</v>
+      </c>
+      <c r="C16" s="220">
+        <f>C36</f>
+        <v>104.53732642258541</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="221" t="s">
+        <v>358</v>
+      </c>
+      <c r="C17" s="222">
+        <v>0.18</v>
+      </c>
+      <c r="E17" s="223" t="s">
+        <v>359</v>
+      </c>
+      <c r="F17" s="223"/>
+      <c r="G17" s="223"/>
+      <c r="H17" s="223"/>
+      <c r="I17" s="223"/>
+    </row>
+    <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B19" s="217" t="s">
+        <v>276</v>
+      </c>
+      <c r="C19" s="218"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B20" s="224" t="s">
+        <v>265</v>
+      </c>
+      <c r="C20" s="225">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B21" s="224" t="s">
+        <v>251</v>
+      </c>
+      <c r="C21" s="226">
+        <f>WACC!C20</f>
+        <v>8.5535E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B22" s="224" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="227">
+        <f>'Statement Q'!N116</f>
+        <v>47400</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B23" s="224" t="s">
+        <v>242</v>
+      </c>
+      <c r="C23" s="227">
+        <f>C15*C22</f>
+        <v>5035776</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B24" s="224" t="s">
+        <v>243</v>
+      </c>
+      <c r="C24" s="227">
+        <f>Statements!S23</f>
+        <v>1140467</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B25" s="224" t="s">
+        <v>239</v>
+      </c>
+      <c r="C25" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="221" t="s">
+        <v>360</v>
+      </c>
+      <c r="C26" s="228">
+        <f>C23+C25-C24</f>
+        <v>3895309</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B28" s="217" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="218"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B29" s="224" t="s">
+        <v>274</v>
+      </c>
+      <c r="C29" s="227">
+        <f>SUM(H10:L10)</f>
+        <v>985322.55058992468</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B30" s="224" t="s">
+        <v>268</v>
+      </c>
+      <c r="C30" s="227">
+        <f>L11</f>
+        <v>3915460.7218406242</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B31" s="229" t="s">
+        <v>271</v>
+      </c>
+      <c r="C31" s="230">
+        <f>C29+C30</f>
+        <v>4900783.2724305484</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B32" s="224" t="s">
+        <v>269</v>
+      </c>
+      <c r="C32" s="231">
+        <f>[2]Statements!W21+[2]Statements!W27</f>
+        <v>144795</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B33" s="224" t="s">
+        <v>270</v>
+      </c>
+      <c r="C33" s="231">
+        <f>[2]Statements!W35+[2]Statements!W36+[2]Statements!W38</f>
+        <v>90509</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B34" s="229" t="s">
+        <v>272</v>
+      </c>
+      <c r="C34" s="230">
+        <f>C31+C32-C33</f>
+        <v>4955069.2724305484</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B35" s="224" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="227">
+        <f>C22</f>
+        <v>47400</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="232" t="s">
+        <v>273</v>
+      </c>
+      <c r="C36" s="233">
+        <f>C34/C35</f>
+        <v>104.53732642258541</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C39" s="207" t="s">
+        <v>361</v>
+      </c>
+      <c r="D39" s="207"/>
+      <c r="E39" s="207"/>
+      <c r="F39" s="207"/>
+      <c r="G39" s="207"/>
+      <c r="H39" s="207"/>
+      <c r="I39" s="207"/>
+      <c r="J39" s="207"/>
+      <c r="K39" s="207"/>
+      <c r="L39" s="207"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C40" s="62">
+        <f>C6</f>
+        <v>2021</v>
+      </c>
+      <c r="D40" s="62">
+        <f t="shared" ref="D40:L41" si="2">D6</f>
+        <v>2022</v>
+      </c>
+      <c r="E40" s="62">
+        <f t="shared" si="2"/>
+        <v>2023</v>
+      </c>
+      <c r="F40" s="62">
+        <f t="shared" si="2"/>
+        <v>2024</v>
+      </c>
+      <c r="G40" s="62">
+        <f t="shared" si="2"/>
+        <v>2025</v>
+      </c>
+      <c r="H40" s="62">
+        <f t="shared" si="2"/>
+        <v>2026</v>
+      </c>
+      <c r="I40" s="62">
+        <f t="shared" si="2"/>
+        <v>2027</v>
+      </c>
+      <c r="J40" s="62">
+        <f t="shared" si="2"/>
+        <v>2028</v>
+      </c>
+      <c r="K40" s="62">
+        <f t="shared" si="2"/>
+        <v>2029</v>
+      </c>
+      <c r="L40" s="62">
+        <f t="shared" si="2"/>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B41" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C41" s="153">
+        <f>C7</f>
+        <v>-34914.855348744117</v>
+      </c>
+      <c r="D41" s="153">
+        <f t="shared" si="2"/>
+        <v>-30304.075687291086</v>
+      </c>
+      <c r="E41" s="153">
+        <f t="shared" si="2"/>
+        <v>26818.405861506442</v>
+      </c>
+      <c r="F41" s="153">
+        <f t="shared" si="2"/>
+        <v>128852.20010556566</v>
+      </c>
+      <c r="G41" s="155">
+        <f t="shared" si="2"/>
+        <v>152361.29999999999</v>
+      </c>
+      <c r="H41" s="195">
+        <f t="shared" si="2"/>
+        <v>179786.33399999997</v>
+      </c>
+      <c r="I41" s="195">
+        <f t="shared" si="2"/>
+        <v>212147.87411999996</v>
+      </c>
+      <c r="J41" s="195">
+        <f t="shared" si="2"/>
+        <v>250334.49146159994</v>
+      </c>
+      <c r="K41" s="195">
+        <f t="shared" si="2"/>
+        <v>295394.69992468791</v>
+      </c>
+      <c r="L41" s="195">
+        <f t="shared" si="2"/>
+        <v>348565.74591113173</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B42" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C42" s="153">
+        <f>'[2]FCF &amp; Other'!C12</f>
+        <v>108949</v>
+      </c>
+      <c r="D42" s="153">
+        <f>'[2]FCF &amp; Other'!D12</f>
+        <v>119437</v>
+      </c>
+      <c r="E42" s="153">
+        <f>'[2]FCF &amp; Other'!E12</f>
+        <v>114301</v>
+      </c>
+      <c r="F42" s="153">
+        <f>'[2]FCF &amp; Other'!F12</f>
+        <v>123216</v>
+      </c>
+      <c r="G42" s="155">
+        <f>'[2]FCF &amp; Other'!G12</f>
+        <v>133050</v>
+      </c>
+      <c r="H42" s="195">
+        <f>H41/H43</f>
+        <v>179786.33399999997</v>
+      </c>
+      <c r="I42" s="195">
+        <f t="shared" ref="I42:L42" si="3">I41/I43</f>
+        <v>212147.87411999996</v>
+      </c>
+      <c r="J42" s="195">
+        <f t="shared" si="3"/>
+        <v>263509.99101221049</v>
+      </c>
+      <c r="K42" s="195">
+        <f t="shared" si="3"/>
+        <v>328216.33324965322</v>
+      </c>
+      <c r="L42" s="195">
+        <f t="shared" si="3"/>
+        <v>435707.18238891463</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B43" s="198" t="s">
+        <v>362</v>
+      </c>
+      <c r="C43" s="116">
+        <f>C41/C42</f>
+        <v>-0.32046971838882521</v>
+      </c>
+      <c r="D43" s="116">
+        <f t="shared" ref="D43:G43" si="4">D41/D42</f>
+        <v>-0.25372435415567274</v>
+      </c>
+      <c r="E43" s="116">
+        <f t="shared" si="4"/>
+        <v>0.23462966956987641</v>
+      </c>
+      <c r="F43" s="116">
+        <f t="shared" si="4"/>
+        <v>1.0457424369040194</v>
+      </c>
+      <c r="G43" s="117">
+        <f t="shared" si="4"/>
+        <v>1.1451431792559188</v>
+      </c>
+      <c r="H43" s="194">
+        <v>1</v>
+      </c>
+      <c r="I43" s="194">
+        <v>1</v>
+      </c>
+      <c r="J43" s="194">
+        <v>0.95</v>
+      </c>
+      <c r="K43" s="194">
+        <v>0.9</v>
+      </c>
+      <c r="L43" s="194">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="153">
+        <f>'[2]FCF &amp; Other'!C6</f>
+        <v>365817</v>
+      </c>
+      <c r="D44" s="153">
+        <f>'[2]FCF &amp; Other'!D6</f>
+        <v>394328</v>
+      </c>
+      <c r="E44" s="153">
+        <f>'[2]FCF &amp; Other'!E6</f>
+        <v>383285</v>
+      </c>
+      <c r="F44" s="153">
+        <f>'[2]FCF &amp; Other'!F6</f>
+        <v>391035</v>
+      </c>
+      <c r="G44" s="155">
+        <f>'[2]FCF &amp; Other'!G6</f>
+        <v>416161</v>
+      </c>
+      <c r="H44" s="195">
+        <f>H41/H45</f>
+        <v>449465.8349999999</v>
+      </c>
+      <c r="I44" s="195">
+        <f t="shared" ref="I44:L44" si="5">I41/I45</f>
+        <v>530369.6852999999</v>
+      </c>
+      <c r="J44" s="195">
+        <f t="shared" si="5"/>
+        <v>715241.40417599992</v>
+      </c>
+      <c r="K44" s="195">
+        <f t="shared" si="5"/>
+        <v>984648.99974895979</v>
+      </c>
+      <c r="L44" s="195">
+        <f t="shared" si="5"/>
+        <v>1161885.8197037724</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B45" s="198" t="s">
+        <v>363</v>
+      </c>
+      <c r="C45" s="116">
+        <f>C41/C44</f>
+        <v>-9.5443501392073402E-2</v>
+      </c>
+      <c r="D45" s="116">
+        <f t="shared" ref="D45:G45" si="6">D41/D44</f>
+        <v>-7.6849921099417448E-2</v>
+      </c>
+      <c r="E45" s="116">
+        <f t="shared" si="6"/>
+        <v>6.9969881058498093E-2</v>
+      </c>
+      <c r="F45" s="116">
+        <f t="shared" si="6"/>
+        <v>0.32951577251541592</v>
+      </c>
+      <c r="G45" s="117">
+        <f t="shared" si="6"/>
+        <v>0.3661114328348884</v>
+      </c>
+      <c r="H45" s="194">
+        <v>0.4</v>
+      </c>
+      <c r="I45" s="194">
+        <v>0.4</v>
+      </c>
+      <c r="J45" s="194">
+        <v>0.35</v>
+      </c>
+      <c r="K45" s="194">
+        <v>0.3</v>
+      </c>
+      <c r="L45" s="194">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B46" s="198" t="s">
+        <v>364</v>
+      </c>
+      <c r="C46" s="151"/>
+      <c r="D46" s="116">
+        <f>D41/C41-1</f>
+        <v>-0.1320578193837163</v>
+      </c>
+      <c r="E46" s="116">
+        <f t="shared" ref="E46:L47" si="7">E41/D41-1</f>
+        <v>-1.8849768637805222</v>
+      </c>
+      <c r="F46" s="116">
+        <f t="shared" si="7"/>
+        <v>3.8046181704824038</v>
+      </c>
+      <c r="G46" s="117">
+        <f t="shared" si="7"/>
+        <v>0.18245012405821437</v>
+      </c>
+      <c r="H46" s="234">
+        <f t="shared" si="7"/>
+        <v>0.17999999999999994</v>
+      </c>
+      <c r="I46" s="234">
+        <f t="shared" si="7"/>
+        <v>0.17999999999999994</v>
+      </c>
+      <c r="J46" s="234">
+        <f t="shared" si="7"/>
+        <v>0.17999999999999994</v>
+      </c>
+      <c r="K46" s="234">
+        <f t="shared" si="7"/>
+        <v>0.17999999999999994</v>
+      </c>
+      <c r="L46" s="234">
+        <f t="shared" si="7"/>
+        <v>0.17999999999999994</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B47" s="198" t="s">
+        <v>365</v>
+      </c>
+      <c r="C47" s="151"/>
+      <c r="D47" s="116">
+        <f>D42/C42-1</f>
+        <v>9.6265225013538513E-2</v>
+      </c>
+      <c r="E47" s="116">
+        <f t="shared" si="7"/>
+        <v>-4.3001749876503959E-2</v>
+      </c>
+      <c r="F47" s="116">
+        <f t="shared" si="7"/>
+        <v>7.7995818059334532E-2</v>
+      </c>
+      <c r="G47" s="117">
+        <f t="shared" si="7"/>
+        <v>7.9811063498246959E-2</v>
+      </c>
+      <c r="H47" s="234">
+        <f t="shared" si="7"/>
+        <v>0.35126895152198401</v>
+      </c>
+      <c r="I47" s="234">
+        <f t="shared" si="7"/>
+        <v>0.17999999999999994</v>
+      </c>
+      <c r="J47" s="234">
+        <f t="shared" si="7"/>
+        <v>0.24210526315789482</v>
+      </c>
+      <c r="K47" s="234">
+        <f t="shared" si="7"/>
+        <v>0.2455555555555553</v>
+      </c>
+      <c r="L47" s="234">
+        <f t="shared" si="7"/>
+        <v>0.3274999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B48" s="198" t="s">
+        <v>366</v>
+      </c>
+      <c r="C48" s="151"/>
+      <c r="D48" s="116">
+        <f>D44/C44-1</f>
+        <v>7.7937876041846099E-2</v>
+      </c>
+      <c r="E48" s="116">
+        <f t="shared" ref="E48:L48" si="8">E44/D44-1</f>
+        <v>-2.800460530319937E-2</v>
+      </c>
+      <c r="F48" s="116">
+        <f t="shared" si="8"/>
+        <v>2.021994077514111E-2</v>
+      </c>
+      <c r="G48" s="117">
+        <f t="shared" si="8"/>
+        <v>6.425511782832749E-2</v>
+      </c>
+      <c r="H48" s="234">
+        <f t="shared" si="8"/>
+        <v>8.0028726862920507E-2</v>
+      </c>
+      <c r="I48" s="234">
+        <f t="shared" si="8"/>
+        <v>0.17999999999999994</v>
+      </c>
+      <c r="J48" s="234">
+        <f t="shared" si="8"/>
+        <v>0.34857142857142875</v>
+      </c>
+      <c r="K48" s="234">
+        <f t="shared" si="8"/>
+        <v>0.37666666666666648</v>
+      </c>
+      <c r="L48" s="234">
+        <f t="shared" si="8"/>
+        <v>0.17999999999999994</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B49" s="198" t="s">
+        <v>367</v>
+      </c>
+      <c r="C49" s="116">
+        <f>C42/C44</f>
+        <v>0.29782377527561593</v>
+      </c>
+      <c r="D49" s="116">
+        <f t="shared" ref="D49:L49" si="9">D42/D44</f>
+        <v>0.30288744395528594</v>
+      </c>
+      <c r="E49" s="116">
+        <f t="shared" si="9"/>
+        <v>0.29821412265024722</v>
+      </c>
+      <c r="F49" s="116">
+        <f t="shared" si="9"/>
+        <v>0.31510222870075566</v>
+      </c>
+      <c r="G49" s="117">
+        <f t="shared" si="9"/>
+        <v>0.31970799762591884</v>
+      </c>
+      <c r="H49" s="234">
+        <f t="shared" si="9"/>
+        <v>0.4</v>
+      </c>
+      <c r="I49" s="234">
+        <f t="shared" si="9"/>
+        <v>0.4</v>
+      </c>
+      <c r="J49" s="234">
+        <f t="shared" si="9"/>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="K49" s="234">
+        <f t="shared" si="9"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L49" s="234">
+        <f t="shared" si="9"/>
+        <v>0.375</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10448,11 +11803,11 @@
         <v>86</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="212" t="s">
+      <c r="P4" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="Q4" s="213"/>
-      <c r="R4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="215"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -20813,8 +22168,8 @@
       <c r="D2" s="208"/>
       <c r="E2" s="208"/>
       <c r="F2" s="208"/>
-      <c r="G2" s="209"/>
-      <c r="H2" s="210" t="s">
+      <c r="G2" s="211"/>
+      <c r="H2" s="212" t="s">
         <v>179</v>
       </c>
       <c r="I2" s="208"/>
@@ -20860,19 +22215,19 @@
       <c r="K4" s="207"/>
       <c r="L4" s="207"/>
       <c r="O4" s="92"/>
-      <c r="S4" s="215" t="s">
+      <c r="S4" s="209" t="s">
         <v>187</v>
       </c>
-      <c r="T4" s="216"/>
-      <c r="U4" s="216"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="216"/>
-      <c r="X4" s="216"/>
-      <c r="Y4" s="216"/>
-      <c r="Z4" s="216"/>
-      <c r="AA4" s="216"/>
-      <c r="AB4" s="216"/>
-      <c r="AC4" s="216"/>
+      <c r="T4" s="210"/>
+      <c r="U4" s="210"/>
+      <c r="V4" s="210"/>
+      <c r="W4" s="210"/>
+      <c r="X4" s="210"/>
+      <c r="Y4" s="210"/>
+      <c r="Z4" s="210"/>
+      <c r="AA4" s="210"/>
+      <c r="AB4" s="210"/>
+      <c r="AC4" s="210"/>
       <c r="AE4" s="140" t="s">
         <v>212</v>
       </c>
@@ -21682,19 +23037,19 @@
       <c r="L14" s="207"/>
       <c r="O14" s="92"/>
       <c r="Q14" s="93"/>
-      <c r="S14" s="215" t="s">
+      <c r="S14" s="209" t="s">
         <v>193</v>
       </c>
-      <c r="T14" s="216"/>
-      <c r="U14" s="216"/>
-      <c r="V14" s="216"/>
-      <c r="W14" s="216"/>
-      <c r="X14" s="216"/>
-      <c r="Y14" s="216"/>
-      <c r="Z14" s="216"/>
-      <c r="AA14" s="216"/>
-      <c r="AB14" s="216"/>
-      <c r="AC14" s="216"/>
+      <c r="T14" s="210"/>
+      <c r="U14" s="210"/>
+      <c r="V14" s="210"/>
+      <c r="W14" s="210"/>
+      <c r="X14" s="210"/>
+      <c r="Y14" s="210"/>
+      <c r="Z14" s="210"/>
+      <c r="AA14" s="210"/>
+      <c r="AB14" s="210"/>
+      <c r="AC14" s="210"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B15" s="7" t="s">
@@ -22401,19 +23756,19 @@
       <c r="L25" s="207"/>
       <c r="O25" s="92"/>
       <c r="Q25" s="93"/>
-      <c r="S25" s="215" t="s">
+      <c r="S25" s="209" t="s">
         <v>195</v>
       </c>
-      <c r="T25" s="216"/>
-      <c r="U25" s="216"/>
-      <c r="V25" s="216"/>
-      <c r="W25" s="216"/>
-      <c r="X25" s="216"/>
-      <c r="Y25" s="216"/>
-      <c r="Z25" s="216"/>
-      <c r="AA25" s="216"/>
-      <c r="AB25" s="216"/>
-      <c r="AC25" s="216"/>
+      <c r="T25" s="210"/>
+      <c r="U25" s="210"/>
+      <c r="V25" s="210"/>
+      <c r="W25" s="210"/>
+      <c r="X25" s="210"/>
+      <c r="Y25" s="210"/>
+      <c r="Z25" s="210"/>
+      <c r="AA25" s="210"/>
+      <c r="AB25" s="210"/>
+      <c r="AC25" s="210"/>
       <c r="AE25" s="140" t="str">
         <f>AE4</f>
         <v>Q1-Q2-Q3</v>
@@ -23749,19 +25104,19 @@
       <c r="K43" s="207"/>
       <c r="L43" s="207"/>
       <c r="O43" s="92"/>
-      <c r="S43" s="215" t="s">
+      <c r="S43" s="209" t="s">
         <v>207</v>
       </c>
-      <c r="T43" s="216"/>
-      <c r="U43" s="216"/>
-      <c r="V43" s="216"/>
-      <c r="W43" s="216"/>
-      <c r="X43" s="216"/>
-      <c r="Y43" s="216"/>
-      <c r="Z43" s="216"/>
-      <c r="AA43" s="216"/>
-      <c r="AB43" s="216"/>
-      <c r="AC43" s="216"/>
+      <c r="T43" s="210"/>
+      <c r="U43" s="210"/>
+      <c r="V43" s="210"/>
+      <c r="W43" s="210"/>
+      <c r="X43" s="210"/>
+      <c r="Y43" s="210"/>
+      <c r="Z43" s="210"/>
+      <c r="AA43" s="210"/>
+      <c r="AB43" s="210"/>
+      <c r="AC43" s="210"/>
     </row>
     <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B44" s="7" t="s">
@@ -24383,8 +25738,8 @@
       <c r="D2" s="208"/>
       <c r="E2" s="208"/>
       <c r="F2" s="208"/>
-      <c r="G2" s="209"/>
-      <c r="H2" s="210" t="s">
+      <c r="G2" s="211"/>
+      <c r="H2" s="212" t="s">
         <v>179</v>
       </c>
       <c r="I2" s="208"/>
@@ -24426,19 +25781,19 @@
       <c r="J4" s="207"/>
       <c r="K4" s="207"/>
       <c r="L4" s="207"/>
-      <c r="P4" s="216" t="s">
+      <c r="P4" s="210" t="s">
         <v>187</v>
       </c>
-      <c r="Q4" s="216"/>
-      <c r="R4" s="216"/>
-      <c r="S4" s="216"/>
-      <c r="T4" s="216"/>
-      <c r="U4" s="216"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="216"/>
-      <c r="X4" s="216"/>
-      <c r="Y4" s="216"/>
-      <c r="Z4" s="216"/>
+      <c r="Q4" s="210"/>
+      <c r="R4" s="210"/>
+      <c r="S4" s="210"/>
+      <c r="T4" s="210"/>
+      <c r="U4" s="210"/>
+      <c r="V4" s="210"/>
+      <c r="W4" s="210"/>
+      <c r="X4" s="210"/>
+      <c r="Y4" s="210"/>
+      <c r="Z4" s="210"/>
       <c r="AB4" s="140" t="s">
         <v>212</v>
       </c>
@@ -24652,19 +26007,19 @@
       <c r="K9" s="207"/>
       <c r="L9" s="207"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="216" t="s">
+      <c r="P9" s="210" t="s">
         <v>219</v>
       </c>
-      <c r="Q9" s="216"/>
-      <c r="R9" s="216"/>
-      <c r="S9" s="216"/>
-      <c r="T9" s="216"/>
-      <c r="U9" s="216"/>
-      <c r="V9" s="216"/>
-      <c r="W9" s="216"/>
-      <c r="X9" s="216"/>
-      <c r="Y9" s="216"/>
-      <c r="Z9" s="216"/>
+      <c r="Q9" s="210"/>
+      <c r="R9" s="210"/>
+      <c r="S9" s="210"/>
+      <c r="T9" s="210"/>
+      <c r="U9" s="210"/>
+      <c r="V9" s="210"/>
+      <c r="W9" s="210"/>
+      <c r="X9" s="210"/>
+      <c r="Y9" s="210"/>
+      <c r="Z9" s="210"/>
       <c r="AB9" s="140" t="str">
         <f>AB4</f>
         <v>Q1-Q2-Q3</v>
@@ -25238,19 +26593,19 @@
       <c r="J18" s="207"/>
       <c r="K18" s="207"/>
       <c r="L18" s="207"/>
-      <c r="P18" s="216" t="s">
+      <c r="P18" s="210" t="s">
         <v>217</v>
       </c>
-      <c r="Q18" s="216"/>
-      <c r="R18" s="216"/>
-      <c r="S18" s="216"/>
-      <c r="T18" s="216"/>
-      <c r="U18" s="216"/>
-      <c r="V18" s="216"/>
-      <c r="W18" s="216"/>
-      <c r="X18" s="216"/>
-      <c r="Y18" s="216"/>
-      <c r="Z18" s="216"/>
+      <c r="Q18" s="210"/>
+      <c r="R18" s="210"/>
+      <c r="S18" s="210"/>
+      <c r="T18" s="210"/>
+      <c r="U18" s="210"/>
+      <c r="V18" s="210"/>
+      <c r="W18" s="210"/>
+      <c r="X18" s="210"/>
+      <c r="Y18" s="210"/>
+      <c r="Z18" s="210"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -25728,25 +27083,25 @@
       <c r="D3" s="208"/>
       <c r="E3" s="208"/>
       <c r="F3" s="208"/>
-      <c r="G3" s="209"/>
-      <c r="H3" s="210" t="s">
+      <c r="G3" s="211"/>
+      <c r="H3" s="212" t="s">
         <v>179</v>
       </c>
       <c r="I3" s="208"/>
       <c r="J3" s="208"/>
       <c r="K3" s="208"/>
       <c r="L3" s="208"/>
-      <c r="P3" s="211"/>
-      <c r="Q3" s="211"/>
-      <c r="R3" s="211"/>
-      <c r="S3" s="211"/>
-      <c r="T3" s="211"/>
-      <c r="U3" s="211"/>
-      <c r="V3" s="211"/>
-      <c r="W3" s="211"/>
-      <c r="X3" s="211"/>
-      <c r="Y3" s="211"/>
-      <c r="Z3" s="211"/>
+      <c r="P3" s="216"/>
+      <c r="Q3" s="216"/>
+      <c r="R3" s="216"/>
+      <c r="S3" s="216"/>
+      <c r="T3" s="216"/>
+      <c r="U3" s="216"/>
+      <c r="V3" s="216"/>
+      <c r="W3" s="216"/>
+      <c r="X3" s="216"/>
+      <c r="Y3" s="216"/>
+      <c r="Z3" s="216"/>
       <c r="AB3" s="143"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -25765,17 +27120,17 @@
       <c r="J5" s="207"/>
       <c r="K5" s="207"/>
       <c r="L5" s="207"/>
-      <c r="P5" s="211"/>
-      <c r="Q5" s="211"/>
-      <c r="R5" s="211"/>
-      <c r="S5" s="211"/>
-      <c r="T5" s="211"/>
-      <c r="U5" s="211"/>
-      <c r="V5" s="211"/>
-      <c r="W5" s="211"/>
-      <c r="X5" s="211"/>
-      <c r="Y5" s="211"/>
-      <c r="Z5" s="211"/>
+      <c r="P5" s="216"/>
+      <c r="Q5" s="216"/>
+      <c r="R5" s="216"/>
+      <c r="S5" s="216"/>
+      <c r="T5" s="216"/>
+      <c r="U5" s="216"/>
+      <c r="V5" s="216"/>
+      <c r="W5" s="216"/>
+      <c r="X5" s="216"/>
+      <c r="Y5" s="216"/>
+      <c r="Z5" s="216"/>
       <c r="AB5" s="144"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -26033,17 +27388,17 @@
       <c r="K12" s="207"/>
       <c r="L12" s="207"/>
       <c r="N12" s="93"/>
-      <c r="P12" s="211"/>
-      <c r="Q12" s="211"/>
-      <c r="R12" s="211"/>
-      <c r="S12" s="211"/>
-      <c r="T12" s="211"/>
-      <c r="U12" s="211"/>
-      <c r="V12" s="211"/>
-      <c r="W12" s="211"/>
-      <c r="X12" s="211"/>
-      <c r="Y12" s="211"/>
-      <c r="Z12" s="211"/>
+      <c r="P12" s="216"/>
+      <c r="Q12" s="216"/>
+      <c r="R12" s="216"/>
+      <c r="S12" s="216"/>
+      <c r="T12" s="216"/>
+      <c r="U12" s="216"/>
+      <c r="V12" s="216"/>
+      <c r="W12" s="216"/>
+      <c r="X12" s="216"/>
+      <c r="Y12" s="216"/>
+      <c r="Z12" s="216"/>
       <c r="AB12" s="144"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -26420,8 +27775,8 @@
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B24" s="211"/>
-      <c r="C24" s="211"/>
+      <c r="B24" s="216"/>
+      <c r="C24" s="216"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="143"/>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694E0D33-1D1F-7C4D-9489-CF7A585AF272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE5B93A-C557-DA49-8F88-FAD139FC65D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="15" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="9" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2205,22 +2205,43 @@
     <xf numFmtId="3" fontId="0" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="11" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="8" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="8" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="3" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="0" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="2" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="1" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="38" fontId="0" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2232,33 +2253,12 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="2" fillId="8" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="2" fillId="8" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="2" fillId="3" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="0" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="2" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="1" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="38" fontId="0" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2348,35 +2348,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="1. List_AutomaticData"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="C4">
-            <v>106.24</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="C10">
-            <v>43.36</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2511,6 +2482,35 @@
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="1. List_AutomaticData"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="C4">
+            <v>108.25</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>44.18</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2973,8 +2973,8 @@
         <v>85</v>
       </c>
       <c r="C3" s="35">
-        <f>[1]Sheet1!$C$4</f>
-        <v>106.24</v>
+        <f>[2]Sheet1!$C$4</f>
+        <v>108.25</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C11" s="95">
         <f>$C$3/'Statement Q'!$N$22</f>
-        <v>12.505399515893458</v>
+        <v>12.741994518029621</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="C12" s="95">
         <f>C3/Statements!S20</f>
-        <v>31.118848116970341</v>
+        <v>31.707598914364077</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="C13" s="102">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$20)</f>
-        <v>4.9904617826021909</v>
+        <v>5.0848784635418598</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C15" s="20">
         <f>C3*'Statement Q'!N116</f>
-        <v>5035776</v>
+        <v>5131050</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="C18" s="20">
         <f>C15+C17-C16</f>
-        <v>3895309</v>
+        <v>3990583</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -3256,60 +3256,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="208" t="s">
+      <c r="C2" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="211"/>
-      <c r="H2" s="212" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="227"/>
+      <c r="H2" s="228" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
-      <c r="S2" s="216"/>
-      <c r="T2" s="216"/>
-      <c r="U2" s="216"/>
-      <c r="V2" s="216"/>
-      <c r="W2" s="216"/>
-      <c r="X2" s="216"/>
-      <c r="Y2" s="216"/>
-      <c r="Z2" s="216"/>
-      <c r="AA2" s="216"/>
-      <c r="AB2" s="216"/>
-      <c r="AC2" s="216"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="226"/>
+      <c r="S2" s="229"/>
+      <c r="T2" s="229"/>
+      <c r="U2" s="229"/>
+      <c r="V2" s="229"/>
+      <c r="W2" s="229"/>
+      <c r="X2" s="229"/>
+      <c r="Y2" s="229"/>
+      <c r="Z2" s="229"/>
+      <c r="AA2" s="229"/>
+      <c r="AB2" s="229"/>
+      <c r="AC2" s="229"/>
       <c r="AE2" s="143"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="207" t="s">
+      <c r="C4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="207"/>
-      <c r="E4" s="207"/>
-      <c r="F4" s="207"/>
-      <c r="G4" s="207"/>
-      <c r="H4" s="207"/>
-      <c r="I4" s="207"/>
-      <c r="J4" s="207"/>
-      <c r="K4" s="207"/>
-      <c r="L4" s="207"/>
-      <c r="S4" s="216"/>
-      <c r="T4" s="216"/>
-      <c r="U4" s="216"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="216"/>
-      <c r="X4" s="216"/>
-      <c r="Y4" s="216"/>
-      <c r="Z4" s="216"/>
-      <c r="AA4" s="216"/>
-      <c r="AB4" s="216"/>
-      <c r="AC4" s="216"/>
+      <c r="D4" s="225"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="225"/>
+      <c r="G4" s="225"/>
+      <c r="H4" s="225"/>
+      <c r="I4" s="225"/>
+      <c r="J4" s="225"/>
+      <c r="K4" s="225"/>
+      <c r="L4" s="225"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="229"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="229"/>
+      <c r="Y4" s="229"/>
+      <c r="Z4" s="229"/>
+      <c r="AA4" s="229"/>
+      <c r="AB4" s="229"/>
+      <c r="AC4" s="229"/>
       <c r="AE4" s="144"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -3855,18 +3855,18 @@
       <c r="AE13" s="108"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C16" s="207" t="s">
+      <c r="C16" s="225" t="s">
         <v>236</v>
       </c>
-      <c r="D16" s="207"/>
-      <c r="E16" s="207"/>
-      <c r="F16" s="207"/>
-      <c r="G16" s="207"/>
-      <c r="H16" s="207"/>
-      <c r="I16" s="207"/>
-      <c r="J16" s="207"/>
-      <c r="K16" s="207"/>
-      <c r="L16" s="207"/>
+      <c r="D16" s="225"/>
+      <c r="E16" s="225"/>
+      <c r="F16" s="225"/>
+      <c r="G16" s="225"/>
+      <c r="H16" s="225"/>
+      <c r="I16" s="225"/>
+      <c r="J16" s="225"/>
+      <c r="K16" s="225"/>
+      <c r="L16" s="225"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C17" s="62">
@@ -3950,18 +3950,18 @@
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="207" t="s">
+      <c r="C21" s="225" t="s">
         <v>331</v>
       </c>
-      <c r="D21" s="207"/>
-      <c r="E21" s="207"/>
-      <c r="F21" s="207"/>
-      <c r="G21" s="207"/>
-      <c r="H21" s="207"/>
-      <c r="I21" s="207"/>
-      <c r="J21" s="207"/>
-      <c r="K21" s="207"/>
-      <c r="L21" s="207"/>
+      <c r="D21" s="225"/>
+      <c r="E21" s="225"/>
+      <c r="F21" s="225"/>
+      <c r="G21" s="225"/>
+      <c r="H21" s="225"/>
+      <c r="I21" s="225"/>
+      <c r="J21" s="225"/>
+      <c r="K21" s="225"/>
+      <c r="L21" s="225"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
@@ -4153,18 +4153,18 @@
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C28" s="207" t="s">
+      <c r="C28" s="225" t="s">
         <v>238</v>
       </c>
-      <c r="D28" s="207"/>
-      <c r="E28" s="207"/>
-      <c r="F28" s="207"/>
-      <c r="G28" s="207"/>
-      <c r="H28" s="207"/>
-      <c r="I28" s="207"/>
-      <c r="J28" s="207"/>
-      <c r="K28" s="207"/>
-      <c r="L28" s="207"/>
+      <c r="D28" s="225"/>
+      <c r="E28" s="225"/>
+      <c r="F28" s="225"/>
+      <c r="G28" s="225"/>
+      <c r="H28" s="225"/>
+      <c r="I28" s="225"/>
+      <c r="J28" s="225"/>
+      <c r="K28" s="225"/>
+      <c r="L28" s="225"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
@@ -4371,10 +4371,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="226" t="s">
         <v>255</v>
       </c>
-      <c r="C4" s="208"/>
+      <c r="C4" s="226"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="C6" s="166">
         <f>Overview!C3</f>
-        <v>106.24</v>
+        <v>108.25</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C7" s="168">
         <f>C5*C6</f>
-        <v>5035776</v>
+        <v>5131050</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4416,8 +4416,8 @@
         <v>257</v>
       </c>
       <c r="C9" s="191">
-        <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.3360000000000003E-2</v>
+        <f>[2]Sheet1!$C$10/1000</f>
+        <v>4.4179999999999997E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4454,10 +4454,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="208" t="s">
+      <c r="B15" s="226" t="s">
         <v>261</v>
       </c>
-      <c r="C15" s="208"/>
+      <c r="C15" s="226"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="C19" s="169">
         <f>C9+C10*C11</f>
-        <v>8.5535E-2</v>
+        <v>8.6355000000000001E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="C20" s="169">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>8.5535E-2</v>
+        <v>8.6355000000000001E-2</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4548,60 +4548,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="104"/>
-      <c r="C3" s="208" t="s">
+      <c r="C3" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="211"/>
-      <c r="H3" s="212" t="s">
+      <c r="D3" s="226"/>
+      <c r="E3" s="226"/>
+      <c r="F3" s="226"/>
+      <c r="G3" s="227"/>
+      <c r="H3" s="228" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="208"/>
-      <c r="J3" s="208"/>
-      <c r="K3" s="208"/>
-      <c r="L3" s="208"/>
-      <c r="P3" s="216"/>
-      <c r="Q3" s="216"/>
-      <c r="R3" s="216"/>
-      <c r="S3" s="216"/>
-      <c r="T3" s="216"/>
-      <c r="U3" s="216"/>
-      <c r="V3" s="216"/>
-      <c r="W3" s="216"/>
-      <c r="X3" s="216"/>
-      <c r="Y3" s="216"/>
-      <c r="Z3" s="216"/>
+      <c r="I3" s="226"/>
+      <c r="J3" s="226"/>
+      <c r="K3" s="226"/>
+      <c r="L3" s="226"/>
+      <c r="P3" s="229"/>
+      <c r="Q3" s="229"/>
+      <c r="R3" s="229"/>
+      <c r="S3" s="229"/>
+      <c r="T3" s="229"/>
+      <c r="U3" s="229"/>
+      <c r="V3" s="229"/>
+      <c r="W3" s="229"/>
+      <c r="X3" s="229"/>
+      <c r="Y3" s="229"/>
+      <c r="Z3" s="229"/>
       <c r="AB3" s="143"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="109"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="207" t="s">
+      <c r="C5" s="225" t="s">
         <v>275</v>
       </c>
-      <c r="D5" s="207"/>
-      <c r="E5" s="207"/>
-      <c r="F5" s="207"/>
-      <c r="G5" s="207"/>
-      <c r="H5" s="207"/>
-      <c r="I5" s="207"/>
-      <c r="J5" s="207"/>
-      <c r="K5" s="207"/>
-      <c r="L5" s="207"/>
-      <c r="P5" s="216"/>
-      <c r="Q5" s="216"/>
-      <c r="R5" s="216"/>
-      <c r="S5" s="216"/>
-      <c r="T5" s="216"/>
-      <c r="U5" s="216"/>
-      <c r="V5" s="216"/>
-      <c r="W5" s="216"/>
-      <c r="X5" s="216"/>
-      <c r="Y5" s="216"/>
-      <c r="Z5" s="216"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="225"/>
+      <c r="F5" s="225"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="225"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
+      <c r="L5" s="225"/>
+      <c r="P5" s="229"/>
+      <c r="Q5" s="229"/>
+      <c r="R5" s="229"/>
+      <c r="S5" s="229"/>
+      <c r="T5" s="229"/>
+      <c r="U5" s="229"/>
+      <c r="V5" s="229"/>
+      <c r="W5" s="229"/>
+      <c r="X5" s="229"/>
+      <c r="Y5" s="229"/>
+      <c r="Z5" s="229"/>
       <c r="AB5" s="144"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="L8" s="154">
         <f>L7*(1+C14)/(C15-C14)</f>
-        <v>10317388.228638493</v>
+        <v>10189888.2912188</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="7"/>
@@ -4808,23 +4808,23 @@
       <c r="G10" s="171"/>
       <c r="H10" s="154">
         <f>H7/(1+$C$15)^H9</f>
-        <v>143146.55194802422</v>
+        <v>143038.50239461177</v>
       </c>
       <c r="I10" s="154">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$15)^I9</f>
-        <v>216514.21920653529</v>
+        <v>216187.48502856525</v>
       </c>
       <c r="J10" s="154">
         <f t="shared" si="1"/>
-        <v>255747.34610477317</v>
+        <v>255168.65524769839</v>
       </c>
       <c r="K10" s="154">
         <f t="shared" si="1"/>
-        <v>296965.13217522728</v>
+        <v>296069.52866804809</v>
       </c>
       <c r="L10" s="154">
         <f t="shared" si="1"/>
-        <v>439768.12882532179</v>
+        <v>438110.90863962681</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -4843,14 +4843,14 @@
       <c r="K11" s="151"/>
       <c r="L11" s="154">
         <f>L8/(1+C15)^L9</f>
-        <v>6844640.1373590948</v>
+        <v>6734581.06868238</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="208" t="s">
+      <c r="B13" s="226" t="s">
         <v>276</v>
       </c>
-      <c r="C13" s="208"/>
+      <c r="C13" s="226"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4866,14 +4866,14 @@
       </c>
       <c r="C15" s="170">
         <f>WACC!C20</f>
-        <v>8.5535E-2</v>
+        <v>8.6355000000000001E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="208" t="s">
+      <c r="B18" s="226" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="208"/>
+      <c r="C18" s="226"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C19" s="108">
         <f>SUM(H10:L10)</f>
-        <v>1352141.3782598819</v>
+        <v>1348575.0799785503</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C20" s="108">
         <f>L11</f>
-        <v>6844640.1373590948</v>
+        <v>6734581.06868238</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="C21" s="113">
         <f>C19+C20</f>
-        <v>8196781.5156189762</v>
+        <v>8083156.1486609299</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="C24" s="113">
         <f>C21+C22-C23</f>
-        <v>9243469.5156189762</v>
+        <v>9129844.1486609299</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="C26" s="173">
         <f>C24/C25</f>
-        <v>189.65180581995355</v>
+        <v>187.3205106288853</v>
       </c>
     </row>
   </sheetData>
@@ -4987,37 +4987,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="208" t="s">
+      <c r="C2" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="211"/>
-      <c r="H2" s="212" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="227"/>
+      <c r="H2" s="228" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="226"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="207" t="s">
+      <c r="C4" s="225" t="s">
         <v>338</v>
       </c>
-      <c r="D4" s="207"/>
-      <c r="E4" s="207"/>
-      <c r="F4" s="207"/>
-      <c r="G4" s="207"/>
-      <c r="H4" s="207"/>
-      <c r="I4" s="207"/>
-      <c r="J4" s="207"/>
-      <c r="K4" s="207"/>
-      <c r="L4" s="207"/>
+      <c r="D4" s="225"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="225"/>
+      <c r="G4" s="225"/>
+      <c r="H4" s="225"/>
+      <c r="I4" s="225"/>
+      <c r="J4" s="225"/>
+      <c r="K4" s="225"/>
+      <c r="L4" s="225"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -5206,18 +5206,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="207" t="s">
+      <c r="C10" s="225" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="207"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="207"/>
-      <c r="H10" s="207"/>
-      <c r="I10" s="207"/>
-      <c r="J10" s="207"/>
-      <c r="K10" s="207"/>
-      <c r="L10" s="207"/>
+      <c r="D10" s="225"/>
+      <c r="E10" s="225"/>
+      <c r="F10" s="225"/>
+      <c r="G10" s="225"/>
+      <c r="H10" s="225"/>
+      <c r="I10" s="225"/>
+      <c r="J10" s="225"/>
+      <c r="K10" s="225"/>
+      <c r="L10" s="225"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5399,18 +5399,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="207" t="s">
+      <c r="C16" s="225" t="s">
         <v>317</v>
       </c>
-      <c r="D16" s="207"/>
-      <c r="E16" s="207"/>
-      <c r="F16" s="207"/>
-      <c r="G16" s="207"/>
-      <c r="H16" s="207"/>
-      <c r="I16" s="207"/>
-      <c r="J16" s="207"/>
-      <c r="K16" s="207"/>
-      <c r="L16" s="207"/>
+      <c r="D16" s="225"/>
+      <c r="E16" s="225"/>
+      <c r="F16" s="225"/>
+      <c r="G16" s="225"/>
+      <c r="H16" s="225"/>
+      <c r="I16" s="225"/>
+      <c r="J16" s="225"/>
+      <c r="K16" s="225"/>
+      <c r="L16" s="225"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5544,18 +5544,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="207" t="s">
+      <c r="C21" s="225" t="s">
         <v>339</v>
       </c>
-      <c r="D21" s="207"/>
-      <c r="E21" s="207"/>
-      <c r="F21" s="207"/>
-      <c r="G21" s="207"/>
-      <c r="H21" s="207"/>
-      <c r="I21" s="207"/>
-      <c r="J21" s="207"/>
-      <c r="K21" s="207"/>
-      <c r="L21" s="207"/>
+      <c r="D21" s="225"/>
+      <c r="E21" s="225"/>
+      <c r="F21" s="225"/>
+      <c r="G21" s="225"/>
+      <c r="H21" s="225"/>
+      <c r="I21" s="225"/>
+      <c r="J21" s="225"/>
+      <c r="K21" s="225"/>
+      <c r="L21" s="225"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5639,18 +5639,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="207" t="s">
+      <c r="C26" s="225" t="s">
         <v>341</v>
       </c>
-      <c r="D26" s="207"/>
-      <c r="E26" s="207"/>
-      <c r="F26" s="207"/>
-      <c r="G26" s="207"/>
-      <c r="H26" s="207"/>
-      <c r="I26" s="207"/>
-      <c r="J26" s="207"/>
-      <c r="K26" s="207"/>
-      <c r="L26" s="207"/>
+      <c r="D26" s="225"/>
+      <c r="E26" s="225"/>
+      <c r="F26" s="225"/>
+      <c r="G26" s="225"/>
+      <c r="H26" s="225"/>
+      <c r="I26" s="225"/>
+      <c r="J26" s="225"/>
+      <c r="K26" s="225"/>
+      <c r="L26" s="225"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -5915,10 +5915,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="208" t="s">
+      <c r="B37" s="226" t="s">
         <v>343</v>
       </c>
-      <c r="C37" s="208"/>
+      <c r="C37" s="226"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C39" s="159">
         <f>WACC!C20</f>
-        <v>8.5535E-2</v>
+        <v>8.6355000000000001E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -5980,14 +5980,14 @@
       </c>
       <c r="C44" s="173">
         <f>C43/(1+C48)^5</f>
-        <v>191.57915793566005</v>
+        <v>190.85721192166065</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="208" t="s">
+      <c r="B46" s="226" t="s">
         <v>290</v>
       </c>
-      <c r="C46" s="208"/>
+      <c r="C46" s="226"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="C48" s="159">
         <f>WACC!C20</f>
-        <v>8.5535E-2</v>
+        <v>8.6355000000000001E-2</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -6039,14 +6039,14 @@
       </c>
       <c r="C52" s="173">
         <f>C51/(1+C48)^5</f>
-        <v>184.73250727062003</v>
+        <v>184.03636214336703</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="208" t="s">
+      <c r="B54" s="226" t="s">
         <v>347</v>
       </c>
-      <c r="C54" s="208"/>
+      <c r="C54" s="226"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="C56" s="159">
         <f>WACC!C20</f>
-        <v>8.5535E-2</v>
+        <v>8.6355000000000001E-2</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="C61" s="173">
         <f>C60/(1+C56)^5</f>
-        <v>173.89723444542597</v>
+        <v>173.24192091024713</v>
       </c>
     </row>
   </sheetData>
@@ -6156,10 +6156,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="226" t="s">
         <v>298</v>
       </c>
-      <c r="C4" s="208"/>
+      <c r="C4" s="226"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="C5" s="188">
         <f>DCF!C26</f>
-        <v>189.65180581995355</v>
+        <v>187.3205106288853</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="C6" s="188">
         <f>Multiples!C44</f>
-        <v>191.57915793566005</v>
+        <v>190.85721192166065</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C7" s="188">
         <f>Multiples!C52</f>
-        <v>184.73250727062003</v>
+        <v>184.03636214336703</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="C8" s="188">
         <f>Multiples!C61</f>
-        <v>173.89723444542597</v>
+        <v>173.24192091024713</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="C9" s="173">
         <f>AVERAGE(C5:C8)</f>
-        <v>184.96517636791492</v>
+        <v>183.86400140104001</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="C10" s="35">
         <f>Overview!C3</f>
-        <v>106.24</v>
+        <v>108.25</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="C11" s="91">
         <f>(C9-C10)/C10</f>
-        <v>0.74101257876425952</v>
+        <v>0.69851271502115486</v>
       </c>
     </row>
   </sheetData>
@@ -6266,60 +6266,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="104"/>
-      <c r="C3" s="208" t="s">
+      <c r="C3" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="211"/>
-      <c r="H3" s="212" t="s">
+      <c r="D3" s="226"/>
+      <c r="E3" s="226"/>
+      <c r="F3" s="226"/>
+      <c r="G3" s="227"/>
+      <c r="H3" s="228" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="208"/>
-      <c r="J3" s="208"/>
-      <c r="K3" s="208"/>
-      <c r="L3" s="208"/>
-      <c r="P3" s="216"/>
-      <c r="Q3" s="216"/>
-      <c r="R3" s="216"/>
-      <c r="S3" s="216"/>
-      <c r="T3" s="216"/>
-      <c r="U3" s="216"/>
-      <c r="V3" s="216"/>
-      <c r="W3" s="216"/>
-      <c r="X3" s="216"/>
-      <c r="Y3" s="216"/>
-      <c r="Z3" s="216"/>
+      <c r="I3" s="226"/>
+      <c r="J3" s="226"/>
+      <c r="K3" s="226"/>
+      <c r="L3" s="226"/>
+      <c r="P3" s="229"/>
+      <c r="Q3" s="229"/>
+      <c r="R3" s="229"/>
+      <c r="S3" s="229"/>
+      <c r="T3" s="229"/>
+      <c r="U3" s="229"/>
+      <c r="V3" s="229"/>
+      <c r="W3" s="229"/>
+      <c r="X3" s="229"/>
+      <c r="Y3" s="229"/>
+      <c r="Z3" s="229"/>
       <c r="AB3" s="143"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="109"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="207" t="s">
+      <c r="C5" s="225" t="s">
         <v>275</v>
       </c>
-      <c r="D5" s="207"/>
-      <c r="E5" s="207"/>
-      <c r="F5" s="207"/>
-      <c r="G5" s="207"/>
-      <c r="H5" s="207"/>
-      <c r="I5" s="207"/>
-      <c r="J5" s="207"/>
-      <c r="K5" s="207"/>
-      <c r="L5" s="207"/>
-      <c r="P5" s="216"/>
-      <c r="Q5" s="216"/>
-      <c r="R5" s="216"/>
-      <c r="S5" s="216"/>
-      <c r="T5" s="216"/>
-      <c r="U5" s="216"/>
-      <c r="V5" s="216"/>
-      <c r="W5" s="216"/>
-      <c r="X5" s="216"/>
-      <c r="Y5" s="216"/>
-      <c r="Z5" s="216"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="225"/>
+      <c r="F5" s="225"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="225"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
+      <c r="L5" s="225"/>
+      <c r="P5" s="229"/>
+      <c r="Q5" s="229"/>
+      <c r="R5" s="229"/>
+      <c r="S5" s="229"/>
+      <c r="T5" s="229"/>
+      <c r="U5" s="229"/>
+      <c r="V5" s="229"/>
+      <c r="W5" s="229"/>
+      <c r="X5" s="229"/>
+      <c r="Y5" s="229"/>
+      <c r="Z5" s="229"/>
       <c r="AB5" s="144"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -6327,43 +6327,43 @@
         <v>225</v>
       </c>
       <c r="C6" s="62">
-        <f>[2]Revenue!C5</f>
+        <f>[1]Revenue!C5</f>
         <v>2021</v>
       </c>
       <c r="D6" s="62">
-        <f>[2]Revenue!D5</f>
+        <f>[1]Revenue!D5</f>
         <v>2022</v>
       </c>
       <c r="E6" s="62">
-        <f>[2]Revenue!E5</f>
+        <f>[1]Revenue!E5</f>
         <v>2023</v>
       </c>
       <c r="F6" s="62">
-        <f>[2]Revenue!F5</f>
+        <f>[1]Revenue!F5</f>
         <v>2024</v>
       </c>
       <c r="G6" s="62">
-        <f>[2]Revenue!G5</f>
+        <f>[1]Revenue!G5</f>
         <v>2025</v>
       </c>
       <c r="H6" s="62">
-        <f>[2]Revenue!H5</f>
+        <f>[1]Revenue!H5</f>
         <v>2026</v>
       </c>
       <c r="I6" s="62">
-        <f>[2]Revenue!I5</f>
+        <f>[1]Revenue!I5</f>
         <v>2027</v>
       </c>
       <c r="J6" s="62">
-        <f>[2]Revenue!J5</f>
+        <f>[1]Revenue!J5</f>
         <v>2028</v>
       </c>
       <c r="K6" s="62">
-        <f>[2]Revenue!K5</f>
+        <f>[1]Revenue!K5</f>
         <v>2029</v>
       </c>
       <c r="L6" s="62">
-        <f>[2]Revenue!L5</f>
+        <f>[1]Revenue!L5</f>
         <v>2030</v>
       </c>
       <c r="O6" s="7"/>
@@ -6454,7 +6454,7 @@
       <c r="K8" s="151"/>
       <c r="L8" s="154">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>5902038.3176494585</v>
+        <v>5823158.4966002768</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="7"/>
@@ -6508,23 +6508,23 @@
       <c r="G10" s="171"/>
       <c r="H10" s="154">
         <f>H7/(1+$C$21)^H9</f>
-        <v>165620.02514888972</v>
+        <v>165495.0122197624</v>
       </c>
       <c r="I10" s="154">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>180032.54586511708</v>
+        <v>179760.86492842546</v>
       </c>
       <c r="J10" s="154">
         <f t="shared" si="1"/>
-        <v>195699.26729293683</v>
+        <v>195256.44988566544</v>
       </c>
       <c r="K10" s="154">
         <f t="shared" si="1"/>
-        <v>212729.33199359346</v>
+        <v>212087.77136855375</v>
       </c>
       <c r="L10" s="154">
         <f t="shared" si="1"/>
-        <v>231241.38028938754</v>
+        <v>230369.9713398414</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -6543,209 +6543,209 @@
       <c r="K11" s="151"/>
       <c r="L11" s="154">
         <f>L8/(1+C21)^L9</f>
-        <v>3915460.7218406242</v>
+        <v>3848573.3945617699</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="217" t="s">
+      <c r="B14" s="222" t="s">
         <v>355</v>
       </c>
-      <c r="C14" s="218"/>
+      <c r="C14" s="223"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B15" s="219" t="s">
+      <c r="B15" s="207" t="s">
         <v>356</v>
       </c>
-      <c r="C15" s="220">
+      <c r="C15" s="208">
         <f>Overview!C3</f>
-        <v>106.24</v>
+        <v>108.25</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B16" s="219" t="s">
+      <c r="B16" s="207" t="s">
         <v>357</v>
       </c>
-      <c r="C16" s="220">
+      <c r="C16" s="208">
         <f>C36</f>
-        <v>104.53732642258541</v>
+        <v>103.07657097687803</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="221" t="s">
+      <c r="B17" s="209" t="s">
         <v>358</v>
       </c>
-      <c r="C17" s="222">
+      <c r="C17" s="210">
         <v>0.18</v>
       </c>
-      <c r="E17" s="223" t="s">
+      <c r="E17" s="224" t="s">
         <v>359</v>
       </c>
-      <c r="F17" s="223"/>
-      <c r="G17" s="223"/>
-      <c r="H17" s="223"/>
-      <c r="I17" s="223"/>
+      <c r="F17" s="224"/>
+      <c r="G17" s="224"/>
+      <c r="H17" s="224"/>
+      <c r="I17" s="224"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="217" t="s">
+      <c r="B19" s="222" t="s">
         <v>276</v>
       </c>
-      <c r="C19" s="218"/>
+      <c r="C19" s="223"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B20" s="224" t="s">
+      <c r="B20" s="211" t="s">
         <v>265</v>
       </c>
-      <c r="C20" s="225">
+      <c r="C20" s="212">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B21" s="224" t="s">
+      <c r="B21" s="211" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="226">
+      <c r="C21" s="213">
         <f>WACC!C20</f>
-        <v>8.5535E-2</v>
+        <v>8.6355000000000001E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B22" s="224" t="s">
+      <c r="B22" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="227">
+      <c r="C22" s="214">
         <f>'Statement Q'!N116</f>
         <v>47400</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B23" s="224" t="s">
+      <c r="B23" s="211" t="s">
         <v>242</v>
       </c>
-      <c r="C23" s="227">
+      <c r="C23" s="214">
         <f>C15*C22</f>
-        <v>5035776</v>
+        <v>5131050</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B24" s="224" t="s">
+      <c r="B24" s="211" t="s">
         <v>243</v>
       </c>
-      <c r="C24" s="227">
+      <c r="C24" s="214">
         <f>Statements!S23</f>
         <v>1140467</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="224" t="s">
+      <c r="B25" s="211" t="s">
         <v>239</v>
       </c>
-      <c r="C25" s="227">
+      <c r="C25" s="214">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="221" t="s">
+      <c r="B26" s="209" t="s">
         <v>360</v>
       </c>
-      <c r="C26" s="228">
+      <c r="C26" s="215">
         <f>C23+C25-C24</f>
-        <v>3895309</v>
+        <v>3990583</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="217" t="s">
+      <c r="B28" s="222" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="218"/>
+      <c r="C28" s="223"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B29" s="224" t="s">
+      <c r="B29" s="211" t="s">
         <v>274</v>
       </c>
-      <c r="C29" s="227">
+      <c r="C29" s="214">
         <f>SUM(H10:L10)</f>
-        <v>985322.55058992468</v>
+        <v>982970.06974224839</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B30" s="224" t="s">
+      <c r="B30" s="211" t="s">
         <v>268</v>
       </c>
-      <c r="C30" s="227">
+      <c r="C30" s="214">
         <f>L11</f>
-        <v>3915460.7218406242</v>
+        <v>3848573.3945617699</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" s="229" t="s">
+      <c r="B31" s="216" t="s">
         <v>271</v>
       </c>
-      <c r="C31" s="230">
+      <c r="C31" s="217">
         <f>C29+C30</f>
-        <v>4900783.2724305484</v>
+        <v>4831543.4643040188</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B32" s="224" t="s">
+      <c r="B32" s="211" t="s">
         <v>269</v>
       </c>
-      <c r="C32" s="231">
-        <f>[2]Statements!W21+[2]Statements!W27</f>
+      <c r="C32" s="218">
+        <f>[1]Statements!W21+[1]Statements!W27</f>
         <v>144795</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B33" s="224" t="s">
+      <c r="B33" s="211" t="s">
         <v>270</v>
       </c>
-      <c r="C33" s="231">
-        <f>[2]Statements!W35+[2]Statements!W36+[2]Statements!W38</f>
+      <c r="C33" s="218">
+        <f>[1]Statements!W35+[1]Statements!W36+[1]Statements!W38</f>
         <v>90509</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="229" t="s">
+      <c r="B34" s="216" t="s">
         <v>272</v>
       </c>
-      <c r="C34" s="230">
+      <c r="C34" s="217">
         <f>C31+C32-C33</f>
-        <v>4955069.2724305484</v>
+        <v>4885829.4643040188</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B35" s="224" t="s">
+      <c r="B35" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="227">
+      <c r="C35" s="214">
         <f>C22</f>
         <v>47400</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="232" t="s">
+      <c r="B36" s="219" t="s">
         <v>273</v>
       </c>
-      <c r="C36" s="233">
+      <c r="C36" s="220">
         <f>C34/C35</f>
-        <v>104.53732642258541</v>
+        <v>103.07657097687803</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="207" t="s">
+      <c r="C39" s="225" t="s">
         <v>361</v>
       </c>
-      <c r="D39" s="207"/>
-      <c r="E39" s="207"/>
-      <c r="F39" s="207"/>
-      <c r="G39" s="207"/>
-      <c r="H39" s="207"/>
-      <c r="I39" s="207"/>
-      <c r="J39" s="207"/>
-      <c r="K39" s="207"/>
-      <c r="L39" s="207"/>
+      <c r="D39" s="225"/>
+      <c r="E39" s="225"/>
+      <c r="F39" s="225"/>
+      <c r="G39" s="225"/>
+      <c r="H39" s="225"/>
+      <c r="I39" s="225"/>
+      <c r="J39" s="225"/>
+      <c r="K39" s="225"/>
+      <c r="L39" s="225"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="62">
@@ -6839,23 +6839,23 @@
         <v>182</v>
       </c>
       <c r="C42" s="153">
-        <f>'[2]FCF &amp; Other'!C12</f>
+        <f>'[1]FCF &amp; Other'!C12</f>
         <v>108949</v>
       </c>
       <c r="D42" s="153">
-        <f>'[2]FCF &amp; Other'!D12</f>
+        <f>'[1]FCF &amp; Other'!D12</f>
         <v>119437</v>
       </c>
       <c r="E42" s="153">
-        <f>'[2]FCF &amp; Other'!E12</f>
+        <f>'[1]FCF &amp; Other'!E12</f>
         <v>114301</v>
       </c>
       <c r="F42" s="153">
-        <f>'[2]FCF &amp; Other'!F12</f>
+        <f>'[1]FCF &amp; Other'!F12</f>
         <v>123216</v>
       </c>
       <c r="G42" s="155">
-        <f>'[2]FCF &amp; Other'!G12</f>
+        <f>'[1]FCF &amp; Other'!G12</f>
         <v>133050</v>
       </c>
       <c r="H42" s="195">
@@ -6924,23 +6924,23 @@
         <v>6</v>
       </c>
       <c r="C44" s="153">
-        <f>'[2]FCF &amp; Other'!C6</f>
+        <f>'[1]FCF &amp; Other'!C6</f>
         <v>365817</v>
       </c>
       <c r="D44" s="153">
-        <f>'[2]FCF &amp; Other'!D6</f>
+        <f>'[1]FCF &amp; Other'!D6</f>
         <v>394328</v>
       </c>
       <c r="E44" s="153">
-        <f>'[2]FCF &amp; Other'!E6</f>
+        <f>'[1]FCF &amp; Other'!E6</f>
         <v>383285</v>
       </c>
       <c r="F44" s="153">
-        <f>'[2]FCF &amp; Other'!F6</f>
+        <f>'[1]FCF &amp; Other'!F6</f>
         <v>391035</v>
       </c>
       <c r="G44" s="155">
-        <f>'[2]FCF &amp; Other'!G6</f>
+        <f>'[1]FCF &amp; Other'!G6</f>
         <v>416161</v>
       </c>
       <c r="H44" s="195">
@@ -7025,23 +7025,23 @@
         <f t="shared" si="7"/>
         <v>0.18245012405821437</v>
       </c>
-      <c r="H46" s="234">
+      <c r="H46" s="221">
         <f t="shared" si="7"/>
         <v>0.17999999999999994</v>
       </c>
-      <c r="I46" s="234">
+      <c r="I46" s="221">
         <f t="shared" si="7"/>
         <v>0.17999999999999994</v>
       </c>
-      <c r="J46" s="234">
+      <c r="J46" s="221">
         <f t="shared" si="7"/>
         <v>0.17999999999999994</v>
       </c>
-      <c r="K46" s="234">
+      <c r="K46" s="221">
         <f t="shared" si="7"/>
         <v>0.17999999999999994</v>
       </c>
-      <c r="L46" s="234">
+      <c r="L46" s="221">
         <f t="shared" si="7"/>
         <v>0.17999999999999994</v>
       </c>
@@ -7067,23 +7067,23 @@
         <f t="shared" si="7"/>
         <v>7.9811063498246959E-2</v>
       </c>
-      <c r="H47" s="234">
+      <c r="H47" s="221">
         <f t="shared" si="7"/>
         <v>0.35126895152198401</v>
       </c>
-      <c r="I47" s="234">
+      <c r="I47" s="221">
         <f t="shared" si="7"/>
         <v>0.17999999999999994</v>
       </c>
-      <c r="J47" s="234">
+      <c r="J47" s="221">
         <f t="shared" si="7"/>
         <v>0.24210526315789482</v>
       </c>
-      <c r="K47" s="234">
+      <c r="K47" s="221">
         <f t="shared" si="7"/>
         <v>0.2455555555555553</v>
       </c>
-      <c r="L47" s="234">
+      <c r="L47" s="221">
         <f t="shared" si="7"/>
         <v>0.3274999999999999</v>
       </c>
@@ -7109,23 +7109,23 @@
         <f t="shared" si="8"/>
         <v>6.425511782832749E-2</v>
       </c>
-      <c r="H48" s="234">
+      <c r="H48" s="221">
         <f t="shared" si="8"/>
         <v>8.0028726862920507E-2</v>
       </c>
-      <c r="I48" s="234">
+      <c r="I48" s="221">
         <f t="shared" si="8"/>
         <v>0.17999999999999994</v>
       </c>
-      <c r="J48" s="234">
+      <c r="J48" s="221">
         <f t="shared" si="8"/>
         <v>0.34857142857142875</v>
       </c>
-      <c r="K48" s="234">
+      <c r="K48" s="221">
         <f t="shared" si="8"/>
         <v>0.37666666666666648</v>
       </c>
-      <c r="L48" s="234">
+      <c r="L48" s="221">
         <f t="shared" si="8"/>
         <v>0.17999999999999994</v>
       </c>
@@ -7154,40 +7154,40 @@
         <f t="shared" si="9"/>
         <v>0.31970799762591884</v>
       </c>
-      <c r="H49" s="234">
+      <c r="H49" s="221">
         <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
-      <c r="I49" s="234">
+      <c r="I49" s="221">
         <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
-      <c r="J49" s="234">
+      <c r="J49" s="221">
         <f t="shared" si="9"/>
         <v>0.36842105263157893</v>
       </c>
-      <c r="K49" s="234">
+      <c r="K49" s="221">
         <f t="shared" si="9"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="L49" s="234">
+      <c r="L49" s="221">
         <f t="shared" si="9"/>
         <v>0.375</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -11803,11 +11803,11 @@
         <v>86</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="213" t="s">
+      <c r="P4" s="230" t="s">
         <v>87</v>
       </c>
-      <c r="Q4" s="214"/>
-      <c r="R4" s="215"/>
+      <c r="Q4" s="231"/>
+      <c r="R4" s="232"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -22162,36 +22162,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="208" t="s">
+      <c r="C2" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="211"/>
-      <c r="H2" s="212" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="227"/>
+      <c r="H2" s="228" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="226"/>
       <c r="O2" s="92"/>
-      <c r="S2" s="208" t="s">
+      <c r="S2" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="T2" s="208"/>
-      <c r="U2" s="208"/>
-      <c r="V2" s="208"/>
-      <c r="W2" s="208"/>
-      <c r="X2" s="208"/>
-      <c r="Y2" s="208"/>
-      <c r="Z2" s="208"/>
-      <c r="AA2" s="208" t="s">
+      <c r="T2" s="226"/>
+      <c r="U2" s="226"/>
+      <c r="V2" s="226"/>
+      <c r="W2" s="226"/>
+      <c r="X2" s="226"/>
+      <c r="Y2" s="226"/>
+      <c r="Z2" s="226"/>
+      <c r="AA2" s="226" t="s">
         <v>179</v>
       </c>
-      <c r="AB2" s="208"/>
-      <c r="AC2" s="208"/>
+      <c r="AB2" s="226"/>
+      <c r="AC2" s="226"/>
       <c r="AE2" s="128" t="s">
         <v>86</v>
       </c>
@@ -22202,32 +22202,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="207" t="s">
+      <c r="C4" s="225" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="207"/>
-      <c r="E4" s="207"/>
-      <c r="F4" s="207"/>
-      <c r="G4" s="207"/>
-      <c r="H4" s="207"/>
-      <c r="I4" s="207"/>
-      <c r="J4" s="207"/>
-      <c r="K4" s="207"/>
-      <c r="L4" s="207"/>
+      <c r="D4" s="225"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="225"/>
+      <c r="G4" s="225"/>
+      <c r="H4" s="225"/>
+      <c r="I4" s="225"/>
+      <c r="J4" s="225"/>
+      <c r="K4" s="225"/>
+      <c r="L4" s="225"/>
       <c r="O4" s="92"/>
-      <c r="S4" s="209" t="s">
+      <c r="S4" s="233" t="s">
         <v>187</v>
       </c>
-      <c r="T4" s="210"/>
-      <c r="U4" s="210"/>
-      <c r="V4" s="210"/>
-      <c r="W4" s="210"/>
-      <c r="X4" s="210"/>
-      <c r="Y4" s="210"/>
-      <c r="Z4" s="210"/>
-      <c r="AA4" s="210"/>
-      <c r="AB4" s="210"/>
-      <c r="AC4" s="210"/>
+      <c r="T4" s="234"/>
+      <c r="U4" s="234"/>
+      <c r="V4" s="234"/>
+      <c r="W4" s="234"/>
+      <c r="X4" s="234"/>
+      <c r="Y4" s="234"/>
+      <c r="Z4" s="234"/>
+      <c r="AA4" s="234"/>
+      <c r="AB4" s="234"/>
+      <c r="AC4" s="234"/>
       <c r="AE4" s="140" t="s">
         <v>212</v>
       </c>
@@ -23023,33 +23023,33 @@
       <c r="Q13" s="93"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C14" s="207" t="s">
+      <c r="C14" s="225" t="s">
         <v>193</v>
       </c>
-      <c r="D14" s="207"/>
-      <c r="E14" s="207"/>
-      <c r="F14" s="207"/>
-      <c r="G14" s="207"/>
-      <c r="H14" s="207"/>
-      <c r="I14" s="207"/>
-      <c r="J14" s="207"/>
-      <c r="K14" s="207"/>
-      <c r="L14" s="207"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="225"/>
+      <c r="F14" s="225"/>
+      <c r="G14" s="225"/>
+      <c r="H14" s="225"/>
+      <c r="I14" s="225"/>
+      <c r="J14" s="225"/>
+      <c r="K14" s="225"/>
+      <c r="L14" s="225"/>
       <c r="O14" s="92"/>
       <c r="Q14" s="93"/>
-      <c r="S14" s="209" t="s">
+      <c r="S14" s="233" t="s">
         <v>193</v>
       </c>
-      <c r="T14" s="210"/>
-      <c r="U14" s="210"/>
-      <c r="V14" s="210"/>
-      <c r="W14" s="210"/>
-      <c r="X14" s="210"/>
-      <c r="Y14" s="210"/>
-      <c r="Z14" s="210"/>
-      <c r="AA14" s="210"/>
-      <c r="AB14" s="210"/>
-      <c r="AC14" s="210"/>
+      <c r="T14" s="234"/>
+      <c r="U14" s="234"/>
+      <c r="V14" s="234"/>
+      <c r="W14" s="234"/>
+      <c r="X14" s="234"/>
+      <c r="Y14" s="234"/>
+      <c r="Z14" s="234"/>
+      <c r="AA14" s="234"/>
+      <c r="AB14" s="234"/>
+      <c r="AC14" s="234"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B15" s="7" t="s">
@@ -23742,33 +23742,33 @@
       <c r="Q24" s="93"/>
     </row>
     <row r="25" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C25" s="207" t="s">
+      <c r="C25" s="225" t="s">
         <v>195</v>
       </c>
-      <c r="D25" s="207"/>
-      <c r="E25" s="207"/>
-      <c r="F25" s="207"/>
-      <c r="G25" s="207"/>
-      <c r="H25" s="207"/>
-      <c r="I25" s="207"/>
-      <c r="J25" s="207"/>
-      <c r="K25" s="207"/>
-      <c r="L25" s="207"/>
+      <c r="D25" s="225"/>
+      <c r="E25" s="225"/>
+      <c r="F25" s="225"/>
+      <c r="G25" s="225"/>
+      <c r="H25" s="225"/>
+      <c r="I25" s="225"/>
+      <c r="J25" s="225"/>
+      <c r="K25" s="225"/>
+      <c r="L25" s="225"/>
       <c r="O25" s="92"/>
       <c r="Q25" s="93"/>
-      <c r="S25" s="209" t="s">
+      <c r="S25" s="233" t="s">
         <v>195</v>
       </c>
-      <c r="T25" s="210"/>
-      <c r="U25" s="210"/>
-      <c r="V25" s="210"/>
-      <c r="W25" s="210"/>
-      <c r="X25" s="210"/>
-      <c r="Y25" s="210"/>
-      <c r="Z25" s="210"/>
-      <c r="AA25" s="210"/>
-      <c r="AB25" s="210"/>
-      <c r="AC25" s="210"/>
+      <c r="T25" s="234"/>
+      <c r="U25" s="234"/>
+      <c r="V25" s="234"/>
+      <c r="W25" s="234"/>
+      <c r="X25" s="234"/>
+      <c r="Y25" s="234"/>
+      <c r="Z25" s="234"/>
+      <c r="AA25" s="234"/>
+      <c r="AB25" s="234"/>
+      <c r="AC25" s="234"/>
       <c r="AE25" s="140" t="str">
         <f>AE4</f>
         <v>Q1-Q2-Q3</v>
@@ -25091,32 +25091,32 @@
       <c r="O42" s="92"/>
     </row>
     <row r="43" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C43" s="207" t="s">
+      <c r="C43" s="225" t="s">
         <v>207</v>
       </c>
-      <c r="D43" s="207"/>
-      <c r="E43" s="207"/>
-      <c r="F43" s="207"/>
-      <c r="G43" s="207"/>
-      <c r="H43" s="207"/>
-      <c r="I43" s="207"/>
-      <c r="J43" s="207"/>
-      <c r="K43" s="207"/>
-      <c r="L43" s="207"/>
+      <c r="D43" s="225"/>
+      <c r="E43" s="225"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="225"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="225"/>
+      <c r="K43" s="225"/>
+      <c r="L43" s="225"/>
       <c r="O43" s="92"/>
-      <c r="S43" s="209" t="s">
+      <c r="S43" s="233" t="s">
         <v>207</v>
       </c>
-      <c r="T43" s="210"/>
-      <c r="U43" s="210"/>
-      <c r="V43" s="210"/>
-      <c r="W43" s="210"/>
-      <c r="X43" s="210"/>
-      <c r="Y43" s="210"/>
-      <c r="Z43" s="210"/>
-      <c r="AA43" s="210"/>
-      <c r="AB43" s="210"/>
-      <c r="AC43" s="210"/>
+      <c r="T43" s="234"/>
+      <c r="U43" s="234"/>
+      <c r="V43" s="234"/>
+      <c r="W43" s="234"/>
+      <c r="X43" s="234"/>
+      <c r="Y43" s="234"/>
+      <c r="Z43" s="234"/>
+      <c r="AA43" s="234"/>
+      <c r="AB43" s="234"/>
+      <c r="AC43" s="234"/>
     </row>
     <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B44" s="7" t="s">
@@ -25732,35 +25732,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="208" t="s">
+      <c r="C2" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="211"/>
-      <c r="H2" s="212" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="227"/>
+      <c r="H2" s="228" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
-      <c r="P2" s="208" t="s">
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="226"/>
+      <c r="P2" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="Q2" s="208"/>
-      <c r="R2" s="208"/>
-      <c r="S2" s="208"/>
-      <c r="T2" s="208"/>
-      <c r="U2" s="208"/>
-      <c r="V2" s="208"/>
-      <c r="W2" s="208"/>
-      <c r="X2" s="208" t="s">
+      <c r="Q2" s="226"/>
+      <c r="R2" s="226"/>
+      <c r="S2" s="226"/>
+      <c r="T2" s="226"/>
+      <c r="U2" s="226"/>
+      <c r="V2" s="226"/>
+      <c r="W2" s="226"/>
+      <c r="X2" s="226" t="s">
         <v>179</v>
       </c>
-      <c r="Y2" s="208"/>
-      <c r="Z2" s="208"/>
+      <c r="Y2" s="226"/>
+      <c r="Z2" s="226"/>
       <c r="AB2" s="128" t="s">
         <v>86</v>
       </c>
@@ -25769,31 +25769,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="207" t="s">
+      <c r="C4" s="225" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="207"/>
-      <c r="E4" s="207"/>
-      <c r="F4" s="207"/>
-      <c r="G4" s="207"/>
-      <c r="H4" s="207"/>
-      <c r="I4" s="207"/>
-      <c r="J4" s="207"/>
-      <c r="K4" s="207"/>
-      <c r="L4" s="207"/>
-      <c r="P4" s="210" t="s">
+      <c r="D4" s="225"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="225"/>
+      <c r="G4" s="225"/>
+      <c r="H4" s="225"/>
+      <c r="I4" s="225"/>
+      <c r="J4" s="225"/>
+      <c r="K4" s="225"/>
+      <c r="L4" s="225"/>
+      <c r="P4" s="234" t="s">
         <v>187</v>
       </c>
-      <c r="Q4" s="210"/>
-      <c r="R4" s="210"/>
-      <c r="S4" s="210"/>
-      <c r="T4" s="210"/>
-      <c r="U4" s="210"/>
-      <c r="V4" s="210"/>
-      <c r="W4" s="210"/>
-      <c r="X4" s="210"/>
-      <c r="Y4" s="210"/>
-      <c r="Z4" s="210"/>
+      <c r="Q4" s="234"/>
+      <c r="R4" s="234"/>
+      <c r="S4" s="234"/>
+      <c r="T4" s="234"/>
+      <c r="U4" s="234"/>
+      <c r="V4" s="234"/>
+      <c r="W4" s="234"/>
+      <c r="X4" s="234"/>
+      <c r="Y4" s="234"/>
+      <c r="Z4" s="234"/>
       <c r="AB4" s="140" t="s">
         <v>212</v>
       </c>
@@ -25994,32 +25994,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="207" t="s">
+      <c r="C9" s="225" t="s">
         <v>214</v>
       </c>
-      <c r="D9" s="207"/>
-      <c r="E9" s="207"/>
-      <c r="F9" s="207"/>
-      <c r="G9" s="207"/>
-      <c r="H9" s="207"/>
-      <c r="I9" s="207"/>
-      <c r="J9" s="207"/>
-      <c r="K9" s="207"/>
-      <c r="L9" s="207"/>
+      <c r="D9" s="225"/>
+      <c r="E9" s="225"/>
+      <c r="F9" s="225"/>
+      <c r="G9" s="225"/>
+      <c r="H9" s="225"/>
+      <c r="I9" s="225"/>
+      <c r="J9" s="225"/>
+      <c r="K9" s="225"/>
+      <c r="L9" s="225"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="210" t="s">
+      <c r="P9" s="234" t="s">
         <v>219</v>
       </c>
-      <c r="Q9" s="210"/>
-      <c r="R9" s="210"/>
-      <c r="S9" s="210"/>
-      <c r="T9" s="210"/>
-      <c r="U9" s="210"/>
-      <c r="V9" s="210"/>
-      <c r="W9" s="210"/>
-      <c r="X9" s="210"/>
-      <c r="Y9" s="210"/>
-      <c r="Z9" s="210"/>
+      <c r="Q9" s="234"/>
+      <c r="R9" s="234"/>
+      <c r="S9" s="234"/>
+      <c r="T9" s="234"/>
+      <c r="U9" s="234"/>
+      <c r="V9" s="234"/>
+      <c r="W9" s="234"/>
+      <c r="X9" s="234"/>
+      <c r="Y9" s="234"/>
+      <c r="Z9" s="234"/>
       <c r="AB9" s="140" t="str">
         <f>AB4</f>
         <v>Q1-Q2-Q3</v>
@@ -26581,31 +26581,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="207" t="s">
+      <c r="C18" s="225" t="s">
         <v>217</v>
       </c>
-      <c r="D18" s="207"/>
-      <c r="E18" s="207"/>
-      <c r="F18" s="207"/>
-      <c r="G18" s="207"/>
-      <c r="H18" s="207"/>
-      <c r="I18" s="207"/>
-      <c r="J18" s="207"/>
-      <c r="K18" s="207"/>
-      <c r="L18" s="207"/>
-      <c r="P18" s="210" t="s">
+      <c r="D18" s="225"/>
+      <c r="E18" s="225"/>
+      <c r="F18" s="225"/>
+      <c r="G18" s="225"/>
+      <c r="H18" s="225"/>
+      <c r="I18" s="225"/>
+      <c r="J18" s="225"/>
+      <c r="K18" s="225"/>
+      <c r="L18" s="225"/>
+      <c r="P18" s="234" t="s">
         <v>217</v>
       </c>
-      <c r="Q18" s="210"/>
-      <c r="R18" s="210"/>
-      <c r="S18" s="210"/>
-      <c r="T18" s="210"/>
-      <c r="U18" s="210"/>
-      <c r="V18" s="210"/>
-      <c r="W18" s="210"/>
-      <c r="X18" s="210"/>
-      <c r="Y18" s="210"/>
-      <c r="Z18" s="210"/>
+      <c r="Q18" s="234"/>
+      <c r="R18" s="234"/>
+      <c r="S18" s="234"/>
+      <c r="T18" s="234"/>
+      <c r="U18" s="234"/>
+      <c r="V18" s="234"/>
+      <c r="W18" s="234"/>
+      <c r="X18" s="234"/>
+      <c r="Y18" s="234"/>
+      <c r="Z18" s="234"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -27077,60 +27077,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="104"/>
-      <c r="C3" s="208" t="s">
+      <c r="C3" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="211"/>
-      <c r="H3" s="212" t="s">
+      <c r="D3" s="226"/>
+      <c r="E3" s="226"/>
+      <c r="F3" s="226"/>
+      <c r="G3" s="227"/>
+      <c r="H3" s="228" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="208"/>
-      <c r="J3" s="208"/>
-      <c r="K3" s="208"/>
-      <c r="L3" s="208"/>
-      <c r="P3" s="216"/>
-      <c r="Q3" s="216"/>
-      <c r="R3" s="216"/>
-      <c r="S3" s="216"/>
-      <c r="T3" s="216"/>
-      <c r="U3" s="216"/>
-      <c r="V3" s="216"/>
-      <c r="W3" s="216"/>
-      <c r="X3" s="216"/>
-      <c r="Y3" s="216"/>
-      <c r="Z3" s="216"/>
+      <c r="I3" s="226"/>
+      <c r="J3" s="226"/>
+      <c r="K3" s="226"/>
+      <c r="L3" s="226"/>
+      <c r="P3" s="229"/>
+      <c r="Q3" s="229"/>
+      <c r="R3" s="229"/>
+      <c r="S3" s="229"/>
+      <c r="T3" s="229"/>
+      <c r="U3" s="229"/>
+      <c r="V3" s="229"/>
+      <c r="W3" s="229"/>
+      <c r="X3" s="229"/>
+      <c r="Y3" s="229"/>
+      <c r="Z3" s="229"/>
       <c r="AB3" s="143"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="109"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="207" t="s">
+      <c r="C5" s="225" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="207"/>
-      <c r="E5" s="207"/>
-      <c r="F5" s="207"/>
-      <c r="G5" s="207"/>
-      <c r="H5" s="207"/>
-      <c r="I5" s="207"/>
-      <c r="J5" s="207"/>
-      <c r="K5" s="207"/>
-      <c r="L5" s="207"/>
-      <c r="P5" s="216"/>
-      <c r="Q5" s="216"/>
-      <c r="R5" s="216"/>
-      <c r="S5" s="216"/>
-      <c r="T5" s="216"/>
-      <c r="U5" s="216"/>
-      <c r="V5" s="216"/>
-      <c r="W5" s="216"/>
-      <c r="X5" s="216"/>
-      <c r="Y5" s="216"/>
-      <c r="Z5" s="216"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="225"/>
+      <c r="F5" s="225"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="225"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
+      <c r="L5" s="225"/>
+      <c r="P5" s="229"/>
+      <c r="Q5" s="229"/>
+      <c r="R5" s="229"/>
+      <c r="S5" s="229"/>
+      <c r="T5" s="229"/>
+      <c r="U5" s="229"/>
+      <c r="V5" s="229"/>
+      <c r="W5" s="229"/>
+      <c r="X5" s="229"/>
+      <c r="Y5" s="229"/>
+      <c r="Z5" s="229"/>
       <c r="AB5" s="144"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -27375,30 +27375,30 @@
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C12" s="207" t="s">
+      <c r="C12" s="225" t="s">
         <v>226</v>
       </c>
-      <c r="D12" s="207"/>
-      <c r="E12" s="207"/>
-      <c r="F12" s="207"/>
-      <c r="G12" s="207"/>
-      <c r="H12" s="207"/>
-      <c r="I12" s="207"/>
-      <c r="J12" s="207"/>
-      <c r="K12" s="207"/>
-      <c r="L12" s="207"/>
+      <c r="D12" s="225"/>
+      <c r="E12" s="225"/>
+      <c r="F12" s="225"/>
+      <c r="G12" s="225"/>
+      <c r="H12" s="225"/>
+      <c r="I12" s="225"/>
+      <c r="J12" s="225"/>
+      <c r="K12" s="225"/>
+      <c r="L12" s="225"/>
       <c r="N12" s="93"/>
-      <c r="P12" s="216"/>
-      <c r="Q12" s="216"/>
-      <c r="R12" s="216"/>
-      <c r="S12" s="216"/>
-      <c r="T12" s="216"/>
-      <c r="U12" s="216"/>
-      <c r="V12" s="216"/>
-      <c r="W12" s="216"/>
-      <c r="X12" s="216"/>
-      <c r="Y12" s="216"/>
-      <c r="Z12" s="216"/>
+      <c r="P12" s="229"/>
+      <c r="Q12" s="229"/>
+      <c r="R12" s="229"/>
+      <c r="S12" s="229"/>
+      <c r="T12" s="229"/>
+      <c r="U12" s="229"/>
+      <c r="V12" s="229"/>
+      <c r="W12" s="229"/>
+      <c r="X12" s="229"/>
+      <c r="Y12" s="229"/>
+      <c r="Z12" s="229"/>
       <c r="AB12" s="144"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -27581,18 +27581,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="207" t="s">
+      <c r="C18" s="225" t="s">
         <v>235</v>
       </c>
-      <c r="D18" s="207"/>
-      <c r="E18" s="207"/>
-      <c r="F18" s="207"/>
-      <c r="G18" s="207"/>
-      <c r="H18" s="207"/>
-      <c r="I18" s="207"/>
-      <c r="J18" s="207"/>
-      <c r="K18" s="207"/>
-      <c r="L18" s="207"/>
+      <c r="D18" s="225"/>
+      <c r="E18" s="225"/>
+      <c r="F18" s="225"/>
+      <c r="G18" s="225"/>
+      <c r="H18" s="225"/>
+      <c r="I18" s="225"/>
+      <c r="J18" s="225"/>
+      <c r="K18" s="225"/>
+      <c r="L18" s="225"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -27775,23 +27775,23 @@
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B24" s="216"/>
-      <c r="C24" s="216"/>
+      <c r="B24" s="229"/>
+      <c r="C24" s="229"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="143"/>
-      <c r="C25" s="207" t="s">
+      <c r="C25" s="225" t="s">
         <v>320</v>
       </c>
-      <c r="D25" s="207"/>
-      <c r="E25" s="207"/>
-      <c r="F25" s="207"/>
-      <c r="G25" s="207"/>
-      <c r="H25" s="207"/>
-      <c r="I25" s="207"/>
-      <c r="J25" s="207"/>
-      <c r="K25" s="207"/>
-      <c r="L25" s="207"/>
+      <c r="D25" s="225"/>
+      <c r="E25" s="225"/>
+      <c r="F25" s="225"/>
+      <c r="G25" s="225"/>
+      <c r="H25" s="225"/>
+      <c r="I25" s="225"/>
+      <c r="J25" s="225"/>
+      <c r="K25" s="225"/>
+      <c r="L25" s="225"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
@@ -27938,18 +27938,18 @@
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="143"/>
-      <c r="C31" s="207" t="s">
+      <c r="C31" s="225" t="s">
         <v>323</v>
       </c>
-      <c r="D31" s="207"/>
-      <c r="E31" s="207"/>
-      <c r="F31" s="207"/>
-      <c r="G31" s="207"/>
-      <c r="H31" s="207"/>
-      <c r="I31" s="207"/>
-      <c r="J31" s="207"/>
-      <c r="K31" s="207"/>
-      <c r="L31" s="207"/>
+      <c r="D31" s="225"/>
+      <c r="E31" s="225"/>
+      <c r="F31" s="225"/>
+      <c r="G31" s="225"/>
+      <c r="H31" s="225"/>
+      <c r="I31" s="225"/>
+      <c r="J31" s="225"/>
+      <c r="K31" s="225"/>
+      <c r="L31" s="225"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
@@ -28133,18 +28133,18 @@
       <c r="C37" s="152"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C38" s="207" t="s">
+      <c r="C38" s="225" t="s">
         <v>327</v>
       </c>
-      <c r="D38" s="207"/>
-      <c r="E38" s="207"/>
-      <c r="F38" s="207"/>
-      <c r="G38" s="207"/>
-      <c r="H38" s="207"/>
-      <c r="I38" s="207"/>
-      <c r="J38" s="207"/>
-      <c r="K38" s="207"/>
-      <c r="L38" s="207"/>
+      <c r="D38" s="225"/>
+      <c r="E38" s="225"/>
+      <c r="F38" s="225"/>
+      <c r="G38" s="225"/>
+      <c r="H38" s="225"/>
+      <c r="I38" s="225"/>
+      <c r="J38" s="225"/>
+      <c r="K38" s="225"/>
+      <c r="L38" s="225"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B39" s="7" t="s">
@@ -28408,6 +28408,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C38:L38"/>
@@ -28415,12 +28421,6 @@
     <mergeCell ref="P12:Z12"/>
     <mergeCell ref="C18:L18"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59ED5FE2-A5FF-4449-99E1-FA7F66C4AAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DD0058-C863-C64F-94CA-8F2FA5251720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="9" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2387,15 +2387,15 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="C4">
-            <v>105.02</v>
+            <v>107.99</v>
           </cell>
           <cell r="F4">
-            <v>0.90069999999999995</v>
+            <v>0.9</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>44.16</v>
+            <v>43.92</v>
           </cell>
         </row>
       </sheetData>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$4</f>
-        <v>105.02</v>
+        <v>107.99</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="C11" s="95">
         <f>$C$3/'Statement Q'!$N$22</f>
-        <v>12.148610115265351</v>
+        <v>12.492176788683157</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C12" s="95">
         <f>C3/Statements!S20</f>
-        <v>29.302389010004553</v>
+        <v>30.131070169400033</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C13" s="102">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$20)</f>
-        <v>4.6699951917086269</v>
+        <v>4.8020641854181552</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="C15" s="20">
         <f>C3*'Statement Q'!N118</f>
-        <v>4893196.8599999994</v>
+        <v>5031578.0699999994</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="C18" s="20">
         <f>C15+C17-C16</f>
-        <v>3641586.8599999994</v>
+        <v>3779968.0699999994</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C6" s="166">
         <f>Overview!C3</f>
-        <v>105.02</v>
+        <v>107.99</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="C7" s="168">
         <f>C5*C6</f>
-        <v>5131451.4265869316</v>
+        <v>5276570.5537718786</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="C9" s="191">
         <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.4159999999999998E-2</v>
+        <v>4.3920000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="C10" s="166">
         <f>[1]Sheet1!$F$4</f>
-        <v>0.90069999999999995</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="C19" s="169">
         <f>C9+C10*C11</f>
-        <v>8.9194999999999997E-2</v>
+        <v>8.8919999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="C20" s="169">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>8.9194999999999997E-2</v>
+        <v>8.8919999999999999E-2</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="L8" s="154">
         <f>L7*(1+C14)/(C15-C14)</f>
-        <v>7905144.7094607577</v>
+        <v>7936687.2920942698</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="7"/>
@@ -4899,23 +4899,23 @@
       <c r="G10" s="171"/>
       <c r="H10" s="154">
         <f>H7/(1+$C$15)^H9</f>
-        <v>131723.40208461988</v>
+        <v>131756.66801377287</v>
       </c>
       <c r="I10" s="154">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$15)^I9</f>
-        <v>197892.14522707503</v>
+        <v>197992.11071893357</v>
       </c>
       <c r="J10" s="154">
         <f t="shared" si="1"/>
-        <v>223837.30811636642</v>
+        <v>224006.93712430127</v>
       </c>
       <c r="K10" s="154">
         <f t="shared" si="1"/>
-        <v>253695.62607434497</v>
+        <v>253952.0002072088</v>
       </c>
       <c r="L10" s="154">
         <f t="shared" si="1"/>
-        <v>349829.29206146882</v>
+        <v>350271.25133561692</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -4934,7 +4934,7 @@
       <c r="K11" s="151"/>
       <c r="L11" s="154">
         <f>L8/(1+C15)^L9</f>
-        <v>5156815.9246000173</v>
+        <v>5183933.2031678651</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="C15" s="170">
         <f>WACC!C20</f>
-        <v>8.9194999999999997E-2</v>
+        <v>8.8919999999999999E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="C19" s="108">
         <f>SUM(H10:L10)</f>
-        <v>1156977.7735638751</v>
+        <v>1157978.9673998335</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C20" s="108">
         <f>L11</f>
-        <v>5156815.9246000173</v>
+        <v>5183933.2031678651</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="C21" s="113">
         <f>C19+C20</f>
-        <v>6313793.6981638921</v>
+        <v>6341912.1705676988</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="C24" s="113">
         <f>C21+C22-C23</f>
-        <v>7473530.6981638921</v>
+        <v>7501649.1705676988</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="C26" s="173">
         <f>C24/C25</f>
-        <v>152.95286434060833</v>
+        <v>153.52833543569611</v>
       </c>
     </row>
   </sheetData>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="C39" s="159">
         <f>WACC!C20</f>
-        <v>8.9194999999999997E-2</v>
+        <v>8.8919999999999999E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="C44" s="173">
         <f>C43/(1+C48)^5</f>
-        <v>152.68080668970461</v>
+        <v>152.8736970508956</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="C48" s="159">
         <f>WACC!C20</f>
-        <v>8.9194999999999997E-2</v>
+        <v>8.8919999999999999E-2</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C52" s="173">
         <f>C51/(1+C48)^5</f>
-        <v>144.82677965180255</v>
+        <v>145.00974757319909</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="C56" s="159">
         <f>WACC!C20</f>
-        <v>8.9194999999999997E-2</v>
+        <v>8.8919999999999999E-2</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="C61" s="173">
         <f>C60/(1+C56)^5</f>
-        <v>138.22293644334053</v>
+        <v>138.39756135339633</v>
       </c>
     </row>
   </sheetData>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="C5" s="188">
         <f>DCF!C26</f>
-        <v>152.95286434060833</v>
+        <v>153.52833543569611</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="C6" s="188">
         <f>Multiples!C44</f>
-        <v>152.68080668970461</v>
+        <v>152.8736970508956</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="C7" s="188">
         <f>Multiples!C52</f>
-        <v>144.82677965180255</v>
+        <v>145.00974757319909</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="C8" s="188">
         <f>Multiples!C61</f>
-        <v>138.22293644334053</v>
+        <v>138.39756135339633</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="C9" s="173">
         <f>AVERAGE(C5:C8)</f>
-        <v>147.17084678136399</v>
+        <v>147.45233535329677</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C10" s="35">
         <f>Overview!C3</f>
-        <v>105.02</v>
+        <v>107.99</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="C11" s="91">
         <f>(C9-C10)/C10</f>
-        <v>0.40136018645366595</v>
+        <v>0.3654258297369829</v>
       </c>
     </row>
   </sheetData>
@@ -6545,7 +6545,7 @@
       <c r="K8" s="151"/>
       <c r="L8" s="154">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>6194312.3849683134</v>
+        <v>6219028.5182513408</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="7"/>
@@ -6599,23 +6599,23 @@
       <c r="G10" s="171"/>
       <c r="H10" s="154">
         <f>H7/(1+$C$21)^H9</f>
-        <v>163183.13249693581</v>
+        <v>163224.34338610733</v>
       </c>
       <c r="I10" s="154">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>185776.72895689055</v>
+        <v>185870.57432940265</v>
       </c>
       <c r="J10" s="154">
         <f t="shared" si="1"/>
-        <v>211498.53231656805</v>
+        <v>211658.81071929922</v>
       </c>
       <c r="K10" s="154">
         <f t="shared" si="1"/>
-        <v>240781.6599163092</v>
+        <v>241024.98373795234</v>
       </c>
       <c r="L10" s="154">
         <f t="shared" si="1"/>
-        <v>274119.19655913167</v>
+        <v>274465.50695648981</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -6634,7 +6634,7 @@
       <c r="K11" s="151"/>
       <c r="L11" s="154">
         <f>L8/(1+C21)^L9</f>
-        <v>4040777.2308738255</v>
+        <v>4062025.7849045219</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="C15" s="208">
         <f>Overview!C3</f>
-        <v>105.02</v>
+        <v>107.99</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="C16" s="208">
         <f>C36</f>
-        <v>104.66860084933667</v>
+        <v>105.12158430045085</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="C21" s="213">
         <f>WACC!C20</f>
-        <v>8.9194999999999997E-2</v>
+        <v>8.8919999999999999E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C23" s="214">
         <f>C15*C22</f>
-        <v>5131451.4265869316</v>
+        <v>5276570.5537718786</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="C26" s="215">
         <f>C23+C25-C24</f>
-        <v>3879841.4265869316</v>
+        <v>4024960.5537718786</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="C29" s="214">
         <f>SUM(H10:L10)</f>
-        <v>1075359.2502458352</v>
+        <v>1076244.2191292513</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="C30" s="214">
         <f>L11</f>
-        <v>4040777.2308738255</v>
+        <v>4062025.7849045219</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="C31" s="217">
         <f>C29+C30</f>
-        <v>5116136.4811196607</v>
+        <v>5138270.0040337732</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="C34" s="217">
         <f>C31+C32-C33</f>
-        <v>5114281.4811196607</v>
+        <v>5136415.0040337732</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="C36" s="220">
         <f>C34/C35</f>
-        <v>104.66860084933667</v>
+        <v>105.12158430045085</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DD0058-C863-C64F-94CA-8F2FA5251720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACA129B-1A81-DB46-BCAF-1F68CA979E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="9" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -89,7 +89,7 @@
     Can be used as accumulated amortization to calculate the year's amortization expense</t>
       </text>
     </comment>
-    <comment ref="B143" authorId="3" shapeId="0" xr:uid="{62BF7902-5C15-3640-A488-08AAC22928CA}">
+    <comment ref="B144" authorId="3" shapeId="0" xr:uid="{62BF7902-5C15-3640-A488-08AAC22928CA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -97,7 +97,7 @@
     Daily active users</t>
       </text>
     </comment>
-    <comment ref="B144" authorId="4" shapeId="0" xr:uid="{E9E95286-BB0F-9A48-8DD2-49D754B20E3C}">
+    <comment ref="B145" authorId="4" shapeId="0" xr:uid="{E9E95286-BB0F-9A48-8DD2-49D754B20E3C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -105,7 +105,7 @@
     Monthly active users</t>
       </text>
     </comment>
-    <comment ref="B167" authorId="5" shapeId="0" xr:uid="{D32AD234-EAC2-EA43-AC27-5680646CEFEA}">
+    <comment ref="B168" authorId="5" shapeId="0" xr:uid="{D32AD234-EAC2-EA43-AC27-5680646CEFEA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -124,7 +124,7 @@
     <author>tc={285C01A7-F0A8-3D42-9492-4C51EDE56FEF}</author>
   </authors>
   <commentList>
-    <comment ref="B133" authorId="0" shapeId="0" xr:uid="{7DB38267-A7EF-9146-B902-E966352B6452}">
+    <comment ref="B134" authorId="0" shapeId="0" xr:uid="{7DB38267-A7EF-9146-B902-E966352B6452}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -132,7 +132,7 @@
     Daily active users</t>
       </text>
     </comment>
-    <comment ref="B134" authorId="1" shapeId="0" xr:uid="{285C01A7-F0A8-3D42-9492-4C51EDE56FEF}">
+    <comment ref="B135" authorId="1" shapeId="0" xr:uid="{285C01A7-F0A8-3D42-9492-4C51EDE56FEF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -217,7 +217,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="387">
   <si>
     <t>Date</t>
   </si>
@@ -1348,6 +1348,36 @@
   </si>
   <si>
     <t>Change in NWC less RIP</t>
+  </si>
+  <si>
+    <t>Adjustments</t>
+  </si>
+  <si>
+    <t>Operating Interest</t>
+  </si>
+  <si>
+    <t>EBITDAR</t>
+  </si>
+  <si>
+    <t>Operating lease cost</t>
+  </si>
+  <si>
+    <t>Cost of operating lease debt</t>
+  </si>
+  <si>
+    <t>Operating lease interest</t>
+  </si>
+  <si>
+    <t>From 10-K Leases note</t>
+  </si>
+  <si>
+    <t>Cost of financial lease debt</t>
+  </si>
+  <si>
+    <t>Operating lease amortization</t>
+  </si>
+  <si>
+    <t>WACC set manually</t>
   </si>
 </sst>
 </file>
@@ -1978,7 +2008,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="235">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2247,7 +2277,20 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2259,22 +2302,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2387,15 +2418,15 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="C4">
-            <v>107.99</v>
+            <v>112.06</v>
           </cell>
           <cell r="F4">
-            <v>0.9</v>
+            <v>0.89770000000000005</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>43.92</v>
+            <v>45.95</v>
           </cell>
         </row>
       </sheetData>
@@ -2874,13 +2905,13 @@
   <threadedComment ref="B123" dT="2026-02-17T23:24:57.80" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{956F0D8B-0692-4D4E-AB6C-385CCF335882}">
     <text>Can be used as accumulated amortization to calculate the year's amortization expense</text>
   </threadedComment>
-  <threadedComment ref="B143" dT="2026-01-18T19:47:23.76" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{62BF7902-5C15-3640-A488-08AAC22928CA}">
+  <threadedComment ref="B144" dT="2026-01-18T19:47:23.76" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{62BF7902-5C15-3640-A488-08AAC22928CA}">
     <text>Daily active users</text>
   </threadedComment>
-  <threadedComment ref="B144" dT="2026-01-18T19:47:33.64" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{E9E95286-BB0F-9A48-8DD2-49D754B20E3C}">
+  <threadedComment ref="B145" dT="2026-01-18T19:47:33.64" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{E9E95286-BB0F-9A48-8DD2-49D754B20E3C}">
     <text>Monthly active users</text>
   </threadedComment>
-  <threadedComment ref="B167" dT="2026-04-25T21:52:20.00" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{D32AD234-EAC2-EA43-AC27-5680646CEFEA}">
+  <threadedComment ref="B168" dT="2026-04-25T21:52:20.00" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{D32AD234-EAC2-EA43-AC27-5680646CEFEA}">
     <text>Take the closing price of the last day of the period. In case the price has seen heavy fluctuations make an average of the last days. Info found at Yahoo Finance in the Historical Data section</text>
   </threadedComment>
 </ThreadedComments>
@@ -2888,10 +2919,10 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B133" dT="2026-01-18T19:47:23.76" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{7DB38267-A7EF-9146-B902-E966352B6452}">
+  <threadedComment ref="B134" dT="2026-01-18T19:47:23.76" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{7DB38267-A7EF-9146-B902-E966352B6452}">
     <text>Daily active users</text>
   </threadedComment>
-  <threadedComment ref="B134" dT="2026-01-18T19:47:33.64" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{285C01A7-F0A8-3D42-9492-4C51EDE56FEF}">
+  <threadedComment ref="B135" dT="2026-01-18T19:47:33.64" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{285C01A7-F0A8-3D42-9492-4C51EDE56FEF}">
     <text>Check footnote to DAU in the letter</text>
   </threadedComment>
 </ThreadedComments>
@@ -2977,11 +3008,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8A3889E-47F7-E641-9FC7-1CBF49DF9C8A}">
-  <dimension ref="A2:G62"/>
+  <dimension ref="A2:G63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
-    <col min="2" max="2" width="19.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="10.83203125" style="1"/>
   </cols>
@@ -3000,316 +3031,331 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$4</f>
-        <v>107.99</v>
+        <v>112.06</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C4" s="167">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="E4" s="95"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="E6" s="35"/>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B5" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C5" s="167">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E5" s="95"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B7" s="1" t="s">
+      <c r="E7" s="35"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C10" s="95"/>
-    </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C11" s="95">
-        <f>$C$3/'Statement Q'!$N$22</f>
-        <v>12.492176788683157</v>
-      </c>
+      <c r="C11" s="95"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>283</v>
+        <v>181</v>
       </c>
       <c r="C12" s="95">
-        <f>C3/Statements!S20</f>
-        <v>30.131070169400033</v>
+        <f>$C$3/'Statement Q'!$N$22</f>
+        <v>12.962990378181635</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C13" s="95">
+        <f>C3/Statements!S20</f>
+        <v>31.266670276719772</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C13" s="102">
+      <c r="C14" s="102">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$20)</f>
-        <v>4.8020641854181552</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B15" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C15" s="20">
-        <f>C3*'Statement Q'!N118</f>
-        <v>5031578.0699999994</v>
+        <v>4.9830476212423234</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C16" s="20">
+        <f>C3*'Statement Q'!N118</f>
+        <v>5221211.58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C17" s="20">
         <f>Statements!S23</f>
         <v>1251610</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C17" s="20">
-        <v>0</v>
-      </c>
-    </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C18" s="20">
-        <f>C15+C17-C16</f>
-        <v>3779968.0699999994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C19" s="20">
+        <f>C16+C18-C17</f>
+        <v>3969601.58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C19" s="95">
-        <f>C16/'Statement Q'!N118</f>
+      <c r="C20" s="95">
+        <f>C17/'Statement Q'!N118</f>
         <v>26.862618848324857</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="1" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C21" s="180">
+      <c r="C22" s="180">
         <f>_xlfn.RRI(5,Statements!C5,Statements!H5)</f>
         <v>0.45032461021270742</v>
       </c>
-      <c r="D21" s="180"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B22" s="1" t="s">
+      <c r="D22" s="180"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C22" s="180">
+      <c r="C23" s="180">
         <f>(Statements!H18-Statements!C18)/ABS(Statements!C18)</f>
         <v>11.577459432048682</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B23" s="1" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C23" s="180">
+      <c r="C24" s="180">
         <f>(Statements!H20-Statements!C20)/ABS(Statements!C20)</f>
         <v>3.7852801278278343</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B28" s="1" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B29" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29"/>
-      <c r="B29" s="1" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30"/>
+      <c r="B30" s="1" t="s">
         <v>298</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B30" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B32" s="1" t="s">
         <v>303</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B33" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C33" s="20">
-        <v>7278</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C34" s="20">
+        <v>7278</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B35" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C34" s="20">
+      <c r="C35" s="20">
         <f>'Statement Q'!N118</f>
         <v>46593</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B35" s="1" t="s">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B36" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C35" s="180">
-        <f>C33/C34</f>
+      <c r="C36" s="180">
+        <f>C34/C35</f>
         <v>0.15620372158907991</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B37" s="1" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B43" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B44" s="1" t="s">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B45" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="20">
+      <c r="C45" s="20">
         <f>Statements!S12*(1-'Statement Y'!G118)</f>
         <v>135496.41977987604</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C45" s="20">
+      <c r="C46" s="20">
         <f>Statements!S38-Statements!S23</f>
         <v>806384</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="C46" s="20">
+      <c r="C47" s="20">
         <f>SUM(Statements!S39:S42)</f>
         <v>574114</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B47" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C47" s="20">
-        <f>C45-C46</f>
-        <v>232270</v>
-      </c>
-      <c r="D47" s="20"/>
-    </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C48" s="20">
+        <f>C46-C47</f>
+        <v>232270</v>
+      </c>
+      <c r="D48" s="20"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C48" s="180">
-        <f>C44/C47</f>
+      <c r="C49" s="180">
+        <f>C45/C48</f>
         <v>0.58335738485330024</v>
       </c>
-      <c r="D48" s="180"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C50" s="108"/>
+      <c r="D49" s="180"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="222" t="s">
+      <c r="C51" s="108"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="224" t="s">
         <v>363</v>
       </c>
-      <c r="B51" s="222"/>
-      <c r="C51" s="222"/>
-      <c r="D51" s="222"/>
-      <c r="E51" s="222"/>
-      <c r="F51" s="222"/>
-      <c r="G51" s="222"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
-        <v>364</v>
-      </c>
+      <c r="B52" s="224"/>
+      <c r="C52" s="224"/>
+      <c r="D52" s="224"/>
+      <c r="E52" s="224"/>
+      <c r="F52" s="224"/>
+      <c r="G52" s="224"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="222" t="s">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="224" t="s">
         <v>297</v>
       </c>
-      <c r="B57" s="222"/>
-      <c r="C57" s="222"/>
-      <c r="D57" s="222"/>
-      <c r="E57" s="222"/>
-      <c r="F57" s="222"/>
-      <c r="G57" s="222"/>
-    </row>
-    <row r="58" spans="1:7" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59" s="7" t="s">
+      <c r="B58" s="224"/>
+      <c r="C58" s="224"/>
+      <c r="D58" s="224"/>
+      <c r="E58" s="224"/>
+      <c r="F58" s="224"/>
+      <c r="G58" s="224"/>
+    </row>
+    <row r="59" spans="1:7" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B60" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C60" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="D59" s="8"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
-        <v>369</v>
-      </c>
+      <c r="D60" s="8"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
         <v>373</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A58:G58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3317,7 +3363,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A4D25C-54F4-A248-899A-8DB25690A5F6}">
-  <dimension ref="A1:AE31"/>
+  <dimension ref="A1:AE33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="103" customWidth="1"/>
@@ -3346,60 +3392,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="222" t="s">
+      <c r="C2" s="224" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="222"/>
-      <c r="E2" s="222"/>
-      <c r="F2" s="222"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230" t="s">
+      <c r="D2" s="224"/>
+      <c r="E2" s="224"/>
+      <c r="F2" s="224"/>
+      <c r="G2" s="225"/>
+      <c r="H2" s="226" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="222"/>
-      <c r="J2" s="222"/>
-      <c r="K2" s="222"/>
-      <c r="L2" s="222"/>
-      <c r="S2" s="231"/>
-      <c r="T2" s="231"/>
-      <c r="U2" s="231"/>
-      <c r="V2" s="231"/>
-      <c r="W2" s="231"/>
-      <c r="X2" s="231"/>
-      <c r="Y2" s="231"/>
-      <c r="Z2" s="231"/>
-      <c r="AA2" s="231"/>
-      <c r="AB2" s="231"/>
-      <c r="AC2" s="231"/>
+      <c r="I2" s="224"/>
+      <c r="J2" s="224"/>
+      <c r="K2" s="224"/>
+      <c r="L2" s="224"/>
+      <c r="S2" s="227"/>
+      <c r="T2" s="227"/>
+      <c r="U2" s="227"/>
+      <c r="V2" s="227"/>
+      <c r="W2" s="227"/>
+      <c r="X2" s="227"/>
+      <c r="Y2" s="227"/>
+      <c r="Z2" s="227"/>
+      <c r="AA2" s="227"/>
+      <c r="AB2" s="227"/>
+      <c r="AC2" s="227"/>
       <c r="AE2" s="143"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="226" t="s">
+      <c r="C4" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="226"/>
-      <c r="E4" s="226"/>
-      <c r="F4" s="226"/>
-      <c r="G4" s="226"/>
-      <c r="H4" s="226"/>
-      <c r="I4" s="226"/>
-      <c r="J4" s="226"/>
-      <c r="K4" s="226"/>
-      <c r="L4" s="226"/>
-      <c r="S4" s="231"/>
-      <c r="T4" s="231"/>
-      <c r="U4" s="231"/>
-      <c r="V4" s="231"/>
-      <c r="W4" s="231"/>
-      <c r="X4" s="231"/>
-      <c r="Y4" s="231"/>
-      <c r="Z4" s="231"/>
-      <c r="AA4" s="231"/>
-      <c r="AB4" s="231"/>
-      <c r="AC4" s="231"/>
+      <c r="D4" s="223"/>
+      <c r="E4" s="223"/>
+      <c r="F4" s="223"/>
+      <c r="G4" s="223"/>
+      <c r="H4" s="223"/>
+      <c r="I4" s="223"/>
+      <c r="J4" s="223"/>
+      <c r="K4" s="223"/>
+      <c r="L4" s="223"/>
+      <c r="S4" s="227"/>
+      <c r="T4" s="227"/>
+      <c r="U4" s="227"/>
+      <c r="V4" s="227"/>
+      <c r="W4" s="227"/>
+      <c r="X4" s="227"/>
+      <c r="Y4" s="227"/>
+      <c r="Z4" s="227"/>
+      <c r="AA4" s="227"/>
+      <c r="AB4" s="227"/>
+      <c r="AC4" s="227"/>
       <c r="AE4" s="144"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -3886,50 +3932,47 @@
       <c r="AE12" s="108"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B13" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C13" s="113">
-        <f>C8-C12</f>
-        <v>-60007</v>
-      </c>
-      <c r="D13" s="113">
-        <f t="shared" ref="D13:L13" si="1">D8-D12</f>
-        <v>-65195</v>
-      </c>
-      <c r="E13" s="113">
-        <f t="shared" si="1"/>
-        <v>-13259</v>
-      </c>
-      <c r="F13" s="113">
-        <f t="shared" si="1"/>
-        <v>62595</v>
-      </c>
-      <c r="G13" s="157">
-        <f t="shared" si="1"/>
-        <v>135570</v>
-      </c>
-      <c r="H13" s="113">
-        <f t="shared" si="1"/>
-        <v>71481.02555999998</v>
-      </c>
-      <c r="I13" s="113">
-        <f t="shared" si="1"/>
-        <v>176826.08176406147</v>
-      </c>
-      <c r="J13" s="113">
-        <f t="shared" si="1"/>
-        <v>239857.68322192831</v>
-      </c>
-      <c r="K13" s="113">
-        <f t="shared" si="1"/>
-        <v>304878.22082084324</v>
-      </c>
-      <c r="L13" s="113">
-        <f t="shared" si="1"/>
-        <v>478662.87556607369</v>
-      </c>
-      <c r="N13" s="126"/>
+      <c r="B13" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C13" s="107">
+        <f>'Statement Y'!D174</f>
+        <v>2038.6800000000003</v>
+      </c>
+      <c r="D13" s="107">
+        <f>'Statement Y'!E174</f>
+        <v>1645.2100000000003</v>
+      </c>
+      <c r="E13" s="107">
+        <f>'Statement Y'!F174</f>
+        <v>1476.5800000000002</v>
+      </c>
+      <c r="F13" s="107">
+        <f>'Statement Y'!G174</f>
+        <v>3825.9200000000005</v>
+      </c>
+      <c r="G13" s="110">
+        <f>'Statement Y'!H174</f>
+        <v>6564.5300000000007</v>
+      </c>
+      <c r="H13" s="222">
+        <v>13931</v>
+      </c>
+      <c r="I13" s="222">
+        <v>15969</v>
+      </c>
+      <c r="J13" s="222">
+        <v>14606</v>
+      </c>
+      <c r="K13" s="222">
+        <v>15053</v>
+      </c>
+      <c r="L13" s="222">
+        <v>14217</v>
+      </c>
+      <c r="N13" s="164" t="s">
+        <v>383</v>
+      </c>
       <c r="Q13" s="126"/>
       <c r="S13" s="107"/>
       <c r="T13" s="107"/>
@@ -3944,464 +3987,582 @@
       <c r="AC13" s="108"/>
       <c r="AE13" s="108"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C16" s="226" t="s">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C14" s="107">
+        <f>'Statement Y'!D175</f>
+        <v>1074.3199999999997</v>
+      </c>
+      <c r="D14" s="107">
+        <f>'Statement Y'!E175</f>
+        <v>5618.79</v>
+      </c>
+      <c r="E14" s="107">
+        <f>'Statement Y'!F175</f>
+        <v>6282.42</v>
+      </c>
+      <c r="F14" s="107">
+        <f>'Statement Y'!G175</f>
+        <v>6707.08</v>
+      </c>
+      <c r="G14" s="110">
+        <f>'Statement Y'!H175</f>
+        <v>6289.4699999999993</v>
+      </c>
+      <c r="H14" s="195">
+        <f>H13-H13*Overview!$C$4</f>
+        <v>12955.83</v>
+      </c>
+      <c r="I14" s="195">
+        <f>I13-I13*Overview!$C$4</f>
+        <v>14851.17</v>
+      </c>
+      <c r="J14" s="195">
+        <f>J13-J13*Overview!$C$4</f>
+        <v>13583.58</v>
+      </c>
+      <c r="K14" s="195">
+        <f>K13-K13*Overview!$C$4</f>
+        <v>13999.29</v>
+      </c>
+      <c r="L14" s="195">
+        <f>L13-L13*Overview!$C$4</f>
+        <v>13221.81</v>
+      </c>
+      <c r="N14" s="164"/>
+      <c r="Q14" s="126"/>
+      <c r="S14" s="107"/>
+      <c r="T14" s="107"/>
+      <c r="U14" s="107"/>
+      <c r="V14" s="107"/>
+      <c r="W14" s="107"/>
+      <c r="X14" s="107"/>
+      <c r="Y14" s="107"/>
+      <c r="Z14" s="107"/>
+      <c r="AA14" s="108"/>
+      <c r="AB14" s="108"/>
+      <c r="AC14" s="108"/>
+      <c r="AE14" s="108"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B15" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="113">
+        <f>C8-C12+C13-C14</f>
+        <v>-59042.64</v>
+      </c>
+      <c r="D15" s="113">
+        <f t="shared" ref="D15:G15" si="1">D8-D12+D13-D14</f>
+        <v>-69168.58</v>
+      </c>
+      <c r="E15" s="113">
+        <f t="shared" si="1"/>
+        <v>-18064.84</v>
+      </c>
+      <c r="F15" s="113">
+        <f t="shared" si="1"/>
+        <v>59713.84</v>
+      </c>
+      <c r="G15" s="157">
+        <f t="shared" si="1"/>
+        <v>135845.06</v>
+      </c>
+      <c r="H15" s="113">
+        <f>H8-H12+H13*Overview!$C$4-H14</f>
+        <v>59500.365559999977</v>
+      </c>
+      <c r="I15" s="113">
+        <f>I8-I12+I13*Overview!$C$4-I14</f>
+        <v>163092.74176406144</v>
+      </c>
+      <c r="J15" s="113">
+        <f>J8-J12+J13*Overview!$C$4-J14</f>
+        <v>227296.52322192834</v>
+      </c>
+      <c r="K15" s="113">
+        <f>K8-K12+K13*Overview!$C$4-K14</f>
+        <v>291932.64082084328</v>
+      </c>
+      <c r="L15" s="113">
+        <f>L8-L12+L13*Overview!$C$4-L14</f>
+        <v>466436.2555660737</v>
+      </c>
+      <c r="N15" s="126"/>
+      <c r="Q15" s="126"/>
+      <c r="S15" s="107"/>
+      <c r="T15" s="107"/>
+      <c r="U15" s="107"/>
+      <c r="V15" s="107"/>
+      <c r="W15" s="107"/>
+      <c r="X15" s="107"/>
+      <c r="Y15" s="107"/>
+      <c r="Z15" s="107"/>
+      <c r="AA15" s="108"/>
+      <c r="AB15" s="108"/>
+      <c r="AC15" s="108"/>
+      <c r="AE15" s="108"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C18" s="223" t="s">
         <v>234</v>
       </c>
-      <c r="D16" s="226"/>
-      <c r="E16" s="226"/>
-      <c r="F16" s="226"/>
-      <c r="G16" s="226"/>
-      <c r="H16" s="226"/>
-      <c r="I16" s="226"/>
-      <c r="J16" s="226"/>
-      <c r="K16" s="226"/>
-      <c r="L16" s="226"/>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="62">
+      <c r="D18" s="223"/>
+      <c r="E18" s="223"/>
+      <c r="F18" s="223"/>
+      <c r="G18" s="223"/>
+      <c r="H18" s="223"/>
+      <c r="I18" s="223"/>
+      <c r="J18" s="223"/>
+      <c r="K18" s="223"/>
+      <c r="L18" s="223"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C19" s="62">
         <f>C5</f>
         <v>2021</v>
       </c>
-      <c r="D17" s="62">
-        <f t="shared" ref="D17:L17" si="2">D5</f>
+      <c r="D19" s="62">
+        <f t="shared" ref="D19:L19" si="2">D5</f>
         <v>2022</v>
       </c>
-      <c r="E17" s="62">
+      <c r="E19" s="62">
         <f t="shared" si="2"/>
         <v>2023</v>
       </c>
-      <c r="F17" s="62">
+      <c r="F19" s="62">
         <f t="shared" si="2"/>
         <v>2024</v>
       </c>
-      <c r="G17" s="62">
+      <c r="G19" s="62">
         <f t="shared" si="2"/>
         <v>2025</v>
       </c>
-      <c r="H17" s="62">
+      <c r="H19" s="62">
         <f t="shared" si="2"/>
         <v>2026</v>
       </c>
-      <c r="I17" s="62">
+      <c r="I19" s="62">
         <f t="shared" si="2"/>
         <v>2027</v>
       </c>
-      <c r="J17" s="62">
+      <c r="J19" s="62">
         <f t="shared" si="2"/>
         <v>2028</v>
       </c>
-      <c r="K17" s="62">
+      <c r="K19" s="62">
         <f t="shared" si="2"/>
         <v>2029</v>
       </c>
-      <c r="L17" s="62">
+      <c r="L19" s="62">
         <f t="shared" si="2"/>
         <v>2030</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B18" s="1" t="s">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="98">
+      <c r="C20" s="98">
         <f>'Statement Y'!D118</f>
         <v>2.9520664465125588E-3</v>
       </c>
-      <c r="D18" s="98">
+      <c r="D20" s="98">
         <f>'Statement Y'!E118</f>
         <v>1.599699843099802E-2</v>
       </c>
-      <c r="E18" s="98">
+      <c r="E20" s="98">
         <f>'Statement Y'!F118</f>
         <v>9.6191708387241948E-2</v>
       </c>
-      <c r="F18" s="98">
+      <c r="F20" s="98">
         <f>'Statement Y'!G118</f>
         <v>0.13422477665044083</v>
       </c>
-      <c r="G18" s="158">
+      <c r="G20" s="158">
         <v>0.21</v>
       </c>
-      <c r="H18" s="99">
+      <c r="H20" s="99">
         <v>0.21</v>
       </c>
-      <c r="I18" s="99">
+      <c r="I20" s="99">
         <v>0.21</v>
       </c>
-      <c r="J18" s="99">
+      <c r="J20" s="99">
         <v>0.21</v>
       </c>
-      <c r="K18" s="99">
+      <c r="K20" s="99">
         <v>0.21</v>
       </c>
-      <c r="L18" s="99">
+      <c r="L20" s="99">
         <v>0.21</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="226" t="s">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C23" s="223" t="s">
         <v>326</v>
       </c>
-      <c r="D21" s="226"/>
-      <c r="E21" s="226"/>
-      <c r="F21" s="226"/>
-      <c r="G21" s="226"/>
-      <c r="H21" s="226"/>
-      <c r="I21" s="226"/>
-      <c r="J21" s="226"/>
-      <c r="K21" s="226"/>
-      <c r="L21" s="226"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B22" s="7" t="s">
+      <c r="D23" s="223"/>
+      <c r="E23" s="223"/>
+      <c r="F23" s="223"/>
+      <c r="G23" s="223"/>
+      <c r="H23" s="223"/>
+      <c r="I23" s="223"/>
+      <c r="J23" s="223"/>
+      <c r="K23" s="223"/>
+      <c r="L23" s="223"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B24" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C22" s="62">
+      <c r="C24" s="62">
         <f>C5</f>
         <v>2021</v>
       </c>
-      <c r="D22" s="62">
-        <f t="shared" ref="D22:L22" si="3">D5</f>
+      <c r="D24" s="62">
+        <f t="shared" ref="D24:L24" si="3">D5</f>
         <v>2022</v>
       </c>
-      <c r="E22" s="62">
+      <c r="E24" s="62">
         <f t="shared" si="3"/>
         <v>2023</v>
       </c>
-      <c r="F22" s="62">
+      <c r="F24" s="62">
         <f t="shared" si="3"/>
         <v>2024</v>
       </c>
-      <c r="G22" s="62">
+      <c r="G24" s="62">
         <f t="shared" si="3"/>
         <v>2025</v>
       </c>
-      <c r="H22" s="62">
+      <c r="H24" s="62">
         <f t="shared" si="3"/>
         <v>2026</v>
       </c>
-      <c r="I22" s="62">
+      <c r="I24" s="62">
         <f t="shared" si="3"/>
         <v>2027</v>
       </c>
-      <c r="J22" s="62">
+      <c r="J24" s="62">
         <f t="shared" si="3"/>
         <v>2028</v>
       </c>
-      <c r="K22" s="62">
+      <c r="K24" s="62">
         <f t="shared" si="3"/>
         <v>2029</v>
       </c>
-      <c r="L22" s="62">
+      <c r="L24" s="62">
         <f t="shared" si="3"/>
         <v>2030</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B23" s="1" t="s">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="107">
+      <c r="C25" s="107">
         <f>'WC &amp; Investments'!C40</f>
         <v>2726</v>
       </c>
-      <c r="D23" s="107">
+      <c r="D25" s="107">
         <f>'WC &amp; Investments'!D40</f>
         <v>4870</v>
       </c>
-      <c r="E23" s="107">
+      <c r="E25" s="107">
         <f>'WC &amp; Investments'!E40</f>
         <v>7095</v>
       </c>
-      <c r="F23" s="107">
+      <c r="F25" s="107">
         <f>'WC &amp; Investments'!F40</f>
         <v>10854</v>
       </c>
-      <c r="G23" s="110">
+      <c r="G25" s="110">
         <f>'WC &amp; Investments'!G40</f>
         <v>14391</v>
       </c>
-      <c r="H23" s="107">
+      <c r="H25" s="107">
         <f>'WC &amp; Investments'!H40</f>
         <v>15487.555537999999</v>
       </c>
-      <c r="I23" s="107">
+      <c r="I25" s="107">
         <f>'WC &amp; Investments'!I40</f>
         <v>17682.60817640616</v>
       </c>
-      <c r="J23" s="107">
+      <c r="J25" s="107">
         <f>'WC &amp; Investments'!J40</f>
         <v>22272.499156321919</v>
       </c>
-      <c r="K23" s="107">
+      <c r="K25" s="107">
         <f>'WC &amp; Investments'!K40</f>
         <v>30025.885383870911</v>
       </c>
-      <c r="L23" s="107">
+      <c r="L25" s="107">
         <f>'WC &amp; Investments'!L40</f>
         <v>40406.606378954268</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="N25" s="1" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B24" s="1" t="s">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B26" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="107">
+      <c r="C26" s="107">
         <f>'WC &amp; Investments'!C43</f>
         <v>4224</v>
       </c>
-      <c r="D24" s="107">
+      <c r="D26" s="107">
         <f>'WC &amp; Investments'!D43</f>
         <v>8182</v>
       </c>
-      <c r="E24" s="107">
+      <c r="E26" s="107">
         <f>'WC &amp; Investments'!E43</f>
         <v>7753</v>
       </c>
-      <c r="F24" s="107">
+      <c r="F26" s="107">
         <f>'WC &amp; Investments'!F43</f>
         <v>22609</v>
       </c>
-      <c r="G24" s="110">
+      <c r="G26" s="110">
         <f>'WC &amp; Investments'!G43</f>
         <v>27120</v>
       </c>
-      <c r="H24" s="107">
+      <c r="H26" s="107">
         <f>'WC &amp; Investments'!H43</f>
         <v>29783.76065</v>
       </c>
-      <c r="I24" s="107">
+      <c r="I26" s="107">
         <f>'WC &amp; Investments'!I43</f>
         <v>34005.015723858</v>
       </c>
-      <c r="J24" s="107">
+      <c r="J26" s="107">
         <f>'WC &amp; Investments'!J43</f>
         <v>42831.72914677293</v>
       </c>
-      <c r="K24" s="107">
+      <c r="K26" s="107">
         <f>'WC &amp; Investments'!K43</f>
         <v>57742.087276674836</v>
       </c>
-      <c r="L24" s="107">
+      <c r="L26" s="107">
         <f>'WC &amp; Investments'!L43</f>
         <v>77705.012267219761</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="N26" s="1" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B25" s="1" t="s">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B27" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="107">
+      <c r="C27" s="107">
         <f>'WC &amp; Investments'!C33</f>
         <v>25775</v>
       </c>
-      <c r="D25" s="107">
+      <c r="D27" s="107">
         <f>'WC &amp; Investments'!D33</f>
         <v>34540</v>
       </c>
-      <c r="E25" s="107">
+      <c r="E27" s="107">
         <f>'WC &amp; Investments'!E33</f>
         <v>34898</v>
       </c>
-      <c r="F25" s="107">
+      <c r="F27" s="107">
         <f>'WC &amp; Investments'!F33</f>
         <v>75921</v>
       </c>
-      <c r="G25" s="110">
+      <c r="G27" s="110">
         <f>'WC &amp; Investments'!G33</f>
         <v>48966</v>
       </c>
-      <c r="H25" s="107">
+      <c r="H27" s="107">
         <f>'WC &amp; Investments'!H33</f>
         <v>101298.66585315757</v>
       </c>
-      <c r="I25" s="107">
+      <c r="I27" s="107">
         <f>'WC &amp; Investments'!I33</f>
         <v>111398.3080115295</v>
       </c>
-      <c r="J25" s="107">
+      <c r="J27" s="107">
         <f>'WC &amp; Investments'!J33</f>
         <v>120305.69197114962</v>
       </c>
-      <c r="K25" s="107">
+      <c r="K27" s="107">
         <f>'WC &amp; Investments'!K33</f>
         <v>143917.75003988505</v>
       </c>
-      <c r="L25" s="107">
+      <c r="L27" s="107">
         <f>'WC &amp; Investments'!L33</f>
         <v>195425.80102551548</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="N27" s="1" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C28" s="226" t="s">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C30" s="223" t="s">
         <v>236</v>
       </c>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="226"/>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B29" s="7" t="s">
+      <c r="D30" s="223"/>
+      <c r="E30" s="223"/>
+      <c r="F30" s="223"/>
+      <c r="G30" s="223"/>
+      <c r="H30" s="223"/>
+      <c r="I30" s="223"/>
+      <c r="J30" s="223"/>
+      <c r="K30" s="223"/>
+      <c r="L30" s="223"/>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B31" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C29" s="62">
+      <c r="C31" s="62">
         <f>C5</f>
         <v>2021</v>
       </c>
-      <c r="D29" s="62">
-        <f t="shared" ref="D29:L29" si="4">D5</f>
+      <c r="D31" s="62">
+        <f t="shared" ref="D31:L31" si="4">D5</f>
         <v>2022</v>
       </c>
-      <c r="E29" s="62">
+      <c r="E31" s="62">
         <f t="shared" si="4"/>
         <v>2023</v>
       </c>
-      <c r="F29" s="62">
+      <c r="F31" s="62">
         <f t="shared" si="4"/>
         <v>2024</v>
       </c>
-      <c r="G29" s="62">
+      <c r="G31" s="62">
         <f t="shared" si="4"/>
         <v>2025</v>
       </c>
-      <c r="H29" s="62">
+      <c r="H31" s="62">
         <f t="shared" si="4"/>
         <v>2026</v>
       </c>
-      <c r="I29" s="62">
+      <c r="I31" s="62">
         <f t="shared" si="4"/>
         <v>2027</v>
       </c>
-      <c r="J29" s="62">
+      <c r="J31" s="62">
         <f t="shared" si="4"/>
         <v>2028</v>
       </c>
-      <c r="K29" s="62">
+      <c r="K31" s="62">
         <f t="shared" si="4"/>
         <v>2029</v>
       </c>
-      <c r="L29" s="62">
+      <c r="L31" s="62">
         <f t="shared" si="4"/>
         <v>2030</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B30" s="1" t="s">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B32" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C30" s="154">
-        <f>C13*(1-C18)</f>
-        <v>-59829.855348744117</v>
-      </c>
-      <c r="D30" s="154">
-        <f t="shared" ref="D30:L30" si="5">D13*(1-D18)</f>
-        <v>-64152.075687291086</v>
-      </c>
-      <c r="E30" s="154">
+      <c r="C32" s="154">
+        <f>C15*(1-C20)</f>
+        <v>-58868.342203542481</v>
+      </c>
+      <c r="D32" s="154">
+        <f t="shared" ref="D32:L32" si="5">D15*(1-D20)</f>
+        <v>-68062.090334265638</v>
+      </c>
+      <c r="E32" s="154">
         <f t="shared" si="5"/>
-        <v>-11983.59413849356</v>
-      </c>
-      <c r="F30" s="154">
+        <v>-16327.152178657818</v>
+      </c>
+      <c r="F32" s="154">
         <f t="shared" si="5"/>
-        <v>54193.200105565651</v>
-      </c>
-      <c r="G30" s="161">
+        <v>51698.763163059833</v>
+      </c>
+      <c r="G32" s="161">
         <f t="shared" si="5"/>
-        <v>107100.3</v>
-      </c>
-      <c r="H30" s="154">
+        <v>107317.5974</v>
+      </c>
+      <c r="H32" s="154">
         <f t="shared" si="5"/>
-        <v>56470.01019239999</v>
-      </c>
-      <c r="I30" s="154">
+        <v>47005.288792399981</v>
+      </c>
+      <c r="I32" s="154">
         <f t="shared" si="5"/>
-        <v>139692.60459360856</v>
-      </c>
-      <c r="J30" s="154">
+        <v>128843.26599360854</v>
+      </c>
+      <c r="J32" s="154">
         <f t="shared" si="5"/>
-        <v>189487.56974532336</v>
-      </c>
-      <c r="K30" s="154">
+        <v>179564.25334532341</v>
+      </c>
+      <c r="K32" s="154">
         <f t="shared" si="5"/>
-        <v>240853.79444846619</v>
-      </c>
-      <c r="L30" s="154">
+        <v>230626.7862484662</v>
+      </c>
+      <c r="L32" s="154">
         <f t="shared" si="5"/>
-        <v>378143.67169719824</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B31" s="7" t="s">
+        <v>368484.64189719822</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B33" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="C31" s="113">
-        <f>C30+C23-C24+C25</f>
-        <v>-35552.855348744117</v>
-      </c>
-      <c r="D31" s="113">
-        <f t="shared" ref="D31:L31" si="6">D30+D23-D24+D25</f>
-        <v>-32924.075687291086</v>
-      </c>
-      <c r="E31" s="113">
+      <c r="C33" s="113">
+        <f>C32+C25-C26+C27</f>
+        <v>-34591.342203542481</v>
+      </c>
+      <c r="D33" s="113">
+        <f t="shared" ref="D33:L33" si="6">D32+D25-D26+D27</f>
+        <v>-36834.090334265638</v>
+      </c>
+      <c r="E33" s="113">
         <f t="shared" si="6"/>
-        <v>22256.405861506442</v>
-      </c>
-      <c r="F31" s="113">
+        <v>17912.847821342184</v>
+      </c>
+      <c r="F33" s="113">
         <f t="shared" si="6"/>
-        <v>118359.20010556566</v>
-      </c>
-      <c r="G31" s="157">
+        <v>115864.76316305983</v>
+      </c>
+      <c r="G33" s="157">
         <f t="shared" si="6"/>
-        <v>143337.29999999999</v>
-      </c>
-      <c r="H31" s="113">
+        <v>143554.5974</v>
+      </c>
+      <c r="H33" s="113">
         <f t="shared" si="6"/>
-        <v>143472.47093355755</v>
-      </c>
-      <c r="I31" s="113">
+        <v>134007.74953355754</v>
+      </c>
+      <c r="I33" s="113">
         <f t="shared" si="6"/>
-        <v>234768.50505768621</v>
-      </c>
-      <c r="J31" s="113">
+        <v>223919.16645768619</v>
+      </c>
+      <c r="J33" s="113">
         <f t="shared" si="6"/>
-        <v>289234.03172602196</v>
-      </c>
-      <c r="K31" s="113">
+        <v>279310.71532602201</v>
+      </c>
+      <c r="K33" s="113">
         <f t="shared" si="6"/>
-        <v>357055.34259554732</v>
-      </c>
-      <c r="L31" s="113">
+        <v>346828.33439554734</v>
+      </c>
+      <c r="L33" s="113">
         <f t="shared" si="6"/>
-        <v>536271.06683444814</v>
+        <v>526612.03703444824</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C28:L28"/>
+    <mergeCell ref="C30:L30"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C16:L16"/>
-    <mergeCell ref="C21:L21"/>
+    <mergeCell ref="C18:L18"/>
+    <mergeCell ref="C23:L23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4461,10 +4622,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="222" t="s">
+      <c r="B4" s="224" t="s">
         <v>253</v>
       </c>
-      <c r="C4" s="222"/>
+      <c r="C4" s="224"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4481,7 +4642,7 @@
       </c>
       <c r="C6" s="166">
         <f>Overview!C3</f>
-        <v>107.99</v>
+        <v>112.06</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4490,7 +4651,7 @@
       </c>
       <c r="C7" s="168">
         <f>C5*C6</f>
-        <v>5276570.5537718786</v>
+        <v>5475437.5058401404</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4498,7 +4659,8 @@
         <v>237</v>
       </c>
       <c r="C8" s="153">
-        <v>0</v>
+        <f>'Statement Q'!N158</f>
+        <v>91873</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4507,7 +4669,7 @@
       </c>
       <c r="C9" s="191">
         <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.3920000000000001E-2</v>
+        <v>4.5950000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4516,7 +4678,7 @@
       </c>
       <c r="C10" s="166">
         <f>[1]Sheet1!$F$4</f>
-        <v>0.9</v>
+        <v>0.89770000000000005</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4540,15 +4702,16 @@
         <v>258</v>
       </c>
       <c r="C13" s="167">
-        <v>6.9099999999999995E-2</v>
+        <f>Overview!C5</f>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="222" t="s">
+      <c r="B15" s="224" t="s">
         <v>259</v>
       </c>
-      <c r="C15" s="222"/>
+      <c r="C15" s="224"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -4556,7 +4719,7 @@
       </c>
       <c r="C16" s="169">
         <f>C8/(C8+C7)</f>
-        <v>0</v>
+        <v>1.650222309383044E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4565,7 +4728,7 @@
       </c>
       <c r="C17" s="169">
         <f>C7/(C8+C7)</f>
-        <v>1</v>
+        <v>0.98349777690616957</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4574,7 +4737,7 @@
       </c>
       <c r="C18" s="169">
         <f>C13*(1-C12)</f>
-        <v>5.4588999999999999E-2</v>
+        <v>5.5300000000000009E-2</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4583,7 +4746,7 @@
       </c>
       <c r="C19" s="169">
         <f>C9+C10*C11</f>
-        <v>8.8919999999999999E-2</v>
+        <v>9.0835000000000013E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4592,10 +4755,17 @@
       </c>
       <c r="C20" s="169">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>8.8919999999999999E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
+        <v>9.0248593502360752E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C21" s="167">
+        <v>0.1</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B4:C4"/>
@@ -4639,60 +4809,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="104"/>
-      <c r="C3" s="222" t="s">
+      <c r="C3" s="224" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="222"/>
-      <c r="E3" s="222"/>
-      <c r="F3" s="222"/>
-      <c r="G3" s="229"/>
-      <c r="H3" s="230" t="s">
+      <c r="D3" s="224"/>
+      <c r="E3" s="224"/>
+      <c r="F3" s="224"/>
+      <c r="G3" s="225"/>
+      <c r="H3" s="226" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="222"/>
-      <c r="J3" s="222"/>
-      <c r="K3" s="222"/>
-      <c r="L3" s="222"/>
-      <c r="P3" s="231"/>
-      <c r="Q3" s="231"/>
-      <c r="R3" s="231"/>
-      <c r="S3" s="231"/>
-      <c r="T3" s="231"/>
-      <c r="U3" s="231"/>
-      <c r="V3" s="231"/>
-      <c r="W3" s="231"/>
-      <c r="X3" s="231"/>
-      <c r="Y3" s="231"/>
-      <c r="Z3" s="231"/>
+      <c r="I3" s="224"/>
+      <c r="J3" s="224"/>
+      <c r="K3" s="224"/>
+      <c r="L3" s="224"/>
+      <c r="P3" s="227"/>
+      <c r="Q3" s="227"/>
+      <c r="R3" s="227"/>
+      <c r="S3" s="227"/>
+      <c r="T3" s="227"/>
+      <c r="U3" s="227"/>
+      <c r="V3" s="227"/>
+      <c r="W3" s="227"/>
+      <c r="X3" s="227"/>
+      <c r="Y3" s="227"/>
+      <c r="Z3" s="227"/>
       <c r="AB3" s="143"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="109"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="226" t="s">
+      <c r="C5" s="223" t="s">
         <v>273</v>
       </c>
-      <c r="D5" s="226"/>
-      <c r="E5" s="226"/>
-      <c r="F5" s="226"/>
-      <c r="G5" s="226"/>
-      <c r="H5" s="226"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="226"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="226"/>
-      <c r="P5" s="231"/>
-      <c r="Q5" s="231"/>
-      <c r="R5" s="231"/>
-      <c r="S5" s="231"/>
-      <c r="T5" s="231"/>
-      <c r="U5" s="231"/>
-      <c r="V5" s="231"/>
-      <c r="W5" s="231"/>
-      <c r="X5" s="231"/>
-      <c r="Y5" s="231"/>
-      <c r="Z5" s="231"/>
+      <c r="D5" s="223"/>
+      <c r="E5" s="223"/>
+      <c r="F5" s="223"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="223"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="223"/>
+      <c r="K5" s="223"/>
+      <c r="L5" s="223"/>
+      <c r="P5" s="227"/>
+      <c r="Q5" s="227"/>
+      <c r="R5" s="227"/>
+      <c r="S5" s="227"/>
+      <c r="T5" s="227"/>
+      <c r="U5" s="227"/>
+      <c r="V5" s="227"/>
+      <c r="W5" s="227"/>
+      <c r="X5" s="227"/>
+      <c r="Y5" s="227"/>
+      <c r="Z5" s="227"/>
       <c r="AB5" s="144"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4758,44 +4928,44 @@
         <v>236</v>
       </c>
       <c r="C7" s="153">
-        <f>'FCF &amp; Other'!C31</f>
-        <v>-35552.855348744117</v>
+        <f>'FCF &amp; Other'!C33</f>
+        <v>-34591.342203542481</v>
       </c>
       <c r="D7" s="153">
-        <f>'FCF &amp; Other'!D31</f>
-        <v>-32924.075687291086</v>
+        <f>'FCF &amp; Other'!D33</f>
+        <v>-36834.090334265638</v>
       </c>
       <c r="E7" s="153">
-        <f>'FCF &amp; Other'!E31</f>
-        <v>22256.405861506442</v>
+        <f>'FCF &amp; Other'!E33</f>
+        <v>17912.847821342184</v>
       </c>
       <c r="F7" s="153">
-        <f>'FCF &amp; Other'!F31</f>
-        <v>118359.20010556566</v>
+        <f>'FCF &amp; Other'!F33</f>
+        <v>115864.76316305983</v>
       </c>
       <c r="G7" s="155">
-        <f>'FCF &amp; Other'!G31</f>
-        <v>143337.29999999999</v>
+        <f>'FCF &amp; Other'!G33</f>
+        <v>143554.5974</v>
       </c>
       <c r="H7" s="153">
-        <f>'FCF &amp; Other'!H31</f>
-        <v>143472.47093355755</v>
+        <f>'FCF &amp; Other'!H33</f>
+        <v>134007.74953355754</v>
       </c>
       <c r="I7" s="153">
-        <f>'FCF &amp; Other'!I31</f>
-        <v>234768.50505768621</v>
+        <f>'FCF &amp; Other'!I33</f>
+        <v>223919.16645768619</v>
       </c>
       <c r="J7" s="153">
-        <f>'FCF &amp; Other'!J31</f>
-        <v>289234.03172602196</v>
+        <f>'FCF &amp; Other'!J33</f>
+        <v>279310.71532602201</v>
       </c>
       <c r="K7" s="153">
-        <f>'FCF &amp; Other'!K31</f>
-        <v>357055.34259554732</v>
+        <f>'FCF &amp; Other'!K33</f>
+        <v>346828.33439554734</v>
       </c>
       <c r="L7" s="153">
-        <f>'FCF &amp; Other'!L31</f>
-        <v>536271.06683444814</v>
+        <f>'FCF &amp; Other'!L33</f>
+        <v>526612.03703444824</v>
       </c>
       <c r="N7" s="93"/>
       <c r="O7" s="7"/>
@@ -4845,7 +5015,7 @@
       </c>
       <c r="L8" s="154">
         <f>L7*(1+C14)/(C15-C14)</f>
-        <v>7936687.2920942698</v>
+        <v>7646334.9797471194</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="7"/>
@@ -4899,23 +5069,23 @@
       <c r="G10" s="171"/>
       <c r="H10" s="154">
         <f>H7/(1+$C$15)^H9</f>
-        <v>131756.66801377287</v>
+        <v>122914.85660446061</v>
       </c>
       <c r="I10" s="154">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$15)^I9</f>
-        <v>197992.11071893357</v>
+        <v>188382.3449618867</v>
       </c>
       <c r="J10" s="154">
         <f t="shared" si="1"/>
-        <v>224006.93712430127</v>
+        <v>215531.61931408988</v>
       </c>
       <c r="K10" s="154">
         <f t="shared" si="1"/>
-        <v>253952.0002072088</v>
+        <v>245477.91730088624</v>
       </c>
       <c r="L10" s="154">
         <f t="shared" si="1"/>
-        <v>350271.25133561692</v>
+        <v>341871.66444169253</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -4934,14 +5104,14 @@
       <c r="K11" s="151"/>
       <c r="L11" s="154">
         <f>L8/(1+C15)^L9</f>
-        <v>5183933.2031678651</v>
+        <v>4963929.957100248</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="222" t="s">
+      <c r="B13" s="224" t="s">
         <v>274</v>
       </c>
-      <c r="C13" s="222"/>
+      <c r="C13" s="224"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4957,14 +5127,14 @@
       </c>
       <c r="C15" s="170">
         <f>WACC!C20</f>
-        <v>8.8919999999999999E-2</v>
+        <v>9.0248593502360752E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="222" t="s">
+      <c r="B18" s="224" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="222"/>
+      <c r="C18" s="224"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -4972,7 +5142,7 @@
       </c>
       <c r="C19" s="108">
         <f>SUM(H10:L10)</f>
-        <v>1157978.9673998335</v>
+        <v>1114178.4026230159</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -4981,7 +5151,7 @@
       </c>
       <c r="C20" s="108">
         <f>L11</f>
-        <v>5183933.2031678651</v>
+        <v>4963929.957100248</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -4990,7 +5160,7 @@
       </c>
       <c r="C21" s="113">
         <f>C19+C20</f>
-        <v>6341912.1705676988</v>
+        <v>6078108.3597232644</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -4998,7 +5168,7 @@
         <v>267</v>
       </c>
       <c r="C22" s="20">
-        <f>'Statement Q'!N25+'Statement Q'!N26</f>
+        <f>'Statement Q'!N159</f>
         <v>1251610</v>
       </c>
     </row>
@@ -5007,7 +5177,7 @@
         <v>268</v>
       </c>
       <c r="C23" s="20">
-        <f>'Statement Q'!N47</f>
+        <f>'Statement Q'!N158</f>
         <v>91873</v>
       </c>
     </row>
@@ -5017,7 +5187,7 @@
       </c>
       <c r="C24" s="113">
         <f>C21+C22-C23</f>
-        <v>7501649.1705676988</v>
+        <v>7237845.3597232644</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -5035,7 +5205,7 @@
       </c>
       <c r="C26" s="173">
         <f>C24/C25</f>
-        <v>153.52833543569611</v>
+        <v>148.12934128925642</v>
       </c>
     </row>
   </sheetData>
@@ -5078,37 +5248,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="222" t="s">
+      <c r="C2" s="224" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="222"/>
-      <c r="E2" s="222"/>
-      <c r="F2" s="222"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230" t="s">
+      <c r="D2" s="224"/>
+      <c r="E2" s="224"/>
+      <c r="F2" s="224"/>
+      <c r="G2" s="225"/>
+      <c r="H2" s="226" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="222"/>
-      <c r="J2" s="222"/>
-      <c r="K2" s="222"/>
-      <c r="L2" s="222"/>
+      <c r="I2" s="224"/>
+      <c r="J2" s="224"/>
+      <c r="K2" s="224"/>
+      <c r="L2" s="224"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="226" t="s">
+      <c r="C4" s="223" t="s">
         <v>333</v>
       </c>
-      <c r="D4" s="226"/>
-      <c r="E4" s="226"/>
-      <c r="F4" s="226"/>
-      <c r="G4" s="226"/>
-      <c r="H4" s="226"/>
-      <c r="I4" s="226"/>
-      <c r="J4" s="226"/>
-      <c r="K4" s="226"/>
-      <c r="L4" s="226"/>
+      <c r="D4" s="223"/>
+      <c r="E4" s="223"/>
+      <c r="F4" s="223"/>
+      <c r="G4" s="223"/>
+      <c r="H4" s="223"/>
+      <c r="I4" s="223"/>
+      <c r="J4" s="223"/>
+      <c r="K4" s="223"/>
+      <c r="L4" s="223"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -5206,44 +5376,44 @@
         <v>180</v>
       </c>
       <c r="C7" s="111">
-        <f>'FCF &amp; Other'!C13</f>
-        <v>-60007</v>
+        <f>'FCF &amp; Other'!C15</f>
+        <v>-59042.64</v>
       </c>
       <c r="D7" s="111">
-        <f>'FCF &amp; Other'!D13</f>
-        <v>-65195</v>
+        <f>'FCF &amp; Other'!D15</f>
+        <v>-69168.58</v>
       </c>
       <c r="E7" s="111">
-        <f>'FCF &amp; Other'!E13</f>
-        <v>-13259</v>
+        <f>'FCF &amp; Other'!E15</f>
+        <v>-18064.84</v>
       </c>
       <c r="F7" s="111">
-        <f>'FCF &amp; Other'!F13</f>
-        <v>62595</v>
+        <f>'FCF &amp; Other'!F15</f>
+        <v>59713.84</v>
       </c>
       <c r="G7" s="112">
-        <f>'FCF &amp; Other'!G13</f>
-        <v>135570</v>
+        <f>'FCF &amp; Other'!G15</f>
+        <v>135845.06</v>
       </c>
       <c r="H7" s="111">
-        <f>'FCF &amp; Other'!H13</f>
-        <v>71481.02555999998</v>
+        <f>'FCF &amp; Other'!H15</f>
+        <v>59500.365559999977</v>
       </c>
       <c r="I7" s="111">
-        <f>'FCF &amp; Other'!I13</f>
-        <v>176826.08176406147</v>
+        <f>'FCF &amp; Other'!I15</f>
+        <v>163092.74176406144</v>
       </c>
       <c r="J7" s="111">
-        <f>'FCF &amp; Other'!J13</f>
-        <v>239857.68322192831</v>
+        <f>'FCF &amp; Other'!J15</f>
+        <v>227296.52322192834</v>
       </c>
       <c r="K7" s="111">
-        <f>'FCF &amp; Other'!K13</f>
-        <v>304878.22082084324</v>
+        <f>'FCF &amp; Other'!K15</f>
+        <v>291932.64082084328</v>
       </c>
       <c r="L7" s="111">
-        <f>'FCF &amp; Other'!L13</f>
-        <v>478662.87556607369</v>
+        <f>'FCF &amp; Other'!L15</f>
+        <v>466436.2555660737</v>
       </c>
       <c r="N7" s="93"/>
     </row>
@@ -5252,44 +5422,44 @@
         <v>236</v>
       </c>
       <c r="C8" s="111">
-        <f>'FCF &amp; Other'!C31</f>
-        <v>-35552.855348744117</v>
+        <f>'FCF &amp; Other'!C33</f>
+        <v>-34591.342203542481</v>
       </c>
       <c r="D8" s="111">
-        <f>'FCF &amp; Other'!D31</f>
-        <v>-32924.075687291086</v>
+        <f>'FCF &amp; Other'!D33</f>
+        <v>-36834.090334265638</v>
       </c>
       <c r="E8" s="111">
-        <f>'FCF &amp; Other'!E31</f>
-        <v>22256.405861506442</v>
+        <f>'FCF &amp; Other'!E33</f>
+        <v>17912.847821342184</v>
       </c>
       <c r="F8" s="111">
-        <f>'FCF &amp; Other'!F31</f>
-        <v>118359.20010556566</v>
+        <f>'FCF &amp; Other'!F33</f>
+        <v>115864.76316305983</v>
       </c>
       <c r="G8" s="112">
-        <f>'FCF &amp; Other'!G31</f>
-        <v>143337.29999999999</v>
+        <f>'FCF &amp; Other'!G33</f>
+        <v>143554.5974</v>
       </c>
       <c r="H8" s="111">
-        <f>'FCF &amp; Other'!H31</f>
-        <v>143472.47093355755</v>
+        <f>'FCF &amp; Other'!H33</f>
+        <v>134007.74953355754</v>
       </c>
       <c r="I8" s="111">
-        <f>'FCF &amp; Other'!I31</f>
-        <v>234768.50505768621</v>
+        <f>'FCF &amp; Other'!I33</f>
+        <v>223919.16645768619</v>
       </c>
       <c r="J8" s="111">
-        <f>'FCF &amp; Other'!J31</f>
-        <v>289234.03172602196</v>
+        <f>'FCF &amp; Other'!J33</f>
+        <v>279310.71532602201</v>
       </c>
       <c r="K8" s="111">
-        <f>'FCF &amp; Other'!K31</f>
-        <v>357055.34259554732</v>
+        <f>'FCF &amp; Other'!K33</f>
+        <v>346828.33439554734</v>
       </c>
       <c r="L8" s="111">
-        <f>'FCF &amp; Other'!L31</f>
-        <v>536271.06683444814</v>
+        <f>'FCF &amp; Other'!L33</f>
+        <v>526612.03703444824</v>
       </c>
       <c r="N8" s="93"/>
     </row>
@@ -5297,18 +5467,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="226" t="s">
+      <c r="C10" s="223" t="s">
         <v>191</v>
       </c>
-      <c r="D10" s="226"/>
-      <c r="E10" s="226"/>
-      <c r="F10" s="226"/>
-      <c r="G10" s="226"/>
-      <c r="H10" s="226"/>
-      <c r="I10" s="226"/>
-      <c r="J10" s="226"/>
-      <c r="K10" s="226"/>
-      <c r="L10" s="226"/>
+      <c r="D10" s="223"/>
+      <c r="E10" s="223"/>
+      <c r="F10" s="223"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="223"/>
+      <c r="I10" s="223"/>
+      <c r="J10" s="223"/>
+      <c r="K10" s="223"/>
+      <c r="L10" s="223"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5407,39 +5577,39 @@
       <c r="C13" s="151"/>
       <c r="D13" s="116">
         <f t="shared" ref="D13:D14" si="3">(D7-C7)/C7</f>
-        <v>8.6456580065659011E-2</v>
+        <v>0.1715021550526874</v>
       </c>
       <c r="E13" s="116">
         <f t="shared" ref="E13:E14" si="4">(E7-D7)/D7</f>
-        <v>-0.79662550809111132</v>
+        <v>-0.73882881504868259</v>
       </c>
       <c r="F13" s="116">
         <f t="shared" ref="F13:F14" si="5">(F7-E7)/E7</f>
-        <v>-5.7209442642733235</v>
+        <v>-4.3055283080281912</v>
       </c>
       <c r="G13" s="117">
         <f t="shared" ref="G13:G14" si="6">(G7-F7)/F7</f>
-        <v>1.1658279415288761</v>
+        <v>1.2749342530977743</v>
       </c>
       <c r="H13" s="116">
         <f t="shared" ref="H13:H14" si="7">(H7-G7)/G7</f>
-        <v>-0.47273714273069278</v>
+        <v>-0.56199831219479035</v>
       </c>
       <c r="I13" s="116">
         <f t="shared" ref="I13:I14" si="8">(I7-H7)/H7</f>
-        <v>1.4737485280710838</v>
+        <v>1.7410376428628702</v>
       </c>
       <c r="J13" s="116">
         <f t="shared" ref="J13:J14" si="9">(J7-I7)/I7</f>
-        <v>0.35646099732034847</v>
+        <v>0.39366424749145162</v>
       </c>
       <c r="K13" s="116">
         <f t="shared" ref="K13:K14" si="10">(K7-J7)/J7</f>
-        <v>0.27107965325736377</v>
+        <v>0.28436914336699015</v>
       </c>
       <c r="L13" s="116">
         <f t="shared" ref="L13:L14" si="11">(L7-K7)/K7</f>
-        <v>0.57001334591017638</v>
+        <v>0.59775300992231928</v>
       </c>
       <c r="N13" s="93"/>
     </row>
@@ -5450,39 +5620,39 @@
       <c r="C14" s="151"/>
       <c r="D14" s="116">
         <f t="shared" si="3"/>
-        <v>-7.3940043230476871E-2</v>
+        <v>6.4835533629379632E-2</v>
       </c>
       <c r="E14" s="116">
         <f t="shared" si="4"/>
-        <v>-1.6759918204810094</v>
+        <v>-1.4863116656006679</v>
       </c>
       <c r="F14" s="116">
         <f t="shared" si="5"/>
-        <v>4.3179835433480198</v>
+        <v>5.4682491761590963</v>
       </c>
       <c r="G14" s="117">
         <f t="shared" si="6"/>
-        <v>0.2110364033565294</v>
+        <v>0.23898408352133305</v>
       </c>
       <c r="H14" s="116">
         <f t="shared" si="7"/>
-        <v>9.4302692709823533E-4</v>
+        <v>-6.6503254088346328E-2</v>
       </c>
       <c r="I14" s="116">
         <f t="shared" si="8"/>
-        <v>0.63633137095971593</v>
+        <v>0.67094192117309981</v>
       </c>
       <c r="J14" s="116">
         <f t="shared" si="9"/>
-        <v>0.231996735060151</v>
+        <v>0.24737296831087974</v>
       </c>
       <c r="K14" s="116">
         <f t="shared" si="10"/>
-        <v>0.23448592983611746</v>
+        <v>0.24172942663770067</v>
       </c>
       <c r="L14" s="116">
         <f t="shared" si="11"/>
-        <v>0.50192702043365456</v>
+        <v>0.51836509537846165</v>
       </c>
       <c r="N14" s="93"/>
     </row>
@@ -5490,18 +5660,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="226" t="s">
+      <c r="C16" s="223" t="s">
         <v>315</v>
       </c>
-      <c r="D16" s="226"/>
-      <c r="E16" s="226"/>
-      <c r="F16" s="226"/>
-      <c r="G16" s="226"/>
-      <c r="H16" s="226"/>
-      <c r="I16" s="226"/>
-      <c r="J16" s="226"/>
-      <c r="K16" s="226"/>
-      <c r="L16" s="226"/>
+      <c r="D16" s="223"/>
+      <c r="E16" s="223"/>
+      <c r="F16" s="223"/>
+      <c r="G16" s="223"/>
+      <c r="H16" s="223"/>
+      <c r="I16" s="223"/>
+      <c r="J16" s="223"/>
+      <c r="K16" s="223"/>
+      <c r="L16" s="223"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5635,18 +5805,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="226" t="s">
+      <c r="C21" s="223" t="s">
         <v>334</v>
       </c>
-      <c r="D21" s="226"/>
-      <c r="E21" s="226"/>
-      <c r="F21" s="226"/>
-      <c r="G21" s="226"/>
-      <c r="H21" s="226"/>
-      <c r="I21" s="226"/>
-      <c r="J21" s="226"/>
-      <c r="K21" s="226"/>
-      <c r="L21" s="226"/>
+      <c r="D21" s="223"/>
+      <c r="E21" s="223"/>
+      <c r="F21" s="223"/>
+      <c r="G21" s="223"/>
+      <c r="H21" s="223"/>
+      <c r="I21" s="223"/>
+      <c r="J21" s="223"/>
+      <c r="K21" s="223"/>
+      <c r="L21" s="223"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5697,23 +5867,23 @@
         <v>84</v>
       </c>
       <c r="C23" s="199">
-        <f>'Statement Y'!D167</f>
+        <f>'Statement Y'!D168</f>
         <v>110.58</v>
       </c>
       <c r="D23" s="199">
-        <f>'Statement Y'!E167</f>
+        <f>'Statement Y'!E168</f>
         <v>71.13</v>
       </c>
       <c r="E23" s="199">
-        <f>'Statement Y'!F167</f>
+        <f>'Statement Y'!F168</f>
         <v>226.85</v>
       </c>
       <c r="F23" s="199">
-        <f>'Statement Y'!G167</f>
+        <f>'Statement Y'!G168</f>
         <v>325.2</v>
       </c>
       <c r="G23" s="201">
-        <f>'Statement Y'!H167</f>
+        <f>'Statement Y'!H168</f>
         <v>177.14</v>
       </c>
       <c r="H23" s="151"/>
@@ -5730,18 +5900,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="226" t="s">
+      <c r="C26" s="223" t="s">
         <v>336</v>
       </c>
-      <c r="D26" s="226"/>
-      <c r="E26" s="226"/>
-      <c r="F26" s="226"/>
-      <c r="G26" s="226"/>
-      <c r="H26" s="226"/>
-      <c r="I26" s="226"/>
-      <c r="J26" s="226"/>
-      <c r="K26" s="226"/>
-      <c r="L26" s="226"/>
+      <c r="D26" s="223"/>
+      <c r="E26" s="223"/>
+      <c r="F26" s="223"/>
+      <c r="G26" s="223"/>
+      <c r="H26" s="223"/>
+      <c r="I26" s="223"/>
+      <c r="J26" s="223"/>
+      <c r="K26" s="223"/>
+      <c r="L26" s="223"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -5853,20 +6023,25 @@
       <c r="B30" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C30" s="199">
-        <v>0</v>
+      <c r="C30" s="205">
+        <f>'Statement Y'!D172</f>
+        <v>29124</v>
       </c>
       <c r="D30" s="199">
-        <v>0</v>
+        <f>'Statement Y'!E172</f>
+        <v>23503</v>
       </c>
       <c r="E30" s="199">
-        <v>0</v>
+        <f>'Statement Y'!F172</f>
+        <v>21094</v>
       </c>
       <c r="F30" s="199">
-        <v>0</v>
+        <f>'Statement Y'!G172</f>
+        <v>54656</v>
       </c>
       <c r="G30" s="201">
-        <v>0</v>
+        <f>'Statement Y'!H172</f>
+        <v>93779</v>
       </c>
       <c r="H30" s="151"/>
       <c r="I30" s="151"/>
@@ -5880,23 +6055,23 @@
         <v>241</v>
       </c>
       <c r="C31" s="205">
-        <f>Statements!D23</f>
+        <f>'Statement Y'!D173</f>
         <v>553922</v>
       </c>
       <c r="D31" s="205">
-        <f>Statements!E23</f>
+        <f>'Statement Y'!E173</f>
         <v>608180</v>
       </c>
       <c r="E31" s="205">
-        <f>Statements!F23</f>
+        <f>'Statement Y'!F173</f>
         <v>747610</v>
       </c>
       <c r="F31" s="205">
-        <f>Statements!G23</f>
+        <f>'Statement Y'!G173</f>
         <v>877645</v>
       </c>
       <c r="G31" s="206">
-        <f>Statements!H23</f>
+        <f>'Statement Y'!H173</f>
         <v>1140467</v>
       </c>
       <c r="H31" s="151"/>
@@ -5912,23 +6087,23 @@
       </c>
       <c r="C32" s="195">
         <f>C29+C30-C31</f>
-        <v>2037299.1400000001</v>
+        <v>2066423.1400000001</v>
       </c>
       <c r="D32" s="195">
         <f t="shared" ref="D32:G32" si="19">D29+D30-D31</f>
-        <v>2199321.0999999996</v>
+        <v>2222824.0999999996</v>
       </c>
       <c r="E32" s="195">
         <f t="shared" si="19"/>
-        <v>9805905.6999999993</v>
+        <v>9826999.6999999993</v>
       </c>
       <c r="F32" s="195">
         <f t="shared" si="19"/>
-        <v>14439600.199999999</v>
+        <v>14494256.199999999</v>
       </c>
       <c r="G32" s="204">
         <f t="shared" si="19"/>
-        <v>7418164.7502917144</v>
+        <v>7511943.7502917144</v>
       </c>
       <c r="H32" s="151"/>
       <c r="I32" s="151"/>
@@ -5943,23 +6118,23 @@
       </c>
       <c r="C33" s="202">
         <f>C32/C7</f>
-        <v>-33.951024713783397</v>
+        <v>-34.998826949472452</v>
       </c>
       <c r="D33" s="202">
         <f t="shared" ref="D33:G33" si="20">D32/D7</f>
-        <v>-33.734505713628337</v>
+        <v>-32.136326927631011</v>
       </c>
       <c r="E33" s="202">
         <f t="shared" si="20"/>
-        <v>-739.56600799456965</v>
+        <v>-543.98487337834149</v>
       </c>
       <c r="F33" s="202">
         <f t="shared" si="20"/>
-        <v>230.68296509305853</v>
+        <v>242.7285902229701</v>
       </c>
       <c r="G33" s="203">
         <f t="shared" si="20"/>
-        <v>54.718335548364053</v>
+        <v>55.297879439206071</v>
       </c>
       <c r="H33" s="151"/>
       <c r="I33" s="151"/>
@@ -5974,23 +6149,23 @@
       </c>
       <c r="C34" s="202">
         <f>C32/C8</f>
-        <v>-57.303390121996671</v>
+        <v>-59.738160139631091</v>
       </c>
       <c r="D34" s="202">
         <f t="shared" ref="D34:G34" si="21">D32/D8</f>
-        <v>-66.799782654155194</v>
+        <v>-60.346925357137806</v>
       </c>
       <c r="E34" s="202">
         <f t="shared" si="21"/>
-        <v>440.58801591858997</v>
+        <v>548.6006355891476</v>
       </c>
       <c r="F34" s="202">
         <f t="shared" si="21"/>
-        <v>121.99812255507969</v>
+        <v>125.09632613326808</v>
       </c>
       <c r="G34" s="203">
         <f t="shared" si="21"/>
-        <v>51.75320555285829</v>
+        <v>52.328130804201706</v>
       </c>
       <c r="H34" s="151"/>
       <c r="I34" s="151"/>
@@ -6006,10 +6181,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="222" t="s">
+      <c r="B37" s="224" t="s">
         <v>338</v>
       </c>
-      <c r="C37" s="222"/>
+      <c r="C37" s="224"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -6018,7 +6193,7 @@
       </c>
       <c r="C38" s="108">
         <f>L7</f>
-        <v>478662.87556607369</v>
+        <v>466436.2555660737</v>
       </c>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
@@ -6027,7 +6202,7 @@
       </c>
       <c r="C39" s="159">
         <f>WACC!C20</f>
-        <v>8.8919999999999999E-2</v>
+        <v>9.0248593502360752E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -6053,7 +6228,7 @@
       </c>
       <c r="C42" s="20">
         <f>(C38*C40)-G30+G31</f>
-        <v>13107038.889151841</v>
+        <v>12707594.389151843</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -6062,7 +6237,7 @@
       </c>
       <c r="C43" s="20">
         <f>C42/C41</f>
-        <v>234.05215328350812</v>
+        <v>226.91928016602373</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -6071,14 +6246,14 @@
       </c>
       <c r="C44" s="173">
         <f>C43/(1+C48)^5</f>
-        <v>152.8736970508956</v>
+        <v>147.31389818040671</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="224" t="s">
         <v>288</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="224"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -6095,7 +6270,7 @@
       </c>
       <c r="C48" s="159">
         <f>WACC!C20</f>
-        <v>8.8919999999999999E-2</v>
+        <v>9.0248593502360752E-2</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -6130,14 +6305,14 @@
       </c>
       <c r="C52" s="173">
         <f>C51/(1+C48)^5</f>
-        <v>145.00974757319909</v>
+        <v>144.1283429696183</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="222" t="s">
+      <c r="B54" s="224" t="s">
         <v>342</v>
       </c>
-      <c r="C54" s="222"/>
+      <c r="C54" s="224"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -6145,7 +6320,7 @@
       </c>
       <c r="C55" s="108">
         <f>L8</f>
-        <v>536271.06683444814</v>
+        <v>526612.03703444824</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
@@ -6154,7 +6329,7 @@
       </c>
       <c r="C56" s="159">
         <f>WACC!C20</f>
-        <v>8.8919999999999999E-2</v>
+        <v>9.0248593502360752E-2</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6162,7 +6337,7 @@
         <v>344</v>
       </c>
       <c r="C57" s="138">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
@@ -6180,7 +6355,7 @@
       </c>
       <c r="C59" s="20">
         <f>(C55*C57)-G30+G31</f>
-        <v>11865888.336688962</v>
+        <v>12632152.814757861</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -6189,7 +6364,7 @@
       </c>
       <c r="C60" s="20">
         <f>C59/C58</f>
-        <v>211.88895060976137</v>
+        <v>225.57212135438522</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -6198,7 +6373,7 @@
       </c>
       <c r="C61" s="173">
         <f>C60/(1+C56)^5</f>
-        <v>138.39756135339633</v>
+        <v>146.43933513814184</v>
       </c>
     </row>
   </sheetData>
@@ -6247,10 +6422,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="222" t="s">
+      <c r="B4" s="224" t="s">
         <v>296</v>
       </c>
-      <c r="C4" s="222"/>
+      <c r="C4" s="224"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -6259,7 +6434,7 @@
       </c>
       <c r="C5" s="188">
         <f>DCF!C26</f>
-        <v>153.52833543569611</v>
+        <v>148.12934128925642</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6268,7 +6443,7 @@
       </c>
       <c r="C6" s="188">
         <f>Multiples!C44</f>
-        <v>152.8736970508956</v>
+        <v>147.31389818040671</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6277,7 +6452,7 @@
       </c>
       <c r="C7" s="188">
         <f>Multiples!C52</f>
-        <v>145.00974757319909</v>
+        <v>144.1283429696183</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6286,7 +6461,7 @@
       </c>
       <c r="C8" s="188">
         <f>Multiples!C61</f>
-        <v>138.39756135339633</v>
+        <v>146.43933513814184</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6295,7 +6470,7 @@
       </c>
       <c r="C9" s="173">
         <f>AVERAGE(C5:C8)</f>
-        <v>147.45233535329677</v>
+        <v>146.50272939435581</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6304,7 +6479,7 @@
       </c>
       <c r="C10" s="35">
         <f>Overview!C3</f>
-        <v>107.99</v>
+        <v>112.06</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6313,7 +6488,7 @@
       </c>
       <c r="C11" s="91">
         <f>(C9-C10)/C10</f>
-        <v>0.3654258297369829</v>
+        <v>0.30735971260356781</v>
       </c>
     </row>
   </sheetData>
@@ -6357,60 +6532,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="104"/>
-      <c r="C3" s="222" t="s">
+      <c r="C3" s="224" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="222"/>
-      <c r="E3" s="222"/>
-      <c r="F3" s="222"/>
-      <c r="G3" s="229"/>
-      <c r="H3" s="230" t="s">
+      <c r="D3" s="224"/>
+      <c r="E3" s="224"/>
+      <c r="F3" s="224"/>
+      <c r="G3" s="225"/>
+      <c r="H3" s="226" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="222"/>
-      <c r="J3" s="222"/>
-      <c r="K3" s="222"/>
-      <c r="L3" s="222"/>
-      <c r="P3" s="231"/>
-      <c r="Q3" s="231"/>
-      <c r="R3" s="231"/>
-      <c r="S3" s="231"/>
-      <c r="T3" s="231"/>
-      <c r="U3" s="231"/>
-      <c r="V3" s="231"/>
-      <c r="W3" s="231"/>
-      <c r="X3" s="231"/>
-      <c r="Y3" s="231"/>
-      <c r="Z3" s="231"/>
+      <c r="I3" s="224"/>
+      <c r="J3" s="224"/>
+      <c r="K3" s="224"/>
+      <c r="L3" s="224"/>
+      <c r="P3" s="227"/>
+      <c r="Q3" s="227"/>
+      <c r="R3" s="227"/>
+      <c r="S3" s="227"/>
+      <c r="T3" s="227"/>
+      <c r="U3" s="227"/>
+      <c r="V3" s="227"/>
+      <c r="W3" s="227"/>
+      <c r="X3" s="227"/>
+      <c r="Y3" s="227"/>
+      <c r="Z3" s="227"/>
       <c r="AB3" s="143"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="109"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="226" t="s">
+      <c r="C5" s="223" t="s">
         <v>273</v>
       </c>
-      <c r="D5" s="226"/>
-      <c r="E5" s="226"/>
-      <c r="F5" s="226"/>
-      <c r="G5" s="226"/>
-      <c r="H5" s="226"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="226"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="226"/>
-      <c r="P5" s="231"/>
-      <c r="Q5" s="231"/>
-      <c r="R5" s="231"/>
-      <c r="S5" s="231"/>
-      <c r="T5" s="231"/>
-      <c r="U5" s="231"/>
-      <c r="V5" s="231"/>
-      <c r="W5" s="231"/>
-      <c r="X5" s="231"/>
-      <c r="Y5" s="231"/>
-      <c r="Z5" s="231"/>
+      <c r="D5" s="223"/>
+      <c r="E5" s="223"/>
+      <c r="F5" s="223"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="223"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="223"/>
+      <c r="K5" s="223"/>
+      <c r="L5" s="223"/>
+      <c r="P5" s="227"/>
+      <c r="Q5" s="227"/>
+      <c r="R5" s="227"/>
+      <c r="S5" s="227"/>
+      <c r="T5" s="227"/>
+      <c r="U5" s="227"/>
+      <c r="V5" s="227"/>
+      <c r="W5" s="227"/>
+      <c r="X5" s="227"/>
+      <c r="Y5" s="227"/>
+      <c r="Z5" s="227"/>
       <c r="AB5" s="144"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -6476,44 +6651,44 @@
         <v>236</v>
       </c>
       <c r="C7" s="153">
-        <f>'FCF &amp; Other'!C31</f>
-        <v>-35552.855348744117</v>
+        <f>'FCF &amp; Other'!C33</f>
+        <v>-34591.342203542481</v>
       </c>
       <c r="D7" s="153">
-        <f>'FCF &amp; Other'!D31</f>
-        <v>-32924.075687291086</v>
+        <f>'FCF &amp; Other'!D33</f>
+        <v>-36834.090334265638</v>
       </c>
       <c r="E7" s="153">
-        <f>'FCF &amp; Other'!E31</f>
-        <v>22256.405861506442</v>
+        <f>'FCF &amp; Other'!E33</f>
+        <v>17912.847821342184</v>
       </c>
       <c r="F7" s="153">
-        <f>'FCF &amp; Other'!F31</f>
-        <v>118359.20010556566</v>
+        <f>'FCF &amp; Other'!F33</f>
+        <v>115864.76316305983</v>
       </c>
       <c r="G7" s="155">
-        <f>'FCF &amp; Other'!G31</f>
-        <v>143337.29999999999</v>
+        <f>'FCF &amp; Other'!G33</f>
+        <v>143554.5974</v>
       </c>
       <c r="H7" s="154">
         <f>G7*(1+$C$17)</f>
-        <v>177738.25199999998</v>
+        <v>178007.70077599998</v>
       </c>
       <c r="I7" s="154">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>220395.43247999996</v>
+        <v>220729.54896223999</v>
       </c>
       <c r="J7" s="154">
         <f t="shared" si="0"/>
-        <v>273290.33627519995</v>
+        <v>273704.64071317756</v>
       </c>
       <c r="K7" s="154">
         <f t="shared" si="0"/>
-        <v>338880.01698124793</v>
+        <v>339393.7544843402</v>
       </c>
       <c r="L7" s="154">
         <f t="shared" si="0"/>
-        <v>420211.22105674742</v>
+        <v>420848.25556058186</v>
       </c>
       <c r="N7" s="93"/>
       <c r="O7" s="7"/>
@@ -6545,7 +6720,7 @@
       <c r="K8" s="151"/>
       <c r="L8" s="154">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>6219028.5182513408</v>
+        <v>6110659.2925218893</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="7"/>
@@ -6599,23 +6774,23 @@
       <c r="G10" s="171"/>
       <c r="H10" s="154">
         <f>H7/(1+$C$21)^H9</f>
-        <v>163224.34338610733</v>
+        <v>163272.58006741427</v>
       </c>
       <c r="I10" s="154">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>185870.57432940265</v>
+        <v>185698.9318676478</v>
       </c>
       <c r="J10" s="154">
         <f t="shared" si="1"/>
-        <v>211658.81071929922</v>
+        <v>211205.66161536137</v>
       </c>
       <c r="K10" s="154">
         <f t="shared" si="1"/>
-        <v>241024.98373795234</v>
+        <v>240215.87550204995</v>
       </c>
       <c r="L10" s="154">
         <f t="shared" si="1"/>
-        <v>274465.50695648981</v>
+        <v>273210.79559081036</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -6634,15 +6809,15 @@
       <c r="K11" s="151"/>
       <c r="L11" s="154">
         <f>L8/(1+C21)^L9</f>
-        <v>4062025.7849045219</v>
+        <v>3966983.5025702193</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="232" t="s">
+      <c r="B14" s="233" t="s">
         <v>350</v>
       </c>
-      <c r="C14" s="233"/>
+      <c r="C14" s="234"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="207" t="s">
@@ -6650,7 +6825,7 @@
       </c>
       <c r="C15" s="208">
         <f>Overview!C3</f>
-        <v>107.99</v>
+        <v>112.06</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6659,7 +6834,7 @@
       </c>
       <c r="C16" s="208">
         <f>C36</f>
-        <v>105.12158430045085</v>
+        <v>103.1224164692768</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6669,20 +6844,20 @@
       <c r="C17" s="210">
         <v>0.24</v>
       </c>
-      <c r="E17" s="234" t="s">
+      <c r="E17" s="235" t="s">
         <v>354</v>
       </c>
-      <c r="F17" s="234"/>
-      <c r="G17" s="234"/>
-      <c r="H17" s="234"/>
-      <c r="I17" s="234"/>
+      <c r="F17" s="235"/>
+      <c r="G17" s="235"/>
+      <c r="H17" s="235"/>
+      <c r="I17" s="235"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="232" t="s">
+      <c r="B19" s="233" t="s">
         <v>274</v>
       </c>
-      <c r="C19" s="233"/>
+      <c r="C19" s="234"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="211" t="s">
@@ -6698,7 +6873,7 @@
       </c>
       <c r="C21" s="213">
         <f>WACC!C20</f>
-        <v>8.8919999999999999E-2</v>
+        <v>9.0248593502360752E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6716,7 +6891,7 @@
       </c>
       <c r="C23" s="214">
         <f>C15*C22</f>
-        <v>5276570.5537718786</v>
+        <v>5475437.5058401404</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6724,7 +6899,7 @@
         <v>241</v>
       </c>
       <c r="C24" s="214">
-        <f>Statements!S23</f>
+        <f>'Statement Q'!N159</f>
         <v>1251610</v>
       </c>
     </row>
@@ -6733,7 +6908,8 @@
         <v>237</v>
       </c>
       <c r="C25" s="214">
-        <v>0</v>
+        <f>'Statement Q'!N158</f>
+        <v>91873</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6742,15 +6918,15 @@
       </c>
       <c r="C26" s="215">
         <f>C23+C25-C24</f>
-        <v>4024960.5537718786</v>
+        <v>4315700.5058401404</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="232" t="s">
+      <c r="B28" s="233" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="233"/>
+      <c r="C28" s="234"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="211" t="s">
@@ -6758,7 +6934,7 @@
       </c>
       <c r="C29" s="214">
         <f>SUM(H10:L10)</f>
-        <v>1076244.2191292513</v>
+        <v>1073603.8446432836</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6767,7 +6943,7 @@
       </c>
       <c r="C30" s="214">
         <f>L11</f>
-        <v>4062025.7849045219</v>
+        <v>3966983.5025702193</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6776,7 +6952,7 @@
       </c>
       <c r="C31" s="217">
         <f>C29+C30</f>
-        <v>5138270.0040337732</v>
+        <v>5040587.347213503</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6803,7 +6979,7 @@
       </c>
       <c r="C34" s="217">
         <f>C31+C32-C33</f>
-        <v>5136415.0040337732</v>
+        <v>5038732.347213503</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6821,22 +6997,22 @@
       </c>
       <c r="C36" s="220">
         <f>C34/C35</f>
-        <v>105.12158430045085</v>
+        <v>103.1224164692768</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="226" t="s">
+      <c r="C39" s="223" t="s">
         <v>356</v>
       </c>
-      <c r="D39" s="226"/>
-      <c r="E39" s="226"/>
-      <c r="F39" s="226"/>
-      <c r="G39" s="226"/>
-      <c r="H39" s="226"/>
-      <c r="I39" s="226"/>
-      <c r="J39" s="226"/>
-      <c r="K39" s="226"/>
-      <c r="L39" s="226"/>
+      <c r="D39" s="223"/>
+      <c r="E39" s="223"/>
+      <c r="F39" s="223"/>
+      <c r="G39" s="223"/>
+      <c r="H39" s="223"/>
+      <c r="I39" s="223"/>
+      <c r="J39" s="223"/>
+      <c r="K39" s="223"/>
+      <c r="L39" s="223"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="62">
@@ -6886,43 +7062,43 @@
       </c>
       <c r="C41" s="153">
         <f>C7</f>
-        <v>-35552.855348744117</v>
+        <v>-34591.342203542481</v>
       </c>
       <c r="D41" s="153">
         <f t="shared" si="2"/>
-        <v>-32924.075687291086</v>
+        <v>-36834.090334265638</v>
       </c>
       <c r="E41" s="153">
         <f t="shared" si="2"/>
-        <v>22256.405861506442</v>
+        <v>17912.847821342184</v>
       </c>
       <c r="F41" s="153">
         <f t="shared" si="2"/>
-        <v>118359.20010556566</v>
+        <v>115864.76316305983</v>
       </c>
       <c r="G41" s="155">
         <f t="shared" si="2"/>
-        <v>143337.29999999999</v>
+        <v>143554.5974</v>
       </c>
       <c r="H41" s="195">
         <f t="shared" si="2"/>
-        <v>177738.25199999998</v>
+        <v>178007.70077599998</v>
       </c>
       <c r="I41" s="195">
         <f t="shared" si="2"/>
-        <v>220395.43247999996</v>
+        <v>220729.54896223999</v>
       </c>
       <c r="J41" s="195">
         <f t="shared" si="2"/>
-        <v>273290.33627519995</v>
+        <v>273704.64071317756</v>
       </c>
       <c r="K41" s="195">
         <f t="shared" si="2"/>
-        <v>338880.01698124793</v>
+        <v>339393.7544843402</v>
       </c>
       <c r="L41" s="195">
         <f t="shared" si="2"/>
-        <v>420211.22105674742</v>
+        <v>420848.25556058186</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -6951,23 +7127,23 @@
       </c>
       <c r="H42" s="195">
         <f>H41/H43</f>
-        <v>177738.25199999998</v>
+        <v>178007.70077599998</v>
       </c>
       <c r="I42" s="195">
         <f t="shared" ref="I42:L42" si="3">I41/I43</f>
-        <v>220395.43247999996</v>
+        <v>220729.54896223999</v>
       </c>
       <c r="J42" s="195">
         <f t="shared" si="3"/>
-        <v>287674.03818442102</v>
+        <v>288110.1481191343</v>
       </c>
       <c r="K42" s="195">
         <f t="shared" si="3"/>
-        <v>376533.35220138659</v>
+        <v>377104.17164926691</v>
       </c>
       <c r="L42" s="195">
         <f t="shared" si="3"/>
-        <v>525264.0263209343</v>
+        <v>526060.31945072731</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -6976,23 +7152,23 @@
       </c>
       <c r="C43" s="116">
         <f>C41/C42</f>
-        <v>-0.32632566933835205</v>
+        <v>-0.31750031853016075</v>
       </c>
       <c r="D43" s="116">
         <f t="shared" ref="D43:G43" si="4">D41/D42</f>
-        <v>-0.27566060506619461</v>
+        <v>-0.30839765176842721</v>
       </c>
       <c r="E43" s="116">
         <f t="shared" si="4"/>
-        <v>0.19471750782151023</v>
+        <v>0.15671645761053871</v>
       </c>
       <c r="F43" s="116">
         <f t="shared" si="4"/>
-        <v>0.96058304202023814</v>
+        <v>0.94033861806145169</v>
       </c>
       <c r="G43" s="117">
         <f t="shared" si="4"/>
-        <v>1.0773190529875987</v>
+        <v>1.0789522540398346</v>
       </c>
       <c r="H43" s="194">
         <v>1</v>
@@ -7036,23 +7212,23 @@
       </c>
       <c r="H44" s="195">
         <f>H41/H45</f>
-        <v>444345.62999999995</v>
+        <v>445019.25193999993</v>
       </c>
       <c r="I44" s="195">
         <f t="shared" ref="I44:L44" si="5">I41/I45</f>
-        <v>550988.5811999999</v>
+        <v>551823.87240559992</v>
       </c>
       <c r="J44" s="195">
         <f t="shared" si="5"/>
-        <v>780829.53221485706</v>
+        <v>782013.25918050739</v>
       </c>
       <c r="K44" s="195">
         <f t="shared" si="5"/>
-        <v>1129600.0566041598</v>
+        <v>1131312.5149478007</v>
       </c>
       <c r="L44" s="195">
         <f t="shared" si="5"/>
-        <v>1400704.0701891582</v>
+        <v>1402827.5185352729</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -7061,23 +7237,23 @@
       </c>
       <c r="C45" s="116">
         <f>C41/C44</f>
-        <v>-9.7187542811690314E-2</v>
+        <v>-9.4559143515863073E-2</v>
       </c>
       <c r="D45" s="116">
         <f t="shared" ref="D45:G45" si="6">D41/D44</f>
-        <v>-8.3494136067667243E-2</v>
+        <v>-9.3409776465951291E-2</v>
       </c>
       <c r="E45" s="116">
         <f t="shared" si="6"/>
-        <v>5.8067510759634323E-2</v>
+        <v>4.6735060911181459E-2</v>
       </c>
       <c r="F45" s="116">
         <f t="shared" si="6"/>
-        <v>0.30268185739272868</v>
+        <v>0.29630279428455208</v>
       </c>
       <c r="G45" s="117">
         <f t="shared" si="6"/>
-        <v>0.34442751723491627</v>
+        <v>0.34494966467304722</v>
       </c>
       <c r="H45" s="194">
         <v>0.4</v>
@@ -7102,19 +7278,19 @@
       <c r="C46" s="151"/>
       <c r="D46" s="116">
         <f>D41/C41-1</f>
-        <v>-7.3940043230476871E-2</v>
+        <v>6.4835533629379549E-2</v>
       </c>
       <c r="E46" s="116">
         <f t="shared" ref="E46:L47" si="7">E41/D41-1</f>
-        <v>-1.6759918204810094</v>
+        <v>-1.4863116656006679</v>
       </c>
       <c r="F46" s="116">
         <f t="shared" si="7"/>
-        <v>4.3179835433480198</v>
+        <v>5.4682491761590954</v>
       </c>
       <c r="G46" s="117">
         <f t="shared" si="7"/>
-        <v>0.21103640335652929</v>
+        <v>0.23898408352133305</v>
       </c>
       <c r="H46" s="221">
         <f t="shared" si="7"/>
@@ -7160,7 +7336,7 @@
       </c>
       <c r="H47" s="221">
         <f t="shared" si="7"/>
-        <v>0.33587562570462226</v>
+        <v>0.33790079500939485</v>
       </c>
       <c r="I47" s="221">
         <f t="shared" si="7"/>
@@ -7172,7 +7348,7 @@
       </c>
       <c r="K47" s="221">
         <f t="shared" si="7"/>
-        <v>0.30888888888888877</v>
+        <v>0.30888888888888899</v>
       </c>
       <c r="L47" s="221">
         <f t="shared" si="7"/>
@@ -7202,7 +7378,7 @@
       </c>
       <c r="H48" s="221">
         <f t="shared" si="8"/>
-        <v>6.7725303428240347E-2</v>
+        <v>6.9343960486446088E-2</v>
       </c>
       <c r="I48" s="221">
         <f t="shared" si="8"/>
@@ -7259,7 +7435,7 @@
       </c>
       <c r="K49" s="221">
         <f t="shared" si="9"/>
-        <v>0.33333333333333331</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="L49" s="221">
         <f t="shared" si="9"/>
@@ -7268,17 +7444,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7309,7 +7485,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="A1:L169"/>
+  <dimension ref="A1:O181"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="2" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="1" customWidth="1"/>
@@ -10871,165 +11047,162 @@
       <c r="K123" s="27"/>
       <c r="L123" s="27"/>
     </row>
-    <row r="124" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B125" s="1"/>
-    </row>
-    <row r="126" spans="1:12" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="4"/>
-      <c r="B126" s="15" t="s">
+    <row r="124" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B124" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="C124" s="27">
+        <v>2038</v>
+      </c>
+      <c r="D124" s="27">
+        <v>3113</v>
+      </c>
+      <c r="E124" s="27">
+        <v>7264</v>
+      </c>
+      <c r="F124" s="27">
+        <v>7759</v>
+      </c>
+      <c r="G124" s="27">
+        <v>10533</v>
+      </c>
+      <c r="H124" s="27">
+        <v>12854</v>
+      </c>
+      <c r="I124" s="27"/>
+      <c r="J124" s="27"/>
+      <c r="K124" s="27"/>
+      <c r="L124" s="27"/>
+    </row>
+    <row r="125" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B126" s="1"/>
+    </row>
+    <row r="127" spans="1:12" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="4"/>
+      <c r="B127" s="15" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="127" spans="1:12" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="7"/>
-      <c r="B127" s="17" t="s">
+    <row r="128" spans="1:12" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="7"/>
+      <c r="B128" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C127" s="81"/>
-      <c r="D127" s="76">
-        <f t="shared" ref="D127:H131" si="27">IF(C5=0,
+      <c r="C128" s="81"/>
+      <c r="D128" s="76">
+        <f t="shared" ref="D128:H132" si="27">IF(C5=0,
 IF(D5=0,0,IF(D5&gt;0,1,-1)),
 (D5-C5)/ABS(C5)
 )</f>
         <v>0.5508856125074213</v>
       </c>
-      <c r="E127" s="76">
+      <c r="E128" s="76">
         <f t="shared" si="27"/>
         <v>0.47343004801173977</v>
       </c>
-      <c r="F127" s="76">
+      <c r="F128" s="76">
         <f t="shared" si="27"/>
         <v>0.43739157498748293</v>
       </c>
-      <c r="G127" s="76">
+      <c r="G128" s="76">
         <f t="shared" si="27"/>
         <v>0.40841898743948984</v>
       </c>
-      <c r="H127" s="76">
+      <c r="H128" s="76">
         <f t="shared" si="27"/>
         <v>0.38710656342577243</v>
       </c>
-      <c r="I127" s="76"/>
-      <c r="J127" s="76"/>
-      <c r="K127" s="76"/>
-      <c r="L127" s="76"/>
-    </row>
-    <row r="128" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B128" s="9" t="s">
+      <c r="I128" s="76"/>
+      <c r="J128" s="76"/>
+      <c r="K128" s="76"/>
+      <c r="L128" s="76"/>
+    </row>
+    <row r="129" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B129" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C128" s="80"/>
-      <c r="D128" s="75">
+      <c r="C129" s="80"/>
+      <c r="D129" s="75">
         <f t="shared" si="27"/>
         <v>0.5044686541848783</v>
       </c>
-      <c r="E128" s="75">
+      <c r="E129" s="75">
         <f t="shared" si="27"/>
         <v>0.43715491573439713</v>
       </c>
-      <c r="F128" s="75">
+      <c r="F129" s="75">
         <f t="shared" si="27"/>
         <v>0.42918204584083436</v>
       </c>
-      <c r="G128" s="75">
+      <c r="G129" s="75">
         <f t="shared" si="27"/>
         <v>0.43306006122233559</v>
       </c>
-      <c r="H128" s="75">
+      <c r="H129" s="75">
         <f t="shared" si="27"/>
         <v>0.41487392275774021</v>
       </c>
-      <c r="I128" s="75"/>
-      <c r="J128" s="75"/>
-      <c r="K128" s="75"/>
-      <c r="L128" s="75"/>
-    </row>
-    <row r="129" spans="1:12" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="7"/>
-      <c r="B129" s="17" t="s">
+      <c r="I129" s="75"/>
+      <c r="J129" s="75"/>
+      <c r="K129" s="75"/>
+      <c r="L129" s="75"/>
+    </row>
+    <row r="130" spans="1:12" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="7"/>
+      <c r="B130" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C129" s="81"/>
-      <c r="D129" s="76">
+      <c r="C130" s="81"/>
+      <c r="D130" s="76">
         <f t="shared" si="27"/>
         <v>0.56933341399545412</v>
       </c>
-      <c r="E129" s="76">
+      <c r="E130" s="76">
         <f t="shared" si="27"/>
         <v>0.48725121980769442</v>
       </c>
-      <c r="F129" s="76">
+      <c r="F130" s="76">
         <f t="shared" si="27"/>
         <v>0.44041412405948221</v>
       </c>
-      <c r="G129" s="76">
+      <c r="G130" s="76">
         <f t="shared" si="27"/>
         <v>0.39941748670964822</v>
       </c>
-      <c r="H129" s="76">
+      <c r="H130" s="76">
         <f t="shared" si="27"/>
         <v>0.37671916073176959</v>
       </c>
-      <c r="I129" s="76"/>
-      <c r="J129" s="76"/>
-      <c r="K129" s="76"/>
-      <c r="L129" s="76"/>
-    </row>
-    <row r="130" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="9" t="s">
+      <c r="I130" s="76"/>
+      <c r="J130" s="76"/>
+      <c r="K130" s="76"/>
+      <c r="L130" s="76"/>
+    </row>
+    <row r="131" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B131" s="9" t="s">
         <v>9</v>
-      </c>
-      <c r="C130" s="80"/>
-      <c r="D130" s="75">
-        <f t="shared" si="27"/>
-        <v>0.95822646348823171</v>
-      </c>
-      <c r="E130" s="75">
-        <f t="shared" si="27"/>
-        <v>0.4489035277801855</v>
-      </c>
-      <c r="F130" s="75">
-        <f t="shared" si="27"/>
-        <v>0.29185610592645767</v>
-      </c>
-      <c r="G130" s="75">
-        <f t="shared" si="27"/>
-        <v>0.2106795916687248</v>
-      </c>
-      <c r="H130" s="75">
-        <f t="shared" si="27"/>
-        <v>0.30185126945405399</v>
-      </c>
-      <c r="I130" s="75"/>
-      <c r="J130" s="75"/>
-      <c r="K130" s="75"/>
-      <c r="L130" s="75"/>
-    </row>
-    <row r="131" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="12" t="s">
-        <v>10</v>
       </c>
       <c r="C131" s="80"/>
       <c r="D131" s="75">
         <f t="shared" si="27"/>
-        <v>0.69139296229597236</v>
+        <v>0.95822646348823171</v>
       </c>
       <c r="E131" s="75">
         <f t="shared" si="27"/>
-        <v>0.13177285786716242</v>
+        <v>0.4489035277801855</v>
       </c>
       <c r="F131" s="75">
         <f t="shared" si="27"/>
-        <v>0.13172159421804769</v>
+        <v>0.29185610592645767</v>
       </c>
       <c r="G131" s="75">
         <f t="shared" si="27"/>
-        <v>0.19404127302475327</v>
+        <v>0.2106795916687248</v>
       </c>
       <c r="H131" s="75">
         <f t="shared" si="27"/>
-        <v>0.38878820695294714</v>
+        <v>0.30185126945405399</v>
       </c>
       <c r="I131" s="75"/>
       <c r="J131" s="75"/>
@@ -11038,761 +11211,1039 @@
     </row>
     <row r="132" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B132" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C132" s="80"/>
       <c r="D132" s="75">
-        <f t="shared" ref="D132:H133" si="28">IF(C11=0,
+        <f t="shared" si="27"/>
+        <v>0.69139296229597236</v>
+      </c>
+      <c r="E132" s="75">
+        <f t="shared" si="27"/>
+        <v>0.13177285786716242</v>
+      </c>
+      <c r="F132" s="75">
+        <f t="shared" si="27"/>
+        <v>0.13172159421804769</v>
+      </c>
+      <c r="G132" s="75">
+        <f t="shared" si="27"/>
+        <v>0.19404127302475327</v>
+      </c>
+      <c r="H132" s="75">
+        <f t="shared" si="27"/>
+        <v>0.38878820695294714</v>
+      </c>
+      <c r="I132" s="75"/>
+      <c r="J132" s="75"/>
+      <c r="K132" s="75"/>
+      <c r="L132" s="75"/>
+    </row>
+    <row r="133" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B133" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" s="80"/>
+      <c r="D133" s="75">
+        <f t="shared" ref="D133:H134" si="28">IF(C11=0,
 IF(D11=0,0,IF(D11&gt;0,1,-1)),
 (D11-C11)/ABS(C11)
 )</f>
         <v>0.83414060127543277</v>
       </c>
-      <c r="E132" s="75">
+      <c r="E133" s="75">
         <f t="shared" si="28"/>
         <v>0.38770163042803391</v>
       </c>
-      <c r="F132" s="75">
+      <c r="F133" s="75">
         <f t="shared" si="28"/>
         <v>0.19985742366349599</v>
       </c>
-      <c r="G132" s="75">
+      <c r="G133" s="75">
         <f t="shared" si="28"/>
         <v>0.19768410219184962</v>
       </c>
-      <c r="H132" s="75">
+      <c r="H133" s="75">
         <f t="shared" si="28"/>
         <v>0.27419549009514638</v>
       </c>
-      <c r="I132" s="75"/>
-      <c r="J132" s="75"/>
-      <c r="K132" s="75"/>
-      <c r="L132" s="75"/>
-    </row>
-    <row r="133" spans="1:12" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="7"/>
-      <c r="B133" s="17" t="s">
+      <c r="I133" s="75"/>
+      <c r="J133" s="75"/>
+      <c r="K133" s="75"/>
+      <c r="L133" s="75"/>
+    </row>
+    <row r="134" spans="1:12" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="7"/>
+      <c r="B134" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C133" s="81"/>
-      <c r="D133" s="76">
+      <c r="C134" s="81"/>
+      <c r="D134" s="76">
         <f t="shared" si="28"/>
         <v>-2.7478608456686029</v>
       </c>
-      <c r="E133" s="76">
+      <c r="E134" s="76">
         <f t="shared" si="28"/>
         <v>-8.6456580065659011E-2</v>
       </c>
-      <c r="F133" s="76">
+      <c r="F134" s="76">
         <f t="shared" si="28"/>
         <v>0.79662550809111132</v>
       </c>
-      <c r="G133" s="76">
+      <c r="G134" s="76">
         <f t="shared" si="28"/>
         <v>5.7209442642733235</v>
       </c>
-      <c r="H133" s="76">
+      <c r="H134" s="76">
         <f t="shared" si="28"/>
         <v>1.1658279415288761</v>
       </c>
-      <c r="I133" s="76"/>
-      <c r="J133" s="76"/>
-      <c r="K133" s="76"/>
-      <c r="L133" s="76"/>
-    </row>
-    <row r="134" spans="1:12" s="77" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="7"/>
-      <c r="B134" s="78" t="s">
+      <c r="I134" s="76"/>
+      <c r="J134" s="76"/>
+      <c r="K134" s="76"/>
+      <c r="L134" s="76"/>
+    </row>
+    <row r="135" spans="1:12" s="77" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="7"/>
+      <c r="B135" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C134" s="81"/>
-      <c r="D134" s="79">
+      <c r="C135" s="81"/>
+      <c r="D135" s="79">
         <f>IF(C16=0,
 IF(D16=0,0,IF(D16&gt;0,1,-1)),
 (D16-C16)/ABS(C16)
 )</f>
         <v>-2.8170359052711995</v>
       </c>
-      <c r="E134" s="79">
+      <c r="E135" s="79">
         <f>IF(D16=0,
 IF(E16=0,0,IF(E16&gt;0,1,-1)),
 (E16-D16)/ABS(D16)
 )</f>
         <v>1.9779512325294373</v>
       </c>
-      <c r="F134" s="79">
+      <c r="F135" s="79">
         <f>IF(E16=0,
 IF(F16=0,0,IF(F16&gt;0,1,-1)),
 (F16-E16)/ABS(E16)
 )</f>
         <v>-0.69682447643086154</v>
       </c>
-      <c r="G134" s="79">
+      <c r="G135" s="79">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>4.7549642796872362</v>
       </c>
-      <c r="H134" s="79">
+      <c r="H135" s="79">
         <f>IF(G16=0,
 IF(H16=0,0,IF(H16&gt;0,1,-1)),
 (H16-G16)/ABS(G16)
 )</f>
         <v>0.78298438019275507</v>
       </c>
-      <c r="I134" s="79"/>
-      <c r="J134" s="79"/>
-      <c r="K134" s="79"/>
-      <c r="L134" s="79"/>
-    </row>
-    <row r="135" spans="1:12" s="77" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="7"/>
-      <c r="B135" s="78" t="s">
+      <c r="I135" s="79"/>
+      <c r="J135" s="79"/>
+      <c r="K135" s="79"/>
+      <c r="L135" s="79"/>
+    </row>
+    <row r="136" spans="1:12" s="77" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="7"/>
+      <c r="B136" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="C135" s="81"/>
-      <c r="D135" s="79">
+      <c r="C136" s="81"/>
+      <c r="D136" s="79">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.8118027383367141</v>
       </c>
-      <c r="E135" s="79">
+      <c r="E136" s="79">
         <f>IF(D18=0,
 IF(E18=0,0,IF(E18&gt;0,1,-1)),
 (E18-D18)/ABS(D18)
 )</f>
         <v>9.3290097281117489E-3</v>
       </c>
-      <c r="F135" s="79">
+      <c r="F136" s="79">
         <f>IF(E18=0,
 IF(F18=0,0,IF(F18&gt;0,1,-1)),
 (F18-E18)/ABS(E18)
 )</f>
         <v>1.2696981904857825</v>
       </c>
-      <c r="G135" s="79">
+      <c r="G136" s="79">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>4.512790191074874</v>
       </c>
-      <c r="H135" s="79">
+      <c r="H136" s="79">
         <f>IF(G18=0,
 IF(H18=0,0,IF(H18&gt;0,1,-1)),
 (H18-G18)/ABS(G18)
 )</f>
         <v>3.6747916995958181</v>
       </c>
-      <c r="I135" s="79"/>
-      <c r="J135" s="79"/>
-      <c r="K135" s="79"/>
-      <c r="L135" s="79"/>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B136" s="1"/>
-    </row>
-    <row r="137" spans="1:12" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="4"/>
-      <c r="B137" s="15" t="s">
+      <c r="I136" s="79"/>
+      <c r="J136" s="79"/>
+      <c r="K136" s="79"/>
+      <c r="L136" s="79"/>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B137" s="1"/>
+    </row>
+    <row r="138" spans="1:12" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="4"/>
+      <c r="B138" s="15" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="138" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B138" s="9" t="s">
+    <row r="139" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B139" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C138" s="75">
-        <f t="shared" ref="C138:H138" si="29">C7/C5</f>
+      <c r="C139" s="75">
+        <f t="shared" ref="C139:H139" si="29">C7/C5</f>
         <v>0.71559593310904412</v>
       </c>
-      <c r="D138" s="75">
+      <c r="D139" s="75">
         <f t="shared" si="29"/>
         <v>0.72410795463608379</v>
       </c>
-      <c r="E138" s="75">
+      <c r="E139" s="75">
         <f t="shared" si="29"/>
         <v>0.73090028281844144</v>
       </c>
-      <c r="F138" s="75">
+      <c r="F139" s="75">
         <f t="shared" si="29"/>
         <v>0.7324372209847696</v>
       </c>
-      <c r="G138" s="75">
+      <c r="G139" s="75">
         <f t="shared" si="29"/>
         <v>0.72775606130284587</v>
       </c>
-      <c r="H138" s="75">
+      <c r="H139" s="75">
         <f t="shared" si="29"/>
         <v>0.7223062310799363</v>
-      </c>
-      <c r="I138" s="75"/>
-      <c r="J138" s="75"/>
-      <c r="K138" s="75"/>
-      <c r="L138" s="75"/>
-    </row>
-    <row r="139" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B139" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C139" s="75">
-        <f t="shared" ref="C139:H139" si="30">C12/C5</f>
-        <v>-9.9019147041361569E-2</v>
-      </c>
-      <c r="D139" s="75">
-        <f t="shared" si="30"/>
-        <v>-0.23928907533536439</v>
-      </c>
-      <c r="E139" s="75">
-        <f t="shared" si="30"/>
-        <v>-0.17644352426961121</v>
-      </c>
-      <c r="F139" s="75">
-        <f t="shared" si="30"/>
-        <v>-2.4964743583708805E-2</v>
-      </c>
-      <c r="G139" s="75">
-        <f t="shared" si="30"/>
-        <v>8.3680470145342925E-2</v>
-      </c>
-      <c r="H139" s="75">
-        <f t="shared" si="30"/>
-        <v>0.13065867120796384</v>
       </c>
       <c r="I139" s="75"/>
       <c r="J139" s="75"/>
       <c r="K139" s="75"/>
       <c r="L139" s="75"/>
     </row>
-    <row r="140" spans="1:12" s="84" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="1"/>
-      <c r="B140" s="82" t="s">
+    <row r="140" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B140" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C140" s="75">
+        <f t="shared" ref="C140:H140" si="30">C12/C5</f>
+        <v>-9.9019147041361569E-2</v>
+      </c>
+      <c r="D140" s="75">
+        <f t="shared" si="30"/>
+        <v>-0.23928907533536439</v>
+      </c>
+      <c r="E140" s="75">
+        <f t="shared" si="30"/>
+        <v>-0.17644352426961121</v>
+      </c>
+      <c r="F140" s="75">
+        <f t="shared" si="30"/>
+        <v>-2.4964743583708805E-2</v>
+      </c>
+      <c r="G140" s="75">
+        <f t="shared" si="30"/>
+        <v>8.3680470145342925E-2</v>
+      </c>
+      <c r="H140" s="75">
+        <f t="shared" si="30"/>
+        <v>0.13065867120796384</v>
+      </c>
+      <c r="I140" s="75"/>
+      <c r="J140" s="75"/>
+      <c r="K140" s="75"/>
+      <c r="L140" s="75"/>
+    </row>
+    <row r="141" spans="1:12" s="84" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="1"/>
+      <c r="B141" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="C140" s="83">
-        <f t="shared" ref="C140:H140" si="31">C18/C5</f>
+      <c r="C141" s="83">
+        <f t="shared" ref="C141:H141" si="31">C18/C5</f>
         <v>-9.7565802493568179E-2</v>
       </c>
-      <c r="D140" s="83">
+      <c r="D141" s="83">
         <f t="shared" si="31"/>
         <v>-0.2397994991466352</v>
       </c>
-      <c r="E140" s="83">
+      <c r="E141" s="83">
         <f t="shared" si="31"/>
         <v>-0.16123086915925791</v>
       </c>
-      <c r="F140" s="83">
+      <c r="F141" s="83">
         <f t="shared" si="31"/>
         <v>3.0251793887883655E-2</v>
       </c>
-      <c r="G140" s="83">
+      <c r="G141" s="83">
         <f t="shared" si="31"/>
         <v>0.11841063923082681</v>
       </c>
-      <c r="H140" s="83">
+      <c r="H141" s="83">
         <f t="shared" si="31"/>
         <v>0.39906456217249797</v>
       </c>
-      <c r="I140" s="83"/>
-      <c r="J140" s="83"/>
-      <c r="K140" s="83"/>
-      <c r="L140" s="83"/>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B141" s="1"/>
-    </row>
-    <row r="142" spans="1:12" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="4"/>
-      <c r="B142" s="15" t="s">
+      <c r="I141" s="83"/>
+      <c r="J141" s="83"/>
+      <c r="K141" s="83"/>
+      <c r="L141" s="83"/>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B142" s="1"/>
+    </row>
+    <row r="143" spans="1:12" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="4"/>
+      <c r="B143" s="15" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="143" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B143" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C143" s="27">
-        <v>8200</v>
-      </c>
-      <c r="D143" s="27">
-        <v>9600</v>
-      </c>
-      <c r="E143" s="27">
-        <v>16300</v>
-      </c>
-      <c r="F143" s="27">
-        <v>26900</v>
-      </c>
-      <c r="G143" s="27">
-        <v>40500</v>
-      </c>
-      <c r="H143" s="27">
-        <v>52700</v>
-      </c>
-      <c r="I143" s="27"/>
     </row>
     <row r="144" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B144" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C144" s="27">
-        <v>36700</v>
+        <v>8200</v>
       </c>
       <c r="D144" s="27">
+        <v>9600</v>
+      </c>
+      <c r="E144" s="27">
+        <v>16300</v>
+      </c>
+      <c r="F144" s="27">
+        <v>26900</v>
+      </c>
+      <c r="G144" s="27">
         <v>40500</v>
       </c>
-      <c r="E144" s="27">
-        <v>60700</v>
-      </c>
-      <c r="F144" s="27">
-        <v>88400</v>
-      </c>
-      <c r="G144" s="27">
-        <v>116700</v>
-      </c>
       <c r="H144" s="27">
-        <v>133100</v>
+        <v>52700</v>
       </c>
       <c r="I144" s="27"/>
     </row>
     <row r="145" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B145" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C145" s="27">
-        <v>1600</v>
+        <v>36700</v>
       </c>
       <c r="D145" s="27">
-        <v>2500</v>
+        <v>40500</v>
       </c>
       <c r="E145" s="27">
-        <v>4200</v>
+        <v>60700</v>
       </c>
       <c r="F145" s="27">
-        <v>6600</v>
+        <v>88400</v>
       </c>
       <c r="G145" s="27">
-        <v>9500</v>
+        <v>116700</v>
       </c>
       <c r="H145" s="27">
-        <v>12200</v>
+        <v>133100</v>
       </c>
       <c r="I145" s="27"/>
-      <c r="J145" s="27"/>
     </row>
     <row r="146" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B146" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C146" s="27">
+        <v>1600</v>
+      </c>
+      <c r="D146" s="27">
+        <v>2500</v>
+      </c>
+      <c r="E146" s="27">
+        <v>4200</v>
+      </c>
+      <c r="F146" s="27">
+        <v>6600</v>
+      </c>
+      <c r="G146" s="27">
+        <v>9500</v>
+      </c>
+      <c r="H146" s="27">
+        <v>12200</v>
+      </c>
+      <c r="I146" s="27"/>
+      <c r="J146" s="27"/>
+    </row>
+    <row r="147" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B147" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C146" s="34">
-        <f>C144-C145</f>
+      <c r="C147" s="34">
+        <f>C145-C146</f>
         <v>35100</v>
       </c>
-      <c r="D146" s="34">
-        <f t="shared" ref="D146:H146" si="32">D144-D145</f>
+      <c r="D147" s="34">
+        <f t="shared" ref="D147:H147" si="32">D145-D146</f>
         <v>38000</v>
       </c>
-      <c r="E146" s="34">
+      <c r="E147" s="34">
         <f t="shared" si="32"/>
         <v>56500</v>
       </c>
-      <c r="F146" s="34">
+      <c r="F147" s="34">
         <f t="shared" si="32"/>
         <v>81800</v>
       </c>
-      <c r="G146" s="34">
+      <c r="G147" s="34">
         <f t="shared" si="32"/>
         <v>107200</v>
       </c>
-      <c r="H146" s="34">
+      <c r="H147" s="34">
         <f t="shared" si="32"/>
         <v>120900</v>
       </c>
-      <c r="I146" s="27"/>
-      <c r="J146" s="27"/>
-    </row>
-    <row r="147" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="C147" s="34"/>
-      <c r="D147" s="34"/>
-      <c r="E147" s="34"/>
-      <c r="F147" s="34"/>
-      <c r="G147" s="34"/>
-      <c r="H147" s="27"/>
       <c r="I147" s="27"/>
       <c r="J147" s="27"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B148" s="1"/>
-    </row>
-    <row r="149" spans="1:10" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="4"/>
-      <c r="B149" s="15" t="s">
+    <row r="148" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="C148" s="34"/>
+      <c r="D148" s="34"/>
+      <c r="E148" s="34"/>
+      <c r="F148" s="34"/>
+      <c r="G148" s="34"/>
+      <c r="H148" s="27"/>
+      <c r="I148" s="27"/>
+      <c r="J148" s="27"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B149" s="1"/>
+    </row>
+    <row r="150" spans="1:10" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="4"/>
+      <c r="B150" s="15" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="150" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B150" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C150" s="27">
-        <v>117501</v>
-      </c>
-      <c r="D150" s="27">
-        <v>180698</v>
-      </c>
-      <c r="E150" s="27">
-        <v>273507</v>
-      </c>
-      <c r="F150" s="27">
-        <v>404684</v>
-      </c>
-      <c r="G150" s="27">
-        <v>607531</v>
-      </c>
-      <c r="H150" s="27">
-        <v>873442</v>
-      </c>
-      <c r="I150" s="27"/>
     </row>
     <row r="151" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B151" s="9" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C151" s="27">
-        <v>27043</v>
+        <v>117501</v>
       </c>
       <c r="D151" s="27">
-        <v>38501</v>
+        <v>180698</v>
       </c>
       <c r="E151" s="27">
-        <v>44731</v>
+        <v>273507</v>
       </c>
       <c r="F151" s="27">
-        <v>49858</v>
+        <v>404684</v>
       </c>
       <c r="G151" s="27">
-        <v>54907</v>
+        <v>607531</v>
       </c>
       <c r="H151" s="27">
-        <v>79725</v>
+        <v>873442</v>
       </c>
       <c r="I151" s="27"/>
     </row>
     <row r="152" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B152" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C152" s="27">
-        <v>15155</v>
+        <v>27043</v>
       </c>
       <c r="D152" s="27">
-        <v>24658</v>
+        <v>38501</v>
       </c>
       <c r="E152" s="27">
-        <v>32718</v>
+        <v>44731</v>
       </c>
       <c r="F152" s="27">
-        <v>41212</v>
+        <v>49858</v>
       </c>
       <c r="G152" s="27">
-        <v>45640</v>
+        <v>54907</v>
       </c>
       <c r="H152" s="27">
-        <v>42006</v>
+        <v>79725</v>
       </c>
       <c r="I152" s="27"/>
     </row>
     <row r="153" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B153" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C153" s="27">
-        <v>1997</v>
+        <v>15155</v>
       </c>
       <c r="D153" s="27">
-        <v>6915</v>
+        <v>24658</v>
       </c>
       <c r="E153" s="27">
-        <v>18539</v>
+        <v>32718</v>
       </c>
       <c r="F153" s="27">
-        <v>34673</v>
+        <v>41212</v>
       </c>
       <c r="G153" s="27">
-        <v>38653</v>
+        <v>45640</v>
       </c>
       <c r="H153" s="27">
-        <v>40479</v>
+        <v>42006</v>
       </c>
       <c r="I153" s="27"/>
     </row>
     <row r="154" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B154" s="9" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C154" s="27">
-        <v>0</v>
+        <v>1997</v>
       </c>
       <c r="D154" s="27">
-        <v>79</v>
+        <v>6915</v>
       </c>
       <c r="E154" s="27">
-        <v>625</v>
+        <v>18539</v>
       </c>
       <c r="F154" s="27">
-        <v>682</v>
+        <v>34673</v>
       </c>
       <c r="G154" s="27">
-        <v>1293</v>
+        <v>38653</v>
       </c>
       <c r="H154" s="27">
-        <v>1937</v>
+        <v>40479</v>
       </c>
       <c r="I154" s="27"/>
     </row>
     <row r="155" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B155" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C155" s="27">
+        <v>0</v>
+      </c>
+      <c r="D155" s="27">
+        <v>79</v>
+      </c>
+      <c r="E155" s="27">
+        <v>625</v>
+      </c>
+      <c r="F155" s="27">
+        <v>682</v>
+      </c>
+      <c r="G155" s="27">
+        <v>1293</v>
+      </c>
+      <c r="H155" s="27">
+        <v>1937</v>
+      </c>
+      <c r="I155" s="27"/>
+    </row>
+    <row r="156" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B156" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C155" s="34">
-        <f>SUM(C151:C154)</f>
+      <c r="C156" s="34">
+        <f>SUM(C152:C155)</f>
         <v>44195</v>
       </c>
-      <c r="D155" s="34">
-        <f t="shared" ref="D155:H155" si="33">SUM(D151:D154)</f>
+      <c r="D156" s="34">
+        <f t="shared" ref="D156:H156" si="33">SUM(D152:D155)</f>
         <v>70153</v>
       </c>
-      <c r="E155" s="34">
+      <c r="E156" s="34">
         <f t="shared" si="33"/>
         <v>96613</v>
       </c>
-      <c r="F155" s="34">
+      <c r="F156" s="34">
         <f t="shared" si="33"/>
         <v>126425</v>
       </c>
-      <c r="G155" s="34">
+      <c r="G156" s="34">
         <f t="shared" si="33"/>
         <v>140493</v>
       </c>
-      <c r="H155" s="34">
+      <c r="H156" s="34">
         <f t="shared" si="33"/>
         <v>164147</v>
       </c>
-      <c r="I155" s="27"/>
-    </row>
-    <row r="156" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="C156" s="34"/>
-      <c r="D156" s="34"/>
-      <c r="E156" s="34"/>
-      <c r="F156" s="34"/>
-      <c r="G156" s="34"/>
-      <c r="H156" s="27"/>
       <c r="I156" s="27"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B157" s="1"/>
-    </row>
-    <row r="158" spans="1:10" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="4"/>
-      <c r="B158" s="15" t="s">
+    <row r="157" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="C157" s="34"/>
+      <c r="D157" s="34"/>
+      <c r="E157" s="34"/>
+      <c r="F157" s="34"/>
+      <c r="G157" s="34"/>
+      <c r="H157" s="27"/>
+      <c r="I157" s="27"/>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B158" s="1"/>
+    </row>
+    <row r="159" spans="1:10" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="4"/>
+      <c r="B159" s="15" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="159" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B159" s="9" t="s">
+    <row r="160" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B160" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C159" s="90">
-        <f>C150/C145</f>
+      <c r="C160" s="90">
+        <f>C151/C146</f>
         <v>73.438124999999999</v>
       </c>
-      <c r="D159" s="90">
-        <f t="shared" ref="D159:H159" si="34">D150/D145</f>
+      <c r="D160" s="90">
+        <f t="shared" ref="D160:H160" si="34">D151/D146</f>
         <v>72.279200000000003</v>
       </c>
-      <c r="E159" s="90">
+      <c r="E160" s="90">
         <f t="shared" si="34"/>
         <v>65.120714285714286</v>
       </c>
-      <c r="F159" s="90">
+      <c r="F160" s="90">
         <f t="shared" si="34"/>
         <v>61.315757575757573</v>
       </c>
-      <c r="G159" s="90">
+      <c r="G160" s="90">
         <f t="shared" si="34"/>
         <v>63.950631578947366</v>
       </c>
-      <c r="H159" s="90">
+      <c r="H160" s="90">
         <f t="shared" si="34"/>
         <v>71.593606557377043</v>
       </c>
     </row>
-    <row r="160" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B160" s="9" t="s">
+    <row r="161" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B161" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C160" s="89">
-        <f>C143/C144</f>
+      <c r="C161" s="89">
+        <f>C144/C145</f>
         <v>0.22343324250681199</v>
       </c>
-      <c r="D160" s="89">
-        <f t="shared" ref="D160:H160" si="35">D143/D144</f>
+      <c r="D161" s="89">
+        <f t="shared" ref="D161:H161" si="35">D144/D145</f>
         <v>0.23703703703703705</v>
       </c>
-      <c r="E160" s="89">
+      <c r="E161" s="89">
         <f t="shared" si="35"/>
         <v>0.26853377265238881</v>
       </c>
-      <c r="F160" s="89">
+      <c r="F161" s="89">
         <f t="shared" si="35"/>
         <v>0.30429864253393663</v>
       </c>
-      <c r="G160" s="89">
+      <c r="G161" s="89">
         <f t="shared" si="35"/>
         <v>0.34704370179948585</v>
       </c>
-      <c r="H160" s="89">
+      <c r="H161" s="89">
         <f t="shared" si="35"/>
         <v>0.3959429000751315</v>
       </c>
     </row>
-    <row r="161" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B161" s="9" t="s">
+    <row r="162" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B162" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="C161" s="89">
-        <f>C145/C144</f>
+      <c r="C162" s="89">
+        <f>C146/C145</f>
         <v>4.3596730245231606E-2</v>
       </c>
-      <c r="D161" s="89">
-        <f t="shared" ref="D161:H161" si="36">D145/D144</f>
+      <c r="D162" s="89">
+        <f t="shared" ref="D162:H162" si="36">D146/D145</f>
         <v>6.1728395061728392E-2</v>
       </c>
-      <c r="E161" s="89">
+      <c r="E162" s="89">
         <f t="shared" si="36"/>
         <v>6.919275123558484E-2</v>
       </c>
-      <c r="F161" s="89">
+      <c r="F162" s="89">
         <f t="shared" si="36"/>
         <v>7.4660633484162894E-2</v>
       </c>
-      <c r="G161" s="89">
+      <c r="G162" s="89">
         <f t="shared" si="36"/>
         <v>8.1405312767780638E-2</v>
       </c>
-      <c r="H161" s="89">
+      <c r="H162" s="89">
         <f t="shared" si="36"/>
         <v>9.1660405709992482E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B162" s="9" t="s">
+    <row r="163" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B163" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C162" s="139">
-        <f>C151/C146</f>
+      <c r="C163" s="139">
+        <f>C152/C147</f>
         <v>0.77045584045584048</v>
       </c>
-      <c r="D162" s="139">
-        <f t="shared" ref="D162:H162" si="37">D151/D146</f>
+      <c r="D163" s="139">
+        <f t="shared" ref="D163:H163" si="37">D152/D147</f>
         <v>1.0131842105263158</v>
       </c>
-      <c r="E162" s="139">
+      <c r="E163" s="139">
         <f t="shared" si="37"/>
         <v>0.79169911504424784</v>
       </c>
-      <c r="F162" s="139">
+      <c r="F163" s="139">
         <f t="shared" si="37"/>
         <v>0.60951100244498779</v>
       </c>
-      <c r="G162" s="139">
+      <c r="G163" s="139">
         <f t="shared" si="37"/>
         <v>0.51219216417910451</v>
       </c>
-      <c r="H162" s="139">
+      <c r="H163" s="139">
         <f t="shared" si="37"/>
         <v>0.65942928039702231</v>
       </c>
     </row>
-    <row r="163" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B163" s="9" t="s">
+    <row r="164" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B164" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="C163" s="89">
-        <f>C153/C143</f>
+      <c r="C164" s="89">
+        <f>C154/C144</f>
         <v>0.24353658536585365</v>
       </c>
-      <c r="D163" s="89">
-        <f t="shared" ref="D163:H163" si="38">D153/D143</f>
+      <c r="D164" s="89">
+        <f t="shared" ref="D164:H164" si="38">D154/D144</f>
         <v>0.72031250000000002</v>
       </c>
-      <c r="E163" s="89">
+      <c r="E164" s="89">
         <f t="shared" si="38"/>
         <v>1.1373619631901841</v>
       </c>
-      <c r="F163" s="89">
+      <c r="F164" s="89">
         <f t="shared" si="38"/>
         <v>1.2889591078066915</v>
       </c>
-      <c r="G163" s="89">
+      <c r="G164" s="89">
         <f t="shared" si="38"/>
         <v>0.95439506172839506</v>
       </c>
-      <c r="H163" s="89">
+      <c r="H164" s="89">
         <f t="shared" si="38"/>
         <v>0.76810246679316885</v>
       </c>
     </row>
-    <row r="164" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="C164" s="90"/>
-      <c r="D164" s="90"/>
-      <c r="E164" s="90"/>
-      <c r="F164" s="90"/>
-      <c r="G164" s="90"/>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B165" s="1"/>
-    </row>
-    <row r="166" spans="1:10" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="4"/>
-      <c r="B166" s="15" t="s">
+    <row r="165" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="C165" s="90"/>
+      <c r="D165" s="90"/>
+      <c r="E165" s="90"/>
+      <c r="F165" s="90"/>
+      <c r="G165" s="90"/>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B166" s="1"/>
+    </row>
+    <row r="167" spans="1:15" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="4"/>
+      <c r="B167" s="15" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B167" s="9" t="s">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B168" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="C167" s="31"/>
-      <c r="D167" s="31">
+      <c r="C168" s="31"/>
+      <c r="D168" s="31">
         <v>110.58</v>
       </c>
-      <c r="E167" s="31">
+      <c r="E168" s="31">
         <v>71.13</v>
       </c>
-      <c r="F167" s="31">
+      <c r="F168" s="31">
         <v>226.85</v>
       </c>
-      <c r="G167" s="31">
+      <c r="G168" s="31">
         <v>325.2</v>
       </c>
-      <c r="H167" s="31">
+      <c r="H168" s="31">
         <v>177.14</v>
       </c>
-      <c r="I167" s="31"/>
-      <c r="J167" s="31"/>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B169" s="1"/>
+      <c r="I168" s="31"/>
+      <c r="J168" s="31"/>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B170" s="1"/>
+    </row>
+    <row r="171" spans="1:15" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="4"/>
+      <c r="B171" s="15" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B172" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C172" s="168">
+        <f>C47</f>
+        <v>8131</v>
+      </c>
+      <c r="D172" s="168">
+        <f t="shared" ref="D172:H172" si="39">D47</f>
+        <v>29124</v>
+      </c>
+      <c r="E172" s="168">
+        <f t="shared" si="39"/>
+        <v>23503</v>
+      </c>
+      <c r="F172" s="168">
+        <f t="shared" si="39"/>
+        <v>21094</v>
+      </c>
+      <c r="G172" s="168">
+        <f t="shared" si="39"/>
+        <v>54656</v>
+      </c>
+      <c r="H172" s="168">
+        <f t="shared" si="39"/>
+        <v>93779</v>
+      </c>
+      <c r="I172" s="31"/>
+      <c r="J172" s="31"/>
+      <c r="K172" s="31"/>
+      <c r="L172" s="31"/>
+      <c r="M172" s="31"/>
+      <c r="N172" s="31"/>
+      <c r="O172" s="31"/>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B173" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C173" s="168">
+        <f>C25+C26</f>
+        <v>120490</v>
+      </c>
+      <c r="D173" s="168">
+        <f t="shared" ref="D173:H173" si="40">D25+D26</f>
+        <v>553922</v>
+      </c>
+      <c r="E173" s="168">
+        <f t="shared" si="40"/>
+        <v>608180</v>
+      </c>
+      <c r="F173" s="168">
+        <f t="shared" si="40"/>
+        <v>747610</v>
+      </c>
+      <c r="G173" s="168">
+        <f t="shared" si="40"/>
+        <v>877645</v>
+      </c>
+      <c r="H173" s="168">
+        <f t="shared" si="40"/>
+        <v>1140467</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B174" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C174" s="168">
+        <f>C47*Overview!$C$4</f>
+        <v>569.17000000000007</v>
+      </c>
+      <c r="D174" s="168">
+        <f>D47*Overview!$C$4</f>
+        <v>2038.6800000000003</v>
+      </c>
+      <c r="E174" s="168">
+        <f>E47*Overview!$C$4</f>
+        <v>1645.2100000000003</v>
+      </c>
+      <c r="F174" s="168">
+        <f>F47*Overview!$C$4</f>
+        <v>1476.5800000000002</v>
+      </c>
+      <c r="G174" s="168">
+        <f>G47*Overview!$C$4</f>
+        <v>3825.9200000000005</v>
+      </c>
+      <c r="H174" s="168">
+        <f>H47*Overview!$C$4</f>
+        <v>6564.5300000000007</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B175" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="C175" s="168">
+        <f>C124-C174</f>
+        <v>1468.83</v>
+      </c>
+      <c r="D175" s="168">
+        <f t="shared" ref="D175:H175" si="41">D124-D174</f>
+        <v>1074.3199999999997</v>
+      </c>
+      <c r="E175" s="168">
+        <f t="shared" si="41"/>
+        <v>5618.79</v>
+      </c>
+      <c r="F175" s="168">
+        <f t="shared" si="41"/>
+        <v>6282.42</v>
+      </c>
+      <c r="G175" s="168">
+        <f t="shared" si="41"/>
+        <v>6707.08</v>
+      </c>
+      <c r="H175" s="168">
+        <f t="shared" si="41"/>
+        <v>6289.4699999999993</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B176" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C176" s="168">
+        <f>C12+C174-C175</f>
+        <v>-16910.66</v>
+      </c>
+      <c r="D176" s="168">
+        <f t="shared" ref="D176:H176" si="42">D12+D174-D175</f>
+        <v>-59042.64</v>
+      </c>
+      <c r="E176" s="168">
+        <f t="shared" si="42"/>
+        <v>-69168.58</v>
+      </c>
+      <c r="F176" s="168">
+        <f t="shared" si="42"/>
+        <v>-18064.84</v>
+      </c>
+      <c r="G176" s="168">
+        <f t="shared" si="42"/>
+        <v>59713.84</v>
+      </c>
+      <c r="H176" s="168">
+        <f t="shared" si="42"/>
+        <v>135845.06</v>
+      </c>
+    </row>
+    <row r="177" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B177" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C177" s="195">
+        <f>C172+C55-C173</f>
+        <v>-193050</v>
+      </c>
+      <c r="D177" s="195">
+        <f t="shared" ref="D177:H177" si="43">D172+D55-D173</f>
+        <v>-11742</v>
+      </c>
+      <c r="E177" s="195">
+        <f t="shared" si="43"/>
+        <v>-42599</v>
+      </c>
+      <c r="F177" s="195">
+        <f t="shared" si="43"/>
+        <v>-71015</v>
+      </c>
+      <c r="G177" s="195">
+        <f t="shared" si="43"/>
+        <v>1561</v>
+      </c>
+      <c r="H177" s="195">
+        <f t="shared" si="43"/>
+        <v>300318</v>
+      </c>
+    </row>
+    <row r="178" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B178" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C178" s="195">
+        <f>C176</f>
+        <v>-16910.66</v>
+      </c>
+      <c r="D178" s="195">
+        <f t="shared" ref="D178:F178" si="44">D176</f>
+        <v>-59042.64</v>
+      </c>
+      <c r="E178" s="195">
+        <f t="shared" si="44"/>
+        <v>-69168.58</v>
+      </c>
+      <c r="F178" s="195">
+        <f t="shared" si="44"/>
+        <v>-18064.84</v>
+      </c>
+      <c r="G178" s="195">
+        <f>G176*(1-G118)</f>
+        <v>51698.763163059833</v>
+      </c>
+      <c r="H178" s="195">
+        <f>H176</f>
+        <v>135845.06</v>
+      </c>
+    </row>
+    <row r="179" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B179" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="C179" s="195">
+        <f>C176+C60+C124</f>
+        <v>-12616.66</v>
+      </c>
+      <c r="D179" s="195">
+        <f t="shared" ref="D179:H179" si="45">D176+D60+D124</f>
+        <v>-53203.64</v>
+      </c>
+      <c r="E179" s="195">
+        <f t="shared" si="45"/>
+        <v>-57034.58</v>
+      </c>
+      <c r="F179" s="195">
+        <f t="shared" si="45"/>
+        <v>-3210.84</v>
+      </c>
+      <c r="G179" s="195">
+        <f t="shared" si="45"/>
+        <v>81100.84</v>
+      </c>
+      <c r="H179" s="195">
+        <f t="shared" si="45"/>
+        <v>163090.06</v>
+      </c>
+    </row>
+    <row r="181" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B181" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C40:F40 G40:L40 C106 D106:L106 C108:G108 C101:H101 C155:H155 C49:H49" formulaRange="1"/>
-    <ignoredError sqref="D132" formula="1"/>
+    <ignoredError sqref="C40:F40 G40:L40 C106 D106:L106 C108:G108 C101:H101 C156:H156 C49:H49" formulaRange="1"/>
+    <ignoredError sqref="D133 G178" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -11800,7 +12251,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEB41336-2E39-7442-9864-91E9B0A07818}">
-  <dimension ref="A1:S155"/>
+  <dimension ref="A1:S167"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="2" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
@@ -11920,11 +12371,11 @@
         <v>85</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="223" t="s">
+      <c r="P4" s="228" t="s">
         <v>86</v>
       </c>
-      <c r="Q4" s="224"/>
-      <c r="R4" s="225"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="230"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -16111,93 +16562,104 @@
       <c r="K119" s="8"/>
       <c r="L119" s="8"/>
       <c r="M119" s="8"/>
+      <c r="N119" s="1">
+        <f>SUM(G119:J119)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="120" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="12"/>
-      <c r="C120" s="28"/>
-      <c r="D120" s="28"/>
-      <c r="E120" s="28"/>
-      <c r="F120" s="28"/>
-      <c r="G120" s="28"/>
-      <c r="H120" s="28"/>
-      <c r="I120" s="28"/>
-      <c r="J120" s="28"/>
+      <c r="B120" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="C120" s="27">
+        <v>2825</v>
+      </c>
+      <c r="D120" s="27">
+        <v>2267</v>
+      </c>
+      <c r="E120" s="27">
+        <v>3141</v>
+      </c>
+      <c r="F120" s="27">
+        <v>2300</v>
+      </c>
+      <c r="G120" s="27">
+        <v>2954</v>
+      </c>
+      <c r="H120" s="27">
+        <v>3597</v>
+      </c>
+      <c r="I120" s="27">
+        <v>4003</v>
+      </c>
+      <c r="J120" s="27">
+        <v>3450</v>
+      </c>
       <c r="K120" s="8"/>
       <c r="L120" s="8"/>
       <c r="M120" s="8"/>
-    </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B121" s="1"/>
-    </row>
-    <row r="122" spans="1:19" s="63" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="1"/>
-      <c r="B122" s="15" t="s">
+      <c r="N120" s="20">
+        <f>SUM(G120:J120)</f>
+        <v>14004</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B121" s="12"/>
+      <c r="C121" s="28"/>
+      <c r="D121" s="28"/>
+      <c r="E121" s="28"/>
+      <c r="F121" s="28"/>
+      <c r="G121" s="28"/>
+      <c r="H121" s="28"/>
+      <c r="I121" s="28"/>
+      <c r="J121" s="28"/>
+      <c r="K121" s="8"/>
+      <c r="L121" s="8"/>
+      <c r="M121" s="8"/>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B122" s="1"/>
+    </row>
+    <row r="123" spans="1:19" s="63" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="1"/>
+      <c r="B123" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C122" s="65"/>
-      <c r="D122" s="65"/>
-      <c r="E122" s="65"/>
-      <c r="F122" s="65"/>
-      <c r="G122" s="65"/>
-      <c r="H122" s="65"/>
-      <c r="I122" s="65"/>
-      <c r="J122" s="65"/>
-      <c r="K122" s="1"/>
-      <c r="L122" s="1"/>
-      <c r="M122" s="1"/>
-      <c r="O122" s="4"/>
-      <c r="S122" s="4"/>
-    </row>
-    <row r="123" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C123" s="27">
-        <v>186700</v>
-      </c>
-      <c r="D123" s="27">
-        <v>202500</v>
-      </c>
-      <c r="E123" s="27">
-        <v>220500</v>
-      </c>
-      <c r="F123" s="27">
-        <v>238500</v>
-      </c>
-      <c r="G123" s="27">
-        <v>257000</v>
-      </c>
-      <c r="H123" s="27">
-        <v>273000</v>
-      </c>
-      <c r="I123" s="27">
-        <v>288500</v>
-      </c>
-      <c r="J123" s="27">
-        <v>295500</v>
-      </c>
+      <c r="C123" s="65"/>
+      <c r="D123" s="65"/>
+      <c r="E123" s="65"/>
+      <c r="F123" s="65"/>
+      <c r="G123" s="65"/>
+      <c r="H123" s="65"/>
+      <c r="I123" s="65"/>
+      <c r="J123" s="65"/>
+      <c r="K123" s="1"/>
+      <c r="L123" s="1"/>
+      <c r="M123" s="1"/>
+      <c r="O123" s="4"/>
+      <c r="S123" s="4"/>
     </row>
     <row r="124" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B124" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C124" s="27">
-        <v>189700</v>
+        <v>186700</v>
       </c>
       <c r="D124" s="27">
-        <v>205500</v>
+        <v>202500</v>
       </c>
       <c r="E124" s="27">
-        <v>223500</v>
+        <v>220500</v>
       </c>
       <c r="F124" s="27">
-        <v>241500</v>
+        <v>238500</v>
       </c>
       <c r="G124" s="27">
-        <v>261000</v>
+        <v>257000</v>
       </c>
       <c r="H124" s="27">
-        <v>277000</v>
+        <v>273000</v>
       </c>
       <c r="I124" s="27">
         <v>288500</v>
@@ -16208,94 +16670,110 @@
     </row>
     <row r="125" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B125" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C125" s="34">
-        <f t="shared" ref="C125" si="52">D5</f>
-        <v>192594</v>
-      </c>
-      <c r="D125" s="34">
-        <f t="shared" ref="D125" si="53">E5</f>
-        <v>209550</v>
-      </c>
-      <c r="E125" s="34">
-        <f t="shared" ref="E125" si="54">F5</f>
-        <v>230743</v>
-      </c>
-      <c r="F125" s="34">
-        <f t="shared" ref="F125" si="55">G5</f>
-        <v>252265</v>
-      </c>
-      <c r="G125" s="34">
-        <f t="shared" ref="G125" si="56">H5</f>
-        <v>271713</v>
-      </c>
-      <c r="H125" s="34">
-        <f t="shared" ref="H125" si="57">I5</f>
-        <v>282868</v>
-      </c>
-      <c r="I125" s="34">
-        <f t="shared" ref="I125" si="58">J5</f>
-        <v>291967</v>
-      </c>
-      <c r="J125" s="34">
-        <f t="shared" ref="J125" si="59">K5</f>
-        <v>0</v>
+        <v>89</v>
+      </c>
+      <c r="C125" s="27">
+        <v>189700</v>
+      </c>
+      <c r="D125" s="27">
+        <v>205500</v>
+      </c>
+      <c r="E125" s="27">
+        <v>223500</v>
+      </c>
+      <c r="F125" s="27">
+        <v>241500</v>
+      </c>
+      <c r="G125" s="27">
+        <v>261000</v>
+      </c>
+      <c r="H125" s="27">
+        <v>277000</v>
+      </c>
+      <c r="I125" s="27">
+        <v>288500</v>
+      </c>
+      <c r="J125" s="27">
+        <v>295500</v>
       </c>
     </row>
     <row r="126" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B126" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C126" s="64" t="str">
-        <f t="shared" ref="C126" si="60">IF(D5&gt;C124, "BEAT", IF(D5&lt;C123, "MISSED", "MET"))</f>
-        <v>BEAT</v>
-      </c>
-      <c r="D126" s="64" t="str">
-        <f t="shared" ref="D126" si="61">IF(E5&gt;D124, "BEAT", IF(E5&lt;D123, "MISSED", "MET"))</f>
-        <v>BEAT</v>
-      </c>
-      <c r="E126" s="64" t="str">
-        <f t="shared" ref="E126" si="62">IF(F5&gt;E124, "BEAT", IF(F5&lt;E123, "MISSED", "MET"))</f>
-        <v>BEAT</v>
-      </c>
-      <c r="F126" s="64" t="str">
-        <f t="shared" ref="F126" si="63">IF(G5&gt;F124, "BEAT", IF(G5&lt;F123, "MISSED", "MET"))</f>
-        <v>BEAT</v>
-      </c>
-      <c r="G126" s="64" t="str">
-        <f t="shared" ref="G126" si="64">IF(H5&gt;G124, "BEAT", IF(H5&lt;G123, "MISSED", "MET"))</f>
-        <v>BEAT</v>
-      </c>
-      <c r="H126" s="64" t="str">
-        <f t="shared" ref="H126" si="65">IF(I5&gt;H124, "BEAT", IF(I5&lt;H123, "MISSED", "MET"))</f>
-        <v>BEAT</v>
-      </c>
-      <c r="I126" s="64" t="str">
-        <f t="shared" ref="I126" si="66">IF(J5&gt;I124, "BEAT", IF(J5&lt;I123, "MISSED", "MET"))</f>
-        <v>BEAT</v>
-      </c>
-      <c r="J126" s="64" t="str">
-        <f t="shared" ref="J126" si="67">IF(K5&gt;J124, "BEAT", IF(K5&lt;J123, "MISSED", "MET"))</f>
-        <v>MISSED</v>
+        <v>93</v>
+      </c>
+      <c r="C126" s="34">
+        <f t="shared" ref="C126" si="52">D5</f>
+        <v>192594</v>
+      </c>
+      <c r="D126" s="34">
+        <f t="shared" ref="D126" si="53">E5</f>
+        <v>209550</v>
+      </c>
+      <c r="E126" s="34">
+        <f t="shared" ref="E126" si="54">F5</f>
+        <v>230743</v>
+      </c>
+      <c r="F126" s="34">
+        <f t="shared" ref="F126" si="55">G5</f>
+        <v>252265</v>
+      </c>
+      <c r="G126" s="34">
+        <f t="shared" ref="G126" si="56">H5</f>
+        <v>271713</v>
+      </c>
+      <c r="H126" s="34">
+        <f t="shared" ref="H126" si="57">I5</f>
+        <v>282868</v>
+      </c>
+      <c r="I126" s="34">
+        <f t="shared" ref="I126" si="58">J5</f>
+        <v>291967</v>
+      </c>
+      <c r="J126" s="34">
+        <f t="shared" ref="J126" si="59">K5</f>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B127" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C127" s="31"/>
-      <c r="D127" s="31"/>
-      <c r="E127" s="31"/>
-      <c r="F127" s="31"/>
-      <c r="G127" s="31"/>
-      <c r="H127" s="31"/>
-      <c r="I127" s="31"/>
-      <c r="J127" s="31"/>
+        <v>90</v>
+      </c>
+      <c r="C127" s="64" t="str">
+        <f t="shared" ref="C127" si="60">IF(D5&gt;C125, "BEAT", IF(D5&lt;C124, "MISSED", "MET"))</f>
+        <v>BEAT</v>
+      </c>
+      <c r="D127" s="64" t="str">
+        <f t="shared" ref="D127" si="61">IF(E5&gt;D125, "BEAT", IF(E5&lt;D124, "MISSED", "MET"))</f>
+        <v>BEAT</v>
+      </c>
+      <c r="E127" s="64" t="str">
+        <f t="shared" ref="E127" si="62">IF(F5&gt;E125, "BEAT", IF(F5&lt;E124, "MISSED", "MET"))</f>
+        <v>BEAT</v>
+      </c>
+      <c r="F127" s="64" t="str">
+        <f t="shared" ref="F127" si="63">IF(G5&gt;F125, "BEAT", IF(G5&lt;F124, "MISSED", "MET"))</f>
+        <v>BEAT</v>
+      </c>
+      <c r="G127" s="64" t="str">
+        <f t="shared" ref="G127" si="64">IF(H5&gt;G125, "BEAT", IF(H5&lt;G124, "MISSED", "MET"))</f>
+        <v>BEAT</v>
+      </c>
+      <c r="H127" s="64" t="str">
+        <f t="shared" ref="H127" si="65">IF(I5&gt;H125, "BEAT", IF(I5&lt;H124, "MISSED", "MET"))</f>
+        <v>BEAT</v>
+      </c>
+      <c r="I127" s="64" t="str">
+        <f t="shared" ref="I127" si="66">IF(J5&gt;I125, "BEAT", IF(J5&lt;I124, "MISSED", "MET"))</f>
+        <v>BEAT</v>
+      </c>
+      <c r="J127" s="64" t="str">
+        <f t="shared" ref="J127" si="67">IF(K5&gt;J125, "BEAT", IF(K5&lt;J124, "MISSED", "MET"))</f>
+        <v>MISSED</v>
+      </c>
     </row>
     <row r="128" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B128" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C128" s="31"/>
       <c r="D128" s="31"/>
@@ -16308,596 +16786,906 @@
     </row>
     <row r="129" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B129" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C129" s="31"/>
+      <c r="D129" s="31"/>
+      <c r="E129" s="31"/>
+      <c r="F129" s="31"/>
+      <c r="G129" s="31"/>
+      <c r="H129" s="31"/>
+      <c r="I129" s="31"/>
+      <c r="J129" s="31"/>
+    </row>
+    <row r="130" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B130" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C129" s="25"/>
-      <c r="D129" s="25"/>
-      <c r="E129" s="25"/>
-      <c r="F129" s="25"/>
-      <c r="G129" s="25"/>
-      <c r="H129" s="25"/>
-      <c r="I129" s="25"/>
-      <c r="J129" s="25"/>
-      <c r="K129" s="20"/>
-      <c r="L129" s="20"/>
-      <c r="M129" s="20"/>
-    </row>
-    <row r="130" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="12" t="s">
+      <c r="C130" s="25"/>
+      <c r="D130" s="25"/>
+      <c r="E130" s="25"/>
+      <c r="F130" s="25"/>
+      <c r="G130" s="25"/>
+      <c r="H130" s="25"/>
+      <c r="I130" s="25"/>
+      <c r="J130" s="25"/>
+      <c r="K130" s="20"/>
+      <c r="L130" s="20"/>
+      <c r="M130" s="20"/>
+    </row>
+    <row r="131" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B131" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C130" s="64"/>
-      <c r="D130" s="64"/>
-      <c r="E130" s="64"/>
-      <c r="F130" s="64"/>
-      <c r="G130" s="64"/>
-      <c r="H130" s="64"/>
-      <c r="I130" s="64"/>
-      <c r="J130" s="64"/>
-      <c r="K130" s="8"/>
-      <c r="L130" s="8"/>
-      <c r="M130" s="8"/>
-    </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B131" s="1"/>
-    </row>
-    <row r="132" spans="1:19" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="4"/>
-      <c r="B132" s="15" t="s">
+      <c r="C131" s="64"/>
+      <c r="D131" s="64"/>
+      <c r="E131" s="64"/>
+      <c r="F131" s="64"/>
+      <c r="G131" s="64"/>
+      <c r="H131" s="64"/>
+      <c r="I131" s="64"/>
+      <c r="J131" s="64"/>
+      <c r="K131" s="8"/>
+      <c r="L131" s="8"/>
+      <c r="M131" s="8"/>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B132" s="1"/>
+    </row>
+    <row r="133" spans="1:19" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="4"/>
+      <c r="B133" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="K132" s="8"/>
-      <c r="L132" s="8"/>
-      <c r="M132" s="8"/>
-      <c r="O132" s="1"/>
-      <c r="S132" s="1"/>
-    </row>
-    <row r="133" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C133" s="27">
-        <v>34100</v>
-      </c>
-      <c r="D133" s="27">
-        <v>37200</v>
-      </c>
-      <c r="E133" s="27">
-        <v>40500</v>
-      </c>
-      <c r="F133" s="27">
-        <v>46600</v>
-      </c>
-      <c r="G133" s="27">
-        <v>47700</v>
-      </c>
-      <c r="H133" s="27">
-        <v>50500</v>
-      </c>
-      <c r="I133" s="27">
-        <v>52700</v>
-      </c>
-      <c r="J133" s="27">
-        <v>56500</v>
-      </c>
+      <c r="K133" s="8"/>
+      <c r="L133" s="8"/>
+      <c r="M133" s="8"/>
+      <c r="O133" s="1"/>
+      <c r="S133" s="1"/>
     </row>
     <row r="134" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B134" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C134" s="27">
-        <v>103600</v>
+        <v>34100</v>
       </c>
       <c r="D134" s="27">
-        <v>113100</v>
+        <v>37200</v>
       </c>
       <c r="E134" s="27">
-        <v>116700</v>
+        <v>40500</v>
       </c>
       <c r="F134" s="27">
-        <v>130200</v>
+        <v>46600</v>
       </c>
       <c r="G134" s="27">
-        <v>128300</v>
+        <v>47700</v>
       </c>
       <c r="H134" s="27">
-        <v>135300</v>
+        <v>50500</v>
       </c>
       <c r="I134" s="27">
-        <v>133100</v>
+        <v>52700</v>
       </c>
       <c r="J134" s="27">
-        <v>137800</v>
+        <v>56500</v>
       </c>
     </row>
     <row r="135" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B135" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C135" s="27">
-        <v>8000</v>
+        <v>103600</v>
       </c>
       <c r="D135" s="27">
-        <v>8600</v>
+        <v>113100</v>
       </c>
       <c r="E135" s="27">
-        <v>9500</v>
+        <v>116700</v>
       </c>
       <c r="F135" s="27">
-        <v>10300</v>
+        <v>130200</v>
       </c>
       <c r="G135" s="27">
-        <v>10900</v>
+        <v>128300</v>
       </c>
       <c r="H135" s="27">
-        <v>11500</v>
+        <v>135300</v>
       </c>
       <c r="I135" s="27">
-        <v>12200</v>
+        <v>133100</v>
       </c>
       <c r="J135" s="27">
-        <v>12500</v>
+        <v>137800</v>
       </c>
     </row>
     <row r="136" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B136" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C136" s="27">
+        <v>8000</v>
+      </c>
+      <c r="D136" s="27">
+        <v>8600</v>
+      </c>
+      <c r="E136" s="27">
+        <v>9500</v>
+      </c>
+      <c r="F136" s="27">
+        <v>10300</v>
+      </c>
+      <c r="G136" s="27">
+        <v>10900</v>
+      </c>
+      <c r="H136" s="27">
+        <v>11500</v>
+      </c>
+      <c r="I136" s="27">
+        <v>12200</v>
+      </c>
+      <c r="J136" s="27">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B137" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C136" s="34">
-        <f t="shared" ref="C136:H136" si="68">C134-C135</f>
+      <c r="C137" s="34">
+        <f t="shared" ref="C137:H137" si="68">C135-C136</f>
         <v>95600</v>
       </c>
-      <c r="D136" s="34">
+      <c r="D137" s="34">
         <f t="shared" si="68"/>
         <v>104500</v>
       </c>
-      <c r="E136" s="34">
+      <c r="E137" s="34">
         <f t="shared" si="68"/>
         <v>107200</v>
       </c>
-      <c r="F136" s="34">
+      <c r="F137" s="34">
         <f t="shared" si="68"/>
         <v>119900</v>
       </c>
-      <c r="G136" s="34">
+      <c r="G137" s="34">
         <f t="shared" si="68"/>
         <v>117400</v>
       </c>
-      <c r="H136" s="34">
+      <c r="H137" s="34">
         <f t="shared" si="68"/>
         <v>123800</v>
       </c>
-      <c r="I136" s="34">
-        <f t="shared" ref="I136:J136" si="69">I134-I135</f>
+      <c r="I137" s="34">
+        <f t="shared" ref="I137:J137" si="69">I135-I136</f>
         <v>120900</v>
       </c>
-      <c r="J136" s="34">
+      <c r="J137" s="34">
         <f t="shared" si="69"/>
         <v>125300</v>
       </c>
     </row>
-    <row r="137" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="C137" s="34"/>
-      <c r="D137" s="34"/>
-      <c r="E137" s="34"/>
-      <c r="F137" s="34"/>
-      <c r="G137" s="34"/>
-      <c r="H137" s="34"/>
-      <c r="I137" s="34"/>
-      <c r="J137" s="34"/>
-    </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B138" s="1"/>
-    </row>
-    <row r="139" spans="1:19" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="4"/>
-      <c r="B139" s="15" t="s">
+    <row r="138" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="C138" s="34"/>
+      <c r="D138" s="34"/>
+      <c r="E138" s="34"/>
+      <c r="F138" s="34"/>
+      <c r="G138" s="34"/>
+      <c r="H138" s="34"/>
+      <c r="I138" s="34"/>
+      <c r="J138" s="34"/>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B139" s="1"/>
+    </row>
+    <row r="140" spans="1:19" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="4"/>
+      <c r="B140" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="K139" s="8"/>
-      <c r="L139" s="8"/>
-      <c r="M139" s="8"/>
-      <c r="O139" s="1"/>
-      <c r="S139" s="94"/>
-    </row>
-    <row r="140" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B140" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C140" s="27">
-        <v>143909</v>
-      </c>
-      <c r="D140" s="27">
-        <v>157617</v>
-      </c>
-      <c r="E140" s="27">
-        <v>174317</v>
-      </c>
-      <c r="F140" s="27">
-        <v>190987</v>
-      </c>
-      <c r="G140" s="27">
-        <v>210678</v>
-      </c>
-      <c r="H140" s="27">
-        <v>229491</v>
-      </c>
-      <c r="I140" s="27">
-        <v>242286</v>
-      </c>
-      <c r="J140" s="27">
-        <v>250908</v>
-      </c>
-      <c r="L140" s="27"/>
+      <c r="K140" s="8"/>
+      <c r="L140" s="8"/>
+      <c r="M140" s="8"/>
+      <c r="O140" s="1"/>
+      <c r="S140" s="94"/>
     </row>
     <row r="141" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B141" s="9" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C141" s="27">
-        <v>13258</v>
+        <v>143909</v>
       </c>
       <c r="D141" s="27">
-        <v>14405</v>
+        <v>157617</v>
       </c>
       <c r="E141" s="27">
-        <v>14292</v>
+        <v>174317</v>
       </c>
       <c r="F141" s="27">
-        <v>17882</v>
+        <v>190987</v>
       </c>
       <c r="G141" s="27">
-        <v>20603</v>
+        <v>210678</v>
       </c>
       <c r="H141" s="27">
-        <v>21019</v>
+        <v>229491</v>
       </c>
       <c r="I141" s="27">
-        <v>20221</v>
+        <v>242286</v>
       </c>
       <c r="J141" s="27">
-        <v>20614</v>
+        <v>250908</v>
       </c>
       <c r="L141" s="27"/>
     </row>
     <row r="142" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B142" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C142" s="27">
-        <v>10698</v>
+        <v>13258</v>
       </c>
       <c r="D142" s="27">
-        <v>10772</v>
+        <v>14405</v>
       </c>
       <c r="E142" s="27">
-        <v>11415</v>
+        <v>14292</v>
       </c>
       <c r="F142" s="27">
-        <v>11986</v>
+        <v>17882</v>
       </c>
       <c r="G142" s="27">
-        <v>10088</v>
+        <v>20603</v>
       </c>
       <c r="H142" s="27">
-        <v>9649</v>
+        <v>21019</v>
       </c>
       <c r="I142" s="27">
-        <v>10283</v>
+        <v>20221</v>
       </c>
       <c r="J142" s="27">
-        <v>11317</v>
+        <v>20614</v>
       </c>
       <c r="L142" s="27"/>
     </row>
     <row r="143" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B143" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C143" s="27">
-        <v>10176</v>
+        <v>10698</v>
       </c>
       <c r="D143" s="27">
-        <v>9411</v>
+        <v>10772</v>
       </c>
       <c r="E143" s="27">
-        <v>9142</v>
+        <v>11415</v>
       </c>
       <c r="F143" s="27">
-        <v>9442</v>
+        <v>11986</v>
       </c>
       <c r="G143" s="27">
-        <v>10390</v>
+        <v>10088</v>
       </c>
       <c r="H143" s="27">
-        <v>11096</v>
+        <v>9649</v>
       </c>
       <c r="I143" s="27">
-        <v>9551</v>
+        <v>10283</v>
       </c>
       <c r="J143" s="27">
-        <v>8446</v>
+        <v>11317</v>
       </c>
       <c r="L143" s="27"/>
     </row>
     <row r="144" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B144" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C144" s="27">
+        <v>10176</v>
+      </c>
+      <c r="D144" s="27">
+        <v>9411</v>
+      </c>
+      <c r="E144" s="27">
+        <v>9142</v>
+      </c>
+      <c r="F144" s="27">
+        <v>9442</v>
+      </c>
+      <c r="G144" s="27">
+        <v>10390</v>
+      </c>
+      <c r="H144" s="27">
+        <v>11096</v>
+      </c>
+      <c r="I144" s="27">
+        <v>9551</v>
+      </c>
+      <c r="J144" s="27">
+        <v>8446</v>
+      </c>
+      <c r="L144" s="27"/>
+    </row>
+    <row r="145" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B145" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="C144" s="27">
+      <c r="C145" s="27">
         <v>286</v>
       </c>
-      <c r="D144" s="27">
+      <c r="D145" s="27">
         <v>389</v>
       </c>
-      <c r="E144" s="27">
+      <c r="E145" s="27">
         <v>384</v>
       </c>
-      <c r="F144" s="27">
+      <c r="F145" s="27">
         <v>446</v>
       </c>
-      <c r="G144" s="27">
+      <c r="G145" s="27">
         <v>506</v>
       </c>
-      <c r="H144" s="27">
+      <c r="H145" s="27">
         <v>458</v>
       </c>
-      <c r="I144" s="27">
+      <c r="I145" s="27">
         <v>527</v>
       </c>
-      <c r="J144" s="27">
+      <c r="J145" s="27">
         <v>682</v>
       </c>
-      <c r="L144" s="27"/>
-    </row>
-    <row r="145" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B145" s="9" t="s">
+      <c r="L145" s="27"/>
+    </row>
+    <row r="146" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B146" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C145" s="34">
-        <f t="shared" ref="C145:H145" si="70">SUM(C141:C144)</f>
+      <c r="C146" s="34">
+        <f t="shared" ref="C146:H146" si="70">SUM(C142:C145)</f>
         <v>34418</v>
       </c>
-      <c r="D145" s="34">
+      <c r="D146" s="34">
         <f t="shared" si="70"/>
         <v>34977</v>
       </c>
-      <c r="E145" s="34">
+      <c r="E146" s="34">
         <f t="shared" si="70"/>
         <v>35233</v>
       </c>
-      <c r="F145" s="34">
+      <c r="F146" s="34">
         <f t="shared" si="70"/>
         <v>39756</v>
       </c>
-      <c r="G145" s="34">
+      <c r="G146" s="34">
         <f t="shared" si="70"/>
         <v>41587</v>
       </c>
-      <c r="H145" s="34">
+      <c r="H146" s="34">
         <f t="shared" si="70"/>
         <v>42222</v>
       </c>
-      <c r="I145" s="34">
-        <f t="shared" ref="I145:J145" si="71">SUM(I141:I144)</f>
+      <c r="I146" s="34">
+        <f t="shared" ref="I146:J146" si="71">SUM(I142:I145)</f>
         <v>40582</v>
       </c>
-      <c r="J145" s="34">
+      <c r="J146" s="34">
         <f t="shared" si="71"/>
         <v>41059</v>
       </c>
     </row>
-    <row r="146" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="C146" s="34"/>
-      <c r="D146" s="34"/>
-      <c r="E146" s="34"/>
-      <c r="F146" s="34"/>
-      <c r="G146" s="34"/>
-      <c r="H146" s="34"/>
-      <c r="I146" s="34"/>
-      <c r="J146" s="34"/>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B147" s="1"/>
-    </row>
-    <row r="148" spans="1:13" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="4"/>
-      <c r="B148" s="15" t="s">
+    <row r="147" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="C147" s="34"/>
+      <c r="D147" s="34"/>
+      <c r="E147" s="34"/>
+      <c r="F147" s="34"/>
+      <c r="G147" s="34"/>
+      <c r="H147" s="34"/>
+      <c r="I147" s="34"/>
+      <c r="J147" s="34"/>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B148" s="1"/>
+    </row>
+    <row r="149" spans="1:14" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="4"/>
+      <c r="B149" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="K148" s="1"/>
-      <c r="L148" s="1"/>
-      <c r="M148" s="1"/>
-    </row>
-    <row r="149" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B149" s="9" t="s">
+      <c r="K149" s="1"/>
+      <c r="L149" s="1"/>
+      <c r="M149" s="1"/>
+    </row>
+    <row r="150" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B150" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C149" s="90">
-        <f t="shared" ref="C149:H149" si="72">C140/C135</f>
+      <c r="C150" s="90">
+        <f t="shared" ref="C150:H150" si="72">C141/C136</f>
         <v>17.988624999999999</v>
       </c>
-      <c r="D149" s="90">
+      <c r="D150" s="90">
         <f t="shared" si="72"/>
         <v>18.327558139534883</v>
       </c>
-      <c r="E149" s="90">
+      <c r="E150" s="90">
         <f t="shared" si="72"/>
         <v>18.349157894736841</v>
       </c>
-      <c r="F149" s="90">
+      <c r="F150" s="90">
         <f t="shared" si="72"/>
         <v>18.542427184466021</v>
       </c>
-      <c r="G149" s="90">
+      <c r="G150" s="90">
         <f t="shared" si="72"/>
         <v>19.328256880733946</v>
       </c>
-      <c r="H149" s="90">
+      <c r="H150" s="90">
         <f t="shared" si="72"/>
         <v>19.955739130434782</v>
       </c>
-      <c r="I149" s="90">
-        <f t="shared" ref="I149:J149" si="73">I140/I135</f>
+      <c r="I150" s="90">
+        <f t="shared" ref="I150:J150" si="73">I141/I136</f>
         <v>19.859508196721311</v>
       </c>
-      <c r="J149" s="90">
+      <c r="J150" s="90">
         <f t="shared" si="73"/>
         <v>20.07264</v>
       </c>
     </row>
-    <row r="150" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B150" s="9" t="s">
+    <row r="151" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B151" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C150" s="89">
-        <f t="shared" ref="C150:H150" si="74">C133/C134</f>
+      <c r="C151" s="89">
+        <f t="shared" ref="C151:H151" si="74">C134/C135</f>
         <v>0.32915057915057916</v>
       </c>
-      <c r="D150" s="89">
+      <c r="D151" s="89">
         <f t="shared" si="74"/>
         <v>0.32891246684350134</v>
       </c>
-      <c r="E150" s="89">
+      <c r="E151" s="89">
         <f t="shared" si="74"/>
         <v>0.34704370179948585</v>
       </c>
-      <c r="F150" s="89">
+      <c r="F151" s="89">
         <f t="shared" si="74"/>
         <v>0.3579109062980031</v>
       </c>
-      <c r="G150" s="89">
+      <c r="G151" s="89">
         <f t="shared" si="74"/>
         <v>0.37178487918939984</v>
       </c>
-      <c r="H150" s="89">
+      <c r="H151" s="89">
         <f t="shared" si="74"/>
         <v>0.37324464153732445</v>
       </c>
-      <c r="I150" s="89">
-        <f t="shared" ref="I150:J150" si="75">I133/I134</f>
+      <c r="I151" s="89">
+        <f t="shared" ref="I151:J151" si="75">I134/I135</f>
         <v>0.3959429000751315</v>
       </c>
-      <c r="J150" s="89">
+      <c r="J151" s="89">
         <f t="shared" si="75"/>
         <v>0.41001451378809867</v>
       </c>
     </row>
-    <row r="151" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B151" s="9" t="s">
+    <row r="152" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B152" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="C151" s="89">
-        <f t="shared" ref="C151:H151" si="76">C135/C134</f>
+      <c r="C152" s="89">
+        <f t="shared" ref="C152:H152" si="76">C136/C135</f>
         <v>7.7220077220077218E-2</v>
       </c>
-      <c r="D151" s="89">
+      <c r="D152" s="89">
         <f t="shared" si="76"/>
         <v>7.6038903625110524E-2</v>
       </c>
-      <c r="E151" s="89">
+      <c r="E152" s="89">
         <f t="shared" si="76"/>
         <v>8.1405312767780638E-2</v>
       </c>
-      <c r="F151" s="89">
+      <c r="F152" s="89">
         <f t="shared" si="76"/>
         <v>7.9109062980030717E-2</v>
       </c>
-      <c r="G151" s="89">
+      <c r="G152" s="89">
         <f t="shared" si="76"/>
         <v>8.4957131722525336E-2</v>
       </c>
-      <c r="H151" s="89">
+      <c r="H152" s="89">
         <f t="shared" si="76"/>
         <v>8.4996304508499626E-2</v>
       </c>
-      <c r="I151" s="89">
-        <f t="shared" ref="I151:J151" si="77">I135/I134</f>
+      <c r="I152" s="89">
+        <f t="shared" ref="I152:J152" si="77">I136/I135</f>
         <v>9.1660405709992482E-2</v>
       </c>
-      <c r="J151" s="89">
+      <c r="J152" s="89">
         <f t="shared" si="77"/>
         <v>9.071117561683599E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B152" s="9" t="s">
+    <row r="153" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B153" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C152" s="139">
-        <f t="shared" ref="C152:H152" si="78">C141/C136</f>
+      <c r="C153" s="139">
+        <f t="shared" ref="C153:H153" si="78">C142/C137</f>
         <v>0.13868200836820083</v>
       </c>
-      <c r="D152" s="139">
+      <c r="D153" s="139">
         <f t="shared" si="78"/>
         <v>0.13784688995215311</v>
       </c>
-      <c r="E152" s="139">
+      <c r="E153" s="139">
         <f t="shared" si="78"/>
         <v>0.13332089552238807</v>
       </c>
-      <c r="F152" s="139">
+      <c r="F153" s="139">
         <f t="shared" si="78"/>
         <v>0.14914095079232695</v>
       </c>
-      <c r="G152" s="139">
+      <c r="G153" s="139">
         <f t="shared" si="78"/>
         <v>0.17549403747870529</v>
       </c>
-      <c r="H152" s="139">
+      <c r="H153" s="139">
         <f t="shared" si="78"/>
         <v>0.16978190630048465</v>
       </c>
-      <c r="I152" s="139">
-        <f t="shared" ref="I152:J152" si="79">I141/I136</f>
+      <c r="I153" s="139">
+        <f t="shared" ref="I153:J153" si="79">I142/I137</f>
         <v>0.1672539288668321</v>
       </c>
-      <c r="J152" s="139">
+      <c r="J153" s="139">
         <f t="shared" si="79"/>
         <v>0.1645171588188348</v>
       </c>
-      <c r="K152" s="90"/>
-    </row>
-    <row r="153" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B153" s="9" t="s">
+      <c r="K153" s="90"/>
+    </row>
+    <row r="154" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B154" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="C153" s="89">
-        <f t="shared" ref="C153:H153" si="80">C143/C133</f>
+      <c r="C154" s="89">
+        <f t="shared" ref="C154:H154" si="80">C144/C134</f>
         <v>0.29841642228739002</v>
       </c>
-      <c r="D153" s="89">
+      <c r="D154" s="89">
         <f t="shared" si="80"/>
         <v>0.25298387096774194</v>
       </c>
-      <c r="E153" s="89">
+      <c r="E154" s="89">
         <f t="shared" si="80"/>
         <v>0.2257283950617284</v>
       </c>
-      <c r="F153" s="89">
+      <c r="F154" s="89">
         <f t="shared" si="80"/>
         <v>0.20261802575107296</v>
       </c>
-      <c r="G153" s="89">
+      <c r="G154" s="89">
         <f t="shared" si="80"/>
         <v>0.21781970649895177</v>
       </c>
-      <c r="H153" s="89">
+      <c r="H154" s="89">
         <f t="shared" si="80"/>
         <v>0.21972277227722772</v>
       </c>
-      <c r="I153" s="89">
-        <f t="shared" ref="I153:J153" si="81">I143/I133</f>
+      <c r="I154" s="89">
+        <f t="shared" ref="I154:J154" si="81">I144/I134</f>
         <v>0.18123339658444024</v>
       </c>
-      <c r="J153" s="89">
+      <c r="J154" s="89">
         <f t="shared" si="81"/>
         <v>0.14948672566371682</v>
       </c>
     </row>
-    <row r="154" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B155" s="94"/>
+    <row r="155" spans="1:14" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B156" s="94"/>
+    </row>
+    <row r="157" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B157" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="C157" s="14"/>
+      <c r="D157" s="14"/>
+      <c r="E157" s="14"/>
+      <c r="F157" s="14"/>
+      <c r="G157" s="14"/>
+      <c r="H157" s="14"/>
+      <c r="I157" s="14"/>
+      <c r="J157" s="14"/>
+      <c r="N157" s="14"/>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B158" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C158" s="168">
+        <f>C47</f>
+        <v>0</v>
+      </c>
+      <c r="D158" s="168">
+        <f t="shared" ref="D158:J158" si="82">D47</f>
+        <v>0</v>
+      </c>
+      <c r="E158" s="168">
+        <f t="shared" si="82"/>
+        <v>54656</v>
+      </c>
+      <c r="F158" s="168">
+        <f t="shared" si="82"/>
+        <v>54533</v>
+      </c>
+      <c r="G158" s="168">
+        <f t="shared" si="82"/>
+        <v>93843</v>
+      </c>
+      <c r="H158" s="168">
+        <f t="shared" si="82"/>
+        <v>93257</v>
+      </c>
+      <c r="I158" s="168">
+        <f t="shared" si="82"/>
+        <v>93779</v>
+      </c>
+      <c r="J158" s="168">
+        <f t="shared" si="82"/>
+        <v>91873</v>
+      </c>
+      <c r="N158" s="168">
+        <f>J158</f>
+        <v>91873</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B159" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C159" s="168">
+        <f>C25+C26</f>
+        <v>0</v>
+      </c>
+      <c r="D159" s="168">
+        <f t="shared" ref="D159:J159" si="83">D25+D26</f>
+        <v>0</v>
+      </c>
+      <c r="E159" s="168">
+        <f t="shared" si="83"/>
+        <v>877645</v>
+      </c>
+      <c r="F159" s="168">
+        <f t="shared" si="83"/>
+        <v>999280</v>
+      </c>
+      <c r="G159" s="168">
+        <f t="shared" si="83"/>
+        <v>1097883</v>
+      </c>
+      <c r="H159" s="168">
+        <f t="shared" si="83"/>
+        <v>1121454</v>
+      </c>
+      <c r="I159" s="168">
+        <f t="shared" si="83"/>
+        <v>1140467</v>
+      </c>
+      <c r="J159" s="168">
+        <f t="shared" si="83"/>
+        <v>1251610</v>
+      </c>
+      <c r="N159" s="168">
+        <f>J159</f>
+        <v>1251610</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B160" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C160" s="168">
+        <f>C47*Overview!$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="D160" s="168">
+        <f>D47*Overview!$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="E160" s="168">
+        <f>E47*Overview!$C$4</f>
+        <v>3825.9200000000005</v>
+      </c>
+      <c r="F160" s="168">
+        <f>F47*Overview!$C$4</f>
+        <v>3817.3100000000004</v>
+      </c>
+      <c r="G160" s="168">
+        <f>G47*Overview!$C$4</f>
+        <v>6569.01</v>
+      </c>
+      <c r="H160" s="168">
+        <f>H47*Overview!$C$4</f>
+        <v>6527.9900000000007</v>
+      </c>
+      <c r="I160" s="168">
+        <f>I47*Overview!$C$4</f>
+        <v>6564.5300000000007</v>
+      </c>
+      <c r="J160" s="168">
+        <f>J47*Overview!$C$4</f>
+        <v>6431.1100000000006</v>
+      </c>
+      <c r="N160" s="168">
+        <f>J160</f>
+        <v>6431.1100000000006</v>
+      </c>
+    </row>
+    <row r="161" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B161" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="C161" s="168"/>
+      <c r="D161" s="168"/>
+      <c r="E161" s="168"/>
+      <c r="F161" s="168"/>
+      <c r="G161" s="168"/>
+      <c r="H161" s="168"/>
+      <c r="I161" s="168"/>
+      <c r="J161" s="168"/>
+      <c r="N161" s="168">
+        <f>N120-N160</f>
+        <v>7572.8899999999994</v>
+      </c>
+    </row>
+    <row r="162" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B162" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C162" s="168">
+        <f>C12+C160</f>
+        <v>18700</v>
+      </c>
+      <c r="D162" s="168">
+        <f t="shared" ref="D162:J162" si="84">D12+D160</f>
+        <v>13574</v>
+      </c>
+      <c r="E162" s="168">
+        <f t="shared" si="84"/>
+        <v>17707.920000000002</v>
+      </c>
+      <c r="F162" s="168">
+        <f t="shared" si="84"/>
+        <v>27411.31</v>
+      </c>
+      <c r="G162" s="168">
+        <f t="shared" si="84"/>
+        <v>39932.01</v>
+      </c>
+      <c r="H162" s="168">
+        <f t="shared" si="84"/>
+        <v>41686.99</v>
+      </c>
+      <c r="I162" s="168">
+        <f t="shared" si="84"/>
+        <v>50018.53</v>
+      </c>
+      <c r="J162" s="168">
+        <f t="shared" si="84"/>
+        <v>50958.11</v>
+      </c>
+      <c r="N162" s="168">
+        <f>N12+N160-N161</f>
+        <v>155361.21999999997</v>
+      </c>
+    </row>
+    <row r="163" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B163" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C163" s="195">
+        <f>C158+C55-C159</f>
+        <v>0</v>
+      </c>
+      <c r="D163" s="195">
+        <f t="shared" ref="D163:J163" si="85">D158+D55-D159</f>
+        <v>0</v>
+      </c>
+      <c r="E163" s="195">
+        <f t="shared" si="85"/>
+        <v>1561</v>
+      </c>
+      <c r="F163" s="195">
+        <f t="shared" si="85"/>
+        <v>-50921</v>
+      </c>
+      <c r="G163" s="195">
+        <f t="shared" si="85"/>
+        <v>-27009</v>
+      </c>
+      <c r="H163" s="195">
+        <f t="shared" si="85"/>
+        <v>279342</v>
+      </c>
+      <c r="I163" s="195">
+        <f t="shared" si="85"/>
+        <v>300318</v>
+      </c>
+      <c r="J163" s="195">
+        <f t="shared" si="85"/>
+        <v>232027</v>
+      </c>
+      <c r="N163" s="195">
+        <f>J163</f>
+        <v>232027</v>
+      </c>
+    </row>
+    <row r="164" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B164" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C164" s="195"/>
+      <c r="D164" s="195"/>
+      <c r="E164" s="195"/>
+      <c r="F164" s="195"/>
+      <c r="G164" s="195"/>
+      <c r="H164" s="195"/>
+      <c r="I164" s="195"/>
+      <c r="J164" s="195"/>
+      <c r="N164" s="195">
+        <f>N162*(1-0.21)</f>
+        <v>122735.36379999998</v>
+      </c>
+    </row>
+    <row r="165" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B165" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="C165" s="195">
+        <f>C162+C120+C60</f>
+        <v>23768</v>
+      </c>
+      <c r="D165" s="195">
+        <f t="shared" ref="D165:J165" si="86">D162+D120+D60</f>
+        <v>18717</v>
+      </c>
+      <c r="E165" s="195">
+        <f t="shared" si="86"/>
+        <v>24509.920000000002</v>
+      </c>
+      <c r="F165" s="195">
+        <f t="shared" si="86"/>
+        <v>33301.31</v>
+      </c>
+      <c r="G165" s="195">
+        <f t="shared" si="86"/>
+        <v>46326.01</v>
+      </c>
+      <c r="H165" s="195">
+        <f t="shared" si="86"/>
+        <v>48836.99</v>
+      </c>
+      <c r="I165" s="195">
+        <f t="shared" si="86"/>
+        <v>57829.53</v>
+      </c>
+      <c r="J165" s="195">
+        <f t="shared" si="86"/>
+        <v>58599.11</v>
+      </c>
+      <c r="N165" s="195">
+        <f>N162+N120+N60</f>
+        <v>184357.21999999997</v>
+      </c>
+    </row>
+    <row r="167" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B167" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16906,7 +17694,7 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="J49 J110 J40 N5:N6 N8:N10 N12:N20 J145 N91:N94 N60:N89" formulaRange="1"/>
+    <ignoredError sqref="J49 J110 J40 N5:N6 N8:N10 N12:N20 J146 N91:N94 N60:N89 N119:N120" formulaRange="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -22480,36 +23268,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="222" t="s">
+      <c r="C2" s="224" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="222"/>
-      <c r="E2" s="222"/>
-      <c r="F2" s="222"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230" t="s">
+      <c r="D2" s="224"/>
+      <c r="E2" s="224"/>
+      <c r="F2" s="224"/>
+      <c r="G2" s="225"/>
+      <c r="H2" s="226" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="222"/>
-      <c r="J2" s="222"/>
-      <c r="K2" s="222"/>
-      <c r="L2" s="222"/>
+      <c r="I2" s="224"/>
+      <c r="J2" s="224"/>
+      <c r="K2" s="224"/>
+      <c r="L2" s="224"/>
       <c r="O2" s="92"/>
-      <c r="S2" s="222" t="s">
+      <c r="S2" s="224" t="s">
         <v>176</v>
       </c>
-      <c r="T2" s="222"/>
-      <c r="U2" s="222"/>
-      <c r="V2" s="222"/>
-      <c r="W2" s="222"/>
-      <c r="X2" s="222"/>
-      <c r="Y2" s="222"/>
-      <c r="Z2" s="222"/>
-      <c r="AA2" s="222" t="s">
+      <c r="T2" s="224"/>
+      <c r="U2" s="224"/>
+      <c r="V2" s="224"/>
+      <c r="W2" s="224"/>
+      <c r="X2" s="224"/>
+      <c r="Y2" s="224"/>
+      <c r="Z2" s="224"/>
+      <c r="AA2" s="224" t="s">
         <v>177</v>
       </c>
-      <c r="AB2" s="222"/>
-      <c r="AC2" s="222"/>
+      <c r="AB2" s="224"/>
+      <c r="AC2" s="224"/>
       <c r="AE2" s="128" t="s">
         <v>85</v>
       </c>
@@ -22520,32 +23308,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="226" t="s">
+      <c r="C4" s="223" t="s">
         <v>185</v>
       </c>
-      <c r="D4" s="226"/>
-      <c r="E4" s="226"/>
-      <c r="F4" s="226"/>
-      <c r="G4" s="226"/>
-      <c r="H4" s="226"/>
-      <c r="I4" s="226"/>
-      <c r="J4" s="226"/>
-      <c r="K4" s="226"/>
-      <c r="L4" s="226"/>
+      <c r="D4" s="223"/>
+      <c r="E4" s="223"/>
+      <c r="F4" s="223"/>
+      <c r="G4" s="223"/>
+      <c r="H4" s="223"/>
+      <c r="I4" s="223"/>
+      <c r="J4" s="223"/>
+      <c r="K4" s="223"/>
+      <c r="L4" s="223"/>
       <c r="O4" s="92"/>
-      <c r="S4" s="227" t="s">
+      <c r="S4" s="231" t="s">
         <v>185</v>
       </c>
-      <c r="T4" s="228"/>
-      <c r="U4" s="228"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="228"/>
-      <c r="X4" s="228"/>
-      <c r="Y4" s="228"/>
-      <c r="Z4" s="228"/>
-      <c r="AA4" s="228"/>
-      <c r="AB4" s="228"/>
-      <c r="AC4" s="228"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="232"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="232"/>
+      <c r="Y4" s="232"/>
+      <c r="Z4" s="232"/>
+      <c r="AA4" s="232"/>
+      <c r="AB4" s="232"/>
+      <c r="AC4" s="232"/>
       <c r="AE4" s="140" t="s">
         <v>210</v>
       </c>
@@ -22645,27 +23433,27 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="str">
-        <f>'Statement Y'!B150</f>
+        <f>'Statement Y'!B151</f>
         <v>Subscription</v>
       </c>
       <c r="C6" s="107">
-        <f>'Statement Y'!D150</f>
+        <f>'Statement Y'!D151</f>
         <v>180698</v>
       </c>
       <c r="D6" s="107">
-        <f>'Statement Y'!E150</f>
+        <f>'Statement Y'!E151</f>
         <v>273507</v>
       </c>
       <c r="E6" s="107">
-        <f>'Statement Y'!F150</f>
+        <f>'Statement Y'!F151</f>
         <v>404684</v>
       </c>
       <c r="F6" s="107">
-        <f>'Statement Y'!G150</f>
+        <f>'Statement Y'!G151</f>
         <v>607531</v>
       </c>
       <c r="G6" s="110">
-        <f>'Statement Y'!H150</f>
+        <f>'Statement Y'!H151</f>
         <v>873442</v>
       </c>
       <c r="H6" s="108">
@@ -22696,39 +23484,39 @@
         <v>190</v>
       </c>
       <c r="R6" s="1" t="str">
-        <f>'Statement Q'!B140</f>
+        <f>'Statement Q'!B141</f>
         <v>Subscription</v>
       </c>
       <c r="S6" s="107">
-        <f>'Statement Q'!C140</f>
+        <f>'Statement Q'!C141</f>
         <v>143909</v>
       </c>
       <c r="T6" s="107">
-        <f>'Statement Q'!D140</f>
+        <f>'Statement Q'!D141</f>
         <v>157617</v>
       </c>
       <c r="U6" s="107">
-        <f>'Statement Q'!E140</f>
+        <f>'Statement Q'!E141</f>
         <v>174317</v>
       </c>
       <c r="V6" s="107">
-        <f>'Statement Q'!F140</f>
+        <f>'Statement Q'!F141</f>
         <v>190987</v>
       </c>
       <c r="W6" s="107">
-        <f>'Statement Q'!G140</f>
+        <f>'Statement Q'!G141</f>
         <v>210678</v>
       </c>
       <c r="X6" s="107">
-        <f>'Statement Q'!H140</f>
+        <f>'Statement Q'!H141</f>
         <v>229491</v>
       </c>
       <c r="Y6" s="107">
-        <f>'Statement Q'!I140</f>
+        <f>'Statement Q'!I141</f>
         <v>242286</v>
       </c>
       <c r="Z6" s="110">
-        <f>'Statement Q'!J140</f>
+        <f>'Statement Q'!J141</f>
         <v>250908</v>
       </c>
       <c r="AA6" s="108">
@@ -22744,27 +23532,27 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="str">
-        <f>'Statement Y'!B151</f>
+        <f>'Statement Y'!B152</f>
         <v>Advertising</v>
       </c>
       <c r="C7" s="107">
-        <f>'Statement Y'!D151</f>
+        <f>'Statement Y'!D152</f>
         <v>38501</v>
       </c>
       <c r="D7" s="107">
-        <f>'Statement Y'!E151</f>
+        <f>'Statement Y'!E152</f>
         <v>44731</v>
       </c>
       <c r="E7" s="107">
-        <f>'Statement Y'!F151</f>
+        <f>'Statement Y'!F152</f>
         <v>49858</v>
       </c>
       <c r="F7" s="107">
-        <f>'Statement Y'!G151</f>
+        <f>'Statement Y'!G152</f>
         <v>54907</v>
       </c>
       <c r="G7" s="110">
-        <f>'Statement Y'!H151</f>
+        <f>'Statement Y'!H152</f>
         <v>79725</v>
       </c>
       <c r="H7" s="108">
@@ -22795,39 +23583,39 @@
         <v>197</v>
       </c>
       <c r="R7" s="1" t="str">
-        <f>'Statement Q'!B141</f>
+        <f>'Statement Q'!B142</f>
         <v>Advertising</v>
       </c>
       <c r="S7" s="107">
-        <f>'Statement Q'!C141</f>
+        <f>'Statement Q'!C142</f>
         <v>13258</v>
       </c>
       <c r="T7" s="107">
-        <f>'Statement Q'!D141</f>
+        <f>'Statement Q'!D142</f>
         <v>14405</v>
       </c>
       <c r="U7" s="107">
-        <f>'Statement Q'!E141</f>
+        <f>'Statement Q'!E142</f>
         <v>14292</v>
       </c>
       <c r="V7" s="107">
-        <f>'Statement Q'!F141</f>
+        <f>'Statement Q'!F142</f>
         <v>17882</v>
       </c>
       <c r="W7" s="107">
-        <f>'Statement Q'!G141</f>
+        <f>'Statement Q'!G142</f>
         <v>20603</v>
       </c>
       <c r="X7" s="107">
-        <f>'Statement Q'!H141</f>
+        <f>'Statement Q'!H142</f>
         <v>21019</v>
       </c>
       <c r="Y7" s="107">
-        <f>'Statement Q'!I141</f>
+        <f>'Statement Q'!I142</f>
         <v>20221</v>
       </c>
       <c r="Z7" s="110">
-        <f>'Statement Q'!J141</f>
+        <f>'Statement Q'!J142</f>
         <v>20614</v>
       </c>
       <c r="AA7" s="108">
@@ -22843,27 +23631,27 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="str">
-        <f>'Statement Y'!B152</f>
+        <f>'Statement Y'!B153</f>
         <v>English test</v>
       </c>
       <c r="C8" s="107">
-        <f>'Statement Y'!D152</f>
+        <f>'Statement Y'!D153</f>
         <v>24658</v>
       </c>
       <c r="D8" s="107">
-        <f>'Statement Y'!E152</f>
+        <f>'Statement Y'!E153</f>
         <v>32718</v>
       </c>
       <c r="E8" s="107">
-        <f>'Statement Y'!F152</f>
+        <f>'Statement Y'!F153</f>
         <v>41212</v>
       </c>
       <c r="F8" s="107">
-        <f>'Statement Y'!G152</f>
+        <f>'Statement Y'!G153</f>
         <v>45640</v>
       </c>
       <c r="G8" s="110">
-        <f>'Statement Y'!H152</f>
+        <f>'Statement Y'!H153</f>
         <v>42006</v>
       </c>
       <c r="H8" s="108">
@@ -22894,39 +23682,39 @@
         <v>187</v>
       </c>
       <c r="R8" s="1" t="str">
-        <f>'Statement Q'!B142</f>
+        <f>'Statement Q'!B143</f>
         <v>English test</v>
       </c>
       <c r="S8" s="107">
-        <f>'Statement Q'!C142</f>
+        <f>'Statement Q'!C143</f>
         <v>10698</v>
       </c>
       <c r="T8" s="107">
-        <f>'Statement Q'!D142</f>
+        <f>'Statement Q'!D143</f>
         <v>10772</v>
       </c>
       <c r="U8" s="107">
-        <f>'Statement Q'!E142</f>
+        <f>'Statement Q'!E143</f>
         <v>11415</v>
       </c>
       <c r="V8" s="107">
-        <f>'Statement Q'!F142</f>
+        <f>'Statement Q'!F143</f>
         <v>11986</v>
       </c>
       <c r="W8" s="107">
-        <f>'Statement Q'!G142</f>
+        <f>'Statement Q'!G143</f>
         <v>10088</v>
       </c>
       <c r="X8" s="107">
-        <f>'Statement Q'!H142</f>
+        <f>'Statement Q'!H143</f>
         <v>9649</v>
       </c>
       <c r="Y8" s="107">
-        <f>'Statement Q'!I142</f>
+        <f>'Statement Q'!I143</f>
         <v>10283</v>
       </c>
       <c r="Z8" s="110">
-        <f>'Statement Q'!J142</f>
+        <f>'Statement Q'!J143</f>
         <v>11317</v>
       </c>
       <c r="AA8" s="108">
@@ -22942,27 +23730,27 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="str">
-        <f>'Statement Y'!B153</f>
+        <f>'Statement Y'!B154</f>
         <v>In-App purchases</v>
       </c>
       <c r="C9" s="107">
-        <f>'Statement Y'!D153</f>
+        <f>'Statement Y'!D154</f>
         <v>6915</v>
       </c>
       <c r="D9" s="107">
-        <f>'Statement Y'!E153</f>
+        <f>'Statement Y'!E154</f>
         <v>18539</v>
       </c>
       <c r="E9" s="107">
-        <f>'Statement Y'!F153</f>
+        <f>'Statement Y'!F154</f>
         <v>34673</v>
       </c>
       <c r="F9" s="107">
-        <f>'Statement Y'!G153</f>
+        <f>'Statement Y'!G154</f>
         <v>38653</v>
       </c>
       <c r="G9" s="110">
-        <f>'Statement Y'!H153</f>
+        <f>'Statement Y'!H154</f>
         <v>40479</v>
       </c>
       <c r="H9" s="108">
@@ -22993,39 +23781,39 @@
         <v>188</v>
       </c>
       <c r="R9" s="1" t="str">
-        <f>'Statement Q'!B143</f>
+        <f>'Statement Q'!B144</f>
         <v>In-App purchases</v>
       </c>
       <c r="S9" s="107">
-        <f>'Statement Q'!C143</f>
+        <f>'Statement Q'!C144</f>
         <v>10176</v>
       </c>
       <c r="T9" s="107">
-        <f>'Statement Q'!D143</f>
+        <f>'Statement Q'!D144</f>
         <v>9411</v>
       </c>
       <c r="U9" s="107">
-        <f>'Statement Q'!E143</f>
+        <f>'Statement Q'!E144</f>
         <v>9142</v>
       </c>
       <c r="V9" s="107">
-        <f>'Statement Q'!F143</f>
+        <f>'Statement Q'!F144</f>
         <v>9442</v>
       </c>
       <c r="W9" s="107">
-        <f>'Statement Q'!G143</f>
+        <f>'Statement Q'!G144</f>
         <v>10390</v>
       </c>
       <c r="X9" s="107">
-        <f>'Statement Q'!H143</f>
+        <f>'Statement Q'!H144</f>
         <v>11096</v>
       </c>
       <c r="Y9" s="107">
-        <f>'Statement Q'!I143</f>
+        <f>'Statement Q'!I144</f>
         <v>9551</v>
       </c>
       <c r="Z9" s="110">
-        <f>'Statement Q'!J143</f>
+        <f>'Statement Q'!J144</f>
         <v>8446</v>
       </c>
       <c r="AA9" s="108">
@@ -23041,27 +23829,27 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="str">
-        <f>'Statement Y'!B154</f>
+        <f>'Statement Y'!B155</f>
         <v>Other</v>
       </c>
       <c r="C10" s="107">
-        <f>'Statement Y'!D154</f>
+        <f>'Statement Y'!D155</f>
         <v>79</v>
       </c>
       <c r="D10" s="107">
-        <f>'Statement Y'!E154</f>
+        <f>'Statement Y'!E155</f>
         <v>625</v>
       </c>
       <c r="E10" s="107">
-        <f>'Statement Y'!F154</f>
+        <f>'Statement Y'!F155</f>
         <v>682</v>
       </c>
       <c r="F10" s="107">
-        <f>'Statement Y'!G154</f>
+        <f>'Statement Y'!G155</f>
         <v>1293</v>
       </c>
       <c r="G10" s="110">
-        <f>'Statement Y'!H154</f>
+        <f>'Statement Y'!H155</f>
         <v>1937</v>
       </c>
       <c r="H10" s="108">
@@ -23092,39 +23880,39 @@
         <v>175</v>
       </c>
       <c r="R10" s="1" t="str">
-        <f>'Statement Q'!B144</f>
+        <f>'Statement Q'!B145</f>
         <v>Other</v>
       </c>
       <c r="S10" s="107">
-        <f>'Statement Q'!C144</f>
+        <f>'Statement Q'!C145</f>
         <v>286</v>
       </c>
       <c r="T10" s="107">
-        <f>'Statement Q'!D144</f>
+        <f>'Statement Q'!D145</f>
         <v>389</v>
       </c>
       <c r="U10" s="107">
-        <f>'Statement Q'!E144</f>
+        <f>'Statement Q'!E145</f>
         <v>384</v>
       </c>
       <c r="V10" s="107">
-        <f>'Statement Q'!F144</f>
+        <f>'Statement Q'!F145</f>
         <v>446</v>
       </c>
       <c r="W10" s="107">
-        <f>'Statement Q'!G144</f>
+        <f>'Statement Q'!G145</f>
         <v>506</v>
       </c>
       <c r="X10" s="107">
-        <f>'Statement Q'!H144</f>
+        <f>'Statement Q'!H145</f>
         <v>458</v>
       </c>
       <c r="Y10" s="107">
-        <f>'Statement Q'!I144</f>
+        <f>'Statement Q'!I145</f>
         <v>527</v>
       </c>
       <c r="Z10" s="110">
-        <f>'Statement Q'!J144</f>
+        <f>'Statement Q'!J145</f>
         <v>682</v>
       </c>
       <c r="AA10" s="108">
@@ -23140,27 +23928,27 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="str">
-        <f>'Statement Y'!B155</f>
+        <f>'Statement Y'!B156</f>
         <v>Total Non-Subscription</v>
       </c>
       <c r="C11" s="107">
-        <f>'Statement Y'!D155</f>
+        <f>'Statement Y'!D156</f>
         <v>70153</v>
       </c>
       <c r="D11" s="107">
-        <f>'Statement Y'!E155</f>
+        <f>'Statement Y'!E156</f>
         <v>96613</v>
       </c>
       <c r="E11" s="107">
-        <f>'Statement Y'!F155</f>
+        <f>'Statement Y'!F156</f>
         <v>126425</v>
       </c>
       <c r="F11" s="107">
-        <f>'Statement Y'!G155</f>
+        <f>'Statement Y'!G156</f>
         <v>140493</v>
       </c>
       <c r="G11" s="110">
-        <f>'Statement Y'!H155</f>
+        <f>'Statement Y'!H156</f>
         <v>164147</v>
       </c>
       <c r="H11" s="108">
@@ -23186,39 +23974,39 @@
       <c r="O11" s="92"/>
       <c r="Q11" s="93"/>
       <c r="R11" s="1" t="str">
-        <f>'Statement Q'!B145</f>
+        <f>'Statement Q'!B146</f>
         <v>Total Non-Subscription</v>
       </c>
       <c r="S11" s="107">
-        <f>'Statement Q'!C145</f>
+        <f>'Statement Q'!C146</f>
         <v>34418</v>
       </c>
       <c r="T11" s="107">
-        <f>'Statement Q'!D145</f>
+        <f>'Statement Q'!D146</f>
         <v>34977</v>
       </c>
       <c r="U11" s="107">
-        <f>'Statement Q'!E145</f>
+        <f>'Statement Q'!E146</f>
         <v>35233</v>
       </c>
       <c r="V11" s="107">
-        <f>'Statement Q'!F145</f>
+        <f>'Statement Q'!F146</f>
         <v>39756</v>
       </c>
       <c r="W11" s="107">
-        <f>'Statement Q'!G145</f>
+        <f>'Statement Q'!G146</f>
         <v>41587</v>
       </c>
       <c r="X11" s="107">
-        <f>'Statement Q'!H145</f>
+        <f>'Statement Q'!H146</f>
         <v>42222</v>
       </c>
       <c r="Y11" s="107">
-        <f>'Statement Q'!I145</f>
+        <f>'Statement Q'!I146</f>
         <v>40582</v>
       </c>
       <c r="Z11" s="110">
-        <f>'Statement Q'!J145</f>
+        <f>'Statement Q'!J146</f>
         <v>41059</v>
       </c>
       <c r="AA11" s="108">
@@ -23341,33 +24129,33 @@
       <c r="Q13" s="93"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C14" s="226" t="s">
+      <c r="C14" s="223" t="s">
         <v>191</v>
       </c>
-      <c r="D14" s="226"/>
-      <c r="E14" s="226"/>
-      <c r="F14" s="226"/>
-      <c r="G14" s="226"/>
-      <c r="H14" s="226"/>
-      <c r="I14" s="226"/>
-      <c r="J14" s="226"/>
-      <c r="K14" s="226"/>
-      <c r="L14" s="226"/>
+      <c r="D14" s="223"/>
+      <c r="E14" s="223"/>
+      <c r="F14" s="223"/>
+      <c r="G14" s="223"/>
+      <c r="H14" s="223"/>
+      <c r="I14" s="223"/>
+      <c r="J14" s="223"/>
+      <c r="K14" s="223"/>
+      <c r="L14" s="223"/>
       <c r="O14" s="92"/>
       <c r="Q14" s="93"/>
-      <c r="S14" s="227" t="s">
+      <c r="S14" s="231" t="s">
         <v>191</v>
       </c>
-      <c r="T14" s="228"/>
-      <c r="U14" s="228"/>
-      <c r="V14" s="228"/>
-      <c r="W14" s="228"/>
-      <c r="X14" s="228"/>
-      <c r="Y14" s="228"/>
-      <c r="Z14" s="228"/>
-      <c r="AA14" s="228"/>
-      <c r="AB14" s="228"/>
-      <c r="AC14" s="228"/>
+      <c r="T14" s="232"/>
+      <c r="U14" s="232"/>
+      <c r="V14" s="232"/>
+      <c r="W14" s="232"/>
+      <c r="X14" s="232"/>
+      <c r="Y14" s="232"/>
+      <c r="Z14" s="232"/>
+      <c r="AA14" s="232"/>
+      <c r="AB14" s="232"/>
+      <c r="AC14" s="232"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B15" s="7" t="s">
@@ -24060,33 +24848,33 @@
       <c r="Q24" s="93"/>
     </row>
     <row r="25" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C25" s="226" t="s">
+      <c r="C25" s="223" t="s">
         <v>193</v>
       </c>
-      <c r="D25" s="226"/>
-      <c r="E25" s="226"/>
-      <c r="F25" s="226"/>
-      <c r="G25" s="226"/>
-      <c r="H25" s="226"/>
-      <c r="I25" s="226"/>
-      <c r="J25" s="226"/>
-      <c r="K25" s="226"/>
-      <c r="L25" s="226"/>
+      <c r="D25" s="223"/>
+      <c r="E25" s="223"/>
+      <c r="F25" s="223"/>
+      <c r="G25" s="223"/>
+      <c r="H25" s="223"/>
+      <c r="I25" s="223"/>
+      <c r="J25" s="223"/>
+      <c r="K25" s="223"/>
+      <c r="L25" s="223"/>
       <c r="O25" s="92"/>
       <c r="Q25" s="93"/>
-      <c r="S25" s="227" t="s">
+      <c r="S25" s="231" t="s">
         <v>193</v>
       </c>
-      <c r="T25" s="228"/>
-      <c r="U25" s="228"/>
-      <c r="V25" s="228"/>
-      <c r="W25" s="228"/>
-      <c r="X25" s="228"/>
-      <c r="Y25" s="228"/>
-      <c r="Z25" s="228"/>
-      <c r="AA25" s="228"/>
-      <c r="AB25" s="228"/>
-      <c r="AC25" s="228"/>
+      <c r="T25" s="232"/>
+      <c r="U25" s="232"/>
+      <c r="V25" s="232"/>
+      <c r="W25" s="232"/>
+      <c r="X25" s="232"/>
+      <c r="Y25" s="232"/>
+      <c r="Z25" s="232"/>
+      <c r="AA25" s="232"/>
+      <c r="AB25" s="232"/>
+      <c r="AC25" s="232"/>
       <c r="AE25" s="140" t="str">
         <f>AE4</f>
         <v>Q1-Q2-Q3</v>
@@ -24349,23 +25137,23 @@
         <v>157</v>
       </c>
       <c r="C29" s="114">
-        <f>'Statement Y'!D143</f>
+        <f>'Statement Y'!D144</f>
         <v>9600</v>
       </c>
       <c r="D29" s="114">
-        <f>'Statement Y'!E143</f>
+        <f>'Statement Y'!E144</f>
         <v>16300</v>
       </c>
       <c r="E29" s="114">
-        <f>'Statement Y'!F143</f>
+        <f>'Statement Y'!F144</f>
         <v>26900</v>
       </c>
       <c r="F29" s="114">
-        <f>'Statement Y'!G143</f>
+        <f>'Statement Y'!G144</f>
         <v>40500</v>
       </c>
       <c r="G29" s="122">
-        <f>'Statement Y'!H143</f>
+        <f>'Statement Y'!H144</f>
         <v>52700</v>
       </c>
       <c r="H29" s="20">
@@ -24399,35 +25187,35 @@
         <v>157</v>
       </c>
       <c r="S29" s="114">
-        <f>'Statement Q'!C133</f>
+        <f>'Statement Q'!C134</f>
         <v>34100</v>
       </c>
       <c r="T29" s="114">
-        <f>'Statement Q'!D133</f>
+        <f>'Statement Q'!D134</f>
         <v>37200</v>
       </c>
       <c r="U29" s="114">
-        <f>'Statement Q'!E133</f>
+        <f>'Statement Q'!E134</f>
         <v>40500</v>
       </c>
       <c r="V29" s="114">
-        <f>'Statement Q'!F133</f>
+        <f>'Statement Q'!F134</f>
         <v>46600</v>
       </c>
       <c r="W29" s="114">
-        <f>'Statement Q'!G133</f>
+        <f>'Statement Q'!G134</f>
         <v>47700</v>
       </c>
       <c r="X29" s="114">
-        <f>'Statement Q'!H133</f>
+        <f>'Statement Q'!H134</f>
         <v>50500</v>
       </c>
       <c r="Y29" s="114">
-        <f>'Statement Q'!I133</f>
+        <f>'Statement Q'!I134</f>
         <v>52700</v>
       </c>
       <c r="Z29" s="130">
-        <f>'Statement Q'!J133</f>
+        <f>'Statement Q'!J134</f>
         <v>56500</v>
       </c>
       <c r="AA29" s="20">
@@ -24446,23 +25234,23 @@
         <v>158</v>
       </c>
       <c r="C30" s="114">
-        <f>'Statement Y'!D144</f>
+        <f>'Statement Y'!D145</f>
         <v>40500</v>
       </c>
       <c r="D30" s="114">
-        <f>'Statement Y'!E144</f>
+        <f>'Statement Y'!E145</f>
         <v>60700</v>
       </c>
       <c r="E30" s="114">
-        <f>'Statement Y'!F144</f>
+        <f>'Statement Y'!F145</f>
         <v>88400</v>
       </c>
       <c r="F30" s="114">
-        <f>'Statement Y'!G144</f>
+        <f>'Statement Y'!G145</f>
         <v>116700</v>
       </c>
       <c r="G30" s="122">
-        <f>'Statement Y'!H144</f>
+        <f>'Statement Y'!H145</f>
         <v>133100</v>
       </c>
       <c r="H30" s="20">
@@ -24496,35 +25284,35 @@
         <v>158</v>
       </c>
       <c r="S30" s="114">
-        <f>'Statement Q'!C134</f>
+        <f>'Statement Q'!C135</f>
         <v>103600</v>
       </c>
       <c r="T30" s="114">
-        <f>'Statement Q'!D134</f>
+        <f>'Statement Q'!D135</f>
         <v>113100</v>
       </c>
       <c r="U30" s="114">
-        <f>'Statement Q'!E134</f>
+        <f>'Statement Q'!E135</f>
         <v>116700</v>
       </c>
       <c r="V30" s="114">
-        <f>'Statement Q'!F134</f>
+        <f>'Statement Q'!F135</f>
         <v>130200</v>
       </c>
       <c r="W30" s="114">
-        <f>'Statement Q'!G134</f>
+        <f>'Statement Q'!G135</f>
         <v>128300</v>
       </c>
       <c r="X30" s="114">
-        <f>'Statement Q'!H134</f>
+        <f>'Statement Q'!H135</f>
         <v>135300</v>
       </c>
       <c r="Y30" s="114">
-        <f>'Statement Q'!I134</f>
+        <f>'Statement Q'!I135</f>
         <v>133100</v>
       </c>
       <c r="Z30" s="130">
-        <f>'Statement Q'!J134</f>
+        <f>'Statement Q'!J135</f>
         <v>137800</v>
       </c>
       <c r="AA30" s="20">
@@ -24699,23 +25487,23 @@
         <v>196</v>
       </c>
       <c r="C33" s="135">
-        <f>'Statement Y'!D162</f>
+        <f>'Statement Y'!D163</f>
         <v>1.0131842105263158</v>
       </c>
       <c r="D33" s="135">
-        <f>'Statement Y'!E162</f>
+        <f>'Statement Y'!E163</f>
         <v>0.79169911504424784</v>
       </c>
       <c r="E33" s="135">
-        <f>'Statement Y'!F162</f>
+        <f>'Statement Y'!F163</f>
         <v>0.60951100244498779</v>
       </c>
       <c r="F33" s="135">
-        <f>'Statement Y'!G162</f>
+        <f>'Statement Y'!G163</f>
         <v>0.51219216417910451</v>
       </c>
       <c r="G33" s="137">
-        <f>'Statement Y'!H162</f>
+        <f>'Statement Y'!H163</f>
         <v>0.65942928039702231</v>
       </c>
       <c r="H33" s="138">
@@ -24740,35 +25528,35 @@
         <v>196</v>
       </c>
       <c r="S33" s="135">
-        <f>'Statement Q'!C152</f>
+        <f>'Statement Q'!C153</f>
         <v>0.13868200836820083</v>
       </c>
       <c r="T33" s="135">
-        <f>'Statement Q'!D152</f>
+        <f>'Statement Q'!D153</f>
         <v>0.13784688995215311</v>
       </c>
       <c r="U33" s="135">
-        <f>'Statement Q'!E152</f>
+        <f>'Statement Q'!E153</f>
         <v>0.13332089552238807</v>
       </c>
       <c r="V33" s="135">
-        <f>'Statement Q'!F152</f>
+        <f>'Statement Q'!F153</f>
         <v>0.14914095079232695</v>
       </c>
       <c r="W33" s="135">
-        <f>'Statement Q'!G152</f>
+        <f>'Statement Q'!G153</f>
         <v>0.17549403747870529</v>
       </c>
       <c r="X33" s="135">
-        <f>'Statement Q'!H152</f>
+        <f>'Statement Q'!H153</f>
         <v>0.16978190630048465</v>
       </c>
       <c r="Y33" s="135">
-        <f>'Statement Q'!I152</f>
+        <f>'Statement Q'!I153</f>
         <v>0.1672539288668321</v>
       </c>
       <c r="Z33" s="136">
-        <f>'Statement Q'!J152</f>
+        <f>'Statement Q'!J153</f>
         <v>0.1645171588188348</v>
       </c>
       <c r="AA33" s="138">
@@ -24786,23 +25574,23 @@
         <v>167</v>
       </c>
       <c r="C34" s="97">
-        <f>'Statement Y'!D161</f>
+        <f>'Statement Y'!D162</f>
         <v>6.1728395061728392E-2</v>
       </c>
       <c r="D34" s="97">
-        <f>'Statement Y'!E161</f>
+        <f>'Statement Y'!E162</f>
         <v>6.919275123558484E-2</v>
       </c>
       <c r="E34" s="97">
-        <f>'Statement Y'!F161</f>
+        <f>'Statement Y'!F162</f>
         <v>7.4660633484162894E-2</v>
       </c>
       <c r="F34" s="97">
-        <f>'Statement Y'!G161</f>
+        <f>'Statement Y'!G162</f>
         <v>8.1405312767780638E-2</v>
       </c>
       <c r="G34" s="123">
-        <f>'Statement Y'!H161</f>
+        <f>'Statement Y'!H162</f>
         <v>9.1660405709992482E-2</v>
       </c>
       <c r="H34" s="91">
@@ -24837,35 +25625,35 @@
         <v>167</v>
       </c>
       <c r="S34" s="97">
-        <f>'Statement Q'!C151</f>
+        <f>'Statement Q'!C152</f>
         <v>7.7220077220077218E-2</v>
       </c>
       <c r="T34" s="97">
-        <f>'Statement Q'!D151</f>
+        <f>'Statement Q'!D152</f>
         <v>7.6038903625110524E-2</v>
       </c>
       <c r="U34" s="97">
-        <f>'Statement Q'!E151</f>
+        <f>'Statement Q'!E152</f>
         <v>8.1405312767780638E-2</v>
       </c>
       <c r="V34" s="97">
-        <f>'Statement Q'!F151</f>
+        <f>'Statement Q'!F152</f>
         <v>7.9109062980030717E-2</v>
       </c>
       <c r="W34" s="97">
-        <f>'Statement Q'!G151</f>
+        <f>'Statement Q'!G152</f>
         <v>8.4957131722525336E-2</v>
       </c>
       <c r="X34" s="97">
-        <f>'Statement Q'!H151</f>
+        <f>'Statement Q'!H152</f>
         <v>8.4996304508499626E-2</v>
       </c>
       <c r="Y34" s="97">
-        <f>'Statement Q'!I151</f>
+        <f>'Statement Q'!I152</f>
         <v>9.1660405709992482E-2</v>
       </c>
       <c r="Z34" s="132">
-        <f>'Statement Q'!J151</f>
+        <f>'Statement Q'!J152</f>
         <v>9.071117561683599E-2</v>
       </c>
       <c r="AA34" s="91">
@@ -24959,23 +25747,23 @@
         <v>199</v>
       </c>
       <c r="C36" s="96">
-        <f>'Statement Y'!D145</f>
+        <f>'Statement Y'!D146</f>
         <v>2500</v>
       </c>
       <c r="D36" s="96">
-        <f>'Statement Y'!E145</f>
+        <f>'Statement Y'!E146</f>
         <v>4200</v>
       </c>
       <c r="E36" s="96">
-        <f>'Statement Y'!F145</f>
+        <f>'Statement Y'!F146</f>
         <v>6600</v>
       </c>
       <c r="F36" s="96">
-        <f>'Statement Y'!G145</f>
+        <f>'Statement Y'!G146</f>
         <v>9500</v>
       </c>
       <c r="G36" s="124">
-        <f>'Statement Y'!H145</f>
+        <f>'Statement Y'!H146</f>
         <v>12200</v>
       </c>
       <c r="H36" s="20">
@@ -25009,35 +25797,35 @@
         <v>199</v>
       </c>
       <c r="S36" s="96">
-        <f>'Statement Q'!C135</f>
+        <f>'Statement Q'!C136</f>
         <v>8000</v>
       </c>
       <c r="T36" s="96">
-        <f>'Statement Q'!D135</f>
+        <f>'Statement Q'!D136</f>
         <v>8600</v>
       </c>
       <c r="U36" s="96">
-        <f>'Statement Q'!E135</f>
+        <f>'Statement Q'!E136</f>
         <v>9500</v>
       </c>
       <c r="V36" s="96">
-        <f>'Statement Q'!F135</f>
+        <f>'Statement Q'!F136</f>
         <v>10300</v>
       </c>
       <c r="W36" s="96">
-        <f>'Statement Q'!G135</f>
+        <f>'Statement Q'!G136</f>
         <v>10900</v>
       </c>
       <c r="X36" s="96">
-        <f>'Statement Q'!H135</f>
+        <f>'Statement Q'!H136</f>
         <v>11500</v>
       </c>
       <c r="Y36" s="96">
-        <f>'Statement Q'!I135</f>
+        <f>'Statement Q'!I136</f>
         <v>12200</v>
       </c>
       <c r="Z36" s="133">
-        <f>'Statement Q'!J135</f>
+        <f>'Statement Q'!J136</f>
         <v>12500</v>
       </c>
       <c r="AA36" s="20">
@@ -25056,23 +25844,23 @@
         <v>174</v>
       </c>
       <c r="C37" s="96">
-        <f>'Statement Y'!D146</f>
+        <f>'Statement Y'!D147</f>
         <v>38000</v>
       </c>
       <c r="D37" s="96">
-        <f>'Statement Y'!E146</f>
+        <f>'Statement Y'!E147</f>
         <v>56500</v>
       </c>
       <c r="E37" s="96">
-        <f>'Statement Y'!F146</f>
+        <f>'Statement Y'!F147</f>
         <v>81800</v>
       </c>
       <c r="F37" s="96">
-        <f>'Statement Y'!G146</f>
+        <f>'Statement Y'!G147</f>
         <v>107200</v>
       </c>
       <c r="G37" s="124">
-        <f>'Statement Y'!H146</f>
+        <f>'Statement Y'!H147</f>
         <v>120900</v>
       </c>
       <c r="H37" s="20">
@@ -25106,35 +25894,35 @@
         <v>174</v>
       </c>
       <c r="S37" s="96">
-        <f>'Statement Q'!C136</f>
+        <f>'Statement Q'!C137</f>
         <v>95600</v>
       </c>
       <c r="T37" s="96">
-        <f>'Statement Q'!D136</f>
+        <f>'Statement Q'!D137</f>
         <v>104500</v>
       </c>
       <c r="U37" s="96">
-        <f>'Statement Q'!E136</f>
+        <f>'Statement Q'!E137</f>
         <v>107200</v>
       </c>
       <c r="V37" s="96">
-        <f>'Statement Q'!F136</f>
+        <f>'Statement Q'!F137</f>
         <v>119900</v>
       </c>
       <c r="W37" s="96">
-        <f>'Statement Q'!G136</f>
+        <f>'Statement Q'!G137</f>
         <v>117400</v>
       </c>
       <c r="X37" s="96">
-        <f>'Statement Q'!H136</f>
+        <f>'Statement Q'!H137</f>
         <v>123800</v>
       </c>
       <c r="Y37" s="96">
-        <f>'Statement Q'!I136</f>
+        <f>'Statement Q'!I137</f>
         <v>120900</v>
       </c>
       <c r="Z37" s="133">
-        <f>'Statement Q'!J136</f>
+        <f>'Statement Q'!J137</f>
         <v>125300</v>
       </c>
       <c r="AA37" s="20">
@@ -25153,23 +25941,23 @@
         <v>203</v>
       </c>
       <c r="C38" s="97">
-        <f>'Statement Y'!D163</f>
+        <f>'Statement Y'!D164</f>
         <v>0.72031250000000002</v>
       </c>
       <c r="D38" s="97">
-        <f>'Statement Y'!E163</f>
+        <f>'Statement Y'!E164</f>
         <v>1.1373619631901841</v>
       </c>
       <c r="E38" s="97">
-        <f>'Statement Y'!F163</f>
+        <f>'Statement Y'!F164</f>
         <v>1.2889591078066915</v>
       </c>
       <c r="F38" s="97">
-        <f>'Statement Y'!G163</f>
+        <f>'Statement Y'!G164</f>
         <v>0.95439506172839506</v>
       </c>
       <c r="G38" s="123">
-        <f>'Statement Y'!H163</f>
+        <f>'Statement Y'!H164</f>
         <v>0.76810246679316885</v>
       </c>
       <c r="H38" s="100">
@@ -25193,35 +25981,35 @@
         <v>203</v>
       </c>
       <c r="S38" s="97">
-        <f>'Statement Q'!C153</f>
+        <f>'Statement Q'!C154</f>
         <v>0.29841642228739002</v>
       </c>
       <c r="T38" s="97">
-        <f>'Statement Q'!D153</f>
+        <f>'Statement Q'!D154</f>
         <v>0.25298387096774194</v>
       </c>
       <c r="U38" s="97">
-        <f>'Statement Q'!E153</f>
+        <f>'Statement Q'!E154</f>
         <v>0.2257283950617284</v>
       </c>
       <c r="V38" s="97">
-        <f>'Statement Q'!F153</f>
+        <f>'Statement Q'!F154</f>
         <v>0.20261802575107296</v>
       </c>
       <c r="W38" s="97">
-        <f>'Statement Q'!G153</f>
+        <f>'Statement Q'!G154</f>
         <v>0.21781970649895177</v>
       </c>
       <c r="X38" s="97">
-        <f>'Statement Q'!H153</f>
+        <f>'Statement Q'!H154</f>
         <v>0.21972277227722772</v>
       </c>
       <c r="Y38" s="97">
-        <f>'Statement Q'!I153</f>
+        <f>'Statement Q'!I154</f>
         <v>0.18123339658444024</v>
       </c>
       <c r="Z38" s="132">
-        <f>'Statement Q'!J153</f>
+        <f>'Statement Q'!J154</f>
         <v>0.14948672566371682</v>
       </c>
       <c r="AA38" s="100">
@@ -25236,23 +26024,23 @@
         <v>189</v>
       </c>
       <c r="C39" s="115">
-        <f>'Statement Y'!D159</f>
+        <f>'Statement Y'!D160</f>
         <v>72.279200000000003</v>
       </c>
       <c r="D39" s="115">
-        <f>'Statement Y'!E159</f>
+        <f>'Statement Y'!E160</f>
         <v>65.120714285714286</v>
       </c>
       <c r="E39" s="115">
-        <f>'Statement Y'!F159</f>
+        <f>'Statement Y'!F160</f>
         <v>61.315757575757573</v>
       </c>
       <c r="F39" s="115">
-        <f>'Statement Y'!G159</f>
+        <f>'Statement Y'!G160</f>
         <v>63.950631578947366</v>
       </c>
       <c r="G39" s="125">
-        <f>'Statement Y'!H159</f>
+        <f>'Statement Y'!H160</f>
         <v>71.593606557377043</v>
       </c>
       <c r="H39" s="101">
@@ -25276,35 +26064,35 @@
         <v>189</v>
       </c>
       <c r="S39" s="115">
-        <f>'Statement Q'!C149</f>
+        <f>'Statement Q'!C150</f>
         <v>17.988624999999999</v>
       </c>
       <c r="T39" s="115">
-        <f>'Statement Q'!D149</f>
+        <f>'Statement Q'!D150</f>
         <v>18.327558139534883</v>
       </c>
       <c r="U39" s="115">
-        <f>'Statement Q'!E149</f>
+        <f>'Statement Q'!E150</f>
         <v>18.349157894736841</v>
       </c>
       <c r="V39" s="115">
-        <f>'Statement Q'!F149</f>
+        <f>'Statement Q'!F150</f>
         <v>18.542427184466021</v>
       </c>
       <c r="W39" s="115">
-        <f>'Statement Q'!G149</f>
+        <f>'Statement Q'!G150</f>
         <v>19.328256880733946</v>
       </c>
       <c r="X39" s="115">
-        <f>'Statement Q'!H149</f>
+        <f>'Statement Q'!H150</f>
         <v>19.955739130434782</v>
       </c>
       <c r="Y39" s="115">
-        <f>'Statement Q'!I149</f>
+        <f>'Statement Q'!I150</f>
         <v>19.859508196721311</v>
       </c>
       <c r="Z39" s="134">
-        <f>'Statement Q'!J149</f>
+        <f>'Statement Q'!J150</f>
         <v>20.07264</v>
       </c>
       <c r="AA39" s="101">
@@ -25319,23 +26107,23 @@
         <v>166</v>
       </c>
       <c r="C40" s="97">
-        <f>'Statement Y'!D160</f>
+        <f>'Statement Y'!D161</f>
         <v>0.23703703703703705</v>
       </c>
       <c r="D40" s="97">
-        <f>'Statement Y'!E160</f>
+        <f>'Statement Y'!E161</f>
         <v>0.26853377265238881</v>
       </c>
       <c r="E40" s="97">
-        <f>'Statement Y'!F160</f>
+        <f>'Statement Y'!F161</f>
         <v>0.30429864253393663</v>
       </c>
       <c r="F40" s="97">
-        <f>'Statement Y'!G160</f>
+        <f>'Statement Y'!G161</f>
         <v>0.34704370179948585</v>
       </c>
       <c r="G40" s="123">
-        <f>'Statement Y'!H160</f>
+        <f>'Statement Y'!H161</f>
         <v>0.3959429000751315</v>
       </c>
       <c r="H40" s="91">
@@ -25363,35 +26151,35 @@
         <v>166</v>
       </c>
       <c r="S40" s="97">
-        <f>'Statement Q'!C150</f>
+        <f>'Statement Q'!C151</f>
         <v>0.32915057915057916</v>
       </c>
       <c r="T40" s="97">
-        <f>'Statement Q'!D150</f>
+        <f>'Statement Q'!D151</f>
         <v>0.32891246684350134</v>
       </c>
       <c r="U40" s="97">
-        <f>'Statement Q'!E150</f>
+        <f>'Statement Q'!E151</f>
         <v>0.34704370179948585</v>
       </c>
       <c r="V40" s="97">
-        <f>'Statement Q'!F150</f>
+        <f>'Statement Q'!F151</f>
         <v>0.3579109062980031</v>
       </c>
       <c r="W40" s="97">
-        <f>'Statement Q'!G150</f>
+        <f>'Statement Q'!G151</f>
         <v>0.37178487918939984</v>
       </c>
       <c r="X40" s="97">
-        <f>'Statement Q'!H150</f>
+        <f>'Statement Q'!H151</f>
         <v>0.37324464153732445</v>
       </c>
       <c r="Y40" s="97">
-        <f>'Statement Q'!I150</f>
+        <f>'Statement Q'!I151</f>
         <v>0.3959429000751315</v>
       </c>
       <c r="Z40" s="132">
-        <f>'Statement Q'!J150</f>
+        <f>'Statement Q'!J151</f>
         <v>0.41001451378809867</v>
       </c>
       <c r="AA40" s="91">
@@ -25409,32 +26197,32 @@
       <c r="O42" s="92"/>
     </row>
     <row r="43" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C43" s="226" t="s">
+      <c r="C43" s="223" t="s">
         <v>205</v>
       </c>
-      <c r="D43" s="226"/>
-      <c r="E43" s="226"/>
-      <c r="F43" s="226"/>
-      <c r="G43" s="226"/>
-      <c r="H43" s="226"/>
-      <c r="I43" s="226"/>
-      <c r="J43" s="226"/>
-      <c r="K43" s="226"/>
-      <c r="L43" s="226"/>
+      <c r="D43" s="223"/>
+      <c r="E43" s="223"/>
+      <c r="F43" s="223"/>
+      <c r="G43" s="223"/>
+      <c r="H43" s="223"/>
+      <c r="I43" s="223"/>
+      <c r="J43" s="223"/>
+      <c r="K43" s="223"/>
+      <c r="L43" s="223"/>
       <c r="O43" s="92"/>
-      <c r="S43" s="227" t="s">
+      <c r="S43" s="231" t="s">
         <v>205</v>
       </c>
-      <c r="T43" s="228"/>
-      <c r="U43" s="228"/>
-      <c r="V43" s="228"/>
-      <c r="W43" s="228"/>
-      <c r="X43" s="228"/>
-      <c r="Y43" s="228"/>
-      <c r="Z43" s="228"/>
-      <c r="AA43" s="228"/>
-      <c r="AB43" s="228"/>
-      <c r="AC43" s="228"/>
+      <c r="T43" s="232"/>
+      <c r="U43" s="232"/>
+      <c r="V43" s="232"/>
+      <c r="W43" s="232"/>
+      <c r="X43" s="232"/>
+      <c r="Y43" s="232"/>
+      <c r="Z43" s="232"/>
+      <c r="AA43" s="232"/>
+      <c r="AB43" s="232"/>
+      <c r="AC43" s="232"/>
     </row>
     <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B44" s="7" t="s">
@@ -26050,35 +26838,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="222" t="s">
+      <c r="C2" s="224" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="222"/>
-      <c r="E2" s="222"/>
-      <c r="F2" s="222"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230" t="s">
+      <c r="D2" s="224"/>
+      <c r="E2" s="224"/>
+      <c r="F2" s="224"/>
+      <c r="G2" s="225"/>
+      <c r="H2" s="226" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="222"/>
-      <c r="J2" s="222"/>
-      <c r="K2" s="222"/>
-      <c r="L2" s="222"/>
-      <c r="P2" s="222" t="s">
+      <c r="I2" s="224"/>
+      <c r="J2" s="224"/>
+      <c r="K2" s="224"/>
+      <c r="L2" s="224"/>
+      <c r="P2" s="224" t="s">
         <v>176</v>
       </c>
-      <c r="Q2" s="222"/>
-      <c r="R2" s="222"/>
-      <c r="S2" s="222"/>
-      <c r="T2" s="222"/>
-      <c r="U2" s="222"/>
-      <c r="V2" s="222"/>
-      <c r="W2" s="222"/>
-      <c r="X2" s="222" t="s">
+      <c r="Q2" s="224"/>
+      <c r="R2" s="224"/>
+      <c r="S2" s="224"/>
+      <c r="T2" s="224"/>
+      <c r="U2" s="224"/>
+      <c r="V2" s="224"/>
+      <c r="W2" s="224"/>
+      <c r="X2" s="224" t="s">
         <v>177</v>
       </c>
-      <c r="Y2" s="222"/>
-      <c r="Z2" s="222"/>
+      <c r="Y2" s="224"/>
+      <c r="Z2" s="224"/>
       <c r="AB2" s="128" t="s">
         <v>85</v>
       </c>
@@ -26087,31 +26875,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="226" t="s">
+      <c r="C4" s="223" t="s">
         <v>185</v>
       </c>
-      <c r="D4" s="226"/>
-      <c r="E4" s="226"/>
-      <c r="F4" s="226"/>
-      <c r="G4" s="226"/>
-      <c r="H4" s="226"/>
-      <c r="I4" s="226"/>
-      <c r="J4" s="226"/>
-      <c r="K4" s="226"/>
-      <c r="L4" s="226"/>
-      <c r="P4" s="228" t="s">
+      <c r="D4" s="223"/>
+      <c r="E4" s="223"/>
+      <c r="F4" s="223"/>
+      <c r="G4" s="223"/>
+      <c r="H4" s="223"/>
+      <c r="I4" s="223"/>
+      <c r="J4" s="223"/>
+      <c r="K4" s="223"/>
+      <c r="L4" s="223"/>
+      <c r="P4" s="232" t="s">
         <v>185</v>
       </c>
-      <c r="Q4" s="228"/>
-      <c r="R4" s="228"/>
-      <c r="S4" s="228"/>
-      <c r="T4" s="228"/>
-      <c r="U4" s="228"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="228"/>
-      <c r="X4" s="228"/>
-      <c r="Y4" s="228"/>
-      <c r="Z4" s="228"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="232"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="232"/>
+      <c r="Y4" s="232"/>
+      <c r="Z4" s="232"/>
       <c r="AB4" s="140" t="s">
         <v>210</v>
       </c>
@@ -26312,32 +27100,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="226" t="s">
+      <c r="C9" s="223" t="s">
         <v>212</v>
       </c>
-      <c r="D9" s="226"/>
-      <c r="E9" s="226"/>
-      <c r="F9" s="226"/>
-      <c r="G9" s="226"/>
-      <c r="H9" s="226"/>
-      <c r="I9" s="226"/>
-      <c r="J9" s="226"/>
-      <c r="K9" s="226"/>
-      <c r="L9" s="226"/>
+      <c r="D9" s="223"/>
+      <c r="E9" s="223"/>
+      <c r="F9" s="223"/>
+      <c r="G9" s="223"/>
+      <c r="H9" s="223"/>
+      <c r="I9" s="223"/>
+      <c r="J9" s="223"/>
+      <c r="K9" s="223"/>
+      <c r="L9" s="223"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="228" t="s">
+      <c r="P9" s="232" t="s">
         <v>217</v>
       </c>
-      <c r="Q9" s="228"/>
-      <c r="R9" s="228"/>
-      <c r="S9" s="228"/>
-      <c r="T9" s="228"/>
-      <c r="U9" s="228"/>
-      <c r="V9" s="228"/>
-      <c r="W9" s="228"/>
-      <c r="X9" s="228"/>
-      <c r="Y9" s="228"/>
-      <c r="Z9" s="228"/>
+      <c r="Q9" s="232"/>
+      <c r="R9" s="232"/>
+      <c r="S9" s="232"/>
+      <c r="T9" s="232"/>
+      <c r="U9" s="232"/>
+      <c r="V9" s="232"/>
+      <c r="W9" s="232"/>
+      <c r="X9" s="232"/>
+      <c r="Y9" s="232"/>
+      <c r="Z9" s="232"/>
       <c r="AB9" s="140" t="str">
         <f>AB4</f>
         <v>Q1-Q2-Q3</v>
@@ -26899,31 +27687,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="226" t="s">
+      <c r="C18" s="223" t="s">
         <v>215</v>
       </c>
-      <c r="D18" s="226"/>
-      <c r="E18" s="226"/>
-      <c r="F18" s="226"/>
-      <c r="G18" s="226"/>
-      <c r="H18" s="226"/>
-      <c r="I18" s="226"/>
-      <c r="J18" s="226"/>
-      <c r="K18" s="226"/>
-      <c r="L18" s="226"/>
-      <c r="P18" s="228" t="s">
+      <c r="D18" s="223"/>
+      <c r="E18" s="223"/>
+      <c r="F18" s="223"/>
+      <c r="G18" s="223"/>
+      <c r="H18" s="223"/>
+      <c r="I18" s="223"/>
+      <c r="J18" s="223"/>
+      <c r="K18" s="223"/>
+      <c r="L18" s="223"/>
+      <c r="P18" s="232" t="s">
         <v>215</v>
       </c>
-      <c r="Q18" s="228"/>
-      <c r="R18" s="228"/>
-      <c r="S18" s="228"/>
-      <c r="T18" s="228"/>
-      <c r="U18" s="228"/>
-      <c r="V18" s="228"/>
-      <c r="W18" s="228"/>
-      <c r="X18" s="228"/>
-      <c r="Y18" s="228"/>
-      <c r="Z18" s="228"/>
+      <c r="Q18" s="232"/>
+      <c r="R18" s="232"/>
+      <c r="S18" s="232"/>
+      <c r="T18" s="232"/>
+      <c r="U18" s="232"/>
+      <c r="V18" s="232"/>
+      <c r="W18" s="232"/>
+      <c r="X18" s="232"/>
+      <c r="Y18" s="232"/>
+      <c r="Z18" s="232"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -27395,60 +28183,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="104"/>
-      <c r="C3" s="222" t="s">
+      <c r="C3" s="224" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="222"/>
-      <c r="E3" s="222"/>
-      <c r="F3" s="222"/>
-      <c r="G3" s="229"/>
-      <c r="H3" s="230" t="s">
+      <c r="D3" s="224"/>
+      <c r="E3" s="224"/>
+      <c r="F3" s="224"/>
+      <c r="G3" s="225"/>
+      <c r="H3" s="226" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="222"/>
-      <c r="J3" s="222"/>
-      <c r="K3" s="222"/>
-      <c r="L3" s="222"/>
-      <c r="P3" s="231"/>
-      <c r="Q3" s="231"/>
-      <c r="R3" s="231"/>
-      <c r="S3" s="231"/>
-      <c r="T3" s="231"/>
-      <c r="U3" s="231"/>
-      <c r="V3" s="231"/>
-      <c r="W3" s="231"/>
-      <c r="X3" s="231"/>
-      <c r="Y3" s="231"/>
-      <c r="Z3" s="231"/>
+      <c r="I3" s="224"/>
+      <c r="J3" s="224"/>
+      <c r="K3" s="224"/>
+      <c r="L3" s="224"/>
+      <c r="P3" s="227"/>
+      <c r="Q3" s="227"/>
+      <c r="R3" s="227"/>
+      <c r="S3" s="227"/>
+      <c r="T3" s="227"/>
+      <c r="U3" s="227"/>
+      <c r="V3" s="227"/>
+      <c r="W3" s="227"/>
+      <c r="X3" s="227"/>
+      <c r="Y3" s="227"/>
+      <c r="Z3" s="227"/>
       <c r="AB3" s="143"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="109"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="226" t="s">
+      <c r="C5" s="223" t="s">
         <v>185</v>
       </c>
-      <c r="D5" s="226"/>
-      <c r="E5" s="226"/>
-      <c r="F5" s="226"/>
-      <c r="G5" s="226"/>
-      <c r="H5" s="226"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="226"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="226"/>
-      <c r="P5" s="231"/>
-      <c r="Q5" s="231"/>
-      <c r="R5" s="231"/>
-      <c r="S5" s="231"/>
-      <c r="T5" s="231"/>
-      <c r="U5" s="231"/>
-      <c r="V5" s="231"/>
-      <c r="W5" s="231"/>
-      <c r="X5" s="231"/>
-      <c r="Y5" s="231"/>
-      <c r="Z5" s="231"/>
+      <c r="D5" s="223"/>
+      <c r="E5" s="223"/>
+      <c r="F5" s="223"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="223"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="223"/>
+      <c r="K5" s="223"/>
+      <c r="L5" s="223"/>
+      <c r="P5" s="227"/>
+      <c r="Q5" s="227"/>
+      <c r="R5" s="227"/>
+      <c r="S5" s="227"/>
+      <c r="T5" s="227"/>
+      <c r="U5" s="227"/>
+      <c r="V5" s="227"/>
+      <c r="W5" s="227"/>
+      <c r="X5" s="227"/>
+      <c r="Y5" s="227"/>
+      <c r="Z5" s="227"/>
       <c r="AB5" s="144"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -27693,30 +28481,30 @@
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C12" s="226" t="s">
+      <c r="C12" s="223" t="s">
         <v>224</v>
       </c>
-      <c r="D12" s="226"/>
-      <c r="E12" s="226"/>
-      <c r="F12" s="226"/>
-      <c r="G12" s="226"/>
-      <c r="H12" s="226"/>
-      <c r="I12" s="226"/>
-      <c r="J12" s="226"/>
-      <c r="K12" s="226"/>
-      <c r="L12" s="226"/>
+      <c r="D12" s="223"/>
+      <c r="E12" s="223"/>
+      <c r="F12" s="223"/>
+      <c r="G12" s="223"/>
+      <c r="H12" s="223"/>
+      <c r="I12" s="223"/>
+      <c r="J12" s="223"/>
+      <c r="K12" s="223"/>
+      <c r="L12" s="223"/>
       <c r="N12" s="93"/>
-      <c r="P12" s="231"/>
-      <c r="Q12" s="231"/>
-      <c r="R12" s="231"/>
-      <c r="S12" s="231"/>
-      <c r="T12" s="231"/>
-      <c r="U12" s="231"/>
-      <c r="V12" s="231"/>
-      <c r="W12" s="231"/>
-      <c r="X12" s="231"/>
-      <c r="Y12" s="231"/>
-      <c r="Z12" s="231"/>
+      <c r="P12" s="227"/>
+      <c r="Q12" s="227"/>
+      <c r="R12" s="227"/>
+      <c r="S12" s="227"/>
+      <c r="T12" s="227"/>
+      <c r="U12" s="227"/>
+      <c r="V12" s="227"/>
+      <c r="W12" s="227"/>
+      <c r="X12" s="227"/>
+      <c r="Y12" s="227"/>
+      <c r="Z12" s="227"/>
       <c r="AB12" s="144"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -27899,18 +28687,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="226" t="s">
+      <c r="C18" s="223" t="s">
         <v>233</v>
       </c>
-      <c r="D18" s="226"/>
-      <c r="E18" s="226"/>
-      <c r="F18" s="226"/>
-      <c r="G18" s="226"/>
-      <c r="H18" s="226"/>
-      <c r="I18" s="226"/>
-      <c r="J18" s="226"/>
-      <c r="K18" s="226"/>
-      <c r="L18" s="226"/>
+      <c r="D18" s="223"/>
+      <c r="E18" s="223"/>
+      <c r="F18" s="223"/>
+      <c r="G18" s="223"/>
+      <c r="H18" s="223"/>
+      <c r="I18" s="223"/>
+      <c r="J18" s="223"/>
+      <c r="K18" s="223"/>
+      <c r="L18" s="223"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -28093,23 +28881,23 @@
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B24" s="231"/>
-      <c r="C24" s="231"/>
+      <c r="B24" s="227"/>
+      <c r="C24" s="227"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="143"/>
-      <c r="C25" s="226" t="s">
+      <c r="C25" s="223" t="s">
         <v>374</v>
       </c>
-      <c r="D25" s="226"/>
-      <c r="E25" s="226"/>
-      <c r="F25" s="226"/>
-      <c r="G25" s="226"/>
-      <c r="H25" s="226"/>
-      <c r="I25" s="226"/>
-      <c r="J25" s="226"/>
-      <c r="K25" s="226"/>
-      <c r="L25" s="226"/>
+      <c r="D25" s="223"/>
+      <c r="E25" s="223"/>
+      <c r="F25" s="223"/>
+      <c r="G25" s="223"/>
+      <c r="H25" s="223"/>
+      <c r="I25" s="223"/>
+      <c r="J25" s="223"/>
+      <c r="K25" s="223"/>
+      <c r="L25" s="223"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
@@ -28256,18 +29044,18 @@
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="143"/>
-      <c r="C31" s="226" t="s">
+      <c r="C31" s="223" t="s">
         <v>375</v>
       </c>
-      <c r="D31" s="226"/>
-      <c r="E31" s="226"/>
-      <c r="F31" s="226"/>
-      <c r="G31" s="226"/>
-      <c r="H31" s="226"/>
-      <c r="I31" s="226"/>
-      <c r="J31" s="226"/>
-      <c r="K31" s="226"/>
-      <c r="L31" s="226"/>
+      <c r="D31" s="223"/>
+      <c r="E31" s="223"/>
+      <c r="F31" s="223"/>
+      <c r="G31" s="223"/>
+      <c r="H31" s="223"/>
+      <c r="I31" s="223"/>
+      <c r="J31" s="223"/>
+      <c r="K31" s="223"/>
+      <c r="L31" s="223"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
@@ -28451,18 +29239,18 @@
       <c r="C37" s="152"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C38" s="226" t="s">
+      <c r="C38" s="223" t="s">
         <v>322</v>
       </c>
-      <c r="D38" s="226"/>
-      <c r="E38" s="226"/>
-      <c r="F38" s="226"/>
-      <c r="G38" s="226"/>
-      <c r="H38" s="226"/>
-      <c r="I38" s="226"/>
-      <c r="J38" s="226"/>
-      <c r="K38" s="226"/>
-      <c r="L38" s="226"/>
+      <c r="D38" s="223"/>
+      <c r="E38" s="223"/>
+      <c r="F38" s="223"/>
+      <c r="G38" s="223"/>
+      <c r="H38" s="223"/>
+      <c r="I38" s="223"/>
+      <c r="J38" s="223"/>
+      <c r="K38" s="223"/>
+      <c r="L38" s="223"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B39" s="7" t="s">
@@ -28726,6 +29514,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C38:L38"/>
@@ -28733,12 +29527,6 @@
     <mergeCell ref="P12:Z12"/>
     <mergeCell ref="C18:L18"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACA129B-1A81-DB46-BCAF-1F68CA979E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB28DE9-5F57-9941-9B29-0546BADE5F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="4" activeTab="14" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2278,19 +2278,7 @@
     <xf numFmtId="169" fontId="0" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2302,10 +2290,22 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2418,15 +2418,15 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="C4">
-            <v>112.06</v>
+            <v>104.96</v>
           </cell>
           <cell r="F4">
-            <v>0.89770000000000005</v>
+            <v>0.88739999999999997</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>45.95</v>
+            <v>44.55</v>
           </cell>
         </row>
       </sheetData>
@@ -3030,8 +3030,8 @@
         <v>84</v>
       </c>
       <c r="C3" s="35">
-        <f>[1]Sheet1!$C$4</f>
-        <v>112.06</v>
+        <f ca="1">[1]Sheet1!$C$4</f>
+        <v>104.96</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -3071,8 +3071,8 @@
         <v>181</v>
       </c>
       <c r="C12" s="95">
-        <f>$C$3/'Statement Q'!$N$22</f>
-        <v>12.962990378181635</v>
+        <f ca="1">$C$3/'Statement Q'!$N$22</f>
+        <v>12.141669374388222</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -3080,8 +3080,8 @@
         <v>283</v>
       </c>
       <c r="C13" s="95">
-        <f>C3/Statements!S20</f>
-        <v>31.266670276719772</v>
+        <f ca="1">C3/Statements!S20</f>
+        <v>29.28564797648141</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
@@ -3089,8 +3089,8 @@
         <v>182</v>
       </c>
       <c r="C14" s="102">
-        <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$20)</f>
-        <v>4.9830476212423234</v>
+        <f ca="1">$C$3/('Statement Q'!$N$5/'Statement Q'!$N$20)</f>
+        <v>4.667327131229646</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -3098,8 +3098,8 @@
         <v>240</v>
       </c>
       <c r="C16" s="20">
-        <f>C3*'Statement Q'!N118</f>
-        <v>5221211.58</v>
+        <f ca="1">C3*'Statement Q'!N118</f>
+        <v>4890401.2799999993</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -3124,8 +3124,8 @@
         <v>242</v>
       </c>
       <c r="C19" s="20">
-        <f>C16+C18-C17</f>
-        <v>3969601.58</v>
+        <f ca="1">C16+C18-C17</f>
+        <v>3638791.2799999993</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -3293,15 +3293,15 @@
       <c r="C51" s="108"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="224" t="s">
+      <c r="A52" s="223" t="s">
         <v>363</v>
       </c>
-      <c r="B52" s="224"/>
-      <c r="C52" s="224"/>
-      <c r="D52" s="224"/>
-      <c r="E52" s="224"/>
-      <c r="F52" s="224"/>
-      <c r="G52" s="224"/>
+      <c r="B52" s="223"/>
+      <c r="C52" s="223"/>
+      <c r="D52" s="223"/>
+      <c r="E52" s="223"/>
+      <c r="F52" s="223"/>
+      <c r="G52" s="223"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
@@ -3314,15 +3314,15 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58" s="224" t="s">
+      <c r="A58" s="223" t="s">
         <v>297</v>
       </c>
-      <c r="B58" s="224"/>
-      <c r="C58" s="224"/>
-      <c r="D58" s="224"/>
-      <c r="E58" s="224"/>
-      <c r="F58" s="224"/>
-      <c r="G58" s="224"/>
+      <c r="B58" s="223"/>
+      <c r="C58" s="223"/>
+      <c r="D58" s="223"/>
+      <c r="E58" s="223"/>
+      <c r="F58" s="223"/>
+      <c r="G58" s="223"/>
     </row>
     <row r="59" spans="1:7" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
@@ -3392,60 +3392,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="224" t="s">
+      <c r="C2" s="223" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="224"/>
-      <c r="E2" s="224"/>
-      <c r="F2" s="224"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="226" t="s">
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="230"/>
+      <c r="H2" s="231" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="224"/>
-      <c r="J2" s="224"/>
-      <c r="K2" s="224"/>
-      <c r="L2" s="224"/>
-      <c r="S2" s="227"/>
-      <c r="T2" s="227"/>
-      <c r="U2" s="227"/>
-      <c r="V2" s="227"/>
-      <c r="W2" s="227"/>
-      <c r="X2" s="227"/>
-      <c r="Y2" s="227"/>
-      <c r="Z2" s="227"/>
-      <c r="AA2" s="227"/>
-      <c r="AB2" s="227"/>
-      <c r="AC2" s="227"/>
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="223"/>
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="232"/>
+      <c r="AB2" s="232"/>
+      <c r="AC2" s="232"/>
       <c r="AE2" s="143"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="223" t="s">
+      <c r="C4" s="227" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="223"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="223"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="223"/>
-      <c r="I4" s="223"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="223"/>
-      <c r="L4" s="223"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="227"/>
-      <c r="X4" s="227"/>
-      <c r="Y4" s="227"/>
-      <c r="Z4" s="227"/>
-      <c r="AA4" s="227"/>
-      <c r="AB4" s="227"/>
-      <c r="AC4" s="227"/>
+      <c r="D4" s="227"/>
+      <c r="E4" s="227"/>
+      <c r="F4" s="227"/>
+      <c r="G4" s="227"/>
+      <c r="H4" s="227"/>
+      <c r="I4" s="227"/>
+      <c r="J4" s="227"/>
+      <c r="K4" s="227"/>
+      <c r="L4" s="227"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="232"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="232"/>
+      <c r="Y4" s="232"/>
+      <c r="Z4" s="232"/>
+      <c r="AA4" s="232"/>
+      <c r="AB4" s="232"/>
+      <c r="AC4" s="232"/>
       <c r="AE4" s="144"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -4106,18 +4106,18 @@
       <c r="AE15" s="108"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="223" t="s">
+      <c r="C18" s="227" t="s">
         <v>234</v>
       </c>
-      <c r="D18" s="223"/>
-      <c r="E18" s="223"/>
-      <c r="F18" s="223"/>
-      <c r="G18" s="223"/>
-      <c r="H18" s="223"/>
-      <c r="I18" s="223"/>
-      <c r="J18" s="223"/>
-      <c r="K18" s="223"/>
-      <c r="L18" s="223"/>
+      <c r="D18" s="227"/>
+      <c r="E18" s="227"/>
+      <c r="F18" s="227"/>
+      <c r="G18" s="227"/>
+      <c r="H18" s="227"/>
+      <c r="I18" s="227"/>
+      <c r="J18" s="227"/>
+      <c r="K18" s="227"/>
+      <c r="L18" s="227"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C19" s="62">
@@ -4201,18 +4201,18 @@
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C23" s="223" t="s">
+      <c r="C23" s="227" t="s">
         <v>326</v>
       </c>
-      <c r="D23" s="223"/>
-      <c r="E23" s="223"/>
-      <c r="F23" s="223"/>
-      <c r="G23" s="223"/>
-      <c r="H23" s="223"/>
-      <c r="I23" s="223"/>
-      <c r="J23" s="223"/>
-      <c r="K23" s="223"/>
-      <c r="L23" s="223"/>
+      <c r="D23" s="227"/>
+      <c r="E23" s="227"/>
+      <c r="F23" s="227"/>
+      <c r="G23" s="227"/>
+      <c r="H23" s="227"/>
+      <c r="I23" s="227"/>
+      <c r="J23" s="227"/>
+      <c r="K23" s="227"/>
+      <c r="L23" s="227"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B24" s="7" t="s">
@@ -4404,18 +4404,18 @@
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C30" s="223" t="s">
+      <c r="C30" s="227" t="s">
         <v>236</v>
       </c>
-      <c r="D30" s="223"/>
-      <c r="E30" s="223"/>
-      <c r="F30" s="223"/>
-      <c r="G30" s="223"/>
-      <c r="H30" s="223"/>
-      <c r="I30" s="223"/>
-      <c r="J30" s="223"/>
-      <c r="K30" s="223"/>
-      <c r="L30" s="223"/>
+      <c r="D30" s="227"/>
+      <c r="E30" s="227"/>
+      <c r="F30" s="227"/>
+      <c r="G30" s="227"/>
+      <c r="H30" s="227"/>
+      <c r="I30" s="227"/>
+      <c r="J30" s="227"/>
+      <c r="K30" s="227"/>
+      <c r="L30" s="227"/>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
@@ -4622,10 +4622,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="224" t="s">
+      <c r="B4" s="223" t="s">
         <v>253</v>
       </c>
-      <c r="C4" s="224"/>
+      <c r="C4" s="223"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4641,8 +4641,8 @@
         <v>84</v>
       </c>
       <c r="C6" s="166">
-        <f>Overview!C3</f>
-        <v>112.06</v>
+        <f ca="1">Overview!C3</f>
+        <v>104.96</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4650,8 +4650,8 @@
         <v>238</v>
       </c>
       <c r="C7" s="168">
-        <f>C5*C6</f>
-        <v>5475437.5058401404</v>
+        <f ca="1">C5*C6</f>
+        <v>5128519.7270478411</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4668,8 +4668,8 @@
         <v>255</v>
       </c>
       <c r="C9" s="191">
-        <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.5950000000000005E-2</v>
+        <f ca="1">[1]Sheet1!$C$10/1000</f>
+        <v>4.4549999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4677,8 +4677,8 @@
         <v>256</v>
       </c>
       <c r="C10" s="166">
-        <f>[1]Sheet1!$F$4</f>
-        <v>0.89770000000000005</v>
+        <f ca="1">[1]Sheet1!$F$4</f>
+        <v>0.88739999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4708,18 +4708,18 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="224" t="s">
+      <c r="B15" s="223" t="s">
         <v>259</v>
       </c>
-      <c r="C15" s="224"/>
+      <c r="C15" s="223"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>250</v>
       </c>
       <c r="C16" s="169">
-        <f>C8/(C8+C7)</f>
-        <v>1.650222309383044E-2</v>
+        <f ca="1">C8/(C8+C7)</f>
+        <v>1.7598867518910717E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4727,8 +4727,8 @@
         <v>251</v>
       </c>
       <c r="C17" s="169">
-        <f>C7/(C8+C7)</f>
-        <v>0.98349777690616957</v>
+        <f ca="1">C7/(C8+C7)</f>
+        <v>0.98240113248108929</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4745,8 +4745,8 @@
         <v>252</v>
       </c>
       <c r="C19" s="169">
-        <f>C9+C10*C11</f>
-        <v>9.0835000000000013E-2</v>
+        <f ca="1">C9+C10*C11</f>
+        <v>8.8919999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4754,8 +4754,8 @@
         <v>249</v>
       </c>
       <c r="C20" s="169">
-        <f>(C17*C19)+(C16*C18)</f>
-        <v>9.0248593502360752E-2</v>
+        <f ca="1">(C17*C19)+(C16*C18)</f>
+        <v>8.832832607401421E-2</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4809,60 +4809,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="104"/>
-      <c r="C3" s="224" t="s">
+      <c r="C3" s="223" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="224"/>
-      <c r="E3" s="224"/>
-      <c r="F3" s="224"/>
-      <c r="G3" s="225"/>
-      <c r="H3" s="226" t="s">
+      <c r="D3" s="223"/>
+      <c r="E3" s="223"/>
+      <c r="F3" s="223"/>
+      <c r="G3" s="230"/>
+      <c r="H3" s="231" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="224"/>
-      <c r="J3" s="224"/>
-      <c r="K3" s="224"/>
-      <c r="L3" s="224"/>
-      <c r="P3" s="227"/>
-      <c r="Q3" s="227"/>
-      <c r="R3" s="227"/>
-      <c r="S3" s="227"/>
-      <c r="T3" s="227"/>
-      <c r="U3" s="227"/>
-      <c r="V3" s="227"/>
-      <c r="W3" s="227"/>
-      <c r="X3" s="227"/>
-      <c r="Y3" s="227"/>
-      <c r="Z3" s="227"/>
+      <c r="I3" s="223"/>
+      <c r="J3" s="223"/>
+      <c r="K3" s="223"/>
+      <c r="L3" s="223"/>
+      <c r="P3" s="232"/>
+      <c r="Q3" s="232"/>
+      <c r="R3" s="232"/>
+      <c r="S3" s="232"/>
+      <c r="T3" s="232"/>
+      <c r="U3" s="232"/>
+      <c r="V3" s="232"/>
+      <c r="W3" s="232"/>
+      <c r="X3" s="232"/>
+      <c r="Y3" s="232"/>
+      <c r="Z3" s="232"/>
       <c r="AB3" s="143"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="109"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="223" t="s">
+      <c r="C5" s="227" t="s">
         <v>273</v>
       </c>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="223"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="223"/>
-      <c r="K5" s="223"/>
-      <c r="L5" s="223"/>
-      <c r="P5" s="227"/>
-      <c r="Q5" s="227"/>
-      <c r="R5" s="227"/>
-      <c r="S5" s="227"/>
-      <c r="T5" s="227"/>
-      <c r="U5" s="227"/>
-      <c r="V5" s="227"/>
-      <c r="W5" s="227"/>
-      <c r="X5" s="227"/>
-      <c r="Y5" s="227"/>
-      <c r="Z5" s="227"/>
+      <c r="D5" s="227"/>
+      <c r="E5" s="227"/>
+      <c r="F5" s="227"/>
+      <c r="G5" s="227"/>
+      <c r="H5" s="227"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="227"/>
+      <c r="K5" s="227"/>
+      <c r="L5" s="227"/>
+      <c r="P5" s="232"/>
+      <c r="Q5" s="232"/>
+      <c r="R5" s="232"/>
+      <c r="S5" s="232"/>
+      <c r="T5" s="232"/>
+      <c r="U5" s="232"/>
+      <c r="V5" s="232"/>
+      <c r="W5" s="232"/>
+      <c r="X5" s="232"/>
+      <c r="Y5" s="232"/>
+      <c r="Z5" s="232"/>
       <c r="AB5" s="144"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -5014,8 +5014,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="154">
-        <f>L7*(1+C14)/(C15-C14)</f>
-        <v>7646334.9797471194</v>
+        <f ca="1">L7*(1+C14)/(C15-C14)</f>
+        <v>7861224.0140830465</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="7"/>
@@ -5068,24 +5068,24 @@
       <c r="F10" s="151"/>
       <c r="G10" s="171"/>
       <c r="H10" s="154">
-        <f>H7/(1+$C$15)^H9</f>
-        <v>122914.85660446061</v>
+        <f ca="1">H7/(1+$C$15)^H9</f>
+        <v>123131.7299412494</v>
       </c>
       <c r="I10" s="154">
-        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$15)^I9</f>
-        <v>188382.3449618867</v>
+        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$15)^I9</f>
+        <v>189047.70229366093</v>
       </c>
       <c r="J10" s="154">
-        <f t="shared" si="1"/>
-        <v>215531.61931408988</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>216674.49786321039</v>
       </c>
       <c r="K10" s="154">
-        <f t="shared" si="1"/>
-        <v>245477.91730088624</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>247215.01182392135</v>
       </c>
       <c r="L10" s="154">
-        <f t="shared" si="1"/>
-        <v>341871.66444169253</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>344898.35099770111</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -5103,15 +5103,15 @@
       <c r="J11" s="151"/>
       <c r="K11" s="151"/>
       <c r="L11" s="154">
-        <f>L8/(1+C15)^L9</f>
-        <v>4963929.957100248</v>
+        <f ca="1">L8/(1+C15)^L9</f>
+        <v>5148616.0752216354</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="224" t="s">
+      <c r="B13" s="223" t="s">
         <v>274</v>
       </c>
-      <c r="C13" s="224"/>
+      <c r="C13" s="223"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -5126,23 +5126,23 @@
         <v>249</v>
       </c>
       <c r="C15" s="170">
-        <f>WACC!C20</f>
-        <v>9.0248593502360752E-2</v>
+        <f ca="1">WACC!C20</f>
+        <v>8.832832607401421E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="224" t="s">
+      <c r="B18" s="223" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="224"/>
+      <c r="C18" s="223"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>272</v>
       </c>
       <c r="C19" s="108">
-        <f>SUM(H10:L10)</f>
-        <v>1114178.4026230159</v>
+        <f ca="1">SUM(H10:L10)</f>
+        <v>1120967.2929197431</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -5150,8 +5150,8 @@
         <v>266</v>
       </c>
       <c r="C20" s="108">
-        <f>L11</f>
-        <v>4963929.957100248</v>
+        <f ca="1">L11</f>
+        <v>5148616.0752216354</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -5159,8 +5159,8 @@
         <v>269</v>
       </c>
       <c r="C21" s="113">
-        <f>C19+C20</f>
-        <v>6078108.3597232644</v>
+        <f ca="1">C19+C20</f>
+        <v>6269583.3681413783</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -5186,8 +5186,8 @@
         <v>270</v>
       </c>
       <c r="C24" s="113">
-        <f>C21+C22-C23</f>
-        <v>7237845.3597232644</v>
+        <f ca="1">C21+C22-C23</f>
+        <v>7429320.3681413783</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -5204,8 +5204,8 @@
         <v>271</v>
       </c>
       <c r="C26" s="173">
-        <f>C24/C25</f>
-        <v>148.12934128925642</v>
+        <f ca="1">C24/C25</f>
+        <v>152.04805818091083</v>
       </c>
     </row>
   </sheetData>
@@ -5248,37 +5248,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="224" t="s">
+      <c r="C2" s="223" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="224"/>
-      <c r="E2" s="224"/>
-      <c r="F2" s="224"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="226" t="s">
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="230"/>
+      <c r="H2" s="231" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="224"/>
-      <c r="J2" s="224"/>
-      <c r="K2" s="224"/>
-      <c r="L2" s="224"/>
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="223"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="223" t="s">
+      <c r="C4" s="227" t="s">
         <v>333</v>
       </c>
-      <c r="D4" s="223"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="223"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="223"/>
-      <c r="I4" s="223"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="223"/>
-      <c r="L4" s="223"/>
+      <c r="D4" s="227"/>
+      <c r="E4" s="227"/>
+      <c r="F4" s="227"/>
+      <c r="G4" s="227"/>
+      <c r="H4" s="227"/>
+      <c r="I4" s="227"/>
+      <c r="J4" s="227"/>
+      <c r="K4" s="227"/>
+      <c r="L4" s="227"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -5467,18 +5467,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="223" t="s">
+      <c r="C10" s="227" t="s">
         <v>191</v>
       </c>
-      <c r="D10" s="223"/>
-      <c r="E10" s="223"/>
-      <c r="F10" s="223"/>
-      <c r="G10" s="223"/>
-      <c r="H10" s="223"/>
-      <c r="I10" s="223"/>
-      <c r="J10" s="223"/>
-      <c r="K10" s="223"/>
-      <c r="L10" s="223"/>
+      <c r="D10" s="227"/>
+      <c r="E10" s="227"/>
+      <c r="F10" s="227"/>
+      <c r="G10" s="227"/>
+      <c r="H10" s="227"/>
+      <c r="I10" s="227"/>
+      <c r="J10" s="227"/>
+      <c r="K10" s="227"/>
+      <c r="L10" s="227"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5660,18 +5660,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="223" t="s">
+      <c r="C16" s="227" t="s">
         <v>315</v>
       </c>
-      <c r="D16" s="223"/>
-      <c r="E16" s="223"/>
-      <c r="F16" s="223"/>
-      <c r="G16" s="223"/>
-      <c r="H16" s="223"/>
-      <c r="I16" s="223"/>
-      <c r="J16" s="223"/>
-      <c r="K16" s="223"/>
-      <c r="L16" s="223"/>
+      <c r="D16" s="227"/>
+      <c r="E16" s="227"/>
+      <c r="F16" s="227"/>
+      <c r="G16" s="227"/>
+      <c r="H16" s="227"/>
+      <c r="I16" s="227"/>
+      <c r="J16" s="227"/>
+      <c r="K16" s="227"/>
+      <c r="L16" s="227"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5805,18 +5805,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="223" t="s">
+      <c r="C21" s="227" t="s">
         <v>334</v>
       </c>
-      <c r="D21" s="223"/>
-      <c r="E21" s="223"/>
-      <c r="F21" s="223"/>
-      <c r="G21" s="223"/>
-      <c r="H21" s="223"/>
-      <c r="I21" s="223"/>
-      <c r="J21" s="223"/>
-      <c r="K21" s="223"/>
-      <c r="L21" s="223"/>
+      <c r="D21" s="227"/>
+      <c r="E21" s="227"/>
+      <c r="F21" s="227"/>
+      <c r="G21" s="227"/>
+      <c r="H21" s="227"/>
+      <c r="I21" s="227"/>
+      <c r="J21" s="227"/>
+      <c r="K21" s="227"/>
+      <c r="L21" s="227"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5900,18 +5900,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="223" t="s">
+      <c r="C26" s="227" t="s">
         <v>336</v>
       </c>
-      <c r="D26" s="223"/>
-      <c r="E26" s="223"/>
-      <c r="F26" s="223"/>
-      <c r="G26" s="223"/>
-      <c r="H26" s="223"/>
-      <c r="I26" s="223"/>
-      <c r="J26" s="223"/>
-      <c r="K26" s="223"/>
-      <c r="L26" s="223"/>
+      <c r="D26" s="227"/>
+      <c r="E26" s="227"/>
+      <c r="F26" s="227"/>
+      <c r="G26" s="227"/>
+      <c r="H26" s="227"/>
+      <c r="I26" s="227"/>
+      <c r="J26" s="227"/>
+      <c r="K26" s="227"/>
+      <c r="L26" s="227"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -6181,10 +6181,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="224" t="s">
+      <c r="B37" s="223" t="s">
         <v>338</v>
       </c>
-      <c r="C37" s="224"/>
+      <c r="C37" s="223"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -6201,8 +6201,8 @@
         <v>249</v>
       </c>
       <c r="C39" s="159">
-        <f>WACC!C20</f>
-        <v>9.0248593502360752E-2</v>
+        <f ca="1">WACC!C20</f>
+        <v>8.832832607401421E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -6245,15 +6245,15 @@
         <v>335</v>
       </c>
       <c r="C44" s="173">
-        <f>C43/(1+C48)^5</f>
-        <v>147.31389818040671</v>
+        <f ca="1">C43/(1+C48)^5</f>
+        <v>148.61810979403666</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="224" t="s">
+      <c r="B46" s="223" t="s">
         <v>288</v>
       </c>
-      <c r="C46" s="224"/>
+      <c r="C46" s="223"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -6269,8 +6269,8 @@
         <v>249</v>
       </c>
       <c r="C48" s="159">
-        <f>WACC!C20</f>
-        <v>9.0248593502360752E-2</v>
+        <f ca="1">WACC!C20</f>
+        <v>8.832832607401421E-2</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -6304,15 +6304,15 @@
         <v>335</v>
       </c>
       <c r="C52" s="173">
-        <f>C51/(1+C48)^5</f>
-        <v>144.1283429696183</v>
+        <f ca="1">C51/(1+C48)^5</f>
+        <v>145.40435196181818</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="224" t="s">
+      <c r="B54" s="223" t="s">
         <v>342</v>
       </c>
-      <c r="C54" s="224"/>
+      <c r="C54" s="223"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -6328,8 +6328,8 @@
         <v>249</v>
       </c>
       <c r="C56" s="159">
-        <f>WACC!C20</f>
-        <v>9.0248593502360752E-2</v>
+        <f ca="1">WACC!C20</f>
+        <v>8.832832607401421E-2</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6372,8 +6372,8 @@
         <v>335</v>
       </c>
       <c r="C61" s="173">
-        <f>C60/(1+C56)^5</f>
-        <v>146.43933513814184</v>
+        <f ca="1">C60/(1+C56)^5</f>
+        <v>147.73580399775696</v>
       </c>
     </row>
   </sheetData>
@@ -6422,10 +6422,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="224" t="s">
+      <c r="B4" s="223" t="s">
         <v>296</v>
       </c>
-      <c r="C4" s="224"/>
+      <c r="C4" s="223"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -6433,8 +6433,8 @@
         <v>293</v>
       </c>
       <c r="C5" s="188">
-        <f>DCF!C26</f>
-        <v>148.12934128925642</v>
+        <f ca="1">DCF!C26</f>
+        <v>152.04805818091083</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6442,8 +6442,8 @@
         <v>341</v>
       </c>
       <c r="C6" s="188">
-        <f>Multiples!C44</f>
-        <v>147.31389818040671</v>
+        <f ca="1">Multiples!C44</f>
+        <v>148.61810979403666</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6451,8 +6451,8 @@
         <v>294</v>
       </c>
       <c r="C7" s="188">
-        <f>Multiples!C52</f>
-        <v>144.1283429696183</v>
+        <f ca="1">Multiples!C52</f>
+        <v>145.40435196181818</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6460,8 +6460,8 @@
         <v>345</v>
       </c>
       <c r="C8" s="188">
-        <f>Multiples!C61</f>
-        <v>146.43933513814184</v>
+        <f ca="1">Multiples!C61</f>
+        <v>147.73580399775696</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6469,8 +6469,8 @@
         <v>292</v>
       </c>
       <c r="C9" s="173">
-        <f>AVERAGE(C5:C8)</f>
-        <v>146.50272939435581</v>
+        <f ca="1">AVERAGE(C5:C8)</f>
+        <v>148.45158098363066</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6478,8 +6478,8 @@
         <v>347</v>
       </c>
       <c r="C10" s="35">
-        <f>Overview!C3</f>
-        <v>112.06</v>
+        <f ca="1">Overview!C3</f>
+        <v>104.96</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6487,8 +6487,8 @@
         <v>348</v>
       </c>
       <c r="C11" s="91">
-        <f>(C9-C10)/C10</f>
-        <v>0.30735971260356781</v>
+        <f ca="1">(C9-C10)/C10</f>
+        <v>0.41436338589587152</v>
       </c>
     </row>
   </sheetData>
@@ -6532,60 +6532,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="104"/>
-      <c r="C3" s="224" t="s">
+      <c r="C3" s="223" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="224"/>
-      <c r="E3" s="224"/>
-      <c r="F3" s="224"/>
-      <c r="G3" s="225"/>
-      <c r="H3" s="226" t="s">
+      <c r="D3" s="223"/>
+      <c r="E3" s="223"/>
+      <c r="F3" s="223"/>
+      <c r="G3" s="230"/>
+      <c r="H3" s="231" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="224"/>
-      <c r="J3" s="224"/>
-      <c r="K3" s="224"/>
-      <c r="L3" s="224"/>
-      <c r="P3" s="227"/>
-      <c r="Q3" s="227"/>
-      <c r="R3" s="227"/>
-      <c r="S3" s="227"/>
-      <c r="T3" s="227"/>
-      <c r="U3" s="227"/>
-      <c r="V3" s="227"/>
-      <c r="W3" s="227"/>
-      <c r="X3" s="227"/>
-      <c r="Y3" s="227"/>
-      <c r="Z3" s="227"/>
+      <c r="I3" s="223"/>
+      <c r="J3" s="223"/>
+      <c r="K3" s="223"/>
+      <c r="L3" s="223"/>
+      <c r="P3" s="232"/>
+      <c r="Q3" s="232"/>
+      <c r="R3" s="232"/>
+      <c r="S3" s="232"/>
+      <c r="T3" s="232"/>
+      <c r="U3" s="232"/>
+      <c r="V3" s="232"/>
+      <c r="W3" s="232"/>
+      <c r="X3" s="232"/>
+      <c r="Y3" s="232"/>
+      <c r="Z3" s="232"/>
       <c r="AB3" s="143"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="109"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="223" t="s">
+      <c r="C5" s="227" t="s">
         <v>273</v>
       </c>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="223"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="223"/>
-      <c r="K5" s="223"/>
-      <c r="L5" s="223"/>
-      <c r="P5" s="227"/>
-      <c r="Q5" s="227"/>
-      <c r="R5" s="227"/>
-      <c r="S5" s="227"/>
-      <c r="T5" s="227"/>
-      <c r="U5" s="227"/>
-      <c r="V5" s="227"/>
-      <c r="W5" s="227"/>
-      <c r="X5" s="227"/>
-      <c r="Y5" s="227"/>
-      <c r="Z5" s="227"/>
+      <c r="D5" s="227"/>
+      <c r="E5" s="227"/>
+      <c r="F5" s="227"/>
+      <c r="G5" s="227"/>
+      <c r="H5" s="227"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="227"/>
+      <c r="K5" s="227"/>
+      <c r="L5" s="227"/>
+      <c r="P5" s="232"/>
+      <c r="Q5" s="232"/>
+      <c r="R5" s="232"/>
+      <c r="S5" s="232"/>
+      <c r="T5" s="232"/>
+      <c r="U5" s="232"/>
+      <c r="V5" s="232"/>
+      <c r="W5" s="232"/>
+      <c r="X5" s="232"/>
+      <c r="Y5" s="232"/>
+      <c r="Z5" s="232"/>
       <c r="AB5" s="144"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -6719,8 +6719,8 @@
       <c r="J8" s="151"/>
       <c r="K8" s="151"/>
       <c r="L8" s="154">
-        <f>L7*(1+C20)/(C21-C20)</f>
-        <v>6110659.2925218893</v>
+        <f ca="1">L7*(1+C20)/(C21-C20)</f>
+        <v>6282390.4131180877</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="7"/>
@@ -6773,24 +6773,24 @@
       <c r="F10" s="151"/>
       <c r="G10" s="171"/>
       <c r="H10" s="154">
-        <f>H7/(1+$C$21)^H9</f>
-        <v>163272.58006741427</v>
+        <f ca="1">H7/(1+$C$21)^H9</f>
+        <v>163560.66134760712</v>
       </c>
       <c r="I10" s="154">
-        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>185698.9318676478</v>
+        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
+        <v>186354.81151414959</v>
       </c>
       <c r="J10" s="154">
-        <f t="shared" si="1"/>
-        <v>211205.66161536137</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>212325.60132945611</v>
       </c>
       <c r="K10" s="154">
-        <f t="shared" si="1"/>
-        <v>240215.87550204995</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>241915.73382848845</v>
       </c>
       <c r="L10" s="154">
-        <f t="shared" si="1"/>
-        <v>273210.79559081036</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>275629.60805168381</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -6808,8 +6808,8 @@
       <c r="J11" s="151"/>
       <c r="K11" s="151"/>
       <c r="L11" s="154">
-        <f>L8/(1+C21)^L9</f>
-        <v>3966983.5025702193</v>
+        <f ca="1">L8/(1+C21)^L9</f>
+        <v>4114577.6044356818</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6824,8 +6824,8 @@
         <v>351</v>
       </c>
       <c r="C15" s="208">
-        <f>Overview!C3</f>
-        <v>112.06</v>
+        <f ca="1">Overview!C3</f>
+        <v>104.96</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6833,8 +6833,8 @@
         <v>352</v>
       </c>
       <c r="C16" s="208">
-        <f>C36</f>
-        <v>103.1224164692768</v>
+        <f ca="1">C36</f>
+        <v>106.26960132727156</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6872,8 +6872,8 @@
         <v>249</v>
       </c>
       <c r="C21" s="213">
-        <f>WACC!C20</f>
-        <v>9.0248593502360752E-2</v>
+        <f ca="1">WACC!C20</f>
+        <v>8.832832607401421E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6890,8 +6890,8 @@
         <v>240</v>
       </c>
       <c r="C23" s="214">
-        <f>C15*C22</f>
-        <v>5475437.5058401404</v>
+        <f ca="1">C15*C22</f>
+        <v>5128519.7270478411</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6917,8 +6917,8 @@
         <v>355</v>
       </c>
       <c r="C26" s="215">
-        <f>C23+C25-C24</f>
-        <v>4315700.5058401404</v>
+        <f ca="1">C23+C25-C24</f>
+        <v>3968782.7270478411</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6933,8 +6933,8 @@
         <v>272</v>
       </c>
       <c r="C29" s="214">
-        <f>SUM(H10:L10)</f>
-        <v>1073603.8446432836</v>
+        <f ca="1">SUM(H10:L10)</f>
+        <v>1079786.4160713849</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6942,8 +6942,8 @@
         <v>266</v>
       </c>
       <c r="C30" s="214">
-        <f>L11</f>
-        <v>3966983.5025702193</v>
+        <f ca="1">L11</f>
+        <v>4114577.6044356818</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6951,8 +6951,8 @@
         <v>269</v>
       </c>
       <c r="C31" s="217">
-        <f>C29+C30</f>
-        <v>5040587.347213503</v>
+        <f ca="1">C29+C30</f>
+        <v>5194364.0205070665</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6978,8 +6978,8 @@
         <v>270</v>
       </c>
       <c r="C34" s="217">
-        <f>C31+C32-C33</f>
-        <v>5038732.347213503</v>
+        <f ca="1">C31+C32-C33</f>
+        <v>5192509.0205070665</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6996,23 +6996,23 @@
         <v>271</v>
       </c>
       <c r="C36" s="220">
-        <f>C34/C35</f>
-        <v>103.1224164692768</v>
+        <f ca="1">C34/C35</f>
+        <v>106.26960132727156</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="223" t="s">
+      <c r="C39" s="227" t="s">
         <v>356</v>
       </c>
-      <c r="D39" s="223"/>
-      <c r="E39" s="223"/>
-      <c r="F39" s="223"/>
-      <c r="G39" s="223"/>
-      <c r="H39" s="223"/>
-      <c r="I39" s="223"/>
-      <c r="J39" s="223"/>
-      <c r="K39" s="223"/>
-      <c r="L39" s="223"/>
+      <c r="D39" s="227"/>
+      <c r="E39" s="227"/>
+      <c r="F39" s="227"/>
+      <c r="G39" s="227"/>
+      <c r="H39" s="227"/>
+      <c r="I39" s="227"/>
+      <c r="J39" s="227"/>
+      <c r="K39" s="227"/>
+      <c r="L39" s="227"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="62">
@@ -7444,17 +7444,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -12371,11 +12371,11 @@
         <v>85</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="228" t="s">
+      <c r="P4" s="224" t="s">
         <v>86</v>
       </c>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="230"/>
+      <c r="Q4" s="225"/>
+      <c r="R4" s="226"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -23268,36 +23268,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="224" t="s">
+      <c r="C2" s="223" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="224"/>
-      <c r="E2" s="224"/>
-      <c r="F2" s="224"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="226" t="s">
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="230"/>
+      <c r="H2" s="231" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="224"/>
-      <c r="J2" s="224"/>
-      <c r="K2" s="224"/>
-      <c r="L2" s="224"/>
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="223"/>
       <c r="O2" s="92"/>
-      <c r="S2" s="224" t="s">
+      <c r="S2" s="223" t="s">
         <v>176</v>
       </c>
-      <c r="T2" s="224"/>
-      <c r="U2" s="224"/>
-      <c r="V2" s="224"/>
-      <c r="W2" s="224"/>
-      <c r="X2" s="224"/>
-      <c r="Y2" s="224"/>
-      <c r="Z2" s="224"/>
-      <c r="AA2" s="224" t="s">
+      <c r="T2" s="223"/>
+      <c r="U2" s="223"/>
+      <c r="V2" s="223"/>
+      <c r="W2" s="223"/>
+      <c r="X2" s="223"/>
+      <c r="Y2" s="223"/>
+      <c r="Z2" s="223"/>
+      <c r="AA2" s="223" t="s">
         <v>177</v>
       </c>
-      <c r="AB2" s="224"/>
-      <c r="AC2" s="224"/>
+      <c r="AB2" s="223"/>
+      <c r="AC2" s="223"/>
       <c r="AE2" s="128" t="s">
         <v>85</v>
       </c>
@@ -23308,32 +23308,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="223" t="s">
+      <c r="C4" s="227" t="s">
         <v>185</v>
       </c>
-      <c r="D4" s="223"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="223"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="223"/>
-      <c r="I4" s="223"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="223"/>
-      <c r="L4" s="223"/>
+      <c r="D4" s="227"/>
+      <c r="E4" s="227"/>
+      <c r="F4" s="227"/>
+      <c r="G4" s="227"/>
+      <c r="H4" s="227"/>
+      <c r="I4" s="227"/>
+      <c r="J4" s="227"/>
+      <c r="K4" s="227"/>
+      <c r="L4" s="227"/>
       <c r="O4" s="92"/>
-      <c r="S4" s="231" t="s">
+      <c r="S4" s="228" t="s">
         <v>185</v>
       </c>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="232"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="232"/>
-      <c r="Y4" s="232"/>
-      <c r="Z4" s="232"/>
-      <c r="AA4" s="232"/>
-      <c r="AB4" s="232"/>
-      <c r="AC4" s="232"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="229"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="229"/>
+      <c r="Y4" s="229"/>
+      <c r="Z4" s="229"/>
+      <c r="AA4" s="229"/>
+      <c r="AB4" s="229"/>
+      <c r="AC4" s="229"/>
       <c r="AE4" s="140" t="s">
         <v>210</v>
       </c>
@@ -24129,33 +24129,33 @@
       <c r="Q13" s="93"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C14" s="223" t="s">
+      <c r="C14" s="227" t="s">
         <v>191</v>
       </c>
-      <c r="D14" s="223"/>
-      <c r="E14" s="223"/>
-      <c r="F14" s="223"/>
-      <c r="G14" s="223"/>
-      <c r="H14" s="223"/>
-      <c r="I14" s="223"/>
-      <c r="J14" s="223"/>
-      <c r="K14" s="223"/>
-      <c r="L14" s="223"/>
+      <c r="D14" s="227"/>
+      <c r="E14" s="227"/>
+      <c r="F14" s="227"/>
+      <c r="G14" s="227"/>
+      <c r="H14" s="227"/>
+      <c r="I14" s="227"/>
+      <c r="J14" s="227"/>
+      <c r="K14" s="227"/>
+      <c r="L14" s="227"/>
       <c r="O14" s="92"/>
       <c r="Q14" s="93"/>
-      <c r="S14" s="231" t="s">
+      <c r="S14" s="228" t="s">
         <v>191</v>
       </c>
-      <c r="T14" s="232"/>
-      <c r="U14" s="232"/>
-      <c r="V14" s="232"/>
-      <c r="W14" s="232"/>
-      <c r="X14" s="232"/>
-      <c r="Y14" s="232"/>
-      <c r="Z14" s="232"/>
-      <c r="AA14" s="232"/>
-      <c r="AB14" s="232"/>
-      <c r="AC14" s="232"/>
+      <c r="T14" s="229"/>
+      <c r="U14" s="229"/>
+      <c r="V14" s="229"/>
+      <c r="W14" s="229"/>
+      <c r="X14" s="229"/>
+      <c r="Y14" s="229"/>
+      <c r="Z14" s="229"/>
+      <c r="AA14" s="229"/>
+      <c r="AB14" s="229"/>
+      <c r="AC14" s="229"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B15" s="7" t="s">
@@ -24848,33 +24848,33 @@
       <c r="Q24" s="93"/>
     </row>
     <row r="25" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C25" s="223" t="s">
+      <c r="C25" s="227" t="s">
         <v>193</v>
       </c>
-      <c r="D25" s="223"/>
-      <c r="E25" s="223"/>
-      <c r="F25" s="223"/>
-      <c r="G25" s="223"/>
-      <c r="H25" s="223"/>
-      <c r="I25" s="223"/>
-      <c r="J25" s="223"/>
-      <c r="K25" s="223"/>
-      <c r="L25" s="223"/>
+      <c r="D25" s="227"/>
+      <c r="E25" s="227"/>
+      <c r="F25" s="227"/>
+      <c r="G25" s="227"/>
+      <c r="H25" s="227"/>
+      <c r="I25" s="227"/>
+      <c r="J25" s="227"/>
+      <c r="K25" s="227"/>
+      <c r="L25" s="227"/>
       <c r="O25" s="92"/>
       <c r="Q25" s="93"/>
-      <c r="S25" s="231" t="s">
+      <c r="S25" s="228" t="s">
         <v>193</v>
       </c>
-      <c r="T25" s="232"/>
-      <c r="U25" s="232"/>
-      <c r="V25" s="232"/>
-      <c r="W25" s="232"/>
-      <c r="X25" s="232"/>
-      <c r="Y25" s="232"/>
-      <c r="Z25" s="232"/>
-      <c r="AA25" s="232"/>
-      <c r="AB25" s="232"/>
-      <c r="AC25" s="232"/>
+      <c r="T25" s="229"/>
+      <c r="U25" s="229"/>
+      <c r="V25" s="229"/>
+      <c r="W25" s="229"/>
+      <c r="X25" s="229"/>
+      <c r="Y25" s="229"/>
+      <c r="Z25" s="229"/>
+      <c r="AA25" s="229"/>
+      <c r="AB25" s="229"/>
+      <c r="AC25" s="229"/>
       <c r="AE25" s="140" t="str">
         <f>AE4</f>
         <v>Q1-Q2-Q3</v>
@@ -26197,32 +26197,32 @@
       <c r="O42" s="92"/>
     </row>
     <row r="43" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C43" s="223" t="s">
+      <c r="C43" s="227" t="s">
         <v>205</v>
       </c>
-      <c r="D43" s="223"/>
-      <c r="E43" s="223"/>
-      <c r="F43" s="223"/>
-      <c r="G43" s="223"/>
-      <c r="H43" s="223"/>
-      <c r="I43" s="223"/>
-      <c r="J43" s="223"/>
-      <c r="K43" s="223"/>
-      <c r="L43" s="223"/>
+      <c r="D43" s="227"/>
+      <c r="E43" s="227"/>
+      <c r="F43" s="227"/>
+      <c r="G43" s="227"/>
+      <c r="H43" s="227"/>
+      <c r="I43" s="227"/>
+      <c r="J43" s="227"/>
+      <c r="K43" s="227"/>
+      <c r="L43" s="227"/>
       <c r="O43" s="92"/>
-      <c r="S43" s="231" t="s">
+      <c r="S43" s="228" t="s">
         <v>205</v>
       </c>
-      <c r="T43" s="232"/>
-      <c r="U43" s="232"/>
-      <c r="V43" s="232"/>
-      <c r="W43" s="232"/>
-      <c r="X43" s="232"/>
-      <c r="Y43" s="232"/>
-      <c r="Z43" s="232"/>
-      <c r="AA43" s="232"/>
-      <c r="AB43" s="232"/>
-      <c r="AC43" s="232"/>
+      <c r="T43" s="229"/>
+      <c r="U43" s="229"/>
+      <c r="V43" s="229"/>
+      <c r="W43" s="229"/>
+      <c r="X43" s="229"/>
+      <c r="Y43" s="229"/>
+      <c r="Z43" s="229"/>
+      <c r="AA43" s="229"/>
+      <c r="AB43" s="229"/>
+      <c r="AC43" s="229"/>
     </row>
     <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B44" s="7" t="s">
@@ -26838,35 +26838,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
-      <c r="C2" s="224" t="s">
+      <c r="C2" s="223" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="224"/>
-      <c r="E2" s="224"/>
-      <c r="F2" s="224"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="226" t="s">
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="230"/>
+      <c r="H2" s="231" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="224"/>
-      <c r="J2" s="224"/>
-      <c r="K2" s="224"/>
-      <c r="L2" s="224"/>
-      <c r="P2" s="224" t="s">
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="223"/>
+      <c r="P2" s="223" t="s">
         <v>176</v>
       </c>
-      <c r="Q2" s="224"/>
-      <c r="R2" s="224"/>
-      <c r="S2" s="224"/>
-      <c r="T2" s="224"/>
-      <c r="U2" s="224"/>
-      <c r="V2" s="224"/>
-      <c r="W2" s="224"/>
-      <c r="X2" s="224" t="s">
+      <c r="Q2" s="223"/>
+      <c r="R2" s="223"/>
+      <c r="S2" s="223"/>
+      <c r="T2" s="223"/>
+      <c r="U2" s="223"/>
+      <c r="V2" s="223"/>
+      <c r="W2" s="223"/>
+      <c r="X2" s="223" t="s">
         <v>177</v>
       </c>
-      <c r="Y2" s="224"/>
-      <c r="Z2" s="224"/>
+      <c r="Y2" s="223"/>
+      <c r="Z2" s="223"/>
       <c r="AB2" s="128" t="s">
         <v>85</v>
       </c>
@@ -26875,31 +26875,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="94"/>
-      <c r="C4" s="223" t="s">
+      <c r="C4" s="227" t="s">
         <v>185</v>
       </c>
-      <c r="D4" s="223"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="223"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="223"/>
-      <c r="I4" s="223"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="223"/>
-      <c r="L4" s="223"/>
-      <c r="P4" s="232" t="s">
+      <c r="D4" s="227"/>
+      <c r="E4" s="227"/>
+      <c r="F4" s="227"/>
+      <c r="G4" s="227"/>
+      <c r="H4" s="227"/>
+      <c r="I4" s="227"/>
+      <c r="J4" s="227"/>
+      <c r="K4" s="227"/>
+      <c r="L4" s="227"/>
+      <c r="P4" s="229" t="s">
         <v>185</v>
       </c>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="232"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="232"/>
-      <c r="Y4" s="232"/>
-      <c r="Z4" s="232"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="229"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="229"/>
+      <c r="Y4" s="229"/>
+      <c r="Z4" s="229"/>
       <c r="AB4" s="140" t="s">
         <v>210</v>
       </c>
@@ -27100,32 +27100,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="223" t="s">
+      <c r="C9" s="227" t="s">
         <v>212</v>
       </c>
-      <c r="D9" s="223"/>
-      <c r="E9" s="223"/>
-      <c r="F9" s="223"/>
-      <c r="G9" s="223"/>
-      <c r="H9" s="223"/>
-      <c r="I9" s="223"/>
-      <c r="J9" s="223"/>
-      <c r="K9" s="223"/>
-      <c r="L9" s="223"/>
+      <c r="D9" s="227"/>
+      <c r="E9" s="227"/>
+      <c r="F9" s="227"/>
+      <c r="G9" s="227"/>
+      <c r="H9" s="227"/>
+      <c r="I9" s="227"/>
+      <c r="J9" s="227"/>
+      <c r="K9" s="227"/>
+      <c r="L9" s="227"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="232" t="s">
+      <c r="P9" s="229" t="s">
         <v>217</v>
       </c>
-      <c r="Q9" s="232"/>
-      <c r="R9" s="232"/>
-      <c r="S9" s="232"/>
-      <c r="T9" s="232"/>
-      <c r="U9" s="232"/>
-      <c r="V9" s="232"/>
-      <c r="W9" s="232"/>
-      <c r="X9" s="232"/>
-      <c r="Y9" s="232"/>
-      <c r="Z9" s="232"/>
+      <c r="Q9" s="229"/>
+      <c r="R9" s="229"/>
+      <c r="S9" s="229"/>
+      <c r="T9" s="229"/>
+      <c r="U9" s="229"/>
+      <c r="V9" s="229"/>
+      <c r="W9" s="229"/>
+      <c r="X9" s="229"/>
+      <c r="Y9" s="229"/>
+      <c r="Z9" s="229"/>
       <c r="AB9" s="140" t="str">
         <f>AB4</f>
         <v>Q1-Q2-Q3</v>
@@ -27687,31 +27687,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="223" t="s">
+      <c r="C18" s="227" t="s">
         <v>215</v>
       </c>
-      <c r="D18" s="223"/>
-      <c r="E18" s="223"/>
-      <c r="F18" s="223"/>
-      <c r="G18" s="223"/>
-      <c r="H18" s="223"/>
-      <c r="I18" s="223"/>
-      <c r="J18" s="223"/>
-      <c r="K18" s="223"/>
-      <c r="L18" s="223"/>
-      <c r="P18" s="232" t="s">
+      <c r="D18" s="227"/>
+      <c r="E18" s="227"/>
+      <c r="F18" s="227"/>
+      <c r="G18" s="227"/>
+      <c r="H18" s="227"/>
+      <c r="I18" s="227"/>
+      <c r="J18" s="227"/>
+      <c r="K18" s="227"/>
+      <c r="L18" s="227"/>
+      <c r="P18" s="229" t="s">
         <v>215</v>
       </c>
-      <c r="Q18" s="232"/>
-      <c r="R18" s="232"/>
-      <c r="S18" s="232"/>
-      <c r="T18" s="232"/>
-      <c r="U18" s="232"/>
-      <c r="V18" s="232"/>
-      <c r="W18" s="232"/>
-      <c r="X18" s="232"/>
-      <c r="Y18" s="232"/>
-      <c r="Z18" s="232"/>
+      <c r="Q18" s="229"/>
+      <c r="R18" s="229"/>
+      <c r="S18" s="229"/>
+      <c r="T18" s="229"/>
+      <c r="U18" s="229"/>
+      <c r="V18" s="229"/>
+      <c r="W18" s="229"/>
+      <c r="X18" s="229"/>
+      <c r="Y18" s="229"/>
+      <c r="Z18" s="229"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -28183,60 +28183,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="104"/>
-      <c r="C3" s="224" t="s">
+      <c r="C3" s="223" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="224"/>
-      <c r="E3" s="224"/>
-      <c r="F3" s="224"/>
-      <c r="G3" s="225"/>
-      <c r="H3" s="226" t="s">
+      <c r="D3" s="223"/>
+      <c r="E3" s="223"/>
+      <c r="F3" s="223"/>
+      <c r="G3" s="230"/>
+      <c r="H3" s="231" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="224"/>
-      <c r="J3" s="224"/>
-      <c r="K3" s="224"/>
-      <c r="L3" s="224"/>
-      <c r="P3" s="227"/>
-      <c r="Q3" s="227"/>
-      <c r="R3" s="227"/>
-      <c r="S3" s="227"/>
-      <c r="T3" s="227"/>
-      <c r="U3" s="227"/>
-      <c r="V3" s="227"/>
-      <c r="W3" s="227"/>
-      <c r="X3" s="227"/>
-      <c r="Y3" s="227"/>
-      <c r="Z3" s="227"/>
+      <c r="I3" s="223"/>
+      <c r="J3" s="223"/>
+      <c r="K3" s="223"/>
+      <c r="L3" s="223"/>
+      <c r="P3" s="232"/>
+      <c r="Q3" s="232"/>
+      <c r="R3" s="232"/>
+      <c r="S3" s="232"/>
+      <c r="T3" s="232"/>
+      <c r="U3" s="232"/>
+      <c r="V3" s="232"/>
+      <c r="W3" s="232"/>
+      <c r="X3" s="232"/>
+      <c r="Y3" s="232"/>
+      <c r="Z3" s="232"/>
       <c r="AB3" s="143"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="109"/>
       <c r="B5" s="94"/>
-      <c r="C5" s="223" t="s">
+      <c r="C5" s="227" t="s">
         <v>185</v>
       </c>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="223"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="223"/>
-      <c r="K5" s="223"/>
-      <c r="L5" s="223"/>
-      <c r="P5" s="227"/>
-      <c r="Q5" s="227"/>
-      <c r="R5" s="227"/>
-      <c r="S5" s="227"/>
-      <c r="T5" s="227"/>
-      <c r="U5" s="227"/>
-      <c r="V5" s="227"/>
-      <c r="W5" s="227"/>
-      <c r="X5" s="227"/>
-      <c r="Y5" s="227"/>
-      <c r="Z5" s="227"/>
+      <c r="D5" s="227"/>
+      <c r="E5" s="227"/>
+      <c r="F5" s="227"/>
+      <c r="G5" s="227"/>
+      <c r="H5" s="227"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="227"/>
+      <c r="K5" s="227"/>
+      <c r="L5" s="227"/>
+      <c r="P5" s="232"/>
+      <c r="Q5" s="232"/>
+      <c r="R5" s="232"/>
+      <c r="S5" s="232"/>
+      <c r="T5" s="232"/>
+      <c r="U5" s="232"/>
+      <c r="V5" s="232"/>
+      <c r="W5" s="232"/>
+      <c r="X5" s="232"/>
+      <c r="Y5" s="232"/>
+      <c r="Z5" s="232"/>
       <c r="AB5" s="144"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -28481,30 +28481,30 @@
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C12" s="223" t="s">
+      <c r="C12" s="227" t="s">
         <v>224</v>
       </c>
-      <c r="D12" s="223"/>
-      <c r="E12" s="223"/>
-      <c r="F12" s="223"/>
-      <c r="G12" s="223"/>
-      <c r="H12" s="223"/>
-      <c r="I12" s="223"/>
-      <c r="J12" s="223"/>
-      <c r="K12" s="223"/>
-      <c r="L12" s="223"/>
+      <c r="D12" s="227"/>
+      <c r="E12" s="227"/>
+      <c r="F12" s="227"/>
+      <c r="G12" s="227"/>
+      <c r="H12" s="227"/>
+      <c r="I12" s="227"/>
+      <c r="J12" s="227"/>
+      <c r="K12" s="227"/>
+      <c r="L12" s="227"/>
       <c r="N12" s="93"/>
-      <c r="P12" s="227"/>
-      <c r="Q12" s="227"/>
-      <c r="R12" s="227"/>
-      <c r="S12" s="227"/>
-      <c r="T12" s="227"/>
-      <c r="U12" s="227"/>
-      <c r="V12" s="227"/>
-      <c r="W12" s="227"/>
-      <c r="X12" s="227"/>
-      <c r="Y12" s="227"/>
-      <c r="Z12" s="227"/>
+      <c r="P12" s="232"/>
+      <c r="Q12" s="232"/>
+      <c r="R12" s="232"/>
+      <c r="S12" s="232"/>
+      <c r="T12" s="232"/>
+      <c r="U12" s="232"/>
+      <c r="V12" s="232"/>
+      <c r="W12" s="232"/>
+      <c r="X12" s="232"/>
+      <c r="Y12" s="232"/>
+      <c r="Z12" s="232"/>
       <c r="AB12" s="144"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -28687,18 +28687,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="223" t="s">
+      <c r="C18" s="227" t="s">
         <v>233</v>
       </c>
-      <c r="D18" s="223"/>
-      <c r="E18" s="223"/>
-      <c r="F18" s="223"/>
-      <c r="G18" s="223"/>
-      <c r="H18" s="223"/>
-      <c r="I18" s="223"/>
-      <c r="J18" s="223"/>
-      <c r="K18" s="223"/>
-      <c r="L18" s="223"/>
+      <c r="D18" s="227"/>
+      <c r="E18" s="227"/>
+      <c r="F18" s="227"/>
+      <c r="G18" s="227"/>
+      <c r="H18" s="227"/>
+      <c r="I18" s="227"/>
+      <c r="J18" s="227"/>
+      <c r="K18" s="227"/>
+      <c r="L18" s="227"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -28881,23 +28881,23 @@
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B24" s="227"/>
-      <c r="C24" s="227"/>
+      <c r="B24" s="232"/>
+      <c r="C24" s="232"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="143"/>
-      <c r="C25" s="223" t="s">
+      <c r="C25" s="227" t="s">
         <v>374</v>
       </c>
-      <c r="D25" s="223"/>
-      <c r="E25" s="223"/>
-      <c r="F25" s="223"/>
-      <c r="G25" s="223"/>
-      <c r="H25" s="223"/>
-      <c r="I25" s="223"/>
-      <c r="J25" s="223"/>
-      <c r="K25" s="223"/>
-      <c r="L25" s="223"/>
+      <c r="D25" s="227"/>
+      <c r="E25" s="227"/>
+      <c r="F25" s="227"/>
+      <c r="G25" s="227"/>
+      <c r="H25" s="227"/>
+      <c r="I25" s="227"/>
+      <c r="J25" s="227"/>
+      <c r="K25" s="227"/>
+      <c r="L25" s="227"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
@@ -29044,18 +29044,18 @@
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="143"/>
-      <c r="C31" s="223" t="s">
+      <c r="C31" s="227" t="s">
         <v>375</v>
       </c>
-      <c r="D31" s="223"/>
-      <c r="E31" s="223"/>
-      <c r="F31" s="223"/>
-      <c r="G31" s="223"/>
-      <c r="H31" s="223"/>
-      <c r="I31" s="223"/>
-      <c r="J31" s="223"/>
-      <c r="K31" s="223"/>
-      <c r="L31" s="223"/>
+      <c r="D31" s="227"/>
+      <c r="E31" s="227"/>
+      <c r="F31" s="227"/>
+      <c r="G31" s="227"/>
+      <c r="H31" s="227"/>
+      <c r="I31" s="227"/>
+      <c r="J31" s="227"/>
+      <c r="K31" s="227"/>
+      <c r="L31" s="227"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
@@ -29239,18 +29239,18 @@
       <c r="C37" s="152"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C38" s="223" t="s">
+      <c r="C38" s="227" t="s">
         <v>322</v>
       </c>
-      <c r="D38" s="223"/>
-      <c r="E38" s="223"/>
-      <c r="F38" s="223"/>
-      <c r="G38" s="223"/>
-      <c r="H38" s="223"/>
-      <c r="I38" s="223"/>
-      <c r="J38" s="223"/>
-      <c r="K38" s="223"/>
-      <c r="L38" s="223"/>
+      <c r="D38" s="227"/>
+      <c r="E38" s="227"/>
+      <c r="F38" s="227"/>
+      <c r="G38" s="227"/>
+      <c r="H38" s="227"/>
+      <c r="I38" s="227"/>
+      <c r="J38" s="227"/>
+      <c r="K38" s="227"/>
+      <c r="L38" s="227"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B39" s="7" t="s">
@@ -29514,12 +29514,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C38:L38"/>
@@ -29527,6 +29521,12 @@
     <mergeCell ref="P12:Z12"/>
     <mergeCell ref="C18:L18"/>
     <mergeCell ref="B24:C24"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA92DBF-FFEC-1E45-B480-E7B67EAC168C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E59ABC-2DF0-2449-8BBC-DD79604B782C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -1434,8 +1434,8 @@
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="175" formatCode="0.0_);\(0.0\)"/>
-    <numFmt numFmtId="176" formatCode="#,##0.0"/>
+    <numFmt numFmtId="171" formatCode="0.0_);\(0.0\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -2337,65 +2337,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="38" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="175" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="18" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="0" fillId="18" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="0" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="18" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="18" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="18" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2412,6 +2358,60 @@
     <xf numFmtId="2" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13015,13 +13015,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>472.12</v>
+    <v>468</v>
     <v>87.89</v>
-    <v>0.86399999999999999</v>
-    <v>1.69</v>
-    <v>1.3460000000000001E-2</v>
-    <v>-0.19</v>
-    <v>-1.493E-3</v>
+    <v>0.82050000000000001</v>
+    <v>-12.21</v>
+    <v>-9.2394999999999991E-2</v>
+    <v>1.5968</v>
+    <v>1.3312999999999998E-2</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13029,25 +13029,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>130</v>
+    <v>131.57499999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46195.969316075782</v>
+    <v>46198.909386943749</v>
     <v>0</v>
-    <v>123.03</v>
-    <v>5928974520</v>
+    <v>118.87</v>
+    <v>5588378812</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>124.58</v>
-    <v>14.5313</v>
-    <v>125.56</v>
-    <v>127.25</v>
-    <v>127.06</v>
+    <v>131.47999999999999</v>
+    <v>15.294</v>
+    <v>132.15</v>
+    <v>119.94</v>
+    <v>121.5368</v>
     <v>46593120</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>1360821</v>
-    <v>1426718</v>
+    <v>1734040</v>
+    <v>1479800</v>
     <v>2011</v>
   </rv>
   <rv s="2">
@@ -13071,17 +13071,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.57999999999999996</v>
-    <v>1.3030999999999999E-2</v>
+    <v>-0.91</v>
+    <v>-2.0253999999999998E-2</v>
     <v>US</v>
-    <v>45.15</v>
+    <v>44.55</v>
     <v>Index</v>
     <v>3</v>
-    <v>44.81</v>
+    <v>43.98</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.95</v>
-    <v>44.51</v>
-    <v>45.09</v>
+    <v>44.53</v>
+    <v>44.93</v>
+    <v>44.02</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13859,7 +13859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I64"/>
+  <dimension ref="B1:I65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -13876,18 +13876,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="231" t="s">
+      <c r="B2" s="251" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="232"/>
-      <c r="E2" s="231" t="s">
+      <c r="C2" s="252"/>
+      <c r="E2" s="251" t="s">
         <v>296</v>
       </c>
-      <c r="F2" s="232"/>
-      <c r="H2" s="231" t="s">
+      <c r="F2" s="252"/>
+      <c r="H2" s="251" t="s">
         <v>338</v>
       </c>
-      <c r="I2" s="232"/>
+      <c r="I2" s="252"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC149</f>
-        <v>6208145.75</v>
+        <v>5851512.7800000003</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -13926,7 +13926,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>4816324.75</v>
+        <v>4459691.78</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -13943,7 +13943,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>127.25</v>
+        <v>119.94</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>252</v>
@@ -13967,14 +13967,14 @@
       </c>
       <c r="C6" s="210" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>127.06</v>
+        <v>121.5368</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>246</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC146</f>
-        <v>37.530264782647187</v>
+        <v>35.374302224209849</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -13991,14 +13991,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>1.69</v>
+        <v>-12.21</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC147</f>
-        <v>5.6585115991708514</v>
+        <v>5.3334528974817434</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -14015,14 +14015,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.19</v>
+        <v>1.5968</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>274</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC157</f>
-        <v>4.2546037196372205E-2</v>
+        <v>4.513909649189897E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.19325902658177105</v>
+        <v>0.26598475181365988</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14039,14 +14039,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.3460000000000001E-2</v>
+        <v>-9.2394999999999991E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>297</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC158</f>
-        <v>2.6645162398704111E-2</v>
+        <v>2.8269108848049843E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -14055,14 +14055,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.493E-3</v>
+        <v>1.3312999999999998E-2</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>302</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC160</f>
-        <v>3.9192056662007329E-3</v>
+        <v>4.1580700435554716E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="C11" s="211" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>472.12</v>
+        <v>468</v>
       </c>
       <c r="E11" s="188" t="s">
         <v>298</v>
@@ -14103,7 +14103,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.86399999999999999</v>
+        <v>0.82050000000000001</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>104</v>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1426718</v>
+        <v>1479800</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>105</v>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC172</f>
-        <v>0.22419270681587977</v>
+        <v>0.23785661115825163</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14148,10 +14148,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="233" t="s">
+      <c r="B17" s="253" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="233"/>
+      <c r="C17" s="253"/>
       <c r="E17" s="186" t="s">
         <v>305</v>
       </c>
@@ -14224,14 +14224,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="233" t="s">
+      <c r="B25" s="253" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="233"/>
-      <c r="E25" s="231" t="s">
+      <c r="C25" s="253"/>
+      <c r="E25" s="251" t="s">
         <v>353</v>
       </c>
-      <c r="F25" s="232"/>
+      <c r="F25" s="252"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.09</v>
+        <v>44.02</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14260,7 +14260,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.5090000000000005E-2</v>
+        <v>4.4020000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14280,15 +14280,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="230" t="s">
+      <c r="B33" s="254" t="s">
         <v>348</v>
       </c>
-      <c r="C33" s="230"/>
-      <c r="D33" s="230"/>
-      <c r="E33" s="230"/>
-      <c r="F33" s="230"/>
-      <c r="G33" s="230"/>
-      <c r="H33" s="230"/>
+      <c r="C33" s="254"/>
+      <c r="D33" s="254"/>
+      <c r="E33" s="254"/>
+      <c r="F33" s="254"/>
+      <c r="G33" s="254"/>
+      <c r="H33" s="254"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14307,24 +14307,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="230"/>
-      <c r="C39" s="230"/>
-      <c r="D39" s="230"/>
-      <c r="E39" s="230"/>
-      <c r="F39" s="230"/>
-      <c r="G39" s="230"/>
-      <c r="H39" s="230"/>
+      <c r="B39" s="254"/>
+      <c r="C39" s="254"/>
+      <c r="D39" s="254"/>
+      <c r="E39" s="254"/>
+      <c r="F39" s="254"/>
+      <c r="G39" s="254"/>
+      <c r="H39" s="254"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="230" t="s">
+      <c r="B42" s="254" t="s">
         <v>351</v>
       </c>
-      <c r="C42" s="230"/>
-      <c r="D42" s="230"/>
-      <c r="E42" s="230"/>
-      <c r="F42" s="230"/>
-      <c r="G42" s="230"/>
-      <c r="H42" s="230"/>
+      <c r="C42" s="254"/>
+      <c r="D42" s="254"/>
+      <c r="E42" s="254"/>
+      <c r="F42" s="254"/>
+      <c r="G42" s="254"/>
+      <c r="H42" s="254"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14339,24 +14339,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="230"/>
-      <c r="C49" s="230"/>
-      <c r="D49" s="230"/>
-      <c r="E49" s="230"/>
-      <c r="F49" s="230"/>
-      <c r="G49" s="230"/>
-      <c r="H49" s="230"/>
+      <c r="B49" s="254"/>
+      <c r="C49" s="254"/>
+      <c r="D49" s="254"/>
+      <c r="E49" s="254"/>
+      <c r="F49" s="254"/>
+      <c r="G49" s="254"/>
+      <c r="H49" s="254"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="230" t="s">
+      <c r="B52" s="254" t="s">
         <v>109</v>
       </c>
-      <c r="C52" s="230"/>
-      <c r="D52" s="230"/>
-      <c r="E52" s="230"/>
-      <c r="F52" s="230"/>
-      <c r="G52" s="230"/>
-      <c r="H52" s="230"/>
+      <c r="C52" s="254"/>
+      <c r="D52" s="254"/>
+      <c r="E52" s="254"/>
+      <c r="F52" s="254"/>
+      <c r="G52" s="254"/>
+      <c r="H52" s="254"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="41" t="s">
@@ -14392,27 +14392,16 @@
         <v>381</v>
       </c>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B60" s="41" t="s">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B61" s="41" t="s">
         <v>352</v>
       </c>
-      <c r="C60" s="41" t="s">
+      <c r="C61" s="41" t="s">
         <v>400</v>
       </c>
-      <c r="D60" s="41"/>
-      <c r="E60" s="41" t="s">
+      <c r="D61" s="41"/>
+      <c r="E61" s="41" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
@@ -14420,35 +14409,46 @@
         <v>377</v>
       </c>
       <c r="C62" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="230"/>
-      <c r="C64" s="230"/>
-      <c r="D64" s="230"/>
-      <c r="E64" s="230"/>
-      <c r="F64" s="230"/>
-      <c r="G64" s="230"/>
-      <c r="H64" s="230"/>
+    <row r="65" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="254"/>
+      <c r="C65" s="254"/>
+      <c r="D65" s="254"/>
+      <c r="E65" s="254"/>
+      <c r="F65" s="254"/>
+      <c r="G65" s="254"/>
+      <c r="H65" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B64:H64"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14518,36 +14518,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="230" t="s">
+      <c r="S2" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="230"/>
-      <c r="U2" s="230"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="230"/>
-      <c r="Y2" s="230"/>
-      <c r="Z2" s="230"/>
-      <c r="AA2" s="230" t="s">
+      <c r="T2" s="254"/>
+      <c r="U2" s="254"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="254"/>
+      <c r="X2" s="254"/>
+      <c r="Y2" s="254"/>
+      <c r="Z2" s="254"/>
+      <c r="AA2" s="254" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="230"/>
-      <c r="AC2" s="230"/>
+      <c r="AB2" s="254"/>
+      <c r="AC2" s="254"/>
       <c r="AE2" s="86" t="s">
         <v>85</v>
       </c>
@@ -14558,32 +14558,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="262" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="240" t="s">
+      <c r="S4" s="263" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="241"/>
-      <c r="U4" s="241"/>
-      <c r="V4" s="241"/>
-      <c r="W4" s="241"/>
-      <c r="X4" s="241"/>
-      <c r="Y4" s="241"/>
-      <c r="Z4" s="241"/>
-      <c r="AA4" s="241"/>
-      <c r="AB4" s="241"/>
-      <c r="AC4" s="241"/>
+      <c r="T4" s="264"/>
+      <c r="U4" s="264"/>
+      <c r="V4" s="264"/>
+      <c r="W4" s="264"/>
+      <c r="X4" s="264"/>
+      <c r="Y4" s="264"/>
+      <c r="Z4" s="264"/>
+      <c r="AA4" s="264"/>
+      <c r="AB4" s="264"/>
+      <c r="AC4" s="264"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15271,33 +15271,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="239" t="s">
+      <c r="C13" s="262" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="239"/>
-      <c r="G13" s="239"/>
-      <c r="H13" s="239"/>
-      <c r="I13" s="239"/>
-      <c r="J13" s="239"/>
-      <c r="K13" s="239"/>
-      <c r="L13" s="239"/>
+      <c r="D13" s="262"/>
+      <c r="E13" s="262"/>
+      <c r="F13" s="262"/>
+      <c r="G13" s="262"/>
+      <c r="H13" s="262"/>
+      <c r="I13" s="262"/>
+      <c r="J13" s="262"/>
+      <c r="K13" s="262"/>
+      <c r="L13" s="262"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="240" t="s">
+      <c r="S13" s="263" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="241"/>
-      <c r="U13" s="241"/>
-      <c r="V13" s="241"/>
-      <c r="W13" s="241"/>
-      <c r="X13" s="241"/>
-      <c r="Y13" s="241"/>
-      <c r="Z13" s="241"/>
-      <c r="AA13" s="241"/>
-      <c r="AB13" s="241"/>
-      <c r="AC13" s="241"/>
+      <c r="T13" s="264"/>
+      <c r="U13" s="264"/>
+      <c r="V13" s="264"/>
+      <c r="W13" s="264"/>
+      <c r="X13" s="264"/>
+      <c r="Y13" s="264"/>
+      <c r="Z13" s="264"/>
+      <c r="AA13" s="264"/>
+      <c r="AB13" s="264"/>
+      <c r="AC13" s="264"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -15443,35 +15443,35 @@
       </c>
       <c r="S15" s="47"/>
       <c r="T15" s="96">
-        <f>T6/S6-1</f>
+        <f t="shared" ref="T15:AA16" si="12">T6/S6-1</f>
         <v>9.5254640085053799E-2</v>
       </c>
       <c r="U15" s="96">
-        <f>U6/T6-1</f>
+        <f t="shared" si="12"/>
         <v>0.10595303806061529</v>
       </c>
       <c r="V15" s="96">
-        <f>V6/U6-1</f>
+        <f t="shared" si="12"/>
         <v>9.563037454751977E-2</v>
       </c>
       <c r="W15" s="96">
-        <f>W6/V6-1</f>
+        <f t="shared" si="12"/>
         <v>0.10310125820081995</v>
       </c>
       <c r="X15" s="96">
-        <f>X6/W6-1</f>
+        <f t="shared" si="12"/>
         <v>8.9297411215219391E-2</v>
       </c>
       <c r="Y15" s="96">
-        <f>Y6/X6-1</f>
+        <f t="shared" si="12"/>
         <v>5.5753820411257982E-2</v>
       </c>
       <c r="Z15" s="97">
-        <f>Z6/Y6-1</f>
+        <f t="shared" si="12"/>
         <v>3.5586042940987106E-2</v>
       </c>
       <c r="AA15" s="96">
-        <f>AA6/Z6-1</f>
+        <f t="shared" si="12"/>
         <v>5.1492977505698256E-3</v>
       </c>
       <c r="AB15" s="96"/>
@@ -15484,39 +15484,39 @@
       </c>
       <c r="C16" s="47"/>
       <c r="D16" s="96">
-        <f t="shared" ref="D16:L19" si="12">D7/C7-1</f>
+        <f t="shared" ref="D16:L19" si="13">D7/C7-1</f>
         <v>0.161813978857692</v>
       </c>
       <c r="E16" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.11461849723905115</v>
       </c>
       <c r="F16" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.10126759998395451</v>
       </c>
       <c r="G16" s="97">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.45200065565410608</v>
       </c>
       <c r="H16" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.27086178739416744</v>
       </c>
       <c r="I16" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.23422854803247262</v>
       </c>
       <c r="J16" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.20242461740023532</v>
       </c>
       <c r="K16" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.25573578323111579</v>
       </c>
       <c r="L16" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.23321008324965398</v>
       </c>
       <c r="O16" s="5"/>
@@ -15527,35 +15527,35 @@
       </c>
       <c r="S16" s="47"/>
       <c r="T16" s="96">
-        <f>T7/S7-1</f>
+        <f t="shared" si="12"/>
         <v>8.6513802986875943E-2</v>
       </c>
       <c r="U16" s="96">
-        <f>U7/T7-1</f>
+        <f t="shared" si="12"/>
         <v>-7.8444984380423577E-3</v>
       </c>
       <c r="V16" s="96">
-        <f>V7/U7-1</f>
+        <f t="shared" si="12"/>
         <v>0.25118947663028268</v>
       </c>
       <c r="W16" s="96">
-        <f>W7/V7-1</f>
+        <f t="shared" si="12"/>
         <v>0.15216418745106819</v>
       </c>
       <c r="X16" s="96">
-        <f>X7/W7-1</f>
+        <f t="shared" si="12"/>
         <v>2.01912342862689E-2</v>
       </c>
       <c r="Y16" s="96">
-        <f>Y7/X7-1</f>
+        <f t="shared" si="12"/>
         <v>-3.7965650126076445E-2</v>
       </c>
       <c r="Z16" s="97">
-        <f>Z7/Y7-1</f>
+        <f t="shared" si="12"/>
         <v>1.9435240591464398E-2</v>
       </c>
       <c r="AA16" s="96">
-        <f>AA7/Z7-1</f>
+        <f t="shared" si="12"/>
         <v>-4.8932764140875218E-2</v>
       </c>
       <c r="AB16" s="96"/>
@@ -15568,39 +15568,39 @@
       </c>
       <c r="C17" s="47"/>
       <c r="D17" s="96">
-        <f t="shared" ref="D17:H17" si="13">D8/C8-1</f>
+        <f t="shared" ref="D17:H17" si="14">D8/C8-1</f>
         <v>0.32687160353637768</v>
       </c>
       <c r="E17" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.25961244574851761</v>
       </c>
       <c r="F17" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.10744443366009904</v>
       </c>
       <c r="G17" s="97">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-7.9623137598597737E-2</v>
       </c>
       <c r="H17" s="96">
+        <f t="shared" si="14"/>
+        <v>-5.0000000000000044E-2</v>
+      </c>
+      <c r="I17" s="96">
         <f t="shared" si="13"/>
-        <v>-5.0000000000000044E-2</v>
-      </c>
-      <c r="I17" s="96">
-        <f t="shared" si="12"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="J17" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="K17" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="L17" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="O17" s="5"/>
@@ -15615,27 +15615,27 @@
         <v>6.917180781454535E-3</v>
       </c>
       <c r="U17" s="96">
-        <f t="shared" ref="U17:Z17" si="14">U8/T8-1</f>
+        <f t="shared" ref="U17:Z17" si="15">U8/T8-1</f>
         <v>5.9691793538804383E-2</v>
       </c>
       <c r="V17" s="96">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.0021901007446301E-2</v>
       </c>
       <c r="W17" s="96">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.15835140997830799</v>
       </c>
       <c r="X17" s="96">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-4.3517049960348886E-2</v>
       </c>
       <c r="Y17" s="96">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.5706290807337586E-2</v>
       </c>
       <c r="Z17" s="97">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.10055431294369344</v>
       </c>
       <c r="AA17" s="96">
@@ -15647,83 +15647,83 @@
     </row>
     <row r="18" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="str">
-        <f t="shared" ref="B18:B19" si="15">B9</f>
+        <f t="shared" ref="B18:B19" si="16">B9</f>
         <v>In-App purchases</v>
       </c>
       <c r="C18" s="47"/>
       <c r="D18" s="96">
-        <f t="shared" ref="D18:D19" si="16">D9/C9-1</f>
+        <f t="shared" ref="D18:D19" si="17">D9/C9-1</f>
         <v>1.6809833694866234</v>
       </c>
       <c r="E18" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.87027347753384765</v>
       </c>
       <c r="F18" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.11478672165662052</v>
       </c>
       <c r="G18" s="97">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.7240835122758895E-2</v>
       </c>
       <c r="H18" s="96">
-        <f t="shared" ref="H18:H19" si="17">H9/G9-1</f>
+        <f t="shared" ref="H18:H19" si="18">H9/G9-1</f>
         <v>9.3604091010153434E-2</v>
       </c>
       <c r="I18" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.16071428571428581</v>
       </c>
       <c r="J18" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.17230769230769227</v>
       </c>
       <c r="K18" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.37583333333333346</v>
       </c>
       <c r="L18" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="O18" s="5"/>
       <c r="Q18" s="92"/>
       <c r="R18" s="1" t="str">
-        <f t="shared" ref="R18:R19" si="18">R9</f>
+        <f t="shared" ref="R18:R19" si="19">R9</f>
         <v>In-App purchases</v>
       </c>
       <c r="S18" s="47"/>
       <c r="T18" s="96">
-        <f t="shared" ref="T18:AA18" si="19">T9/S9-1</f>
+        <f t="shared" ref="T18:AA18" si="20">T9/S9-1</f>
         <v>-7.5176886792452824E-2</v>
       </c>
       <c r="U18" s="96">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-2.8583572415258773E-2</v>
       </c>
       <c r="V18" s="96">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.2815576460293094E-2</v>
       </c>
       <c r="W18" s="96">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.10040245710654516</v>
       </c>
       <c r="X18" s="96">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>6.7949951876804526E-2</v>
       </c>
       <c r="Y18" s="96">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-0.13923936553713046</v>
       </c>
       <c r="Z18" s="97">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-0.11569469165532409</v>
       </c>
       <c r="AA18" s="96">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-0.13303338858631297</v>
       </c>
       <c r="AB18" s="96"/>
@@ -15731,83 +15731,83 @@
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Other</v>
       </c>
       <c r="C19" s="47"/>
       <c r="D19" s="96">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>6.9113924050632916</v>
       </c>
       <c r="E19" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>9.1199999999999948E-2</v>
       </c>
       <c r="F19" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.89589442815249276</v>
       </c>
       <c r="G19" s="97">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.49806651198762575</v>
       </c>
       <c r="H19" s="96">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="I19" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.35000000000000009</v>
       </c>
       <c r="J19" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="K19" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.25</v>
       </c>
       <c r="L19" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="O19" s="5"/>
       <c r="Q19" s="92"/>
       <c r="R19" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>Other</v>
       </c>
       <c r="S19" s="47"/>
       <c r="T19" s="96">
-        <f t="shared" ref="T19:AA19" si="20">T10/S10-1</f>
+        <f t="shared" ref="T19:AA19" si="21">T10/S10-1</f>
         <v>0.36013986013986021</v>
       </c>
       <c r="U19" s="96">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-1.2853470437018011E-2</v>
       </c>
       <c r="V19" s="96">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.16145833333333326</v>
       </c>
       <c r="W19" s="96">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.13452914798206272</v>
       </c>
       <c r="X19" s="96">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-9.4861660079051391E-2</v>
       </c>
       <c r="Y19" s="96">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.15065502183406121</v>
       </c>
       <c r="Z19" s="97">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.29411764705882359</v>
       </c>
       <c r="AA19" s="96">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-8.9999999999999969E-2</v>
       </c>
       <c r="AB19" s="96"/>
@@ -15820,39 +15820,39 @@
       </c>
       <c r="C20" s="47"/>
       <c r="D20" s="104">
-        <f t="shared" ref="D20:L20" si="21">D11/C11-1</f>
+        <f t="shared" ref="D20:L20" si="22">D11/C11-1</f>
         <v>0.47343004801173971</v>
       </c>
       <c r="E20" s="104">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.43739157498748282</v>
       </c>
       <c r="F20" s="104">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.4084189874394899</v>
       </c>
       <c r="G20" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.38710656342577243</v>
       </c>
       <c r="H20" s="104">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.14819107180203317</v>
       </c>
       <c r="I20" s="104">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.14173008987896241</v>
       </c>
       <c r="J20" s="104">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.25957092608318066</v>
       </c>
       <c r="K20" s="104">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.34811478375780913</v>
       </c>
       <c r="L20" s="104">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.34572572506586563</v>
       </c>
       <c r="O20" s="5"/>
@@ -15863,35 +15863,35 @@
       </c>
       <c r="S20" s="47"/>
       <c r="T20" s="104">
-        <f t="shared" ref="T20:AA20" si="22">T11/S11-1</f>
+        <f t="shared" ref="T20:AA20" si="23">T11/S11-1</f>
         <v>8.0004710447660665E-2</v>
       </c>
       <c r="U20" s="104">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>8.8040125860618712E-2</v>
       </c>
       <c r="V20" s="104">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.10113576712001904</v>
       </c>
       <c r="W20" s="104">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>9.327260198575904E-2</v>
       </c>
       <c r="X20" s="104">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>7.7093532594691982E-2</v>
       </c>
       <c r="Y20" s="104">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4.105434778608319E-2</v>
       </c>
       <c r="Z20" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>3.2166947127282075E-2</v>
       </c>
       <c r="AA20" s="104">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-1.1502327317813865E-3</v>
       </c>
       <c r="AB20" s="104"/>
@@ -15906,33 +15906,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="239" t="s">
+      <c r="C23" s="262" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="239"/>
-      <c r="E23" s="239"/>
-      <c r="F23" s="239"/>
-      <c r="G23" s="239"/>
-      <c r="H23" s="239"/>
-      <c r="I23" s="239"/>
-      <c r="J23" s="239"/>
-      <c r="K23" s="239"/>
-      <c r="L23" s="239"/>
+      <c r="D23" s="262"/>
+      <c r="E23" s="262"/>
+      <c r="F23" s="262"/>
+      <c r="G23" s="262"/>
+      <c r="H23" s="262"/>
+      <c r="I23" s="262"/>
+      <c r="J23" s="262"/>
+      <c r="K23" s="262"/>
+      <c r="L23" s="262"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="240" t="s">
+      <c r="S23" s="263" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="241"/>
-      <c r="U23" s="241"/>
-      <c r="V23" s="241"/>
-      <c r="W23" s="241"/>
-      <c r="X23" s="241"/>
-      <c r="Y23" s="241"/>
-      <c r="Z23" s="241"/>
-      <c r="AA23" s="241"/>
-      <c r="AB23" s="241"/>
-      <c r="AC23" s="241"/>
+      <c r="T23" s="264"/>
+      <c r="U23" s="264"/>
+      <c r="V23" s="264"/>
+      <c r="W23" s="264"/>
+      <c r="X23" s="264"/>
+      <c r="Y23" s="264"/>
+      <c r="Z23" s="264"/>
+      <c r="AA23" s="264"/>
+      <c r="AB23" s="264"/>
+      <c r="AC23" s="264"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -15943,43 +15943,43 @@
         <v>125</v>
       </c>
       <c r="C24" s="12">
-        <f t="shared" ref="C24:L24" si="23">C5</f>
+        <f t="shared" ref="C24:L24" si="24">C5</f>
         <v>2021</v>
       </c>
       <c r="D24" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2022</v>
       </c>
       <c r="E24" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2023</v>
       </c>
       <c r="F24" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2024</v>
       </c>
       <c r="G24" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2025</v>
       </c>
       <c r="H24" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2026</v>
       </c>
       <c r="I24" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2027</v>
       </c>
       <c r="J24" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2028</v>
       </c>
       <c r="K24" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2029</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2030</v>
       </c>
       <c r="O24" s="5"/>
@@ -15988,47 +15988,47 @@
         <v>125</v>
       </c>
       <c r="S24" s="12" t="str">
-        <f t="shared" ref="S24:AC24" si="24">S5</f>
+        <f t="shared" ref="S24:AC24" si="25">S5</f>
         <v>Q2 2024</v>
       </c>
       <c r="T24" s="12" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>Q3 2024</v>
       </c>
       <c r="U24" s="12" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>Q4 2024</v>
       </c>
       <c r="V24" s="12" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>Q1 2025</v>
       </c>
       <c r="W24" s="12" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>Q2 2025</v>
       </c>
       <c r="X24" s="12" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>Q3 2025</v>
       </c>
       <c r="Y24" s="12" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>Q4 2025</v>
       </c>
       <c r="Z24" s="12" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>Q1 2026</v>
       </c>
       <c r="AA24" s="12" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>FQ1</v>
       </c>
       <c r="AB24" s="12" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>FQ2</v>
       </c>
       <c r="AC24" s="12" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>FQ3</v>
       </c>
       <c r="AE24" s="8" t="str">
@@ -16041,20 +16041,20 @@
         <v>408</v>
       </c>
       <c r="C25" s="47"/>
-      <c r="D25" s="257">
+      <c r="D25" s="239">
         <f>D17</f>
         <v>0.32687160353637768</v>
       </c>
-      <c r="E25" s="257">
-        <f t="shared" ref="E25:G25" si="25">E17</f>
+      <c r="E25" s="239">
+        <f t="shared" ref="E25:G25" si="26">E17</f>
         <v>0.25961244574851761</v>
       </c>
-      <c r="F25" s="257">
-        <f t="shared" si="25"/>
+      <c r="F25" s="239">
+        <f t="shared" si="26"/>
         <v>0.10744443366009904</v>
       </c>
-      <c r="G25" s="258">
-        <f t="shared" si="25"/>
+      <c r="G25" s="240">
+        <f t="shared" si="26"/>
         <v>-7.9623137598597737E-2</v>
       </c>
       <c r="H25" s="98">
@@ -16083,28 +16083,28 @@
         <f>T17</f>
         <v>6.917180781454535E-3</v>
       </c>
-      <c r="U25" s="257">
-        <f t="shared" ref="U25:Z25" si="26">U17</f>
+      <c r="U25" s="239">
+        <f t="shared" ref="U25:Z25" si="27">U17</f>
         <v>5.9691793538804383E-2</v>
       </c>
-      <c r="V25" s="257">
-        <f t="shared" si="26"/>
+      <c r="V25" s="239">
+        <f t="shared" si="27"/>
         <v>5.0021901007446301E-2</v>
       </c>
-      <c r="W25" s="257">
-        <f t="shared" si="26"/>
+      <c r="W25" s="239">
+        <f t="shared" si="27"/>
         <v>-0.15835140997830799</v>
       </c>
-      <c r="X25" s="257">
-        <f t="shared" si="26"/>
+      <c r="X25" s="239">
+        <f t="shared" si="27"/>
         <v>-4.3517049960348886E-2</v>
       </c>
-      <c r="Y25" s="257">
-        <f t="shared" si="26"/>
+      <c r="Y25" s="239">
+        <f t="shared" si="27"/>
         <v>6.5706290807337586E-2</v>
       </c>
-      <c r="Z25" s="258">
-        <f t="shared" si="26"/>
+      <c r="Z25" s="240">
+        <f t="shared" si="27"/>
         <v>0.10055431294369344</v>
       </c>
       <c r="AA25" s="98">
@@ -16119,20 +16119,20 @@
         <v>410</v>
       </c>
       <c r="C26" s="47"/>
-      <c r="D26" s="257">
+      <c r="D26" s="239">
         <f>D19</f>
         <v>6.9113924050632916</v>
       </c>
-      <c r="E26" s="257">
-        <f t="shared" ref="E26:G26" si="27">E19</f>
+      <c r="E26" s="239">
+        <f t="shared" ref="E26:G26" si="28">E19</f>
         <v>9.1199999999999948E-2</v>
       </c>
-      <c r="F26" s="257">
-        <f t="shared" si="27"/>
+      <c r="F26" s="239">
+        <f t="shared" si="28"/>
         <v>0.89589442815249276</v>
       </c>
-      <c r="G26" s="258">
-        <f t="shared" si="27"/>
+      <c r="G26" s="240">
+        <f t="shared" si="28"/>
         <v>0.49806651198762575</v>
       </c>
       <c r="H26" s="98">
@@ -16161,28 +16161,28 @@
         <f>T19</f>
         <v>0.36013986013986021</v>
       </c>
-      <c r="U26" s="257">
-        <f t="shared" ref="U26:Z26" si="28">U19</f>
+      <c r="U26" s="239">
+        <f t="shared" ref="U26:Z26" si="29">U19</f>
         <v>-1.2853470437018011E-2</v>
       </c>
-      <c r="V26" s="257">
-        <f t="shared" si="28"/>
+      <c r="V26" s="239">
+        <f t="shared" si="29"/>
         <v>0.16145833333333326</v>
       </c>
-      <c r="W26" s="257">
-        <f t="shared" si="28"/>
+      <c r="W26" s="239">
+        <f t="shared" si="29"/>
         <v>0.13452914798206272</v>
       </c>
-      <c r="X26" s="257">
-        <f t="shared" si="28"/>
+      <c r="X26" s="239">
+        <f t="shared" si="29"/>
         <v>-9.4861660079051391E-2</v>
       </c>
-      <c r="Y26" s="257">
-        <f t="shared" si="28"/>
+      <c r="Y26" s="239">
+        <f t="shared" si="29"/>
         <v>0.15065502183406121</v>
       </c>
-      <c r="Z26" s="258">
-        <f t="shared" si="28"/>
+      <c r="Z26" s="240">
+        <f t="shared" si="29"/>
         <v>0.29411764705882359</v>
       </c>
       <c r="AA26" s="98">
@@ -16221,19 +16221,19 @@
         <v>63240</v>
       </c>
       <c r="I27" s="24">
-        <f t="shared" ref="I27:L27" si="29">H27*(1+I29)</f>
+        <f t="shared" ref="I27:L27" si="30">H27*(1+I29)</f>
         <v>79050</v>
       </c>
       <c r="J27" s="24">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>100393.5</v>
       </c>
       <c r="K27" s="24">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>127499.745</v>
       </c>
       <c r="L27" s="24">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>163199.67360000001</v>
       </c>
       <c r="N27" s="91" t="s">
@@ -16318,19 +16318,19 @@
         <v>158389</v>
       </c>
       <c r="I28" s="24">
-        <f t="shared" ref="I28:L28" si="30">H28*(1+I30)</f>
+        <f t="shared" ref="I28:L28" si="31">H28*(1+I30)</f>
         <v>191650.69</v>
       </c>
       <c r="J28" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>234772.09525000001</v>
       </c>
       <c r="K28" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>288769.6771575</v>
       </c>
       <c r="L28" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>355186.70290372497</v>
       </c>
       <c r="N28" s="91" t="s">
@@ -16396,15 +16396,15 @@
         <v>0.69791666666666674</v>
       </c>
       <c r="E29" s="96">
-        <f t="shared" ref="E29:G29" si="31">E27/D27-1</f>
+        <f t="shared" ref="E29:G29" si="32">E27/D27-1</f>
         <v>0.65030674846625769</v>
       </c>
       <c r="F29" s="96">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.50557620817843874</v>
       </c>
       <c r="G29" s="97">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.30123456790123448</v>
       </c>
       <c r="H29" s="98">
@@ -16433,27 +16433,27 @@
         <v>9.0909090909090828E-2</v>
       </c>
       <c r="U29" s="96">
-        <f t="shared" ref="U29:Z29" si="32">U27/T27-1</f>
+        <f t="shared" ref="U29:Z29" si="33">U27/T27-1</f>
         <v>8.870967741935476E-2</v>
       </c>
       <c r="V29" s="96">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.15061728395061724</v>
       </c>
       <c r="W29" s="96">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2.3605150214592197E-2</v>
       </c>
       <c r="X29" s="96">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.8700209643605783E-2</v>
       </c>
       <c r="Y29" s="96">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4.3564356435643603E-2</v>
       </c>
       <c r="Z29" s="97">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.2106261859582466E-2</v>
       </c>
       <c r="AA29" s="98">
@@ -16473,15 +16473,15 @@
         <v>0.49876543209876534</v>
       </c>
       <c r="E30" s="96">
-        <f t="shared" ref="E30:G30" si="33">E28/D28-1</f>
+        <f t="shared" ref="E30:G30" si="34">E28/D28-1</f>
         <v>0.45634266886326191</v>
       </c>
       <c r="F30" s="96">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.32013574660633481</v>
       </c>
       <c r="G30" s="97">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.14053127677806332</v>
       </c>
       <c r="H30" s="107">
@@ -16510,27 +16510,27 @@
         <v>9.1698841698841793E-2</v>
       </c>
       <c r="U30" s="96">
-        <f t="shared" ref="U30:Z30" si="34">U28/T28-1</f>
+        <f t="shared" ref="U30:Z30" si="35">U28/T28-1</f>
         <v>3.1830238726790361E-2</v>
       </c>
       <c r="V30" s="96">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.11568123393316188</v>
       </c>
       <c r="W30" s="96">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-1.4592933947772613E-2</v>
       </c>
       <c r="X30" s="96">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5.4559625876851037E-2</v>
       </c>
       <c r="Y30" s="96">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-1.6260162601625994E-2</v>
       </c>
       <c r="Z30" s="97">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>3.5311795642374078E-2</v>
       </c>
       <c r="AA30" s="107">
@@ -16544,23 +16544,23 @@
       <c r="B31" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="C31" s="259">
+      <c r="C31" s="241">
         <f>Statement!M216</f>
         <v>1.0131842105263158</v>
       </c>
-      <c r="D31" s="259">
+      <c r="D31" s="241">
         <f>Statement!N216</f>
         <v>0.79169911504424784</v>
       </c>
-      <c r="E31" s="259">
+      <c r="E31" s="241">
         <f>Statement!O216</f>
         <v>0.60951100244498779</v>
       </c>
-      <c r="F31" s="259">
+      <c r="F31" s="241">
         <f>Statement!P216</f>
         <v>0.51219216417910451</v>
       </c>
-      <c r="G31" s="260">
+      <c r="G31" s="242">
         <f>Statement!Q216</f>
         <v>0.65942928039702231</v>
       </c>
@@ -16584,35 +16584,35 @@
       <c r="R31" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="S31" s="259">
+      <c r="S31" s="241">
         <f>Statement!T216</f>
         <v>0.13868200836820083</v>
       </c>
-      <c r="T31" s="266">
+      <c r="T31" s="248">
         <f>Statement!U216</f>
         <v>0.13784688995215311</v>
       </c>
-      <c r="U31" s="259">
+      <c r="U31" s="241">
         <f>Statement!V216</f>
         <v>0.13332089552238807</v>
       </c>
-      <c r="V31" s="259">
+      <c r="V31" s="241">
         <f>Statement!W216</f>
         <v>0.14914095079232695</v>
       </c>
-      <c r="W31" s="259">
+      <c r="W31" s="241">
         <f>Statement!X216</f>
         <v>0.17549403747870529</v>
       </c>
-      <c r="X31" s="259">
+      <c r="X31" s="241">
         <f>Statement!Y216</f>
         <v>0.16978190630048465</v>
       </c>
-      <c r="Y31" s="259">
+      <c r="Y31" s="241">
         <f>Statement!Z216</f>
         <v>0.1672539288668321</v>
       </c>
-      <c r="Z31" s="260">
+      <c r="Z31" s="242">
         <f>Statement!AA216</f>
         <v>0.1645171588188348</v>
       </c>
@@ -16630,23 +16630,23 @@
       <c r="B32" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C32" s="261">
+      <c r="C32" s="243">
         <f>Statement!M215</f>
         <v>6.1728395061728392E-2</v>
       </c>
-      <c r="D32" s="261">
+      <c r="D32" s="243">
         <f>Statement!N215</f>
         <v>6.919275123558484E-2</v>
       </c>
-      <c r="E32" s="261">
+      <c r="E32" s="243">
         <f>Statement!O215</f>
         <v>7.4660633484162894E-2</v>
       </c>
-      <c r="F32" s="261">
+      <c r="F32" s="243">
         <f>Statement!P215</f>
         <v>8.1405312767780638E-2</v>
       </c>
-      <c r="G32" s="262">
+      <c r="G32" s="244">
         <f>Statement!Q215</f>
         <v>9.1660405709992482E-2</v>
       </c>
@@ -16655,19 +16655,19 @@
         <v>8.6160781367392927E-2</v>
       </c>
       <c r="I32" s="156">
-        <f t="shared" ref="I32:L32" si="35">H32*(1+I33)</f>
+        <f t="shared" ref="I32:L32" si="36">H32*(1+I33)</f>
         <v>8.099113448534935E-2</v>
       </c>
       <c r="J32" s="156">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>8.5040691209616825E-2</v>
       </c>
       <c r="K32" s="156">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>9.1843946506386179E-2</v>
       </c>
       <c r="L32" s="156">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.10194678062208867</v>
       </c>
       <c r="N32" s="91" t="s">
@@ -16680,35 +16680,35 @@
       <c r="R32" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="S32" s="261">
+      <c r="S32" s="243">
         <f>Statement!T215</f>
         <v>7.7220077220077218E-2</v>
       </c>
-      <c r="T32" s="267">
+      <c r="T32" s="249">
         <f>Statement!U215</f>
         <v>7.6038903625110524E-2</v>
       </c>
-      <c r="U32" s="261">
+      <c r="U32" s="243">
         <f>Statement!V215</f>
         <v>8.1405312767780638E-2</v>
       </c>
-      <c r="V32" s="261">
+      <c r="V32" s="243">
         <f>Statement!W215</f>
         <v>7.9109062980030717E-2</v>
       </c>
-      <c r="W32" s="261">
+      <c r="W32" s="243">
         <f>Statement!X215</f>
         <v>8.4957131722525336E-2</v>
       </c>
-      <c r="X32" s="261">
+      <c r="X32" s="243">
         <f>Statement!Y215</f>
         <v>8.4996304508499626E-2</v>
       </c>
-      <c r="Y32" s="261">
+      <c r="Y32" s="243">
         <f>Statement!Z215</f>
         <v>9.1660405709992482E-2</v>
       </c>
-      <c r="Z32" s="262">
+      <c r="Z32" s="244">
         <f>Statement!AA215</f>
         <v>9.071117561683599E-2</v>
       </c>
@@ -16730,15 +16730,15 @@
         <v>0.12092257001647444</v>
       </c>
       <c r="E33" s="96">
-        <f t="shared" ref="E33:G33" si="36">E32/D32-1</f>
+        <f t="shared" ref="E33:G33" si="37">E32/D32-1</f>
         <v>7.9023917259211318E-2</v>
       </c>
       <c r="F33" s="96">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>9.0337825556334739E-2</v>
       </c>
       <c r="G33" s="97">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.12597572066906548</v>
       </c>
       <c r="H33" s="98">
@@ -16766,27 +16766,27 @@
         <v>-1</v>
       </c>
       <c r="U33" s="96">
-        <f t="shared" ref="U33" si="37">U32/T32-1</f>
+        <f t="shared" ref="U33" si="38">U32/T32-1</f>
         <v>7.0574520236742933E-2</v>
       </c>
       <c r="V33" s="96">
-        <f t="shared" ref="V33" si="38">V32/U32-1</f>
+        <f t="shared" ref="V33" si="39">V32/U32-1</f>
         <v>-2.8207615813727993E-2</v>
       </c>
       <c r="W33" s="96">
-        <f t="shared" ref="W33" si="39">W32/V32-1</f>
+        <f t="shared" ref="W33" si="40">W32/V32-1</f>
         <v>7.392413109444651E-2</v>
       </c>
       <c r="X33" s="96">
-        <f t="shared" ref="X33" si="40">X32/W32-1</f>
+        <f t="shared" ref="X33" si="41">X32/W32-1</f>
         <v>4.6108884775231118E-4</v>
       </c>
       <c r="Y33" s="96">
-        <f t="shared" ref="Y33" si="41">Y32/X32-1</f>
+        <f t="shared" ref="Y33" si="42">Y32/X32-1</f>
         <v>7.8404599353215865E-2</v>
       </c>
       <c r="Z33" s="97">
-        <f t="shared" ref="Z33" si="42">Z32/Y32-1</f>
+        <f t="shared" ref="Z33" si="43">Z32/Y32-1</f>
         <v>-1.0355944704846687E-2</v>
       </c>
       <c r="AA33" s="98">
@@ -16825,19 +16825,19 @@
         <v>13646.919999999998</v>
       </c>
       <c r="I34" s="24">
-        <f t="shared" ref="I34:L34" si="43">I32*I28</f>
+        <f t="shared" ref="I34:L34" si="44">I32*I28</f>
         <v>15522.006807999998</v>
       </c>
       <c r="J34" s="24">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>19965.181256790001</v>
       </c>
       <c r="K34" s="24">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>26521.746781519836</v>
       </c>
       <c r="L34" s="24">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>36210.140880809035</v>
       </c>
       <c r="N34" s="91" t="s">
@@ -16922,19 +16922,19 @@
         <v>144742.08000000002</v>
       </c>
       <c r="I35" s="24">
-        <f t="shared" ref="I35:L35" si="44">I28-I34</f>
+        <f t="shared" ref="I35:L35" si="45">I28-I34</f>
         <v>176128.683192</v>
       </c>
       <c r="J35" s="24">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>214806.91399321001</v>
       </c>
       <c r="K35" s="24">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>262247.93037598016</v>
       </c>
       <c r="L35" s="24">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>318976.56202291592</v>
       </c>
       <c r="N35" s="91" t="s">
@@ -16994,105 +16994,105 @@
       <c r="B36" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C36" s="261">
+      <c r="C36" s="243">
         <f>Statement!M217</f>
         <v>0.72031250000000002</v>
       </c>
-      <c r="D36" s="261">
+      <c r="D36" s="243">
         <f>Statement!N217</f>
         <v>1.1373619631901841</v>
       </c>
-      <c r="E36" s="261">
+      <c r="E36" s="243">
         <f>Statement!O217</f>
         <v>1.2889591078066915</v>
       </c>
-      <c r="F36" s="261">
+      <c r="F36" s="243">
         <f>Statement!P217</f>
         <v>0.95439506172839506</v>
       </c>
-      <c r="G36" s="262">
+      <c r="G36" s="244">
         <f>Statement!Q217</f>
         <v>0.76810246679316885</v>
       </c>
-      <c r="H36" s="263">
+      <c r="H36" s="245">
         <v>0.7</v>
       </c>
-      <c r="I36" s="263">
+      <c r="I36" s="245">
         <v>0.65</v>
       </c>
-      <c r="J36" s="263">
+      <c r="J36" s="245">
         <v>0.6</v>
       </c>
-      <c r="K36" s="263">
+      <c r="K36" s="245">
         <v>0.65</v>
       </c>
-      <c r="L36" s="263">
+      <c r="L36" s="245">
         <v>0.65</v>
       </c>
       <c r="O36" s="5"/>
       <c r="R36" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="S36" s="261">
+      <c r="S36" s="243">
         <f>Statement!T217</f>
         <v>0.29841642228739002</v>
       </c>
-      <c r="T36" s="267">
+      <c r="T36" s="249">
         <f>Statement!U217</f>
         <v>0.25298387096774194</v>
       </c>
-      <c r="U36" s="261">
+      <c r="U36" s="243">
         <f>Statement!V217</f>
         <v>0.2257283950617284</v>
       </c>
-      <c r="V36" s="261">
+      <c r="V36" s="243">
         <f>Statement!W217</f>
         <v>0.20261802575107296</v>
       </c>
-      <c r="W36" s="261">
+      <c r="W36" s="243">
         <f>Statement!X217</f>
         <v>0.21781970649895177</v>
       </c>
-      <c r="X36" s="261">
+      <c r="X36" s="243">
         <f>Statement!Y217</f>
         <v>0.21972277227722772</v>
       </c>
-      <c r="Y36" s="261">
+      <c r="Y36" s="243">
         <f>Statement!Z217</f>
         <v>0.18123339658444024</v>
       </c>
-      <c r="Z36" s="262">
+      <c r="Z36" s="244">
         <f>Statement!AA217</f>
         <v>0.14948672566371682</v>
       </c>
-      <c r="AA36" s="263">
+      <c r="AA36" s="245">
         <v>0.12</v>
       </c>
-      <c r="AB36" s="263"/>
-      <c r="AC36" s="263"/>
+      <c r="AB36" s="245"/>
+      <c r="AC36" s="245"/>
       <c r="AE36" s="47"/>
     </row>
     <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="C37" s="264">
+      <c r="C37" s="246">
         <f>Statement!M213</f>
         <v>72.279200000000003</v>
       </c>
-      <c r="D37" s="264">
+      <c r="D37" s="246">
         <f>Statement!N213</f>
         <v>65.120714285714286</v>
       </c>
-      <c r="E37" s="264">
+      <c r="E37" s="246">
         <f>Statement!O213</f>
         <v>61.315757575757573</v>
       </c>
-      <c r="F37" s="264">
+      <c r="F37" s="246">
         <f>Statement!P213</f>
         <v>63.950631578947366</v>
       </c>
-      <c r="G37" s="265">
+      <c r="G37" s="247">
         <f>Statement!Q213</f>
         <v>71.593606557377043</v>
       </c>
@@ -17115,35 +17115,35 @@
       <c r="R37" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="S37" s="264">
+      <c r="S37" s="246">
         <f>Statement!T213</f>
         <v>17.988624999999999</v>
       </c>
-      <c r="T37" s="268">
+      <c r="T37" s="250">
         <f>Statement!U213</f>
         <v>18.327558139534883</v>
       </c>
-      <c r="U37" s="264">
+      <c r="U37" s="246">
         <f>Statement!V213</f>
         <v>18.349157894736841</v>
       </c>
-      <c r="V37" s="264">
+      <c r="V37" s="246">
         <f>Statement!W213</f>
         <v>18.542427184466021</v>
       </c>
-      <c r="W37" s="264">
+      <c r="W37" s="246">
         <f>Statement!X213</f>
         <v>19.328256880733946</v>
       </c>
-      <c r="X37" s="264">
+      <c r="X37" s="246">
         <f>Statement!Y213</f>
         <v>19.955739130434782</v>
       </c>
-      <c r="Y37" s="264">
+      <c r="Y37" s="246">
         <f>Statement!Z213</f>
         <v>19.859508196721311</v>
       </c>
-      <c r="Z37" s="265">
+      <c r="Z37" s="247">
         <f>Statement!AA213</f>
         <v>20.07264</v>
       </c>
@@ -17158,43 +17158,43 @@
       <c r="B38" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C38" s="261">
+      <c r="C38" s="243">
         <f>Statement!M214</f>
         <v>0.23703703703703705</v>
       </c>
-      <c r="D38" s="261">
+      <c r="D38" s="243">
         <f>Statement!N214</f>
         <v>0.26853377265238881</v>
       </c>
-      <c r="E38" s="261">
+      <c r="E38" s="243">
         <f>Statement!O214</f>
         <v>0.30429864253393663</v>
       </c>
-      <c r="F38" s="261">
+      <c r="F38" s="243">
         <f>Statement!P214</f>
         <v>0.34704370179948585</v>
       </c>
-      <c r="G38" s="262">
+      <c r="G38" s="244">
         <f>Statement!Q214</f>
         <v>0.3959429000751315</v>
       </c>
-      <c r="H38" s="263">
+      <c r="H38" s="245">
         <v>0.44</v>
       </c>
       <c r="I38" s="156">
-        <f t="shared" ref="I38:L38" si="45">I27/I28</f>
+        <f t="shared" ref="I38:L38" si="46">I27/I28</f>
         <v>0.41246916460358163</v>
       </c>
       <c r="J38" s="156">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.42762109309922341</v>
       </c>
       <c r="K38" s="156">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.44152747011058024</v>
       </c>
       <c r="L38" s="156">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.45947574125328688</v>
       </c>
       <c r="N38" s="1" t="s">
@@ -17207,35 +17207,35 @@
       <c r="R38" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="S38" s="261">
+      <c r="S38" s="243">
         <f>Statement!T214</f>
         <v>0.32915057915057916</v>
       </c>
-      <c r="T38" s="267">
+      <c r="T38" s="249">
         <f>Statement!U214</f>
         <v>0.32891246684350134</v>
       </c>
-      <c r="U38" s="261">
+      <c r="U38" s="243">
         <f>Statement!V214</f>
         <v>0.34704370179948585</v>
       </c>
-      <c r="V38" s="261">
+      <c r="V38" s="243">
         <f>Statement!W214</f>
         <v>0.3579109062980031</v>
       </c>
-      <c r="W38" s="261">
+      <c r="W38" s="243">
         <f>Statement!X214</f>
         <v>0.37178487918939984</v>
       </c>
-      <c r="X38" s="261">
+      <c r="X38" s="243">
         <f>Statement!Y214</f>
         <v>0.37324464153732445</v>
       </c>
-      <c r="Y38" s="261">
+      <c r="Y38" s="243">
         <f>Statement!Z214</f>
         <v>0.3959429000751315</v>
       </c>
-      <c r="Z38" s="262">
+      <c r="Z38" s="244">
         <f>Statement!AA214</f>
         <v>0.41001451378809867</v>
       </c>
@@ -17251,75 +17251,75 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="239" t="s">
+      <c r="C40" s="262" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="239"/>
-      <c r="E40" s="239"/>
-      <c r="F40" s="239"/>
-      <c r="G40" s="239"/>
-      <c r="H40" s="239"/>
-      <c r="I40" s="239"/>
-      <c r="J40" s="239"/>
-      <c r="K40" s="239"/>
-      <c r="L40" s="239"/>
+      <c r="D40" s="262"/>
+      <c r="E40" s="262"/>
+      <c r="F40" s="262"/>
+      <c r="G40" s="262"/>
+      <c r="H40" s="262"/>
+      <c r="I40" s="262"/>
+      <c r="J40" s="262"/>
+      <c r="K40" s="262"/>
+      <c r="L40" s="262"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="240" t="s">
+      <c r="S40" s="263" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="241"/>
-      <c r="U40" s="241"/>
-      <c r="V40" s="241"/>
-      <c r="W40" s="241"/>
-      <c r="X40" s="241"/>
-      <c r="Y40" s="241"/>
-      <c r="Z40" s="241"/>
-      <c r="AA40" s="241"/>
-      <c r="AB40" s="241"/>
-      <c r="AC40" s="241"/>
+      <c r="T40" s="264"/>
+      <c r="U40" s="264"/>
+      <c r="V40" s="264"/>
+      <c r="W40" s="264"/>
+      <c r="X40" s="264"/>
+      <c r="Y40" s="264"/>
+      <c r="Z40" s="264"/>
+      <c r="AA40" s="264"/>
+      <c r="AB40" s="264"/>
+      <c r="AC40" s="264"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
         <v>127</v>
       </c>
       <c r="C41" s="12">
-        <f t="shared" ref="C41:L41" si="46">C5</f>
+        <f t="shared" ref="C41:L41" si="47">C5</f>
         <v>2021</v>
       </c>
       <c r="D41" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>2022</v>
       </c>
       <c r="E41" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>2023</v>
       </c>
       <c r="F41" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>2024</v>
       </c>
       <c r="G41" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>2025</v>
       </c>
       <c r="H41" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>2026</v>
       </c>
       <c r="I41" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>2027</v>
       </c>
       <c r="J41" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>2028</v>
       </c>
       <c r="K41" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>2029</v>
       </c>
       <c r="L41" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>2030</v>
       </c>
       <c r="O41" s="5"/>
@@ -17327,47 +17327,47 @@
         <v>127</v>
       </c>
       <c r="S41" s="12" t="str">
-        <f t="shared" ref="S41:AC41" si="47">S5</f>
+        <f t="shared" ref="S41:AC41" si="48">S5</f>
         <v>Q2 2024</v>
       </c>
       <c r="T41" s="12" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>Q3 2024</v>
       </c>
       <c r="U41" s="12" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>Q4 2024</v>
       </c>
       <c r="V41" s="12" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>Q1 2025</v>
       </c>
       <c r="W41" s="12" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>Q2 2025</v>
       </c>
       <c r="X41" s="12" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>Q3 2025</v>
       </c>
       <c r="Y41" s="12" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>Q4 2025</v>
       </c>
       <c r="Z41" s="12" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>Q1 2026</v>
       </c>
       <c r="AA41" s="12" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>FQ1</v>
       </c>
       <c r="AB41" s="12" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>FQ2</v>
       </c>
       <c r="AC41" s="12" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>FQ3</v>
       </c>
     </row>
@@ -17381,35 +17381,35 @@
         <v>-0.21860298767093278</v>
       </c>
       <c r="E42" s="96">
-        <f t="shared" ref="E42:L42" si="48">E31/D31-1</f>
+        <f t="shared" ref="E42:L42" si="49">E31/D31-1</f>
         <v>-0.23012292061116879</v>
       </c>
       <c r="F42" s="96">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-0.15966707389284074</v>
       </c>
       <c r="G42" s="97">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.28746460120860329</v>
       </c>
       <c r="H42" s="96">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>6.1523988711194688E-2</v>
       </c>
       <c r="I42" s="96">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1.4285714285714235E-2</v>
       </c>
       <c r="J42" s="96">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-1.4084507042253502E-2</v>
       </c>
       <c r="K42" s="96">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>2.8571428571428692E-2</v>
       </c>
       <c r="L42" s="96">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1.388888888888884E-2</v>
       </c>
       <c r="O42" s="5"/>
@@ -17422,31 +17422,31 @@
         <v>-6.0218223392790593E-3</v>
       </c>
       <c r="U42" s="96">
-        <f t="shared" ref="U42:AA42" si="49">U31/T31-1</f>
+        <f t="shared" ref="U42:AA42" si="50">U31/T31-1</f>
         <v>-3.2833489615442302E-2</v>
       </c>
       <c r="V42" s="96">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.11866148369279639</v>
       </c>
       <c r="W42" s="96">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.17669919996067351</v>
       </c>
       <c r="X42" s="96">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>-3.2548861831922737E-2</v>
       </c>
       <c r="Y42" s="96">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>-1.4889557366486783E-2</v>
       </c>
       <c r="Z42" s="97">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>-1.6362964185889561E-2</v>
       </c>
       <c r="AA42" s="96">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>-8.8241001261278762E-2</v>
       </c>
     </row>
@@ -17460,35 +17460,35 @@
         <v>0.67999999999999994</v>
       </c>
       <c r="E43" s="96">
-        <f t="shared" ref="E43:L47" si="50">E34/D34-1</f>
+        <f t="shared" ref="E43:L47" si="51">E34/D34-1</f>
         <v>0.5714285714285714</v>
       </c>
       <c r="F43" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.43939393939393945</v>
       </c>
       <c r="G43" s="97">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.28421052631578947</v>
       </c>
       <c r="H43" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.11859999999999982</v>
       </c>
       <c r="I43" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.13739999999999997</v>
       </c>
       <c r="J43" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.28625000000000034</v>
       </c>
       <c r="K43" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.3283999999999998</v>
       </c>
       <c r="L43" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.36530000000000018</v>
       </c>
       <c r="O43" s="5"/>
@@ -17501,31 +17501,31 @@
         <v>7.4999999999999956E-2</v>
       </c>
       <c r="U43" s="96">
-        <f t="shared" ref="U43:AA43" si="51">U34/T34-1</f>
+        <f t="shared" ref="U43:AA43" si="52">U34/T34-1</f>
         <v>0.10465116279069764</v>
       </c>
       <c r="V43" s="96">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>8.4210526315789513E-2</v>
       </c>
       <c r="W43" s="96">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>5.8252427184465994E-2</v>
       </c>
       <c r="X43" s="96">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>5.504587155963292E-2</v>
       </c>
       <c r="Y43" s="96">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>6.0869565217391397E-2</v>
       </c>
       <c r="Z43" s="97">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>2.4590163934426146E-2</v>
       </c>
       <c r="AA43" s="96">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>8.799999999999919E-3</v>
       </c>
     </row>
@@ -17539,35 +17539,35 @@
         <v>0.48684210526315796</v>
       </c>
       <c r="E44" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.44778761061946892</v>
       </c>
       <c r="F44" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.31051344743276288</v>
       </c>
       <c r="G44" s="97">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.12779850746268662</v>
       </c>
       <c r="H44" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.19720496277915656</v>
       </c>
       <c r="I44" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.21684504735595889</v>
       </c>
       <c r="J44" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.21960211193452461</v>
       </c>
       <c r="K44" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.22085423369691792</v>
       </c>
       <c r="L44" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.2163167944380151</v>
       </c>
       <c r="R44" s="1" t="s">
@@ -17579,31 +17579,31 @@
         <v>9.3096234309623327E-2</v>
       </c>
       <c r="U44" s="96">
-        <f t="shared" ref="U44:AA44" si="52">U35/T35-1</f>
+        <f t="shared" ref="U44:AA44" si="53">U35/T35-1</f>
         <v>2.5837320574162659E-2</v>
       </c>
       <c r="V44" s="96">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.11847014925373145</v>
       </c>
       <c r="W44" s="96">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>-2.0850708924103456E-2</v>
       </c>
       <c r="X44" s="96">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>5.4514480408858645E-2</v>
       </c>
       <c r="Y44" s="96">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>-2.342487883683364E-2</v>
       </c>
       <c r="Z44" s="97">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>3.6393713813068551E-2</v>
       </c>
       <c r="AA44" s="96">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>4.3112529928172494E-2</v>
       </c>
     </row>
@@ -17617,35 +17617,35 @@
         <v>0.57898407037248978</v>
       </c>
       <c r="E45" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.13328838973240575</v>
       </c>
       <c r="F45" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-0.25956141203547933</v>
       </c>
       <c r="G45" s="97">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-0.19519442462102976</v>
       </c>
       <c r="H45" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-8.8663257491538805E-2</v>
       </c>
       <c r="I45" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-7.1428571428571286E-2</v>
       </c>
       <c r="J45" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-7.6923076923076983E-2</v>
       </c>
       <c r="K45" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>8.3333333333333481E-2</v>
       </c>
       <c r="L45" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="R45" s="1" t="s">
@@ -17657,31 +17657,31 @@
         <v>-0.15224547955974832</v>
       </c>
       <c r="U45" s="96">
-        <f t="shared" ref="U45:AA45" si="53">U36/T36-1</f>
+        <f t="shared" ref="U45:AA45" si="54">U36/T36-1</f>
         <v>-0.10773602207031174</v>
       </c>
       <c r="V45" s="96">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>-0.10238131230382252</v>
       </c>
       <c r="W45" s="96">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>7.5026299814779929E-2</v>
       </c>
       <c r="X45" s="96">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>8.7368852380906858E-3</v>
       </c>
       <c r="Y45" s="96">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>-0.17517244705170942</v>
       </c>
       <c r="Z45" s="97">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>-0.17517009292452357</v>
       </c>
       <c r="AA45" s="96">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>-0.19725313757991958</v>
       </c>
     </row>
@@ -17695,35 +17695,35 @@
         <v>-9.9039360068812532E-2</v>
       </c>
       <c r="E46" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-5.8429284010347748E-2</v>
       </c>
       <c r="F46" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>4.2972216398603935E-2</v>
       </c>
       <c r="G46" s="97">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.11951367468504803</v>
       </c>
       <c r="H46" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>2.6627984456895959E-2</v>
       </c>
       <c r="I46" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J46" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-6.8027210884353817E-3</v>
       </c>
       <c r="K46" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>2.7397260273972712E-2</v>
       </c>
       <c r="L46" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="R46" s="1" t="s">
@@ -17735,31 +17735,31 @@
         <v>1.8841525660515224E-2</v>
       </c>
       <c r="U46" s="96">
-        <f t="shared" ref="U46:AA46" si="54">U37/T37-1</f>
+        <f t="shared" ref="U46:AA46" si="55">U37/T37-1</f>
         <v>1.1785397180306134E-3</v>
       </c>
       <c r="V46" s="96">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1.0532869728295147E-2</v>
       </c>
       <c r="W46" s="96">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>4.2380088024627893E-2</v>
       </c>
       <c r="X46" s="96">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>3.2464502803990491E-2</v>
       </c>
       <c r="Y46" s="96">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>-4.8222184647978006E-3</v>
       </c>
       <c r="Z46" s="97">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1.0731977910403367E-2</v>
       </c>
       <c r="AA46" s="96">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>-3.6188563138680463E-3</v>
       </c>
     </row>
@@ -17773,35 +17773,35 @@
         <v>0.13287685337726529</v>
       </c>
       <c r="E47" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.13318574244232839</v>
       </c>
       <c r="F47" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.1404707523819535</v>
       </c>
       <c r="G47" s="97">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.14090213429056409</v>
       </c>
       <c r="H47" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.1112713472485769</v>
       </c>
       <c r="I47" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-6.2570080446405441E-2</v>
       </c>
       <c r="J47" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>3.6734693877551017E-2</v>
       </c>
       <c r="K47" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>3.2520325203251987E-2</v>
       </c>
       <c r="L47" s="96">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>4.0650406504065373E-2</v>
       </c>
       <c r="R47" s="1" t="s">
@@ -17813,48 +17813,48 @@
         <v>-7.2341451651791733E-4</v>
       </c>
       <c r="U47" s="96">
-        <f t="shared" ref="U47:AA47" si="55">U38/T38-1</f>
+        <f t="shared" ref="U47:AA47" si="56">U38/T38-1</f>
         <v>5.5124803051662674E-2</v>
       </c>
       <c r="V47" s="96">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>3.131364851794971E-2</v>
       </c>
       <c r="W47" s="96">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>3.8763761168666422E-2</v>
       </c>
       <c r="X47" s="96">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>3.9263628771222248E-3</v>
       </c>
       <c r="Y47" s="96">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>6.0813354062679181E-2</v>
       </c>
       <c r="Z47" s="97">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>3.5539502565387737E-2</v>
       </c>
       <c r="AA47" s="96">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>3.8461538461538769E-2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="S13:AC13"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="S23:AC23"/>
+    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="S40:AC40"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="S13:AC13"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="S23:AC23"/>
-    <mergeCell ref="C40:L40"/>
-    <mergeCell ref="S40:AC40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17888,35 +17888,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
-      <c r="P2" s="230" t="s">
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
+      <c r="P2" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="230"/>
-      <c r="R2" s="230"/>
-      <c r="S2" s="230"/>
-      <c r="T2" s="230"/>
-      <c r="U2" s="230"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="230" t="s">
+      <c r="Q2" s="254"/>
+      <c r="R2" s="254"/>
+      <c r="S2" s="254"/>
+      <c r="T2" s="254"/>
+      <c r="U2" s="254"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="254"/>
+      <c r="X2" s="254" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="230"/>
-      <c r="Z2" s="230"/>
+      <c r="Y2" s="254"/>
+      <c r="Z2" s="254"/>
       <c r="AB2" s="86" t="s">
         <v>115</v>
       </c>
@@ -17925,31 +17925,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="262" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
-      <c r="P4" s="241" t="s">
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
+      <c r="P4" s="264" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="241"/>
-      <c r="R4" s="241"/>
-      <c r="S4" s="241"/>
-      <c r="T4" s="241"/>
-      <c r="U4" s="241"/>
-      <c r="V4" s="241"/>
-      <c r="W4" s="241"/>
-      <c r="X4" s="241"/>
-      <c r="Y4" s="241"/>
-      <c r="Z4" s="241"/>
+      <c r="Q4" s="264"/>
+      <c r="R4" s="264"/>
+      <c r="S4" s="264"/>
+      <c r="T4" s="264"/>
+      <c r="U4" s="264"/>
+      <c r="V4" s="264"/>
+      <c r="W4" s="264"/>
+      <c r="X4" s="264"/>
+      <c r="Y4" s="264"/>
+      <c r="Z4" s="264"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18144,32 +18144,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="239" t="s">
+      <c r="C9" s="262" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="239"/>
-      <c r="E9" s="239"/>
-      <c r="F9" s="239"/>
-      <c r="G9" s="239"/>
-      <c r="H9" s="239"/>
-      <c r="I9" s="239"/>
-      <c r="J9" s="239"/>
-      <c r="K9" s="239"/>
-      <c r="L9" s="239"/>
+      <c r="D9" s="262"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="262"/>
+      <c r="G9" s="262"/>
+      <c r="H9" s="262"/>
+      <c r="I9" s="262"/>
+      <c r="J9" s="262"/>
+      <c r="K9" s="262"/>
+      <c r="L9" s="262"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="241" t="s">
+      <c r="P9" s="264" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="241"/>
-      <c r="R9" s="241"/>
-      <c r="S9" s="241"/>
-      <c r="T9" s="241"/>
-      <c r="U9" s="241"/>
-      <c r="V9" s="241"/>
-      <c r="W9" s="241"/>
-      <c r="X9" s="241"/>
-      <c r="Y9" s="241"/>
-      <c r="Z9" s="241"/>
+      <c r="Q9" s="264"/>
+      <c r="R9" s="264"/>
+      <c r="S9" s="264"/>
+      <c r="T9" s="264"/>
+      <c r="U9" s="264"/>
+      <c r="V9" s="264"/>
+      <c r="W9" s="264"/>
+      <c r="X9" s="264"/>
+      <c r="Y9" s="264"/>
+      <c r="Z9" s="264"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -18739,127 +18739,127 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="239" t="s">
+      <c r="C18" s="262" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="239"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="239"/>
-      <c r="G18" s="239"/>
-      <c r="H18" s="239"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
-      <c r="P18" s="241" t="s">
+      <c r="D18" s="262"/>
+      <c r="E18" s="262"/>
+      <c r="F18" s="262"/>
+      <c r="G18" s="262"/>
+      <c r="H18" s="262"/>
+      <c r="I18" s="262"/>
+      <c r="J18" s="262"/>
+      <c r="K18" s="262"/>
+      <c r="L18" s="262"/>
+      <c r="P18" s="264" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="241"/>
-      <c r="R18" s="241"/>
-      <c r="S18" s="241"/>
-      <c r="T18" s="241"/>
-      <c r="U18" s="241"/>
-      <c r="V18" s="241"/>
-      <c r="W18" s="241"/>
-      <c r="X18" s="241"/>
-      <c r="Y18" s="241"/>
-      <c r="Z18" s="241"/>
+      <c r="Q18" s="264"/>
+      <c r="R18" s="264"/>
+      <c r="S18" s="264"/>
+      <c r="T18" s="264"/>
+      <c r="U18" s="264"/>
+      <c r="V18" s="264"/>
+      <c r="W18" s="264"/>
+      <c r="X18" s="264"/>
+      <c r="Y18" s="264"/>
+      <c r="Z18" s="264"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
         <v>133</v>
       </c>
       <c r="C19" s="12">
-        <f>C5</f>
+        <f t="shared" ref="C19:L19" si="6">C5</f>
         <v>2021</v>
       </c>
       <c r="D19" s="12">
-        <f>D5</f>
+        <f t="shared" si="6"/>
         <v>2022</v>
       </c>
       <c r="E19" s="12">
-        <f>E5</f>
+        <f t="shared" si="6"/>
         <v>2023</v>
       </c>
       <c r="F19" s="12">
-        <f>F5</f>
+        <f t="shared" si="6"/>
         <v>2024</v>
       </c>
       <c r="G19" s="12">
-        <f>G5</f>
+        <f t="shared" si="6"/>
         <v>2025</v>
       </c>
       <c r="H19" s="12">
-        <f>H5</f>
+        <f t="shared" si="6"/>
         <v>2026</v>
       </c>
       <c r="I19" s="12">
-        <f>I5</f>
+        <f t="shared" si="6"/>
         <v>2027</v>
       </c>
       <c r="J19" s="12">
-        <f>J5</f>
+        <f t="shared" si="6"/>
         <v>2028</v>
       </c>
       <c r="K19" s="12">
-        <f>K5</f>
+        <f t="shared" si="6"/>
         <v>2029</v>
       </c>
       <c r="L19" s="12">
-        <f>L5</f>
+        <f t="shared" si="6"/>
         <v>2030</v>
       </c>
       <c r="O19" s="16" t="s">
         <v>133</v>
       </c>
       <c r="P19" s="12" t="str">
-        <f>P5</f>
+        <f t="shared" ref="P19:Z19" si="7">P5</f>
         <v>Q2 2024</v>
       </c>
       <c r="Q19" s="12" t="str">
-        <f>Q5</f>
+        <f t="shared" si="7"/>
         <v>Q3 2024</v>
       </c>
       <c r="R19" s="12" t="str">
-        <f>R5</f>
+        <f t="shared" si="7"/>
         <v>Q4 2024</v>
       </c>
       <c r="S19" s="12" t="str">
-        <f>S5</f>
+        <f t="shared" si="7"/>
         <v>Q1 2025</v>
       </c>
       <c r="T19" s="12" t="str">
-        <f>T5</f>
+        <f t="shared" si="7"/>
         <v>Q2 2025</v>
       </c>
       <c r="U19" s="12" t="str">
-        <f>U5</f>
+        <f t="shared" si="7"/>
         <v>Q3 2025</v>
       </c>
       <c r="V19" s="12" t="str">
-        <f>V5</f>
+        <f t="shared" si="7"/>
         <v>Q4 2025</v>
       </c>
       <c r="W19" s="12" t="str">
-        <f>W5</f>
+        <f t="shared" si="7"/>
         <v>Q1 2026</v>
       </c>
       <c r="X19" s="12" t="str">
-        <f>X5</f>
+        <f t="shared" si="7"/>
         <v>FQ1</v>
       </c>
       <c r="Y19" s="12" t="str">
-        <f>Y5</f>
+        <f t="shared" si="7"/>
         <v>FQ2</v>
       </c>
       <c r="Z19" s="12" t="str">
-        <f>Z5</f>
+        <f t="shared" si="7"/>
         <v>FQ3</v>
       </c>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B20" s="16" t="str">
-        <f t="shared" ref="B20" si="6">B11</f>
+        <f t="shared" ref="B20" si="8">B11</f>
         <v>COGS</v>
       </c>
       <c r="C20" s="104">
@@ -18867,19 +18867,19 @@
         <v>0.27589204536391621</v>
       </c>
       <c r="D20" s="104">
-        <f t="shared" ref="D20:L20" si="7">D11/D$6</f>
+        <f t="shared" ref="D20:G20" si="9">D11/D$6</f>
         <v>0.26909971718155862</v>
       </c>
       <c r="E20" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.2675627790152304</v>
       </c>
       <c r="F20" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.27224393869715408</v>
       </c>
       <c r="G20" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.2776937689200637</v>
       </c>
       <c r="H20" s="98">
@@ -18898,7 +18898,7 @@
         <v>0.27600000000000002</v>
       </c>
       <c r="O20" s="16" t="str">
-        <f t="shared" ref="O20:O24" si="8">O11</f>
+        <f t="shared" ref="O20:O24" si="10">O11</f>
         <v>COGS</v>
       </c>
       <c r="P20" s="104">
@@ -18906,31 +18906,31 @@
         <v>0.26551784082051511</v>
       </c>
       <c r="Q20" s="104">
-        <f t="shared" ref="Q20:V20" si="9">Q11/Q$6</f>
+        <f t="shared" ref="Q20:V20" si="11">Q11/Q$6</f>
         <v>0.27093263549227908</v>
       </c>
       <c r="R20" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.28119780481985207</v>
       </c>
       <c r="S20" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.28883649774857745</v>
       </c>
       <c r="T20" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.27623332606584344</v>
       </c>
       <c r="U20" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.27529783263958663</v>
       </c>
       <c r="V20" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.27220823847165465</v>
       </c>
       <c r="W20" s="105">
-        <f t="shared" ref="W20:X24" si="10">W11/W$6</f>
+        <f t="shared" ref="W20:X24" si="12">W11/W$6</f>
         <v>0.27013669353043324</v>
       </c>
       <c r="X20" s="98">
@@ -18945,23 +18945,23 @@
         <v>R&amp;D</v>
       </c>
       <c r="C21" s="96">
-        <f t="shared" ref="C21:G21" si="11">C12/C$6</f>
+        <f t="shared" ref="C21:G21" si="13">C12/C$6</f>
         <v>0.41405340309125421</v>
       </c>
       <c r="D21" s="96">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.40716112531969312</v>
       </c>
       <c r="E21" s="96">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.36593618259152078</v>
       </c>
       <c r="F21" s="96">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.31455942590077324</v>
       </c>
       <c r="G21" s="97">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.29522575894694336</v>
       </c>
       <c r="H21" s="98">
@@ -18980,7 +18980,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="O21" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>R&amp;D</v>
       </c>
       <c r="P21" s="96">
@@ -18988,31 +18988,31 @@
         <v>0.30924649660455233</v>
       </c>
       <c r="Q21" s="96">
-        <f t="shared" ref="Q21:V21" si="12">Q12/Q$6</f>
+        <f t="shared" ref="Q21:V21" si="14">Q12/Q$6</f>
         <v>0.32647953726491996</v>
       </c>
       <c r="R21" s="96">
+        <f t="shared" si="14"/>
+        <v>0.31684562157003104</v>
+      </c>
+      <c r="S21" s="96">
+        <f t="shared" si="14"/>
+        <v>0.30505800826027224</v>
+      </c>
+      <c r="T21" s="96">
+        <f t="shared" si="14"/>
+        <v>0.29203417041603075</v>
+      </c>
+      <c r="U21" s="96">
+        <f t="shared" si="14"/>
+        <v>0.30439103024146802</v>
+      </c>
+      <c r="V21" s="96">
+        <f t="shared" si="14"/>
+        <v>0.2812477904888499</v>
+      </c>
+      <c r="W21" s="97">
         <f t="shared" si="12"/>
-        <v>0.31684562157003104</v>
-      </c>
-      <c r="S21" s="96">
-        <f t="shared" si="12"/>
-        <v>0.30505800826027224</v>
-      </c>
-      <c r="T21" s="96">
-        <f t="shared" si="12"/>
-        <v>0.29203417041603075</v>
-      </c>
-      <c r="U21" s="96">
-        <f t="shared" si="12"/>
-        <v>0.30439103024146802</v>
-      </c>
-      <c r="V21" s="96">
-        <f t="shared" si="12"/>
-        <v>0.2812477904888499</v>
-      </c>
-      <c r="W21" s="97">
-        <f t="shared" si="10"/>
         <v>0.2841896515702117</v>
       </c>
       <c r="X21" s="98">
@@ -19023,27 +19023,27 @@
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="str">
-        <f t="shared" ref="B22:B24" si="13">B13</f>
+        <f t="shared" ref="B22:B24" si="15">B13</f>
         <v>Sales and marketing</v>
       </c>
       <c r="C22" s="96">
-        <f t="shared" ref="C22:G22" si="14">C13/C$6</f>
+        <f t="shared" ref="C22:G22" si="16">C13/C$6</f>
         <v>0.23595138213197644</v>
       </c>
       <c r="D22" s="96">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.18123925898861959</v>
       </c>
       <c r="E22" s="96">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.14269763833789298</v>
       </c>
       <c r="F22" s="96">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.12097740179459483</v>
       </c>
       <c r="G22" s="97">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.12112406742939642</v>
       </c>
       <c r="H22" s="98">
@@ -19062,39 +19062,39 @@
         <v>0.11</v>
       </c>
       <c r="O22" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Sales and marketing</v>
       </c>
       <c r="P22" s="96">
-        <f t="shared" ref="P22:V24" si="15">P13/P$6</f>
+        <f t="shared" ref="P22:V24" si="17">P13/P$6</f>
         <v>0.11312925131920573</v>
       </c>
       <c r="Q22" s="96">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.13278710655575979</v>
       </c>
       <c r="R22" s="96">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.11842042471963732</v>
       </c>
       <c r="S22" s="96">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.11554846734245459</v>
       </c>
       <c r="T22" s="96">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.11719025627812023</v>
       </c>
       <c r="U22" s="96">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.1291104952652247</v>
       </c>
       <c r="V22" s="96">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.12150897238287824</v>
       </c>
       <c r="W22" s="97">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.1344295759452267</v>
       </c>
       <c r="X22" s="98">
@@ -19105,27 +19105,27 @@
     </row>
     <row r="23" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>General and administrative</v>
       </c>
       <c r="C23" s="96">
-        <f t="shared" ref="C23:G23" si="16">C14/C$6</f>
+        <f t="shared" ref="C23:G23" si="18">C14/C$6</f>
         <v>0.31339224474821753</v>
       </c>
       <c r="D23" s="96">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.31894342277973992</v>
       </c>
       <c r="E23" s="96">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.24876814363906469</v>
       </c>
       <c r="F23" s="96">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.2085387634621349</v>
       </c>
       <c r="G23" s="97">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.17529773349563266</v>
       </c>
       <c r="H23" s="98">
@@ -19144,39 +19144,39 @@
         <v>0.17</v>
       </c>
       <c r="O23" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>General and administrative</v>
       </c>
       <c r="P23" s="96">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.20724287404599415</v>
       </c>
       <c r="Q23" s="96">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.19932085111685721</v>
       </c>
       <c r="R23" s="96">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.2172894297303746</v>
       </c>
       <c r="S23" s="96">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.18830473730514036</v>
       </c>
       <c r="T23" s="96">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.18228846649356828</v>
       </c>
       <c r="U23" s="96">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.16180307898407512</v>
       </c>
       <c r="V23" s="96">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.17141564263189898</v>
       </c>
       <c r="W23" s="97">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.1587371175509561</v>
       </c>
       <c r="X23" s="98">
@@ -19187,7 +19187,7 @@
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B24" s="16" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>OpEx</v>
       </c>
       <c r="C24" s="104">
@@ -19195,79 +19195,79 @@
         <v>0.96339702997144816</v>
       </c>
       <c r="D24" s="104">
-        <f t="shared" ref="D24:L24" si="17">D15/D$6</f>
+        <f t="shared" ref="D24:L24" si="19">D15/D$6</f>
         <v>0.90734380708805262</v>
       </c>
       <c r="E24" s="104">
+        <f t="shared" si="19"/>
+        <v>0.75740196456847841</v>
+      </c>
+      <c r="F24" s="104">
+        <f t="shared" si="19"/>
+        <v>0.64407559115750301</v>
+      </c>
+      <c r="G24" s="105">
+        <f t="shared" si="19"/>
+        <v>0.59164755987197248</v>
+      </c>
+      <c r="H24" s="104">
+        <f t="shared" si="19"/>
+        <v>0.65999999999999992</v>
+      </c>
+      <c r="I24" s="104">
+        <f t="shared" si="19"/>
+        <v>0.59500000000000008</v>
+      </c>
+      <c r="J24" s="104">
+        <f t="shared" si="19"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="K24" s="104">
+        <f t="shared" si="19"/>
+        <v>0.6</v>
+      </c>
+      <c r="L24" s="104">
+        <f t="shared" si="19"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O24" s="16" t="str">
+        <f t="shared" si="10"/>
+        <v>OpEx</v>
+      </c>
+      <c r="P24" s="104">
         <f t="shared" si="17"/>
-        <v>0.75740196456847841</v>
-      </c>
-      <c r="F24" s="104">
+        <v>0.62961862196975216</v>
+      </c>
+      <c r="Q24" s="104">
         <f t="shared" si="17"/>
-        <v>0.64407559115750301</v>
-      </c>
-      <c r="G24" s="105">
+        <v>0.65858749493753699</v>
+      </c>
+      <c r="R24" s="104">
         <f t="shared" si="17"/>
-        <v>0.59164755987197248</v>
-      </c>
-      <c r="H24" s="104">
+        <v>0.65255547602004293</v>
+      </c>
+      <c r="S24" s="104">
         <f t="shared" si="17"/>
-        <v>0.65999999999999992</v>
-      </c>
-      <c r="I24" s="104">
+        <v>0.60891121290786721</v>
+      </c>
+      <c r="T24" s="104">
         <f t="shared" si="17"/>
-        <v>0.59500000000000008</v>
-      </c>
-      <c r="J24" s="104">
+        <v>0.59151289318771927</v>
+      </c>
+      <c r="U24" s="104">
         <f t="shared" si="17"/>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="K24" s="104">
+        <v>0.59530460449076783</v>
+      </c>
+      <c r="V24" s="104">
         <f t="shared" si="17"/>
-        <v>0.6</v>
-      </c>
-      <c r="L24" s="104">
-        <f t="shared" si="17"/>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="O24" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v>OpEx</v>
-      </c>
-      <c r="P24" s="104">
-        <f t="shared" si="15"/>
-        <v>0.62961862196975216</v>
-      </c>
-      <c r="Q24" s="104">
-        <f t="shared" si="15"/>
-        <v>0.65858749493753699</v>
-      </c>
-      <c r="R24" s="104">
-        <f t="shared" si="15"/>
-        <v>0.65255547602004293</v>
-      </c>
-      <c r="S24" s="104">
-        <f t="shared" si="15"/>
-        <v>0.60891121290786721</v>
-      </c>
-      <c r="T24" s="104">
-        <f t="shared" si="15"/>
-        <v>0.59151289318771927</v>
-      </c>
-      <c r="U24" s="104">
-        <f t="shared" si="15"/>
-        <v>0.59530460449076783</v>
-      </c>
-      <c r="V24" s="104">
-        <f t="shared" si="15"/>
         <v>0.57417240550362714</v>
       </c>
       <c r="W24" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.57735634506639444</v>
       </c>
       <c r="X24" s="104">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.59599999999999997</v>
       </c>
       <c r="Y24" s="16"/>
@@ -19323,60 +19323,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="254"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
-      <c r="P3" s="244"/>
-      <c r="Q3" s="244"/>
-      <c r="R3" s="244"/>
-      <c r="S3" s="244"/>
-      <c r="T3" s="244"/>
-      <c r="U3" s="244"/>
-      <c r="V3" s="244"/>
-      <c r="W3" s="244"/>
-      <c r="X3" s="244"/>
-      <c r="Y3" s="244"/>
-      <c r="Z3" s="244"/>
+      <c r="I3" s="254"/>
+      <c r="J3" s="254"/>
+      <c r="K3" s="254"/>
+      <c r="L3" s="254"/>
+      <c r="P3" s="265"/>
+      <c r="Q3" s="265"/>
+      <c r="R3" s="265"/>
+      <c r="S3" s="265"/>
+      <c r="T3" s="265"/>
+      <c r="U3" s="265"/>
+      <c r="V3" s="265"/>
+      <c r="W3" s="265"/>
+      <c r="X3" s="265"/>
+      <c r="Y3" s="265"/>
+      <c r="Z3" s="265"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="262" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
-      <c r="P5" s="244"/>
-      <c r="Q5" s="244"/>
-      <c r="R5" s="244"/>
-      <c r="S5" s="244"/>
-      <c r="T5" s="244"/>
-      <c r="U5" s="244"/>
-      <c r="V5" s="244"/>
-      <c r="W5" s="244"/>
-      <c r="X5" s="244"/>
-      <c r="Y5" s="244"/>
-      <c r="Z5" s="244"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
+      <c r="P5" s="265"/>
+      <c r="Q5" s="265"/>
+      <c r="R5" s="265"/>
+      <c r="S5" s="265"/>
+      <c r="T5" s="265"/>
+      <c r="U5" s="265"/>
+      <c r="V5" s="265"/>
+      <c r="W5" s="265"/>
+      <c r="X5" s="265"/>
+      <c r="Y5" s="265"/>
+      <c r="Z5" s="265"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19562,30 +19562,30 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="239" t="s">
+      <c r="C11" s="262" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="239"/>
-      <c r="E11" s="239"/>
-      <c r="F11" s="239"/>
-      <c r="G11" s="239"/>
-      <c r="H11" s="239"/>
-      <c r="I11" s="239"/>
-      <c r="J11" s="239"/>
-      <c r="K11" s="239"/>
-      <c r="L11" s="239"/>
+      <c r="D11" s="262"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="262"/>
+      <c r="G11" s="262"/>
+      <c r="H11" s="262"/>
+      <c r="I11" s="262"/>
+      <c r="J11" s="262"/>
+      <c r="K11" s="262"/>
+      <c r="L11" s="262"/>
       <c r="N11" s="92"/>
-      <c r="P11" s="244"/>
-      <c r="Q11" s="244"/>
-      <c r="R11" s="244"/>
-      <c r="S11" s="244"/>
-      <c r="T11" s="244"/>
-      <c r="U11" s="244"/>
-      <c r="V11" s="244"/>
-      <c r="W11" s="244"/>
-      <c r="X11" s="244"/>
-      <c r="Y11" s="244"/>
-      <c r="Z11" s="244"/>
+      <c r="P11" s="265"/>
+      <c r="Q11" s="265"/>
+      <c r="R11" s="265"/>
+      <c r="S11" s="265"/>
+      <c r="T11" s="265"/>
+      <c r="U11" s="265"/>
+      <c r="V11" s="265"/>
+      <c r="W11" s="265"/>
+      <c r="X11" s="265"/>
+      <c r="Y11" s="265"/>
+      <c r="Z11" s="265"/>
       <c r="AB11" s="112"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -19827,18 +19827,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="239" t="s">
+      <c r="C18" s="262" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="239"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="239"/>
-      <c r="G18" s="239"/>
-      <c r="H18" s="239"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
+      <c r="D18" s="262"/>
+      <c r="E18" s="262"/>
+      <c r="F18" s="262"/>
+      <c r="G18" s="262"/>
+      <c r="H18" s="262"/>
+      <c r="I18" s="262"/>
+      <c r="J18" s="262"/>
+      <c r="K18" s="262"/>
+      <c r="L18" s="262"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20051,23 +20051,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="244"/>
-      <c r="C25" s="244"/>
+      <c r="B25" s="265"/>
+      <c r="C25" s="265"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="239" t="s">
+      <c r="C26" s="262" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="239"/>
-      <c r="E26" s="239"/>
-      <c r="F26" s="239"/>
-      <c r="G26" s="239"/>
-      <c r="H26" s="239"/>
-      <c r="I26" s="239"/>
-      <c r="J26" s="239"/>
-      <c r="K26" s="239"/>
-      <c r="L26" s="239"/>
+      <c r="D26" s="262"/>
+      <c r="E26" s="262"/>
+      <c r="F26" s="262"/>
+      <c r="G26" s="262"/>
+      <c r="H26" s="262"/>
+      <c r="I26" s="262"/>
+      <c r="J26" s="262"/>
+      <c r="K26" s="262"/>
+      <c r="L26" s="262"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20259,18 +20259,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="239" t="s">
+      <c r="C33" s="262" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="239"/>
-      <c r="E33" s="239"/>
-      <c r="F33" s="239"/>
-      <c r="G33" s="239"/>
-      <c r="H33" s="239"/>
-      <c r="I33" s="239"/>
-      <c r="J33" s="239"/>
-      <c r="K33" s="239"/>
-      <c r="L33" s="239"/>
+      <c r="D33" s="262"/>
+      <c r="E33" s="262"/>
+      <c r="F33" s="262"/>
+      <c r="G33" s="262"/>
+      <c r="H33" s="262"/>
+      <c r="I33" s="262"/>
+      <c r="J33" s="262"/>
+      <c r="K33" s="262"/>
+      <c r="L33" s="262"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20454,18 +20454,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="239" t="s">
+      <c r="C40" s="262" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="239"/>
-      <c r="E40" s="239"/>
-      <c r="F40" s="239"/>
-      <c r="G40" s="239"/>
-      <c r="H40" s="239"/>
-      <c r="I40" s="239"/>
-      <c r="J40" s="239"/>
-      <c r="K40" s="239"/>
-      <c r="L40" s="239"/>
+      <c r="D40" s="262"/>
+      <c r="E40" s="262"/>
+      <c r="F40" s="262"/>
+      <c r="G40" s="262"/>
+      <c r="H40" s="262"/>
+      <c r="I40" s="262"/>
+      <c r="J40" s="262"/>
+      <c r="K40" s="262"/>
+      <c r="L40" s="262"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20729,6 +20729,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20736,12 +20742,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20779,60 +20779,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
-      <c r="S2" s="244"/>
-      <c r="T2" s="244"/>
-      <c r="U2" s="244"/>
-      <c r="V2" s="244"/>
-      <c r="W2" s="244"/>
-      <c r="X2" s="244"/>
-      <c r="Y2" s="244"/>
-      <c r="Z2" s="244"/>
-      <c r="AA2" s="244"/>
-      <c r="AB2" s="244"/>
-      <c r="AC2" s="244"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
+      <c r="S2" s="265"/>
+      <c r="T2" s="265"/>
+      <c r="U2" s="265"/>
+      <c r="V2" s="265"/>
+      <c r="W2" s="265"/>
+      <c r="X2" s="265"/>
+      <c r="Y2" s="265"/>
+      <c r="Z2" s="265"/>
+      <c r="AA2" s="265"/>
+      <c r="AB2" s="265"/>
+      <c r="AC2" s="265"/>
       <c r="AE2" s="111"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="262" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
-      <c r="S4" s="244"/>
-      <c r="T4" s="244"/>
-      <c r="U4" s="244"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="244"/>
-      <c r="X4" s="244"/>
-      <c r="Y4" s="244"/>
-      <c r="Z4" s="244"/>
-      <c r="AA4" s="244"/>
-      <c r="AB4" s="244"/>
-      <c r="AC4" s="244"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
+      <c r="S4" s="265"/>
+      <c r="T4" s="265"/>
+      <c r="U4" s="265"/>
+      <c r="V4" s="265"/>
+      <c r="W4" s="265"/>
+      <c r="X4" s="265"/>
+      <c r="Y4" s="265"/>
+      <c r="Z4" s="265"/>
+      <c r="AA4" s="265"/>
+      <c r="AB4" s="265"/>
+      <c r="AC4" s="265"/>
       <c r="AE4" s="112"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -21195,18 +21195,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="239" t="s">
+      <c r="C13" s="262" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="239"/>
-      <c r="G13" s="239"/>
-      <c r="H13" s="239"/>
-      <c r="I13" s="239"/>
-      <c r="J13" s="239"/>
-      <c r="K13" s="239"/>
-      <c r="L13" s="239"/>
+      <c r="D13" s="262"/>
+      <c r="E13" s="262"/>
+      <c r="F13" s="262"/>
+      <c r="G13" s="262"/>
+      <c r="H13" s="262"/>
+      <c r="I13" s="262"/>
+      <c r="J13" s="262"/>
+      <c r="K13" s="262"/>
+      <c r="L13" s="262"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21299,18 +21299,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="239" t="s">
+      <c r="C18" s="262" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="239"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="239"/>
-      <c r="G18" s="239"/>
-      <c r="H18" s="239"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
+      <c r="D18" s="262"/>
+      <c r="E18" s="262"/>
+      <c r="F18" s="262"/>
+      <c r="G18" s="262"/>
+      <c r="H18" s="262"/>
+      <c r="I18" s="262"/>
+      <c r="J18" s="262"/>
+      <c r="K18" s="262"/>
+      <c r="L18" s="262"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21502,18 +21502,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="239" t="s">
+      <c r="C25" s="262" t="s">
         <v>271</v>
       </c>
-      <c r="D25" s="239"/>
-      <c r="E25" s="239"/>
-      <c r="F25" s="239"/>
-      <c r="G25" s="239"/>
-      <c r="H25" s="239"/>
-      <c r="I25" s="239"/>
-      <c r="J25" s="239"/>
-      <c r="K25" s="239"/>
-      <c r="L25" s="239"/>
+      <c r="D25" s="262"/>
+      <c r="E25" s="262"/>
+      <c r="F25" s="262"/>
+      <c r="G25" s="262"/>
+      <c r="H25" s="262"/>
+      <c r="I25" s="262"/>
+      <c r="J25" s="262"/>
+      <c r="K25" s="262"/>
+      <c r="L25" s="262"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21651,18 +21651,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="239" t="s">
+      <c r="C31" s="262" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="239"/>
-      <c r="E31" s="239"/>
-      <c r="F31" s="239"/>
-      <c r="G31" s="239"/>
-      <c r="H31" s="239"/>
-      <c r="I31" s="239"/>
-      <c r="J31" s="239"/>
-      <c r="K31" s="239"/>
-      <c r="L31" s="239"/>
+      <c r="D31" s="262"/>
+      <c r="E31" s="262"/>
+      <c r="F31" s="262"/>
+      <c r="G31" s="262"/>
+      <c r="H31" s="262"/>
+      <c r="I31" s="262"/>
+      <c r="J31" s="262"/>
+      <c r="K31" s="262"/>
+      <c r="L31" s="262"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21801,16 +21801,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21873,10 +21873,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="254" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="230"/>
+      <c r="C4" s="254"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21893,7 +21893,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>127.25</v>
+        <v>119.94</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21902,7 +21902,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>6208145.75</v>
+        <v>5851512.7800000003</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21920,7 +21920,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.5090000000000005E-2</v>
+        <v>4.4020000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>0.86399999999999999</v>
+        <v>0.82050000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21961,10 +21961,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="230" t="s">
+      <c r="B15" s="254" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="230"/>
+      <c r="C15" s="254"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21999,7 +21999,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.3970000000000003E-2</v>
+        <v>8.0942500000000001E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22008,7 +22008,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.3970000000000003E-2</v>
+        <v>8.0942500000000001E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22053,60 +22053,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="254"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
-      <c r="P3" s="244"/>
-      <c r="Q3" s="244"/>
-      <c r="R3" s="244"/>
-      <c r="S3" s="244"/>
-      <c r="T3" s="244"/>
-      <c r="U3" s="244"/>
-      <c r="V3" s="244"/>
-      <c r="W3" s="244"/>
-      <c r="X3" s="244"/>
-      <c r="Y3" s="244"/>
-      <c r="Z3" s="244"/>
+      <c r="I3" s="254"/>
+      <c r="J3" s="254"/>
+      <c r="K3" s="254"/>
+      <c r="L3" s="254"/>
+      <c r="P3" s="265"/>
+      <c r="Q3" s="265"/>
+      <c r="R3" s="265"/>
+      <c r="S3" s="265"/>
+      <c r="T3" s="265"/>
+      <c r="U3" s="265"/>
+      <c r="V3" s="265"/>
+      <c r="W3" s="265"/>
+      <c r="X3" s="265"/>
+      <c r="Y3" s="265"/>
+      <c r="Z3" s="265"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="262" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
-      <c r="P5" s="244"/>
-      <c r="Q5" s="244"/>
-      <c r="R5" s="244"/>
-      <c r="S5" s="244"/>
-      <c r="T5" s="244"/>
-      <c r="U5" s="244"/>
-      <c r="V5" s="244"/>
-      <c r="W5" s="244"/>
-      <c r="X5" s="244"/>
-      <c r="Y5" s="244"/>
-      <c r="Z5" s="244"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
+      <c r="P5" s="265"/>
+      <c r="Q5" s="265"/>
+      <c r="R5" s="265"/>
+      <c r="S5" s="265"/>
+      <c r="T5" s="265"/>
+      <c r="U5" s="265"/>
+      <c r="V5" s="265"/>
+      <c r="W5" s="265"/>
+      <c r="X5" s="265"/>
+      <c r="Y5" s="265"/>
+      <c r="Z5" s="265"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22352,10 +22352,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="230" t="s">
+      <c r="B13" s="254" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="230"/>
+      <c r="C13" s="254"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22375,10 +22375,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="230" t="s">
+      <c r="B18" s="254" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="230"/>
+      <c r="C18" s="254"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22492,37 +22492,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="262" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22711,18 +22711,18 @@
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="239" t="s">
+      <c r="C10" s="262" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="239"/>
-      <c r="E10" s="239"/>
-      <c r="F10" s="239"/>
-      <c r="G10" s="239"/>
-      <c r="H10" s="239"/>
-      <c r="I10" s="239"/>
-      <c r="J10" s="239"/>
-      <c r="K10" s="239"/>
-      <c r="L10" s="239"/>
+      <c r="D10" s="262"/>
+      <c r="E10" s="262"/>
+      <c r="F10" s="262"/>
+      <c r="G10" s="262"/>
+      <c r="H10" s="262"/>
+      <c r="I10" s="262"/>
+      <c r="J10" s="262"/>
+      <c r="K10" s="262"/>
+      <c r="L10" s="262"/>
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22916,18 +22916,18 @@
       <c r="N15" s="92"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="239" t="s">
+      <c r="C16" s="262" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="239"/>
-      <c r="E16" s="239"/>
-      <c r="F16" s="239"/>
-      <c r="G16" s="239"/>
-      <c r="H16" s="239"/>
-      <c r="I16" s="239"/>
-      <c r="J16" s="239"/>
-      <c r="K16" s="239"/>
-      <c r="L16" s="239"/>
+      <c r="D16" s="262"/>
+      <c r="E16" s="262"/>
+      <c r="F16" s="262"/>
+      <c r="G16" s="262"/>
+      <c r="H16" s="262"/>
+      <c r="I16" s="262"/>
+      <c r="J16" s="262"/>
+      <c r="K16" s="262"/>
+      <c r="L16" s="262"/>
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -23061,18 +23061,18 @@
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="239" t="s">
+      <c r="C21" s="262" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="239"/>
-      <c r="E21" s="239"/>
-      <c r="F21" s="239"/>
-      <c r="G21" s="239"/>
-      <c r="H21" s="239"/>
-      <c r="I21" s="239"/>
-      <c r="J21" s="239"/>
-      <c r="K21" s="239"/>
-      <c r="L21" s="239"/>
+      <c r="D21" s="262"/>
+      <c r="E21" s="262"/>
+      <c r="F21" s="262"/>
+      <c r="G21" s="262"/>
+      <c r="H21" s="262"/>
+      <c r="I21" s="262"/>
+      <c r="J21" s="262"/>
+      <c r="K21" s="262"/>
+      <c r="L21" s="262"/>
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -23156,18 +23156,18 @@
       <c r="N25" s="92"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="239" t="s">
+      <c r="C26" s="262" t="s">
         <v>204</v>
       </c>
-      <c r="D26" s="239"/>
-      <c r="E26" s="239"/>
-      <c r="F26" s="239"/>
-      <c r="G26" s="239"/>
-      <c r="H26" s="239"/>
-      <c r="I26" s="239"/>
-      <c r="J26" s="239"/>
-      <c r="K26" s="239"/>
-      <c r="L26" s="239"/>
+      <c r="D26" s="262"/>
+      <c r="E26" s="262"/>
+      <c r="F26" s="262"/>
+      <c r="G26" s="262"/>
+      <c r="H26" s="262"/>
+      <c r="I26" s="262"/>
+      <c r="J26" s="262"/>
+      <c r="K26" s="262"/>
+      <c r="L26" s="262"/>
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -23437,10 +23437,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="230" t="s">
+      <c r="B37" s="254" t="s">
         <v>209</v>
       </c>
-      <c r="C37" s="230"/>
+      <c r="C37" s="254"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -23515,10 +23515,10 @@
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="230" t="s">
+      <c r="B47" s="254" t="s">
         <v>214</v>
       </c>
-      <c r="C47" s="230"/>
+      <c r="C47" s="254"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
@@ -23574,10 +23574,10 @@
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="230" t="s">
+      <c r="B55" s="254" t="s">
         <v>332</v>
       </c>
-      <c r="C55" s="230"/>
+      <c r="C55" s="254"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
@@ -23690,10 +23690,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="254" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="230"/>
+      <c r="C4" s="254"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23747,7 +23747,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>127.25</v>
+        <v>119.94</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23756,7 +23756,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.19325902658177105</v>
+        <v>0.26598475181365988</v>
       </c>
     </row>
   </sheetData>
@@ -23822,60 +23822,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="254"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
-      <c r="P3" s="244"/>
-      <c r="Q3" s="244"/>
-      <c r="R3" s="244"/>
-      <c r="S3" s="244"/>
-      <c r="T3" s="244"/>
-      <c r="U3" s="244"/>
-      <c r="V3" s="244"/>
-      <c r="W3" s="244"/>
-      <c r="X3" s="244"/>
-      <c r="Y3" s="244"/>
-      <c r="Z3" s="244"/>
+      <c r="I3" s="254"/>
+      <c r="J3" s="254"/>
+      <c r="K3" s="254"/>
+      <c r="L3" s="254"/>
+      <c r="P3" s="265"/>
+      <c r="Q3" s="265"/>
+      <c r="R3" s="265"/>
+      <c r="S3" s="265"/>
+      <c r="T3" s="265"/>
+      <c r="U3" s="265"/>
+      <c r="V3" s="265"/>
+      <c r="W3" s="265"/>
+      <c r="X3" s="265"/>
+      <c r="Y3" s="265"/>
+      <c r="Z3" s="265"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="262" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
-      <c r="P5" s="244"/>
-      <c r="Q5" s="244"/>
-      <c r="R5" s="244"/>
-      <c r="S5" s="244"/>
-      <c r="T5" s="244"/>
-      <c r="U5" s="244"/>
-      <c r="V5" s="244"/>
-      <c r="W5" s="244"/>
-      <c r="X5" s="244"/>
-      <c r="Y5" s="244"/>
-      <c r="Z5" s="244"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
+      <c r="P5" s="265"/>
+      <c r="Q5" s="265"/>
+      <c r="R5" s="265"/>
+      <c r="S5" s="265"/>
+      <c r="T5" s="265"/>
+      <c r="U5" s="265"/>
+      <c r="V5" s="265"/>
+      <c r="W5" s="265"/>
+      <c r="X5" s="265"/>
+      <c r="Y5" s="265"/>
+      <c r="Z5" s="265"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -24104,10 +24104,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="245" t="s">
+      <c r="B14" s="266" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="246"/>
+      <c r="C14" s="267"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -24115,7 +24115,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>127.25</v>
+        <v>119.94</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24134,20 +24134,20 @@
       <c r="C17" s="160">
         <v>0.2</v>
       </c>
-      <c r="E17" s="247" t="s">
+      <c r="E17" s="268" t="s">
         <v>230</v>
       </c>
-      <c r="F17" s="247"/>
-      <c r="G17" s="247"/>
-      <c r="H17" s="247"/>
-      <c r="I17" s="247"/>
+      <c r="F17" s="268"/>
+      <c r="G17" s="268"/>
+      <c r="H17" s="268"/>
+      <c r="I17" s="268"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="245" t="s">
+      <c r="B19" s="266" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="246"/>
+      <c r="C19" s="267"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -24181,7 +24181,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>5928959.25</v>
+        <v>5588364.4199999999</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24208,15 +24208,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>4537138.25</v>
+        <v>4196543.42</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="245" t="s">
+      <c r="B28" s="266" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="246"/>
+      <c r="C28" s="267"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -24291,18 +24291,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="239" t="s">
+      <c r="C39" s="262" t="s">
         <v>233</v>
       </c>
-      <c r="D39" s="239"/>
-      <c r="E39" s="239"/>
-      <c r="F39" s="239"/>
-      <c r="G39" s="239"/>
-      <c r="H39" s="239"/>
-      <c r="I39" s="239"/>
-      <c r="J39" s="239"/>
-      <c r="K39" s="239"/>
-      <c r="L39" s="239"/>
+      <c r="D39" s="262"/>
+      <c r="E39" s="262"/>
+      <c r="F39" s="262"/>
+      <c r="G39" s="262"/>
+      <c r="H39" s="262"/>
+      <c r="I39" s="262"/>
+      <c r="J39" s="262"/>
+      <c r="K39" s="262"/>
+      <c r="L39" s="262"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -24734,17 +24734,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -25481,19 +25481,19 @@
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
-      <c r="M13" s="248">
+      <c r="M13" s="230">
         <v>19</v>
       </c>
-      <c r="N13" s="248">
+      <c r="N13" s="230">
         <v>7235</v>
       </c>
-      <c r="O13" s="248">
+      <c r="O13" s="230">
         <v>31091</v>
       </c>
-      <c r="P13" s="248">
+      <c r="P13" s="230">
         <v>42697</v>
       </c>
-      <c r="Q13" s="248">
+      <c r="Q13" s="230">
         <v>45231</v>
       </c>
       <c r="T13" s="62">
@@ -26821,19 +26821,19 @@
       <c r="J35" s="21"/>
       <c r="K35" s="21"/>
       <c r="L35" s="21"/>
-      <c r="M35" s="248">
-        <v>0</v>
-      </c>
-      <c r="N35" s="248">
+      <c r="M35" s="230">
+        <v>0</v>
+      </c>
+      <c r="N35" s="230">
         <v>4050</v>
       </c>
-      <c r="O35" s="248">
+      <c r="O35" s="230">
         <v>4050</v>
       </c>
-      <c r="P35" s="248">
+      <c r="P35" s="230">
         <v>10538</v>
       </c>
-      <c r="Q35" s="248">
+      <c r="Q35" s="230">
         <v>35335</v>
       </c>
       <c r="T35" s="21">
@@ -27515,19 +27515,19 @@
       <c r="J46" s="21"/>
       <c r="K46" s="21"/>
       <c r="L46" s="21"/>
-      <c r="M46" s="248">
+      <c r="M46" s="230">
         <v>683966</v>
       </c>
-      <c r="N46" s="248">
+      <c r="N46" s="230">
         <v>772562</v>
       </c>
-      <c r="O46" s="248">
+      <c r="O46" s="230">
         <v>869918</v>
       </c>
-      <c r="P46" s="248">
+      <c r="P46" s="230">
         <v>950393</v>
       </c>
-      <c r="Q46" s="248">
+      <c r="Q46" s="230">
         <v>1058783</v>
       </c>
       <c r="T46" s="62">
@@ -31356,7 +31356,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>127.25</v>
+        <v>119.94</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31403,7 +31403,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>127.25</v>
+        <v>119.94</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31935,55 +31935,55 @@
         <v>143</v>
       </c>
       <c r="M137" s="120">
-        <f>M30/M5*365</f>
+        <f t="shared" ref="M137:Q138" si="78">M30/M5*365</f>
         <v>48.268925557877274</v>
       </c>
       <c r="N137" s="120">
-        <f>N30/N5*365</f>
+        <f t="shared" si="78"/>
         <v>46.15954207770065</v>
       </c>
       <c r="O137" s="120">
-        <f>O30/O5*365</f>
+        <f t="shared" si="78"/>
         <v>61.147288033153274</v>
       </c>
       <c r="P137" s="120">
-        <f>P30/P5*365</f>
+        <f t="shared" si="78"/>
         <v>62.908268986021838</v>
       </c>
       <c r="Q137" s="120">
-        <f>Q30/Q5*365</f>
+        <f t="shared" si="78"/>
         <v>57.278802107578244</v>
       </c>
       <c r="T137" s="120">
-        <f>T30/T5*90</f>
+        <f t="shared" ref="T137:AA137" si="79">T30/T5*90</f>
         <v>39.225579973868236</v>
       </c>
       <c r="U137" s="120">
-        <f>U30/U5*90</f>
+        <f t="shared" si="79"/>
         <v>44.027072494470232</v>
       </c>
       <c r="V137" s="120">
-        <f>V30/V5*90</f>
+        <f t="shared" si="79"/>
         <v>55.371367215461703</v>
       </c>
       <c r="W137" s="120">
-        <f>W30/W5*90</f>
+        <f t="shared" si="79"/>
         <v>44.536432307805654</v>
       </c>
       <c r="X137" s="120">
-        <f>X30/X5*90</f>
+        <f t="shared" si="79"/>
         <v>40.28585019721325</v>
       </c>
       <c r="Y137" s="120">
-        <f>Y30/Y5*90</f>
+        <f t="shared" si="79"/>
         <v>41.234721930860871</v>
       </c>
       <c r="Z137" s="120">
-        <f>Z30/Z5*90</f>
+        <f t="shared" si="79"/>
         <v>51.806602372838213</v>
       </c>
       <c r="AA137" s="120">
-        <f>AA30/AA5*90</f>
+        <f t="shared" si="79"/>
         <v>38.558261721358917</v>
       </c>
       <c r="AC137" s="120">
@@ -31996,55 +31996,55 @@
         <v>144</v>
       </c>
       <c r="M138" s="120">
-        <f>M31/M6*365</f>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="N138" s="120">
-        <f>N31/N6*365</f>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="O138" s="120">
-        <f>O31/O6*365</f>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P138" s="120">
-        <f>P31/P6*365</f>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="Q138" s="120">
-        <f>Q31/Q6*365</f>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="T138" s="120">
-        <f>T31/T6*365</f>
+        <f t="shared" ref="T138:AA138" si="80">T31/T6*365</f>
         <v>0</v>
       </c>
       <c r="U138" s="120">
-        <f>U31/U6*365</f>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="V138" s="120">
-        <f>V31/V6*365</f>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="W138" s="120">
-        <f>W31/W6*365</f>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="X138" s="120">
-        <f>X31/X6*365</f>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="Y138" s="120">
-        <f>Y31/Y6*365</f>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="Z138" s="120">
-        <f>Z31/Z6*365</f>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AA138" s="120">
-        <f>AA31/AA6*365</f>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AC138" s="120">
@@ -32077,35 +32077,35 @@
         <v>10.131710466036401</v>
       </c>
       <c r="T139" s="120">
-        <f>T38/T6*90</f>
+        <f t="shared" ref="T139:AA139" si="81">T38/T6*90</f>
         <v>6.4721535829690167</v>
       </c>
       <c r="U139" s="120">
-        <f>U38/U6*90</f>
+        <f t="shared" si="81"/>
         <v>6.2937907244154845</v>
       </c>
       <c r="V139" s="120">
-        <f>V38/V6*90</f>
+        <f t="shared" si="81"/>
         <v>9.7461179465422152</v>
       </c>
       <c r="W139" s="120">
-        <f>W38/W6*90</f>
+        <f t="shared" si="81"/>
         <v>3.4381142437018921</v>
       </c>
       <c r="X139" s="120">
-        <f>X38/X6*90</f>
+        <f t="shared" si="81"/>
         <v>9.9823488892715684</v>
       </c>
       <c r="Y139" s="120">
-        <f>Y38/Y6*90</f>
+        <f t="shared" si="81"/>
         <v>4.2929333440282349</v>
       </c>
       <c r="Z139" s="120">
-        <f>Z38/Z6*90</f>
+        <f t="shared" si="81"/>
         <v>9.3484330965337215</v>
       </c>
       <c r="AA139" s="120">
-        <f>AA38/AA6*90</f>
+        <f t="shared" si="81"/>
         <v>8.5423032546816948</v>
       </c>
       <c r="AC139" s="120">
@@ -32122,55 +32122,55 @@
         <v>7.0240205192856493</v>
       </c>
       <c r="N140" s="120">
-        <f t="shared" ref="N140:Q140" si="78">N137+N138-N139</f>
+        <f t="shared" ref="N140:Q140" si="82">N137+N138-N139</f>
         <v>41.838907667908934</v>
       </c>
       <c r="O140" s="120">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>54.862111579122804</v>
       </c>
       <c r="P140" s="120">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>51.471381264742163</v>
       </c>
       <c r="Q140" s="120">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>47.147091641541842</v>
       </c>
       <c r="T140" s="120">
-        <f t="shared" ref="T140" si="79">T137+T138-T139</f>
+        <f t="shared" ref="T140" si="83">T137+T138-T139</f>
         <v>32.753426390899222</v>
       </c>
       <c r="U140" s="120">
-        <f t="shared" ref="U140" si="80">U137+U138-U139</f>
+        <f t="shared" ref="U140" si="84">U137+U138-U139</f>
         <v>37.733281770054745</v>
       </c>
       <c r="V140" s="120">
-        <f t="shared" ref="V140" si="81">V137+V138-V139</f>
+        <f t="shared" ref="V140" si="85">V137+V138-V139</f>
         <v>45.62524926891949</v>
       </c>
       <c r="W140" s="120">
-        <f t="shared" ref="W140" si="82">W137+W138-W139</f>
+        <f t="shared" ref="W140" si="86">W137+W138-W139</f>
         <v>41.098318064103765</v>
       </c>
       <c r="X140" s="120">
-        <f t="shared" ref="X140" si="83">X137+X138-X139</f>
+        <f t="shared" ref="X140" si="87">X137+X138-X139</f>
         <v>30.30350130794168</v>
       </c>
       <c r="Y140" s="120">
-        <f t="shared" ref="Y140" si="84">Y137+Y138-Y139</f>
+        <f t="shared" ref="Y140" si="88">Y137+Y138-Y139</f>
         <v>36.941788586832637</v>
       </c>
       <c r="Z140" s="120">
-        <f t="shared" ref="Z140:AA140" si="85">Z137+Z138-Z139</f>
+        <f t="shared" ref="Z140:AA140" si="89">Z137+Z138-Z139</f>
         <v>42.458169276304488</v>
       </c>
       <c r="AA140" s="120">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>30.015958466677223</v>
       </c>
       <c r="AC140" s="120">
-        <f t="shared" ref="AC140" si="86">AC137+AC138-AC139</f>
+        <f t="shared" ref="AC140" si="90">AC137+AC138-AC139</f>
         <v>32.453474658634278</v>
       </c>
     </row>
@@ -32199,35 +32199,35 @@
         <v>0</v>
       </c>
       <c r="T141" s="120">
-        <f>T108/T49</f>
+        <f t="shared" ref="T141:AA141" si="91">T108/T49</f>
         <v>0</v>
       </c>
       <c r="U141" s="120">
-        <f>U108/U49</f>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="V141" s="120">
-        <f>V108/V49</f>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="W141" s="120">
-        <f>W108/W49</f>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="X141" s="120">
-        <f>X108/X49</f>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="Y141" s="120">
-        <f>Y108/Y49</f>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="Z141" s="120">
-        <f>Z108/Z49</f>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AA141" s="120">
-        <f>AA108/AA49</f>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AC141" s="120">
@@ -32260,35 +32260,35 @@
         <v>-0.94696311671959887</v>
       </c>
       <c r="T142" s="181">
-        <f>(T108-T107)/T49</f>
+        <f t="shared" ref="T142:AA142" si="92">(T108-T107)/T49</f>
         <v>-1.1581549630742272</v>
       </c>
       <c r="U142" s="181">
-        <f>(U108-U107)/U49</f>
+        <f t="shared" si="92"/>
         <v>-1.1381695975332329</v>
       </c>
       <c r="V142" s="181">
-        <f>(V108-V107)/V49</f>
+        <f t="shared" si="92"/>
         <v>-1.1835995391425627</v>
       </c>
       <c r="W142" s="181">
-        <f>(W108-W107)/W49</f>
+        <f t="shared" si="92"/>
         <v>-1.2112223184378168</v>
       </c>
       <c r="X142" s="181">
-        <f>(X108-X107)/X49</f>
+        <f t="shared" si="92"/>
         <v>-1.2008267905521934</v>
       </c>
       <c r="Y142" s="181">
-        <f>(Y108-Y107)/Y49</f>
+        <f t="shared" si="92"/>
         <v>-0.93319510928545912</v>
       </c>
       <c r="Z142" s="181">
-        <f>(Z108-Z107)/Z49</f>
+        <f t="shared" si="92"/>
         <v>-0.94696311671959887</v>
       </c>
       <c r="AA142" s="181">
-        <f>(AA108-AA107)/AA49</f>
+        <f t="shared" si="92"/>
         <v>-1.0000409552194194</v>
       </c>
       <c r="AC142" s="181">
@@ -32321,35 +32321,35 @@
         <v>2.6098107949225979</v>
       </c>
       <c r="T143" s="120">
-        <f>(T107+T30)/T40</f>
+        <f t="shared" ref="T143:AA143" si="93">(T107+T30)/T40</f>
         <v>3.040255064143722</v>
       </c>
       <c r="U143" s="120">
-        <f>(U107+U30)/U40</f>
+        <f t="shared" si="93"/>
         <v>3.0114195356776459</v>
       </c>
       <c r="V143" s="120">
-        <f>(V107+V30)/V40</f>
+        <f t="shared" si="93"/>
         <v>2.6167192839938327</v>
       </c>
       <c r="W143" s="120">
-        <f>(W107+W30)/W40</f>
+        <f t="shared" si="93"/>
         <v>2.6333212317238193</v>
       </c>
       <c r="X143" s="120">
-        <f>(X107+X30)/X40</f>
+        <f t="shared" si="93"/>
         <v>2.7284904207406715</v>
       </c>
       <c r="Y143" s="120">
-        <f>(Y107+Y30)/Y40</f>
+        <f t="shared" si="93"/>
         <v>2.7751640731415361</v>
       </c>
       <c r="Z143" s="120">
-        <f>(Z107+Z30)/Z40</f>
+        <f t="shared" si="93"/>
         <v>2.6098107949225979</v>
       </c>
       <c r="AA143" s="120">
-        <f>(AA107+AA30)/AA40</f>
+        <f t="shared" si="93"/>
         <v>2.6421703703445658</v>
       </c>
       <c r="AC143" s="120">
@@ -32382,35 +32382,35 @@
         <v>2.6065702860211775</v>
       </c>
       <c r="T144" s="120">
-        <f>T32/T40</f>
+        <f t="shared" ref="T144:AA144" si="94">T32/T40</f>
         <v>3.2782037239868567</v>
       </c>
       <c r="U144" s="120">
-        <f>U32/U40</f>
+        <f t="shared" si="94"/>
         <v>3.0936419462606648</v>
       </c>
       <c r="V144" s="120">
-        <f>V32/V40</f>
+        <f t="shared" si="94"/>
         <v>2.6089699714137522</v>
       </c>
       <c r="W144" s="120">
-        <f>W32/W40</f>
+        <f t="shared" si="94"/>
         <v>2.6836023191084415</v>
       </c>
       <c r="X144" s="120">
-        <f>X32/X40</f>
+        <f t="shared" si="94"/>
         <v>2.8087351474278877</v>
       </c>
       <c r="Y144" s="120">
-        <f>Y32/Y40</f>
+        <f t="shared" si="94"/>
         <v>2.8214492095595824</v>
       </c>
       <c r="Z144" s="120">
-        <f>Z32/Z40</f>
+        <f t="shared" si="94"/>
         <v>2.6065702860211775</v>
       </c>
       <c r="AA144" s="120">
-        <f>AA32/AA40</f>
+        <f t="shared" si="94"/>
         <v>2.6231009869120072</v>
       </c>
       <c r="AC144" s="120">
@@ -32443,35 +32443,35 @@
         <v>N/A</v>
       </c>
       <c r="T145" s="183" t="str">
-        <f>IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
+        <f t="shared" ref="T145:AA145" si="95">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>N/A</v>
       </c>
       <c r="U145" s="183" t="str">
-        <f>IF(U13&gt;=0,"N/A",IF(U12&lt;=0,"N/A",U12/-U13))</f>
+        <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
       <c r="V145" s="183" t="str">
-        <f>IF(V13&gt;=0,"N/A",IF(V12&lt;=0,"N/A",V12/-V13))</f>
+        <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
       <c r="W145" s="183" t="str">
-        <f>IF(W13&gt;=0,"N/A",IF(W12&lt;=0,"N/A",W12/-W13))</f>
+        <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
       <c r="X145" s="183" t="str">
-        <f>IF(X13&gt;=0,"N/A",IF(X12&lt;=0,"N/A",X12/-X13))</f>
+        <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
       <c r="Y145" s="183" t="str">
-        <f>IF(Y13&gt;=0,"N/A",IF(Y12&lt;=0,"N/A",Y12/-Y13))</f>
+        <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
       <c r="Z145" s="183" t="str">
-        <f>IF(Z13&gt;=0,"N/A",IF(Z12&lt;=0,"N/A",Z12/-Z13))</f>
+        <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
       <c r="AA145" s="183" t="str">
-        <f>IF(AA13&gt;=0,"N/A",IF(AA12&lt;=0,"N/A",AA12/-AA13))</f>
+        <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
       <c r="AC145" s="183" t="str">
@@ -32513,7 +32513,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>37.530264782647187</v>
+        <v>35.374302224209849</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32550,7 +32550,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>5.6585115991708514</v>
+        <v>5.3334528974817434</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32587,7 +32587,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.2600320528480404</v>
+        <v>4.0153103687119369</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32624,7 +32624,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6208145.75</v>
+        <v>5851512.7800000003</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32661,7 +32661,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="145">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>4816324.75</v>
+        <v>4459691.78</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32698,7 +32698,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="185">
         <f ca="1">AC150/AC5</f>
-        <v>4.3832069241991132</v>
+        <v>4.0586449013617427</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32735,7 +32735,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="185">
         <f ca="1">AC150/AC12</f>
-        <v>30.774648089812974</v>
+        <v>28.495886852009228</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32763,35 +32763,35 @@
         <v>222987</v>
       </c>
       <c r="T153" s="64">
-        <f>T59-T54+T110+T65</f>
+        <f t="shared" ref="T153:AA153" si="96">T59-T54+T110+T65</f>
         <v>26986</v>
       </c>
       <c r="U153" s="64">
-        <f>U59-U54+U110+U65</f>
+        <f t="shared" si="96"/>
         <v>22285</v>
       </c>
       <c r="V153" s="64">
-        <f>V59-V54+V110+V65</f>
+        <f t="shared" si="96"/>
         <v>51117</v>
       </c>
       <c r="W153" s="64">
-        <f>W59-W54+W110+W65</f>
+        <f t="shared" si="96"/>
         <v>71994</v>
       </c>
       <c r="X153" s="64">
-        <f>X59-X54+X110+X65</f>
+        <f t="shared" si="96"/>
         <v>51732</v>
       </c>
       <c r="Y153" s="64">
-        <f>Y59-Y54+Y110+Y65</f>
+        <f t="shared" si="96"/>
         <v>41791</v>
       </c>
       <c r="Z153" s="64">
-        <f>Z59-Z54+Z110+Z65</f>
+        <f t="shared" si="96"/>
         <v>57470</v>
       </c>
       <c r="AA153" s="64">
-        <f>AA59-AA54+AA110+AA65</f>
+        <f t="shared" si="96"/>
         <v>113139</v>
       </c>
       <c r="AC153" s="64">
@@ -32845,19 +32845,19 @@
         <v>-112.87400898520085</v>
       </c>
       <c r="N155" s="72">
-        <f t="shared" ref="N155:Q155" si="87">N149/N153</f>
+        <f t="shared" ref="N155:Q155" si="97">N149/N153</f>
         <v>-95.43181061806655</v>
       </c>
       <c r="O155" s="72">
-        <f t="shared" si="87"/>
+        <f t="shared" si="97"/>
         <v>243.27936097877384</v>
       </c>
       <c r="P155" s="72">
-        <f t="shared" si="87"/>
+        <f t="shared" si="97"/>
         <v>103.20455372459323</v>
       </c>
       <c r="Q155" s="72">
-        <f t="shared" si="87"/>
+        <f t="shared" si="97"/>
         <v>39.668168547942251</v>
       </c>
       <c r="T155" s="49"/>
@@ -32869,8 +32869,8 @@
       <c r="Z155" s="49"/>
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
-        <f t="shared" ref="AC155:AC156" ca="1" si="88">AC149/AC153</f>
-        <v>23.503951622673512</v>
+        <f t="shared" ref="AC155:AC156" ca="1" si="98">AC149/AC153</f>
+        <v>22.15374426423152</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32882,19 +32882,19 @@
         <v>-98.568903797199823</v>
       </c>
       <c r="N156" s="72">
-        <f t="shared" ref="N156:Q156" si="89">N150/N154</f>
+        <f t="shared" ref="N156:Q156" si="99">N150/N154</f>
         <v>-63.556731738561353</v>
       </c>
       <c r="O156" s="72">
-        <f t="shared" si="89"/>
+        <f t="shared" si="99"/>
         <v>673.03434883720922</v>
       </c>
       <c r="P156" s="72">
-        <f t="shared" si="89"/>
+        <f t="shared" si="99"/>
         <v>124.4016933148245</v>
       </c>
       <c r="Q156" s="72">
-        <f t="shared" si="89"/>
+        <f t="shared" si="99"/>
         <v>49.504381582091227</v>
       </c>
       <c r="T156" s="49"/>
@@ -32906,8 +32906,8 @@
       <c r="Z156" s="49"/>
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
-        <f t="shared" ca="1" si="88"/>
-        <v>25.780281423357575</v>
+        <f t="shared" ca="1" si="98"/>
+        <v>23.871336572525447</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32919,19 +32919,19 @@
         <v>-8.8594354802363062E-3</v>
       </c>
       <c r="N157" s="74">
-        <f t="shared" ref="N157:Q157" si="90">N153/N149</f>
+        <f t="shared" ref="N157:Q157" si="100">N153/N149</f>
         <v>-1.0478686231807555E-2</v>
       </c>
       <c r="O157" s="74">
-        <f t="shared" si="90"/>
+        <f t="shared" si="100"/>
         <v>4.1105007674171346E-3</v>
       </c>
       <c r="P157" s="74">
-        <f t="shared" si="90"/>
+        <f t="shared" si="100"/>
         <v>9.6894949293473281E-3</v>
       </c>
       <c r="Q157" s="74">
-        <f t="shared" si="90"/>
+        <f t="shared" si="100"/>
         <v>2.5209129551605529E-2</v>
       </c>
       <c r="T157" s="49"/>
@@ -32943,8 +32943,8 @@
       <c r="Z157" s="49"/>
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
-        <f t="shared" ref="AC157" ca="1" si="91">AC153/AC149</f>
-        <v>4.2546037196372205E-2</v>
+        <f t="shared" ref="AC157" ca="1" si="101">AC153/AC149</f>
+        <v>4.513909649189897E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -32981,7 +32981,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.6645162398704111E-2</v>
+        <v>2.8269108848049843E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33055,7 +33055,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="156">
         <f ca="1">-AC63/AC149</f>
-        <v>3.9192056662007329E-3</v>
+        <v>4.1580700435554716E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33092,7 +33092,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="156">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>3.9192056662007329E-3</v>
+        <v>4.1580700435554716E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33342,35 +33342,35 @@
         <v>26.910654008438819</v>
       </c>
       <c r="T168" s="72">
-        <f>T107/T75</f>
+        <f t="shared" ref="T168:AA168" si="102">T107/T75</f>
         <v>20.401019775373804</v>
       </c>
       <c r="U168" s="72">
-        <f>U107/U75</f>
+        <f t="shared" si="102"/>
         <v>21.282534558021098</v>
       </c>
       <c r="V168" s="72">
-        <f>V107/V75</f>
+        <f t="shared" si="102"/>
         <v>21.571005459408084</v>
       </c>
       <c r="W168" s="72">
-        <f>W107/W75</f>
+        <f t="shared" si="102"/>
         <v>23.817445825541746</v>
       </c>
       <c r="X168" s="72">
-        <f>X107/X75</f>
+        <f t="shared" si="102"/>
         <v>25.604403998079526</v>
       </c>
       <c r="Y168" s="72">
-        <f>Y107/Y75</f>
+        <f t="shared" si="102"/>
         <v>26.395020333996712</v>
       </c>
       <c r="Z168" s="72">
-        <f>Z107/Z75</f>
+        <f t="shared" si="102"/>
         <v>26.910654008438819</v>
       </c>
       <c r="AA168" s="72">
-        <f>AA107/AA75</f>
+        <f t="shared" si="102"/>
         <v>29.871890627347454</v>
       </c>
       <c r="AC168" s="72">
@@ -33403,35 +33403,35 @@
         <v>0.35438073554172911</v>
       </c>
       <c r="T169" s="156">
-        <f>T54/T59</f>
+        <f t="shared" ref="T169:AA169" si="103">T54/T59</f>
         <v>0.42870423799448609</v>
       </c>
       <c r="U169" s="156">
-        <f>U54/U59</f>
+        <f t="shared" si="103"/>
         <v>0.51467112161657813</v>
       </c>
       <c r="V169" s="156">
-        <f>V54/V59</f>
+        <f t="shared" si="103"/>
         <v>0.357398253023613</v>
       </c>
       <c r="W169" s="156">
-        <f>W54/W59</f>
+        <f t="shared" si="103"/>
         <v>0.29364485804356677</v>
       </c>
       <c r="X169" s="156">
-        <f>X54/X59</f>
+        <f t="shared" si="103"/>
         <v>0.38149434794596088</v>
       </c>
       <c r="Y169" s="156">
-        <f>Y54/Y59</f>
+        <f t="shared" si="103"/>
         <v>0.42219162145799449</v>
       </c>
       <c r="Z169" s="156">
-        <f>Z54/Z59</f>
+        <f t="shared" si="103"/>
         <v>0.33801897872816422</v>
       </c>
       <c r="AA169" s="156">
-        <f>AA54/AA59</f>
+        <f t="shared" si="103"/>
         <v>0.22979883399327458</v>
       </c>
       <c r="AC169" s="156">
@@ -33464,35 +33464,35 @@
         <v>0.13245803492519678</v>
       </c>
       <c r="T170" s="156">
-        <f>T54/T5</f>
+        <f t="shared" ref="T170:AA170" si="104">T54/T5</f>
         <v>0.14998289658885081</v>
       </c>
       <c r="U170" s="156">
-        <f>U54/U5</f>
+        <f t="shared" si="104"/>
         <v>0.15036293965544098</v>
       </c>
       <c r="V170" s="156">
-        <f>V54/V5</f>
+        <f t="shared" si="104"/>
         <v>0.14214745884037222</v>
       </c>
       <c r="W170" s="156">
-        <f>W54/W5</f>
+        <f t="shared" si="104"/>
         <v>0.13442661315836232</v>
       </c>
       <c r="X170" s="156">
-        <f>X54/X5</f>
+        <f t="shared" si="104"/>
         <v>0.13712564168632194</v>
       </c>
       <c r="Y170" s="156">
-        <f>Y54/Y5</f>
+        <f t="shared" si="104"/>
         <v>0.13089178655419506</v>
       </c>
       <c r="Z170" s="156">
-        <f>Z54/Z5</f>
+        <f t="shared" si="104"/>
         <v>0.1281940693185514</v>
       </c>
       <c r="AA170" s="156">
-        <f>AA54/AA5</f>
+        <f t="shared" si="104"/>
         <v>0.11866752064445639</v>
       </c>
       <c r="AC170" s="156">
@@ -33525,35 +33525,35 @@
         <v>26.910654008438819</v>
       </c>
       <c r="T171" s="72">
-        <f>(T107-T108)/T75</f>
+        <f t="shared" ref="T171:AA171" si="105">(T107-T108)/T75</f>
         <v>20.401019775373804</v>
       </c>
       <c r="U171" s="72">
-        <f>(U107-U108)/U75</f>
+        <f t="shared" si="105"/>
         <v>21.282534558021098</v>
       </c>
       <c r="V171" s="72">
-        <f>(V107-V108)/V75</f>
+        <f t="shared" si="105"/>
         <v>21.571005459408084</v>
       </c>
       <c r="W171" s="72">
-        <f>(W107-W108)/W75</f>
+        <f t="shared" si="105"/>
         <v>23.817445825541746</v>
       </c>
       <c r="X171" s="72">
-        <f>(X107-X108)/X75</f>
+        <f t="shared" si="105"/>
         <v>25.604403998079526</v>
       </c>
       <c r="Y171" s="72">
-        <f>(Y107-Y108)/Y75</f>
+        <f t="shared" si="105"/>
         <v>26.395020333996712</v>
       </c>
       <c r="Z171" s="72">
-        <f>(Z107-Z108)/Z75</f>
+        <f t="shared" si="105"/>
         <v>26.910654008438819</v>
       </c>
       <c r="AA171" s="72">
-        <f>(AA107-AA108)/AA75</f>
+        <f t="shared" si="105"/>
         <v>29.871890627347454</v>
       </c>
       <c r="AC171" s="72">
@@ -33595,7 +33595,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="156">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.22419270681587977</v>
+        <v>0.23785661115825163</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -33623,35 +33623,35 @@
         <v>2.6406409474271603E-2</v>
       </c>
       <c r="T173" s="156">
-        <f>-T110/T5</f>
+        <f t="shared" ref="T173:AA173" si="106">-T110/T5</f>
         <v>4.8540041608954337E-2</v>
       </c>
       <c r="U173" s="156">
-        <f>-U110/U5</f>
+        <f t="shared" si="106"/>
         <v>2.60807709482123E-2</v>
       </c>
       <c r="V173" s="156">
-        <f>-V110/V5</f>
+        <f t="shared" si="106"/>
         <v>1.1643999045573849E-2</v>
       </c>
       <c r="W173" s="156">
-        <f>-W110/W5</f>
+        <f t="shared" si="106"/>
         <v>1.1350290149647009E-2</v>
       </c>
       <c r="X173" s="156">
-        <f>-X110/X5</f>
+        <f t="shared" si="106"/>
         <v>1.7247735516223019E-2</v>
       </c>
       <c r="Y173" s="156">
-        <f>-Y110/Y5</f>
+        <f t="shared" si="106"/>
         <v>2.5331875913187814E-2</v>
       </c>
       <c r="Z173" s="156">
-        <f>-Z110/Z5</f>
+        <f t="shared" si="106"/>
         <v>4.7888060862310337E-2</v>
       </c>
       <c r="AA173" s="156">
-        <f>-AA110/AA5</f>
+        <f t="shared" si="106"/>
         <v>1.0223758164450092E-2</v>
       </c>
       <c r="AC173" s="156">
@@ -33684,35 +33684,35 @@
         <v>7.0648208074301944E-2</v>
       </c>
       <c r="T174" s="156">
-        <f>-(T110/T59)</f>
+        <f t="shared" ref="T174:AA174" si="107">-(T110/T59)</f>
         <v>0.13874463037763674</v>
       </c>
       <c r="U174" s="156">
-        <f>-(U110/U59)</f>
+        <f t="shared" si="107"/>
         <v>8.9270798158778683E-2</v>
       </c>
       <c r="V174" s="156">
-        <f>-(V110/V59)</f>
+        <f t="shared" si="107"/>
         <v>2.9276252639662124E-2</v>
       </c>
       <c r="W174" s="156">
-        <f>-(W110/W59)</f>
+        <f t="shared" si="107"/>
         <v>2.4793857863695316E-2</v>
       </c>
       <c r="X174" s="156">
-        <f>-(X110/X59)</f>
+        <f t="shared" si="107"/>
         <v>4.7984560242624756E-2</v>
       </c>
       <c r="Y174" s="156">
-        <f>-(Y110/Y59)</f>
+        <f t="shared" si="107"/>
         <v>8.1707997483350947E-2</v>
       </c>
       <c r="Z174" s="156">
-        <f>-(Z110/Z59)</f>
+        <f t="shared" si="107"/>
         <v>0.12627006469173549</v>
       </c>
       <c r="AA174" s="156">
-        <f>-(AA110/AA59)</f>
+        <f t="shared" si="107"/>
         <v>1.9798237061503871E-2</v>
       </c>
       <c r="AC174" s="156">
@@ -33745,35 +33745,35 @@
         <v>1.9038982697519282</v>
       </c>
       <c r="T175" s="156">
-        <f>-T110/T53</f>
+        <f t="shared" ref="T175:AA175" si="108">-T110/T53</f>
         <v>3.8591172536781095</v>
       </c>
       <c r="U175" s="156">
-        <f>-U110/U53</f>
+        <f t="shared" si="108"/>
         <v>1.7465229485396383</v>
       </c>
       <c r="V175" s="156">
-        <f>-V110/V53</f>
+        <f t="shared" si="108"/>
         <v>0.66648456705818082</v>
       </c>
       <c r="W175" s="156">
-        <f>-W110/W53</f>
+        <f t="shared" si="108"/>
         <v>0.7295264623955432</v>
       </c>
       <c r="X175" s="156">
-        <f>-X110/X53</f>
+        <f t="shared" si="108"/>
         <v>1.2648255813953488</v>
       </c>
       <c r="Y175" s="156">
-        <f>-Y110/Y53</f>
+        <f t="shared" si="108"/>
         <v>1.9372361384745285</v>
       </c>
       <c r="Z175" s="156">
-        <f>-Z110/Z53</f>
+        <f t="shared" si="108"/>
         <v>3.5572478991596639</v>
       </c>
       <c r="AA175" s="156">
-        <f>-AA110/AA53</f>
+        <f t="shared" si="108"/>
         <v>0.71224051539012168</v>
       </c>
       <c r="AC175" s="156">
@@ -34055,7 +34055,7 @@
         <v>20614</v>
       </c>
       <c r="AC184" s="62">
-        <f t="shared" ref="AC184:AC187" si="92">SUM(X184:AA184)</f>
+        <f t="shared" ref="AC184:AC187" si="109">SUM(X184:AA184)</f>
         <v>82457</v>
       </c>
     </row>
@@ -34113,7 +34113,7 @@
         <v>11317</v>
       </c>
       <c r="AC185" s="62">
-        <f t="shared" si="92"/>
+        <f t="shared" si="109"/>
         <v>41337</v>
       </c>
     </row>
@@ -34171,7 +34171,7 @@
         <v>8446</v>
       </c>
       <c r="AC186" s="62">
-        <f t="shared" si="92"/>
+        <f t="shared" si="109"/>
         <v>39483</v>
       </c>
     </row>
@@ -34229,7 +34229,7 @@
         <v>682</v>
       </c>
       <c r="AC187" s="62">
-        <f t="shared" si="92"/>
+        <f t="shared" si="109"/>
         <v>2173</v>
       </c>
     </row>
@@ -34293,61 +34293,61 @@
       <c r="K191" s="81"/>
       <c r="L191" s="81"/>
       <c r="M191" s="81">
-        <f t="shared" ref="M191:Q193" si="93">IF(L183=0,
+        <f t="shared" ref="M191:Q193" si="110">IF(L183=0,
 IF(M183=0,0,IF(M183&gt;0,1,-1)),
 (M183-L183)/ABS(L183)
 )</f>
         <v>1</v>
       </c>
       <c r="N191" s="81">
-        <f t="shared" si="93"/>
+        <f t="shared" si="110"/>
         <v>0.51361387508439493</v>
       </c>
       <c r="O191" s="81">
-        <f t="shared" si="93"/>
+        <f t="shared" si="110"/>
         <v>0.47961112512659637</v>
       </c>
       <c r="P191" s="81">
-        <f t="shared" si="93"/>
+        <f t="shared" si="110"/>
         <v>0.50124788724041469</v>
       </c>
       <c r="Q191" s="81">
-        <f t="shared" si="93"/>
+        <f t="shared" si="110"/>
         <v>0.43769124538500914</v>
       </c>
       <c r="T191" s="81">
-        <f t="shared" ref="T191:AA193" si="94">IF(S183=0,
+        <f t="shared" ref="T191:AA193" si="111">IF(S183=0,
 IF(T183=0,0,IF(T183&gt;0,1,-1)),
 (T183-S183)/ABS(S183)
 )</f>
         <v>1</v>
       </c>
       <c r="U191" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>9.5254640085053743E-2</v>
       </c>
       <c r="V191" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>0.10595303806061529</v>
       </c>
       <c r="W191" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>9.5630374547519742E-2</v>
       </c>
       <c r="X191" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>0.10310125820081995</v>
       </c>
       <c r="Y191" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>8.9297411215219433E-2</v>
       </c>
       <c r="Z191" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>5.5753820411257961E-2</v>
       </c>
       <c r="AA191" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>3.5586042940987099E-2</v>
       </c>
       <c r="AC191" s="49"/>
@@ -34357,55 +34357,55 @@
         <v>383</v>
       </c>
       <c r="M192" s="81">
-        <f t="shared" si="93"/>
+        <f t="shared" si="110"/>
         <v>1</v>
       </c>
       <c r="N192" s="81">
-        <f t="shared" si="93"/>
+        <f t="shared" si="110"/>
         <v>0.161813978857692</v>
       </c>
       <c r="O192" s="81">
-        <f t="shared" si="93"/>
+        <f t="shared" si="110"/>
         <v>0.11461849723905122</v>
       </c>
       <c r="P192" s="81">
-        <f t="shared" si="93"/>
+        <f t="shared" si="110"/>
         <v>0.10126759998395443</v>
       </c>
       <c r="Q192" s="81">
-        <f t="shared" si="93"/>
+        <f t="shared" si="110"/>
         <v>0.45200065565410602</v>
       </c>
       <c r="T192" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>1</v>
       </c>
       <c r="U192" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>8.6513802986875846E-2</v>
       </c>
       <c r="V192" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>-7.8444984380423455E-3</v>
       </c>
       <c r="W192" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>0.25118947663028268</v>
       </c>
       <c r="X192" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>0.15216418745106811</v>
       </c>
       <c r="Y192" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>2.019123428626899E-2</v>
       </c>
       <c r="Z192" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>-3.796565012607641E-2</v>
       </c>
       <c r="AA192" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>1.9435240591464318E-2</v>
       </c>
       <c r="AC192" s="49"/>
@@ -34415,85 +34415,85 @@
         <v>384</v>
       </c>
       <c r="M193" s="81">
-        <f t="shared" si="93"/>
+        <f t="shared" si="110"/>
         <v>1</v>
       </c>
       <c r="N193" s="81">
-        <f t="shared" ref="N193:N195" si="95">IF(M185=0,
+        <f t="shared" ref="N193:N195" si="112">IF(M185=0,
 IF(N185=0,0,IF(N185&gt;0,1,-1)),
 (N185-M185)/ABS(M185)
 )</f>
         <v>0.32687160353637762</v>
       </c>
       <c r="O193" s="81">
-        <f t="shared" ref="O193:O195" si="96">IF(N185=0,
+        <f t="shared" ref="O193:O195" si="113">IF(N185=0,
 IF(O185=0,0,IF(O185&gt;0,1,-1)),
 (O185-N185)/ABS(N185)
 )</f>
         <v>0.25961244574851766</v>
       </c>
       <c r="P193" s="81">
-        <f t="shared" ref="P193:P195" si="97">IF(O185=0,
+        <f t="shared" ref="P193:P195" si="114">IF(O185=0,
 IF(P185=0,0,IF(P185&gt;0,1,-1)),
 (P185-O185)/ABS(O185)
 )</f>
         <v>0.107444433660099</v>
       </c>
       <c r="Q193" s="81">
-        <f t="shared" ref="Q193:Q195" si="98">IF(P185=0,
+        <f t="shared" ref="Q193:Q195" si="115">IF(P185=0,
 IF(Q185=0,0,IF(Q185&gt;0,1,-1)),
 (Q185-P185)/ABS(P185)
 )</f>
         <v>-7.9623137598597724E-2</v>
       </c>
       <c r="T193" s="81">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>1</v>
       </c>
       <c r="U193" s="81">
-        <f t="shared" ref="U193:U195" si="99">IF(T185=0,
+        <f t="shared" ref="U193:U195" si="116">IF(T185=0,
 IF(U185=0,0,IF(U185&gt;0,1,-1)),
 (U185-T185)/ABS(T185)
 )</f>
         <v>6.9171807814544777E-3</v>
       </c>
       <c r="V193" s="81">
-        <f t="shared" ref="V193:V195" si="100">IF(U185=0,
+        <f t="shared" ref="V193:V195" si="117">IF(U185=0,
 IF(V185=0,0,IF(V185&gt;0,1,-1)),
 (V185-U185)/ABS(U185)
 )</f>
         <v>5.9691793538804307E-2</v>
       </c>
       <c r="W193" s="81">
-        <f t="shared" ref="W193:W195" si="101">IF(V185=0,
+        <f t="shared" ref="W193:W195" si="118">IF(V185=0,
 IF(W185=0,0,IF(W185&gt;0,1,-1)),
 (W185-V185)/ABS(V185)
 )</f>
         <v>5.0021901007446343E-2</v>
       </c>
       <c r="X193" s="81">
-        <f t="shared" ref="X193:X195" si="102">IF(W185=0,
+        <f t="shared" ref="X193:X195" si="119">IF(W185=0,
 IF(X185=0,0,IF(X185&gt;0,1,-1)),
 (X185-W185)/ABS(W185)
 )</f>
         <v>-0.15835140997830802</v>
       </c>
       <c r="Y193" s="81">
-        <f t="shared" ref="Y193:Y195" si="103">IF(X185=0,
+        <f t="shared" ref="Y193:Y195" si="120">IF(X185=0,
 IF(Y185=0,0,IF(Y185&gt;0,1,-1)),
 (Y185-X185)/ABS(X185)
 )</f>
         <v>-4.3517049960348927E-2</v>
       </c>
       <c r="Z193" s="81">
-        <f t="shared" ref="Z193:Z195" si="104">IF(Y185=0,
+        <f t="shared" ref="Z193:Z195" si="121">IF(Y185=0,
 IF(Z185=0,0,IF(Z185&gt;0,1,-1)),
 (Z185-Y185)/ABS(Y185)
 )</f>
         <v>6.5706290807337545E-2</v>
       </c>
       <c r="AA193" s="81">
-        <f t="shared" ref="AA193:AA195" si="105">IF(Z185=0,
+        <f t="shared" ref="AA193:AA195" si="122">IF(Z185=0,
 IF(AA185=0,0,IF(AA185&gt;0,1,-1)),
 (AA185-Z185)/ABS(Z185)
 )</f>
@@ -34506,61 +34506,61 @@
         <v>385</v>
       </c>
       <c r="M194" s="81">
-        <f t="shared" ref="M194:M195" si="106">IF(L186=0,
+        <f t="shared" ref="M194:M195" si="123">IF(L186=0,
 IF(M186=0,0,IF(M186&gt;0,1,-1)),
 (M186-L186)/ABS(L186)
 )</f>
         <v>1</v>
       </c>
       <c r="N194" s="81">
-        <f t="shared" si="95"/>
+        <f t="shared" si="112"/>
         <v>1.6809833694866232</v>
       </c>
       <c r="O194" s="81">
-        <f t="shared" si="96"/>
+        <f t="shared" si="113"/>
         <v>0.87027347753384754</v>
       </c>
       <c r="P194" s="81">
-        <f t="shared" si="97"/>
+        <f t="shared" si="114"/>
         <v>0.11478672165662042</v>
       </c>
       <c r="Q194" s="81">
-        <f t="shared" si="98"/>
+        <f t="shared" si="115"/>
         <v>4.7240835122758909E-2</v>
       </c>
       <c r="T194" s="81">
-        <f t="shared" ref="T194:T195" si="107">IF(S186=0,
+        <f t="shared" ref="T194:T195" si="124">IF(S186=0,
 IF(T186=0,0,IF(T186&gt;0,1,-1)),
 (T186-S186)/ABS(S186)
 )</f>
         <v>1</v>
       </c>
       <c r="U194" s="81">
-        <f t="shared" si="99"/>
+        <f t="shared" si="116"/>
         <v>-7.5176886792452824E-2</v>
       </c>
       <c r="V194" s="81">
-        <f t="shared" si="100"/>
+        <f t="shared" si="117"/>
         <v>-2.8583572415258739E-2</v>
       </c>
       <c r="W194" s="81">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>3.281557646029315E-2</v>
       </c>
       <c r="X194" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="119"/>
         <v>0.10040245710654522</v>
       </c>
       <c r="Y194" s="81">
-        <f t="shared" si="103"/>
+        <f t="shared" si="120"/>
         <v>6.7949951876804623E-2</v>
       </c>
       <c r="Z194" s="81">
-        <f t="shared" si="104"/>
+        <f t="shared" si="121"/>
         <v>-0.13923936553713051</v>
       </c>
       <c r="AA194" s="81">
-        <f t="shared" si="105"/>
+        <f t="shared" si="122"/>
         <v>-0.11569469165532405</v>
       </c>
       <c r="AC194" s="49"/>
@@ -34570,55 +34570,55 @@
         <v>386</v>
       </c>
       <c r="M195" s="81">
-        <f t="shared" si="106"/>
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
       <c r="N195" s="81">
-        <f t="shared" si="95"/>
+        <f t="shared" si="112"/>
         <v>6.9113924050632916</v>
       </c>
       <c r="O195" s="81">
-        <f t="shared" si="96"/>
+        <f t="shared" si="113"/>
         <v>9.1200000000000003E-2</v>
       </c>
       <c r="P195" s="81">
-        <f t="shared" si="97"/>
+        <f t="shared" si="114"/>
         <v>0.89589442815249265</v>
       </c>
       <c r="Q195" s="81">
-        <f t="shared" si="98"/>
+        <f t="shared" si="115"/>
         <v>0.49806651198762569</v>
       </c>
       <c r="T195" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="124"/>
         <v>1</v>
       </c>
       <c r="U195" s="81">
-        <f t="shared" si="99"/>
+        <f t="shared" si="116"/>
         <v>0.36013986013986016</v>
       </c>
       <c r="V195" s="81">
-        <f t="shared" si="100"/>
+        <f t="shared" si="117"/>
         <v>-1.2853470437017995E-2</v>
       </c>
       <c r="W195" s="81">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0.16145833333333334</v>
       </c>
       <c r="X195" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="119"/>
         <v>0.13452914798206278</v>
       </c>
       <c r="Y195" s="81">
-        <f t="shared" si="103"/>
+        <f t="shared" si="120"/>
         <v>-9.4861660079051377E-2</v>
       </c>
       <c r="Z195" s="81">
-        <f t="shared" si="104"/>
+        <f t="shared" si="121"/>
         <v>0.15065502183406113</v>
       </c>
       <c r="AA195" s="81">
-        <f t="shared" si="105"/>
+        <f t="shared" si="122"/>
         <v>0.29411764705882354</v>
       </c>
       <c r="AC195" s="49"/>
@@ -34971,7 +34971,7 @@
         <v>137800</v>
       </c>
       <c r="AC210" s="21">
-        <f t="shared" ref="AC210:AC212" si="108">AA210</f>
+        <f t="shared" ref="AC210:AC212" si="125">AA210</f>
         <v>137800</v>
       </c>
     </row>
@@ -35029,7 +35029,7 @@
         <v>12500</v>
       </c>
       <c r="AC211" s="21">
-        <f t="shared" si="108"/>
+        <f t="shared" si="125"/>
         <v>12500</v>
       </c>
     </row>
@@ -35042,121 +35042,121 @@
         <v>38000</v>
       </c>
       <c r="N212" s="128">
-        <f t="shared" ref="N212:Q212" si="109">N210-N211</f>
+        <f t="shared" ref="N212:Q212" si="126">N210-N211</f>
         <v>56500</v>
       </c>
       <c r="O212" s="128">
-        <f t="shared" si="109"/>
+        <f t="shared" si="126"/>
         <v>81800</v>
       </c>
       <c r="P212" s="128">
-        <f t="shared" si="109"/>
+        <f t="shared" si="126"/>
         <v>107200</v>
       </c>
       <c r="Q212" s="128">
-        <f t="shared" si="109"/>
+        <f t="shared" si="126"/>
         <v>120900</v>
       </c>
       <c r="T212" s="128">
-        <f t="shared" ref="T212" si="110">T210-T211</f>
+        <f t="shared" ref="T212" si="127">T210-T211</f>
         <v>95600</v>
       </c>
       <c r="U212" s="128">
-        <f t="shared" ref="U212" si="111">U210-U211</f>
+        <f t="shared" ref="U212" si="128">U210-U211</f>
         <v>104500</v>
       </c>
       <c r="V212" s="128">
-        <f t="shared" ref="V212" si="112">V210-V211</f>
+        <f t="shared" ref="V212" si="129">V210-V211</f>
         <v>107200</v>
       </c>
       <c r="W212" s="128">
-        <f t="shared" ref="W212" si="113">W210-W211</f>
+        <f t="shared" ref="W212" si="130">W210-W211</f>
         <v>119900</v>
       </c>
       <c r="X212" s="128">
-        <f t="shared" ref="X212" si="114">X210-X211</f>
+        <f t="shared" ref="X212" si="131">X210-X211</f>
         <v>117400</v>
       </c>
       <c r="Y212" s="128">
-        <f t="shared" ref="Y212" si="115">Y210-Y211</f>
+        <f t="shared" ref="Y212" si="132">Y210-Y211</f>
         <v>123800</v>
       </c>
       <c r="Z212" s="128">
-        <f t="shared" ref="Z212" si="116">Z210-Z211</f>
+        <f t="shared" ref="Z212" si="133">Z210-Z211</f>
         <v>120900</v>
       </c>
       <c r="AA212" s="128">
-        <f t="shared" ref="AA212:AC212" si="117">AA210-AA211</f>
+        <f t="shared" ref="AA212" si="134">AA210-AA211</f>
         <v>125300</v>
       </c>
       <c r="AC212" s="21">
-        <f t="shared" si="108"/>
+        <f t="shared" si="125"/>
         <v>125300</v>
       </c>
     </row>
     <row r="213" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B213" s="249" t="s">
+      <c r="B213" s="231" t="s">
         <v>391</v>
       </c>
-      <c r="M213" s="250">
+      <c r="M213" s="232">
         <f>M183/M211</f>
         <v>72.279200000000003</v>
       </c>
-      <c r="N213" s="250">
-        <f t="shared" ref="N213:Q213" si="118">N183/N211</f>
+      <c r="N213" s="232">
+        <f t="shared" ref="N213:Q213" si="135">N183/N211</f>
         <v>65.120714285714286</v>
       </c>
-      <c r="O213" s="250">
-        <f t="shared" si="118"/>
+      <c r="O213" s="232">
+        <f t="shared" si="135"/>
         <v>61.315757575757573</v>
       </c>
-      <c r="P213" s="250">
-        <f t="shared" si="118"/>
+      <c r="P213" s="232">
+        <f t="shared" si="135"/>
         <v>63.950631578947366</v>
       </c>
-      <c r="Q213" s="250">
-        <f t="shared" si="118"/>
+      <c r="Q213" s="232">
+        <f t="shared" si="135"/>
         <v>71.593606557377043</v>
       </c>
-      <c r="T213" s="250">
-        <f t="shared" ref="T213:AC213" si="119">T183/T211</f>
+      <c r="T213" s="232">
+        <f t="shared" ref="T213:AC213" si="136">T183/T211</f>
         <v>17.988624999999999</v>
       </c>
-      <c r="U213" s="250">
-        <f t="shared" si="119"/>
+      <c r="U213" s="232">
+        <f t="shared" si="136"/>
         <v>18.327558139534883</v>
       </c>
-      <c r="V213" s="250">
-        <f t="shared" si="119"/>
+      <c r="V213" s="232">
+        <f t="shared" si="136"/>
         <v>18.349157894736841</v>
       </c>
-      <c r="W213" s="250">
-        <f t="shared" si="119"/>
+      <c r="W213" s="232">
+        <f t="shared" si="136"/>
         <v>18.542427184466021</v>
       </c>
-      <c r="X213" s="250">
-        <f t="shared" si="119"/>
+      <c r="X213" s="232">
+        <f t="shared" si="136"/>
         <v>19.328256880733946</v>
       </c>
-      <c r="Y213" s="250">
-        <f t="shared" si="119"/>
+      <c r="Y213" s="232">
+        <f t="shared" si="136"/>
         <v>19.955739130434782</v>
       </c>
-      <c r="Z213" s="250">
-        <f t="shared" si="119"/>
+      <c r="Z213" s="232">
+        <f t="shared" si="136"/>
         <v>19.859508196721311</v>
       </c>
-      <c r="AA213" s="250">
-        <f t="shared" si="119"/>
+      <c r="AA213" s="232">
+        <f t="shared" si="136"/>
         <v>20.07264</v>
       </c>
-      <c r="AC213" s="250">
-        <f t="shared" si="119"/>
+      <c r="AC213" s="232">
+        <f t="shared" si="136"/>
         <v>74.669039999999995</v>
       </c>
     </row>
     <row r="214" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B214" s="249" t="s">
+      <c r="B214" s="231" t="s">
         <v>392</v>
       </c>
       <c r="M214" s="74">
@@ -35164,51 +35164,51 @@
         <v>0.23703703703703705</v>
       </c>
       <c r="N214" s="74">
-        <f t="shared" ref="N214:Q214" si="120">N209/N210</f>
+        <f t="shared" ref="N214:Q214" si="137">N209/N210</f>
         <v>0.26853377265238881</v>
       </c>
       <c r="O214" s="74">
-        <f t="shared" si="120"/>
+        <f t="shared" si="137"/>
         <v>0.30429864253393663</v>
       </c>
       <c r="P214" s="74">
-        <f t="shared" si="120"/>
+        <f t="shared" si="137"/>
         <v>0.34704370179948585</v>
       </c>
       <c r="Q214" s="74">
-        <f t="shared" si="120"/>
+        <f t="shared" si="137"/>
         <v>0.3959429000751315</v>
       </c>
       <c r="T214" s="74">
-        <f t="shared" ref="T214:AC214" si="121">T209/T210</f>
+        <f t="shared" ref="T214:AA214" si="138">T209/T210</f>
         <v>0.32915057915057916</v>
       </c>
       <c r="U214" s="74">
-        <f t="shared" si="121"/>
+        <f t="shared" si="138"/>
         <v>0.32891246684350134</v>
       </c>
       <c r="V214" s="74">
-        <f t="shared" si="121"/>
+        <f t="shared" si="138"/>
         <v>0.34704370179948585</v>
       </c>
       <c r="W214" s="74">
-        <f t="shared" si="121"/>
+        <f t="shared" si="138"/>
         <v>0.3579109062980031</v>
       </c>
       <c r="X214" s="74">
-        <f t="shared" si="121"/>
+        <f t="shared" si="138"/>
         <v>0.37178487918939984</v>
       </c>
       <c r="Y214" s="74">
-        <f t="shared" si="121"/>
+        <f t="shared" si="138"/>
         <v>0.37324464153732445</v>
       </c>
       <c r="Z214" s="74">
-        <f t="shared" si="121"/>
+        <f t="shared" si="138"/>
         <v>0.3959429000751315</v>
       </c>
       <c r="AA214" s="74">
-        <f t="shared" si="121"/>
+        <f t="shared" si="138"/>
         <v>0.41001451378809867</v>
       </c>
       <c r="AC214" s="74">
@@ -35217,7 +35217,7 @@
       </c>
     </row>
     <row r="215" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B215" s="249" t="s">
+      <c r="B215" s="231" t="s">
         <v>393</v>
       </c>
       <c r="M215" s="74">
@@ -35225,51 +35225,51 @@
         <v>6.1728395061728392E-2</v>
       </c>
       <c r="N215" s="74">
-        <f t="shared" ref="N215:Q215" si="122">N211/N210</f>
+        <f t="shared" ref="N215:Q215" si="139">N211/N210</f>
         <v>6.919275123558484E-2</v>
       </c>
       <c r="O215" s="74">
-        <f t="shared" si="122"/>
+        <f t="shared" si="139"/>
         <v>7.4660633484162894E-2</v>
       </c>
       <c r="P215" s="74">
-        <f t="shared" si="122"/>
+        <f t="shared" si="139"/>
         <v>8.1405312767780638E-2</v>
       </c>
       <c r="Q215" s="74">
-        <f t="shared" si="122"/>
+        <f t="shared" si="139"/>
         <v>9.1660405709992482E-2</v>
       </c>
       <c r="T215" s="74">
-        <f t="shared" ref="T215:AC215" si="123">T211/T210</f>
+        <f t="shared" ref="T215:AA215" si="140">T211/T210</f>
         <v>7.7220077220077218E-2</v>
       </c>
       <c r="U215" s="74">
-        <f t="shared" si="123"/>
+        <f t="shared" si="140"/>
         <v>7.6038903625110524E-2</v>
       </c>
       <c r="V215" s="74">
-        <f t="shared" si="123"/>
+        <f t="shared" si="140"/>
         <v>8.1405312767780638E-2</v>
       </c>
       <c r="W215" s="74">
-        <f t="shared" si="123"/>
+        <f t="shared" si="140"/>
         <v>7.9109062980030717E-2</v>
       </c>
       <c r="X215" s="74">
-        <f t="shared" si="123"/>
+        <f t="shared" si="140"/>
         <v>8.4957131722525336E-2</v>
       </c>
       <c r="Y215" s="74">
-        <f t="shared" si="123"/>
+        <f t="shared" si="140"/>
         <v>8.4996304508499626E-2</v>
       </c>
       <c r="Z215" s="74">
-        <f t="shared" si="123"/>
+        <f t="shared" si="140"/>
         <v>9.1660405709992482E-2</v>
       </c>
       <c r="AA215" s="74">
-        <f t="shared" si="123"/>
+        <f t="shared" si="140"/>
         <v>9.071117561683599E-2</v>
       </c>
       <c r="AC215" s="74">
@@ -35278,7 +35278,7 @@
       </c>
     </row>
     <row r="216" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B216" s="249" t="s">
+      <c r="B216" s="231" t="s">
         <v>394</v>
       </c>
       <c r="M216" s="65">
@@ -35286,60 +35286,60 @@
         <v>1.0131842105263158</v>
       </c>
       <c r="N216" s="65">
-        <f t="shared" ref="N216:Q216" si="124">N184/N212</f>
+        <f t="shared" ref="N216:Q216" si="141">N184/N212</f>
         <v>0.79169911504424784</v>
       </c>
       <c r="O216" s="65">
-        <f t="shared" si="124"/>
+        <f t="shared" si="141"/>
         <v>0.60951100244498779</v>
       </c>
       <c r="P216" s="65">
-        <f t="shared" si="124"/>
+        <f t="shared" si="141"/>
         <v>0.51219216417910451</v>
       </c>
       <c r="Q216" s="65">
-        <f t="shared" si="124"/>
+        <f t="shared" si="141"/>
         <v>0.65942928039702231</v>
       </c>
       <c r="T216" s="65">
-        <f t="shared" ref="T216:AC216" si="125">T184/T212</f>
+        <f t="shared" ref="T216:AC216" si="142">T184/T212</f>
         <v>0.13868200836820083</v>
       </c>
       <c r="U216" s="65">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>0.13784688995215311</v>
       </c>
       <c r="V216" s="65">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>0.13332089552238807</v>
       </c>
       <c r="W216" s="65">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>0.14914095079232695</v>
       </c>
       <c r="X216" s="65">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>0.17549403747870529</v>
       </c>
       <c r="Y216" s="65">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>0.16978190630048465</v>
       </c>
       <c r="Z216" s="65">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>0.1672539288668321</v>
       </c>
       <c r="AA216" s="65">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>0.1645171588188348</v>
       </c>
       <c r="AC216" s="65">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>0.65807661612130885</v>
       </c>
     </row>
     <row r="217" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B217" s="249" t="s">
+      <c r="B217" s="231" t="s">
         <v>395</v>
       </c>
       <c r="M217" s="74">
@@ -35347,55 +35347,55 @@
         <v>0.72031250000000002</v>
       </c>
       <c r="N217" s="74">
-        <f t="shared" ref="N217:Q217" si="126">N186/N209</f>
+        <f t="shared" ref="N217:Q217" si="143">N186/N209</f>
         <v>1.1373619631901841</v>
       </c>
       <c r="O217" s="74">
-        <f t="shared" si="126"/>
+        <f t="shared" si="143"/>
         <v>1.2889591078066915</v>
       </c>
       <c r="P217" s="74">
-        <f t="shared" si="126"/>
+        <f t="shared" si="143"/>
         <v>0.95439506172839506</v>
       </c>
       <c r="Q217" s="74">
-        <f t="shared" si="126"/>
+        <f t="shared" si="143"/>
         <v>0.76810246679316885</v>
       </c>
       <c r="T217" s="74">
-        <f t="shared" ref="T217:AC217" si="127">T186/T209</f>
+        <f t="shared" ref="T217:AC217" si="144">T186/T209</f>
         <v>0.29841642228739002</v>
       </c>
       <c r="U217" s="74">
-        <f t="shared" si="127"/>
+        <f t="shared" si="144"/>
         <v>0.25298387096774194</v>
       </c>
       <c r="V217" s="74">
-        <f t="shared" si="127"/>
+        <f t="shared" si="144"/>
         <v>0.2257283950617284</v>
       </c>
       <c r="W217" s="74">
-        <f t="shared" si="127"/>
+        <f t="shared" si="144"/>
         <v>0.20261802575107296</v>
       </c>
       <c r="X217" s="74">
-        <f t="shared" si="127"/>
+        <f t="shared" si="144"/>
         <v>0.21781970649895177</v>
       </c>
       <c r="Y217" s="74">
-        <f t="shared" si="127"/>
+        <f t="shared" si="144"/>
         <v>0.21972277227722772</v>
       </c>
       <c r="Z217" s="74">
-        <f t="shared" si="127"/>
+        <f t="shared" si="144"/>
         <v>0.18123339658444024</v>
       </c>
       <c r="AA217" s="74">
-        <f t="shared" si="127"/>
+        <f t="shared" si="144"/>
         <v>0.14948672566371682</v>
       </c>
       <c r="AC217" s="74">
-        <f t="shared" si="127"/>
+        <f t="shared" si="144"/>
         <v>0.69881415929203539</v>
       </c>
     </row>
@@ -35469,15 +35469,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="254" t="s">
         <v>242</v>
       </c>
-      <c r="C4" s="230"/>
-      <c r="E4" s="230" t="s">
+      <c r="C4" s="254"/>
+      <c r="E4" s="254" t="s">
         <v>249</v>
       </c>
-      <c r="F4" s="230"/>
-      <c r="G4" s="230"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35485,7 +35485,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>127.25</v>
+        <v>119.94</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>6208145.75</v>
+        <v>5851512.7800000003</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>4816324.75</v>
+        <v>4459691.78</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35541,7 +35541,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>37.530264782647187</v>
+        <v>35.374302224209849</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>252</v>
@@ -35561,7 +35561,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>5.6585115991708514</v>
+        <v>5.3334528974817434</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>253</v>
@@ -35581,7 +35581,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>4.2600320528480404</v>
+        <v>4.0153103687119369</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35601,7 +35601,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.3832069241991132</v>
+        <v>4.0586449013617427</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35610,18 +35610,18 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>30.774648089812974</v>
+        <v>28.495886852009228</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="230" t="s">
+      <c r="B15" s="254" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="230"/>
-      <c r="E15" s="230" t="s">
+      <c r="C15" s="254"/>
+      <c r="E15" s="254" t="s">
         <v>255</v>
       </c>
-      <c r="F15" s="230"/>
+      <c r="F15" s="254"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35672,14 +35672,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="230" t="s">
+      <c r="B21" s="254" t="s">
         <v>254</v>
       </c>
-      <c r="C21" s="230"/>
-      <c r="E21" s="230" t="s">
+      <c r="C21" s="254"/>
+      <c r="E21" s="254" t="s">
         <v>258</v>
       </c>
-      <c r="F21" s="230"/>
+      <c r="F21" s="254"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35748,14 +35748,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="230" t="s">
+      <c r="B29" s="254" t="s">
         <v>259</v>
       </c>
-      <c r="C29" s="230"/>
-      <c r="E29" s="230" t="s">
+      <c r="C29" s="254"/>
+      <c r="E29" s="254" t="s">
         <v>265</v>
       </c>
-      <c r="F29" s="230"/>
+      <c r="F29" s="254"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35831,14 +35831,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="230" t="s">
+      <c r="B37" s="254" t="s">
         <v>277</v>
       </c>
-      <c r="C37" s="230"/>
-      <c r="E37" s="230" t="s">
+      <c r="C37" s="254"/>
+      <c r="E37" s="254" t="s">
         <v>280</v>
       </c>
-      <c r="F37" s="230"/>
+      <c r="F37" s="254"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35846,7 +35846,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.6645162398704111E-2</v>
+        <v>2.8269108848049843E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>279</v>
@@ -35862,7 +35862,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC157</f>
-        <v>4.2546037196372205E-2</v>
+        <v>4.513909649189897E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>281</v>
@@ -35894,7 +35894,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>3.9192056662007329E-3</v>
+        <v>4.1580700435554716E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35903,18 +35903,18 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>3.9192056662007329E-3</v>
+        <v>4.1580700435554716E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="230" t="s">
+      <c r="B45" s="254" t="s">
         <v>288</v>
       </c>
-      <c r="C45" s="230"/>
-      <c r="E45" s="230" t="s">
+      <c r="C45" s="254"/>
+      <c r="E45" s="254" t="s">
         <v>294</v>
       </c>
-      <c r="F45" s="230"/>
+      <c r="F45" s="254"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35947,18 +35947,18 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC172</f>
-        <v>0.22419270681587977</v>
+        <v>0.23785661115825163</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="230" t="s">
+      <c r="B51" s="254" t="s">
         <v>291</v>
       </c>
-      <c r="C51" s="230"/>
-      <c r="E51" s="230" t="s">
+      <c r="C51" s="254"/>
+      <c r="E51" s="254" t="s">
         <v>312</v>
       </c>
-      <c r="F51" s="230"/>
+      <c r="F51" s="254"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36126,7 +36126,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>127.25</v>
+        <v>119.94</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36155,7 +36155,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>6208145.75</v>
+        <v>5851512.7800000003</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36184,7 +36184,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>4816324.75</v>
+        <v>4459691.78</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>37.530264782647187</v>
+        <v>35.374302224209849</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36242,7 +36242,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>5.6585115991708514</v>
+        <v>5.3334528974817434</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36271,7 +36271,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>4.2600320528480404</v>
+        <v>4.0153103687119369</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36300,7 +36300,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.3832069241991132</v>
+        <v>4.0586449013617427</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36329,7 +36329,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>30.774648089812974</v>
+        <v>28.495886852009228</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37102,7 +37102,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.6645162398704111E-2</v>
+        <v>2.8269108848049843E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37131,7 +37131,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC157</f>
-        <v>4.2546037196372205E-2</v>
+        <v>4.513909649189897E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37189,7 +37189,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>3.9192056662007329E-3</v>
+        <v>4.1580700435554716E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37218,7 +37218,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>3.9192056662007329E-3</v>
+        <v>4.1580700435554716E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC172</f>
-        <v>0.22419270681587977</v>
+        <v>0.23785661115825163</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37997,14 +37997,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="257" t="s">
         <v>322</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="F3" s="236" t="s">
+      <c r="D3" s="258"/>
+      <c r="F3" s="259" t="s">
         <v>323</v>
       </c>
-      <c r="G3" s="235"/>
+      <c r="G3" s="258"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38071,19 +38071,19 @@
       <c r="B7" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C7" s="237">
+      <c r="C7" s="255">
         <f>Statement!AA89</f>
         <v>3.2166947127281985E-2</v>
       </c>
-      <c r="D7" s="238"/>
-      <c r="F7" s="237">
+      <c r="D7" s="256"/>
+      <c r="F7" s="255">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.26533415964948015</v>
       </c>
-      <c r="G7" s="238"/>
+      <c r="G7" s="256"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -38110,19 +38110,19 @@
       <c r="B9" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C9" s="237">
+      <c r="C9" s="255">
         <f>Statement!AA90</f>
         <v>2.4312004052000676E-2</v>
       </c>
-      <c r="D9" s="238"/>
-      <c r="F9" s="237">
+      <c r="D9" s="256"/>
+      <c r="F9" s="255">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.18341410716161269</v>
       </c>
-      <c r="G9" s="238"/>
+      <c r="G9" s="256"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -38149,19 +38149,19 @@
       <c r="B11" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C11" s="237">
+      <c r="C11" s="255">
         <f>Statement!AA91</f>
         <v>3.5104848228727975E-2</v>
       </c>
-      <c r="D11" s="238"/>
-      <c r="F11" s="237">
+      <c r="D11" s="256"/>
+      <c r="F11" s="255">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.29860569422776911</v>
       </c>
-      <c r="G11" s="238"/>
+      <c r="G11" s="256"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -38188,19 +38188,19 @@
       <c r="B13" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C13" s="237">
+      <c r="C13" s="255">
         <f>Statement!AA95</f>
         <v>3.7890588923436871E-2</v>
       </c>
-      <c r="D13" s="238"/>
-      <c r="F13" s="237">
+      <c r="D13" s="256"/>
+      <c r="F13" s="255">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.19976228096397206</v>
       </c>
-      <c r="G13" s="238"/>
+      <c r="G13" s="256"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -38227,19 +38227,19 @@
       <c r="B15" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C15" s="237">
+      <c r="C15" s="255">
         <f>Statement!AA96</f>
         <v>2.4692778570442307E-2</v>
       </c>
-      <c r="D15" s="238"/>
-      <c r="F15" s="237">
+      <c r="D15" s="256"/>
+      <c r="F15" s="255">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.88721708909044672</v>
       </c>
-      <c r="G15" s="238"/>
+      <c r="G15" s="256"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -38266,19 +38266,19 @@
       <c r="B17" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C17" s="237">
+      <c r="C17" s="255">
         <f>Statement!AA98</f>
         <v>3.5896458025456456E-2</v>
       </c>
-      <c r="D17" s="238"/>
-      <c r="F17" s="237">
+      <c r="D17" s="256"/>
+      <c r="F17" s="255">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.23694321901238083</v>
       </c>
-      <c r="G17" s="238"/>
+      <c r="G17" s="256"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -38305,22 +38305,22 @@
       <c r="B19" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C19" s="237">
+      <c r="C19" s="255">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3895378744883068E-2</v>
       </c>
-      <c r="D19" s="238"/>
-      <c r="F19" s="237">
+      <c r="D19" s="256"/>
+      <c r="F19" s="255">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.0103717755737469E-2</v>
       </c>
-      <c r="G19" s="238"/>
+      <c r="G19" s="256"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -38347,22 +38347,22 @@
       <c r="B21" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C21" s="237">
+      <c r="C21" s="255">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.4953901558794477E-2</v>
       </c>
-      <c r="D21" s="238"/>
-      <c r="F21" s="237">
+      <c r="D21" s="256"/>
+      <c r="F21" s="255">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.23611111111111119</v>
       </c>
-      <c r="G21" s="238"/>
+      <c r="G21" s="256"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38411,22 +38411,22 @@
       <c r="B25" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C25" s="237">
+      <c r="C25" s="255">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>3.5586042940987099E-2</v>
       </c>
-      <c r="D25" s="238"/>
-      <c r="F25" s="237">
+      <c r="D25" s="256"/>
+      <c r="F25" s="255">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.3137438673836439</v>
       </c>
-      <c r="G25" s="238"/>
+      <c r="G25" s="256"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38454,22 +38454,22 @@
       <c r="B27" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C27" s="237">
+      <c r="C27" s="255">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>1.9435240591464318E-2</v>
       </c>
-      <c r="D27" s="238"/>
-      <c r="F27" s="237">
+      <c r="D27" s="256"/>
+      <c r="F27" s="255">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.15277933117100995</v>
       </c>
-      <c r="G27" s="238"/>
+      <c r="G27" s="256"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38497,22 +38497,22 @@
       <c r="B29" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C29" s="237">
+      <c r="C29" s="255">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.10055431294369348</v>
       </c>
-      <c r="D29" s="238"/>
-      <c r="F29" s="237">
+      <c r="D29" s="256"/>
+      <c r="F29" s="255">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-5.581511763724345E-2</v>
       </c>
-      <c r="G29" s="238"/>
+      <c r="G29" s="256"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -38540,22 +38540,22 @@
       <c r="B31" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C31" s="237">
+      <c r="C31" s="255">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.11569469165532405</v>
       </c>
-      <c r="D31" s="238"/>
-      <c r="F31" s="237">
+      <c r="D31" s="256"/>
+      <c r="F31" s="255">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.10548612582080068</v>
       </c>
-      <c r="G31" s="238"/>
+      <c r="G31" s="256"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -38583,22 +38583,22 @@
       <c r="B33" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C33" s="237">
+      <c r="C33" s="255">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.29411764705882354</v>
       </c>
-      <c r="D33" s="238"/>
-      <c r="F33" s="237">
+      <c r="D33" s="256"/>
+      <c r="F33" s="255">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.52914798206278024</v>
       </c>
-      <c r="G33" s="238"/>
+      <c r="G33" s="256"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -38647,22 +38647,22 @@
       <c r="B37" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C37" s="237">
+      <c r="C37" s="255">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>7.2106261859582549E-2</v>
       </c>
-      <c r="D37" s="238"/>
-      <c r="F37" s="237">
+      <c r="D37" s="256"/>
+      <c r="F37" s="255">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.21244635193133046</v>
       </c>
-      <c r="G37" s="238"/>
+      <c r="G37" s="256"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -38690,22 +38690,22 @@
       <c r="B39" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C39" s="237">
+      <c r="C39" s="255">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>3.5311795642374154E-2</v>
       </c>
-      <c r="D39" s="238"/>
-      <c r="F39" s="237">
+      <c r="D39" s="256"/>
+      <c r="F39" s="255">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>5.8371735791090631E-2</v>
       </c>
-      <c r="G39" s="238"/>
+      <c r="G39" s="256"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -38733,22 +38733,22 @@
       <c r="B41" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C41" s="237">
+      <c r="C41" s="255">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>2.4590163934426229E-2</v>
       </c>
-      <c r="D41" s="238"/>
-      <c r="F41" s="237">
+      <c r="D41" s="256"/>
+      <c r="F41" s="255">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.21359223300970873</v>
       </c>
-      <c r="G41" s="238"/>
+      <c r="G41" s="256"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -38776,41 +38776,41 @@
       <c r="B43" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C43" s="237">
+      <c r="C43" s="255">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>3.6393713813068655E-2</v>
       </c>
-      <c r="D43" s="238"/>
-      <c r="F43" s="237">
+      <c r="D43" s="256"/>
+      <c r="F43" s="255">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>4.5037531276063386E-2</v>
       </c>
-      <c r="G43" s="238"/>
+      <c r="G43" s="256"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
         <f>Statement!B213</f>
         <v>Average revenue per paid user</v>
       </c>
-      <c r="C44" s="251">
+      <c r="C44" s="233">
         <f>Statement!Z213</f>
         <v>19.859508196721311</v>
       </c>
-      <c r="D44" s="251">
+      <c r="D44" s="233">
         <f>Statement!AA213</f>
         <v>20.07264</v>
       </c>
-      <c r="F44" s="251">
+      <c r="F44" s="233">
         <f>Statement!W213</f>
         <v>18.542427184466021</v>
       </c>
-      <c r="G44" s="252">
+      <c r="G44" s="234">
         <f>Statement!AA213</f>
         <v>20.07264</v>
       </c>
@@ -38819,41 +38819,41 @@
       <c r="B45" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C45" s="237">
+      <c r="C45" s="255">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.0731977910403413E-2</v>
       </c>
-      <c r="D45" s="238"/>
-      <c r="F45" s="237">
+      <c r="D45" s="256"/>
+      <c r="F45" s="255">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>8.2524946724122472E-2</v>
       </c>
-      <c r="G45" s="238"/>
+      <c r="G45" s="256"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
         <f>Statement!B214</f>
         <v>DAU to MAU ratio</v>
       </c>
-      <c r="C46" s="253">
+      <c r="C46" s="235">
         <f>Statement!Z214</f>
         <v>0.3959429000751315</v>
       </c>
-      <c r="D46" s="253">
+      <c r="D46" s="235">
         <f>Statement!AA214</f>
         <v>0.41001451378809867</v>
       </c>
-      <c r="F46" s="253">
+      <c r="F46" s="235">
         <f>Statement!W214</f>
         <v>0.3579109062980031</v>
       </c>
-      <c r="G46" s="254">
+      <c r="G46" s="236">
         <f>Statement!AA214</f>
         <v>0.41001451378809867</v>
       </c>
@@ -38862,41 +38862,41 @@
       <c r="B47" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C47" s="237">
+      <c r="C47" s="255">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>3.5539502565387668E-2</v>
       </c>
-      <c r="D47" s="238"/>
-      <c r="F47" s="237">
+      <c r="D47" s="256"/>
+      <c r="F47" s="255">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.14557703208606101</v>
       </c>
-      <c r="G47" s="238"/>
+      <c r="G47" s="256"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
         <f>Statement!B215</f>
         <v>Subscribers to MAU ratio</v>
       </c>
-      <c r="C48" s="253">
+      <c r="C48" s="235">
         <f>Statement!Z215</f>
         <v>9.1660405709992482E-2</v>
       </c>
-      <c r="D48" s="253">
+      <c r="D48" s="235">
         <f>Statement!AA215</f>
         <v>9.071117561683599E-2</v>
       </c>
-      <c r="F48" s="253">
+      <c r="F48" s="235">
         <f>Statement!W215</f>
         <v>7.9109062980030717E-2</v>
       </c>
-      <c r="G48" s="254">
+      <c r="G48" s="236">
         <f>Statement!AA215</f>
         <v>9.071117561683599E-2</v>
       </c>
@@ -38905,41 +38905,41 @@
       <c r="B49" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C49" s="237">
+      <c r="C49" s="255">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-1.0355944704846643E-2</v>
       </c>
-      <c r="D49" s="238"/>
-      <c r="F49" s="237">
+      <c r="D49" s="256"/>
+      <c r="F49" s="255">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>0.14665971507883949</v>
       </c>
-      <c r="G49" s="238"/>
+      <c r="G49" s="256"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
         <f>Statement!B216</f>
         <v>Ad revenue per free user</v>
       </c>
-      <c r="C50" s="255">
+      <c r="C50" s="237">
         <f>Statement!Z216</f>
         <v>0.1672539288668321</v>
       </c>
-      <c r="D50" s="255">
+      <c r="D50" s="237">
         <f>Statement!AA216</f>
         <v>0.1645171588188348</v>
       </c>
-      <c r="F50" s="255">
+      <c r="F50" s="237">
         <f>Statement!W216</f>
         <v>0.14914095079232695</v>
       </c>
-      <c r="G50" s="256">
+      <c r="G50" s="238">
         <f>Statement!AA216</f>
         <v>0.1645171588188348</v>
       </c>
@@ -38948,41 +38948,41 @@
       <c r="B51" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C51" s="237">
+      <c r="C51" s="255">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>-1.63629641858896E-2</v>
       </c>
-      <c r="D51" s="238"/>
-      <c r="F51" s="237">
+      <c r="D51" s="256"/>
+      <c r="F51" s="255">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>0.10309849806387941</v>
       </c>
-      <c r="G51" s="238"/>
+      <c r="G51" s="256"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
         <f>Statement!B217</f>
         <v>In-app purchases % of DAU</v>
       </c>
-      <c r="C52" s="253">
+      <c r="C52" s="235">
         <f>Statement!Z217</f>
         <v>0.18123339658444024</v>
       </c>
-      <c r="D52" s="253">
+      <c r="D52" s="235">
         <f>Statement!AA217</f>
         <v>0.14948672566371682</v>
       </c>
-      <c r="F52" s="253">
+      <c r="F52" s="235">
         <f>Statement!W217</f>
         <v>0.20261802575107296</v>
       </c>
-      <c r="G52" s="254">
+      <c r="G52" s="236">
         <f>Statement!AA217</f>
         <v>0.14948672566371682</v>
       </c>
@@ -38991,39 +38991,43 @@
       <c r="B53" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C53" s="237">
+      <c r="C53" s="255">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-0.17517009292452351</v>
       </c>
-      <c r="D53" s="238"/>
-      <c r="F53" s="237">
+      <c r="D53" s="256"/>
+      <c r="F53" s="255">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.26222395510175772</v>
       </c>
-      <c r="G53" s="238"/>
+      <c r="G53" s="256"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39038,24 +39042,20 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E59ABC-2DF0-2449-8BBC-DD79604B782C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644F0E39-7884-974E-9AB5-AC9069C56E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -13017,11 +13017,11 @@
     <v>Powered by Refinitiv</v>
     <v>468</v>
     <v>87.89</v>
-    <v>0.82050000000000001</v>
-    <v>-12.21</v>
-    <v>-9.2394999999999991E-2</v>
-    <v>1.5968</v>
-    <v>1.3312999999999998E-2</v>
+    <v>0.87080000000000002</v>
+    <v>4.5449999999999999</v>
+    <v>3.7495000000000001E-2</v>
+    <v>-0.56000000000000005</v>
+    <v>-4.4529999999999995E-3</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13029,25 +13029,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>131.57499999999999</v>
+    <v>126.88</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46198.909386943749</v>
+    <v>46205.99772239531</v>
     <v>0</v>
-    <v>118.87</v>
-    <v>5588378812</v>
+    <v>115.51</v>
+    <v>5859550771</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>131.47999999999999</v>
-    <v>15.294</v>
-    <v>132.15</v>
-    <v>119.94</v>
-    <v>121.5368</v>
+    <v>119.99</v>
+    <v>14.028499999999999</v>
+    <v>121.215</v>
+    <v>125.76</v>
+    <v>125.2</v>
     <v>46593120</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>1734040</v>
-    <v>1479800</v>
+    <v>1002431</v>
+    <v>1530289</v>
     <v>2011</v>
   </rv>
   <rv s="2">
@@ -13071,17 +13071,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.91</v>
-    <v>-2.0253999999999998E-2</v>
+    <v>0.1</v>
+    <v>2.235E-3</v>
     <v>US</v>
-    <v>44.55</v>
+    <v>45.05</v>
     <v>Index</v>
     <v>3</v>
-    <v>43.98</v>
+    <v>44.53</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.53</v>
-    <v>44.93</v>
-    <v>44.02</v>
+    <v>45.03</v>
+    <v>44.75</v>
+    <v>44.85</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13303,9 +13303,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13902,7 +13902,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC149</f>
-        <v>5851512.7800000003</v>
+        <v>6135453.1200000001</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -13926,7 +13926,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>4459691.78</v>
+        <v>4743632.12</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -13943,7 +13943,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>119.94</v>
+        <v>125.76</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>252</v>
@@ -13967,14 +13967,14 @@
       </c>
       <c r="C6" s="210" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>121.5368</v>
+        <v>125.2</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>246</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC146</f>
-        <v>35.374302224209849</v>
+        <v>37.090814138040948</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -13991,14 +13991,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-12.21</v>
+        <v>4.5449999999999999</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC147</f>
-        <v>5.3334528974817434</v>
+        <v>5.5922547639428393</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -14015,14 +14015,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>1.5968</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>274</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC157</f>
-        <v>4.513909649189897E-2</v>
+        <v>4.3050121129439907E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.26598475181365988</v>
+        <v>0.20739671702075668</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14039,14 +14039,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-9.2394999999999991E-2</v>
+        <v>3.7495000000000001E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>297</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC158</f>
-        <v>2.8269108848049843E-2</v>
+        <v>2.6960853333612422E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -14055,14 +14055,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.3312999999999998E-2</v>
+        <v>-4.4529999999999995E-3</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>302</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC160</f>
-        <v>4.1580700435554716E-3</v>
+        <v>3.9656402753184107E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.82050000000000001</v>
+        <v>0.87080000000000002</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>104</v>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1479800</v>
+        <v>1530289</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>105</v>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC172</f>
-        <v>0.23785661115825163</v>
+        <v>0.22684893401972567</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.02</v>
+        <v>44.85</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14260,7 +14260,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.4020000000000004E-2</v>
+        <v>4.4850000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -21893,7 +21893,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>119.94</v>
+        <v>125.76</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21902,7 +21902,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>5851512.7800000003</v>
+        <v>6135453.1200000001</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21920,7 +21920,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.4020000000000004E-2</v>
+        <v>4.4850000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>0.82050000000000001</v>
+        <v>0.87080000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21999,7 +21999,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.0942500000000001E-2</v>
+        <v>8.4036E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22008,7 +22008,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.0942500000000001E-2</v>
+        <v>8.4036E-2</v>
       </c>
     </row>
   </sheetData>
@@ -23747,7 +23747,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>119.94</v>
+        <v>125.76</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23756,7 +23756,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.26598475181365988</v>
+        <v>0.20739671702075668</v>
       </c>
     </row>
   </sheetData>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>119.94</v>
+        <v>125.76</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24181,7 +24181,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>5588364.4199999999</v>
+        <v>5859535.6800000006</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>4196543.42</v>
+        <v>4467714.6800000006</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -31356,7 +31356,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>119.94</v>
+        <v>125.76</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31403,7 +31403,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>119.94</v>
+        <v>125.76</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32513,7 +32513,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>35.374302224209849</v>
+        <v>37.090814138040948</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32550,7 +32550,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>5.3334528974817434</v>
+        <v>5.5922547639428393</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32587,7 +32587,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.0153103687119369</v>
+        <v>4.2101503415809001</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32624,7 +32624,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>5851512.7800000003</v>
+        <v>6135453.1200000001</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32661,7 +32661,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="145">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>4459691.78</v>
+        <v>4743632.12</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32698,7 +32698,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="185">
         <f ca="1">AC150/AC5</f>
-        <v>4.0586449013617427</v>
+        <v>4.3170513272049025</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32735,7 +32735,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="185">
         <f ca="1">AC150/AC12</f>
-        <v>28.495886852009228</v>
+        <v>30.31016734503492</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32870,7 +32870,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="98">AC149/AC153</f>
-        <v>22.15374426423152</v>
+        <v>23.228738358093683</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32907,7 +32907,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="98"/>
-        <v>23.871336572525447</v>
+        <v>25.391180489330232</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32944,7 +32944,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="101">AC153/AC149</f>
-        <v>4.513909649189897E-2</v>
+        <v>4.3050121129439907E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -32981,7 +32981,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.8269108848049843E-2</v>
+        <v>2.6960853333612422E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33055,7 +33055,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="156">
         <f ca="1">-AC63/AC149</f>
-        <v>4.1580700435554716E-3</v>
+        <v>3.9656402753184107E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33092,7 +33092,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="156">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>4.1580700435554716E-3</v>
+        <v>3.9656402753184107E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33595,7 +33595,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="156">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.23785661115825163</v>
+        <v>0.22684893401972567</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -35485,7 +35485,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>119.94</v>
+        <v>125.76</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>5851512.7800000003</v>
+        <v>6135453.1200000001</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>4459691.78</v>
+        <v>4743632.12</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35541,7 +35541,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>35.374302224209849</v>
+        <v>37.090814138040948</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>252</v>
@@ -35561,7 +35561,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>5.3334528974817434</v>
+        <v>5.5922547639428393</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>253</v>
@@ -35581,7 +35581,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>4.0153103687119369</v>
+        <v>4.2101503415809001</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35601,7 +35601,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.0586449013617427</v>
+        <v>4.3170513272049025</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35610,7 +35610,7 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>28.495886852009228</v>
+        <v>30.31016734503492</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35846,7 +35846,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.8269108848049843E-2</v>
+        <v>2.6960853333612422E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>279</v>
@@ -35862,7 +35862,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC157</f>
-        <v>4.513909649189897E-2</v>
+        <v>4.3050121129439907E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>281</v>
@@ -35894,7 +35894,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>4.1580700435554716E-3</v>
+        <v>3.9656402753184107E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35903,7 +35903,7 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>4.1580700435554716E-3</v>
+        <v>3.9656402753184107E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -35947,7 +35947,7 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC172</f>
-        <v>0.23785661115825163</v>
+        <v>0.22684893401972567</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -36126,7 +36126,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>119.94</v>
+        <v>125.76</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36155,7 +36155,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>5851512.7800000003</v>
+        <v>6135453.1200000001</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36184,7 +36184,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>4459691.78</v>
+        <v>4743632.12</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>35.374302224209849</v>
+        <v>37.090814138040948</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36242,7 +36242,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>5.3334528974817434</v>
+        <v>5.5922547639428393</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36271,7 +36271,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>4.0153103687119369</v>
+        <v>4.2101503415809001</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36300,7 +36300,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.0586449013617427</v>
+        <v>4.3170513272049025</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36329,7 +36329,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>28.495886852009228</v>
+        <v>30.31016734503492</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37102,7 +37102,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.8269108848049843E-2</v>
+        <v>2.6960853333612422E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37131,7 +37131,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC157</f>
-        <v>4.513909649189897E-2</v>
+        <v>4.3050121129439907E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37189,7 +37189,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>4.1580700435554716E-3</v>
+        <v>3.9656402753184107E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37218,7 +37218,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>4.1580700435554716E-3</v>
+        <v>3.9656402753184107E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC172</f>
-        <v>0.23785661115825163</v>
+        <v>0.22684893401972567</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644F0E39-7884-974E-9AB5-AC9069C56E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7D4504-2662-D449-BE25-BAAAA0741653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2358,6 +2358,9 @@
     <xf numFmtId="2" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2365,15 +2368,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2385,10 +2379,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2398,6 +2392,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -13876,18 +13876,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="251" t="s">
+      <c r="B2" s="252" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="252"/>
-      <c r="E2" s="251" t="s">
+      <c r="C2" s="253"/>
+      <c r="E2" s="252" t="s">
         <v>296</v>
       </c>
-      <c r="F2" s="252"/>
-      <c r="H2" s="251" t="s">
+      <c r="F2" s="253"/>
+      <c r="H2" s="252" t="s">
         <v>338</v>
       </c>
-      <c r="I2" s="252"/>
+      <c r="I2" s="253"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="I3" s="213">
         <f>'AVG target price'!C5</f>
-        <v>130.91279024586424</v>
+        <v>124.42492665170388</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="I6" s="213">
         <f>'AVG target price'!C8</f>
-        <v>178.77179540465104</v>
+        <v>169.62212640275894</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="I7" s="214">
         <f>'AVG target price'!C9</f>
-        <v>151.84221113253037</v>
+        <v>147.93282798351726</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.20739671702075668</v>
+        <v>0.17631065508521987</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14148,10 +14148,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="253" t="s">
+      <c r="B17" s="254" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="253"/>
+      <c r="C17" s="254"/>
       <c r="E17" s="186" t="s">
         <v>305</v>
       </c>
@@ -14224,14 +14224,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="253" t="s">
+      <c r="B25" s="254" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="253"/>
-      <c r="E25" s="251" t="s">
+      <c r="C25" s="254"/>
+      <c r="E25" s="252" t="s">
         <v>353</v>
       </c>
-      <c r="F25" s="252"/>
+      <c r="F25" s="253"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -14280,15 +14280,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="254" t="s">
+      <c r="B33" s="251" t="s">
         <v>348</v>
       </c>
-      <c r="C33" s="254"/>
-      <c r="D33" s="254"/>
-      <c r="E33" s="254"/>
-      <c r="F33" s="254"/>
-      <c r="G33" s="254"/>
-      <c r="H33" s="254"/>
+      <c r="C33" s="251"/>
+      <c r="D33" s="251"/>
+      <c r="E33" s="251"/>
+      <c r="F33" s="251"/>
+      <c r="G33" s="251"/>
+      <c r="H33" s="251"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14307,24 +14307,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="254"/>
-      <c r="C39" s="254"/>
-      <c r="D39" s="254"/>
-      <c r="E39" s="254"/>
-      <c r="F39" s="254"/>
-      <c r="G39" s="254"/>
-      <c r="H39" s="254"/>
+      <c r="B39" s="251"/>
+      <c r="C39" s="251"/>
+      <c r="D39" s="251"/>
+      <c r="E39" s="251"/>
+      <c r="F39" s="251"/>
+      <c r="G39" s="251"/>
+      <c r="H39" s="251"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="254" t="s">
+      <c r="B42" s="251" t="s">
         <v>351</v>
       </c>
-      <c r="C42" s="254"/>
-      <c r="D42" s="254"/>
-      <c r="E42" s="254"/>
-      <c r="F42" s="254"/>
-      <c r="G42" s="254"/>
-      <c r="H42" s="254"/>
+      <c r="C42" s="251"/>
+      <c r="D42" s="251"/>
+      <c r="E42" s="251"/>
+      <c r="F42" s="251"/>
+      <c r="G42" s="251"/>
+      <c r="H42" s="251"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14339,24 +14339,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="254"/>
-      <c r="C49" s="254"/>
-      <c r="D49" s="254"/>
-      <c r="E49" s="254"/>
-      <c r="F49" s="254"/>
-      <c r="G49" s="254"/>
-      <c r="H49" s="254"/>
+      <c r="B49" s="251"/>
+      <c r="C49" s="251"/>
+      <c r="D49" s="251"/>
+      <c r="E49" s="251"/>
+      <c r="F49" s="251"/>
+      <c r="G49" s="251"/>
+      <c r="H49" s="251"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="254" t="s">
+      <c r="B52" s="251" t="s">
         <v>109</v>
       </c>
-      <c r="C52" s="254"/>
-      <c r="D52" s="254"/>
-      <c r="E52" s="254"/>
-      <c r="F52" s="254"/>
-      <c r="G52" s="254"/>
-      <c r="H52" s="254"/>
+      <c r="C52" s="251"/>
+      <c r="D52" s="251"/>
+      <c r="E52" s="251"/>
+      <c r="F52" s="251"/>
+      <c r="G52" s="251"/>
+      <c r="H52" s="251"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="41" t="s">
@@ -14427,28 +14427,28 @@
       </c>
     </row>
     <row r="65" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="254"/>
-      <c r="C65" s="254"/>
-      <c r="D65" s="254"/>
-      <c r="E65" s="254"/>
-      <c r="F65" s="254"/>
-      <c r="G65" s="254"/>
-      <c r="H65" s="254"/>
+      <c r="B65" s="251"/>
+      <c r="C65" s="251"/>
+      <c r="D65" s="251"/>
+      <c r="E65" s="251"/>
+      <c r="F65" s="251"/>
+      <c r="G65" s="251"/>
+      <c r="H65" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B65:H65"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14518,36 +14518,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="251" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="251"/>
+      <c r="E2" s="251"/>
+      <c r="F2" s="251"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
+      <c r="I2" s="251"/>
+      <c r="J2" s="251"/>
+      <c r="K2" s="251"/>
+      <c r="L2" s="251"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="254" t="s">
+      <c r="S2" s="251" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="254"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="254"/>
-      <c r="W2" s="254"/>
-      <c r="X2" s="254"/>
-      <c r="Y2" s="254"/>
-      <c r="Z2" s="254"/>
-      <c r="AA2" s="254" t="s">
+      <c r="T2" s="251"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="251"/>
+      <c r="W2" s="251"/>
+      <c r="X2" s="251"/>
+      <c r="Y2" s="251"/>
+      <c r="Z2" s="251"/>
+      <c r="AA2" s="251" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="254"/>
-      <c r="AC2" s="254"/>
+      <c r="AB2" s="251"/>
+      <c r="AC2" s="251"/>
       <c r="AE2" s="86" t="s">
         <v>85</v>
       </c>
@@ -14558,32 +14558,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="260" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="263" t="s">
+      <c r="S4" s="261" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="264"/>
-      <c r="U4" s="264"/>
-      <c r="V4" s="264"/>
-      <c r="W4" s="264"/>
-      <c r="X4" s="264"/>
-      <c r="Y4" s="264"/>
-      <c r="Z4" s="264"/>
-      <c r="AA4" s="264"/>
-      <c r="AB4" s="264"/>
-      <c r="AC4" s="264"/>
+      <c r="T4" s="262"/>
+      <c r="U4" s="262"/>
+      <c r="V4" s="262"/>
+      <c r="W4" s="262"/>
+      <c r="X4" s="262"/>
+      <c r="Y4" s="262"/>
+      <c r="Z4" s="262"/>
+      <c r="AA4" s="262"/>
+      <c r="AB4" s="262"/>
+      <c r="AC4" s="262"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15271,33 +15271,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="262" t="s">
+      <c r="C13" s="260" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="262"/>
-      <c r="E13" s="262"/>
-      <c r="F13" s="262"/>
-      <c r="G13" s="262"/>
-      <c r="H13" s="262"/>
-      <c r="I13" s="262"/>
-      <c r="J13" s="262"/>
-      <c r="K13" s="262"/>
-      <c r="L13" s="262"/>
+      <c r="D13" s="260"/>
+      <c r="E13" s="260"/>
+      <c r="F13" s="260"/>
+      <c r="G13" s="260"/>
+      <c r="H13" s="260"/>
+      <c r="I13" s="260"/>
+      <c r="J13" s="260"/>
+      <c r="K13" s="260"/>
+      <c r="L13" s="260"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="263" t="s">
+      <c r="S13" s="261" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="264"/>
-      <c r="U13" s="264"/>
-      <c r="V13" s="264"/>
-      <c r="W13" s="264"/>
-      <c r="X13" s="264"/>
-      <c r="Y13" s="264"/>
-      <c r="Z13" s="264"/>
-      <c r="AA13" s="264"/>
-      <c r="AB13" s="264"/>
-      <c r="AC13" s="264"/>
+      <c r="T13" s="262"/>
+      <c r="U13" s="262"/>
+      <c r="V13" s="262"/>
+      <c r="W13" s="262"/>
+      <c r="X13" s="262"/>
+      <c r="Y13" s="262"/>
+      <c r="Z13" s="262"/>
+      <c r="AA13" s="262"/>
+      <c r="AB13" s="262"/>
+      <c r="AC13" s="262"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -15906,33 +15906,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="262" t="s">
+      <c r="C23" s="260" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="262"/>
-      <c r="E23" s="262"/>
-      <c r="F23" s="262"/>
-      <c r="G23" s="262"/>
-      <c r="H23" s="262"/>
-      <c r="I23" s="262"/>
-      <c r="J23" s="262"/>
-      <c r="K23" s="262"/>
-      <c r="L23" s="262"/>
+      <c r="D23" s="260"/>
+      <c r="E23" s="260"/>
+      <c r="F23" s="260"/>
+      <c r="G23" s="260"/>
+      <c r="H23" s="260"/>
+      <c r="I23" s="260"/>
+      <c r="J23" s="260"/>
+      <c r="K23" s="260"/>
+      <c r="L23" s="260"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="263" t="s">
+      <c r="S23" s="261" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="264"/>
-      <c r="U23" s="264"/>
-      <c r="V23" s="264"/>
-      <c r="W23" s="264"/>
-      <c r="X23" s="264"/>
-      <c r="Y23" s="264"/>
-      <c r="Z23" s="264"/>
-      <c r="AA23" s="264"/>
-      <c r="AB23" s="264"/>
-      <c r="AC23" s="264"/>
+      <c r="T23" s="262"/>
+      <c r="U23" s="262"/>
+      <c r="V23" s="262"/>
+      <c r="W23" s="262"/>
+      <c r="X23" s="262"/>
+      <c r="Y23" s="262"/>
+      <c r="Z23" s="262"/>
+      <c r="AA23" s="262"/>
+      <c r="AB23" s="262"/>
+      <c r="AC23" s="262"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17251,32 +17251,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="262" t="s">
+      <c r="C40" s="260" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="262"/>
-      <c r="E40" s="262"/>
-      <c r="F40" s="262"/>
-      <c r="G40" s="262"/>
-      <c r="H40" s="262"/>
-      <c r="I40" s="262"/>
-      <c r="J40" s="262"/>
-      <c r="K40" s="262"/>
-      <c r="L40" s="262"/>
+      <c r="D40" s="260"/>
+      <c r="E40" s="260"/>
+      <c r="F40" s="260"/>
+      <c r="G40" s="260"/>
+      <c r="H40" s="260"/>
+      <c r="I40" s="260"/>
+      <c r="J40" s="260"/>
+      <c r="K40" s="260"/>
+      <c r="L40" s="260"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="263" t="s">
+      <c r="S40" s="261" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="264"/>
-      <c r="U40" s="264"/>
-      <c r="V40" s="264"/>
-      <c r="W40" s="264"/>
-      <c r="X40" s="264"/>
-      <c r="Y40" s="264"/>
-      <c r="Z40" s="264"/>
-      <c r="AA40" s="264"/>
-      <c r="AB40" s="264"/>
-      <c r="AC40" s="264"/>
+      <c r="T40" s="262"/>
+      <c r="U40" s="262"/>
+      <c r="V40" s="262"/>
+      <c r="W40" s="262"/>
+      <c r="X40" s="262"/>
+      <c r="Y40" s="262"/>
+      <c r="Z40" s="262"/>
+      <c r="AA40" s="262"/>
+      <c r="AB40" s="262"/>
+      <c r="AC40" s="262"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -17843,18 +17843,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="S13:AC13"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="S23:AC23"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="S40:AC40"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17888,35 +17888,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="251" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="251"/>
+      <c r="E2" s="251"/>
+      <c r="F2" s="251"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
-      <c r="P2" s="254" t="s">
+      <c r="I2" s="251"/>
+      <c r="J2" s="251"/>
+      <c r="K2" s="251"/>
+      <c r="L2" s="251"/>
+      <c r="P2" s="251" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="254"/>
-      <c r="R2" s="254"/>
-      <c r="S2" s="254"/>
-      <c r="T2" s="254"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="254"/>
-      <c r="W2" s="254"/>
-      <c r="X2" s="254" t="s">
+      <c r="Q2" s="251"/>
+      <c r="R2" s="251"/>
+      <c r="S2" s="251"/>
+      <c r="T2" s="251"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="251"/>
+      <c r="W2" s="251"/>
+      <c r="X2" s="251" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="254"/>
-      <c r="Z2" s="254"/>
+      <c r="Y2" s="251"/>
+      <c r="Z2" s="251"/>
       <c r="AB2" s="86" t="s">
         <v>115</v>
       </c>
@@ -17925,31 +17925,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="260" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
-      <c r="P4" s="264" t="s">
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
+      <c r="P4" s="262" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="264"/>
-      <c r="R4" s="264"/>
-      <c r="S4" s="264"/>
-      <c r="T4" s="264"/>
-      <c r="U4" s="264"/>
-      <c r="V4" s="264"/>
-      <c r="W4" s="264"/>
-      <c r="X4" s="264"/>
-      <c r="Y4" s="264"/>
-      <c r="Z4" s="264"/>
+      <c r="Q4" s="262"/>
+      <c r="R4" s="262"/>
+      <c r="S4" s="262"/>
+      <c r="T4" s="262"/>
+      <c r="U4" s="262"/>
+      <c r="V4" s="262"/>
+      <c r="W4" s="262"/>
+      <c r="X4" s="262"/>
+      <c r="Y4" s="262"/>
+      <c r="Z4" s="262"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18144,32 +18144,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="262" t="s">
+      <c r="C9" s="260" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="262"/>
-      <c r="E9" s="262"/>
-      <c r="F9" s="262"/>
-      <c r="G9" s="262"/>
-      <c r="H9" s="262"/>
-      <c r="I9" s="262"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="262"/>
+      <c r="D9" s="260"/>
+      <c r="E9" s="260"/>
+      <c r="F9" s="260"/>
+      <c r="G9" s="260"/>
+      <c r="H9" s="260"/>
+      <c r="I9" s="260"/>
+      <c r="J9" s="260"/>
+      <c r="K9" s="260"/>
+      <c r="L9" s="260"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="264" t="s">
+      <c r="P9" s="262" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="264"/>
-      <c r="R9" s="264"/>
-      <c r="S9" s="264"/>
-      <c r="T9" s="264"/>
-      <c r="U9" s="264"/>
-      <c r="V9" s="264"/>
-      <c r="W9" s="264"/>
-      <c r="X9" s="264"/>
-      <c r="Y9" s="264"/>
-      <c r="Z9" s="264"/>
+      <c r="Q9" s="262"/>
+      <c r="R9" s="262"/>
+      <c r="S9" s="262"/>
+      <c r="T9" s="262"/>
+      <c r="U9" s="262"/>
+      <c r="V9" s="262"/>
+      <c r="W9" s="262"/>
+      <c r="X9" s="262"/>
+      <c r="Y9" s="262"/>
+      <c r="Z9" s="262"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -18739,31 +18739,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="262" t="s">
+      <c r="C18" s="260" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="262"/>
-      <c r="E18" s="262"/>
-      <c r="F18" s="262"/>
-      <c r="G18" s="262"/>
-      <c r="H18" s="262"/>
-      <c r="I18" s="262"/>
-      <c r="J18" s="262"/>
-      <c r="K18" s="262"/>
-      <c r="L18" s="262"/>
-      <c r="P18" s="264" t="s">
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="260"/>
+      <c r="J18" s="260"/>
+      <c r="K18" s="260"/>
+      <c r="L18" s="260"/>
+      <c r="P18" s="262" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="264"/>
-      <c r="R18" s="264"/>
-      <c r="S18" s="264"/>
-      <c r="T18" s="264"/>
-      <c r="U18" s="264"/>
-      <c r="V18" s="264"/>
-      <c r="W18" s="264"/>
-      <c r="X18" s="264"/>
-      <c r="Y18" s="264"/>
-      <c r="Z18" s="264"/>
+      <c r="Q18" s="262"/>
+      <c r="R18" s="262"/>
+      <c r="S18" s="262"/>
+      <c r="T18" s="262"/>
+      <c r="U18" s="262"/>
+      <c r="V18" s="262"/>
+      <c r="W18" s="262"/>
+      <c r="X18" s="262"/>
+      <c r="Y18" s="262"/>
+      <c r="Z18" s="262"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19323,20 +19323,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="251" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="254"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="251"/>
+      <c r="E3" s="251"/>
+      <c r="F3" s="251"/>
+      <c r="G3" s="263"/>
+      <c r="H3" s="264" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="254"/>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
+      <c r="I3" s="251"/>
+      <c r="J3" s="251"/>
+      <c r="K3" s="251"/>
+      <c r="L3" s="251"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -19354,18 +19354,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="262" t="s">
+      <c r="C5" s="260" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="262"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -19562,18 +19562,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="262" t="s">
+      <c r="C11" s="260" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="262"/>
-      <c r="E11" s="262"/>
-      <c r="F11" s="262"/>
-      <c r="G11" s="262"/>
-      <c r="H11" s="262"/>
-      <c r="I11" s="262"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="262"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="260"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="260"/>
+      <c r="L11" s="260"/>
       <c r="N11" s="92"/>
       <c r="P11" s="265"/>
       <c r="Q11" s="265"/>
@@ -19827,18 +19827,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="262" t="s">
+      <c r="C18" s="260" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="262"/>
-      <c r="E18" s="262"/>
-      <c r="F18" s="262"/>
-      <c r="G18" s="262"/>
-      <c r="H18" s="262"/>
-      <c r="I18" s="262"/>
-      <c r="J18" s="262"/>
-      <c r="K18" s="262"/>
-      <c r="L18" s="262"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="260"/>
+      <c r="J18" s="260"/>
+      <c r="K18" s="260"/>
+      <c r="L18" s="260"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20056,18 +20056,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="262" t="s">
+      <c r="C26" s="260" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="262"/>
-      <c r="E26" s="262"/>
-      <c r="F26" s="262"/>
-      <c r="G26" s="262"/>
-      <c r="H26" s="262"/>
-      <c r="I26" s="262"/>
-      <c r="J26" s="262"/>
-      <c r="K26" s="262"/>
-      <c r="L26" s="262"/>
+      <c r="D26" s="260"/>
+      <c r="E26" s="260"/>
+      <c r="F26" s="260"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="260"/>
+      <c r="I26" s="260"/>
+      <c r="J26" s="260"/>
+      <c r="K26" s="260"/>
+      <c r="L26" s="260"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20259,18 +20259,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="262" t="s">
+      <c r="C33" s="260" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="262"/>
-      <c r="E33" s="262"/>
-      <c r="F33" s="262"/>
-      <c r="G33" s="262"/>
-      <c r="H33" s="262"/>
-      <c r="I33" s="262"/>
-      <c r="J33" s="262"/>
-      <c r="K33" s="262"/>
-      <c r="L33" s="262"/>
+      <c r="D33" s="260"/>
+      <c r="E33" s="260"/>
+      <c r="F33" s="260"/>
+      <c r="G33" s="260"/>
+      <c r="H33" s="260"/>
+      <c r="I33" s="260"/>
+      <c r="J33" s="260"/>
+      <c r="K33" s="260"/>
+      <c r="L33" s="260"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20454,18 +20454,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="262" t="s">
+      <c r="C40" s="260" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="262"/>
-      <c r="E40" s="262"/>
-      <c r="F40" s="262"/>
-      <c r="G40" s="262"/>
-      <c r="H40" s="262"/>
-      <c r="I40" s="262"/>
-      <c r="J40" s="262"/>
-      <c r="K40" s="262"/>
-      <c r="L40" s="262"/>
+      <c r="D40" s="260"/>
+      <c r="E40" s="260"/>
+      <c r="F40" s="260"/>
+      <c r="G40" s="260"/>
+      <c r="H40" s="260"/>
+      <c r="I40" s="260"/>
+      <c r="J40" s="260"/>
+      <c r="K40" s="260"/>
+      <c r="L40" s="260"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20603,43 +20603,43 @@
       </c>
       <c r="C44" s="125">
         <f>C42/C45</f>
-        <v>0.7601784718349136</v>
+        <v>0.43925233644859812</v>
       </c>
       <c r="D44" s="125">
         <f t="shared" ref="D44:L44" si="13">D42/D45</f>
-        <v>0.87558432218626392</v>
+        <v>0.48103516396681156</v>
       </c>
       <c r="E44" s="125">
         <f t="shared" si="13"/>
-        <v>2.2234409276089</v>
+        <v>0.51848874598070738</v>
       </c>
       <c r="F44" s="125">
         <f t="shared" si="13"/>
-        <v>0.89584021129085512</v>
+        <v>0.51343424787133396</v>
       </c>
       <c r="G44" s="126">
         <f t="shared" si="13"/>
-        <v>0.79525862068965514</v>
+        <v>0.52523814737764152</v>
       </c>
       <c r="H44" s="125">
         <f t="shared" si="13"/>
-        <v>0.90909090909090917</v>
+        <v>0.39999999999999997</v>
       </c>
       <c r="I44" s="125">
         <f t="shared" si="13"/>
-        <v>0.90909090909090917</v>
+        <v>0.4</v>
       </c>
       <c r="J44" s="125">
         <f t="shared" si="13"/>
-        <v>0.90909090909090917</v>
+        <v>0.39999999999999997</v>
       </c>
       <c r="K44" s="125">
         <f t="shared" si="13"/>
-        <v>0.90909090909090928</v>
+        <v>0.43478260869565222</v>
       </c>
       <c r="L44" s="125">
         <f t="shared" si="13"/>
-        <v>0.90909090909090917</v>
+        <v>0.45454545454545459</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -20647,44 +20647,44 @@
         <v>61</v>
       </c>
       <c r="C45" s="116">
-        <f>-Statement!M60</f>
-        <v>3586</v>
+        <f>-Statement!M110</f>
+        <v>6206</v>
       </c>
       <c r="D45" s="116">
-        <f>-Statement!N60</f>
-        <v>5562</v>
+        <f>-Statement!N110</f>
+        <v>10124</v>
       </c>
       <c r="E45" s="116">
-        <f>-Statement!O60</f>
-        <v>3191</v>
+        <f>-Statement!O110</f>
+        <v>13684</v>
       </c>
       <c r="F45" s="116">
-        <f>-Statement!P60</f>
-        <v>12116</v>
+        <f>-Statement!P110</f>
+        <v>21140</v>
       </c>
       <c r="G45" s="117">
-        <f>-Statement!Q60</f>
-        <v>18096</v>
+        <f>-Statement!Q110</f>
+        <v>27399</v>
       </c>
       <c r="H45" s="25">
         <f>H7*H46</f>
-        <v>13104.854685999997</v>
+        <v>29783.760649999997</v>
       </c>
       <c r="I45" s="25">
         <f>I7*I46</f>
-        <v>14962.206918497517</v>
+        <v>34005.015723857992</v>
       </c>
       <c r="J45" s="25">
         <f>J7*J46</f>
-        <v>18845.960824580088</v>
+        <v>42831.729146772937</v>
       </c>
       <c r="K45" s="25">
         <f>K7*K46</f>
-        <v>25406.518401736928</v>
+        <v>53122.720294540857</v>
       </c>
       <c r="L45" s="25">
         <f>L7*L46</f>
-        <v>34190.20539757669</v>
+        <v>68380.410795153381</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
@@ -20693,48 +20693,42 @@
       </c>
       <c r="C46" s="125">
         <f>C45/C7</f>
-        <v>1.4299842087633389E-2</v>
+        <v>2.474757947458249E-2</v>
       </c>
       <c r="D46" s="125">
         <f>D45/D7</f>
-        <v>1.505297771282426E-2</v>
+        <v>2.7399558857359368E-2</v>
       </c>
       <c r="E46" s="125">
         <f>E45/E7</f>
-        <v>6.0081828777143673E-3</v>
+        <v>2.5764955969490255E-2</v>
       </c>
       <c r="F46" s="125">
         <f>F45/F7</f>
-        <v>1.6197341261777697E-2</v>
+        <v>2.8261125311487331E-2</v>
       </c>
       <c r="G46" s="126">
         <f>G45/G7</f>
-        <v>1.7440431615986678E-2</v>
+        <v>2.6406409474271603E-2</v>
       </c>
       <c r="H46" s="98">
-        <v>1.0999999999999999E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I46" s="98">
-        <v>1.0999999999999999E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J46" s="98">
-        <v>1.0999999999999999E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="K46" s="98">
-        <v>1.0999999999999999E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="L46" s="98">
-        <v>1.0999999999999999E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20742,6 +20736,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20779,20 +20779,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="251" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="251"/>
+      <c r="E2" s="251"/>
+      <c r="F2" s="251"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
+      <c r="I2" s="251"/>
+      <c r="J2" s="251"/>
+      <c r="K2" s="251"/>
+      <c r="L2" s="251"/>
       <c r="S2" s="265"/>
       <c r="T2" s="265"/>
       <c r="U2" s="265"/>
@@ -20810,18 +20810,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="260" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
       <c r="S4" s="265"/>
       <c r="T4" s="265"/>
       <c r="U4" s="265"/>
@@ -21195,18 +21195,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="262" t="s">
+      <c r="C13" s="260" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="262"/>
-      <c r="E13" s="262"/>
-      <c r="F13" s="262"/>
-      <c r="G13" s="262"/>
-      <c r="H13" s="262"/>
-      <c r="I13" s="262"/>
-      <c r="J13" s="262"/>
-      <c r="K13" s="262"/>
-      <c r="L13" s="262"/>
+      <c r="D13" s="260"/>
+      <c r="E13" s="260"/>
+      <c r="F13" s="260"/>
+      <c r="G13" s="260"/>
+      <c r="H13" s="260"/>
+      <c r="I13" s="260"/>
+      <c r="J13" s="260"/>
+      <c r="K13" s="260"/>
+      <c r="L13" s="260"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21299,18 +21299,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="262" t="s">
+      <c r="C18" s="260" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="262"/>
-      <c r="E18" s="262"/>
-      <c r="F18" s="262"/>
-      <c r="G18" s="262"/>
-      <c r="H18" s="262"/>
-      <c r="I18" s="262"/>
-      <c r="J18" s="262"/>
-      <c r="K18" s="262"/>
-      <c r="L18" s="262"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="260"/>
+      <c r="J18" s="260"/>
+      <c r="K18" s="260"/>
+      <c r="L18" s="260"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21411,43 +21411,43 @@
       </c>
       <c r="C21" s="89">
         <f>'WC &amp; Investments'!C45</f>
-        <v>3586</v>
+        <v>6206</v>
       </c>
       <c r="D21" s="89">
         <f>'WC &amp; Investments'!D45</f>
-        <v>5562</v>
+        <v>10124</v>
       </c>
       <c r="E21" s="89">
         <f>'WC &amp; Investments'!E45</f>
-        <v>3191</v>
+        <v>13684</v>
       </c>
       <c r="F21" s="89">
         <f>'WC &amp; Investments'!F45</f>
-        <v>12116</v>
+        <v>21140</v>
       </c>
       <c r="G21" s="90">
         <f>'WC &amp; Investments'!G45</f>
-        <v>18096</v>
+        <v>27399</v>
       </c>
       <c r="H21" s="89">
         <f>'WC &amp; Investments'!H45</f>
-        <v>13104.854685999997</v>
+        <v>29783.760649999997</v>
       </c>
       <c r="I21" s="89">
         <f>'WC &amp; Investments'!I45</f>
-        <v>14962.206918497517</v>
+        <v>34005.015723857992</v>
       </c>
       <c r="J21" s="89">
         <f>'WC &amp; Investments'!J45</f>
-        <v>18845.960824580088</v>
+        <v>42831.729146772937</v>
       </c>
       <c r="K21" s="89">
         <f>'WC &amp; Investments'!K45</f>
-        <v>25406.518401736928</v>
+        <v>53122.720294540857</v>
       </c>
       <c r="L21" s="89">
         <f>'WC &amp; Investments'!L45</f>
-        <v>34190.20539757669</v>
+        <v>68380.410795153381</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>164</v>
@@ -21502,18 +21502,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="262" t="s">
+      <c r="C25" s="260" t="s">
         <v>271</v>
       </c>
-      <c r="D25" s="262"/>
-      <c r="E25" s="262"/>
-      <c r="F25" s="262"/>
-      <c r="G25" s="262"/>
-      <c r="H25" s="262"/>
-      <c r="I25" s="262"/>
-      <c r="J25" s="262"/>
-      <c r="K25" s="262"/>
-      <c r="L25" s="262"/>
+      <c r="D25" s="260"/>
+      <c r="E25" s="260"/>
+      <c r="F25" s="260"/>
+      <c r="G25" s="260"/>
+      <c r="H25" s="260"/>
+      <c r="I25" s="260"/>
+      <c r="J25" s="260"/>
+      <c r="K25" s="260"/>
+      <c r="L25" s="260"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21611,58 +21611,58 @@
       </c>
       <c r="C28" s="95">
         <f>C27+C20-C21+C22</f>
-        <v>-35092</v>
+        <v>-37712</v>
       </c>
       <c r="D28" s="95">
         <f t="shared" ref="D28:L28" si="7">D27+D20-D21+D22</f>
-        <v>-32389.924312708914</v>
+        <v>-36951.924312708914</v>
       </c>
       <c r="E28" s="95">
         <f t="shared" si="7"/>
-        <v>24267.594138493558</v>
+        <v>13774.594138493558</v>
       </c>
       <c r="F28" s="95">
         <f t="shared" si="7"/>
-        <v>145655.79989443434</v>
+        <v>136631.79989443434</v>
       </c>
       <c r="G28" s="129">
         <f t="shared" si="7"/>
-        <v>199444.84052409406</v>
+        <v>190141.84052409406</v>
       </c>
       <c r="H28" s="95">
         <f t="shared" si="7"/>
-        <v>156382.6515144548</v>
+        <v>139703.74555045483</v>
       </c>
       <c r="I28" s="95">
         <f t="shared" si="7"/>
-        <v>249703.93323373288</v>
+        <v>230661.12442837239</v>
       </c>
       <c r="J28" s="95">
         <f t="shared" si="7"/>
-        <v>308021.4865091613</v>
+        <v>284035.71818696847</v>
       </c>
       <c r="K28" s="95">
         <f t="shared" si="7"/>
-        <v>382367.71409827215</v>
+        <v>354651.51220546826</v>
       </c>
       <c r="L28" s="95">
         <f t="shared" si="7"/>
-        <v>570328.96383558039</v>
+        <v>536138.75843800372</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="262" t="s">
+      <c r="C31" s="260" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="262"/>
-      <c r="E31" s="262"/>
-      <c r="F31" s="262"/>
-      <c r="G31" s="262"/>
-      <c r="H31" s="262"/>
-      <c r="I31" s="262"/>
-      <c r="J31" s="262"/>
-      <c r="K31" s="262"/>
-      <c r="L31" s="262"/>
+      <c r="D31" s="260"/>
+      <c r="E31" s="260"/>
+      <c r="F31" s="260"/>
+      <c r="G31" s="260"/>
+      <c r="H31" s="260"/>
+      <c r="I31" s="260"/>
+      <c r="J31" s="260"/>
+      <c r="K31" s="260"/>
+      <c r="L31" s="260"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21801,16 +21801,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21873,10 +21873,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="251" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="254"/>
+      <c r="C4" s="251"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21961,10 +21961,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="254" t="s">
+      <c r="B15" s="251" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="254"/>
+      <c r="C15" s="251"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22053,20 +22053,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="251" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="254"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="251"/>
+      <c r="E3" s="251"/>
+      <c r="F3" s="251"/>
+      <c r="G3" s="263"/>
+      <c r="H3" s="264" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="254"/>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
+      <c r="I3" s="251"/>
+      <c r="J3" s="251"/>
+      <c r="K3" s="251"/>
+      <c r="L3" s="251"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -22084,18 +22084,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="262" t="s">
+      <c r="C5" s="260" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="262"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -22173,43 +22173,43 @@
       </c>
       <c r="C7" s="114">
         <f>'FCF &amp; Other'!C28</f>
-        <v>-35092</v>
+        <v>-37712</v>
       </c>
       <c r="D7" s="114">
         <f>'FCF &amp; Other'!D28</f>
-        <v>-32389.924312708914</v>
+        <v>-36951.924312708914</v>
       </c>
       <c r="E7" s="114">
         <f>'FCF &amp; Other'!E28</f>
-        <v>24267.594138493558</v>
+        <v>13774.594138493558</v>
       </c>
       <c r="F7" s="114">
         <f>'FCF &amp; Other'!F28</f>
-        <v>145655.79989443434</v>
+        <v>136631.79989443434</v>
       </c>
       <c r="G7" s="115">
         <f>'FCF &amp; Other'!G28</f>
-        <v>199444.84052409406</v>
+        <v>190141.84052409406</v>
       </c>
       <c r="H7" s="114">
         <f>'FCF &amp; Other'!H28</f>
-        <v>156382.6515144548</v>
+        <v>139703.74555045483</v>
       </c>
       <c r="I7" s="114">
         <f>'FCF &amp; Other'!I28</f>
-        <v>249703.93323373288</v>
+        <v>230661.12442837239</v>
       </c>
       <c r="J7" s="114">
         <f>'FCF &amp; Other'!J28</f>
-        <v>308021.4865091613</v>
+        <v>284035.71818696847</v>
       </c>
       <c r="K7" s="114">
         <f>'FCF &amp; Other'!K28</f>
-        <v>382367.71409827215</v>
+        <v>354651.51220546826</v>
       </c>
       <c r="L7" s="114">
         <f>'FCF &amp; Other'!L28</f>
-        <v>570328.96383558039</v>
+        <v>536138.75843800372</v>
       </c>
       <c r="N7" s="92"/>
       <c r="O7" s="16"/>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="L8" s="128">
         <f>L7*(1+C14)/(C15-C14)</f>
-        <v>6463728.2568032444</v>
+        <v>6076239.2622973761</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -22313,23 +22313,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f>H7/(1+$C$15)^H9</f>
-        <v>140885.27163464396</v>
+        <v>125859.23022563496</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>202665.31388177327</v>
+        <v>187209.74306336528</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" si="0"/>
-        <v>225222.65619100563</v>
+        <v>207684.4691199369</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" si="0"/>
-        <v>251877.45678955171</v>
+        <v>233619.93611710551</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" si="0"/>
-        <v>338462.48101848684</v>
+        <v>318172.25821870007</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -22348,14 +22348,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f>L8/(1+C15)^L9</f>
-        <v>3835908.1182095176</v>
+        <v>3605952.2598119345</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="254" t="s">
+      <c r="B13" s="251" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="254"/>
+      <c r="C13" s="251"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22375,10 +22375,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="254" t="s">
+      <c r="B18" s="251" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="254"/>
+      <c r="C18" s="251"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22386,7 +22386,7 @@
       </c>
       <c r="C19" s="64">
         <f>SUM(H10:L10)</f>
-        <v>1159113.1795154614</v>
+        <v>1072545.6367447427</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="C20" s="64">
         <f>L11</f>
-        <v>3835908.1182095176</v>
+        <v>3605952.2598119345</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22404,7 +22404,7 @@
       </c>
       <c r="C21" s="95">
         <f>C19+C20</f>
-        <v>4995021.297724979</v>
+        <v>4678497.8965566773</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="C24" s="95">
         <f>C21+C22-C23</f>
-        <v>6386842.297724979</v>
+        <v>6070318.8965566773</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C26" s="144">
         <f>C24/C25</f>
-        <v>130.91279024586424</v>
+        <v>124.42492665170388</v>
       </c>
     </row>
   </sheetData>
@@ -22492,37 +22492,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="251" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="251"/>
+      <c r="E2" s="251"/>
+      <c r="F2" s="251"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
+      <c r="I2" s="251"/>
+      <c r="J2" s="251"/>
+      <c r="K2" s="251"/>
+      <c r="L2" s="251"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="260" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22667,43 +22667,43 @@
       </c>
       <c r="C8" s="93">
         <f>'FCF &amp; Other'!C28</f>
-        <v>-35092</v>
+        <v>-37712</v>
       </c>
       <c r="D8" s="93">
         <f>'FCF &amp; Other'!D28</f>
-        <v>-32389.924312708914</v>
+        <v>-36951.924312708914</v>
       </c>
       <c r="E8" s="93">
         <f>'FCF &amp; Other'!E28</f>
-        <v>24267.594138493558</v>
+        <v>13774.594138493558</v>
       </c>
       <c r="F8" s="93">
         <f>'FCF &amp; Other'!F28</f>
-        <v>145655.79989443434</v>
+        <v>136631.79989443434</v>
       </c>
       <c r="G8" s="94">
         <f>'FCF &amp; Other'!G28</f>
-        <v>199444.84052409406</v>
+        <v>190141.84052409406</v>
       </c>
       <c r="H8" s="93">
         <f>'FCF &amp; Other'!H28</f>
-        <v>156382.6515144548</v>
+        <v>139703.74555045483</v>
       </c>
       <c r="I8" s="93">
         <f>'FCF &amp; Other'!I28</f>
-        <v>249703.93323373288</v>
+        <v>230661.12442837239</v>
       </c>
       <c r="J8" s="93">
         <f>'FCF &amp; Other'!J28</f>
-        <v>308021.4865091613</v>
+        <v>284035.71818696847</v>
       </c>
       <c r="K8" s="93">
         <f>'FCF &amp; Other'!K28</f>
-        <v>382367.71409827215</v>
+        <v>354651.51220546826</v>
       </c>
       <c r="L8" s="93">
         <f>'FCF &amp; Other'!L28</f>
-        <v>570328.96383558039</v>
+        <v>536138.75843800372</v>
       </c>
       <c r="N8" s="92"/>
     </row>
@@ -22711,18 +22711,18 @@
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="262" t="s">
+      <c r="C10" s="260" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="262"/>
-      <c r="E10" s="262"/>
-      <c r="F10" s="262"/>
-      <c r="G10" s="262"/>
-      <c r="H10" s="262"/>
-      <c r="I10" s="262"/>
-      <c r="J10" s="262"/>
-      <c r="K10" s="262"/>
-      <c r="L10" s="262"/>
+      <c r="D10" s="260"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="260"/>
+      <c r="G10" s="260"/>
+      <c r="H10" s="260"/>
+      <c r="I10" s="260"/>
+      <c r="J10" s="260"/>
+      <c r="K10" s="260"/>
+      <c r="L10" s="260"/>
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22873,42 +22873,42 @@
 IF(D8=0,0,IF(D8&gt;0,1,-1)),
 (D8-C8)/ABS(C8)
 )</f>
-        <v>7.6999763116695721E-2</v>
+        <v>2.0154743511112804E-2</v>
       </c>
       <c r="E14" s="96">
         <f t="shared" ref="E14:L14" si="3">IF(D8=0,
 IF(E8=0,0,IF(E8&gt;0,1,-1)),
 (E8-D8)/ABS(D8)
 )</f>
-        <v>1.7492328140134499</v>
+        <v>1.3727706850101997</v>
       </c>
       <c r="F14" s="96">
         <f t="shared" si="3"/>
-        <v>5.0020700471248327</v>
+        <v>8.9191162019512618</v>
       </c>
       <c r="G14" s="97">
         <f t="shared" si="3"/>
-        <v>0.36928869752281696</v>
+        <v>0.39163679810266072</v>
       </c>
       <c r="H14" s="96">
         <f t="shared" si="3"/>
-        <v>-0.21591026820489298</v>
+        <v>-0.26526562925137936</v>
       </c>
       <c r="I14" s="96">
         <f t="shared" si="3"/>
-        <v>0.59674958069535089</v>
+        <v>0.65107330171808298</v>
       </c>
       <c r="J14" s="96">
         <f t="shared" si="3"/>
-        <v>0.23354679487904123</v>
+        <v>0.23139830732582153</v>
       </c>
       <c r="K14" s="96">
         <f t="shared" si="3"/>
-        <v>0.24136701770932986</v>
+        <v>0.2486158940475805</v>
       </c>
       <c r="L14" s="96">
         <f t="shared" si="3"/>
-        <v>0.49157196804801467</v>
+        <v>0.51173402618227204</v>
       </c>
       <c r="N14" s="92"/>
     </row>
@@ -22916,18 +22916,18 @@
       <c r="N15" s="92"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="262" t="s">
+      <c r="C16" s="260" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="262"/>
-      <c r="E16" s="262"/>
-      <c r="F16" s="262"/>
-      <c r="G16" s="262"/>
-      <c r="H16" s="262"/>
-      <c r="I16" s="262"/>
-      <c r="J16" s="262"/>
-      <c r="K16" s="262"/>
-      <c r="L16" s="262"/>
+      <c r="D16" s="260"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="260"/>
+      <c r="G16" s="260"/>
+      <c r="H16" s="260"/>
+      <c r="I16" s="260"/>
+      <c r="J16" s="260"/>
+      <c r="K16" s="260"/>
+      <c r="L16" s="260"/>
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -23061,18 +23061,18 @@
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="262" t="s">
+      <c r="C21" s="260" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="262"/>
-      <c r="E21" s="262"/>
-      <c r="F21" s="262"/>
-      <c r="G21" s="262"/>
-      <c r="H21" s="262"/>
-      <c r="I21" s="262"/>
-      <c r="J21" s="262"/>
-      <c r="K21" s="262"/>
-      <c r="L21" s="262"/>
+      <c r="D21" s="260"/>
+      <c r="E21" s="260"/>
+      <c r="F21" s="260"/>
+      <c r="G21" s="260"/>
+      <c r="H21" s="260"/>
+      <c r="I21" s="260"/>
+      <c r="J21" s="260"/>
+      <c r="K21" s="260"/>
+      <c r="L21" s="260"/>
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -23156,18 +23156,18 @@
       <c r="N25" s="92"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="262" t="s">
+      <c r="C26" s="260" t="s">
         <v>204</v>
       </c>
-      <c r="D26" s="262"/>
-      <c r="E26" s="262"/>
-      <c r="F26" s="262"/>
-      <c r="G26" s="262"/>
-      <c r="H26" s="262"/>
-      <c r="I26" s="262"/>
-      <c r="J26" s="262"/>
-      <c r="K26" s="262"/>
-      <c r="L26" s="262"/>
+      <c r="D26" s="260"/>
+      <c r="E26" s="260"/>
+      <c r="F26" s="260"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="260"/>
+      <c r="I26" s="260"/>
+      <c r="J26" s="260"/>
+      <c r="K26" s="260"/>
+      <c r="L26" s="260"/>
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -23405,23 +23405,23 @@
       </c>
       <c r="C34" s="151">
         <f>C32/C8</f>
-        <v>-58.055942664994873</v>
+        <v>-54.02256947390751</v>
       </c>
       <c r="D34" s="151">
         <f t="shared" ref="D34:G34" si="13">D32/D8</f>
-        <v>-67.901396704932921</v>
+        <v>-59.518445680610597</v>
       </c>
       <c r="E34" s="151">
         <f t="shared" si="13"/>
-        <v>404.07407689605913</v>
+        <v>711.88345742957847</v>
       </c>
       <c r="F34" s="151">
         <f t="shared" si="13"/>
-        <v>98.460261866633672</v>
+        <v>104.96317995576803</v>
       </c>
       <c r="G34" s="152">
         <f t="shared" si="13"/>
-        <v>36.516696702474384</v>
+        <v>38.303335710946961</v>
       </c>
       <c r="H34" s="139"/>
       <c r="I34" s="139"/>
@@ -23437,10 +23437,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="254" t="s">
+      <c r="B37" s="251" t="s">
         <v>209</v>
       </c>
-      <c r="C37" s="254"/>
+      <c r="C37" s="251"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -23515,10 +23515,10 @@
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="254" t="s">
+      <c r="B47" s="251" t="s">
         <v>214</v>
       </c>
-      <c r="C47" s="254"/>
+      <c r="C47" s="251"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
@@ -23574,10 +23574,10 @@
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="254" t="s">
+      <c r="B55" s="251" t="s">
         <v>332</v>
       </c>
-      <c r="C55" s="254"/>
+      <c r="C55" s="251"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
@@ -23585,7 +23585,7 @@
       </c>
       <c r="C56" s="64">
         <f>L8</f>
-        <v>570328.96383558039</v>
+        <v>536138.75843800372</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="C59" s="24">
         <f>(C56*C58)</f>
-        <v>12547237.204382768</v>
+        <v>11795052.685636081</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -23620,7 +23620,7 @@
       </c>
       <c r="C60" s="24">
         <f>C59/(1+C57)^5-G30+G31</f>
-        <v>8721739.5824067108</v>
+        <v>8275354.6808114005</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -23638,7 +23638,7 @@
       </c>
       <c r="C62" s="144">
         <f>C60/C61</f>
-        <v>178.77179540465104</v>
+        <v>169.62212640275894</v>
       </c>
     </row>
   </sheetData>
@@ -23690,10 +23690,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="251" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="254"/>
+      <c r="C4" s="251"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23702,7 +23702,7 @@
       </c>
       <c r="C5" s="135">
         <f>DCF!C26</f>
-        <v>130.91279024586424</v>
+        <v>124.42492665170388</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="C8" s="135">
         <f>Multiples!C62</f>
-        <v>178.77179540465104</v>
+        <v>169.62212640275894</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="C9" s="144">
         <f>AVERAGE(C5:C8)</f>
-        <v>151.84221113253037</v>
+        <v>147.93282798351726</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23756,7 +23756,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.20739671702075668</v>
+        <v>0.17631065508521987</v>
       </c>
     </row>
   </sheetData>
@@ -23822,20 +23822,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="251" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="254"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="251"/>
+      <c r="E3" s="251"/>
+      <c r="F3" s="251"/>
+      <c r="G3" s="263"/>
+      <c r="H3" s="264" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="254"/>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
+      <c r="I3" s="251"/>
+      <c r="J3" s="251"/>
+      <c r="K3" s="251"/>
+      <c r="L3" s="251"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -23853,18 +23853,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="262" t="s">
+      <c r="C5" s="260" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="262"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -23942,43 +23942,43 @@
       </c>
       <c r="C7" s="114">
         <f>'FCF &amp; Other'!C28</f>
-        <v>-35092</v>
+        <v>-37712</v>
       </c>
       <c r="D7" s="114">
         <f>'FCF &amp; Other'!D28</f>
-        <v>-32389.924312708914</v>
+        <v>-36951.924312708914</v>
       </c>
       <c r="E7" s="114">
         <f>'FCF &amp; Other'!E28</f>
-        <v>24267.594138493558</v>
+        <v>13774.594138493558</v>
       </c>
       <c r="F7" s="114">
         <f>'FCF &amp; Other'!F28</f>
-        <v>145655.79989443434</v>
+        <v>136631.79989443434</v>
       </c>
       <c r="G7" s="115">
         <f>'FCF &amp; Other'!G28</f>
-        <v>199444.84052409406</v>
+        <v>190141.84052409406</v>
       </c>
       <c r="H7" s="128">
         <f>G7*(1+$C$17)</f>
-        <v>239333.80862891287</v>
+        <v>228170.20862891286</v>
       </c>
       <c r="I7" s="128">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>287200.57035469543</v>
+        <v>273804.25035469542</v>
       </c>
       <c r="J7" s="128">
         <f t="shared" si="0"/>
-        <v>344640.68442563451</v>
+        <v>328565.10042563447</v>
       </c>
       <c r="K7" s="128">
         <f t="shared" si="0"/>
-        <v>413568.82131076138</v>
+        <v>394278.12051076134</v>
       </c>
       <c r="L7" s="128">
         <f t="shared" si="0"/>
-        <v>496282.58557291364</v>
+        <v>473133.74461291358</v>
       </c>
       <c r="N7" s="92"/>
       <c r="O7" s="16"/>
@@ -24010,7 +24010,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>5624535.9698263546</v>
+        <v>5362182.4389463542</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -24064,23 +24064,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f>H7/(1+$C$21)^H9</f>
-        <v>215616.0438098314</v>
+        <v>205558.7465125341</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>233098.42574035825</v>
+        <v>222225.67190544223</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" si="1"/>
-        <v>251998.29809768457</v>
+        <v>240243.96962750508</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" si="1"/>
-        <v>272430.59253803734</v>
+        <v>259723.21040811358</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" si="1"/>
-        <v>294519.55950058089</v>
+        <v>280781.84908985248</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -24099,7 +24099,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f>L8/(1+C21)^L9</f>
-        <v>3337888.3410065831</v>
+        <v>3182194.2896849951</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24124,7 +24124,7 @@
       </c>
       <c r="C16" s="158">
         <f>C36</f>
-        <v>128.71831091994667</v>
+        <v>124.10767147915871</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="C29" s="163">
         <f>SUM(H10:L10)</f>
-        <v>1267662.9196864925</v>
+        <v>1208533.4475434474</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24233,7 +24233,7 @@
       </c>
       <c r="C30" s="163">
         <f>L11</f>
-        <v>3337888.3410065831</v>
+        <v>3182194.2896849951</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24242,7 +24242,7 @@
       </c>
       <c r="C31" s="166">
         <f>C29+C30</f>
-        <v>4605551.2606930751</v>
+        <v>4390727.737228442</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24269,7 +24269,7 @@
       </c>
       <c r="C34" s="166">
         <f>C31+C32-C33</f>
-        <v>5997372.2606930751</v>
+        <v>5782548.737228442</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -24287,22 +24287,22 @@
       </c>
       <c r="C36" s="169">
         <f>C34/C35</f>
-        <v>128.71831091994667</v>
+        <v>124.10767147915871</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="262" t="s">
+      <c r="C39" s="260" t="s">
         <v>233</v>
       </c>
-      <c r="D39" s="262"/>
-      <c r="E39" s="262"/>
-      <c r="F39" s="262"/>
-      <c r="G39" s="262"/>
-      <c r="H39" s="262"/>
-      <c r="I39" s="262"/>
-      <c r="J39" s="262"/>
-      <c r="K39" s="262"/>
-      <c r="L39" s="262"/>
+      <c r="D39" s="260"/>
+      <c r="E39" s="260"/>
+      <c r="F39" s="260"/>
+      <c r="G39" s="260"/>
+      <c r="H39" s="260"/>
+      <c r="I39" s="260"/>
+      <c r="J39" s="260"/>
+      <c r="K39" s="260"/>
+      <c r="L39" s="260"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -24352,43 +24352,43 @@
       </c>
       <c r="C41" s="114">
         <f>C7</f>
-        <v>-35092</v>
+        <v>-37712</v>
       </c>
       <c r="D41" s="114">
         <f t="shared" si="2"/>
-        <v>-32389.924312708914</v>
+        <v>-36951.924312708914</v>
       </c>
       <c r="E41" s="114">
         <f t="shared" si="2"/>
-        <v>24267.594138493558</v>
+        <v>13774.594138493558</v>
       </c>
       <c r="F41" s="114">
         <f t="shared" si="2"/>
-        <v>145655.79989443434</v>
+        <v>136631.79989443434</v>
       </c>
       <c r="G41" s="115">
         <f t="shared" si="2"/>
-        <v>199444.84052409406</v>
+        <v>190141.84052409406</v>
       </c>
       <c r="H41" s="145">
         <f t="shared" si="2"/>
-        <v>239333.80862891287</v>
+        <v>228170.20862891286</v>
       </c>
       <c r="I41" s="145">
         <f t="shared" si="2"/>
-        <v>287200.57035469543</v>
+        <v>273804.25035469542</v>
       </c>
       <c r="J41" s="145">
         <f t="shared" si="2"/>
-        <v>344640.68442563451</v>
+        <v>328565.10042563447</v>
       </c>
       <c r="K41" s="145">
         <f t="shared" si="2"/>
-        <v>413568.82131076138</v>
+        <v>394278.12051076134</v>
       </c>
       <c r="L41" s="145">
         <f t="shared" si="2"/>
-        <v>496282.58557291364</v>
+        <v>473133.74461291358</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -24417,23 +24417,23 @@
       </c>
       <c r="H42" s="145">
         <f>H41/H43</f>
-        <v>184102.92971454834</v>
+        <v>175515.54509916375</v>
       </c>
       <c r="I42" s="145">
         <f t="shared" ref="I42:L42" si="3">I41/I43</f>
-        <v>220923.51565745802</v>
+        <v>210618.65411899646</v>
       </c>
       <c r="J42" s="145">
         <f t="shared" si="3"/>
-        <v>265108.2187889496</v>
+        <v>252742.38494279573</v>
       </c>
       <c r="K42" s="145">
         <f t="shared" si="3"/>
-        <v>318129.86254673952</v>
+        <v>303290.86193135486</v>
       </c>
       <c r="L42" s="145">
         <f t="shared" si="3"/>
-        <v>381755.83505608741</v>
+        <v>363949.0343176258</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -24442,23 +24442,23 @@
       </c>
       <c r="C43" s="96">
         <f>C41/C42</f>
-        <v>0.5847984401819788</v>
+        <v>0.62846001299848353</v>
       </c>
       <c r="D43" s="96">
         <f t="shared" ref="D43:G43" si="4">D41/D42</f>
-        <v>0.4968160796488828</v>
+        <v>0.56679077095956609</v>
       </c>
       <c r="E43" s="96">
         <f t="shared" si="4"/>
-        <v>-1.830273334225323</v>
+        <v>-1.0388863517982923</v>
       </c>
       <c r="F43" s="96">
         <f t="shared" si="4"/>
-        <v>2.3269558254562561</v>
+        <v>2.1827909560577416</v>
       </c>
       <c r="G43" s="97">
         <f t="shared" si="4"/>
-        <v>1.4711576346101207</v>
+        <v>1.4025362581994103</v>
       </c>
       <c r="H43" s="170">
         <v>1.3</v>
@@ -24502,23 +24502,23 @@
       </c>
       <c r="H44" s="145">
         <f>H41/H45</f>
-        <v>1329632.2701606271</v>
+        <v>1267612.2701606271</v>
       </c>
       <c r="I44" s="145">
         <f t="shared" ref="I44:L44" si="5">I41/I45</f>
-        <v>1595558.7241927525</v>
+        <v>1521134.7241927525</v>
       </c>
       <c r="J44" s="145">
         <f t="shared" si="5"/>
-        <v>1914670.469031303</v>
+        <v>1825361.6690313027</v>
       </c>
       <c r="K44" s="145">
         <f t="shared" si="5"/>
-        <v>2297604.5628375635</v>
+        <v>2190434.0028375629</v>
       </c>
       <c r="L44" s="145">
         <f t="shared" si="5"/>
-        <v>2757125.4754050761</v>
+        <v>2628520.8034050753</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -24527,23 +24527,23 @@
       </c>
       <c r="C45" s="96">
         <f>C41/C44</f>
-        <v>-0.1399358780087091</v>
+        <v>-0.1503836153956582</v>
       </c>
       <c r="D45" s="96">
         <f t="shared" ref="D45:G45" si="6">D41/D44</f>
-        <v>-8.7659980007060753E-2</v>
+        <v>-0.10000656115159587</v>
       </c>
       <c r="E45" s="96">
         <f t="shared" si="6"/>
-        <v>4.5692304477034956E-2</v>
+        <v>2.5935531385259065E-2</v>
       </c>
       <c r="F45" s="96">
         <f t="shared" si="6"/>
-        <v>0.19472075748162404</v>
+        <v>0.18265697343191439</v>
       </c>
       <c r="G45" s="97">
         <f t="shared" si="6"/>
-        <v>0.19221950167560958</v>
+        <v>0.18325352381732465</v>
       </c>
       <c r="H45" s="170">
         <v>0.18</v>
@@ -24568,19 +24568,19 @@
       <c r="C46" s="139"/>
       <c r="D46" s="96">
         <f>D41/C41-1</f>
-        <v>-7.6999763116695763E-2</v>
+        <v>-2.0154743511112794E-2</v>
       </c>
       <c r="E46" s="96">
         <f t="shared" ref="E46:L47" si="7">E41/D41-1</f>
-        <v>-1.7492328140134499</v>
+        <v>-1.3727706850101997</v>
       </c>
       <c r="F46" s="96">
         <f t="shared" si="7"/>
-        <v>5.0020700471248327</v>
+        <v>8.9191162019512618</v>
       </c>
       <c r="G46" s="97">
         <f t="shared" si="7"/>
-        <v>0.3692886975228169</v>
+        <v>0.39163679810266072</v>
       </c>
       <c r="H46" s="171">
         <f t="shared" si="7"/>
@@ -24626,11 +24626,11 @@
       </c>
       <c r="H47" s="171">
         <f t="shared" si="7"/>
-        <v>0.35799166271703431</v>
+        <v>0.29464885372253269</v>
       </c>
       <c r="I47" s="171">
         <f t="shared" si="7"/>
-        <v>0.19999999999999996</v>
+        <v>0.19999999999999973</v>
       </c>
       <c r="J47" s="171">
         <f t="shared" si="7"/>
@@ -24668,7 +24668,7 @@
       </c>
       <c r="H48" s="171">
         <f t="shared" si="8"/>
-        <v>0.28146334450406374</v>
+        <v>0.22169015878216425</v>
       </c>
       <c r="I48" s="171">
         <f t="shared" si="8"/>
@@ -24676,7 +24676,7 @@
       </c>
       <c r="J48" s="171">
         <f t="shared" si="8"/>
-        <v>0.19999999999999996</v>
+        <v>0.19999999999999973</v>
       </c>
       <c r="K48" s="171">
         <f t="shared" si="8"/>
@@ -24713,7 +24713,7 @@
       </c>
       <c r="H49" s="171">
         <f t="shared" si="9"/>
-        <v>0.13846153846153844</v>
+        <v>0.13846153846153847</v>
       </c>
       <c r="I49" s="171">
         <f t="shared" si="9"/>
@@ -24725,26 +24725,26 @@
       </c>
       <c r="K49" s="171">
         <f t="shared" si="9"/>
-        <v>0.13846153846153844</v>
+        <v>0.13846153846153847</v>
       </c>
       <c r="L49" s="171">
         <f t="shared" si="9"/>
-        <v>0.13846153846153844</v>
+        <v>0.13846153846153847</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -35469,15 +35469,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="251" t="s">
         <v>242</v>
       </c>
-      <c r="C4" s="254"/>
-      <c r="E4" s="254" t="s">
+      <c r="C4" s="251"/>
+      <c r="E4" s="251" t="s">
         <v>249</v>
       </c>
-      <c r="F4" s="254"/>
-      <c r="G4" s="254"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35614,14 +35614,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="254" t="s">
+      <c r="B15" s="251" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="254"/>
-      <c r="E15" s="254" t="s">
+      <c r="C15" s="251"/>
+      <c r="E15" s="251" t="s">
         <v>255</v>
       </c>
-      <c r="F15" s="254"/>
+      <c r="F15" s="251"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35672,14 +35672,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="254" t="s">
+      <c r="B21" s="251" t="s">
         <v>254</v>
       </c>
-      <c r="C21" s="254"/>
-      <c r="E21" s="254" t="s">
+      <c r="C21" s="251"/>
+      <c r="E21" s="251" t="s">
         <v>258</v>
       </c>
-      <c r="F21" s="254"/>
+      <c r="F21" s="251"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35748,14 +35748,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="254" t="s">
+      <c r="B29" s="251" t="s">
         <v>259</v>
       </c>
-      <c r="C29" s="254"/>
-      <c r="E29" s="254" t="s">
+      <c r="C29" s="251"/>
+      <c r="E29" s="251" t="s">
         <v>265</v>
       </c>
-      <c r="F29" s="254"/>
+      <c r="F29" s="251"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35831,14 +35831,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="254" t="s">
+      <c r="B37" s="251" t="s">
         <v>277</v>
       </c>
-      <c r="C37" s="254"/>
-      <c r="E37" s="254" t="s">
+      <c r="C37" s="251"/>
+      <c r="E37" s="251" t="s">
         <v>280</v>
       </c>
-      <c r="F37" s="254"/>
+      <c r="F37" s="251"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35907,14 +35907,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="254" t="s">
+      <c r="B45" s="251" t="s">
         <v>288</v>
       </c>
-      <c r="C45" s="254"/>
-      <c r="E45" s="254" t="s">
+      <c r="C45" s="251"/>
+      <c r="E45" s="251" t="s">
         <v>294</v>
       </c>
-      <c r="F45" s="254"/>
+      <c r="F45" s="251"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35951,14 +35951,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="254" t="s">
+      <c r="B51" s="251" t="s">
         <v>291</v>
       </c>
-      <c r="C51" s="254"/>
-      <c r="E51" s="254" t="s">
+      <c r="C51" s="251"/>
+      <c r="E51" s="251" t="s">
         <v>312</v>
       </c>
-      <c r="F51" s="254"/>
+      <c r="F51" s="251"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37997,14 +37997,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="257" t="s">
+      <c r="C3" s="255" t="s">
         <v>322</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="F3" s="259" t="s">
+      <c r="D3" s="256"/>
+      <c r="F3" s="257" t="s">
         <v>323</v>
       </c>
-      <c r="G3" s="258"/>
+      <c r="G3" s="256"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38071,19 +38071,19 @@
       <c r="B7" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C7" s="255">
+      <c r="C7" s="258">
         <f>Statement!AA89</f>
         <v>3.2166947127281985E-2</v>
       </c>
-      <c r="D7" s="256"/>
-      <c r="F7" s="255">
+      <c r="D7" s="259"/>
+      <c r="F7" s="258">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.26533415964948015</v>
       </c>
-      <c r="G7" s="256"/>
+      <c r="G7" s="259"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -38110,19 +38110,19 @@
       <c r="B9" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C9" s="255">
+      <c r="C9" s="258">
         <f>Statement!AA90</f>
         <v>2.4312004052000676E-2</v>
       </c>
-      <c r="D9" s="256"/>
-      <c r="F9" s="255">
+      <c r="D9" s="259"/>
+      <c r="F9" s="258">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.18341410716161269</v>
       </c>
-      <c r="G9" s="256"/>
+      <c r="G9" s="259"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -38149,19 +38149,19 @@
       <c r="B11" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C11" s="255">
+      <c r="C11" s="258">
         <f>Statement!AA91</f>
         <v>3.5104848228727975E-2</v>
       </c>
-      <c r="D11" s="256"/>
-      <c r="F11" s="255">
+      <c r="D11" s="259"/>
+      <c r="F11" s="258">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.29860569422776911</v>
       </c>
-      <c r="G11" s="256"/>
+      <c r="G11" s="259"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -38188,19 +38188,19 @@
       <c r="B13" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C13" s="255">
+      <c r="C13" s="258">
         <f>Statement!AA95</f>
         <v>3.7890588923436871E-2</v>
       </c>
-      <c r="D13" s="256"/>
-      <c r="F13" s="255">
+      <c r="D13" s="259"/>
+      <c r="F13" s="258">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.19976228096397206</v>
       </c>
-      <c r="G13" s="256"/>
+      <c r="G13" s="259"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -38227,19 +38227,19 @@
       <c r="B15" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C15" s="255">
+      <c r="C15" s="258">
         <f>Statement!AA96</f>
         <v>2.4692778570442307E-2</v>
       </c>
-      <c r="D15" s="256"/>
-      <c r="F15" s="255">
+      <c r="D15" s="259"/>
+      <c r="F15" s="258">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.88721708909044672</v>
       </c>
-      <c r="G15" s="256"/>
+      <c r="G15" s="259"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -38266,19 +38266,19 @@
       <c r="B17" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C17" s="255">
+      <c r="C17" s="258">
         <f>Statement!AA98</f>
         <v>3.5896458025456456E-2</v>
       </c>
-      <c r="D17" s="256"/>
-      <c r="F17" s="255">
+      <c r="D17" s="259"/>
+      <c r="F17" s="258">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.23694321901238083</v>
       </c>
-      <c r="G17" s="256"/>
+      <c r="G17" s="259"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -38305,22 +38305,22 @@
       <c r="B19" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C19" s="255">
+      <c r="C19" s="258">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3895378744883068E-2</v>
       </c>
-      <c r="D19" s="256"/>
-      <c r="F19" s="255">
+      <c r="D19" s="259"/>
+      <c r="F19" s="258">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.0103717755737469E-2</v>
       </c>
-      <c r="G19" s="256"/>
+      <c r="G19" s="259"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -38347,22 +38347,22 @@
       <c r="B21" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C21" s="255">
+      <c r="C21" s="258">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.4953901558794477E-2</v>
       </c>
-      <c r="D21" s="256"/>
-      <c r="F21" s="255">
+      <c r="D21" s="259"/>
+      <c r="F21" s="258">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.23611111111111119</v>
       </c>
-      <c r="G21" s="256"/>
+      <c r="G21" s="259"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38411,22 +38411,22 @@
       <c r="B25" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C25" s="255">
+      <c r="C25" s="258">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>3.5586042940987099E-2</v>
       </c>
-      <c r="D25" s="256"/>
-      <c r="F25" s="255">
+      <c r="D25" s="259"/>
+      <c r="F25" s="258">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.3137438673836439</v>
       </c>
-      <c r="G25" s="256"/>
+      <c r="G25" s="259"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38454,22 +38454,22 @@
       <c r="B27" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C27" s="255">
+      <c r="C27" s="258">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>1.9435240591464318E-2</v>
       </c>
-      <c r="D27" s="256"/>
-      <c r="F27" s="255">
+      <c r="D27" s="259"/>
+      <c r="F27" s="258">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.15277933117100995</v>
       </c>
-      <c r="G27" s="256"/>
+      <c r="G27" s="259"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38497,22 +38497,22 @@
       <c r="B29" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C29" s="255">
+      <c r="C29" s="258">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.10055431294369348</v>
       </c>
-      <c r="D29" s="256"/>
-      <c r="F29" s="255">
+      <c r="D29" s="259"/>
+      <c r="F29" s="258">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-5.581511763724345E-2</v>
       </c>
-      <c r="G29" s="256"/>
+      <c r="G29" s="259"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -38540,22 +38540,22 @@
       <c r="B31" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C31" s="255">
+      <c r="C31" s="258">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.11569469165532405</v>
       </c>
-      <c r="D31" s="256"/>
-      <c r="F31" s="255">
+      <c r="D31" s="259"/>
+      <c r="F31" s="258">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.10548612582080068</v>
       </c>
-      <c r="G31" s="256"/>
+      <c r="G31" s="259"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -38583,22 +38583,22 @@
       <c r="B33" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C33" s="255">
+      <c r="C33" s="258">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.29411764705882354</v>
       </c>
-      <c r="D33" s="256"/>
-      <c r="F33" s="255">
+      <c r="D33" s="259"/>
+      <c r="F33" s="258">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.52914798206278024</v>
       </c>
-      <c r="G33" s="256"/>
+      <c r="G33" s="259"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -38647,22 +38647,22 @@
       <c r="B37" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C37" s="255">
+      <c r="C37" s="258">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>7.2106261859582549E-2</v>
       </c>
-      <c r="D37" s="256"/>
-      <c r="F37" s="255">
+      <c r="D37" s="259"/>
+      <c r="F37" s="258">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.21244635193133046</v>
       </c>
-      <c r="G37" s="256"/>
+      <c r="G37" s="259"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -38690,22 +38690,22 @@
       <c r="B39" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C39" s="255">
+      <c r="C39" s="258">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>3.5311795642374154E-2</v>
       </c>
-      <c r="D39" s="256"/>
-      <c r="F39" s="255">
+      <c r="D39" s="259"/>
+      <c r="F39" s="258">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>5.8371735791090631E-2</v>
       </c>
-      <c r="G39" s="256"/>
+      <c r="G39" s="259"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -38733,22 +38733,22 @@
       <c r="B41" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C41" s="255">
+      <c r="C41" s="258">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>2.4590163934426229E-2</v>
       </c>
-      <c r="D41" s="256"/>
-      <c r="F41" s="255">
+      <c r="D41" s="259"/>
+      <c r="F41" s="258">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.21359223300970873</v>
       </c>
-      <c r="G41" s="256"/>
+      <c r="G41" s="259"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -38776,22 +38776,22 @@
       <c r="B43" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C43" s="255">
+      <c r="C43" s="258">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>3.6393713813068655E-2</v>
       </c>
-      <c r="D43" s="256"/>
-      <c r="F43" s="255">
+      <c r="D43" s="259"/>
+      <c r="F43" s="258">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>4.5037531276063386E-2</v>
       </c>
-      <c r="G43" s="256"/>
+      <c r="G43" s="259"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -38819,22 +38819,22 @@
       <c r="B45" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C45" s="255">
+      <c r="C45" s="258">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.0731977910403413E-2</v>
       </c>
-      <c r="D45" s="256"/>
-      <c r="F45" s="255">
+      <c r="D45" s="259"/>
+      <c r="F45" s="258">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>8.2524946724122472E-2</v>
       </c>
-      <c r="G45" s="256"/>
+      <c r="G45" s="259"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -38862,22 +38862,22 @@
       <c r="B47" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C47" s="255">
+      <c r="C47" s="258">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>3.5539502565387668E-2</v>
       </c>
-      <c r="D47" s="256"/>
-      <c r="F47" s="255">
+      <c r="D47" s="259"/>
+      <c r="F47" s="258">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.14557703208606101</v>
       </c>
-      <c r="G47" s="256"/>
+      <c r="G47" s="259"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -38905,22 +38905,22 @@
       <c r="B49" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C49" s="255">
+      <c r="C49" s="258">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-1.0355944704846643E-2</v>
       </c>
-      <c r="D49" s="256"/>
-      <c r="F49" s="255">
+      <c r="D49" s="259"/>
+      <c r="F49" s="258">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>0.14665971507883949</v>
       </c>
-      <c r="G49" s="256"/>
+      <c r="G49" s="259"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -38948,22 +38948,22 @@
       <c r="B51" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C51" s="255">
+      <c r="C51" s="258">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>-1.63629641858896E-2</v>
       </c>
-      <c r="D51" s="256"/>
-      <c r="F51" s="255">
+      <c r="D51" s="259"/>
+      <c r="F51" s="258">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>0.10309849806387941</v>
       </c>
-      <c r="G51" s="256"/>
+      <c r="G51" s="259"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -38991,43 +38991,39 @@
       <c r="B53" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C53" s="255">
+      <c r="C53" s="258">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-0.17517009292452351</v>
       </c>
-      <c r="D53" s="256"/>
-      <c r="F53" s="255">
+      <c r="D53" s="259"/>
+      <c r="F53" s="258">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.26222395510175772</v>
       </c>
-      <c r="G53" s="256"/>
+      <c r="G53" s="259"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39042,20 +39038,24 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7D4504-2662-D449-BE25-BAAAA0741653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0867F2A0-22F9-E048-9D96-4555B7CAB6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -128,7 +128,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -138,19 +159,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="423">
   <si>
     <t>Ticker</t>
   </si>
@@ -12998,7 +13028,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c2mtim&amp;q=XNAS%3aDUOL&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -13017,11 +13047,9 @@
     <v>Powered by Refinitiv</v>
     <v>468</v>
     <v>87.89</v>
-    <v>0.87080000000000002</v>
-    <v>4.5449999999999999</v>
-    <v>3.7495000000000001E-2</v>
-    <v>-0.56000000000000005</v>
-    <v>-4.4529999999999995E-3</v>
+    <v>0.87490000000000001</v>
+    <v>3.57</v>
+    <v>2.7521E-2</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13029,35 +13057,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>126.88</v>
+    <v>135</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46205.99772239531</v>
+    <v>46210.767281990622</v>
     <v>0</v>
-    <v>115.51</v>
-    <v>5859550771</v>
+    <v>131.41419999999999</v>
+    <v>6210396964</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>119.99</v>
-    <v>14.028499999999999</v>
-    <v>121.215</v>
-    <v>125.76</v>
-    <v>125.2</v>
+    <v>132.96</v>
+    <v>15.425800000000001</v>
+    <v>129.72</v>
+    <v>133.29</v>
     <v>46593120</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>1002431</v>
-    <v>1530289</v>
+    <v>645874</v>
+    <v>1578635</v>
     <v>2011</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -13071,28 +13113,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.1</v>
-    <v>2.235E-3</v>
+    <v>-0.06</v>
+    <v>-1.338E-3</v>
     <v>US</v>
-    <v>45.05</v>
+    <v>44.91</v>
     <v>Index</v>
-    <v>3</v>
-    <v>44.53</v>
+    <v>6</v>
+    <v>44.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.03</v>
-    <v>44.75</v>
+    <v>44.57</v>
     <v>44.85</v>
+    <v>44.79</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13114,8 +13156,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13136,7 +13176,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13146,6 +13185,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13181,7 +13225,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13192,16 +13236,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13295,19 +13336,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13379,9 +13414,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13389,9 +13421,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13902,7 +13931,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC149</f>
-        <v>6135453.1200000001</v>
+        <v>6502819.2299999995</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -13926,7 +13955,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>4743632.12</v>
+        <v>5110998.2299999995</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -13934,7 +13963,7 @@
       </c>
       <c r="I4" s="213">
         <f>'AVG target price'!C6</f>
-        <v>171.70850800265185</v>
+        <v>200.23702994497253</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13943,7 +13972,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>125.76</v>
+        <v>133.29</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>252</v>
@@ -13965,16 +13994,16 @@
       <c r="B6" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="210" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>125.2</v>
+      <c r="C6" s="210" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>246</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC146</f>
-        <v>37.090814138040948</v>
+        <v>39.311662026554366</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -13982,7 +14011,7 @@
       </c>
       <c r="I6" s="213">
         <f>'AVG target price'!C8</f>
-        <v>169.62212640275894</v>
+        <v>198.15064834507967</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13991,14 +14020,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>4.5449999999999999</v>
+        <v>3.57</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC147</f>
-        <v>5.5922547639428393</v>
+        <v>5.927096354054874</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -14006,23 +14035,23 @@
       </c>
       <c r="I7" s="214">
         <f>'AVG target price'!C9</f>
-        <v>147.93282798351726</v>
+        <v>162.19708895467761</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.56000000000000005</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>274</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC157</f>
-        <v>4.3050121129439907E-2</v>
+        <v>4.0618075123702926E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -14030,7 +14059,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.17631065508521987</v>
+        <v>0.21687365109668857</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14039,30 +14068,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.7495000000000001E-2</v>
+        <v>2.7521E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>297</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC158</f>
-        <v>2.6960853333612422E-2</v>
+        <v>2.5437744131105847E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-4.4529999999999995E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>302</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC160</f>
-        <v>3.9656402753184107E-3</v>
+        <v>3.7416079302576588E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -14103,7 +14132,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.87080000000000002</v>
+        <v>0.87490000000000001</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>104</v>
@@ -14119,7 +14148,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1530289</v>
+        <v>1578635</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>105</v>
@@ -14135,7 +14164,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC172</f>
-        <v>0.22684893401972567</v>
+        <v>0.21403347544692553</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14240,12 +14269,12 @@
       <c r="C26" s="172">
         <v>0.21</v>
       </c>
-      <c r="E26" s="187" t="e" vm="2">
+      <c r="E26" s="187" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.85</v>
+        <v>44.79</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14260,7 +14289,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -21893,7 +21922,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>125.76</v>
+        <v>133.29</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21902,7 +21931,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>6135453.1200000001</v>
+        <v>6502819.2299999995</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21920,7 +21949,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21929,7 +21958,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>0.87080000000000002</v>
+        <v>0.87490000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21999,7 +22028,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.4036E-2</v>
+        <v>8.4160499999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22008,7 +22037,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.4036E-2</v>
+        <v>8.4160499999999999E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22470,7 +22499,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="84" customWidth="1"/>
@@ -23471,182 +23500,227 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C41" s="24">
+        <f>(C38*C40)</f>
+        <v>11966571.889151841</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C42" s="24">
+        <f>C41/(1+C39)^5-G30+G31</f>
+        <v>8377142.9799253754</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B43" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C43" s="89">
+        <f>Statement!AC107</f>
+        <v>1391821</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C44" s="89">
+        <f>Statement!AC108</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C45" s="24">
+        <f>C42+C43-C44</f>
+        <v>9768963.9799253754</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="89">
+        <f>Statement!AC78</f>
+        <v>48787</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="143" t="s">
+        <v>213</v>
+      </c>
+      <c r="C47" s="144">
+        <f>C45/C46</f>
+        <v>200.23702994497253</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="251" t="s">
+        <v>214</v>
+      </c>
+      <c r="C49" s="251"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C50" s="64">
+        <f>L6</f>
+        <v>3108200.4906887901</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C51" s="137">
+        <f>Overview!C29</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="C52" s="106">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C53" s="24">
         <f>L18</f>
         <v>56000.505465443181</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C54" s="24">
+        <f>(C50*C52)/C53</f>
+        <v>222.01231684287563</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="143" t="s">
+        <v>213</v>
+      </c>
+      <c r="C55" s="144">
+        <f>C54/(1+C51)^5</f>
+        <v>125.97575087695434</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="251" t="s">
+        <v>332</v>
+      </c>
+      <c r="C57" s="251"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C58" s="64">
+        <f>L8</f>
+        <v>536138.75843800372</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B59" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C59" s="137">
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="C60" s="106">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C42" s="24">
-        <f>(C38*C40)</f>
-        <v>11966571.889151841</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B43" s="1" t="s">
+      <c r="C61" s="24">
+        <f>(C58*C60)</f>
+        <v>11795052.685636081</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C43" s="24">
-        <f>C42/(1+C39)^5-G30+G31</f>
-        <v>8377142.9799253754</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="1" t="s">
+      <c r="C62" s="24">
+        <f>C61/(1+C59)^5-G30+G31</f>
+        <v>8275354.6808114005</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C63" s="89">
+        <f>Statement!AC107</f>
+        <v>1391821</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B64" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C64" s="89">
+        <f>Statement!AC108</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C65" s="24">
+        <f>C62+C63-C64</f>
+        <v>9667175.6808114015</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="89">
+      <c r="C66" s="89">
         <f>Statement!AC78</f>
         <v>48787</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="143" t="s">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="143" t="s">
         <v>213</v>
       </c>
-      <c r="C45" s="144">
-        <f>C43/C44</f>
-        <v>171.70850800265185</v>
-      </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="251" t="s">
-        <v>214</v>
-      </c>
-      <c r="C47" s="251"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C48" s="64">
-        <f>L6</f>
-        <v>3108200.4906887901</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C49" s="137">
-        <f>Overview!C29</f>
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B50" s="39" t="s">
-        <v>216</v>
-      </c>
-      <c r="C50" s="106">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C51" s="24">
-        <f>L18</f>
-        <v>56000.505465443181</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C52" s="24">
-        <f>(C48*C50)/C51</f>
-        <v>222.01231684287563</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="143" t="s">
-        <v>213</v>
-      </c>
-      <c r="C53" s="144">
-        <f>C52/(1+C49)^5</f>
-        <v>125.97575087695434</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="251" t="s">
-        <v>332</v>
-      </c>
-      <c r="C55" s="251"/>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C56" s="64">
-        <f>L8</f>
-        <v>536138.75843800372</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C57" s="137">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B58" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="C58" s="106">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C59" s="24">
-        <f>(C56*C58)</f>
-        <v>11795052.685636081</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C60" s="24">
-        <f>C59/(1+C57)^5-G30+G31</f>
-        <v>8275354.6808114005</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C61" s="89">
-        <f>Statement!AC78</f>
-        <v>48787</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="143" t="s">
-        <v>213</v>
-      </c>
-      <c r="C62" s="144">
-        <f>C60/C61</f>
-        <v>169.62212640275894</v>
+      <c r="C67" s="144">
+        <f>C65/C66</f>
+        <v>198.15064834507967</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -23710,8 +23784,8 @@
         <v>221</v>
       </c>
       <c r="C6" s="135">
-        <f>Multiples!C45</f>
-        <v>171.70850800265185</v>
+        <f>Multiples!C47</f>
+        <v>200.23702994497253</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23719,7 +23793,7 @@
         <v>222</v>
       </c>
       <c r="C7" s="135">
-        <f>Multiples!C53</f>
+        <f>Multiples!C55</f>
         <v>125.97575087695434</v>
       </c>
     </row>
@@ -23728,8 +23802,8 @@
         <v>333</v>
       </c>
       <c r="C8" s="135">
-        <f>Multiples!C62</f>
-        <v>169.62212640275894</v>
+        <f>Multiples!C67</f>
+        <v>198.15064834507967</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23738,7 +23812,7 @@
       </c>
       <c r="C9" s="144">
         <f>AVERAGE(C5:C8)</f>
-        <v>147.93282798351726</v>
+        <v>162.19708895467761</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23747,7 +23821,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>125.76</v>
+        <v>133.29</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23756,7 +23830,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.17631065508521987</v>
+        <v>0.21687365109668857</v>
       </c>
     </row>
   </sheetData>
@@ -24115,7 +24189,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>125.76</v>
+        <v>133.29</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24181,7 +24255,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>5859535.6800000006</v>
+        <v>6210380.9699999997</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24208,7 +24282,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>4467714.6800000006</v>
+        <v>4818559.97</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -31356,7 +31430,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>125.76</v>
+        <v>133.29</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31403,7 +31477,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>125.76</v>
+        <v>133.29</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32513,7 +32587,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>37.090814138040948</v>
+        <v>39.311662026554366</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32550,7 +32624,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>5.5922547639428393</v>
+        <v>5.927096354054874</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32587,7 +32661,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.2101503415809001</v>
+        <v>4.4622371106020848</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32624,7 +32698,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6135453.1200000001</v>
+        <v>6502819.2299999995</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32661,7 +32735,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="145">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>4743632.12</v>
+        <v>5110998.2299999995</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32698,7 +32772,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="185">
         <f ca="1">AC150/AC5</f>
-        <v>4.3170513272049025</v>
+        <v>4.6513812905380618</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32735,7 +32809,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="185">
         <f ca="1">AC150/AC12</f>
-        <v>30.31016734503492</v>
+        <v>32.657509632403212</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32870,7 +32944,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="98">AC149/AC153</f>
-        <v>23.228738358093683</v>
+        <v>24.619581232111216</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32907,7 +32981,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="98"/>
-        <v>25.391180489330232</v>
+        <v>27.357576484783845</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32944,7 +33018,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="101">AC153/AC149</f>
-        <v>4.3050121129439907E-2</v>
+        <v>4.0618075123702926E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -32981,7 +33055,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.6960853333612422E-2</v>
+        <v>2.5437744131105847E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33055,7 +33129,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="156">
         <f ca="1">-AC63/AC149</f>
-        <v>3.9656402753184107E-3</v>
+        <v>3.7416079302576588E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33092,7 +33166,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="156">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>3.9656402753184107E-3</v>
+        <v>3.7416079302576588E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33595,7 +33669,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="156">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.22684893401972567</v>
+        <v>0.21403347544692553</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -35485,7 +35559,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>125.76</v>
+        <v>133.29</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -35501,7 +35575,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>6135453.1200000001</v>
+        <v>6502819.2299999995</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35521,7 +35595,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>4743632.12</v>
+        <v>5110998.2299999995</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35541,7 +35615,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>37.090814138040948</v>
+        <v>39.311662026554366</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>252</v>
@@ -35561,7 +35635,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>5.5922547639428393</v>
+        <v>5.927096354054874</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>253</v>
@@ -35581,7 +35655,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>4.2101503415809001</v>
+        <v>4.4622371106020848</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35601,7 +35675,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.3170513272049025</v>
+        <v>4.6513812905380618</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35610,7 +35684,7 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>30.31016734503492</v>
+        <v>32.657509632403212</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35846,7 +35920,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.6960853333612422E-2</v>
+        <v>2.5437744131105847E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>279</v>
@@ -35862,7 +35936,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC157</f>
-        <v>4.3050121129439907E-2</v>
+        <v>4.0618075123702926E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>281</v>
@@ -35894,7 +35968,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>3.9656402753184107E-3</v>
+        <v>3.7416079302576588E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35903,7 +35977,7 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>3.9656402753184107E-3</v>
+        <v>3.7416079302576588E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -35947,7 +36021,7 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC172</f>
-        <v>0.22684893401972567</v>
+        <v>0.21403347544692553</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -36126,7 +36200,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>125.76</v>
+        <v>133.29</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36155,7 +36229,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>6135453.1200000001</v>
+        <v>6502819.2299999995</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36184,7 +36258,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>4743632.12</v>
+        <v>5110998.2299999995</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36213,7 +36287,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>37.090814138040948</v>
+        <v>39.311662026554366</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36242,7 +36316,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>5.5922547639428393</v>
+        <v>5.927096354054874</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36271,7 +36345,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>4.2101503415809001</v>
+        <v>4.4622371106020848</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36300,7 +36374,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.3170513272049025</v>
+        <v>4.6513812905380618</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36329,7 +36403,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>30.31016734503492</v>
+        <v>32.657509632403212</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37102,7 +37176,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.6960853333612422E-2</v>
+        <v>2.5437744131105847E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37131,7 +37205,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC157</f>
-        <v>4.3050121129439907E-2</v>
+        <v>4.0618075123702926E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37189,7 +37263,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>3.9656402753184107E-3</v>
+        <v>3.7416079302576588E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37218,7 +37292,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>3.9656402753184107E-3</v>
+        <v>3.7416079302576588E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37454,7 +37528,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC172</f>
-        <v>0.22684893401972567</v>
+        <v>0.21403347544692553</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0867F2A0-22F9-E048-9D96-4555B7CAB6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6AC14A-4D74-7A49-AE65-8199733201CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -128,28 +128,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -159,21 +138,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -13028,7 +12998,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c2mtim&amp;q=XNAS%3aDUOL&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -13047,9 +13017,11 @@
     <v>Powered by Refinitiv</v>
     <v>468</v>
     <v>87.89</v>
-    <v>0.87490000000000001</v>
-    <v>3.57</v>
-    <v>2.7521E-2</v>
+    <v>0.87570000000000003</v>
+    <v>-5.19</v>
+    <v>-3.9938000000000001E-2</v>
+    <v>0.24</v>
+    <v>1.9239999999999999E-3</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13057,49 +13029,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>135</v>
+    <v>133.5</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46210.767281990622</v>
+    <v>46213.879717210155</v>
     <v>0</v>
-    <v>131.41419999999999</v>
-    <v>6210396964</v>
+    <v>124.64</v>
+    <v>5812957651</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>132.96</v>
-    <v>15.425800000000001</v>
-    <v>129.72</v>
-    <v>133.29</v>
+    <v>132.19999999999999</v>
+    <v>14.438599999999999</v>
+    <v>129.94999999999999</v>
+    <v>124.76</v>
+    <v>125</v>
     <v>46593120</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>645874</v>
-    <v>1578635</v>
+    <v>625845</v>
+    <v>1498108</v>
     <v>2011</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -13113,28 +13071,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.06</v>
-    <v>-1.338E-3</v>
+    <v>-0.3</v>
+    <v>-6.5659999999999998E-3</v>
     <v>US</v>
-    <v>44.91</v>
+    <v>45.81</v>
     <v>Index</v>
-    <v>6</v>
-    <v>44.57</v>
+    <v>3</v>
+    <v>45.29</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.57</v>
-    <v>44.85</v>
-    <v>44.79</v>
+    <v>45.77</v>
+    <v>45.69</v>
+    <v>45.39</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13156,6 +13114,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13176,6 +13136,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13185,11 +13146,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13225,7 +13181,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13236,13 +13192,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13336,13 +13295,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13414,6 +13379,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13421,6 +13389,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13931,7 +13902,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC149</f>
-        <v>6502819.2299999995</v>
+        <v>6086666.1200000001</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -13955,7 +13926,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>5110998.2299999995</v>
+        <v>4694845.12</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -13972,7 +13943,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>133.29</v>
+        <v>124.76</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>252</v>
@@ -13994,16 +13965,16 @@
       <c r="B6" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="210" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="210" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>125</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>246</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC146</f>
-        <v>39.311662026554366</v>
+        <v>36.795880819513265</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -14020,14 +13991,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>3.57</v>
+        <v>-5.19</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC147</f>
-        <v>5.927096354054874</v>
+        <v>5.5477870892931662</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -14042,16 +14013,16 @@
       <c r="B8" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0.24</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>274</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC157</f>
-        <v>4.0618075123702926E-2</v>
+        <v>4.3395184620378023E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -14059,7 +14030,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.21687365109668857</v>
+        <v>0.30007285151232449</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14068,30 +14039,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.7521E-2</v>
+        <v>-3.9938000000000001E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>297</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC158</f>
-        <v>2.5437744131105847E-2</v>
+        <v>2.7176955075625987E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>1.9239999999999999E-3</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>302</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC160</f>
-        <v>3.7416079302576588E-3</v>
+        <v>3.9974264269320558E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -14132,7 +14103,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.87490000000000001</v>
+        <v>0.87570000000000003</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>104</v>
@@ -14148,7 +14119,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1578635</v>
+        <v>1498108</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>105</v>
@@ -14164,7 +14135,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC172</f>
-        <v>0.21403347544692553</v>
+        <v>0.2286672165944269</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14269,12 +14240,12 @@
       <c r="C26" s="172">
         <v>0.21</v>
       </c>
-      <c r="E26" s="187" t="e" vm="5">
+      <c r="E26" s="187" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.79</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14289,7 +14260,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.539E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -21922,7 +21893,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>133.29</v>
+        <v>124.76</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21931,7 +21902,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>6502819.2299999995</v>
+        <v>6086666.1200000001</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21949,7 +21920,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.539E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21958,7 +21929,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>0.87490000000000001</v>
+        <v>0.87570000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22028,7 +21999,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.4160499999999999E-2</v>
+        <v>8.4796499999999997E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22037,7 +22008,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.4160499999999999E-2</v>
+        <v>8.4796499999999997E-2</v>
       </c>
     </row>
   </sheetData>
@@ -23821,7 +23792,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>133.29</v>
+        <v>124.76</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23830,7 +23801,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.21687365109668857</v>
+        <v>0.30007285151232449</v>
       </c>
     </row>
   </sheetData>
@@ -24189,7 +24160,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>133.29</v>
+        <v>124.76</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24255,7 +24226,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>6210380.9699999997</v>
+        <v>5812942.6800000006</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24282,7 +24253,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>4818559.97</v>
+        <v>4421121.6800000006</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -31430,7 +31401,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>133.29</v>
+        <v>124.76</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31477,7 +31448,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>133.29</v>
+        <v>124.76</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32587,7 +32558,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>39.311662026554366</v>
+        <v>36.795880819513265</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32624,7 +32595,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>5.927096354054874</v>
+        <v>5.5477870892931662</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32661,7 +32632,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.4622371106020848</v>
+        <v>4.1766726830123497</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32698,7 +32669,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6502819.2299999995</v>
+        <v>6086666.1200000001</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32735,7 +32706,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="145">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>5110998.2299999995</v>
+        <v>4694845.12</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32772,7 +32743,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="185">
         <f ca="1">AC150/AC5</f>
-        <v>4.6513812905380618</v>
+        <v>4.2726515976785864</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32809,7 +32780,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="185">
         <f ca="1">AC150/AC12</f>
-        <v>32.657509632403212</v>
+        <v>29.998435301559716</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32944,7 +32915,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f t="shared" ref="AC155:AC156" ca="1" si="98">AC149/AC153</f>
-        <v>24.619581232111216</v>
+        <v>23.044031469113929</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32981,7 +32952,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
         <f t="shared" ca="1" si="98"/>
-        <v>27.357576484783845</v>
+        <v>25.13003892286893</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33018,7 +32989,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
         <f t="shared" ref="AC157" ca="1" si="101">AC153/AC149</f>
-        <v>4.0618075123702926E-2</v>
+        <v>4.3395184620378023E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33055,7 +33026,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.5437744131105847E-2</v>
+        <v>2.7176955075625987E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33129,7 +33100,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="156">
         <f ca="1">-AC63/AC149</f>
-        <v>3.7416079302576588E-3</v>
+        <v>3.9974264269320558E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33166,7 +33137,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="156">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>3.7416079302576588E-3</v>
+        <v>3.9974264269320558E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33669,7 +33640,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="156">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.21403347544692553</v>
+        <v>0.2286672165944269</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -35559,7 +35530,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>133.29</v>
+        <v>124.76</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -35575,7 +35546,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>6502819.2299999995</v>
+        <v>6086666.1200000001</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35595,7 +35566,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>5110998.2299999995</v>
+        <v>4694845.12</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35615,7 +35586,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>39.311662026554366</v>
+        <v>36.795880819513265</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>252</v>
@@ -35635,7 +35606,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>5.927096354054874</v>
+        <v>5.5477870892931662</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>253</v>
@@ -35655,7 +35626,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>4.4622371106020848</v>
+        <v>4.1766726830123497</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35675,7 +35646,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.6513812905380618</v>
+        <v>4.2726515976785864</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35684,7 +35655,7 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>32.657509632403212</v>
+        <v>29.998435301559716</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35920,7 +35891,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.5437744131105847E-2</v>
+        <v>2.7176955075625987E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>279</v>
@@ -35936,7 +35907,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC157</f>
-        <v>4.0618075123702926E-2</v>
+        <v>4.3395184620378023E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>281</v>
@@ -35968,7 +35939,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>3.7416079302576588E-3</v>
+        <v>3.9974264269320558E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35977,7 +35948,7 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>3.7416079302576588E-3</v>
+        <v>3.9974264269320558E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -36021,7 +35992,7 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC172</f>
-        <v>0.21403347544692553</v>
+        <v>0.2286672165944269</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -36200,7 +36171,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>133.29</v>
+        <v>124.76</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36229,7 +36200,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>6502819.2299999995</v>
+        <v>6086666.1200000001</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36258,7 +36229,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>5110998.2299999995</v>
+        <v>4694845.12</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36287,7 +36258,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>39.311662026554366</v>
+        <v>36.795880819513265</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36316,7 +36287,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>5.927096354054874</v>
+        <v>5.5477870892931662</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36345,7 +36316,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>4.4622371106020848</v>
+        <v>4.1766726830123497</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36374,7 +36345,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.6513812905380618</v>
+        <v>4.2726515976785864</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36403,7 +36374,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>32.657509632403212</v>
+        <v>29.998435301559716</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37176,7 +37147,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.5437744131105847E-2</v>
+        <v>2.7176955075625987E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37205,7 +37176,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC157</f>
-        <v>4.0618075123702926E-2</v>
+        <v>4.3395184620378023E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37263,7 +37234,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>3.7416079302576588E-3</v>
+        <v>3.9974264269320558E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37292,7 +37263,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>3.7416079302576588E-3</v>
+        <v>3.9974264269320558E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37528,7 +37499,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC172</f>
-        <v>0.21403347544692553</v>
+        <v>0.2286672165944269</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6AC14A-4D74-7A49-AE65-8199733201CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81EEB74-F56D-A84D-8813-2275A2E87C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -32,10 +32,12 @@
     <sheet name="DCF" sheetId="11" r:id="rId17"/>
     <sheet name="Multiples" sheetId="12" r:id="rId18"/>
     <sheet name="AVG target price" sheetId="13" r:id="rId19"/>
-    <sheet name="Reverse DCF" sheetId="14" r:id="rId20"/>
+    <sheet name="DDM" sheetId="21" r:id="rId20"/>
+    <sheet name="Reverse DCF" sheetId="14" r:id="rId21"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId21"/>
+    <externalReference r:id="rId22"/>
+    <externalReference r:id="rId23"/>
   </externalReferences>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -150,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="434">
   <si>
     <t>Ticker</t>
   </si>
@@ -1419,6 +1421,39 @@
   </si>
   <si>
     <t>Deloitte</t>
+  </si>
+  <si>
+    <t>Manual Cost of Equity</t>
+  </si>
+  <si>
+    <t>Dividend discount model</t>
+  </si>
+  <si>
+    <t>Dividend per share</t>
+  </si>
+  <si>
+    <t>Ratios</t>
+  </si>
+  <si>
+    <t>Payout</t>
+  </si>
+  <si>
+    <t>DDM valuation</t>
+  </si>
+  <si>
+    <t>Latest dividend</t>
+  </si>
+  <si>
+    <t>Year 1 growth rate</t>
+  </si>
+  <si>
+    <t>Year 1 dividend</t>
+  </si>
+  <si>
+    <t>Perpetual dividend growth</t>
+  </si>
+  <si>
+    <t>DDM price</t>
   </si>
 </sst>
 </file>
@@ -2030,7 +2065,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="269">
+  <cellXfs count="274">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2358,9 +2393,6 @@
     <xf numFmtId="2" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2368,6 +2400,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2379,10 +2420,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2392,12 +2433,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2412,6 +2447,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12888,6 +12928,95 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="Financials -&gt;"/>
+      <sheetName val="Statement"/>
+      <sheetName val="Analysis -&gt;"/>
+      <sheetName val="Basic"/>
+      <sheetName val="Yearly Analysis"/>
+      <sheetName val="Quarter analysis"/>
+      <sheetName val="Graphs Year"/>
+      <sheetName val="Graphs Quarter"/>
+      <sheetName val="Forecast -&gt;"/>
+      <sheetName val="Revenue"/>
+      <sheetName val="COGS &amp; OpEx"/>
+      <sheetName val="WC &amp; Investments"/>
+      <sheetName val="FCF &amp; Other"/>
+      <sheetName val="Valuation -&gt;"/>
+      <sheetName val="WACC"/>
+      <sheetName val="DCF"/>
+      <sheetName val="Multiples"/>
+      <sheetName val="AVG target price"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Reverse DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10">
+        <row r="5">
+          <cell r="C5">
+            <v>2021</v>
+          </cell>
+          <cell r="D5">
+            <v>2022</v>
+          </cell>
+          <cell r="E5">
+            <v>2023</v>
+          </cell>
+          <cell r="F5">
+            <v>2024</v>
+          </cell>
+          <cell r="G5">
+            <v>2025</v>
+          </cell>
+          <cell r="H5">
+            <v>2026</v>
+          </cell>
+          <cell r="I5">
+            <v>2027</v>
+          </cell>
+          <cell r="J5">
+            <v>2028</v>
+          </cell>
+          <cell r="K5">
+            <v>2029</v>
+          </cell>
+          <cell r="L5">
+            <v>2030</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="adi dumitras" id="{A0F62302-F8D3-B346-B5DF-839B413AE710}" userId="b24535bb88af1c42" providerId="Windows Live"/>
@@ -13017,7 +13146,7 @@
     <v>Powered by Refinitiv</v>
     <v>468</v>
     <v>87.89</v>
-    <v>0.87570000000000003</v>
+    <v>0.87980000000000003</v>
     <v>-5.19</v>
     <v>-3.9938000000000001E-2</v>
     <v>0.24</v>
@@ -13032,21 +13161,21 @@
     <v>133.5</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46213.879717210155</v>
+    <v>46213.999535219533</v>
     <v>0</v>
     <v>124.64</v>
     <v>5812957651</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
     <v>132.19999999999999</v>
-    <v>14.438599999999999</v>
+    <v>15.039400000000001</v>
     <v>129.94999999999999</v>
     <v>124.76</v>
     <v>125</v>
     <v>46593120</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>625845</v>
+    <v>634743</v>
     <v>1498108</v>
     <v>2011</v>
   </rv>
@@ -13071,17 +13200,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.3</v>
-    <v>-6.5659999999999998E-3</v>
+    <v>0.3</v>
+    <v>6.6090000000000003E-3</v>
     <v>US</v>
-    <v>45.81</v>
+    <v>45.71</v>
     <v>Index</v>
     <v>3</v>
-    <v>45.29</v>
+    <v>45.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.77</v>
+    <v>45.41</v>
+    <v>45.39</v>
     <v>45.69</v>
-    <v>45.39</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13303,9 +13432,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13876,18 +14005,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="252" t="s">
+      <c r="B2" s="251" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="253"/>
-      <c r="E2" s="252" t="s">
+      <c r="C2" s="252"/>
+      <c r="E2" s="251" t="s">
         <v>296</v>
       </c>
-      <c r="F2" s="253"/>
-      <c r="H2" s="252" t="s">
+      <c r="F2" s="252"/>
+      <c r="H2" s="251" t="s">
         <v>338</v>
       </c>
-      <c r="I2" s="253"/>
+      <c r="I2" s="252"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -14064,6 +14193,13 @@
         <f ca="1">Statement!AC160</f>
         <v>3.9974264269320558E-3</v>
       </c>
+      <c r="H10" s="186" t="s">
+        <v>433</v>
+      </c>
+      <c r="I10" s="214">
+        <f>DDM!C26</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="187" t="s">
@@ -14103,7 +14239,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.87570000000000003</v>
+        <v>0.87980000000000003</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>104</v>
@@ -14148,10 +14284,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="254" t="s">
+      <c r="B17" s="253" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="254"/>
+      <c r="C17" s="253"/>
       <c r="E17" s="186" t="s">
         <v>305</v>
       </c>
@@ -14224,14 +14360,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="254" t="s">
+      <c r="B25" s="253" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="254"/>
-      <c r="E25" s="252" t="s">
+      <c r="C25" s="253"/>
+      <c r="E25" s="251" t="s">
         <v>353</v>
       </c>
-      <c r="F25" s="253"/>
+      <c r="F25" s="252"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -14245,7 +14381,7 @@
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.39</v>
+        <v>45.69</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14260,7 +14396,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.539E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14273,22 +14409,22 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="186" t="s">
-        <v>359</v>
+        <v>423</v>
       </c>
       <c r="C29" s="223">
         <v>0.12</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="251" t="s">
+      <c r="B33" s="254" t="s">
         <v>348</v>
       </c>
-      <c r="C33" s="251"/>
-      <c r="D33" s="251"/>
-      <c r="E33" s="251"/>
-      <c r="F33" s="251"/>
-      <c r="G33" s="251"/>
-      <c r="H33" s="251"/>
+      <c r="C33" s="254"/>
+      <c r="D33" s="254"/>
+      <c r="E33" s="254"/>
+      <c r="F33" s="254"/>
+      <c r="G33" s="254"/>
+      <c r="H33" s="254"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14307,24 +14443,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="251"/>
-      <c r="C39" s="251"/>
-      <c r="D39" s="251"/>
-      <c r="E39" s="251"/>
-      <c r="F39" s="251"/>
-      <c r="G39" s="251"/>
-      <c r="H39" s="251"/>
+      <c r="B39" s="254"/>
+      <c r="C39" s="254"/>
+      <c r="D39" s="254"/>
+      <c r="E39" s="254"/>
+      <c r="F39" s="254"/>
+      <c r="G39" s="254"/>
+      <c r="H39" s="254"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="251" t="s">
+      <c r="B42" s="254" t="s">
         <v>351</v>
       </c>
-      <c r="C42" s="251"/>
-      <c r="D42" s="251"/>
-      <c r="E42" s="251"/>
-      <c r="F42" s="251"/>
-      <c r="G42" s="251"/>
-      <c r="H42" s="251"/>
+      <c r="C42" s="254"/>
+      <c r="D42" s="254"/>
+      <c r="E42" s="254"/>
+      <c r="F42" s="254"/>
+      <c r="G42" s="254"/>
+      <c r="H42" s="254"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14339,24 +14475,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="251"/>
-      <c r="C49" s="251"/>
-      <c r="D49" s="251"/>
-      <c r="E49" s="251"/>
-      <c r="F49" s="251"/>
-      <c r="G49" s="251"/>
-      <c r="H49" s="251"/>
+      <c r="B49" s="254"/>
+      <c r="C49" s="254"/>
+      <c r="D49" s="254"/>
+      <c r="E49" s="254"/>
+      <c r="F49" s="254"/>
+      <c r="G49" s="254"/>
+      <c r="H49" s="254"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="251" t="s">
+      <c r="B52" s="254" t="s">
         <v>109</v>
       </c>
-      <c r="C52" s="251"/>
-      <c r="D52" s="251"/>
-      <c r="E52" s="251"/>
-      <c r="F52" s="251"/>
-      <c r="G52" s="251"/>
-      <c r="H52" s="251"/>
+      <c r="C52" s="254"/>
+      <c r="D52" s="254"/>
+      <c r="E52" s="254"/>
+      <c r="F52" s="254"/>
+      <c r="G52" s="254"/>
+      <c r="H52" s="254"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="41" t="s">
@@ -14427,28 +14563,28 @@
       </c>
     </row>
     <row r="65" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="251"/>
-      <c r="C65" s="251"/>
-      <c r="D65" s="251"/>
-      <c r="E65" s="251"/>
-      <c r="F65" s="251"/>
-      <c r="G65" s="251"/>
-      <c r="H65" s="251"/>
+      <c r="B65" s="254"/>
+      <c r="C65" s="254"/>
+      <c r="D65" s="254"/>
+      <c r="E65" s="254"/>
+      <c r="F65" s="254"/>
+      <c r="G65" s="254"/>
+      <c r="H65" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B65:H65"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14518,36 +14654,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="251" t="s">
+      <c r="S2" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="251"/>
-      <c r="U2" s="251"/>
-      <c r="V2" s="251"/>
-      <c r="W2" s="251"/>
-      <c r="X2" s="251"/>
-      <c r="Y2" s="251"/>
-      <c r="Z2" s="251"/>
-      <c r="AA2" s="251" t="s">
+      <c r="T2" s="254"/>
+      <c r="U2" s="254"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="254"/>
+      <c r="X2" s="254"/>
+      <c r="Y2" s="254"/>
+      <c r="Z2" s="254"/>
+      <c r="AA2" s="254" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="251"/>
-      <c r="AC2" s="251"/>
+      <c r="AB2" s="254"/>
+      <c r="AC2" s="254"/>
       <c r="AE2" s="86" t="s">
         <v>85</v>
       </c>
@@ -14558,32 +14694,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="262" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="261" t="s">
+      <c r="S4" s="263" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
-      <c r="AA4" s="262"/>
-      <c r="AB4" s="262"/>
-      <c r="AC4" s="262"/>
+      <c r="T4" s="264"/>
+      <c r="U4" s="264"/>
+      <c r="V4" s="264"/>
+      <c r="W4" s="264"/>
+      <c r="X4" s="264"/>
+      <c r="Y4" s="264"/>
+      <c r="Z4" s="264"/>
+      <c r="AA4" s="264"/>
+      <c r="AB4" s="264"/>
+      <c r="AC4" s="264"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15271,33 +15407,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="260" t="s">
+      <c r="C13" s="262" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="260"/>
-      <c r="E13" s="260"/>
-      <c r="F13" s="260"/>
-      <c r="G13" s="260"/>
-      <c r="H13" s="260"/>
-      <c r="I13" s="260"/>
-      <c r="J13" s="260"/>
-      <c r="K13" s="260"/>
-      <c r="L13" s="260"/>
+      <c r="D13" s="262"/>
+      <c r="E13" s="262"/>
+      <c r="F13" s="262"/>
+      <c r="G13" s="262"/>
+      <c r="H13" s="262"/>
+      <c r="I13" s="262"/>
+      <c r="J13" s="262"/>
+      <c r="K13" s="262"/>
+      <c r="L13" s="262"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="261" t="s">
+      <c r="S13" s="263" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="262"/>
-      <c r="U13" s="262"/>
-      <c r="V13" s="262"/>
-      <c r="W13" s="262"/>
-      <c r="X13" s="262"/>
-      <c r="Y13" s="262"/>
-      <c r="Z13" s="262"/>
-      <c r="AA13" s="262"/>
-      <c r="AB13" s="262"/>
-      <c r="AC13" s="262"/>
+      <c r="T13" s="264"/>
+      <c r="U13" s="264"/>
+      <c r="V13" s="264"/>
+      <c r="W13" s="264"/>
+      <c r="X13" s="264"/>
+      <c r="Y13" s="264"/>
+      <c r="Z13" s="264"/>
+      <c r="AA13" s="264"/>
+      <c r="AB13" s="264"/>
+      <c r="AC13" s="264"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -15906,33 +16042,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="260" t="s">
+      <c r="C23" s="262" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="260"/>
-      <c r="E23" s="260"/>
-      <c r="F23" s="260"/>
-      <c r="G23" s="260"/>
-      <c r="H23" s="260"/>
-      <c r="I23" s="260"/>
-      <c r="J23" s="260"/>
-      <c r="K23" s="260"/>
-      <c r="L23" s="260"/>
+      <c r="D23" s="262"/>
+      <c r="E23" s="262"/>
+      <c r="F23" s="262"/>
+      <c r="G23" s="262"/>
+      <c r="H23" s="262"/>
+      <c r="I23" s="262"/>
+      <c r="J23" s="262"/>
+      <c r="K23" s="262"/>
+      <c r="L23" s="262"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="261" t="s">
+      <c r="S23" s="263" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="262"/>
-      <c r="U23" s="262"/>
-      <c r="V23" s="262"/>
-      <c r="W23" s="262"/>
-      <c r="X23" s="262"/>
-      <c r="Y23" s="262"/>
-      <c r="Z23" s="262"/>
-      <c r="AA23" s="262"/>
-      <c r="AB23" s="262"/>
-      <c r="AC23" s="262"/>
+      <c r="T23" s="264"/>
+      <c r="U23" s="264"/>
+      <c r="V23" s="264"/>
+      <c r="W23" s="264"/>
+      <c r="X23" s="264"/>
+      <c r="Y23" s="264"/>
+      <c r="Z23" s="264"/>
+      <c r="AA23" s="264"/>
+      <c r="AB23" s="264"/>
+      <c r="AC23" s="264"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17251,32 +17387,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="260" t="s">
+      <c r="C40" s="262" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="260"/>
-      <c r="E40" s="260"/>
-      <c r="F40" s="260"/>
-      <c r="G40" s="260"/>
-      <c r="H40" s="260"/>
-      <c r="I40" s="260"/>
-      <c r="J40" s="260"/>
-      <c r="K40" s="260"/>
-      <c r="L40" s="260"/>
+      <c r="D40" s="262"/>
+      <c r="E40" s="262"/>
+      <c r="F40" s="262"/>
+      <c r="G40" s="262"/>
+      <c r="H40" s="262"/>
+      <c r="I40" s="262"/>
+      <c r="J40" s="262"/>
+      <c r="K40" s="262"/>
+      <c r="L40" s="262"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="261" t="s">
+      <c r="S40" s="263" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="262"/>
-      <c r="U40" s="262"/>
-      <c r="V40" s="262"/>
-      <c r="W40" s="262"/>
-      <c r="X40" s="262"/>
-      <c r="Y40" s="262"/>
-      <c r="Z40" s="262"/>
-      <c r="AA40" s="262"/>
-      <c r="AB40" s="262"/>
-      <c r="AC40" s="262"/>
+      <c r="T40" s="264"/>
+      <c r="U40" s="264"/>
+      <c r="V40" s="264"/>
+      <c r="W40" s="264"/>
+      <c r="X40" s="264"/>
+      <c r="Y40" s="264"/>
+      <c r="Z40" s="264"/>
+      <c r="AA40" s="264"/>
+      <c r="AB40" s="264"/>
+      <c r="AC40" s="264"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -17843,18 +17979,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="S13:AC13"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="S23:AC23"/>
+    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="S40:AC40"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="S13:AC13"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="S23:AC23"/>
-    <mergeCell ref="C40:L40"/>
-    <mergeCell ref="S40:AC40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17888,35 +18024,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
-      <c r="P2" s="251" t="s">
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
+      <c r="P2" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="251"/>
-      <c r="R2" s="251"/>
-      <c r="S2" s="251"/>
-      <c r="T2" s="251"/>
-      <c r="U2" s="251"/>
-      <c r="V2" s="251"/>
-      <c r="W2" s="251"/>
-      <c r="X2" s="251" t="s">
+      <c r="Q2" s="254"/>
+      <c r="R2" s="254"/>
+      <c r="S2" s="254"/>
+      <c r="T2" s="254"/>
+      <c r="U2" s="254"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="254"/>
+      <c r="X2" s="254" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="251"/>
-      <c r="Z2" s="251"/>
+      <c r="Y2" s="254"/>
+      <c r="Z2" s="254"/>
       <c r="AB2" s="86" t="s">
         <v>115</v>
       </c>
@@ -17925,31 +18061,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="262" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
-      <c r="P4" s="262" t="s">
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
+      <c r="P4" s="264" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="262"/>
-      <c r="R4" s="262"/>
-      <c r="S4" s="262"/>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
+      <c r="Q4" s="264"/>
+      <c r="R4" s="264"/>
+      <c r="S4" s="264"/>
+      <c r="T4" s="264"/>
+      <c r="U4" s="264"/>
+      <c r="V4" s="264"/>
+      <c r="W4" s="264"/>
+      <c r="X4" s="264"/>
+      <c r="Y4" s="264"/>
+      <c r="Z4" s="264"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18144,32 +18280,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="260" t="s">
+      <c r="C9" s="262" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="E9" s="260"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260"/>
-      <c r="H9" s="260"/>
-      <c r="I9" s="260"/>
-      <c r="J9" s="260"/>
-      <c r="K9" s="260"/>
-      <c r="L9" s="260"/>
+      <c r="D9" s="262"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="262"/>
+      <c r="G9" s="262"/>
+      <c r="H9" s="262"/>
+      <c r="I9" s="262"/>
+      <c r="J9" s="262"/>
+      <c r="K9" s="262"/>
+      <c r="L9" s="262"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="262" t="s">
+      <c r="P9" s="264" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="262"/>
-      <c r="R9" s="262"/>
-      <c r="S9" s="262"/>
-      <c r="T9" s="262"/>
-      <c r="U9" s="262"/>
-      <c r="V9" s="262"/>
-      <c r="W9" s="262"/>
-      <c r="X9" s="262"/>
-      <c r="Y9" s="262"/>
-      <c r="Z9" s="262"/>
+      <c r="Q9" s="264"/>
+      <c r="R9" s="264"/>
+      <c r="S9" s="264"/>
+      <c r="T9" s="264"/>
+      <c r="U9" s="264"/>
+      <c r="V9" s="264"/>
+      <c r="W9" s="264"/>
+      <c r="X9" s="264"/>
+      <c r="Y9" s="264"/>
+      <c r="Z9" s="264"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -18739,31 +18875,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="262" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
-      <c r="P18" s="262" t="s">
+      <c r="D18" s="262"/>
+      <c r="E18" s="262"/>
+      <c r="F18" s="262"/>
+      <c r="G18" s="262"/>
+      <c r="H18" s="262"/>
+      <c r="I18" s="262"/>
+      <c r="J18" s="262"/>
+      <c r="K18" s="262"/>
+      <c r="L18" s="262"/>
+      <c r="P18" s="264" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="262"/>
-      <c r="R18" s="262"/>
-      <c r="S18" s="262"/>
-      <c r="T18" s="262"/>
-      <c r="U18" s="262"/>
-      <c r="V18" s="262"/>
-      <c r="W18" s="262"/>
-      <c r="X18" s="262"/>
-      <c r="Y18" s="262"/>
-      <c r="Z18" s="262"/>
+      <c r="Q18" s="264"/>
+      <c r="R18" s="264"/>
+      <c r="S18" s="264"/>
+      <c r="T18" s="264"/>
+      <c r="U18" s="264"/>
+      <c r="V18" s="264"/>
+      <c r="W18" s="264"/>
+      <c r="X18" s="264"/>
+      <c r="Y18" s="264"/>
+      <c r="Z18" s="264"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19323,20 +19459,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="251" t="s">
+      <c r="C3" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="251"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="264" t="s">
+      <c r="D3" s="254"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="251"/>
-      <c r="J3" s="251"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="251"/>
+      <c r="I3" s="254"/>
+      <c r="J3" s="254"/>
+      <c r="K3" s="254"/>
+      <c r="L3" s="254"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -19354,18 +19490,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="262" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -19562,18 +19698,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="262" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="262"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="262"/>
+      <c r="G11" s="262"/>
+      <c r="H11" s="262"/>
+      <c r="I11" s="262"/>
+      <c r="J11" s="262"/>
+      <c r="K11" s="262"/>
+      <c r="L11" s="262"/>
       <c r="N11" s="92"/>
       <c r="P11" s="265"/>
       <c r="Q11" s="265"/>
@@ -19827,18 +19963,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="262" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
+      <c r="D18" s="262"/>
+      <c r="E18" s="262"/>
+      <c r="F18" s="262"/>
+      <c r="G18" s="262"/>
+      <c r="H18" s="262"/>
+      <c r="I18" s="262"/>
+      <c r="J18" s="262"/>
+      <c r="K18" s="262"/>
+      <c r="L18" s="262"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20056,18 +20192,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="260" t="s">
+      <c r="C26" s="262" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="260"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="260"/>
-      <c r="G26" s="260"/>
-      <c r="H26" s="260"/>
-      <c r="I26" s="260"/>
-      <c r="J26" s="260"/>
-      <c r="K26" s="260"/>
-      <c r="L26" s="260"/>
+      <c r="D26" s="262"/>
+      <c r="E26" s="262"/>
+      <c r="F26" s="262"/>
+      <c r="G26" s="262"/>
+      <c r="H26" s="262"/>
+      <c r="I26" s="262"/>
+      <c r="J26" s="262"/>
+      <c r="K26" s="262"/>
+      <c r="L26" s="262"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20259,18 +20395,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="260" t="s">
+      <c r="C33" s="262" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="260"/>
-      <c r="E33" s="260"/>
-      <c r="F33" s="260"/>
-      <c r="G33" s="260"/>
-      <c r="H33" s="260"/>
-      <c r="I33" s="260"/>
-      <c r="J33" s="260"/>
-      <c r="K33" s="260"/>
-      <c r="L33" s="260"/>
+      <c r="D33" s="262"/>
+      <c r="E33" s="262"/>
+      <c r="F33" s="262"/>
+      <c r="G33" s="262"/>
+      <c r="H33" s="262"/>
+      <c r="I33" s="262"/>
+      <c r="J33" s="262"/>
+      <c r="K33" s="262"/>
+      <c r="L33" s="262"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20454,18 +20590,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="260" t="s">
+      <c r="C40" s="262" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="260"/>
-      <c r="E40" s="260"/>
-      <c r="F40" s="260"/>
-      <c r="G40" s="260"/>
-      <c r="H40" s="260"/>
-      <c r="I40" s="260"/>
-      <c r="J40" s="260"/>
-      <c r="K40" s="260"/>
-      <c r="L40" s="260"/>
+      <c r="D40" s="262"/>
+      <c r="E40" s="262"/>
+      <c r="F40" s="262"/>
+      <c r="G40" s="262"/>
+      <c r="H40" s="262"/>
+      <c r="I40" s="262"/>
+      <c r="J40" s="262"/>
+      <c r="K40" s="262"/>
+      <c r="L40" s="262"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20729,6 +20865,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20736,12 +20878,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20779,20 +20915,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
       <c r="S2" s="265"/>
       <c r="T2" s="265"/>
       <c r="U2" s="265"/>
@@ -20810,18 +20946,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="262" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
       <c r="S4" s="265"/>
       <c r="T4" s="265"/>
       <c r="U4" s="265"/>
@@ -21195,18 +21331,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="260" t="s">
+      <c r="C13" s="262" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="260"/>
-      <c r="E13" s="260"/>
-      <c r="F13" s="260"/>
-      <c r="G13" s="260"/>
-      <c r="H13" s="260"/>
-      <c r="I13" s="260"/>
-      <c r="J13" s="260"/>
-      <c r="K13" s="260"/>
-      <c r="L13" s="260"/>
+      <c r="D13" s="262"/>
+      <c r="E13" s="262"/>
+      <c r="F13" s="262"/>
+      <c r="G13" s="262"/>
+      <c r="H13" s="262"/>
+      <c r="I13" s="262"/>
+      <c r="J13" s="262"/>
+      <c r="K13" s="262"/>
+      <c r="L13" s="262"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21299,18 +21435,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="262" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
+      <c r="D18" s="262"/>
+      <c r="E18" s="262"/>
+      <c r="F18" s="262"/>
+      <c r="G18" s="262"/>
+      <c r="H18" s="262"/>
+      <c r="I18" s="262"/>
+      <c r="J18" s="262"/>
+      <c r="K18" s="262"/>
+      <c r="L18" s="262"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21502,18 +21638,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="260" t="s">
+      <c r="C25" s="262" t="s">
         <v>271</v>
       </c>
-      <c r="D25" s="260"/>
-      <c r="E25" s="260"/>
-      <c r="F25" s="260"/>
-      <c r="G25" s="260"/>
-      <c r="H25" s="260"/>
-      <c r="I25" s="260"/>
-      <c r="J25" s="260"/>
-      <c r="K25" s="260"/>
-      <c r="L25" s="260"/>
+      <c r="D25" s="262"/>
+      <c r="E25" s="262"/>
+      <c r="F25" s="262"/>
+      <c r="G25" s="262"/>
+      <c r="H25" s="262"/>
+      <c r="I25" s="262"/>
+      <c r="J25" s="262"/>
+      <c r="K25" s="262"/>
+      <c r="L25" s="262"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21651,18 +21787,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="260" t="s">
+      <c r="C31" s="262" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="260"/>
-      <c r="E31" s="260"/>
-      <c r="F31" s="260"/>
-      <c r="G31" s="260"/>
-      <c r="H31" s="260"/>
-      <c r="I31" s="260"/>
-      <c r="J31" s="260"/>
-      <c r="K31" s="260"/>
-      <c r="L31" s="260"/>
+      <c r="D31" s="262"/>
+      <c r="E31" s="262"/>
+      <c r="F31" s="262"/>
+      <c r="G31" s="262"/>
+      <c r="H31" s="262"/>
+      <c r="I31" s="262"/>
+      <c r="J31" s="262"/>
+      <c r="K31" s="262"/>
+      <c r="L31" s="262"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21801,16 +21937,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21873,10 +22009,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="251" t="s">
+      <c r="B4" s="254" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="251"/>
+      <c r="C4" s="254"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21920,7 +22056,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.539E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21929,7 +22065,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>0.87570000000000003</v>
+        <v>0.87980000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21961,10 +22097,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="251" t="s">
+      <c r="B15" s="254" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="251"/>
+      <c r="C15" s="254"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21999,7 +22135,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.4796499999999997E-2</v>
+        <v>8.5280999999999996E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22008,7 +22144,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.4796499999999997E-2</v>
+        <v>8.5280999999999996E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22053,20 +22189,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="251" t="s">
+      <c r="C3" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="251"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="264" t="s">
+      <c r="D3" s="254"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="251"/>
-      <c r="J3" s="251"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="251"/>
+      <c r="I3" s="254"/>
+      <c r="J3" s="254"/>
+      <c r="K3" s="254"/>
+      <c r="L3" s="254"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -22084,18 +22220,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="262" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -22352,10 +22488,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="251" t="s">
+      <c r="B13" s="254" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="251"/>
+      <c r="C13" s="254"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22375,10 +22511,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="251" t="s">
+      <c r="B18" s="254" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="251"/>
+      <c r="C18" s="254"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22492,37 +22628,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="262" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22711,18 +22847,18 @@
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="260" t="s">
+      <c r="C10" s="262" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="260"/>
-      <c r="E10" s="260"/>
-      <c r="F10" s="260"/>
-      <c r="G10" s="260"/>
-      <c r="H10" s="260"/>
-      <c r="I10" s="260"/>
-      <c r="J10" s="260"/>
-      <c r="K10" s="260"/>
-      <c r="L10" s="260"/>
+      <c r="D10" s="262"/>
+      <c r="E10" s="262"/>
+      <c r="F10" s="262"/>
+      <c r="G10" s="262"/>
+      <c r="H10" s="262"/>
+      <c r="I10" s="262"/>
+      <c r="J10" s="262"/>
+      <c r="K10" s="262"/>
+      <c r="L10" s="262"/>
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22916,18 +23052,18 @@
       <c r="N15" s="92"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="260" t="s">
+      <c r="C16" s="262" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="260"/>
-      <c r="E16" s="260"/>
-      <c r="F16" s="260"/>
-      <c r="G16" s="260"/>
-      <c r="H16" s="260"/>
-      <c r="I16" s="260"/>
-      <c r="J16" s="260"/>
-      <c r="K16" s="260"/>
-      <c r="L16" s="260"/>
+      <c r="D16" s="262"/>
+      <c r="E16" s="262"/>
+      <c r="F16" s="262"/>
+      <c r="G16" s="262"/>
+      <c r="H16" s="262"/>
+      <c r="I16" s="262"/>
+      <c r="J16" s="262"/>
+      <c r="K16" s="262"/>
+      <c r="L16" s="262"/>
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -23061,18 +23197,18 @@
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="260" t="s">
+      <c r="C21" s="262" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="260"/>
-      <c r="E21" s="260"/>
-      <c r="F21" s="260"/>
-      <c r="G21" s="260"/>
-      <c r="H21" s="260"/>
-      <c r="I21" s="260"/>
-      <c r="J21" s="260"/>
-      <c r="K21" s="260"/>
-      <c r="L21" s="260"/>
+      <c r="D21" s="262"/>
+      <c r="E21" s="262"/>
+      <c r="F21" s="262"/>
+      <c r="G21" s="262"/>
+      <c r="H21" s="262"/>
+      <c r="I21" s="262"/>
+      <c r="J21" s="262"/>
+      <c r="K21" s="262"/>
+      <c r="L21" s="262"/>
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -23156,18 +23292,18 @@
       <c r="N25" s="92"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="260" t="s">
+      <c r="C26" s="262" t="s">
         <v>204</v>
       </c>
-      <c r="D26" s="260"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="260"/>
-      <c r="G26" s="260"/>
-      <c r="H26" s="260"/>
-      <c r="I26" s="260"/>
-      <c r="J26" s="260"/>
-      <c r="K26" s="260"/>
-      <c r="L26" s="260"/>
+      <c r="D26" s="262"/>
+      <c r="E26" s="262"/>
+      <c r="F26" s="262"/>
+      <c r="G26" s="262"/>
+      <c r="H26" s="262"/>
+      <c r="I26" s="262"/>
+      <c r="J26" s="262"/>
+      <c r="K26" s="262"/>
+      <c r="L26" s="262"/>
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -23437,10 +23573,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="251" t="s">
+      <c r="B37" s="254" t="s">
         <v>209</v>
       </c>
-      <c r="C37" s="251"/>
+      <c r="C37" s="254"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -23533,10 +23669,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="251" t="s">
+      <c r="B49" s="254" t="s">
         <v>214</v>
       </c>
-      <c r="C49" s="251"/>
+      <c r="C49" s="254"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -23552,7 +23688,7 @@
         <v>359</v>
       </c>
       <c r="C51" s="137">
-        <f>Overview!C29</f>
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
         <v>0.12</v>
       </c>
     </row>
@@ -23592,10 +23728,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="251" t="s">
+      <c r="B57" s="254" t="s">
         <v>332</v>
       </c>
-      <c r="C57" s="251"/>
+      <c r="C57" s="254"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -23735,10 +23871,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="251" t="s">
+      <c r="B4" s="254" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="251"/>
+      <c r="C4" s="254"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23834,6 +23970,477 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8DF3B3F-C42B-D543-BED5-DFA30C21101C}">
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2" style="84" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="10.83203125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="10.83203125" style="1"/>
+    <col min="13" max="14" width="9.5" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="84" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4"/>
+      <c r="B1" s="83" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="4"/>
+      <c r="C2" s="254" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
+        <v>114</v>
+      </c>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
+    </row>
+    <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="87"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="262" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B5" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="12">
+        <f>[2]Revenue!C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D5" s="12">
+        <f>[2]Revenue!D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E5" s="12">
+        <f>[2]Revenue!E5</f>
+        <v>2023</v>
+      </c>
+      <c r="F5" s="12">
+        <f>[2]Revenue!F5</f>
+        <v>2024</v>
+      </c>
+      <c r="G5" s="12">
+        <f>[2]Revenue!G5</f>
+        <v>2025</v>
+      </c>
+      <c r="H5" s="12">
+        <f>[2]Revenue!H5</f>
+        <v>2026</v>
+      </c>
+      <c r="I5" s="12">
+        <f>[2]Revenue!I5</f>
+        <v>2027</v>
+      </c>
+      <c r="J5" s="12">
+        <f>[2]Revenue!J5</f>
+        <v>2028</v>
+      </c>
+      <c r="K5" s="12">
+        <f>[2]Revenue!K5</f>
+        <v>2029</v>
+      </c>
+      <c r="L5" s="12">
+        <f>[2]Revenue!L5</f>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B6" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="C6" s="269">
+        <f>Statement!M26</f>
+        <v>-2.57</v>
+      </c>
+      <c r="D6" s="269">
+        <f>Statement!N26</f>
+        <v>-1.51</v>
+      </c>
+      <c r="E6" s="269">
+        <f>Statement!O26</f>
+        <v>0.35</v>
+      </c>
+      <c r="F6" s="269">
+        <f>Statement!P26</f>
+        <v>1.88</v>
+      </c>
+      <c r="G6" s="270">
+        <f>Statement!Q26</f>
+        <v>3.2570201538405805</v>
+      </c>
+      <c r="H6" s="139"/>
+      <c r="I6" s="139"/>
+      <c r="J6" s="139"/>
+      <c r="K6" s="139"/>
+      <c r="L6" s="139"/>
+      <c r="N6" s="92"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B7" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="C7" s="269">
+        <f>Statement!M82</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="269">
+        <f>Statement!N82</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="269">
+        <f>Statement!O82</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="269">
+        <f>Statement!P82</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="270">
+        <f>Statement!Q82</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="139"/>
+      <c r="N7" s="92"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="92"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C9" s="262" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="262"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="262"/>
+      <c r="G9" s="262"/>
+      <c r="H9" s="262"/>
+      <c r="I9" s="262"/>
+      <c r="J9" s="262"/>
+      <c r="K9" s="262"/>
+      <c r="L9" s="262"/>
+      <c r="N9" s="92"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C10" s="12">
+        <f t="shared" ref="C10:L10" si="0">C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" si="0"/>
+        <v>2022</v>
+      </c>
+      <c r="E10" s="12">
+        <f t="shared" si="0"/>
+        <v>2023</v>
+      </c>
+      <c r="F10" s="12">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
+      <c r="G10" s="12">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="H10" s="12">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="I10" s="12">
+        <f t="shared" si="0"/>
+        <v>2027</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="0"/>
+        <v>2028</v>
+      </c>
+      <c r="K10" s="12">
+        <f t="shared" si="0"/>
+        <v>2029</v>
+      </c>
+      <c r="L10" s="12">
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+      <c r="N10" s="92"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C11" s="139"/>
+      <c r="D11" s="96">
+        <f>(D6-C6)/C6</f>
+        <v>-0.41245136186770426</v>
+      </c>
+      <c r="E11" s="96">
+        <f>(E6-D6)/D6</f>
+        <v>-1.2317880794701985</v>
+      </c>
+      <c r="F11" s="96">
+        <f>(F6-E6)/E6</f>
+        <v>4.371428571428571</v>
+      </c>
+      <c r="G11" s="97">
+        <f>(G6-F6)/F6</f>
+        <v>0.7324575286386068</v>
+      </c>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
+      <c r="J11" s="139"/>
+      <c r="K11" s="139"/>
+      <c r="L11" s="139"/>
+      <c r="N11" s="92"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" s="139"/>
+      <c r="D12" s="96">
+        <f>IF(C7=0,
+IF(D7=0,0,IF(D7&gt;0,1,-1)),
+(D7-C7)/ABS(C7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="96">
+        <f>IF(D7=0,
+IF(E7=0,0,IF(E7&gt;0,1,-1)),
+(E7-D7)/ABS(D7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="96">
+        <f>IF(E7=0,
+IF(F7=0,0,IF(F7&gt;0,1,-1)),
+(F7-E7)/ABS(E7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="97">
+        <f>IF(F7=0,
+IF(G7=0,0,IF(G7&gt;0,1,-1)),
+(G7-F7)/ABS(F7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="139"/>
+      <c r="I12" s="139"/>
+      <c r="J12" s="139"/>
+      <c r="K12" s="139"/>
+      <c r="L12" s="139"/>
+      <c r="N12" s="92"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="92"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C14" s="262" t="s">
+        <v>426</v>
+      </c>
+      <c r="D14" s="262"/>
+      <c r="E14" s="262"/>
+      <c r="F14" s="262"/>
+      <c r="G14" s="262"/>
+      <c r="H14" s="262"/>
+      <c r="I14" s="262"/>
+      <c r="J14" s="262"/>
+      <c r="K14" s="262"/>
+      <c r="L14" s="262"/>
+      <c r="N14" s="92"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B15" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="C15" s="12">
+        <f>C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D15" s="12">
+        <f t="shared" ref="D15:L15" si="1">D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E15" s="12">
+        <f t="shared" si="1"/>
+        <v>2023</v>
+      </c>
+      <c r="F15" s="12">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="G15" s="12">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="H15" s="12">
+        <f t="shared" si="1"/>
+        <v>2026</v>
+      </c>
+      <c r="I15" s="12">
+        <f t="shared" si="1"/>
+        <v>2027</v>
+      </c>
+      <c r="J15" s="12">
+        <f t="shared" si="1"/>
+        <v>2028</v>
+      </c>
+      <c r="K15" s="12">
+        <f t="shared" si="1"/>
+        <v>2029</v>
+      </c>
+      <c r="L15" s="12">
+        <f t="shared" si="1"/>
+        <v>2030</v>
+      </c>
+      <c r="N15" s="92"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C16" s="96">
+        <f>C7/C6</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="96">
+        <f t="shared" ref="D16:G16" si="2">D7/D6</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="96">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="96">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="97">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="139"/>
+      <c r="I16" s="139"/>
+      <c r="J16" s="139"/>
+      <c r="K16" s="139"/>
+      <c r="L16" s="139"/>
+      <c r="N16" s="92"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="92"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="92"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N19" s="92"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20" s="254" t="s">
+        <v>428</v>
+      </c>
+      <c r="C20" s="254"/>
+      <c r="N20" s="92"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C21" s="271">
+        <f>G7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C22" s="272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B23" s="39" t="s">
+        <v>431</v>
+      </c>
+      <c r="C23" s="273">
+        <f>C21*(1+C22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C24" s="137">
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B25" s="39" t="s">
+        <v>432</v>
+      </c>
+      <c r="C25" s="272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B26" s="143" t="s">
+        <v>213</v>
+      </c>
+      <c r="C26" s="144">
+        <f>C23/(C24-C25)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="B20:C20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0116CE1A-CCEC-514B-9208-A0DCC7740441}">
   <dimension ref="A1:AB49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -23867,20 +24474,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="251" t="s">
+      <c r="C3" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="251"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="264" t="s">
+      <c r="D3" s="254"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="251"/>
-      <c r="J3" s="251"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="251"/>
+      <c r="I3" s="254"/>
+      <c r="J3" s="254"/>
+      <c r="K3" s="254"/>
+      <c r="L3" s="254"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -23898,18 +24505,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="262" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -24336,18 +24943,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="260" t="s">
+      <c r="C39" s="262" t="s">
         <v>233</v>
       </c>
-      <c r="D39" s="260"/>
-      <c r="E39" s="260"/>
-      <c r="F39" s="260"/>
-      <c r="G39" s="260"/>
-      <c r="H39" s="260"/>
-      <c r="I39" s="260"/>
-      <c r="J39" s="260"/>
-      <c r="K39" s="260"/>
-      <c r="L39" s="260"/>
+      <c r="D39" s="262"/>
+      <c r="E39" s="262"/>
+      <c r="F39" s="262"/>
+      <c r="G39" s="262"/>
+      <c r="H39" s="262"/>
+      <c r="I39" s="262"/>
+      <c r="J39" s="262"/>
+      <c r="K39" s="262"/>
+      <c r="L39" s="262"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -24779,17 +25386,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -35514,15 +36121,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="251" t="s">
+      <c r="B4" s="254" t="s">
         <v>242</v>
       </c>
-      <c r="C4" s="251"/>
-      <c r="E4" s="251" t="s">
+      <c r="C4" s="254"/>
+      <c r="E4" s="254" t="s">
         <v>249</v>
       </c>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35659,14 +36266,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="251" t="s">
+      <c r="B15" s="254" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="251"/>
-      <c r="E15" s="251" t="s">
+      <c r="C15" s="254"/>
+      <c r="E15" s="254" t="s">
         <v>255</v>
       </c>
-      <c r="F15" s="251"/>
+      <c r="F15" s="254"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35717,14 +36324,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="251" t="s">
+      <c r="B21" s="254" t="s">
         <v>254</v>
       </c>
-      <c r="C21" s="251"/>
-      <c r="E21" s="251" t="s">
+      <c r="C21" s="254"/>
+      <c r="E21" s="254" t="s">
         <v>258</v>
       </c>
-      <c r="F21" s="251"/>
+      <c r="F21" s="254"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35793,14 +36400,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="251" t="s">
+      <c r="B29" s="254" t="s">
         <v>259</v>
       </c>
-      <c r="C29" s="251"/>
-      <c r="E29" s="251" t="s">
+      <c r="C29" s="254"/>
+      <c r="E29" s="254" t="s">
         <v>265</v>
       </c>
-      <c r="F29" s="251"/>
+      <c r="F29" s="254"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35876,14 +36483,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="251" t="s">
+      <c r="B37" s="254" t="s">
         <v>277</v>
       </c>
-      <c r="C37" s="251"/>
-      <c r="E37" s="251" t="s">
+      <c r="C37" s="254"/>
+      <c r="E37" s="254" t="s">
         <v>280</v>
       </c>
-      <c r="F37" s="251"/>
+      <c r="F37" s="254"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35952,14 +36559,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="251" t="s">
+      <c r="B45" s="254" t="s">
         <v>288</v>
       </c>
-      <c r="C45" s="251"/>
-      <c r="E45" s="251" t="s">
+      <c r="C45" s="254"/>
+      <c r="E45" s="254" t="s">
         <v>294</v>
       </c>
-      <c r="F45" s="251"/>
+      <c r="F45" s="254"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35996,14 +36603,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="251" t="s">
+      <c r="B51" s="254" t="s">
         <v>291</v>
       </c>
-      <c r="C51" s="251"/>
-      <c r="E51" s="251" t="s">
+      <c r="C51" s="254"/>
+      <c r="E51" s="254" t="s">
         <v>312</v>
       </c>
-      <c r="F51" s="251"/>
+      <c r="F51" s="254"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -38042,14 +38649,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="255" t="s">
+      <c r="C3" s="257" t="s">
         <v>322</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="F3" s="257" t="s">
+      <c r="D3" s="258"/>
+      <c r="F3" s="259" t="s">
         <v>323</v>
       </c>
-      <c r="G3" s="256"/>
+      <c r="G3" s="258"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38116,19 +38723,19 @@
       <c r="B7" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C7" s="258">
+      <c r="C7" s="255">
         <f>Statement!AA89</f>
         <v>3.2166947127281985E-2</v>
       </c>
-      <c r="D7" s="259"/>
-      <c r="F7" s="258">
+      <c r="D7" s="256"/>
+      <c r="F7" s="255">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.26533415964948015</v>
       </c>
-      <c r="G7" s="259"/>
+      <c r="G7" s="256"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -38155,19 +38762,19 @@
       <c r="B9" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C9" s="258">
+      <c r="C9" s="255">
         <f>Statement!AA90</f>
         <v>2.4312004052000676E-2</v>
       </c>
-      <c r="D9" s="259"/>
-      <c r="F9" s="258">
+      <c r="D9" s="256"/>
+      <c r="F9" s="255">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.18341410716161269</v>
       </c>
-      <c r="G9" s="259"/>
+      <c r="G9" s="256"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -38194,19 +38801,19 @@
       <c r="B11" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C11" s="258">
+      <c r="C11" s="255">
         <f>Statement!AA91</f>
         <v>3.5104848228727975E-2</v>
       </c>
-      <c r="D11" s="259"/>
-      <c r="F11" s="258">
+      <c r="D11" s="256"/>
+      <c r="F11" s="255">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.29860569422776911</v>
       </c>
-      <c r="G11" s="259"/>
+      <c r="G11" s="256"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -38233,19 +38840,19 @@
       <c r="B13" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C13" s="258">
+      <c r="C13" s="255">
         <f>Statement!AA95</f>
         <v>3.7890588923436871E-2</v>
       </c>
-      <c r="D13" s="259"/>
-      <c r="F13" s="258">
+      <c r="D13" s="256"/>
+      <c r="F13" s="255">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.19976228096397206</v>
       </c>
-      <c r="G13" s="259"/>
+      <c r="G13" s="256"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -38272,19 +38879,19 @@
       <c r="B15" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C15" s="258">
+      <c r="C15" s="255">
         <f>Statement!AA96</f>
         <v>2.4692778570442307E-2</v>
       </c>
-      <c r="D15" s="259"/>
-      <c r="F15" s="258">
+      <c r="D15" s="256"/>
+      <c r="F15" s="255">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.88721708909044672</v>
       </c>
-      <c r="G15" s="259"/>
+      <c r="G15" s="256"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -38311,19 +38918,19 @@
       <c r="B17" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C17" s="258">
+      <c r="C17" s="255">
         <f>Statement!AA98</f>
         <v>3.5896458025456456E-2</v>
       </c>
-      <c r="D17" s="259"/>
-      <c r="F17" s="258">
+      <c r="D17" s="256"/>
+      <c r="F17" s="255">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.23694321901238083</v>
       </c>
-      <c r="G17" s="259"/>
+      <c r="G17" s="256"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -38350,22 +38957,22 @@
       <c r="B19" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C19" s="258">
+      <c r="C19" s="255">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3895378744883068E-2</v>
       </c>
-      <c r="D19" s="259"/>
-      <c r="F19" s="258">
+      <c r="D19" s="256"/>
+      <c r="F19" s="255">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.0103717755737469E-2</v>
       </c>
-      <c r="G19" s="259"/>
+      <c r="G19" s="256"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -38392,22 +38999,22 @@
       <c r="B21" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C21" s="258">
+      <c r="C21" s="255">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.4953901558794477E-2</v>
       </c>
-      <c r="D21" s="259"/>
-      <c r="F21" s="258">
+      <c r="D21" s="256"/>
+      <c r="F21" s="255">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.23611111111111119</v>
       </c>
-      <c r="G21" s="259"/>
+      <c r="G21" s="256"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38456,22 +39063,22 @@
       <c r="B25" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C25" s="258">
+      <c r="C25" s="255">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>3.5586042940987099E-2</v>
       </c>
-      <c r="D25" s="259"/>
-      <c r="F25" s="258">
+      <c r="D25" s="256"/>
+      <c r="F25" s="255">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.3137438673836439</v>
       </c>
-      <c r="G25" s="259"/>
+      <c r="G25" s="256"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38499,22 +39106,22 @@
       <c r="B27" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C27" s="258">
+      <c r="C27" s="255">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>1.9435240591464318E-2</v>
       </c>
-      <c r="D27" s="259"/>
-      <c r="F27" s="258">
+      <c r="D27" s="256"/>
+      <c r="F27" s="255">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.15277933117100995</v>
       </c>
-      <c r="G27" s="259"/>
+      <c r="G27" s="256"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38542,22 +39149,22 @@
       <c r="B29" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C29" s="258">
+      <c r="C29" s="255">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.10055431294369348</v>
       </c>
-      <c r="D29" s="259"/>
-      <c r="F29" s="258">
+      <c r="D29" s="256"/>
+      <c r="F29" s="255">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-5.581511763724345E-2</v>
       </c>
-      <c r="G29" s="259"/>
+      <c r="G29" s="256"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -38585,22 +39192,22 @@
       <c r="B31" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C31" s="258">
+      <c r="C31" s="255">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.11569469165532405</v>
       </c>
-      <c r="D31" s="259"/>
-      <c r="F31" s="258">
+      <c r="D31" s="256"/>
+      <c r="F31" s="255">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.10548612582080068</v>
       </c>
-      <c r="G31" s="259"/>
+      <c r="G31" s="256"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -38628,22 +39235,22 @@
       <c r="B33" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C33" s="258">
+      <c r="C33" s="255">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.29411764705882354</v>
       </c>
-      <c r="D33" s="259"/>
-      <c r="F33" s="258">
+      <c r="D33" s="256"/>
+      <c r="F33" s="255">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.52914798206278024</v>
       </c>
-      <c r="G33" s="259"/>
+      <c r="G33" s="256"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -38692,22 +39299,22 @@
       <c r="B37" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C37" s="258">
+      <c r="C37" s="255">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>7.2106261859582549E-2</v>
       </c>
-      <c r="D37" s="259"/>
-      <c r="F37" s="258">
+      <c r="D37" s="256"/>
+      <c r="F37" s="255">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.21244635193133046</v>
       </c>
-      <c r="G37" s="259"/>
+      <c r="G37" s="256"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -38735,22 +39342,22 @@
       <c r="B39" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C39" s="258">
+      <c r="C39" s="255">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>3.5311795642374154E-2</v>
       </c>
-      <c r="D39" s="259"/>
-      <c r="F39" s="258">
+      <c r="D39" s="256"/>
+      <c r="F39" s="255">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>5.8371735791090631E-2</v>
       </c>
-      <c r="G39" s="259"/>
+      <c r="G39" s="256"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -38778,22 +39385,22 @@
       <c r="B41" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C41" s="258">
+      <c r="C41" s="255">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>2.4590163934426229E-2</v>
       </c>
-      <c r="D41" s="259"/>
-      <c r="F41" s="258">
+      <c r="D41" s="256"/>
+      <c r="F41" s="255">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.21359223300970873</v>
       </c>
-      <c r="G41" s="259"/>
+      <c r="G41" s="256"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -38821,22 +39428,22 @@
       <c r="B43" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C43" s="258">
+      <c r="C43" s="255">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>3.6393713813068655E-2</v>
       </c>
-      <c r="D43" s="259"/>
-      <c r="F43" s="258">
+      <c r="D43" s="256"/>
+      <c r="F43" s="255">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>4.5037531276063386E-2</v>
       </c>
-      <c r="G43" s="259"/>
+      <c r="G43" s="256"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -38864,22 +39471,22 @@
       <c r="B45" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C45" s="258">
+      <c r="C45" s="255">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.0731977910403413E-2</v>
       </c>
-      <c r="D45" s="259"/>
-      <c r="F45" s="258">
+      <c r="D45" s="256"/>
+      <c r="F45" s="255">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>8.2524946724122472E-2</v>
       </c>
-      <c r="G45" s="259"/>
+      <c r="G45" s="256"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -38907,22 +39514,22 @@
       <c r="B47" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C47" s="258">
+      <c r="C47" s="255">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>3.5539502565387668E-2</v>
       </c>
-      <c r="D47" s="259"/>
-      <c r="F47" s="258">
+      <c r="D47" s="256"/>
+      <c r="F47" s="255">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.14557703208606101</v>
       </c>
-      <c r="G47" s="259"/>
+      <c r="G47" s="256"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -38950,22 +39557,22 @@
       <c r="B49" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C49" s="258">
+      <c r="C49" s="255">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-1.0355944704846643E-2</v>
       </c>
-      <c r="D49" s="259"/>
-      <c r="F49" s="258">
+      <c r="D49" s="256"/>
+      <c r="F49" s="255">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>0.14665971507883949</v>
       </c>
-      <c r="G49" s="259"/>
+      <c r="G49" s="256"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -38993,22 +39600,22 @@
       <c r="B51" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C51" s="258">
+      <c r="C51" s="255">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>-1.63629641858896E-2</v>
       </c>
-      <c r="D51" s="259"/>
-      <c r="F51" s="258">
+      <c r="D51" s="256"/>
+      <c r="F51" s="255">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>0.10309849806387941</v>
       </c>
-      <c r="G51" s="259"/>
+      <c r="G51" s="256"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -39036,39 +39643,43 @@
       <c r="B53" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C53" s="258">
+      <c r="C53" s="255">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-0.17517009292452351</v>
       </c>
-      <c r="D53" s="259"/>
-      <c r="F53" s="258">
+      <c r="D53" s="256"/>
+      <c r="F53" s="255">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.26222395510175772</v>
       </c>
-      <c r="G53" s="259"/>
+      <c r="G53" s="256"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -39083,24 +39694,20 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="F51:G51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/DUOL.xlsx
+++ b/DUOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81EEB74-F56D-A84D-8813-2275A2E87C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C0917F-C738-6C47-917D-2A38E264165B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2393,6 +2393,11 @@
     <xf numFmtId="2" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2447,11 +2452,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13146,11 +13146,11 @@
     <v>Powered by Refinitiv</v>
     <v>468</v>
     <v>87.89</v>
-    <v>0.87980000000000003</v>
-    <v>-5.19</v>
-    <v>-3.9938000000000001E-2</v>
-    <v>0.24</v>
-    <v>1.9239999999999999E-3</v>
+    <v>0.81510000000000005</v>
+    <v>1.21</v>
+    <v>9.0569999999999991E-3</v>
+    <v>-0.51</v>
+    <v>-3.7830000000000003E-3</v>
     <v>USD</v>
     <v>Duolingo, Inc. is a technology company. The Company is engaged in offering a mobile learning platform, as well as a digital English language proficiency assessment exam. It operates a freemium business model, namely, the app and the Website are accessible free of charge, although Duolingo also offers premium services for a subscription fee. Its solutions consist of the Duolingo App, Super Duolingo, Duolingo Max, Duolingo English Test: AI-Driven Language Assessment, Duolingo for Schools, and Duolingo ABC. The Duolingo App offers courses in over 40 different languages, including Spanish, English, French, German, Italian, Portuguese, Japanese and Chinese. Duolingo can also be accessed on desktop computers via a Web browser. Its subscription offering, Super Duolingo, offers learners additional features to enhance their learning experience. The Duolingo English Test is an online, on-demand, high-stakes English proficiency assessment. It also operates an animation and motion design studio.</v>
     <v>900</v>
@@ -13158,25 +13158,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5900 PENN AVE, SECOND FLOOR, PITTSBURGH, PA, 15206 US</v>
-    <v>133.5</v>
+    <v>134.99</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46213.999535219533</v>
+    <v>46234.909688402346</v>
     <v>0</v>
-    <v>124.64</v>
-    <v>5812957651</v>
+    <v>130.5</v>
+    <v>6281218507</v>
     <v>DUOLINGO, INC.</v>
     <v>DUOLINGO, INC.</v>
-    <v>132.19999999999999</v>
-    <v>15.039400000000001</v>
-    <v>129.94999999999999</v>
-    <v>124.76</v>
-    <v>125</v>
+    <v>131.75</v>
+    <v>15.4618</v>
+    <v>133.6</v>
+    <v>134.81</v>
+    <v>134.30000000000001</v>
     <v>46593120</v>
     <v>DUOL</v>
     <v>DUOLINGO, INC. (XNAS:DUOL)</v>
-    <v>634743</v>
-    <v>1498108</v>
+    <v>1025858</v>
+    <v>1112886</v>
     <v>2011</v>
   </rv>
   <rv s="2">
@@ -13198,19 +13198,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>46.87</v>
+    <v>47.14</v>
     <v>39.47</v>
-    <v>0.3</v>
-    <v>6.6090000000000003E-3</v>
+    <v>0.41</v>
+    <v>8.8710000000000004E-3</v>
     <v>US</v>
-    <v>45.71</v>
+    <v>46.86</v>
     <v>Index</v>
     <v>3</v>
-    <v>45.39</v>
+    <v>46.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.41</v>
-    <v>45.39</v>
-    <v>45.69</v>
+    <v>46.69</v>
+    <v>46.22</v>
+    <v>46.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13432,9 +13432,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -14005,18 +14005,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="251" t="s">
+      <c r="B2" s="256" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="252"/>
-      <c r="E2" s="251" t="s">
+      <c r="C2" s="257"/>
+      <c r="E2" s="256" t="s">
         <v>296</v>
       </c>
-      <c r="F2" s="252"/>
-      <c r="H2" s="251" t="s">
+      <c r="F2" s="257"/>
+      <c r="H2" s="256" t="s">
         <v>338</v>
       </c>
-      <c r="I2" s="252"/>
+      <c r="I2" s="257"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC149</f>
-        <v>6086666.1200000001</v>
+        <v>6576975.4699999997</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -14055,7 +14055,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>4694845.12</v>
+        <v>5185154.47</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -14072,7 +14072,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>124.76</v>
+        <v>134.81</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>252</v>
@@ -14096,14 +14096,14 @@
       </c>
       <c r="C6" s="210" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>125</v>
+        <v>134.30000000000001</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>246</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC146</f>
-        <v>36.795880819513265</v>
+        <v>39.759960670716445</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -14120,14 +14120,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-5.19</v>
+        <v>1.21</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>205</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC147</f>
-        <v>5.5477870892931662</v>
+        <v>5.994687219522377</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -14144,14 +14144,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.24</v>
+        <v>-0.51</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>274</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC157</f>
-        <v>4.3395184620378023E-2</v>
+        <v>4.0160101129280937E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.30007285151232449</v>
+        <v>0.20315324497201698</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14168,14 +14168,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-3.9938000000000001E-2</v>
+        <v>9.0569999999999991E-3</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>297</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC158</f>
-        <v>2.7176955075625987E-2</v>
+        <v>2.5150930311068156E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -14184,14 +14184,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.9239999999999999E-3</v>
+        <v>-3.7830000000000003E-3</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>302</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC160</f>
-        <v>3.9974264269320558E-3</v>
+        <v>3.6994208220758351E-3</v>
       </c>
       <c r="H10" s="186" t="s">
         <v>433</v>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.87980000000000003</v>
+        <v>0.81510000000000005</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>104</v>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1498108</v>
+        <v>1112886</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>105</v>
@@ -14271,7 +14271,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC172</f>
-        <v>0.2286672165944269</v>
+        <v>0.21162022062399452</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14284,10 +14284,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="253" t="s">
+      <c r="B17" s="258" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="253"/>
+      <c r="C17" s="258"/>
       <c r="E17" s="186" t="s">
         <v>305</v>
       </c>
@@ -14360,14 +14360,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="253" t="s">
+      <c r="B25" s="258" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="253"/>
-      <c r="E25" s="251" t="s">
+      <c r="C25" s="258"/>
+      <c r="E25" s="256" t="s">
         <v>353</v>
       </c>
-      <c r="F25" s="252"/>
+      <c r="F25" s="257"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.69</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14416,15 +14416,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="254" t="s">
+      <c r="B33" s="259" t="s">
         <v>348</v>
       </c>
-      <c r="C33" s="254"/>
-      <c r="D33" s="254"/>
-      <c r="E33" s="254"/>
-      <c r="F33" s="254"/>
-      <c r="G33" s="254"/>
-      <c r="H33" s="254"/>
+      <c r="C33" s="259"/>
+      <c r="D33" s="259"/>
+      <c r="E33" s="259"/>
+      <c r="F33" s="259"/>
+      <c r="G33" s="259"/>
+      <c r="H33" s="259"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14443,24 +14443,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="254"/>
-      <c r="C39" s="254"/>
-      <c r="D39" s="254"/>
-      <c r="E39" s="254"/>
-      <c r="F39" s="254"/>
-      <c r="G39" s="254"/>
-      <c r="H39" s="254"/>
+      <c r="B39" s="259"/>
+      <c r="C39" s="259"/>
+      <c r="D39" s="259"/>
+      <c r="E39" s="259"/>
+      <c r="F39" s="259"/>
+      <c r="G39" s="259"/>
+      <c r="H39" s="259"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="254" t="s">
+      <c r="B42" s="259" t="s">
         <v>351</v>
       </c>
-      <c r="C42" s="254"/>
-      <c r="D42" s="254"/>
-      <c r="E42" s="254"/>
-      <c r="F42" s="254"/>
-      <c r="G42" s="254"/>
-      <c r="H42" s="254"/>
+      <c r="C42" s="259"/>
+      <c r="D42" s="259"/>
+      <c r="E42" s="259"/>
+      <c r="F42" s="259"/>
+      <c r="G42" s="259"/>
+      <c r="H42" s="259"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14475,24 +14475,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="254"/>
-      <c r="C49" s="254"/>
-      <c r="D49" s="254"/>
-      <c r="E49" s="254"/>
-      <c r="F49" s="254"/>
-      <c r="G49" s="254"/>
-      <c r="H49" s="254"/>
+      <c r="B49" s="259"/>
+      <c r="C49" s="259"/>
+      <c r="D49" s="259"/>
+      <c r="E49" s="259"/>
+      <c r="F49" s="259"/>
+      <c r="G49" s="259"/>
+      <c r="H49" s="259"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="254" t="s">
+      <c r="B52" s="259" t="s">
         <v>109</v>
       </c>
-      <c r="C52" s="254"/>
-      <c r="D52" s="254"/>
-      <c r="E52" s="254"/>
-      <c r="F52" s="254"/>
-      <c r="G52" s="254"/>
-      <c r="H52" s="254"/>
+      <c r="C52" s="259"/>
+      <c r="D52" s="259"/>
+      <c r="E52" s="259"/>
+      <c r="F52" s="259"/>
+      <c r="G52" s="259"/>
+      <c r="H52" s="259"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="41" t="s">
@@ -14563,13 +14563,13 @@
       </c>
     </row>
     <row r="65" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="254"/>
-      <c r="C65" s="254"/>
-      <c r="D65" s="254"/>
-      <c r="E65" s="254"/>
-      <c r="F65" s="254"/>
-      <c r="G65" s="254"/>
-      <c r="H65" s="254"/>
+      <c r="B65" s="259"/>
+      <c r="C65" s="259"/>
+      <c r="D65" s="259"/>
+      <c r="E65" s="259"/>
+      <c r="F65" s="259"/>
+      <c r="G65" s="259"/>
+      <c r="H65" s="259"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14654,36 +14654,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="254" t="s">
+      <c r="S2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="254"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="254"/>
-      <c r="W2" s="254"/>
-      <c r="X2" s="254"/>
-      <c r="Y2" s="254"/>
-      <c r="Z2" s="254"/>
-      <c r="AA2" s="254" t="s">
+      <c r="T2" s="259"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="259"/>
+      <c r="X2" s="259"/>
+      <c r="Y2" s="259"/>
+      <c r="Z2" s="259"/>
+      <c r="AA2" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="254"/>
-      <c r="AC2" s="254"/>
+      <c r="AB2" s="259"/>
+      <c r="AC2" s="259"/>
       <c r="AE2" s="86" t="s">
         <v>85</v>
       </c>
@@ -14694,32 +14694,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="267" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="263" t="s">
+      <c r="S4" s="268" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="264"/>
-      <c r="U4" s="264"/>
-      <c r="V4" s="264"/>
-      <c r="W4" s="264"/>
-      <c r="X4" s="264"/>
-      <c r="Y4" s="264"/>
-      <c r="Z4" s="264"/>
-      <c r="AA4" s="264"/>
-      <c r="AB4" s="264"/>
-      <c r="AC4" s="264"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
+      <c r="AA4" s="269"/>
+      <c r="AB4" s="269"/>
+      <c r="AC4" s="269"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15407,33 +15407,33 @@
       <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="262" t="s">
+      <c r="C13" s="267" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="262"/>
-      <c r="E13" s="262"/>
-      <c r="F13" s="262"/>
-      <c r="G13" s="262"/>
-      <c r="H13" s="262"/>
-      <c r="I13" s="262"/>
-      <c r="J13" s="262"/>
-      <c r="K13" s="262"/>
-      <c r="L13" s="262"/>
+      <c r="D13" s="267"/>
+      <c r="E13" s="267"/>
+      <c r="F13" s="267"/>
+      <c r="G13" s="267"/>
+      <c r="H13" s="267"/>
+      <c r="I13" s="267"/>
+      <c r="J13" s="267"/>
+      <c r="K13" s="267"/>
+      <c r="L13" s="267"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="92"/>
-      <c r="S13" s="263" t="s">
+      <c r="S13" s="268" t="s">
         <v>122</v>
       </c>
-      <c r="T13" s="264"/>
-      <c r="U13" s="264"/>
-      <c r="V13" s="264"/>
-      <c r="W13" s="264"/>
-      <c r="X13" s="264"/>
-      <c r="Y13" s="264"/>
-      <c r="Z13" s="264"/>
-      <c r="AA13" s="264"/>
-      <c r="AB13" s="264"/>
-      <c r="AC13" s="264"/>
+      <c r="T13" s="269"/>
+      <c r="U13" s="269"/>
+      <c r="V13" s="269"/>
+      <c r="W13" s="269"/>
+      <c r="X13" s="269"/>
+      <c r="Y13" s="269"/>
+      <c r="Z13" s="269"/>
+      <c r="AA13" s="269"/>
+      <c r="AB13" s="269"/>
+      <c r="AC13" s="269"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -16042,33 +16042,33 @@
       <c r="Q22" s="92"/>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C23" s="262" t="s">
+      <c r="C23" s="267" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="262"/>
-      <c r="E23" s="262"/>
-      <c r="F23" s="262"/>
-      <c r="G23" s="262"/>
-      <c r="H23" s="262"/>
-      <c r="I23" s="262"/>
-      <c r="J23" s="262"/>
-      <c r="K23" s="262"/>
-      <c r="L23" s="262"/>
+      <c r="D23" s="267"/>
+      <c r="E23" s="267"/>
+      <c r="F23" s="267"/>
+      <c r="G23" s="267"/>
+      <c r="H23" s="267"/>
+      <c r="I23" s="267"/>
+      <c r="J23" s="267"/>
+      <c r="K23" s="267"/>
+      <c r="L23" s="267"/>
       <c r="O23" s="5"/>
       <c r="Q23" s="92"/>
-      <c r="S23" s="263" t="s">
+      <c r="S23" s="268" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="264"/>
-      <c r="U23" s="264"/>
-      <c r="V23" s="264"/>
-      <c r="W23" s="264"/>
-      <c r="X23" s="264"/>
-      <c r="Y23" s="264"/>
-      <c r="Z23" s="264"/>
-      <c r="AA23" s="264"/>
-      <c r="AB23" s="264"/>
-      <c r="AC23" s="264"/>
+      <c r="T23" s="269"/>
+      <c r="U23" s="269"/>
+      <c r="V23" s="269"/>
+      <c r="W23" s="269"/>
+      <c r="X23" s="269"/>
+      <c r="Y23" s="269"/>
+      <c r="Z23" s="269"/>
+      <c r="AA23" s="269"/>
+      <c r="AB23" s="269"/>
+      <c r="AC23" s="269"/>
       <c r="AE23" s="88" t="str">
         <f>AE2</f>
         <v>TTM/YTD</v>
@@ -17387,32 +17387,32 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="262" t="s">
+      <c r="C40" s="267" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="262"/>
-      <c r="E40" s="262"/>
-      <c r="F40" s="262"/>
-      <c r="G40" s="262"/>
-      <c r="H40" s="262"/>
-      <c r="I40" s="262"/>
-      <c r="J40" s="262"/>
-      <c r="K40" s="262"/>
-      <c r="L40" s="262"/>
+      <c r="D40" s="267"/>
+      <c r="E40" s="267"/>
+      <c r="F40" s="267"/>
+      <c r="G40" s="267"/>
+      <c r="H40" s="267"/>
+      <c r="I40" s="267"/>
+      <c r="J40" s="267"/>
+      <c r="K40" s="267"/>
+      <c r="L40" s="267"/>
       <c r="O40" s="5"/>
-      <c r="S40" s="263" t="s">
+      <c r="S40" s="268" t="s">
         <v>126</v>
       </c>
-      <c r="T40" s="264"/>
-      <c r="U40" s="264"/>
-      <c r="V40" s="264"/>
-      <c r="W40" s="264"/>
-      <c r="X40" s="264"/>
-      <c r="Y40" s="264"/>
-      <c r="Z40" s="264"/>
-      <c r="AA40" s="264"/>
-      <c r="AB40" s="264"/>
-      <c r="AC40" s="264"/>
+      <c r="T40" s="269"/>
+      <c r="U40" s="269"/>
+      <c r="V40" s="269"/>
+      <c r="W40" s="269"/>
+      <c r="X40" s="269"/>
+      <c r="Y40" s="269"/>
+      <c r="Z40" s="269"/>
+      <c r="AA40" s="269"/>
+      <c r="AB40" s="269"/>
+      <c r="AC40" s="269"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18024,35 +18024,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
-      <c r="P2" s="254" t="s">
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
+      <c r="P2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="254"/>
-      <c r="R2" s="254"/>
-      <c r="S2" s="254"/>
-      <c r="T2" s="254"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="254"/>
-      <c r="W2" s="254"/>
-      <c r="X2" s="254" t="s">
+      <c r="Q2" s="259"/>
+      <c r="R2" s="259"/>
+      <c r="S2" s="259"/>
+      <c r="T2" s="259"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="259"/>
+      <c r="X2" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="254"/>
-      <c r="Z2" s="254"/>
+      <c r="Y2" s="259"/>
+      <c r="Z2" s="259"/>
       <c r="AB2" s="86" t="s">
         <v>115</v>
       </c>
@@ -18061,31 +18061,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="267" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
-      <c r="P4" s="264" t="s">
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
+      <c r="P4" s="269" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="264"/>
-      <c r="R4" s="264"/>
-      <c r="S4" s="264"/>
-      <c r="T4" s="264"/>
-      <c r="U4" s="264"/>
-      <c r="V4" s="264"/>
-      <c r="W4" s="264"/>
-      <c r="X4" s="264"/>
-      <c r="Y4" s="264"/>
-      <c r="Z4" s="264"/>
+      <c r="Q4" s="269"/>
+      <c r="R4" s="269"/>
+      <c r="S4" s="269"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18280,32 +18280,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="262" t="s">
+      <c r="C9" s="267" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="262"/>
-      <c r="E9" s="262"/>
-      <c r="F9" s="262"/>
-      <c r="G9" s="262"/>
-      <c r="H9" s="262"/>
-      <c r="I9" s="262"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="262"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="264" t="s">
+      <c r="P9" s="269" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="264"/>
-      <c r="R9" s="264"/>
-      <c r="S9" s="264"/>
-      <c r="T9" s="264"/>
-      <c r="U9" s="264"/>
-      <c r="V9" s="264"/>
-      <c r="W9" s="264"/>
-      <c r="X9" s="264"/>
-      <c r="Y9" s="264"/>
-      <c r="Z9" s="264"/>
+      <c r="Q9" s="269"/>
+      <c r="R9" s="269"/>
+      <c r="S9" s="269"/>
+      <c r="T9" s="269"/>
+      <c r="U9" s="269"/>
+      <c r="V9" s="269"/>
+      <c r="W9" s="269"/>
+      <c r="X9" s="269"/>
+      <c r="Y9" s="269"/>
+      <c r="Z9" s="269"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -18875,31 +18875,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="262" t="s">
+      <c r="C18" s="267" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="262"/>
-      <c r="E18" s="262"/>
-      <c r="F18" s="262"/>
-      <c r="G18" s="262"/>
-      <c r="H18" s="262"/>
-      <c r="I18" s="262"/>
-      <c r="J18" s="262"/>
-      <c r="K18" s="262"/>
-      <c r="L18" s="262"/>
-      <c r="P18" s="264" t="s">
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
+      <c r="P18" s="269" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="264"/>
-      <c r="R18" s="264"/>
-      <c r="S18" s="264"/>
-      <c r="T18" s="264"/>
-      <c r="U18" s="264"/>
-      <c r="V18" s="264"/>
-      <c r="W18" s="264"/>
-      <c r="X18" s="264"/>
-      <c r="Y18" s="264"/>
-      <c r="Z18" s="264"/>
+      <c r="Q18" s="269"/>
+      <c r="R18" s="269"/>
+      <c r="S18" s="269"/>
+      <c r="T18" s="269"/>
+      <c r="U18" s="269"/>
+      <c r="V18" s="269"/>
+      <c r="W18" s="269"/>
+      <c r="X18" s="269"/>
+      <c r="Y18" s="269"/>
+      <c r="Z18" s="269"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19459,60 +19459,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="254"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="254"/>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="265"/>
-      <c r="S3" s="265"/>
-      <c r="T3" s="265"/>
-      <c r="U3" s="265"/>
-      <c r="V3" s="265"/>
-      <c r="W3" s="265"/>
-      <c r="X3" s="265"/>
-      <c r="Y3" s="265"/>
-      <c r="Z3" s="265"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
+      <c r="P3" s="270"/>
+      <c r="Q3" s="270"/>
+      <c r="R3" s="270"/>
+      <c r="S3" s="270"/>
+      <c r="T3" s="270"/>
+      <c r="U3" s="270"/>
+      <c r="V3" s="270"/>
+      <c r="W3" s="270"/>
+      <c r="X3" s="270"/>
+      <c r="Y3" s="270"/>
+      <c r="Z3" s="270"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="262" t="s">
+      <c r="C5" s="267" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="262"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
-      <c r="P5" s="265"/>
-      <c r="Q5" s="265"/>
-      <c r="R5" s="265"/>
-      <c r="S5" s="265"/>
-      <c r="T5" s="265"/>
-      <c r="U5" s="265"/>
-      <c r="V5" s="265"/>
-      <c r="W5" s="265"/>
-      <c r="X5" s="265"/>
-      <c r="Y5" s="265"/>
-      <c r="Z5" s="265"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
+      <c r="P5" s="270"/>
+      <c r="Q5" s="270"/>
+      <c r="R5" s="270"/>
+      <c r="S5" s="270"/>
+      <c r="T5" s="270"/>
+      <c r="U5" s="270"/>
+      <c r="V5" s="270"/>
+      <c r="W5" s="270"/>
+      <c r="X5" s="270"/>
+      <c r="Y5" s="270"/>
+      <c r="Z5" s="270"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19698,30 +19698,30 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="262" t="s">
+      <c r="C11" s="267" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="262"/>
-      <c r="E11" s="262"/>
-      <c r="F11" s="262"/>
-      <c r="G11" s="262"/>
-      <c r="H11" s="262"/>
-      <c r="I11" s="262"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="262"/>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="267"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="267"/>
+      <c r="K11" s="267"/>
+      <c r="L11" s="267"/>
       <c r="N11" s="92"/>
-      <c r="P11" s="265"/>
-      <c r="Q11" s="265"/>
-      <c r="R11" s="265"/>
-      <c r="S11" s="265"/>
-      <c r="T11" s="265"/>
-      <c r="U11" s="265"/>
-      <c r="V11" s="265"/>
-      <c r="W11" s="265"/>
-      <c r="X11" s="265"/>
-      <c r="Y11" s="265"/>
-      <c r="Z11" s="265"/>
+      <c r="P11" s="270"/>
+      <c r="Q11" s="270"/>
+      <c r="R11" s="270"/>
+      <c r="S11" s="270"/>
+      <c r="T11" s="270"/>
+      <c r="U11" s="270"/>
+      <c r="V11" s="270"/>
+      <c r="W11" s="270"/>
+      <c r="X11" s="270"/>
+      <c r="Y11" s="270"/>
+      <c r="Z11" s="270"/>
       <c r="AB11" s="112"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -19963,18 +19963,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="262" t="s">
+      <c r="C18" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="262"/>
-      <c r="E18" s="262"/>
-      <c r="F18" s="262"/>
-      <c r="G18" s="262"/>
-      <c r="H18" s="262"/>
-      <c r="I18" s="262"/>
-      <c r="J18" s="262"/>
-      <c r="K18" s="262"/>
-      <c r="L18" s="262"/>
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20187,23 +20187,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="265"/>
-      <c r="C25" s="265"/>
+      <c r="B25" s="270"/>
+      <c r="C25" s="270"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="262" t="s">
+      <c r="C26" s="267" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="262"/>
-      <c r="E26" s="262"/>
-      <c r="F26" s="262"/>
-      <c r="G26" s="262"/>
-      <c r="H26" s="262"/>
-      <c r="I26" s="262"/>
-      <c r="J26" s="262"/>
-      <c r="K26" s="262"/>
-      <c r="L26" s="262"/>
+      <c r="D26" s="267"/>
+      <c r="E26" s="267"/>
+      <c r="F26" s="267"/>
+      <c r="G26" s="267"/>
+      <c r="H26" s="267"/>
+      <c r="I26" s="267"/>
+      <c r="J26" s="267"/>
+      <c r="K26" s="267"/>
+      <c r="L26" s="267"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20395,18 +20395,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="262" t="s">
+      <c r="C33" s="267" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="262"/>
-      <c r="E33" s="262"/>
-      <c r="F33" s="262"/>
-      <c r="G33" s="262"/>
-      <c r="H33" s="262"/>
-      <c r="I33" s="262"/>
-      <c r="J33" s="262"/>
-      <c r="K33" s="262"/>
-      <c r="L33" s="262"/>
+      <c r="D33" s="267"/>
+      <c r="E33" s="267"/>
+      <c r="F33" s="267"/>
+      <c r="G33" s="267"/>
+      <c r="H33" s="267"/>
+      <c r="I33" s="267"/>
+      <c r="J33" s="267"/>
+      <c r="K33" s="267"/>
+      <c r="L33" s="267"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20590,18 +20590,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="262" t="s">
+      <c r="C40" s="267" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="262"/>
-      <c r="E40" s="262"/>
-      <c r="F40" s="262"/>
-      <c r="G40" s="262"/>
-      <c r="H40" s="262"/>
-      <c r="I40" s="262"/>
-      <c r="J40" s="262"/>
-      <c r="K40" s="262"/>
-      <c r="L40" s="262"/>
+      <c r="D40" s="267"/>
+      <c r="E40" s="267"/>
+      <c r="F40" s="267"/>
+      <c r="G40" s="267"/>
+      <c r="H40" s="267"/>
+      <c r="I40" s="267"/>
+      <c r="J40" s="267"/>
+      <c r="K40" s="267"/>
+      <c r="L40" s="267"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20915,60 +20915,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
-      <c r="S2" s="265"/>
-      <c r="T2" s="265"/>
-      <c r="U2" s="265"/>
-      <c r="V2" s="265"/>
-      <c r="W2" s="265"/>
-      <c r="X2" s="265"/>
-      <c r="Y2" s="265"/>
-      <c r="Z2" s="265"/>
-      <c r="AA2" s="265"/>
-      <c r="AB2" s="265"/>
-      <c r="AC2" s="265"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
+      <c r="S2" s="270"/>
+      <c r="T2" s="270"/>
+      <c r="U2" s="270"/>
+      <c r="V2" s="270"/>
+      <c r="W2" s="270"/>
+      <c r="X2" s="270"/>
+      <c r="Y2" s="270"/>
+      <c r="Z2" s="270"/>
+      <c r="AA2" s="270"/>
+      <c r="AB2" s="270"/>
+      <c r="AC2" s="270"/>
       <c r="AE2" s="111"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="267" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
-      <c r="S4" s="265"/>
-      <c r="T4" s="265"/>
-      <c r="U4" s="265"/>
-      <c r="V4" s="265"/>
-      <c r="W4" s="265"/>
-      <c r="X4" s="265"/>
-      <c r="Y4" s="265"/>
-      <c r="Z4" s="265"/>
-      <c r="AA4" s="265"/>
-      <c r="AB4" s="265"/>
-      <c r="AC4" s="265"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
+      <c r="S4" s="270"/>
+      <c r="T4" s="270"/>
+      <c r="U4" s="270"/>
+      <c r="V4" s="270"/>
+      <c r="W4" s="270"/>
+      <c r="X4" s="270"/>
+      <c r="Y4" s="270"/>
+      <c r="Z4" s="270"/>
+      <c r="AA4" s="270"/>
+      <c r="AB4" s="270"/>
+      <c r="AC4" s="270"/>
       <c r="AE4" s="112"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -21331,18 +21331,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="262" t="s">
+      <c r="C13" s="267" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="262"/>
-      <c r="E13" s="262"/>
-      <c r="F13" s="262"/>
-      <c r="G13" s="262"/>
-      <c r="H13" s="262"/>
-      <c r="I13" s="262"/>
-      <c r="J13" s="262"/>
-      <c r="K13" s="262"/>
-      <c r="L13" s="262"/>
+      <c r="D13" s="267"/>
+      <c r="E13" s="267"/>
+      <c r="F13" s="267"/>
+      <c r="G13" s="267"/>
+      <c r="H13" s="267"/>
+      <c r="I13" s="267"/>
+      <c r="J13" s="267"/>
+      <c r="K13" s="267"/>
+      <c r="L13" s="267"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21435,18 +21435,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="262" t="s">
+      <c r="C18" s="267" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="262"/>
-      <c r="E18" s="262"/>
-      <c r="F18" s="262"/>
-      <c r="G18" s="262"/>
-      <c r="H18" s="262"/>
-      <c r="I18" s="262"/>
-      <c r="J18" s="262"/>
-      <c r="K18" s="262"/>
-      <c r="L18" s="262"/>
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21638,18 +21638,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="262" t="s">
+      <c r="C25" s="267" t="s">
         <v>271</v>
       </c>
-      <c r="D25" s="262"/>
-      <c r="E25" s="262"/>
-      <c r="F25" s="262"/>
-      <c r="G25" s="262"/>
-      <c r="H25" s="262"/>
-      <c r="I25" s="262"/>
-      <c r="J25" s="262"/>
-      <c r="K25" s="262"/>
-      <c r="L25" s="262"/>
+      <c r="D25" s="267"/>
+      <c r="E25" s="267"/>
+      <c r="F25" s="267"/>
+      <c r="G25" s="267"/>
+      <c r="H25" s="267"/>
+      <c r="I25" s="267"/>
+      <c r="J25" s="267"/>
+      <c r="K25" s="267"/>
+      <c r="L25" s="267"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21787,18 +21787,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="262" t="s">
+      <c r="C31" s="267" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="262"/>
-      <c r="E31" s="262"/>
-      <c r="F31" s="262"/>
-      <c r="G31" s="262"/>
-      <c r="H31" s="262"/>
-      <c r="I31" s="262"/>
-      <c r="J31" s="262"/>
-      <c r="K31" s="262"/>
-      <c r="L31" s="262"/>
+      <c r="D31" s="267"/>
+      <c r="E31" s="267"/>
+      <c r="F31" s="267"/>
+      <c r="G31" s="267"/>
+      <c r="H31" s="267"/>
+      <c r="I31" s="267"/>
+      <c r="J31" s="267"/>
+      <c r="K31" s="267"/>
+      <c r="L31" s="267"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -22009,10 +22009,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="259" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="254"/>
+      <c r="C4" s="259"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>124.76</v>
+        <v>134.81</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22038,7 +22038,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>6086666.1200000001</v>
+        <v>6576975.4699999997</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22056,7 +22056,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22065,7 +22065,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>0.87980000000000003</v>
+        <v>0.81510000000000005</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22097,10 +22097,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="254" t="s">
+      <c r="B15" s="259" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="254"/>
+      <c r="C15" s="259"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22135,7 +22135,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.5280999999999996E-2</v>
+        <v>8.3309500000000009E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22144,7 +22144,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.5280999999999996E-2</v>
+        <v>8.3309500000000009E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22189,60 +22189,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="254"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="254"/>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="265"/>
-      <c r="S3" s="265"/>
-      <c r="T3" s="265"/>
-      <c r="U3" s="265"/>
-      <c r="V3" s="265"/>
-      <c r="W3" s="265"/>
-      <c r="X3" s="265"/>
-      <c r="Y3" s="265"/>
-      <c r="Z3" s="265"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
+      <c r="P3" s="270"/>
+      <c r="Q3" s="270"/>
+      <c r="R3" s="270"/>
+      <c r="S3" s="270"/>
+      <c r="T3" s="270"/>
+      <c r="U3" s="270"/>
+      <c r="V3" s="270"/>
+      <c r="W3" s="270"/>
+      <c r="X3" s="270"/>
+      <c r="Y3" s="270"/>
+      <c r="Z3" s="270"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="262" t="s">
+      <c r="C5" s="267" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="262"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
-      <c r="P5" s="265"/>
-      <c r="Q5" s="265"/>
-      <c r="R5" s="265"/>
-      <c r="S5" s="265"/>
-      <c r="T5" s="265"/>
-      <c r="U5" s="265"/>
-      <c r="V5" s="265"/>
-      <c r="W5" s="265"/>
-      <c r="X5" s="265"/>
-      <c r="Y5" s="265"/>
-      <c r="Z5" s="265"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
+      <c r="P5" s="270"/>
+      <c r="Q5" s="270"/>
+      <c r="R5" s="270"/>
+      <c r="S5" s="270"/>
+      <c r="T5" s="270"/>
+      <c r="U5" s="270"/>
+      <c r="V5" s="270"/>
+      <c r="W5" s="270"/>
+      <c r="X5" s="270"/>
+      <c r="Y5" s="270"/>
+      <c r="Z5" s="270"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22488,10 +22488,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="254" t="s">
+      <c r="B13" s="259" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="254"/>
+      <c r="C13" s="259"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22511,10 +22511,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="254" t="s">
+      <c r="B18" s="259" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="254"/>
+      <c r="C18" s="259"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22628,37 +22628,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="267" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22847,18 +22847,18 @@
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="262" t="s">
+      <c r="C10" s="267" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="262"/>
-      <c r="E10" s="262"/>
-      <c r="F10" s="262"/>
-      <c r="G10" s="262"/>
-      <c r="H10" s="262"/>
-      <c r="I10" s="262"/>
-      <c r="J10" s="262"/>
-      <c r="K10" s="262"/>
-      <c r="L10" s="262"/>
+      <c r="D10" s="267"/>
+      <c r="E10" s="267"/>
+      <c r="F10" s="267"/>
+      <c r="G10" s="267"/>
+      <c r="H10" s="267"/>
+      <c r="I10" s="267"/>
+      <c r="J10" s="267"/>
+      <c r="K10" s="267"/>
+      <c r="L10" s="267"/>
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23052,18 +23052,18 @@
       <c r="N15" s="92"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="262" t="s">
+      <c r="C16" s="267" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="262"/>
-      <c r="E16" s="262"/>
-      <c r="F16" s="262"/>
-      <c r="G16" s="262"/>
-      <c r="H16" s="262"/>
-      <c r="I16" s="262"/>
-      <c r="J16" s="262"/>
-      <c r="K16" s="262"/>
-      <c r="L16" s="262"/>
+      <c r="D16" s="267"/>
+      <c r="E16" s="267"/>
+      <c r="F16" s="267"/>
+      <c r="G16" s="267"/>
+      <c r="H16" s="267"/>
+      <c r="I16" s="267"/>
+      <c r="J16" s="267"/>
+      <c r="K16" s="267"/>
+      <c r="L16" s="267"/>
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -23197,18 +23197,18 @@
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="262" t="s">
+      <c r="C21" s="267" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="262"/>
-      <c r="E21" s="262"/>
-      <c r="F21" s="262"/>
-      <c r="G21" s="262"/>
-      <c r="H21" s="262"/>
-      <c r="I21" s="262"/>
-      <c r="J21" s="262"/>
-      <c r="K21" s="262"/>
-      <c r="L21" s="262"/>
+      <c r="D21" s="267"/>
+      <c r="E21" s="267"/>
+      <c r="F21" s="267"/>
+      <c r="G21" s="267"/>
+      <c r="H21" s="267"/>
+      <c r="I21" s="267"/>
+      <c r="J21" s="267"/>
+      <c r="K21" s="267"/>
+      <c r="L21" s="267"/>
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -23292,18 +23292,18 @@
       <c r="N25" s="92"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="262" t="s">
+      <c r="C26" s="267" t="s">
         <v>204</v>
       </c>
-      <c r="D26" s="262"/>
-      <c r="E26" s="262"/>
-      <c r="F26" s="262"/>
-      <c r="G26" s="262"/>
-      <c r="H26" s="262"/>
-      <c r="I26" s="262"/>
-      <c r="J26" s="262"/>
-      <c r="K26" s="262"/>
-      <c r="L26" s="262"/>
+      <c r="D26" s="267"/>
+      <c r="E26" s="267"/>
+      <c r="F26" s="267"/>
+      <c r="G26" s="267"/>
+      <c r="H26" s="267"/>
+      <c r="I26" s="267"/>
+      <c r="J26" s="267"/>
+      <c r="K26" s="267"/>
+      <c r="L26" s="267"/>
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -23573,10 +23573,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="254" t="s">
+      <c r="B37" s="259" t="s">
         <v>209</v>
       </c>
-      <c r="C37" s="254"/>
+      <c r="C37" s="259"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -23669,10 +23669,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="254" t="s">
+      <c r="B49" s="259" t="s">
         <v>214</v>
       </c>
-      <c r="C49" s="254"/>
+      <c r="C49" s="259"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -23728,10 +23728,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="254" t="s">
+      <c r="B57" s="259" t="s">
         <v>332</v>
       </c>
-      <c r="C57" s="254"/>
+      <c r="C57" s="259"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -23871,10 +23871,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="259" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="254"/>
+      <c r="C4" s="259"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>124.76</v>
+        <v>134.81</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23937,7 +23937,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.30007285151232449</v>
+        <v>0.20315324497201698</v>
       </c>
     </row>
   </sheetData>
@@ -23993,37 +23993,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="267" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24074,23 +24074,23 @@
       <c r="B6" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="C6" s="269">
+      <c r="C6" s="251">
         <f>Statement!M26</f>
         <v>-2.57</v>
       </c>
-      <c r="D6" s="269">
+      <c r="D6" s="251">
         <f>Statement!N26</f>
         <v>-1.51</v>
       </c>
-      <c r="E6" s="269">
+      <c r="E6" s="251">
         <f>Statement!O26</f>
         <v>0.35</v>
       </c>
-      <c r="F6" s="269">
+      <c r="F6" s="251">
         <f>Statement!P26</f>
         <v>1.88</v>
       </c>
-      <c r="G6" s="270">
+      <c r="G6" s="252">
         <f>Statement!Q26</f>
         <v>3.2570201538405805</v>
       </c>
@@ -24105,23 +24105,23 @@
       <c r="B7" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="C7" s="269">
+      <c r="C7" s="251">
         <f>Statement!M82</f>
         <v>0</v>
       </c>
-      <c r="D7" s="269">
+      <c r="D7" s="251">
         <f>Statement!N82</f>
         <v>0</v>
       </c>
-      <c r="E7" s="269">
+      <c r="E7" s="251">
         <f>Statement!O82</f>
         <v>0</v>
       </c>
-      <c r="F7" s="269">
+      <c r="F7" s="251">
         <f>Statement!P82</f>
         <v>0</v>
       </c>
-      <c r="G7" s="270">
+      <c r="G7" s="252">
         <f>Statement!Q82</f>
         <v>0</v>
       </c>
@@ -24136,18 +24136,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="262" t="s">
+      <c r="C9" s="267" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="262"/>
-      <c r="E9" s="262"/>
-      <c r="F9" s="262"/>
-      <c r="G9" s="262"/>
-      <c r="H9" s="262"/>
-      <c r="I9" s="262"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="262"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24268,18 +24268,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="262" t="s">
+      <c r="C14" s="267" t="s">
         <v>426</v>
       </c>
-      <c r="D14" s="262"/>
-      <c r="E14" s="262"/>
-      <c r="F14" s="262"/>
-      <c r="G14" s="262"/>
-      <c r="H14" s="262"/>
-      <c r="I14" s="262"/>
-      <c r="J14" s="262"/>
-      <c r="K14" s="262"/>
-      <c r="L14" s="262"/>
+      <c r="D14" s="267"/>
+      <c r="E14" s="267"/>
+      <c r="F14" s="267"/>
+      <c r="G14" s="267"/>
+      <c r="H14" s="267"/>
+      <c r="I14" s="267"/>
+      <c r="J14" s="267"/>
+      <c r="K14" s="267"/>
+      <c r="L14" s="267"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24369,17 +24369,17 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="254" t="s">
+      <c r="B20" s="259" t="s">
         <v>428</v>
       </c>
-      <c r="C20" s="254"/>
+      <c r="C20" s="259"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C21" s="271">
+      <c r="C21" s="253">
         <f>G7</f>
         <v>0</v>
       </c>
@@ -24388,7 +24388,7 @@
       <c r="B22" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C22" s="272">
+      <c r="C22" s="254">
         <v>0</v>
       </c>
     </row>
@@ -24396,7 +24396,7 @@
       <c r="B23" s="39" t="s">
         <v>431</v>
       </c>
-      <c r="C23" s="273">
+      <c r="C23" s="255">
         <f>C21*(1+C22)</f>
         <v>0</v>
       </c>
@@ -24414,7 +24414,7 @@
       <c r="B25" s="39" t="s">
         <v>432</v>
       </c>
-      <c r="C25" s="272">
+      <c r="C25" s="254">
         <v>0</v>
       </c>
     </row>
@@ -24429,12 +24429,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C9:L9"/>
     <mergeCell ref="C14:L14"/>
-    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24474,60 +24474,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="254"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="254"/>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="265"/>
-      <c r="S3" s="265"/>
-      <c r="T3" s="265"/>
-      <c r="U3" s="265"/>
-      <c r="V3" s="265"/>
-      <c r="W3" s="265"/>
-      <c r="X3" s="265"/>
-      <c r="Y3" s="265"/>
-      <c r="Z3" s="265"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
+      <c r="P3" s="270"/>
+      <c r="Q3" s="270"/>
+      <c r="R3" s="270"/>
+      <c r="S3" s="270"/>
+      <c r="T3" s="270"/>
+      <c r="U3" s="270"/>
+      <c r="V3" s="270"/>
+      <c r="W3" s="270"/>
+      <c r="X3" s="270"/>
+      <c r="Y3" s="270"/>
+      <c r="Z3" s="270"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="262" t="s">
+      <c r="C5" s="267" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="262"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
-      <c r="P5" s="265"/>
-      <c r="Q5" s="265"/>
-      <c r="R5" s="265"/>
-      <c r="S5" s="265"/>
-      <c r="T5" s="265"/>
-      <c r="U5" s="265"/>
-      <c r="V5" s="265"/>
-      <c r="W5" s="265"/>
-      <c r="X5" s="265"/>
-      <c r="Y5" s="265"/>
-      <c r="Z5" s="265"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
+      <c r="P5" s="270"/>
+      <c r="Q5" s="270"/>
+      <c r="R5" s="270"/>
+      <c r="S5" s="270"/>
+      <c r="T5" s="270"/>
+      <c r="U5" s="270"/>
+      <c r="V5" s="270"/>
+      <c r="W5" s="270"/>
+      <c r="X5" s="270"/>
+      <c r="Y5" s="270"/>
+      <c r="Z5" s="270"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -24756,10 +24756,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="266" t="s">
+      <c r="B14" s="271" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="267"/>
+      <c r="C14" s="272"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -24767,7 +24767,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>124.76</v>
+        <v>134.81</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24786,20 +24786,20 @@
       <c r="C17" s="160">
         <v>0.2</v>
       </c>
-      <c r="E17" s="268" t="s">
+      <c r="E17" s="273" t="s">
         <v>230</v>
       </c>
-      <c r="F17" s="268"/>
-      <c r="G17" s="268"/>
-      <c r="H17" s="268"/>
-      <c r="I17" s="268"/>
+      <c r="F17" s="273"/>
+      <c r="G17" s="273"/>
+      <c r="H17" s="273"/>
+      <c r="I17" s="273"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="266" t="s">
+      <c r="B19" s="271" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="267"/>
+      <c r="C19" s="272"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -24833,7 +24833,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>5812942.6800000006</v>
+        <v>6281202.3300000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24860,15 +24860,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>4421121.6800000006</v>
+        <v>4889381.33</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="266" t="s">
+      <c r="B28" s="271" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="267"/>
+      <c r="C28" s="272"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -24943,18 +24943,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="262" t="s">
+      <c r="C39" s="267" t="s">
         <v>233</v>
       </c>
-      <c r="D39" s="262"/>
-      <c r="E39" s="262"/>
-      <c r="F39" s="262"/>
-      <c r="G39" s="262"/>
-      <c r="H39" s="262"/>
-      <c r="I39" s="262"/>
-      <c r="J39" s="262"/>
-      <c r="K39" s="262"/>
-      <c r="L39" s="262"/>
+      <c r="D39" s="267"/>
+      <c r="E39" s="267"/>
+      <c r="F39" s="267"/>
+      <c r="G39" s="267"/>
+      <c r="H39" s="267"/>
+      <c r="I39" s="267"/>
+      <c r="J39" s="267"/>
+      <c r="K39" s="267"/>
+      <c r="L39" s="267"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -31998,17 +31998,33 @@
       <c r="Q116" s="26">
         <v>177.14</v>
       </c>
-      <c r="T116" s="68"/>
-      <c r="U116" s="68"/>
-      <c r="V116" s="68"/>
-      <c r="W116" s="68"/>
-      <c r="X116" s="68"/>
-      <c r="Y116" s="68"/>
-      <c r="Z116" s="68"/>
-      <c r="AA116" s="68"/>
+      <c r="T116" s="26">
+        <v>208.67</v>
+      </c>
+      <c r="U116" s="26">
+        <v>282.02</v>
+      </c>
+      <c r="V116" s="26">
+        <v>325.2</v>
+      </c>
+      <c r="W116" s="26">
+        <v>310.54000000000002</v>
+      </c>
+      <c r="X116" s="26">
+        <v>410.02</v>
+      </c>
+      <c r="Y116" s="26">
+        <v>321.83999999999997</v>
+      </c>
+      <c r="Z116" s="26">
+        <v>177.14</v>
+      </c>
+      <c r="AA116" s="26">
+        <v>98.57</v>
+      </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>124.76</v>
+        <v>134.81</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32045,17 +32061,41 @@
         <f>Q116/Q85</f>
         <v>177.14</v>
       </c>
-      <c r="T117" s="68"/>
-      <c r="U117" s="68"/>
-      <c r="V117" s="68"/>
-      <c r="W117" s="68"/>
-      <c r="X117" s="68"/>
-      <c r="Y117" s="68"/>
-      <c r="Z117" s="68"/>
-      <c r="AA117" s="68"/>
+      <c r="T117" s="65">
+        <f t="shared" ref="T117:AA117" si="74">T116/T85</f>
+        <v>208.67</v>
+      </c>
+      <c r="U117" s="65">
+        <f t="shared" si="74"/>
+        <v>282.02</v>
+      </c>
+      <c r="V117" s="65">
+        <f t="shared" si="74"/>
+        <v>325.2</v>
+      </c>
+      <c r="W117" s="65">
+        <f t="shared" si="74"/>
+        <v>310.54000000000002</v>
+      </c>
+      <c r="X117" s="65">
+        <f t="shared" si="74"/>
+        <v>410.02</v>
+      </c>
+      <c r="Y117" s="65">
+        <f t="shared" si="74"/>
+        <v>321.83999999999997</v>
+      </c>
+      <c r="Z117" s="65">
+        <f t="shared" si="74"/>
+        <v>177.14</v>
+      </c>
+      <c r="AA117" s="65">
+        <f t="shared" si="74"/>
+        <v>98.57</v>
+      </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>124.76</v>
+        <v>134.81</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32169,19 +32209,19 @@
         <v>102</v>
       </c>
       <c r="M123" s="76">
-        <f t="shared" ref="M123:P123" si="74">M121*M122</f>
+        <f t="shared" ref="M123:P123" si="75">M121*M122</f>
         <v>-9.0933010338554776E-2</v>
       </c>
       <c r="N123" s="76">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>-7.9713974900548212E-2</v>
       </c>
       <c r="O123" s="76">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1.6842478224909509E-2</v>
       </c>
       <c r="P123" s="76">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>6.804340077189705E-2</v>
       </c>
       <c r="Q123" s="76">
@@ -32243,19 +32283,19 @@
         <v>104</v>
       </c>
       <c r="M125" s="76">
-        <f t="shared" ref="M125:P125" si="75">M123*M124</f>
+        <f t="shared" ref="M125:P125" si="76">M123*M124</f>
         <v>-0.1172094274309237</v>
       </c>
       <c r="N125" s="76">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>-0.1098993133829449</v>
       </c>
       <c r="O125" s="76">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>2.4511022866479229E-2</v>
       </c>
       <c r="P125" s="76">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0.10742101752471045</v>
       </c>
       <c r="Q125" s="76">
@@ -32417,35 +32457,35 @@
       <c r="P131" s="49"/>
       <c r="Q131" s="49"/>
       <c r="T131" s="25">
-        <f t="shared" ref="T131:AA131" si="76">U5</f>
+        <f t="shared" ref="T131:AA131" si="77">U5</f>
         <v>192594</v>
       </c>
       <c r="U131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>209550</v>
       </c>
       <c r="V131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>230743</v>
       </c>
       <c r="W131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>252265</v>
       </c>
       <c r="X131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>271713</v>
       </c>
       <c r="Y131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>282868</v>
       </c>
       <c r="Z131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>291967</v>
       </c>
       <c r="AA131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AC131" s="49"/>
@@ -32470,31 +32510,31 @@
       <c r="P132" s="49"/>
       <c r="Q132" s="49"/>
       <c r="T132" s="227" t="str">
-        <f t="shared" ref="T132:Z132" si="77">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
+        <f t="shared" ref="T132:Z132" si="78">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U132" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="V132" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="W132" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="X132" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="Y132" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="Z132" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="AA132" s="227" t="str">
@@ -32587,55 +32627,55 @@
         <v>143</v>
       </c>
       <c r="M137" s="120">
-        <f t="shared" ref="M137:Q138" si="78">M30/M5*365</f>
+        <f t="shared" ref="M137:Q138" si="79">M30/M5*365</f>
         <v>48.268925557877274</v>
       </c>
       <c r="N137" s="120">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>46.15954207770065</v>
       </c>
       <c r="O137" s="120">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>61.147288033153274</v>
       </c>
       <c r="P137" s="120">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>62.908268986021838</v>
       </c>
       <c r="Q137" s="120">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>57.278802107578244</v>
       </c>
       <c r="T137" s="120">
-        <f t="shared" ref="T137:AA137" si="79">T30/T5*90</f>
+        <f t="shared" ref="T137:AA137" si="80">T30/T5*90</f>
         <v>39.225579973868236</v>
       </c>
       <c r="U137" s="120">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>44.027072494470232</v>
       </c>
       <c r="V137" s="120">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>55.371367215461703</v>
       </c>
       <c r="W137" s="120">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>44.536432307805654</v>
       </c>
       <c r="X137" s="120">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>40.28585019721325</v>
       </c>
       <c r="Y137" s="120">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>41.234721930860871</v>
       </c>
       <c r="Z137" s="120">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>51.806602372838213</v>
       </c>
       <c r="AA137" s="120">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>38.558261721358917</v>
       </c>
       <c r="AC137" s="120">
@@ -32648,55 +32688,55 @@
         <v>144</v>
       </c>
       <c r="M138" s="120">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="N138" s="120">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="O138" s="120">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="P138" s="120">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q138" s="120">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="T138" s="120">
-        <f t="shared" ref="T138:AA138" si="80">T31/T6*365</f>
+        <f t="shared" ref="T138:AA138" si="81">T31/T6*365</f>
         <v>0</v>
       </c>
       <c r="U138" s="120">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="V138" s="120">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W138" s="120">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="X138" s="120">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="Y138" s="120">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="Z138" s="120">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AA138" s="120">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AC138" s="120">
@@ -32729,35 +32769,35 @@
         <v>10.131710466036401</v>
       </c>
       <c r="T139" s="120">
-        <f t="shared" ref="T139:AA139" si="81">T38/T6*90</f>
+        <f t="shared" ref="T139:AA139" si="82">T38/T6*90</f>
         <v>6.4721535829690167</v>
       </c>
       <c r="U139" s="120">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>6.2937907244154845</v>
       </c>
       <c r="V139" s="120">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>9.7461179465422152</v>
       </c>
       <c r="W139" s="120">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>3.4381142437018921</v>
       </c>
       <c r="X139" s="120">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>9.9823488892715684</v>
       </c>
       <c r="Y139" s="120">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>4.2929333440282349</v>
       </c>
       <c r="Z139" s="120">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>9.3484330965337215</v>
       </c>
       <c r="AA139" s="120">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>8.5423032546816948</v>
       </c>
       <c r="AC139" s="120">
@@ -32774,55 +32814,55 @@
         <v>7.0240205192856493</v>
       </c>
       <c r="N140" s="120">
-        <f t="shared" ref="N140:Q140" si="82">N137+N138-N139</f>
+        <f t="shared" ref="N140:Q140" si="83">N137+N138-N139</f>
         <v>41.838907667908934</v>
       </c>
       <c r="O140" s="120">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>54.862111579122804</v>
       </c>
       <c r="P140" s="120">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>51.471381264742163</v>
       </c>
       <c r="Q140" s="120">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>47.147091641541842</v>
       </c>
       <c r="T140" s="120">
-        <f t="shared" ref="T140" si="83">T137+T138-T139</f>
+        <f t="shared" ref="T140" si="84">T137+T138-T139</f>
         <v>32.753426390899222</v>
       </c>
       <c r="U140" s="120">
-        <f t="shared" ref="U140" si="84">U137+U138-U139</f>
+        <f t="shared" ref="U140" si="85">U137+U138-U139</f>
         <v>37.733281770054745</v>
       </c>
       <c r="V140" s="120">
-        <f t="shared" ref="V140" si="85">V137+V138-V139</f>
+        <f t="shared" ref="V140" si="86">V137+V138-V139</f>
         <v>45.62524926891949</v>
       </c>
       <c r="W140" s="120">
-        <f t="shared" ref="W140" si="86">W137+W138-W139</f>
+        <f t="shared" ref="W140" si="87">W137+W138-W139</f>
         <v>41.098318064103765</v>
       </c>
       <c r="X140" s="120">
-        <f t="shared" ref="X140" si="87">X137+X138-X139</f>
+        <f t="shared" ref="X140" si="88">X137+X138-X139</f>
         <v>30.30350130794168</v>
       </c>
       <c r="Y140" s="120">
-        <f t="shared" ref="Y140" si="88">Y137+Y138-Y139</f>
+        <f t="shared" ref="Y140" si="89">Y137+Y138-Y139</f>
         <v>36.941788586832637</v>
       </c>
       <c r="Z140" s="120">
-        <f t="shared" ref="Z140:AA140" si="89">Z137+Z138-Z139</f>
+        <f t="shared" ref="Z140:AA140" si="90">Z137+Z138-Z139</f>
         <v>42.458169276304488</v>
       </c>
       <c r="AA140" s="120">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>30.015958466677223</v>
       </c>
       <c r="AC140" s="120">
-        <f t="shared" ref="AC140" si="90">AC137+AC138-AC139</f>
+        <f t="shared" ref="AC140" si="91">AC137+AC138-AC139</f>
         <v>32.453474658634278</v>
       </c>
     </row>
@@ -32851,35 +32891,35 @@
         <v>0</v>
       </c>
       <c r="T141" s="120">
-        <f t="shared" ref="T141:AA141" si="91">T108/T49</f>
+        <f t="shared" ref="T141:AA141" si="92">T108/T49</f>
         <v>0</v>
       </c>
       <c r="U141" s="120">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="V141" s="120">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="W141" s="120">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="X141" s="120">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Y141" s="120">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Z141" s="120">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AA141" s="120">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AC141" s="120">
@@ -32912,35 +32952,35 @@
         <v>-0.94696311671959887</v>
       </c>
       <c r="T142" s="181">
-        <f t="shared" ref="T142:AA142" si="92">(T108-T107)/T49</f>
+        <f t="shared" ref="T142:AA142" si="93">(T108-T107)/T49</f>
         <v>-1.1581549630742272</v>
       </c>
       <c r="U142" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>-1.1381695975332329</v>
       </c>
       <c r="V142" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>-1.1835995391425627</v>
       </c>
       <c r="W142" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>-1.2112223184378168</v>
       </c>
       <c r="X142" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>-1.2008267905521934</v>
       </c>
       <c r="Y142" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>-0.93319510928545912</v>
       </c>
       <c r="Z142" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>-0.94696311671959887</v>
       </c>
       <c r="AA142" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>-1.0000409552194194</v>
       </c>
       <c r="AC142" s="181">
@@ -32973,35 +33013,35 @@
         <v>2.6098107949225979</v>
       </c>
       <c r="T143" s="120">
-        <f t="shared" ref="T143:AA143" si="93">(T107+T30)/T40</f>
+        <f t="shared" ref="T143:AA143" si="94">(T107+T30)/T40</f>
         <v>3.040255064143722</v>
       </c>
       <c r="U143" s="120">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>3.0114195356776459</v>
       </c>
       <c r="V143" s="120">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.6167192839938327</v>
       </c>
       <c r="W143" s="120">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.6333212317238193</v>
       </c>
       <c r="X143" s="120">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.7284904207406715</v>
       </c>
       <c r="Y143" s="120">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.7751640731415361</v>
       </c>
       <c r="Z143" s="120">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.6098107949225979</v>
       </c>
       <c r="AA143" s="120">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.6421703703445658</v>
       </c>
       <c r="AC143" s="120">
@@ -33034,35 +33074,35 @@
         <v>2.6065702860211775</v>
       </c>
       <c r="T144" s="120">
-        <f t="shared" ref="T144:AA144" si="94">T32/T40</f>
+        <f t="shared" ref="T144:AA144" si="95">T32/T40</f>
         <v>3.2782037239868567</v>
       </c>
       <c r="U144" s="120">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>3.0936419462606648</v>
       </c>
       <c r="V144" s="120">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.6089699714137522</v>
       </c>
       <c r="W144" s="120">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.6836023191084415</v>
       </c>
       <c r="X144" s="120">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.8087351474278877</v>
       </c>
       <c r="Y144" s="120">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.8214492095595824</v>
       </c>
       <c r="Z144" s="120">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.6065702860211775</v>
       </c>
       <c r="AA144" s="120">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.6231009869120072</v>
       </c>
       <c r="AC144" s="120">
@@ -33095,35 +33135,35 @@
         <v>N/A</v>
       </c>
       <c r="T145" s="183" t="str">
-        <f t="shared" ref="T145:AA145" si="95">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
+        <f t="shared" ref="T145:AA145" si="96">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>N/A</v>
       </c>
       <c r="U145" s="183" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>N/A</v>
       </c>
       <c r="V145" s="183" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>N/A</v>
       </c>
       <c r="W145" s="183" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>N/A</v>
       </c>
       <c r="X145" s="183" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>N/A</v>
       </c>
       <c r="Y145" s="183" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>N/A</v>
       </c>
       <c r="Z145" s="183" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>N/A</v>
       </c>
       <c r="AA145" s="183" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>N/A</v>
       </c>
       <c r="AC145" s="183" t="str">
@@ -33165,7 +33205,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>36.795880819513265</v>
+        <v>39.759960670716445</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -33202,7 +33242,7 @@
       <c r="AA147" s="49"/>
       <c r="AC147" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>5.5477870892931662</v>
+        <v>5.994687219522377</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -33229,17 +33269,41 @@
         <f>Q117/(Statement!Q49/Statement!Q75)</f>
         <v>6.2334065327103216</v>
       </c>
-      <c r="T148" s="49"/>
-      <c r="U148" s="49"/>
-      <c r="V148" s="49"/>
-      <c r="W148" s="49"/>
-      <c r="X148" s="49"/>
-      <c r="Y148" s="49"/>
-      <c r="Z148" s="49"/>
-      <c r="AA148" s="49"/>
+      <c r="T148" s="72">
+        <f>T117/(Statement!T49/Statement!T75)</f>
+        <v>11.846084107835773</v>
+      </c>
+      <c r="U148" s="72">
+        <f>U117/(Statement!U49/Statement!U75)</f>
+        <v>15.082159928895633</v>
+      </c>
+      <c r="V148" s="72">
+        <f>V117/(Statement!V49/Statement!V75)</f>
+        <v>17.843700927778787</v>
+      </c>
+      <c r="W148" s="72">
+        <f>W117/(Statement!W49/Statement!W75)</f>
+        <v>15.792330610208252</v>
+      </c>
+      <c r="X148" s="72">
+        <f>X117/(Statement!X49/Statement!X75)</f>
+        <v>19.229621618966032</v>
+      </c>
+      <c r="Y148" s="72">
+        <f>Y117/(Statement!Y49/Statement!Y75)</f>
+        <v>11.378643023267374</v>
+      </c>
+      <c r="Z148" s="72">
+        <f>Z117/(Statement!Z49/Statement!Z75)</f>
+        <v>6.2334065327103216</v>
+      </c>
+      <c r="AA148" s="72">
+        <f>AA117/(Statement!AA49/Statement!AA75)</f>
+        <v>3.2998928051020142</v>
+      </c>
       <c r="AC148" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.1766726830123497</v>
+        <v>4.5131231516262815</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -33266,17 +33330,41 @@
         <f>Statement!Q117*Statement!Q78</f>
         <v>8845485.8999999985</v>
       </c>
-      <c r="T149" s="49"/>
-      <c r="U149" s="49"/>
-      <c r="V149" s="49"/>
-      <c r="W149" s="49"/>
-      <c r="X149" s="49"/>
-      <c r="Y149" s="49"/>
-      <c r="Z149" s="49"/>
-      <c r="AA149" s="49"/>
+      <c r="T149" s="145">
+        <f>Statement!T117*Statement!T78</f>
+        <v>10026384.83</v>
+      </c>
+      <c r="U149" s="145">
+        <f>Statement!U117*Statement!U78</f>
+        <v>13606336.92</v>
+      </c>
+      <c r="V149" s="145">
+        <f>Statement!V117*Statement!V78</f>
+        <v>15882768</v>
+      </c>
+      <c r="W149" s="145">
+        <f>Statement!W117*Statement!W78</f>
+        <v>15155594.16</v>
+      </c>
+      <c r="X149" s="145">
+        <f>Statement!X117*Statement!X78</f>
+        <v>20177904.239999998</v>
+      </c>
+      <c r="Y149" s="145">
+        <f>Statement!Y117*Statement!Y78</f>
+        <v>15905976.479999999</v>
+      </c>
+      <c r="Z149" s="145">
+        <f>Statement!Z117*Statement!Z78</f>
+        <v>8845485.8999999985</v>
+      </c>
+      <c r="AA149" s="145">
+        <f>Statement!AA117*Statement!AA78</f>
+        <v>4808934.59</v>
+      </c>
       <c r="AC149" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6086666.1200000001</v>
+        <v>6576975.4699999997</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33303,17 +33391,41 @@
         <f>Q149+Q108-Q107+Q48+Q45</f>
         <v>7569920.8999999985</v>
       </c>
-      <c r="T150" s="49"/>
-      <c r="U150" s="49"/>
-      <c r="V150" s="49"/>
-      <c r="W150" s="49"/>
-      <c r="X150" s="49"/>
-      <c r="Y150" s="49"/>
-      <c r="Z150" s="49"/>
-      <c r="AA150" s="49"/>
+      <c r="T150" s="145">
+        <f t="shared" ref="T150:AA150" si="97">T149+T108-T107+T48+T45</f>
+        <v>9138144.8300000001</v>
+      </c>
+      <c r="U150" s="145">
+        <f t="shared" si="97"/>
+        <v>12670245.92</v>
+      </c>
+      <c r="V150" s="145">
+        <f t="shared" si="97"/>
+        <v>14906831</v>
+      </c>
+      <c r="W150" s="145">
+        <f t="shared" si="97"/>
+        <v>14072972.16</v>
+      </c>
+      <c r="X150" s="145">
+        <f t="shared" si="97"/>
+        <v>19004659.239999998</v>
+      </c>
+      <c r="Y150" s="145">
+        <f t="shared" si="97"/>
+        <v>14685787.479999999</v>
+      </c>
+      <c r="Z150" s="145">
+        <f t="shared" si="97"/>
+        <v>7569920.8999999985</v>
+      </c>
+      <c r="AA150" s="145">
+        <f t="shared" si="97"/>
+        <v>3417113.59</v>
+      </c>
       <c r="AC150" s="145">
         <f ca="1">AC149+AC108-AC107+AC48+AC45</f>
-        <v>4694845.12</v>
+        <v>5185154.47</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33350,7 +33462,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="185">
         <f ca="1">AC150/AC5</f>
-        <v>4.2726515976785864</v>
+        <v>4.7188688794180624</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33387,7 +33499,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="185">
         <f ca="1">AC150/AC12</f>
-        <v>29.998435301559716</v>
+        <v>33.131342338485524</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33415,35 +33527,35 @@
         <v>222987</v>
       </c>
       <c r="T153" s="64">
-        <f t="shared" ref="T153:AA153" si="96">T59-T54+T110+T65</f>
+        <f t="shared" ref="T153:AA153" si="98">T59-T54+T110+T65</f>
         <v>26986</v>
       </c>
       <c r="U153" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>22285</v>
       </c>
       <c r="V153" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>51117</v>
       </c>
       <c r="W153" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>71994</v>
       </c>
       <c r="X153" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>51732</v>
       </c>
       <c r="Y153" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>41791</v>
       </c>
       <c r="Z153" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>57470</v>
       </c>
       <c r="AA153" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>113139</v>
       </c>
       <c r="AC153" s="64">
@@ -33497,19 +33609,19 @@
         <v>-112.87400898520085</v>
       </c>
       <c r="N155" s="72">
-        <f t="shared" ref="N155:Q155" si="97">N149/N153</f>
+        <f t="shared" ref="N155:Q155" si="99">N149/N153</f>
         <v>-95.43181061806655</v>
       </c>
       <c r="O155" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>243.27936097877384</v>
       </c>
       <c r="P155" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>103.20455372459323</v>
       </c>
       <c r="Q155" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>39.668168547942251</v>
       </c>
       <c r="T155" s="49"/>
@@ -33521,8 +33633,8 @@
       <c r="Z155" s="49"/>
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
-        <f t="shared" ref="AC155:AC156" ca="1" si="98">AC149/AC153</f>
-        <v>23.044031469113929</v>
+        <f t="shared" ref="AC155:AC156" ca="1" si="100">AC149/AC153</f>
+        <v>24.90033570336044</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33534,19 +33646,19 @@
         <v>-98.568903797199823</v>
       </c>
       <c r="N156" s="72">
-        <f t="shared" ref="N156:Q156" si="99">N150/N154</f>
+        <f t="shared" ref="N156:Q156" si="101">N150/N154</f>
         <v>-63.556731738561353</v>
       </c>
       <c r="O156" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>673.03434883720922</v>
       </c>
       <c r="P156" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>124.4016933148245</v>
       </c>
       <c r="Q156" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>49.504381582091227</v>
       </c>
       <c r="T156" s="49"/>
@@ -33558,8 +33670,8 @@
       <c r="Z156" s="49"/>
       <c r="AA156" s="49"/>
       <c r="AC156" s="72">
-        <f t="shared" ca="1" si="98"/>
-        <v>25.13003892286893</v>
+        <f t="shared" ca="1" si="100"/>
+        <v>27.75451166580503</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33571,19 +33683,19 @@
         <v>-8.8594354802363062E-3</v>
       </c>
       <c r="N157" s="74">
-        <f t="shared" ref="N157:Q157" si="100">N153/N149</f>
+        <f t="shared" ref="N157:Q157" si="102">N153/N149</f>
         <v>-1.0478686231807555E-2</v>
       </c>
       <c r="O157" s="74">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>4.1105007674171346E-3</v>
       </c>
       <c r="P157" s="74">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>9.6894949293473281E-3</v>
       </c>
       <c r="Q157" s="74">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>2.5209129551605529E-2</v>
       </c>
       <c r="T157" s="49"/>
@@ -33595,8 +33707,8 @@
       <c r="Z157" s="49"/>
       <c r="AA157" s="49"/>
       <c r="AC157" s="74">
-        <f t="shared" ref="AC157" ca="1" si="101">AC153/AC149</f>
-        <v>4.3395184620378023E-2</v>
+        <f t="shared" ref="AC157" ca="1" si="103">AC153/AC149</f>
+        <v>4.0160101129280937E-2</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33633,7 +33745,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>2.7176955075625987E-2</v>
+        <v>2.5150930311068156E-2</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -33707,7 +33819,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="156">
         <f ca="1">-AC63/AC149</f>
-        <v>3.9974264269320558E-3</v>
+        <v>3.6994208220758351E-3</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33744,7 +33856,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="156">
         <f ca="1">-(AC63+AC64)/AC149</f>
-        <v>3.9974264269320558E-3</v>
+        <v>3.6994208220758351E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33994,35 +34106,35 @@
         <v>26.910654008438819</v>
       </c>
       <c r="T168" s="72">
-        <f t="shared" ref="T168:AA168" si="102">T107/T75</f>
+        <f t="shared" ref="T168:AA168" si="104">T107/T75</f>
         <v>20.401019775373804</v>
       </c>
       <c r="U168" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>21.282534558021098</v>
       </c>
       <c r="V168" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>21.571005459408084</v>
       </c>
       <c r="W168" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>23.817445825541746</v>
       </c>
       <c r="X168" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>25.604403998079526</v>
       </c>
       <c r="Y168" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>26.395020333996712</v>
       </c>
       <c r="Z168" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>26.910654008438819</v>
       </c>
       <c r="AA168" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>29.871890627347454</v>
       </c>
       <c r="AC168" s="72">
@@ -34055,35 +34167,35 @@
         <v>0.35438073554172911</v>
       </c>
       <c r="T169" s="156">
-        <f t="shared" ref="T169:AA169" si="103">T54/T59</f>
+        <f t="shared" ref="T169:AA169" si="105">T54/T59</f>
         <v>0.42870423799448609</v>
       </c>
       <c r="U169" s="156">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.51467112161657813</v>
       </c>
       <c r="V169" s="156">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.357398253023613</v>
       </c>
       <c r="W169" s="156">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.29364485804356677</v>
       </c>
       <c r="X169" s="156">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.38149434794596088</v>
       </c>
       <c r="Y169" s="156">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.42219162145799449</v>
       </c>
       <c r="Z169" s="156">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.33801897872816422</v>
       </c>
       <c r="AA169" s="156">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.22979883399327458</v>
       </c>
       <c r="AC169" s="156">
@@ -34116,35 +34228,35 @@
         <v>0.13245803492519678</v>
       </c>
       <c r="T170" s="156">
-        <f t="shared" ref="T170:AA170" si="104">T54/T5</f>
+        <f t="shared" ref="T170:AA170" si="106">T54/T5</f>
         <v>0.14998289658885081</v>
       </c>
       <c r="U170" s="156">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.15036293965544098</v>
       </c>
       <c r="V170" s="156">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.14214745884037222</v>
       </c>
       <c r="W170" s="156">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.13442661315836232</v>
       </c>
       <c r="X170" s="156">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.13712564168632194</v>
       </c>
       <c r="Y170" s="156">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.13089178655419506</v>
       </c>
       <c r="Z170" s="156">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.1281940693185514</v>
       </c>
       <c r="AA170" s="156">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.11866752064445639</v>
       </c>
       <c r="AC170" s="156">
@@ -34177,35 +34289,35 @@
         <v>26.910654008438819</v>
       </c>
       <c r="T171" s="72">
-        <f t="shared" ref="T171:AA171" si="105">(T107-T108)/T75</f>
+        <f t="shared" ref="T171:AA171" si="107">(T107-T108)/T75</f>
         <v>20.401019775373804</v>
       </c>
       <c r="U171" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>21.282534558021098</v>
       </c>
       <c r="V171" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>21.571005459408084</v>
       </c>
       <c r="W171" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>23.817445825541746</v>
       </c>
       <c r="X171" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>25.604403998079526</v>
       </c>
       <c r="Y171" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>26.395020333996712</v>
       </c>
       <c r="Z171" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>26.910654008438819</v>
       </c>
       <c r="AA171" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>29.871890627347454</v>
       </c>
       <c r="AC171" s="72">
@@ -34247,7 +34359,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="156">
         <f ca="1">(AC107-AC108)/AC149</f>
-        <v>0.2286672165944269</v>
+        <v>0.21162022062399452</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -34275,35 +34387,35 @@
         <v>2.6406409474271603E-2</v>
       </c>
       <c r="T173" s="156">
-        <f t="shared" ref="T173:AA173" si="106">-T110/T5</f>
+        <f t="shared" ref="T173:AA173" si="108">-T110/T5</f>
         <v>4.8540041608954337E-2</v>
       </c>
       <c r="U173" s="156">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.60807709482123E-2</v>
       </c>
       <c r="V173" s="156">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>1.1643999045573849E-2</v>
       </c>
       <c r="W173" s="156">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>1.1350290149647009E-2</v>
       </c>
       <c r="X173" s="156">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>1.7247735516223019E-2</v>
       </c>
       <c r="Y173" s="156">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.5331875913187814E-2</v>
       </c>
       <c r="Z173" s="156">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>4.7888060862310337E-2</v>
       </c>
       <c r="AA173" s="156">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>1.0223758164450092E-2</v>
       </c>
       <c r="AC173" s="156">
@@ -34336,35 +34448,35 @@
         <v>7.0648208074301944E-2</v>
       </c>
       <c r="T174" s="156">
-        <f t="shared" ref="T174:AA174" si="107">-(T110/T59)</f>
+        <f t="shared" ref="T174:AA174" si="109">-(T110/T59)</f>
         <v>0.13874463037763674</v>
       </c>
       <c r="U174" s="156">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>8.9270798158778683E-2</v>
       </c>
       <c r="V174" s="156">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>2.9276252639662124E-2</v>
       </c>
       <c r="W174" s="156">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>2.4793857863695316E-2</v>
       </c>
       <c r="X174" s="156">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>4.7984560242624756E-2</v>
       </c>
       <c r="Y174" s="156">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>8.1707997483350947E-2</v>
       </c>
       <c r="Z174" s="156">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.12627006469173549</v>
       </c>
       <c r="AA174" s="156">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>1.9798237061503871E-2</v>
       </c>
       <c r="AC174" s="156">
@@ -34397,35 +34509,35 @@
         <v>1.9038982697519282</v>
       </c>
       <c r="T175" s="156">
-        <f t="shared" ref="T175:AA175" si="108">-T110/T53</f>
+        <f t="shared" ref="T175:AA175" si="110">-T110/T53</f>
         <v>3.8591172536781095</v>
       </c>
       <c r="U175" s="156">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>1.7465229485396383</v>
       </c>
       <c r="V175" s="156">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.66648456705818082</v>
       </c>
       <c r="W175" s="156">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.7295264623955432</v>
       </c>
       <c r="X175" s="156">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>1.2648255813953488</v>
       </c>
       <c r="Y175" s="156">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>1.9372361384745285</v>
       </c>
       <c r="Z175" s="156">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>3.5572478991596639</v>
       </c>
       <c r="AA175" s="156">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.71224051539012168</v>
       </c>
       <c r="AC175" s="156">
@@ -34707,7 +34819,7 @@
         <v>20614</v>
       </c>
       <c r="AC184" s="62">
-        <f t="shared" ref="AC184:AC187" si="109">SUM(X184:AA184)</f>
+        <f t="shared" ref="AC184:AC187" si="111">SUM(X184:AA184)</f>
         <v>82457</v>
       </c>
     </row>
@@ -34765,7 +34877,7 @@
         <v>11317</v>
       </c>
       <c r="AC185" s="62">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>41337</v>
       </c>
     </row>
@@ -34823,7 +34935,7 @@
         <v>8446</v>
       </c>
       <c r="AC186" s="62">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>39483</v>
       </c>
     </row>
@@ -34881,7 +34993,7 @@
         <v>682</v>
       </c>
       <c r="AC187" s="62">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>2173</v>
       </c>
     </row>
@@ -34945,61 +35057,61 @@
       <c r="K191" s="81"/>
       <c r="L191" s="81"/>
       <c r="M191" s="81">
-        <f t="shared" ref="M191:Q193" si="110">IF(L183=0,
+        <f t="shared" ref="M191:Q193" si="112">IF(L183=0,
 IF(M183=0,0,IF(M183&gt;0,1,-1)),
 (M183-L183)/ABS(L183)
 )</f>
         <v>1</v>
       </c>
       <c r="N191" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>0.51361387508439493</v>
       </c>
       <c r="O191" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>0.47961112512659637</v>
       </c>
       <c r="P191" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>0.50124788724041469</v>
       </c>
       <c r="Q191" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>0.43769124538500914</v>
       </c>
       <c r="T191" s="81">
-        <f t="shared" ref="T191:AA193" si="111">IF(S183=0,
+        <f t="shared" ref="T191:AA193" si="113">IF(S183=0,
 IF(T183=0,0,IF(T183&gt;0,1,-1)),
 (T183-S183)/ABS(S183)
 )</f>
         <v>1</v>
       </c>
       <c r="U191" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>9.5254640085053743E-2</v>
       </c>
       <c r="V191" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.10595303806061529</v>
       </c>
       <c r="W191" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>9.5630374547519742E-2</v>
       </c>
       <c r="X191" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.10310125820081995</v>
       </c>
       <c r="Y191" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>8.9297411215219433E-2</v>
       </c>
       <c r="Z191" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>5.5753820411257961E-2</v>
       </c>
       <c r="AA191" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>3.5586042940987099E-2</v>
       </c>
       <c r="AC191" s="49"/>
@@ -35009,55 +35121,55 @@
         <v>383</v>
       </c>
       <c r="M192" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>1</v>
       </c>
       <c r="N192" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>0.161813978857692</v>
       </c>
       <c r="O192" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>0.11461849723905122</v>
       </c>
       <c r="P192" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>0.10126759998395443</v>
       </c>
       <c r="Q192" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>0.45200065565410602</v>
       </c>
       <c r="T192" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>1</v>
       </c>
       <c r="U192" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>8.6513802986875846E-2</v>
       </c>
       <c r="V192" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>-7.8444984380423455E-3</v>
       </c>
       <c r="W192" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.25118947663028268</v>
       </c>
       <c r="X192" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.15216418745106811</v>
       </c>
       <c r="Y192" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>2.019123428626899E-2</v>
       </c>
       <c r="Z192" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>-3.796565012607641E-2</v>
       </c>
       <c r="AA192" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>1.9435240591464318E-2</v>
       </c>
       <c r="AC192" s="49"/>
@@ -35067,85 +35179,85 @@
         <v>384</v>
       </c>
       <c r="M193" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>1</v>
       </c>
       <c r="N193" s="81">
-        <f t="shared" ref="N193:N195" si="112">IF(M185=0,
+        <f t="shared" ref="N193:N195" si="114">IF(M185=0,
 IF(N185=0,0,IF(N185&gt;0,1,-1)),
 (N185-M185)/ABS(M185)
 )</f>
         <v>0.32687160353637762</v>
       </c>
       <c r="O193" s="81">
-        <f t="shared" ref="O193:O195" si="113">IF(N185=0,
+        <f t="shared" ref="O193:O195" si="115">IF(N185=0,
 IF(O185=0,0,IF(O185&gt;0,1,-1)),
 (O185-N185)/ABS(N185)
 )</f>
         <v>0.25961244574851766</v>
       </c>
       <c r="P193" s="81">
-        <f t="shared" ref="P193:P195" si="114">IF(O185=0,
+        <f t="shared" ref="P193:P195" si="116">IF(O185=0,
 IF(P185=0,0,IF(P185&gt;0,1,-1)),
 (P185-O185)/ABS(O185)
 )</f>
         <v>0.107444433660099</v>
       </c>
       <c r="Q193" s="81">
-        <f t="shared" ref="Q193:Q195" si="115">IF(P185=0,
+        <f t="shared" ref="Q193:Q195" si="117">IF(P185=0,
 IF(Q185=0,0,IF(Q185&gt;0,1,-1)),
 (Q185-P185)/ABS(P185)
 )</f>
         <v>-7.9623137598597724E-2</v>
       </c>
       <c r="T193" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>1</v>
       </c>
       <c r="U193" s="81">
-        <f t="shared" ref="U193:U195" si="116">IF(T185=0,
+        <f t="shared" ref="U193:U195" si="118">IF(T185=0,
 IF(U185=0,0,IF(U185&gt;0,1,-1)),
 (U185-T185)/ABS(T185)
 )</f>
         <v>6.9171807814544777E-3</v>
       </c>
       <c r="V193" s="81">
-        <f t="shared" ref="V193:V195" si="117">IF(U185=0,
+        <f t="shared" ref="V193:V195" si="119">IF(U185=0,
 IF(V185=0,0,IF(V185&gt;0,1,-1)),
 (V185-U185)/ABS(U185)
 )</f>
         <v>5.9691793538804307E-2</v>
       </c>
       <c r="W193" s="81">
-        <f t="shared" ref="W193:W195" si="118">IF(V185=0,
+        <f t="shared" ref="W193:W195" si="120">IF(V185=0,
 IF(W185=0,0,IF(W185&gt;0,1,-1)),
 (W185-V185)/ABS(V185)
 )</f>
         <v>5.0021901007446343E-2</v>
       </c>
       <c r="X193" s="81">
-        <f t="shared" ref="X193:X195" si="119">IF(W185=0,
+        <f t="shared" ref="X193:X195" si="121">IF(W185=0,
 IF(X185=0,0,IF(X185&gt;0,1,-1)),
 (X185-W185)/ABS(W185)
 )</f>
         <v>-0.15835140997830802</v>
       </c>
       <c r="Y193" s="81">
-        <f t="shared" ref="Y193:Y195" si="120">IF(X185=0,
+        <f t="shared" ref="Y193:Y195" si="122">IF(X185=0,
 IF(Y185=0,0,IF(Y185&gt;0,1,-1)),
 (Y185-X185)/ABS(X185)
 )</f>
         <v>-4.3517049960348927E-2</v>
       </c>
       <c r="Z193" s="81">
-        <f t="shared" ref="Z193:Z195" si="121">IF(Y185=0,
+        <f t="shared" ref="Z193:Z195" si="123">IF(Y185=0,
 IF(Z185=0,0,IF(Z185&gt;0,1,-1)),
 (Z185-Y185)/ABS(Y185)
 )</f>
         <v>6.5706290807337545E-2</v>
       </c>
       <c r="AA193" s="81">
-        <f t="shared" ref="AA193:AA195" si="122">IF(Z185=0,
+        <f t="shared" ref="AA193:AA195" si="124">IF(Z185=0,
 IF(AA185=0,0,IF(AA185&gt;0,1,-1)),
 (AA185-Z185)/ABS(Z185)
 )</f>
@@ -35158,61 +35270,61 @@
         <v>385</v>
       </c>
       <c r="M194" s="81">
-        <f t="shared" ref="M194:M195" si="123">IF(L186=0,
+        <f t="shared" ref="M194:M195" si="125">IF(L186=0,
 IF(M186=0,0,IF(M186&gt;0,1,-1)),
 (M186-L186)/ABS(L186)
 )</f>
         <v>1</v>
       </c>
       <c r="N194" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>1.6809833694866232</v>
       </c>
       <c r="O194" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>0.87027347753384754</v>
       </c>
       <c r="P194" s="81">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>0.11478672165662042</v>
       </c>
       <c r="Q194" s="81">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>4.7240835122758909E-2</v>
       </c>
       <c r="T194" s="81">
-        <f t="shared" ref="T194:T195" si="124">IF(S186=0,
+        <f t="shared" ref="T194:T195" si="126">IF(S186=0,
 IF(T186=0,0,IF(T186&gt;0,1,-1)),
 (T186-S186)/ABS(S186)
 )</f>
         <v>1</v>
       </c>
       <c r="U194" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>-7.5176886792452824E-2</v>
       </c>
       <c r="V194" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>-2.8583572415258739E-2</v>
       </c>
       <c r="W194" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>3.281557646029315E-2</v>
       </c>
       <c r="X194" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>0.10040245710654522</v>
       </c>
       <c r="Y194" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>6.7949951876804623E-2</v>
       </c>
       <c r="Z194" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.13923936553713051</v>
       </c>
       <c r="AA194" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>-0.11569469165532405</v>
       </c>
       <c r="AC194" s="49"/>
@@ -35222,55 +35334,55 @@
         <v>386</v>
       </c>
       <c r="M195" s="81">
+        <f t="shared" si="125"/>
+        <v>1</v>
+      </c>
+      <c r="N195" s="81">
+        <f t="shared" si="114"/>
+        <v>6.9113924050632916</v>
+      </c>
+      <c r="O195" s="81">
+        <f t="shared" si="115"/>
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="P195" s="81">
+        <f t="shared" si="116"/>
+        <v>0.89589442815249265</v>
+      </c>
+      <c r="Q195" s="81">
+        <f t="shared" si="117"/>
+        <v>0.49806651198762569</v>
+      </c>
+      <c r="T195" s="81">
+        <f t="shared" si="126"/>
+        <v>1</v>
+      </c>
+      <c r="U195" s="81">
+        <f t="shared" si="118"/>
+        <v>0.36013986013986016</v>
+      </c>
+      <c r="V195" s="81">
+        <f t="shared" si="119"/>
+        <v>-1.2853470437017995E-2</v>
+      </c>
+      <c r="W195" s="81">
+        <f t="shared" si="120"/>
+        <v>0.16145833333333334</v>
+      </c>
+      <c r="X195" s="81">
+        <f t="shared" si="121"/>
+        <v>0.13452914798206278</v>
+      </c>
+      <c r="Y195" s="81">
+        <f t="shared" si="122"/>
+        <v>-9.4861660079051377E-2</v>
+      </c>
+      <c r="Z195" s="81">
         <f t="shared" si="123"/>
-        <v>1</v>
-      </c>
-      <c r="N195" s="81">
-        <f t="shared" si="112"/>
-        <v>6.9113924050632916</v>
-      </c>
-      <c r="O195" s="81">
-        <f t="shared" si="113"/>
-        <v>9.1200000000000003E-2</v>
-      </c>
-      <c r="P195" s="81">
-        <f t="shared" si="114"/>
-        <v>0.89589442815249265</v>
-      </c>
-      <c r="Q195" s="81">
-        <f t="shared" si="115"/>
-        <v>0.49806651198762569</v>
-      </c>
-      <c r="T195" s="81">
+        <v>0.15065502183406113</v>
+      </c>
+      <c r="AA195" s="81">
         <f t="shared" si="124"/>
-        <v>1</v>
-      </c>
-      <c r="U195" s="81">
-        <f t="shared" si="116"/>
-        <v>0.36013986013986016</v>
-      </c>
-      <c r="V195" s="81">
-        <f t="shared" si="117"/>
-        <v>-1.2853470437017995E-2</v>
-      </c>
-      <c r="W195" s="81">
-        <f t="shared" si="118"/>
-        <v>0.16145833333333334</v>
-      </c>
-      <c r="X195" s="81">
-        <f t="shared" si="119"/>
-        <v>0.13452914798206278</v>
-      </c>
-      <c r="Y195" s="81">
-        <f t="shared" si="120"/>
-        <v>-9.4861660079051377E-2</v>
-      </c>
-      <c r="Z195" s="81">
-        <f t="shared" si="121"/>
-        <v>0.15065502183406113</v>
-      </c>
-      <c r="AA195" s="81">
-        <f t="shared" si="122"/>
         <v>0.29411764705882354</v>
       </c>
       <c r="AC195" s="49"/>
@@ -35623,7 +35735,7 @@
         <v>137800</v>
       </c>
       <c r="AC210" s="21">
-        <f t="shared" ref="AC210:AC212" si="125">AA210</f>
+        <f t="shared" ref="AC210:AC212" si="127">AA210</f>
         <v>137800</v>
       </c>
     </row>
@@ -35681,7 +35793,7 @@
         <v>12500</v>
       </c>
       <c r="AC211" s="21">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>12500</v>
       </c>
     </row>
@@ -35694,55 +35806,55 @@
         <v>38000</v>
       </c>
       <c r="N212" s="128">
-        <f t="shared" ref="N212:Q212" si="126">N210-N211</f>
+        <f t="shared" ref="N212:Q212" si="128">N210-N211</f>
         <v>56500</v>
       </c>
       <c r="O212" s="128">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>81800</v>
       </c>
       <c r="P212" s="128">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>107200</v>
       </c>
       <c r="Q212" s="128">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>120900</v>
       </c>
       <c r="T212" s="128">
-        <f t="shared" ref="T212" si="127">T210-T211</f>
+        <f t="shared" ref="T212" si="129">T210-T211</f>
         <v>95600</v>
       </c>
       <c r="U212" s="128">
-        <f t="shared" ref="U212" si="128">U210-U211</f>
+        <f t="shared" ref="U212" si="130">U210-U211</f>
         <v>104500</v>
       </c>
       <c r="V212" s="128">
-        <f t="shared" ref="V212" si="129">V210-V211</f>
+        <f t="shared" ref="V212" si="131">V210-V211</f>
         <v>107200</v>
       </c>
       <c r="W212" s="128">
-        <f t="shared" ref="W212" si="130">W210-W211</f>
+        <f t="shared" ref="W212" si="132">W210-W211</f>
         <v>119900</v>
       </c>
       <c r="X212" s="128">
-        <f t="shared" ref="X212" si="131">X210-X211</f>
+        <f t="shared" ref="X212" si="133">X210-X211</f>
         <v>117400</v>
       </c>
       <c r="Y212" s="128">
-        <f t="shared" ref="Y212" si="132">Y210-Y211</f>
+        <f t="shared" ref="Y212" si="134">Y210-Y211</f>
         <v>123800</v>
       </c>
       <c r="Z212" s="128">
-        <f t="shared" ref="Z212" si="133">Z210-Z211</f>
+        <f t="shared" ref="Z212" si="135">Z210-Z211</f>
         <v>120900</v>
       </c>
       <c r="AA212" s="128">
-        <f t="shared" ref="AA212" si="134">AA210-AA211</f>
+        <f t="shared" ref="AA212" si="136">AA210-AA211</f>
         <v>125300</v>
       </c>
       <c r="AC212" s="21">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>125300</v>
       </c>
     </row>
@@ -35755,55 +35867,55 @@
         <v>72.279200000000003</v>
       </c>
       <c r="N213" s="232">
-        <f t="shared" ref="N213:Q213" si="135">N183/N211</f>
+        <f t="shared" ref="N213:Q213" si="137">N183/N211</f>
         <v>65.120714285714286</v>
       </c>
       <c r="O213" s="232">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>61.315757575757573</v>
       </c>
       <c r="P213" s="232">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>63.950631578947366</v>
       </c>
       <c r="Q213" s="232">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>71.593606557377043</v>
       </c>
       <c r="T213" s="232">
-        <f t="shared" ref="T213:AC213" si="136">T183/T211</f>
+        <f t="shared" ref="T213:AC213" si="138">T183/T211</f>
         <v>17.988624999999999</v>
       </c>
       <c r="U213" s="232">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>18.327558139534883</v>
       </c>
       <c r="V213" s="232">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>18.349157894736841</v>
       </c>
       <c r="W213" s="232">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>18.542427184466021</v>
       </c>
       <c r="X213" s="232">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>19.328256880733946</v>
       </c>
       <c r="Y213" s="232">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>19.955739130434782</v>
       </c>
       <c r="Z213" s="232">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>19.859508196721311</v>
       </c>
       <c r="AA213" s="232">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>20.07264</v>
       </c>
       <c r="AC213" s="232">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>74.669039999999995</v>
       </c>
     </row>
@@ -35816,51 +35928,51 @@
         <v>0.23703703703703705</v>
       </c>
       <c r="N214" s="74">
-        <f t="shared" ref="N214:Q214" si="137">N209/N210</f>
+        <f t="shared" ref="N214:Q214" si="139">N209/N210</f>
         <v>0.26853377265238881</v>
       </c>
       <c r="O214" s="74">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>0.30429864253393663</v>
       </c>
       <c r="P214" s="74">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>0.34704370179948585</v>
       </c>
       <c r="Q214" s="74">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>0.3959429000751315</v>
       </c>
       <c r="T214" s="74">
-        <f t="shared" ref="T214:AA214" si="138">T209/T210</f>
+        <f t="shared" ref="T214:AA214" si="140">T209/T210</f>
         <v>0.32915057915057916</v>
       </c>
       <c r="U214" s="74">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>0.32891246684350134</v>
       </c>
       <c r="V214" s="74">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>0.34704370179948585</v>
       </c>
       <c r="W214" s="74">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>0.3579109062980031</v>
       </c>
       <c r="X214" s="74">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>0.37178487918939984</v>
       </c>
       <c r="Y214" s="74">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>0.37324464153732445</v>
       </c>
       <c r="Z214" s="74">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>0.3959429000751315</v>
       </c>
       <c r="AA214" s="74">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>0.41001451378809867</v>
       </c>
       <c r="AC214" s="74">
@@ -35877,51 +35989,51 @@
         <v>6.1728395061728392E-2</v>
       </c>
       <c r="N215" s="74">
-        <f t="shared" ref="N215:Q215" si="139">N211/N210</f>
+        <f t="shared" ref="N215:Q215" si="141">N211/N210</f>
         <v>6.919275123558484E-2</v>
       </c>
       <c r="O215" s="74">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>7.4660633484162894E-2</v>
       </c>
       <c r="P215" s="74">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>8.1405312767780638E-2</v>
       </c>
       <c r="Q215" s="74">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>9.1660405709992482E-2</v>
       </c>
       <c r="T215" s="74">
-        <f t="shared" ref="T215:AA215" si="140">T211/T210</f>
+        <f t="shared" ref="T215:AA215" si="142">T211/T210</f>
         <v>7.7220077220077218E-2</v>
       </c>
       <c r="U215" s="74">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>7.6038903625110524E-2</v>
       </c>
       <c r="V215" s="74">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>8.1405312767780638E-2</v>
       </c>
       <c r="W215" s="74">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>7.9109062980030717E-2</v>
       </c>
       <c r="X215" s="74">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>8.4957131722525336E-2</v>
       </c>
       <c r="Y215" s="74">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>8.4996304508499626E-2</v>
       </c>
       <c r="Z215" s="74">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>9.1660405709992482E-2</v>
       </c>
       <c r="AA215" s="74">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>9.071117561683599E-2</v>
       </c>
       <c r="AC215" s="74">
@@ -35938,55 +36050,55 @@
         <v>1.0131842105263158</v>
       </c>
       <c r="N216" s="65">
-        <f t="shared" ref="N216:Q216" si="141">N184/N212</f>
+        <f t="shared" ref="N216:Q216" si="143">N184/N212</f>
         <v>0.79169911504424784</v>
       </c>
       <c r="O216" s="65">
-        <f t="shared" si="141"/>
+        <f t="shared" si="143"/>
         <v>0.60951100244498779</v>
       </c>
       <c r="P216" s="65">
-        <f t="shared" si="141"/>
+        <f t="shared" si="143"/>
         <v>0.51219216417910451</v>
       </c>
       <c r="Q216" s="65">
-        <f t="shared" si="141"/>
+        <f t="shared" si="143"/>
         <v>0.65942928039702231</v>
       </c>
       <c r="T216" s="65">
-        <f t="shared" ref="T216:AC216" si="142">T184/T212</f>
+        <f t="shared" ref="T216:AC216" si="144">T184/T212</f>
         <v>0.13868200836820083</v>
       </c>
       <c r="U216" s="65">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>0.13784688995215311</v>
       </c>
       <c r="V216" s="65">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>0.13332089552238807</v>
       </c>
       <c r="W216" s="65">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>0.14914095079232695</v>
       </c>
       <c r="X216" s="65">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>0.17549403747870529</v>
       </c>
       <c r="Y216" s="65">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>0.16978190630048465</v>
       </c>
       <c r="Z216" s="65">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>0.1672539288668321</v>
       </c>
       <c r="AA216" s="65">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>0.1645171588188348</v>
       </c>
       <c r="AC216" s="65">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>0.65807661612130885</v>
       </c>
     </row>
@@ -35999,55 +36111,55 @@
         <v>0.72031250000000002</v>
       </c>
       <c r="N217" s="74">
-        <f t="shared" ref="N217:Q217" si="143">N186/N209</f>
+        <f t="shared" ref="N217:Q217" si="145">N186/N209</f>
         <v>1.1373619631901841</v>
       </c>
       <c r="O217" s="74">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>1.2889591078066915</v>
       </c>
       <c r="P217" s="74">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>0.95439506172839506</v>
       </c>
       <c r="Q217" s="74">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>0.76810246679316885</v>
       </c>
       <c r="T217" s="74">
-        <f t="shared" ref="T217:AC217" si="144">T186/T209</f>
+        <f t="shared" ref="T217:AC217" si="146">T186/T209</f>
         <v>0.29841642228739002</v>
       </c>
       <c r="U217" s="74">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0.25298387096774194</v>
       </c>
       <c r="V217" s="74">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0.2257283950617284</v>
       </c>
       <c r="W217" s="74">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0.20261802575107296</v>
       </c>
       <c r="X217" s="74">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0.21781970649895177</v>
       </c>
       <c r="Y217" s="74">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0.21972277227722772</v>
       </c>
       <c r="Z217" s="74">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0.18123339658444024</v>
       </c>
       <c r="AA217" s="74">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0.14948672566371682</v>
       </c>
       <c r="AC217" s="74">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0.69881415929203539</v>
       </c>
     </row>
@@ -36121,15 +36233,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="259" t="s">
         <v>242</v>
       </c>
-      <c r="C4" s="254"/>
-      <c r="E4" s="254" t="s">
+      <c r="C4" s="259"/>
+      <c r="E4" s="259" t="s">
         <v>249</v>
       </c>
-      <c r="F4" s="254"/>
-      <c r="G4" s="254"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36137,7 +36249,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>124.76</v>
+        <v>134.81</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -36153,7 +36265,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>6086666.1200000001</v>
+        <v>6576975.4699999997</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -36173,7 +36285,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>4694845.12</v>
+        <v>5185154.47</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -36193,7 +36305,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>36.795880819513265</v>
+        <v>39.759960670716445</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>252</v>
@@ -36213,7 +36325,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>5.5477870892931662</v>
+        <v>5.994687219522377</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>253</v>
@@ -36233,7 +36345,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>4.1766726830123497</v>
+        <v>4.5131231516262815</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36253,7 +36365,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.2726515976785864</v>
+        <v>4.7188688794180624</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36262,18 +36374,18 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>29.998435301559716</v>
+        <v>33.131342338485524</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="254" t="s">
+      <c r="B15" s="259" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="254"/>
-      <c r="E15" s="254" t="s">
+      <c r="C15" s="259"/>
+      <c r="E15" s="259" t="s">
         <v>255</v>
       </c>
-      <c r="F15" s="254"/>
+      <c r="F15" s="259"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -36324,14 +36436,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="254" t="s">
+      <c r="B21" s="259" t="s">
         <v>254</v>
       </c>
-      <c r="C21" s="254"/>
-      <c r="E21" s="254" t="s">
+      <c r="C21" s="259"/>
+      <c r="E21" s="259" t="s">
         <v>258</v>
       </c>
-      <c r="F21" s="254"/>
+      <c r="F21" s="259"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -36400,14 +36512,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="254" t="s">
+      <c r="B29" s="259" t="s">
         <v>259</v>
       </c>
-      <c r="C29" s="254"/>
-      <c r="E29" s="254" t="s">
+      <c r="C29" s="259"/>
+      <c r="E29" s="259" t="s">
         <v>265</v>
       </c>
-      <c r="F29" s="254"/>
+      <c r="F29" s="259"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36483,14 +36595,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="254" t="s">
+      <c r="B37" s="259" t="s">
         <v>277</v>
       </c>
-      <c r="C37" s="254"/>
-      <c r="E37" s="254" t="s">
+      <c r="C37" s="259"/>
+      <c r="E37" s="259" t="s">
         <v>280</v>
       </c>
-      <c r="F37" s="254"/>
+      <c r="F37" s="259"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -36498,7 +36610,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.7176955075625987E-2</v>
+        <v>2.5150930311068156E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>279</v>
@@ -36514,7 +36626,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC157</f>
-        <v>4.3395184620378023E-2</v>
+        <v>4.0160101129280937E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>281</v>
@@ -36546,7 +36658,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>3.9974264269320558E-3</v>
+        <v>3.6994208220758351E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36555,18 +36667,18 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>3.9974264269320558E-3</v>
+        <v>3.6994208220758351E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="254" t="s">
+      <c r="B45" s="259" t="s">
         <v>288</v>
       </c>
-      <c r="C45" s="254"/>
-      <c r="E45" s="254" t="s">
+      <c r="C45" s="259"/>
+      <c r="E45" s="259" t="s">
         <v>294</v>
       </c>
-      <c r="F45" s="254"/>
+      <c r="F45" s="259"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -36599,18 +36711,18 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC172</f>
-        <v>0.2286672165944269</v>
+        <v>0.21162022062399452</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="254" t="s">
+      <c r="B51" s="259" t="s">
         <v>291</v>
       </c>
-      <c r="C51" s="254"/>
-      <c r="E51" s="254" t="s">
+      <c r="C51" s="259"/>
+      <c r="E51" s="259" t="s">
         <v>312</v>
       </c>
-      <c r="F51" s="254"/>
+      <c r="F51" s="259"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36778,7 +36890,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>124.76</v>
+        <v>134.81</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36807,7 +36919,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC149</f>
-        <v>6086666.1200000001</v>
+        <v>6576975.4699999997</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36836,7 +36948,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>4694845.12</v>
+        <v>5185154.47</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36865,7 +36977,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC146</f>
-        <v>36.795880819513265</v>
+        <v>39.759960670716445</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36894,7 +37006,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC147</f>
-        <v>5.5477870892931662</v>
+        <v>5.994687219522377</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36923,7 +37035,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC148</f>
-        <v>4.1766726830123497</v>
+        <v>4.5131231516262815</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36952,7 +37064,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.2726515976785864</v>
+        <v>4.7188688794180624</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36981,7 +37093,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>29.998435301559716</v>
+        <v>33.131342338485524</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37754,7 +37866,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC158</f>
-        <v>2.7176955075625987E-2</v>
+        <v>2.5150930311068156E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37783,7 +37895,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC157</f>
-        <v>4.3395184620378023E-2</v>
+        <v>4.0160101129280937E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37841,7 +37953,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC160</f>
-        <v>3.9974264269320558E-3</v>
+        <v>3.6994208220758351E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37870,7 +37982,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>3.9974264269320558E-3</v>
+        <v>3.6994208220758351E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38106,7 +38218,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC172</f>
-        <v>0.2286672165944269</v>
+        <v>0.21162022062399452</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38649,14 +38761,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="257" t="s">
+      <c r="C3" s="262" t="s">
         <v>322</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="F3" s="259" t="s">
+      <c r="D3" s="263"/>
+      <c r="F3" s="264" t="s">
         <v>323</v>
       </c>
-      <c r="G3" s="258"/>
+      <c r="G3" s="263"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38723,19 +38835,19 @@
       <c r="B7" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C7" s="255">
+      <c r="C7" s="260">
         <f>Statement!AA89</f>
         <v>3.2166947127281985E-2</v>
       </c>
-      <c r="D7" s="256"/>
-      <c r="F7" s="255">
+      <c r="D7" s="261"/>
+      <c r="F7" s="260">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.26533415964948015</v>
       </c>
-      <c r="G7" s="256"/>
+      <c r="G7" s="261"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -38762,19 +38874,19 @@
       <c r="B9" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C9" s="255">
+      <c r="C9" s="260">
         <f>Statement!AA90</f>
         <v>2.4312004052000676E-2</v>
       </c>
-      <c r="D9" s="256"/>
-      <c r="F9" s="255">
+      <c r="D9" s="261"/>
+      <c r="F9" s="260">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.18341410716161269</v>
       </c>
-      <c r="G9" s="256"/>
+      <c r="G9" s="261"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -38801,19 +38913,19 @@
       <c r="B11" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C11" s="255">
+      <c r="C11" s="260">
         <f>Statement!AA91</f>
         <v>3.5104848228727975E-2</v>
       </c>
-      <c r="D11" s="256"/>
-      <c r="F11" s="255">
+      <c r="D11" s="261"/>
+      <c r="F11" s="260">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.29860569422776911</v>
       </c>
-      <c r="G11" s="256"/>
+      <c r="G11" s="261"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -38840,19 +38952,19 @@
       <c r="B13" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C13" s="255">
+      <c r="C13" s="260">
         <f>Statement!AA95</f>
         <v>3.7890588923436871E-2</v>
       </c>
-      <c r="D13" s="256"/>
-      <c r="F13" s="255">
+      <c r="D13" s="261"/>
+      <c r="F13" s="260">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.19976228096397206</v>
       </c>
-      <c r="G13" s="256"/>
+      <c r="G13" s="261"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -38879,19 +38991,19 @@
       <c r="B15" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C15" s="255">
+      <c r="C15" s="260">
         <f>Statement!AA96</f>
         <v>2.4692778570442307E-2</v>
       </c>
-      <c r="D15" s="256"/>
-      <c r="F15" s="255">
+      <c r="D15" s="261"/>
+      <c r="F15" s="260">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.88721708909044672</v>
       </c>
-      <c r="G15" s="256"/>
+      <c r="G15" s="261"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -38918,19 +39030,19 @@
       <c r="B17" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C17" s="255">
+      <c r="C17" s="260">
         <f>Statement!AA98</f>
         <v>3.5896458025456456E-2</v>
       </c>
-      <c r="D17" s="256"/>
-      <c r="F17" s="255">
+      <c r="D17" s="261"/>
+      <c r="F17" s="260">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.23694321901238083</v>
       </c>
-      <c r="G17" s="256"/>
+      <c r="G17" s="261"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -38957,22 +39069,22 @@
       <c r="B19" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C19" s="255">
+      <c r="C19" s="260">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3895378744883068E-2</v>
       </c>
-      <c r="D19" s="256"/>
-      <c r="F19" s="255">
+      <c r="D19" s="261"/>
+      <c r="F19" s="260">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.0103717755737469E-2</v>
       </c>
-      <c r="G19" s="256"/>
+      <c r="G19" s="261"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -38999,22 +39111,22 @@
       <c r="B21" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C21" s="255">
+      <c r="C21" s="260">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.4953901558794477E-2</v>
       </c>
-      <c r="D21" s="256"/>
-      <c r="F21" s="255">
+      <c r="D21" s="261"/>
+      <c r="F21" s="260">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.23611111111111119</v>
       </c>
-      <c r="G21" s="256"/>
+      <c r="G21" s="261"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39063,22 +39175,22 @@
       <c r="B25" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C25" s="255">
+      <c r="C25" s="260">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>3.5586042940987099E-2</v>
       </c>
-      <c r="D25" s="256"/>
-      <c r="F25" s="255">
+      <c r="D25" s="261"/>
+      <c r="F25" s="260">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.3137438673836439</v>
       </c>
-      <c r="G25" s="256"/>
+      <c r="G25" s="261"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39106,22 +39218,22 @@
       <c r="B27" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C27" s="255">
+      <c r="C27" s="260">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>1.9435240591464318E-2</v>
       </c>
-      <c r="D27" s="256"/>
-      <c r="F27" s="255">
+      <c r="D27" s="261"/>
+      <c r="F27" s="260">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.15277933117100995</v>
       </c>
-      <c r="G27" s="256"/>
+      <c r="G27" s="261"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39149,22 +39261,22 @@
       <c r="B29" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C29" s="255">
+      <c r="C29" s="260">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.10055431294369348</v>
       </c>
-      <c r="D29" s="256"/>
-      <c r="F29" s="255">
+      <c r="D29" s="261"/>
+      <c r="F29" s="260">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-5.581511763724345E-2</v>
       </c>
-      <c r="G29" s="256"/>
+      <c r="G29" s="261"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -39192,22 +39304,22 @@
       <c r="B31" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C31" s="255">
+      <c r="C31" s="260">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.11569469165532405</v>
       </c>
-      <c r="D31" s="256"/>
-      <c r="F31" s="255">
+      <c r="D31" s="261"/>
+      <c r="F31" s="260">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-0.10548612582080068</v>
       </c>
-      <c r="G31" s="256"/>
+      <c r="G31" s="261"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -39235,22 +39347,22 @@
       <c r="B33" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C33" s="255">
+      <c r="C33" s="260">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.29411764705882354</v>
       </c>
-      <c r="D33" s="256"/>
-      <c r="F33" s="255">
+      <c r="D33" s="261"/>
+      <c r="F33" s="260">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.52914798206278024</v>
       </c>
-      <c r="G33" s="256"/>
+      <c r="G33" s="261"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -39299,22 +39411,22 @@
       <c r="B37" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C37" s="255">
+      <c r="C37" s="260">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>7.2106261859582549E-2</v>
       </c>
-      <c r="D37" s="256"/>
-      <c r="F37" s="255">
+      <c r="D37" s="261"/>
+      <c r="F37" s="260">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.21244635193133046</v>
       </c>
-      <c r="G37" s="256"/>
+      <c r="G37" s="261"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="str">
@@ -39342,22 +39454,22 @@
       <c r="B39" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C39" s="255">
+      <c r="C39" s="260">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>3.5311795642374154E-2</v>
       </c>
-      <c r="D39" s="256"/>
-      <c r="F39" s="255">
+      <c r="D39" s="261"/>
+      <c r="F39" s="260">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>5.8371735791090631E-2</v>
       </c>
-      <c r="G39" s="256"/>
+      <c r="G39" s="261"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="str">
@@ -39385,22 +39497,22 @@
       <c r="B41" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C41" s="255">
+      <c r="C41" s="260">
         <f>IF(C40=0,
 IF(D40=0,0,IF(D40&gt;0,1,-1)),
 (D40-C40)/ABS(C40)
 )</f>
         <v>2.4590163934426229E-2</v>
       </c>
-      <c r="D41" s="256"/>
-      <c r="F41" s="255">
+      <c r="D41" s="261"/>
+      <c r="F41" s="260">
         <f>IF(F40=0,
 IF(G40=0,0,IF(G40&gt;0,1,-1)),
 (G40-F40)/ABS(F40)
 )</f>
         <v>0.21359223300970873</v>
       </c>
-      <c r="G41" s="256"/>
+      <c r="G41" s="261"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="str">
@@ -39428,22 +39540,22 @@
       <c r="B43" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C43" s="255">
+      <c r="C43" s="260">
         <f>IF(C42=0,
 IF(D42=0,0,IF(D42&gt;0,1,-1)),
 (D42-C42)/ABS(C42)
 )</f>
         <v>3.6393713813068655E-2</v>
       </c>
-      <c r="D43" s="256"/>
-      <c r="F43" s="255">
+      <c r="D43" s="261"/>
+      <c r="F43" s="260">
         <f>IF(F42=0,
 IF(G42=0,0,IF(G42&gt;0,1,-1)),
 (G42-F42)/ABS(F42)
 )</f>
         <v>4.5037531276063386E-2</v>
       </c>
-      <c r="G43" s="256"/>
+      <c r="G43" s="261"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="str">
@@ -39471,22 +39583,22 @@
       <c r="B45" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C45" s="255">
+      <c r="C45" s="260">
         <f>IF(C44=0,
 IF(D44=0,0,IF(D44&gt;0,1,-1)),
 (D44-C44)/ABS(C44)
 )</f>
         <v>1.0731977910403413E-2</v>
       </c>
-      <c r="D45" s="256"/>
-      <c r="F45" s="255">
+      <c r="D45" s="261"/>
+      <c r="F45" s="260">
         <f>IF(F44=0,
 IF(G44=0,0,IF(G44&gt;0,1,-1)),
 (G44-F44)/ABS(F44)
 )</f>
         <v>8.2524946724122472E-2</v>
       </c>
-      <c r="G45" s="256"/>
+      <c r="G45" s="261"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="str">
@@ -39514,22 +39626,22 @@
       <c r="B47" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C47" s="255">
+      <c r="C47" s="260">
         <f>IF(C46=0,
 IF(D46=0,0,IF(D46&gt;0,1,-1)),
 (D46-C46)/ABS(C46)
 )</f>
         <v>3.5539502565387668E-2</v>
       </c>
-      <c r="D47" s="256"/>
-      <c r="F47" s="255">
+      <c r="D47" s="261"/>
+      <c r="F47" s="260">
         <f>IF(F46=0,
 IF(G46=0,0,IF(G46&gt;0,1,-1)),
 (G46-F46)/ABS(F46)
 )</f>
         <v>0.14557703208606101</v>
       </c>
-      <c r="G47" s="256"/>
+      <c r="G47" s="261"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="str">
@@ -39557,22 +39669,22 @@
       <c r="B49" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C49" s="255">
+      <c r="C49" s="260">
         <f>IF(C48=0,
 IF(D48=0,0,IF(D48&gt;0,1,-1)),
 (D48-C48)/ABS(C48)
 )</f>
         <v>-1.0355944704846643E-2</v>
       </c>
-      <c r="D49" s="256"/>
-      <c r="F49" s="255">
+      <c r="D49" s="261"/>
+      <c r="F49" s="260">
         <f>IF(F48=0,
 IF(G48=0,0,IF(G48&gt;0,1,-1)),
 (G48-F48)/ABS(F48)
 )</f>
         <v>0.14665971507883949</v>
       </c>
-      <c r="G49" s="256"/>
+      <c r="G49" s="261"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="20" t="str">
@@ -39600,22 +39712,22 @@
       <c r="B51" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C51" s="255">
+      <c r="C51" s="260">
         <f>IF(C50=0,
 IF(D50=0,0,IF(D50&gt;0,1,-1)),
 (D50-C50)/ABS(C50)
 )</f>
         <v>-1.63629641858896E-2</v>
       </c>
-      <c r="D51" s="256"/>
-      <c r="F51" s="255">
+      <c r="D51" s="261"/>
+      <c r="F51" s="260">
         <f>IF(F50=0,
 IF(G50=0,0,IF(G50&gt;0,1,-1)),
 (G50-F50)/ABS(F50)
 )</f>
         <v>0.10309849806387941</v>
       </c>
-      <c r="G51" s="256"/>
+      <c r="G51" s="261"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="str">
@@ -39643,22 +39755,22 @@
       <c r="B53" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C53" s="255">
+      <c r="C53" s="260">
         <f>IF(C52=0,
 IF(D52=0,0,IF(D52&gt;0,1,-1)),
 (D52-C52)/ABS(C52)
 )</f>
         <v>-0.17517009292452351</v>
       </c>
-      <c r="D53" s="256"/>
-      <c r="F53" s="255">
+      <c r="D53" s="261"/>
+      <c r="F53" s="260">
         <f>IF(F52=0,
 IF(G52=0,0,IF(G52&gt;0,1,-1)),
 (G52-F52)/ABS(F52)
 )</f>
         <v>-0.26222395510175772</v>
       </c>
-      <c r="G53" s="256"/>
+      <c r="G53" s="261"/>
     </row>
   </sheetData>
   <mergeCells count="46">
